--- a/devis_2027/Devis_Enedril_2027.xlsx
+++ b/devis_2027/Devis_Enedril_2027.xlsx
@@ -12,12 +12,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 Options" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 Devis" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5 Tool List" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listes" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Textes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6 Page de garde" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Textes" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'4 Devis'!$A$1:$L$67</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'5 Tool List'!$A$1:$R$75</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'6 Page de garde'!$A$1:$F$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -27,8 +29,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="9">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="0;-0;;@"/>
-    <numFmt numFmtId="166" formatCode="#,##0;-#,##0;;@"/>
+    <numFmt numFmtId="165" formatCode="#,##0;-#,##0;;@"/>
+    <numFmt numFmtId="166" formatCode="0;-0;;@"/>
     <numFmt numFmtId="167" formatCode="#,##0.00 &quot;€&quot;"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
     <numFmt numFmtId="169" formatCode="dd/mm"/>
@@ -36,7 +38,7 @@
     <numFmt numFmtId="171" formatCode="#,##0.0 &quot;kg&quot;"/>
     <numFmt numFmtId="172" formatCode="0.000 &quot;m³&quot;"/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="45">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -104,6 +106,12 @@
       <name val="Calibri"/>
       <color rgb="0051647A"/>
       <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="0051647A"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -238,6 +246,11 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="000B1B2E"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="00B8C4D2"/>
       <sz val="8"/>
     </font>
@@ -254,8 +267,32 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0000AEEF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000A4FA0"/>
+      <sz val="26"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0008203F"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="000B1B2E"/>
-      <sz val="9.5"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000B1B2E"/>
+      <sz val="11.5"/>
     </font>
   </fonts>
   <fills count="9">
@@ -387,7 +424,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -418,14 +455,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -437,38 +477,41 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="4" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="167" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -476,10 +519,10 @@
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -494,43 +537,43 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="4" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf numFmtId="167" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -540,43 +583,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="168" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="38" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="38" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="1" fontId="10" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -591,7 +634,7 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -609,8 +652,45 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -780,6 +860,36 @@
       <rowOff>0</rowOff>
     </from>
     <ext cx="1333500" cy="304800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2000250" cy="704850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -1090,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1424,23 +1534,123 @@
       </c>
     </row>
     <row r="27"/>
-    <row r="28">
-      <c r="B28" s="12" t="inlineStr">
+    <row r="28" ht="20" customHeight="1">
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>DOSSIER COMMERCIAL (page de garde et pièces jointes)</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="n"/>
+      <c r="D28" s="1" t="n"/>
+      <c r="E28" s="1" t="n"/>
+      <c r="F28" s="1" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Type de prestation</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="n"/>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Joindre : présentation de l’entreprise</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Périmètre du contrat</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="n"/>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>Joindre : nos engagements (politique QHSE et RSE)</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Type de proposition</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Technique et commerciale</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>Joindre : certificat ISO 9001</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Titre du projet (sinon : puits / chantier)</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="n"/>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>Joindre : proposition technique</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>Proposition commerciale (le devis)</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>toujours jointe</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="13" t="inlineStr">
         <is>
           <t>➜ Étape suivante : onglet « 2 Matériel »</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B28:F28"/>
     <mergeCell ref="E26:F27"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="E17:F17"/>
   </mergeCells>
-  <dataValidations count="9">
+  <dataValidations count="15">
     <dataValidation sqref="F6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="warning">
       <formula1>=Listes!$A$2:$A$12</formula1>
     </dataValidation>
@@ -1468,6 +1678,24 @@
     <dataValidation sqref="F25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="stop">
       <formula1>=Listes!$G$2:$G$12</formula1>
     </dataValidation>
+    <dataValidation sqref="C29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="warning">
+      <formula1>=Listes!$R$2:$R$12</formula1>
+    </dataValidation>
+    <dataValidation sqref="C31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="stop">
+      <formula1>=Listes!$S$2:$S$12</formula1>
+    </dataValidation>
+    <dataValidation sqref="F29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="stop">
+      <formula1>=Listes!$G$2:$G$12</formula1>
+    </dataValidation>
+    <dataValidation sqref="F30" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="stop">
+      <formula1>=Listes!$G$2:$G$12</formula1>
+    </dataValidation>
+    <dataValidation sqref="F31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="stop">
+      <formula1>=Listes!$G$2:$G$12</formula1>
+    </dataValidation>
+    <dataValidation sqref="F32" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="stop">
+      <formula1>=Listes!$G$2:$G$12</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -1485,7 +1713,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -1495,7 +1723,7 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
     <col width="8" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
@@ -1561,85 +1789,86 @@
       <c r="O3" s="4" t="n"/>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Réf PL / instructions</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Note pour la tool list</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>Qté</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>Stand-by (S)
 € / jour</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t>Opérations (O)
 € / jour</t>
         </is>
       </c>
-      <c r="G5" s="13" t="inlineStr">
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>UC
 € / item</t>
         </is>
       </c>
-      <c r="H5" s="13" t="inlineStr">
+      <c r="H5" s="14" t="inlineStr">
         <is>
           <t>LIH / DBR
 € / item</t>
         </is>
       </c>
-      <c r="I5" s="13" t="inlineStr">
+      <c r="I5" s="14" t="inlineStr">
         <is>
           <t>Inspection
 € / item</t>
         </is>
       </c>
-      <c r="J5" s="13" t="inlineStr">
+      <c r="J5" s="14" t="inlineStr">
         <is>
           <t>Restocking
 €</t>
         </is>
       </c>
-      <c r="K5" s="13" t="inlineStr">
+      <c r="K5" s="14" t="inlineStr">
         <is>
           <t>Inclus au
 forfait ?</t>
         </is>
       </c>
-      <c r="L5" s="13" t="inlineStr">
-        <is>
-          <t>Note technique (sur la tool list)</t>
-        </is>
-      </c>
-      <c r="M5" s="14" t="inlineStr">
+      <c r="L5" s="15" t="inlineStr">
+        <is>
+          <t>Forfait
+€ (calc.)</t>
+        </is>
+      </c>
+      <c r="M5" s="15" t="inlineStr">
         <is>
           <t>Qté
 retenue</t>
         </is>
       </c>
-      <c r="N5" s="14" t="inlineStr">
+      <c r="N5" s="15" t="inlineStr">
         <is>
           <t>Cumul</t>
         </is>
       </c>
-      <c r="O5" s="14" t="inlineStr">
+      <c r="O5" s="15" t="inlineStr">
         <is>
           <t>Estim.
 € (calc.)</t>
@@ -1647,711 +1876,783 @@
       </c>
     </row>
     <row r="6" ht="21" customHeight="1">
-      <c r="A6" s="15">
+      <c r="A6" s="16">
         <f>IF(M6&gt;0,COUNTIF(M$6:M6,"&gt;0"),"")</f>
         <v/>
       </c>
       <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n"/>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="17" t="n"/>
-      <c r="F6" s="17" t="n"/>
-      <c r="G6" s="17" t="n"/>
-      <c r="H6" s="17" t="n"/>
-      <c r="I6" s="17" t="n"/>
-      <c r="J6" s="17" t="n"/>
-      <c r="K6" s="18" t="n"/>
-      <c r="L6" s="7" t="n"/>
-      <c r="M6" s="19">
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="18" t="n"/>
+      <c r="F6" s="18" t="n"/>
+      <c r="G6" s="18" t="n"/>
+      <c r="H6" s="18" t="n"/>
+      <c r="I6" s="18" t="n"/>
+      <c r="J6" s="18" t="n"/>
+      <c r="K6" s="19" t="n"/>
+      <c r="L6" s="20">
+        <f>IF(AND(M6&gt;0,K6="Oui"),M6*(N(E6)*N('3 Options'!$C$16)+N(F6)*N('3 Options'!$C$17)+N(G6)),0)</f>
+        <v/>
+      </c>
+      <c r="M6" s="21">
         <f>IF($C6="",0,IF(N($D6)&gt;0,INT($D6),1))</f>
         <v/>
       </c>
-      <c r="N6" s="20">
+      <c r="N6" s="22">
         <f>SUM(M$6:M6)</f>
         <v/>
       </c>
-      <c r="O6" s="21">
+      <c r="O6" s="20">
         <f>IF(OR(M6=0,AND(K6="Oui",'3 Options'!$C$14="Oui")),0,M6*(N(E6)*N('1 Affaire'!$C$25)+N(F6)*N('1 Affaire'!$C$26)+N(G6)))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="21" customHeight="1">
-      <c r="A7" s="15">
+      <c r="A7" s="16">
         <f>IF(M7&gt;0,COUNTIF(M$6:M7,"&gt;0"),"")</f>
         <v/>
       </c>
       <c r="B7" s="7" t="n"/>
       <c r="C7" s="7" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="17" t="n"/>
-      <c r="F7" s="17" t="n"/>
-      <c r="G7" s="17" t="n"/>
-      <c r="H7" s="17" t="n"/>
-      <c r="I7" s="17" t="n"/>
-      <c r="J7" s="17" t="n"/>
-      <c r="K7" s="18" t="n"/>
-      <c r="L7" s="7" t="n"/>
-      <c r="M7" s="19">
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="18" t="n"/>
+      <c r="F7" s="18" t="n"/>
+      <c r="G7" s="18" t="n"/>
+      <c r="H7" s="18" t="n"/>
+      <c r="I7" s="18" t="n"/>
+      <c r="J7" s="18" t="n"/>
+      <c r="K7" s="19" t="n"/>
+      <c r="L7" s="20">
+        <f>IF(AND(M7&gt;0,K7="Oui"),M7*(N(E7)*N('3 Options'!$C$16)+N(F7)*N('3 Options'!$C$17)+N(G7)),0)</f>
+        <v/>
+      </c>
+      <c r="M7" s="21">
         <f>IF($C7="",0,IF(N($D7)&gt;0,INT($D7),1))</f>
         <v/>
       </c>
-      <c r="N7" s="20">
+      <c r="N7" s="22">
         <f>SUM(M$6:M7)</f>
         <v/>
       </c>
-      <c r="O7" s="21">
+      <c r="O7" s="20">
         <f>IF(OR(M7=0,AND(K7="Oui",'3 Options'!$C$14="Oui")),0,M7*(N(E7)*N('1 Affaire'!$C$25)+N(F7)*N('1 Affaire'!$C$26)+N(G7)))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="21" customHeight="1">
-      <c r="A8" s="15">
+      <c r="A8" s="16">
         <f>IF(M8&gt;0,COUNTIF(M$6:M8,"&gt;0"),"")</f>
         <v/>
       </c>
       <c r="B8" s="7" t="n"/>
       <c r="C8" s="7" t="n"/>
-      <c r="D8" s="16" t="n"/>
-      <c r="E8" s="17" t="n"/>
-      <c r="F8" s="17" t="n"/>
-      <c r="G8" s="17" t="n"/>
-      <c r="H8" s="17" t="n"/>
-      <c r="I8" s="17" t="n"/>
-      <c r="J8" s="17" t="n"/>
-      <c r="K8" s="18" t="n"/>
-      <c r="L8" s="7" t="n"/>
-      <c r="M8" s="19">
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="18" t="n"/>
+      <c r="F8" s="18" t="n"/>
+      <c r="G8" s="18" t="n"/>
+      <c r="H8" s="18" t="n"/>
+      <c r="I8" s="18" t="n"/>
+      <c r="J8" s="18" t="n"/>
+      <c r="K8" s="19" t="n"/>
+      <c r="L8" s="20">
+        <f>IF(AND(M8&gt;0,K8="Oui"),M8*(N(E8)*N('3 Options'!$C$16)+N(F8)*N('3 Options'!$C$17)+N(G8)),0)</f>
+        <v/>
+      </c>
+      <c r="M8" s="21">
         <f>IF($C8="",0,IF(N($D8)&gt;0,INT($D8),1))</f>
         <v/>
       </c>
-      <c r="N8" s="20">
+      <c r="N8" s="22">
         <f>SUM(M$6:M8)</f>
         <v/>
       </c>
-      <c r="O8" s="21">
+      <c r="O8" s="20">
         <f>IF(OR(M8=0,AND(K8="Oui",'3 Options'!$C$14="Oui")),0,M8*(N(E8)*N('1 Affaire'!$C$25)+N(F8)*N('1 Affaire'!$C$26)+N(G8)))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="21" customHeight="1">
-      <c r="A9" s="15">
+      <c r="A9" s="16">
         <f>IF(M9&gt;0,COUNTIF(M$6:M9,"&gt;0"),"")</f>
         <v/>
       </c>
       <c r="B9" s="7" t="n"/>
       <c r="C9" s="7" t="n"/>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="17" t="n"/>
-      <c r="F9" s="17" t="n"/>
-      <c r="G9" s="17" t="n"/>
-      <c r="H9" s="17" t="n"/>
-      <c r="I9" s="17" t="n"/>
-      <c r="J9" s="17" t="n"/>
-      <c r="K9" s="18" t="n"/>
-      <c r="L9" s="7" t="n"/>
-      <c r="M9" s="19">
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="18" t="n"/>
+      <c r="F9" s="18" t="n"/>
+      <c r="G9" s="18" t="n"/>
+      <c r="H9" s="18" t="n"/>
+      <c r="I9" s="18" t="n"/>
+      <c r="J9" s="18" t="n"/>
+      <c r="K9" s="19" t="n"/>
+      <c r="L9" s="20">
+        <f>IF(AND(M9&gt;0,K9="Oui"),M9*(N(E9)*N('3 Options'!$C$16)+N(F9)*N('3 Options'!$C$17)+N(G9)),0)</f>
+        <v/>
+      </c>
+      <c r="M9" s="21">
         <f>IF($C9="",0,IF(N($D9)&gt;0,INT($D9),1))</f>
         <v/>
       </c>
-      <c r="N9" s="20">
+      <c r="N9" s="22">
         <f>SUM(M$6:M9)</f>
         <v/>
       </c>
-      <c r="O9" s="21">
+      <c r="O9" s="20">
         <f>IF(OR(M9=0,AND(K9="Oui",'3 Options'!$C$14="Oui")),0,M9*(N(E9)*N('1 Affaire'!$C$25)+N(F9)*N('1 Affaire'!$C$26)+N(G9)))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="21" customHeight="1">
-      <c r="A10" s="15">
+      <c r="A10" s="16">
         <f>IF(M10&gt;0,COUNTIF(M$6:M10,"&gt;0"),"")</f>
         <v/>
       </c>
       <c r="B10" s="7" t="n"/>
       <c r="C10" s="7" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="17" t="n"/>
-      <c r="F10" s="17" t="n"/>
-      <c r="G10" s="17" t="n"/>
-      <c r="H10" s="17" t="n"/>
-      <c r="I10" s="17" t="n"/>
-      <c r="J10" s="17" t="n"/>
-      <c r="K10" s="18" t="n"/>
-      <c r="L10" s="7" t="n"/>
-      <c r="M10" s="19">
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="18" t="n"/>
+      <c r="F10" s="18" t="n"/>
+      <c r="G10" s="18" t="n"/>
+      <c r="H10" s="18" t="n"/>
+      <c r="I10" s="18" t="n"/>
+      <c r="J10" s="18" t="n"/>
+      <c r="K10" s="19" t="n"/>
+      <c r="L10" s="20">
+        <f>IF(AND(M10&gt;0,K10="Oui"),M10*(N(E10)*N('3 Options'!$C$16)+N(F10)*N('3 Options'!$C$17)+N(G10)),0)</f>
+        <v/>
+      </c>
+      <c r="M10" s="21">
         <f>IF($C10="",0,IF(N($D10)&gt;0,INT($D10),1))</f>
         <v/>
       </c>
-      <c r="N10" s="20">
+      <c r="N10" s="22">
         <f>SUM(M$6:M10)</f>
         <v/>
       </c>
-      <c r="O10" s="21">
+      <c r="O10" s="20">
         <f>IF(OR(M10=0,AND(K10="Oui",'3 Options'!$C$14="Oui")),0,M10*(N(E10)*N('1 Affaire'!$C$25)+N(F10)*N('1 Affaire'!$C$26)+N(G10)))</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="21" customHeight="1">
-      <c r="A11" s="15">
+      <c r="A11" s="16">
         <f>IF(M11&gt;0,COUNTIF(M$6:M11,"&gt;0"),"")</f>
         <v/>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
-      <c r="D11" s="16" t="n"/>
-      <c r="E11" s="17" t="n"/>
-      <c r="F11" s="17" t="n"/>
-      <c r="G11" s="17" t="n"/>
-      <c r="H11" s="17" t="n"/>
-      <c r="I11" s="17" t="n"/>
-      <c r="J11" s="17" t="n"/>
-      <c r="K11" s="18" t="n"/>
-      <c r="L11" s="7" t="n"/>
-      <c r="M11" s="19">
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="18" t="n"/>
+      <c r="F11" s="18" t="n"/>
+      <c r="G11" s="18" t="n"/>
+      <c r="H11" s="18" t="n"/>
+      <c r="I11" s="18" t="n"/>
+      <c r="J11" s="18" t="n"/>
+      <c r="K11" s="19" t="n"/>
+      <c r="L11" s="20">
+        <f>IF(AND(M11&gt;0,K11="Oui"),M11*(N(E11)*N('3 Options'!$C$16)+N(F11)*N('3 Options'!$C$17)+N(G11)),0)</f>
+        <v/>
+      </c>
+      <c r="M11" s="21">
         <f>IF($C11="",0,IF(N($D11)&gt;0,INT($D11),1))</f>
         <v/>
       </c>
-      <c r="N11" s="20">
+      <c r="N11" s="22">
         <f>SUM(M$6:M11)</f>
         <v/>
       </c>
-      <c r="O11" s="21">
+      <c r="O11" s="20">
         <f>IF(OR(M11=0,AND(K11="Oui",'3 Options'!$C$14="Oui")),0,M11*(N(E11)*N('1 Affaire'!$C$25)+N(F11)*N('1 Affaire'!$C$26)+N(G11)))</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="21" customHeight="1">
-      <c r="A12" s="15">
+      <c r="A12" s="16">
         <f>IF(M12&gt;0,COUNTIF(M$6:M12,"&gt;0"),"")</f>
         <v/>
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="17" t="n"/>
-      <c r="F12" s="17" t="n"/>
-      <c r="G12" s="17" t="n"/>
-      <c r="H12" s="17" t="n"/>
-      <c r="I12" s="17" t="n"/>
-      <c r="J12" s="17" t="n"/>
-      <c r="K12" s="18" t="n"/>
-      <c r="L12" s="7" t="n"/>
-      <c r="M12" s="19">
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="18" t="n"/>
+      <c r="H12" s="18" t="n"/>
+      <c r="I12" s="18" t="n"/>
+      <c r="J12" s="18" t="n"/>
+      <c r="K12" s="19" t="n"/>
+      <c r="L12" s="20">
+        <f>IF(AND(M12&gt;0,K12="Oui"),M12*(N(E12)*N('3 Options'!$C$16)+N(F12)*N('3 Options'!$C$17)+N(G12)),0)</f>
+        <v/>
+      </c>
+      <c r="M12" s="21">
         <f>IF($C12="",0,IF(N($D12)&gt;0,INT($D12),1))</f>
         <v/>
       </c>
-      <c r="N12" s="20">
+      <c r="N12" s="22">
         <f>SUM(M$6:M12)</f>
         <v/>
       </c>
-      <c r="O12" s="21">
+      <c r="O12" s="20">
         <f>IF(OR(M12=0,AND(K12="Oui",'3 Options'!$C$14="Oui")),0,M12*(N(E12)*N('1 Affaire'!$C$25)+N(F12)*N('1 Affaire'!$C$26)+N(G12)))</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="21" customHeight="1">
-      <c r="A13" s="15">
+      <c r="A13" s="16">
         <f>IF(M13&gt;0,COUNTIF(M$6:M13,"&gt;0"),"")</f>
         <v/>
       </c>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="17" t="n"/>
-      <c r="F13" s="17" t="n"/>
-      <c r="G13" s="17" t="n"/>
-      <c r="H13" s="17" t="n"/>
-      <c r="I13" s="17" t="n"/>
-      <c r="J13" s="17" t="n"/>
-      <c r="K13" s="18" t="n"/>
-      <c r="L13" s="7" t="n"/>
-      <c r="M13" s="19">
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="18" t="n"/>
+      <c r="F13" s="18" t="n"/>
+      <c r="G13" s="18" t="n"/>
+      <c r="H13" s="18" t="n"/>
+      <c r="I13" s="18" t="n"/>
+      <c r="J13" s="18" t="n"/>
+      <c r="K13" s="19" t="n"/>
+      <c r="L13" s="20">
+        <f>IF(AND(M13&gt;0,K13="Oui"),M13*(N(E13)*N('3 Options'!$C$16)+N(F13)*N('3 Options'!$C$17)+N(G13)),0)</f>
+        <v/>
+      </c>
+      <c r="M13" s="21">
         <f>IF($C13="",0,IF(N($D13)&gt;0,INT($D13),1))</f>
         <v/>
       </c>
-      <c r="N13" s="20">
+      <c r="N13" s="22">
         <f>SUM(M$6:M13)</f>
         <v/>
       </c>
-      <c r="O13" s="21">
+      <c r="O13" s="20">
         <f>IF(OR(M13=0,AND(K13="Oui",'3 Options'!$C$14="Oui")),0,M13*(N(E13)*N('1 Affaire'!$C$25)+N(F13)*N('1 Affaire'!$C$26)+N(G13)))</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="21" customHeight="1">
-      <c r="A14" s="15">
+      <c r="A14" s="16">
         <f>IF(M14&gt;0,COUNTIF(M$6:M14,"&gt;0"),"")</f>
         <v/>
       </c>
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
-      <c r="D14" s="16" t="n"/>
-      <c r="E14" s="17" t="n"/>
-      <c r="F14" s="17" t="n"/>
-      <c r="G14" s="17" t="n"/>
-      <c r="H14" s="17" t="n"/>
-      <c r="I14" s="17" t="n"/>
-      <c r="J14" s="17" t="n"/>
-      <c r="K14" s="18" t="n"/>
-      <c r="L14" s="7" t="n"/>
-      <c r="M14" s="19">
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="18" t="n"/>
+      <c r="F14" s="18" t="n"/>
+      <c r="G14" s="18" t="n"/>
+      <c r="H14" s="18" t="n"/>
+      <c r="I14" s="18" t="n"/>
+      <c r="J14" s="18" t="n"/>
+      <c r="K14" s="19" t="n"/>
+      <c r="L14" s="20">
+        <f>IF(AND(M14&gt;0,K14="Oui"),M14*(N(E14)*N('3 Options'!$C$16)+N(F14)*N('3 Options'!$C$17)+N(G14)),0)</f>
+        <v/>
+      </c>
+      <c r="M14" s="21">
         <f>IF($C14="",0,IF(N($D14)&gt;0,INT($D14),1))</f>
         <v/>
       </c>
-      <c r="N14" s="20">
+      <c r="N14" s="22">
         <f>SUM(M$6:M14)</f>
         <v/>
       </c>
-      <c r="O14" s="21">
+      <c r="O14" s="20">
         <f>IF(OR(M14=0,AND(K14="Oui",'3 Options'!$C$14="Oui")),0,M14*(N(E14)*N('1 Affaire'!$C$25)+N(F14)*N('1 Affaire'!$C$26)+N(G14)))</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="21" customHeight="1">
-      <c r="A15" s="15">
+      <c r="A15" s="16">
         <f>IF(M15&gt;0,COUNTIF(M$6:M15,"&gt;0"),"")</f>
         <v/>
       </c>
       <c r="B15" s="7" t="n"/>
       <c r="C15" s="7" t="n"/>
-      <c r="D15" s="16" t="n"/>
-      <c r="E15" s="17" t="n"/>
-      <c r="F15" s="17" t="n"/>
-      <c r="G15" s="17" t="n"/>
-      <c r="H15" s="17" t="n"/>
-      <c r="I15" s="17" t="n"/>
-      <c r="J15" s="17" t="n"/>
-      <c r="K15" s="18" t="n"/>
-      <c r="L15" s="7" t="n"/>
-      <c r="M15" s="19">
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="18" t="n"/>
+      <c r="F15" s="18" t="n"/>
+      <c r="G15" s="18" t="n"/>
+      <c r="H15" s="18" t="n"/>
+      <c r="I15" s="18" t="n"/>
+      <c r="J15" s="18" t="n"/>
+      <c r="K15" s="19" t="n"/>
+      <c r="L15" s="20">
+        <f>IF(AND(M15&gt;0,K15="Oui"),M15*(N(E15)*N('3 Options'!$C$16)+N(F15)*N('3 Options'!$C$17)+N(G15)),0)</f>
+        <v/>
+      </c>
+      <c r="M15" s="21">
         <f>IF($C15="",0,IF(N($D15)&gt;0,INT($D15),1))</f>
         <v/>
       </c>
-      <c r="N15" s="20">
+      <c r="N15" s="22">
         <f>SUM(M$6:M15)</f>
         <v/>
       </c>
-      <c r="O15" s="21">
+      <c r="O15" s="20">
         <f>IF(OR(M15=0,AND(K15="Oui",'3 Options'!$C$14="Oui")),0,M15*(N(E15)*N('1 Affaire'!$C$25)+N(F15)*N('1 Affaire'!$C$26)+N(G15)))</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="21" customHeight="1">
-      <c r="A16" s="15">
+      <c r="A16" s="16">
         <f>IF(M16&gt;0,COUNTIF(M$6:M16,"&gt;0"),"")</f>
         <v/>
       </c>
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="16" t="n"/>
-      <c r="E16" s="17" t="n"/>
-      <c r="F16" s="17" t="n"/>
-      <c r="G16" s="17" t="n"/>
-      <c r="H16" s="17" t="n"/>
-      <c r="I16" s="17" t="n"/>
-      <c r="J16" s="17" t="n"/>
-      <c r="K16" s="18" t="n"/>
-      <c r="L16" s="7" t="n"/>
-      <c r="M16" s="19">
+      <c r="D16" s="17" t="n"/>
+      <c r="E16" s="18" t="n"/>
+      <c r="F16" s="18" t="n"/>
+      <c r="G16" s="18" t="n"/>
+      <c r="H16" s="18" t="n"/>
+      <c r="I16" s="18" t="n"/>
+      <c r="J16" s="18" t="n"/>
+      <c r="K16" s="19" t="n"/>
+      <c r="L16" s="20">
+        <f>IF(AND(M16&gt;0,K16="Oui"),M16*(N(E16)*N('3 Options'!$C$16)+N(F16)*N('3 Options'!$C$17)+N(G16)),0)</f>
+        <v/>
+      </c>
+      <c r="M16" s="21">
         <f>IF($C16="",0,IF(N($D16)&gt;0,INT($D16),1))</f>
         <v/>
       </c>
-      <c r="N16" s="20">
+      <c r="N16" s="22">
         <f>SUM(M$6:M16)</f>
         <v/>
       </c>
-      <c r="O16" s="21">
+      <c r="O16" s="20">
         <f>IF(OR(M16=0,AND(K16="Oui",'3 Options'!$C$14="Oui")),0,M16*(N(E16)*N('1 Affaire'!$C$25)+N(F16)*N('1 Affaire'!$C$26)+N(G16)))</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
-      <c r="A17" s="15">
+      <c r="A17" s="16">
         <f>IF(M17&gt;0,COUNTIF(M$6:M17,"&gt;0"),"")</f>
         <v/>
       </c>
       <c r="B17" s="7" t="n"/>
       <c r="C17" s="7" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="17" t="n"/>
-      <c r="F17" s="17" t="n"/>
-      <c r="G17" s="17" t="n"/>
-      <c r="H17" s="17" t="n"/>
-      <c r="I17" s="17" t="n"/>
-      <c r="J17" s="17" t="n"/>
-      <c r="K17" s="18" t="n"/>
-      <c r="L17" s="7" t="n"/>
-      <c r="M17" s="19">
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="18" t="n"/>
+      <c r="F17" s="18" t="n"/>
+      <c r="G17" s="18" t="n"/>
+      <c r="H17" s="18" t="n"/>
+      <c r="I17" s="18" t="n"/>
+      <c r="J17" s="18" t="n"/>
+      <c r="K17" s="19" t="n"/>
+      <c r="L17" s="20">
+        <f>IF(AND(M17&gt;0,K17="Oui"),M17*(N(E17)*N('3 Options'!$C$16)+N(F17)*N('3 Options'!$C$17)+N(G17)),0)</f>
+        <v/>
+      </c>
+      <c r="M17" s="21">
         <f>IF($C17="",0,IF(N($D17)&gt;0,INT($D17),1))</f>
         <v/>
       </c>
-      <c r="N17" s="20">
+      <c r="N17" s="22">
         <f>SUM(M$6:M17)</f>
         <v/>
       </c>
-      <c r="O17" s="21">
+      <c r="O17" s="20">
         <f>IF(OR(M17=0,AND(K17="Oui",'3 Options'!$C$14="Oui")),0,M17*(N(E17)*N('1 Affaire'!$C$25)+N(F17)*N('1 Affaire'!$C$26)+N(G17)))</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
-      <c r="A18" s="15">
+      <c r="A18" s="16">
         <f>IF(M18&gt;0,COUNTIF(M$6:M18,"&gt;0"),"")</f>
         <v/>
       </c>
       <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="17" t="n"/>
-      <c r="F18" s="17" t="n"/>
-      <c r="G18" s="17" t="n"/>
-      <c r="H18" s="17" t="n"/>
-      <c r="I18" s="17" t="n"/>
-      <c r="J18" s="17" t="n"/>
-      <c r="K18" s="18" t="n"/>
-      <c r="L18" s="7" t="n"/>
-      <c r="M18" s="19">
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="18" t="n"/>
+      <c r="F18" s="18" t="n"/>
+      <c r="G18" s="18" t="n"/>
+      <c r="H18" s="18" t="n"/>
+      <c r="I18" s="18" t="n"/>
+      <c r="J18" s="18" t="n"/>
+      <c r="K18" s="19" t="n"/>
+      <c r="L18" s="20">
+        <f>IF(AND(M18&gt;0,K18="Oui"),M18*(N(E18)*N('3 Options'!$C$16)+N(F18)*N('3 Options'!$C$17)+N(G18)),0)</f>
+        <v/>
+      </c>
+      <c r="M18" s="21">
         <f>IF($C18="",0,IF(N($D18)&gt;0,INT($D18),1))</f>
         <v/>
       </c>
-      <c r="N18" s="20">
+      <c r="N18" s="22">
         <f>SUM(M$6:M18)</f>
         <v/>
       </c>
-      <c r="O18" s="21">
+      <c r="O18" s="20">
         <f>IF(OR(M18=0,AND(K18="Oui",'3 Options'!$C$14="Oui")),0,M18*(N(E18)*N('1 Affaire'!$C$25)+N(F18)*N('1 Affaire'!$C$26)+N(G18)))</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="21" customHeight="1">
-      <c r="A19" s="15">
+      <c r="A19" s="16">
         <f>IF(M19&gt;0,COUNTIF(M$6:M19,"&gt;0"),"")</f>
         <v/>
       </c>
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="16" t="n"/>
-      <c r="E19" s="17" t="n"/>
-      <c r="F19" s="17" t="n"/>
-      <c r="G19" s="17" t="n"/>
-      <c r="H19" s="17" t="n"/>
-      <c r="I19" s="17" t="n"/>
-      <c r="J19" s="17" t="n"/>
-      <c r="K19" s="18" t="n"/>
-      <c r="L19" s="7" t="n"/>
-      <c r="M19" s="19">
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="18" t="n"/>
+      <c r="F19" s="18" t="n"/>
+      <c r="G19" s="18" t="n"/>
+      <c r="H19" s="18" t="n"/>
+      <c r="I19" s="18" t="n"/>
+      <c r="J19" s="18" t="n"/>
+      <c r="K19" s="19" t="n"/>
+      <c r="L19" s="20">
+        <f>IF(AND(M19&gt;0,K19="Oui"),M19*(N(E19)*N('3 Options'!$C$16)+N(F19)*N('3 Options'!$C$17)+N(G19)),0)</f>
+        <v/>
+      </c>
+      <c r="M19" s="21">
         <f>IF($C19="",0,IF(N($D19)&gt;0,INT($D19),1))</f>
         <v/>
       </c>
-      <c r="N19" s="20">
+      <c r="N19" s="22">
         <f>SUM(M$6:M19)</f>
         <v/>
       </c>
-      <c r="O19" s="21">
+      <c r="O19" s="20">
         <f>IF(OR(M19=0,AND(K19="Oui",'3 Options'!$C$14="Oui")),0,M19*(N(E19)*N('1 Affaire'!$C$25)+N(F19)*N('1 Affaire'!$C$26)+N(G19)))</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="21" customHeight="1">
-      <c r="A20" s="15">
+      <c r="A20" s="16">
         <f>IF(M20&gt;0,COUNTIF(M$6:M20,"&gt;0"),"")</f>
         <v/>
       </c>
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="17" t="n"/>
-      <c r="F20" s="17" t="n"/>
-      <c r="G20" s="17" t="n"/>
-      <c r="H20" s="17" t="n"/>
-      <c r="I20" s="17" t="n"/>
-      <c r="J20" s="17" t="n"/>
-      <c r="K20" s="18" t="n"/>
-      <c r="L20" s="7" t="n"/>
-      <c r="M20" s="19">
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="18" t="n"/>
+      <c r="F20" s="18" t="n"/>
+      <c r="G20" s="18" t="n"/>
+      <c r="H20" s="18" t="n"/>
+      <c r="I20" s="18" t="n"/>
+      <c r="J20" s="18" t="n"/>
+      <c r="K20" s="19" t="n"/>
+      <c r="L20" s="20">
+        <f>IF(AND(M20&gt;0,K20="Oui"),M20*(N(E20)*N('3 Options'!$C$16)+N(F20)*N('3 Options'!$C$17)+N(G20)),0)</f>
+        <v/>
+      </c>
+      <c r="M20" s="21">
         <f>IF($C20="",0,IF(N($D20)&gt;0,INT($D20),1))</f>
         <v/>
       </c>
-      <c r="N20" s="20">
+      <c r="N20" s="22">
         <f>SUM(M$6:M20)</f>
         <v/>
       </c>
-      <c r="O20" s="21">
+      <c r="O20" s="20">
         <f>IF(OR(M20=0,AND(K20="Oui",'3 Options'!$C$14="Oui")),0,M20*(N(E20)*N('1 Affaire'!$C$25)+N(F20)*N('1 Affaire'!$C$26)+N(G20)))</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="21" customHeight="1">
-      <c r="A21" s="15">
+      <c r="A21" s="16">
         <f>IF(M21&gt;0,COUNTIF(M$6:M21,"&gt;0"),"")</f>
         <v/>
       </c>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="16" t="n"/>
-      <c r="E21" s="17" t="n"/>
-      <c r="F21" s="17" t="n"/>
-      <c r="G21" s="17" t="n"/>
-      <c r="H21" s="17" t="n"/>
-      <c r="I21" s="17" t="n"/>
-      <c r="J21" s="17" t="n"/>
-      <c r="K21" s="18" t="n"/>
-      <c r="L21" s="7" t="n"/>
-      <c r="M21" s="19">
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="18" t="n"/>
+      <c r="F21" s="18" t="n"/>
+      <c r="G21" s="18" t="n"/>
+      <c r="H21" s="18" t="n"/>
+      <c r="I21" s="18" t="n"/>
+      <c r="J21" s="18" t="n"/>
+      <c r="K21" s="19" t="n"/>
+      <c r="L21" s="20">
+        <f>IF(AND(M21&gt;0,K21="Oui"),M21*(N(E21)*N('3 Options'!$C$16)+N(F21)*N('3 Options'!$C$17)+N(G21)),0)</f>
+        <v/>
+      </c>
+      <c r="M21" s="21">
         <f>IF($C21="",0,IF(N($D21)&gt;0,INT($D21),1))</f>
         <v/>
       </c>
-      <c r="N21" s="20">
+      <c r="N21" s="22">
         <f>SUM(M$6:M21)</f>
         <v/>
       </c>
-      <c r="O21" s="21">
+      <c r="O21" s="20">
         <f>IF(OR(M21=0,AND(K21="Oui",'3 Options'!$C$14="Oui")),0,M21*(N(E21)*N('1 Affaire'!$C$25)+N(F21)*N('1 Affaire'!$C$26)+N(G21)))</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="21" customHeight="1">
-      <c r="A22" s="15">
+      <c r="A22" s="16">
         <f>IF(M22&gt;0,COUNTIF(M$6:M22,"&gt;0"),"")</f>
         <v/>
       </c>
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="16" t="n"/>
-      <c r="E22" s="17" t="n"/>
-      <c r="F22" s="17" t="n"/>
-      <c r="G22" s="17" t="n"/>
-      <c r="H22" s="17" t="n"/>
-      <c r="I22" s="17" t="n"/>
-      <c r="J22" s="17" t="n"/>
-      <c r="K22" s="18" t="n"/>
-      <c r="L22" s="7" t="n"/>
-      <c r="M22" s="19">
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="18" t="n"/>
+      <c r="F22" s="18" t="n"/>
+      <c r="G22" s="18" t="n"/>
+      <c r="H22" s="18" t="n"/>
+      <c r="I22" s="18" t="n"/>
+      <c r="J22" s="18" t="n"/>
+      <c r="K22" s="19" t="n"/>
+      <c r="L22" s="20">
+        <f>IF(AND(M22&gt;0,K22="Oui"),M22*(N(E22)*N('3 Options'!$C$16)+N(F22)*N('3 Options'!$C$17)+N(G22)),0)</f>
+        <v/>
+      </c>
+      <c r="M22" s="21">
         <f>IF($C22="",0,IF(N($D22)&gt;0,INT($D22),1))</f>
         <v/>
       </c>
-      <c r="N22" s="20">
+      <c r="N22" s="22">
         <f>SUM(M$6:M22)</f>
         <v/>
       </c>
-      <c r="O22" s="21">
+      <c r="O22" s="20">
         <f>IF(OR(M22=0,AND(K22="Oui",'3 Options'!$C$14="Oui")),0,M22*(N(E22)*N('1 Affaire'!$C$25)+N(F22)*N('1 Affaire'!$C$26)+N(G22)))</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="21" customHeight="1">
-      <c r="A23" s="15">
+      <c r="A23" s="16">
         <f>IF(M23&gt;0,COUNTIF(M$6:M23,"&gt;0"),"")</f>
         <v/>
       </c>
       <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
-      <c r="D23" s="16" t="n"/>
-      <c r="E23" s="17" t="n"/>
-      <c r="F23" s="17" t="n"/>
-      <c r="G23" s="17" t="n"/>
-      <c r="H23" s="17" t="n"/>
-      <c r="I23" s="17" t="n"/>
-      <c r="J23" s="17" t="n"/>
-      <c r="K23" s="18" t="n"/>
-      <c r="L23" s="7" t="n"/>
-      <c r="M23" s="19">
+      <c r="D23" s="17" t="n"/>
+      <c r="E23" s="18" t="n"/>
+      <c r="F23" s="18" t="n"/>
+      <c r="G23" s="18" t="n"/>
+      <c r="H23" s="18" t="n"/>
+      <c r="I23" s="18" t="n"/>
+      <c r="J23" s="18" t="n"/>
+      <c r="K23" s="19" t="n"/>
+      <c r="L23" s="20">
+        <f>IF(AND(M23&gt;0,K23="Oui"),M23*(N(E23)*N('3 Options'!$C$16)+N(F23)*N('3 Options'!$C$17)+N(G23)),0)</f>
+        <v/>
+      </c>
+      <c r="M23" s="21">
         <f>IF($C23="",0,IF(N($D23)&gt;0,INT($D23),1))</f>
         <v/>
       </c>
-      <c r="N23" s="20">
+      <c r="N23" s="22">
         <f>SUM(M$6:M23)</f>
         <v/>
       </c>
-      <c r="O23" s="21">
+      <c r="O23" s="20">
         <f>IF(OR(M23=0,AND(K23="Oui",'3 Options'!$C$14="Oui")),0,M23*(N(E23)*N('1 Affaire'!$C$25)+N(F23)*N('1 Affaire'!$C$26)+N(G23)))</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="21" customHeight="1">
-      <c r="A24" s="15">
+      <c r="A24" s="16">
         <f>IF(M24&gt;0,COUNTIF(M$6:M24,"&gt;0"),"")</f>
         <v/>
       </c>
       <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
-      <c r="D24" s="16" t="n"/>
-      <c r="E24" s="17" t="n"/>
-      <c r="F24" s="17" t="n"/>
-      <c r="G24" s="17" t="n"/>
-      <c r="H24" s="17" t="n"/>
-      <c r="I24" s="17" t="n"/>
-      <c r="J24" s="17" t="n"/>
-      <c r="K24" s="18" t="n"/>
-      <c r="L24" s="7" t="n"/>
-      <c r="M24" s="19">
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="18" t="n"/>
+      <c r="F24" s="18" t="n"/>
+      <c r="G24" s="18" t="n"/>
+      <c r="H24" s="18" t="n"/>
+      <c r="I24" s="18" t="n"/>
+      <c r="J24" s="18" t="n"/>
+      <c r="K24" s="19" t="n"/>
+      <c r="L24" s="20">
+        <f>IF(AND(M24&gt;0,K24="Oui"),M24*(N(E24)*N('3 Options'!$C$16)+N(F24)*N('3 Options'!$C$17)+N(G24)),0)</f>
+        <v/>
+      </c>
+      <c r="M24" s="21">
         <f>IF($C24="",0,IF(N($D24)&gt;0,INT($D24),1))</f>
         <v/>
       </c>
-      <c r="N24" s="20">
+      <c r="N24" s="22">
         <f>SUM(M$6:M24)</f>
         <v/>
       </c>
-      <c r="O24" s="21">
+      <c r="O24" s="20">
         <f>IF(OR(M24=0,AND(K24="Oui",'3 Options'!$C$14="Oui")),0,M24*(N(E24)*N('1 Affaire'!$C$25)+N(F24)*N('1 Affaire'!$C$26)+N(G24)))</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1">
-      <c r="A25" s="15">
+      <c r="A25" s="16">
         <f>IF(M25&gt;0,COUNTIF(M$6:M25,"&gt;0"),"")</f>
         <v/>
       </c>
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="16" t="n"/>
-      <c r="E25" s="17" t="n"/>
-      <c r="F25" s="17" t="n"/>
-      <c r="G25" s="17" t="n"/>
-      <c r="H25" s="17" t="n"/>
-      <c r="I25" s="17" t="n"/>
-      <c r="J25" s="17" t="n"/>
-      <c r="K25" s="18" t="n"/>
-      <c r="L25" s="7" t="n"/>
-      <c r="M25" s="19">
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="18" t="n"/>
+      <c r="F25" s="18" t="n"/>
+      <c r="G25" s="18" t="n"/>
+      <c r="H25" s="18" t="n"/>
+      <c r="I25" s="18" t="n"/>
+      <c r="J25" s="18" t="n"/>
+      <c r="K25" s="19" t="n"/>
+      <c r="L25" s="20">
+        <f>IF(AND(M25&gt;0,K25="Oui"),M25*(N(E25)*N('3 Options'!$C$16)+N(F25)*N('3 Options'!$C$17)+N(G25)),0)</f>
+        <v/>
+      </c>
+      <c r="M25" s="21">
         <f>IF($C25="",0,IF(N($D25)&gt;0,INT($D25),1))</f>
         <v/>
       </c>
-      <c r="N25" s="20">
+      <c r="N25" s="22">
         <f>SUM(M$6:M25)</f>
         <v/>
       </c>
-      <c r="O25" s="21">
+      <c r="O25" s="20">
         <f>IF(OR(M25=0,AND(K25="Oui",'3 Options'!$C$14="Oui")),0,M25*(N(E25)*N('1 Affaire'!$C$25)+N(F25)*N('1 Affaire'!$C$26)+N(G25)))</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="21" customHeight="1">
-      <c r="A26" s="15">
+      <c r="A26" s="16">
         <f>IF(M26&gt;0,COUNTIF(M$6:M26,"&gt;0"),"")</f>
         <v/>
       </c>
       <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="n"/>
-      <c r="D26" s="16" t="n"/>
-      <c r="E26" s="17" t="n"/>
-      <c r="F26" s="17" t="n"/>
-      <c r="G26" s="17" t="n"/>
-      <c r="H26" s="17" t="n"/>
-      <c r="I26" s="17" t="n"/>
-      <c r="J26" s="17" t="n"/>
-      <c r="K26" s="18" t="n"/>
-      <c r="L26" s="7" t="n"/>
-      <c r="M26" s="19">
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="18" t="n"/>
+      <c r="F26" s="18" t="n"/>
+      <c r="G26" s="18" t="n"/>
+      <c r="H26" s="18" t="n"/>
+      <c r="I26" s="18" t="n"/>
+      <c r="J26" s="18" t="n"/>
+      <c r="K26" s="19" t="n"/>
+      <c r="L26" s="20">
+        <f>IF(AND(M26&gt;0,K26="Oui"),M26*(N(E26)*N('3 Options'!$C$16)+N(F26)*N('3 Options'!$C$17)+N(G26)),0)</f>
+        <v/>
+      </c>
+      <c r="M26" s="21">
         <f>IF($C26="",0,IF(N($D26)&gt;0,INT($D26),1))</f>
         <v/>
       </c>
-      <c r="N26" s="20">
+      <c r="N26" s="22">
         <f>SUM(M$6:M26)</f>
         <v/>
       </c>
-      <c r="O26" s="21">
+      <c r="O26" s="20">
         <f>IF(OR(M26=0,AND(K26="Oui",'3 Options'!$C$14="Oui")),0,M26*(N(E26)*N('1 Affaire'!$C$25)+N(F26)*N('1 Affaire'!$C$26)+N(G26)))</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="21" customHeight="1">
-      <c r="A27" s="15">
+      <c r="A27" s="16">
         <f>IF(M27&gt;0,COUNTIF(M$6:M27,"&gt;0"),"")</f>
         <v/>
       </c>
       <c r="B27" s="7" t="n"/>
       <c r="C27" s="7" t="n"/>
-      <c r="D27" s="16" t="n"/>
-      <c r="E27" s="17" t="n"/>
-      <c r="F27" s="17" t="n"/>
-      <c r="G27" s="17" t="n"/>
-      <c r="H27" s="17" t="n"/>
-      <c r="I27" s="17" t="n"/>
-      <c r="J27" s="17" t="n"/>
-      <c r="K27" s="18" t="n"/>
-      <c r="L27" s="7" t="n"/>
-      <c r="M27" s="19">
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="18" t="n"/>
+      <c r="F27" s="18" t="n"/>
+      <c r="G27" s="18" t="n"/>
+      <c r="H27" s="18" t="n"/>
+      <c r="I27" s="18" t="n"/>
+      <c r="J27" s="18" t="n"/>
+      <c r="K27" s="19" t="n"/>
+      <c r="L27" s="20">
+        <f>IF(AND(M27&gt;0,K27="Oui"),M27*(N(E27)*N('3 Options'!$C$16)+N(F27)*N('3 Options'!$C$17)+N(G27)),0)</f>
+        <v/>
+      </c>
+      <c r="M27" s="21">
         <f>IF($C27="",0,IF(N($D27)&gt;0,INT($D27),1))</f>
         <v/>
       </c>
-      <c r="N27" s="20">
+      <c r="N27" s="22">
         <f>SUM(M$6:M27)</f>
         <v/>
       </c>
-      <c r="O27" s="21">
+      <c r="O27" s="20">
         <f>IF(OR(M27=0,AND(K27="Oui",'3 Options'!$C$14="Oui")),0,M27*(N(E27)*N('1 Affaire'!$C$25)+N(F27)*N('1 Affaire'!$C$26)+N(G27)))</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="21" customHeight="1">
-      <c r="A28" s="15">
+      <c r="A28" s="16">
         <f>IF(M28&gt;0,COUNTIF(M$6:M28,"&gt;0"),"")</f>
         <v/>
       </c>
       <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="17" t="n"/>
-      <c r="F28" s="17" t="n"/>
-      <c r="G28" s="17" t="n"/>
-      <c r="H28" s="17" t="n"/>
-      <c r="I28" s="17" t="n"/>
-      <c r="J28" s="17" t="n"/>
-      <c r="K28" s="18" t="n"/>
-      <c r="L28" s="7" t="n"/>
-      <c r="M28" s="19">
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="18" t="n"/>
+      <c r="F28" s="18" t="n"/>
+      <c r="G28" s="18" t="n"/>
+      <c r="H28" s="18" t="n"/>
+      <c r="I28" s="18" t="n"/>
+      <c r="J28" s="18" t="n"/>
+      <c r="K28" s="19" t="n"/>
+      <c r="L28" s="20">
+        <f>IF(AND(M28&gt;0,K28="Oui"),M28*(N(E28)*N('3 Options'!$C$16)+N(F28)*N('3 Options'!$C$17)+N(G28)),0)</f>
+        <v/>
+      </c>
+      <c r="M28" s="21">
         <f>IF($C28="",0,IF(N($D28)&gt;0,INT($D28),1))</f>
         <v/>
       </c>
-      <c r="N28" s="20">
+      <c r="N28" s="22">
         <f>SUM(M$6:M28)</f>
         <v/>
       </c>
-      <c r="O28" s="21">
+      <c r="O28" s="20">
         <f>IF(OR(M28=0,AND(K28="Oui",'3 Options'!$C$14="Oui")),0,M28*(N(E28)*N('1 Affaire'!$C$25)+N(F28)*N('1 Affaire'!$C$26)+N(G28)))</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="21" customHeight="1">
-      <c r="A29" s="15">
+      <c r="A29" s="16">
         <f>IF(M29&gt;0,COUNTIF(M$6:M29,"&gt;0"),"")</f>
         <v/>
       </c>
       <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
-      <c r="D29" s="16" t="n"/>
-      <c r="E29" s="17" t="n"/>
-      <c r="F29" s="17" t="n"/>
-      <c r="G29" s="17" t="n"/>
-      <c r="H29" s="17" t="n"/>
-      <c r="I29" s="17" t="n"/>
-      <c r="J29" s="17" t="n"/>
-      <c r="K29" s="18" t="n"/>
-      <c r="L29" s="7" t="n"/>
-      <c r="M29" s="19">
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="18" t="n"/>
+      <c r="F29" s="18" t="n"/>
+      <c r="G29" s="18" t="n"/>
+      <c r="H29" s="18" t="n"/>
+      <c r="I29" s="18" t="n"/>
+      <c r="J29" s="18" t="n"/>
+      <c r="K29" s="19" t="n"/>
+      <c r="L29" s="20">
+        <f>IF(AND(M29&gt;0,K29="Oui"),M29*(N(E29)*N('3 Options'!$C$16)+N(F29)*N('3 Options'!$C$17)+N(G29)),0)</f>
+        <v/>
+      </c>
+      <c r="M29" s="21">
         <f>IF($C29="",0,IF(N($D29)&gt;0,INT($D29),1))</f>
         <v/>
       </c>
-      <c r="N29" s="20">
+      <c r="N29" s="22">
         <f>SUM(M$6:M29)</f>
         <v/>
       </c>
-      <c r="O29" s="21">
+      <c r="O29" s="20">
         <f>IF(OR(M29=0,AND(K29="Oui",'3 Options'!$C$14="Oui")),0,M29*(N(E29)*N('1 Affaire'!$C$25)+N(F29)*N('1 Affaire'!$C$26)+N(G29)))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="C31" s="22">
+      <c r="C31" s="23">
         <f>SUM(M6:M29)&amp;" ligne(s) sur la tool list  ·  "&amp;COUNTIF(M6:M29,"&gt;0")&amp;" référence(s) au devis"</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="C32" s="23" t="inlineStr">
-        <is>
-          <t>Le devis affiche les 14 premières lignes (les suivantes sont repliées dans l’onglet 4, avec une alerte). Colonnes grises (M à O) : calculs, ne pas modifier. « Inclus au forfait » ne s’applique que si l’option Forfait est activée dans l’onglet 3.</t>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>Le devis affiche les 14 premières lignes (les suivantes sont repliées dans l’onglet 4, avec une alerte). Colonnes grises (L à O) : calculs, ne pas modifier. « Inclus au forfait » ne s’applique que si l’option Forfait est activée dans l’onglet 3.</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2437,326 +2738,326 @@
       <c r="J3" s="4" t="n"/>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Option</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>Inclure ?</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>Intitulé affiché (facultatif)</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>Qté</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t>Prix €</t>
         </is>
       </c>
-      <c r="G5" s="13" t="inlineStr">
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>Unité / mode</t>
         </is>
       </c>
-      <c r="H5" s="13" t="inlineStr">
+      <c r="H5" s="14" t="inlineStr">
         <is>
           <t>Total €</t>
         </is>
       </c>
-      <c r="I5" s="14" t="inlineStr">
+      <c r="I5" s="15" t="inlineStr">
         <is>
           <t>Rang</t>
         </is>
       </c>
-      <c r="J5" s="14" t="inlineStr">
+      <c r="J5" s="15" t="inlineStr">
         <is>
           <t>Détail affiché sur le devis</t>
         </is>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>👷  Opérateur · tarif journalier</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
       <c r="D6" s="7" t="n"/>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="17" t="n"/>
-      <c r="G6" s="18" t="inlineStr">
+      <c r="F6" s="18" t="n"/>
+      <c r="G6" s="19" t="inlineStr">
         <is>
           <t>€/jour/pers</t>
         </is>
       </c>
-      <c r="H6" s="25">
+      <c r="H6" s="26">
         <f>IF(C6="Oui",IF(AND(OR(G6="Coût réel +15 %"),F6=""),0,N(E6)*N(F6)),0)</f>
         <v/>
       </c>
-      <c r="I6" s="20">
+      <c r="I6" s="22">
         <f>IF(C6="Oui",COUNTIF(C$6:C6,"Oui"),"")</f>
         <v/>
       </c>
       <c r="J6" s="7" t="n"/>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>👷  Opérateur · Mob / Demob</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
       <c r="D7" s="7" t="n"/>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="17" t="n"/>
-      <c r="G7" s="18" t="inlineStr">
+      <c r="F7" s="18" t="n"/>
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t>€/pers</t>
         </is>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="26">
         <f>IF(C7="Oui",IF(AND(OR(G7="Coût réel +15 %"),F7=""),0,N(E7)*N(F7)),0)</f>
         <v/>
       </c>
-      <c r="I7" s="20">
+      <c r="I7" s="22">
         <f>IF(C7="Oui",COUNTIF(C$6:C7,"Oui"),"")</f>
         <v/>
       </c>
       <c r="J7" s="7" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>🔧  Serrage · Make-up</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
       <c r="D8" s="7" t="n"/>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="17" t="n"/>
-      <c r="G8" s="18" t="inlineStr">
+      <c r="F8" s="18" t="n"/>
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>forfait</t>
         </is>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="26">
         <f>IF(C8="Oui",IF(AND(OR(G8="Coût réel +15 %"),F8=""),0,N(E8)*N(F8)),0)</f>
         <v/>
       </c>
-      <c r="I8" s="20">
+      <c r="I8" s="22">
         <f>IF(C8="Oui",COUNTIF(C$6:C8,"Oui"),"")</f>
         <v/>
       </c>
       <c r="J8" s="7" t="n"/>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>🚚  Transport MOB</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
       <c r="D9" s="7" t="n"/>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="17" t="n"/>
-      <c r="G9" s="18" t="inlineStr">
+      <c r="F9" s="18" t="n"/>
+      <c r="G9" s="19" t="inlineStr">
         <is>
           <t>Coût réel +15 %</t>
         </is>
       </c>
-      <c r="H9" s="25">
+      <c r="H9" s="26">
         <f>IF(C9="Oui",IF(AND(OR(G9="Coût réel +15 %"),F9=""),0,N(E9)*N(F9)),0)</f>
         <v/>
       </c>
-      <c r="I9" s="20">
+      <c r="I9" s="22">
         <f>IF(C9="Oui",COUNTIF(C$6:C9,"Oui"),"")</f>
         <v/>
       </c>
       <c r="J9" s="7" t="n"/>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>🚚  Transport DEMOB</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
       <c r="D10" s="7" t="n"/>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="17" t="n"/>
-      <c r="G10" s="18" t="inlineStr">
+      <c r="F10" s="18" t="n"/>
+      <c r="G10" s="19" t="inlineStr">
         <is>
           <t>Coût réel +15 %</t>
         </is>
       </c>
-      <c r="H10" s="25">
+      <c r="H10" s="26">
         <f>IF(C10="Oui",IF(AND(OR(G10="Coût réel +15 %"),F10=""),0,N(E10)*N(F10)),0)</f>
         <v/>
       </c>
-      <c r="I10" s="20">
+      <c r="I10" s="22">
         <f>IF(C10="Oui",COUNTIF(C$6:C10,"Oui"),"")</f>
         <v/>
       </c>
       <c r="J10" s="7" t="n"/>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>➕  Option libre 1</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
       <c r="D11" s="7" t="n"/>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="17" t="n"/>
-      <c r="G11" s="18" t="inlineStr">
+      <c r="F11" s="18" t="n"/>
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>forfait</t>
         </is>
       </c>
-      <c r="H11" s="25">
+      <c r="H11" s="26">
         <f>IF(C11="Oui",IF(AND(OR(G11="Coût réel +15 %"),F11=""),0,N(E11)*N(F11)),0)</f>
         <v/>
       </c>
-      <c r="I11" s="20">
+      <c r="I11" s="22">
         <f>IF(C11="Oui",COUNTIF(C$6:C11,"Oui"),"")</f>
         <v/>
       </c>
       <c r="J11" s="7" t="n"/>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>➕  Option libre 2</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
       <c r="D12" s="7" t="n"/>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="17" t="n"/>
-      <c r="G12" s="18" t="inlineStr">
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="19" t="inlineStr">
         <is>
           <t>forfait</t>
         </is>
       </c>
-      <c r="H12" s="25">
+      <c r="H12" s="26">
         <f>IF(C12="Oui",IF(AND(OR(G12="Coût réel +15 %"),F12=""),0,N(E12)*N(F12)),0)</f>
         <v/>
       </c>
-      <c r="I12" s="20">
+      <c r="I12" s="22">
         <f>IF(C12="Oui",COUNTIF(C$6:C12,"Oui"),"")</f>
         <v/>
       </c>
       <c r="J12" s="7" t="n"/>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>➕  Option libre 3</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
       <c r="D13" s="7" t="n"/>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="17" t="n"/>
-      <c r="G13" s="18" t="inlineStr">
+      <c r="F13" s="18" t="n"/>
+      <c r="G13" s="19" t="inlineStr">
         <is>
           <t>forfait</t>
         </is>
       </c>
-      <c r="H13" s="25">
+      <c r="H13" s="26">
         <f>IF(C13="Oui",IF(AND(OR(G13="Coût réel +15 %"),F13=""),0,N(E13)*N(F13)),0)</f>
         <v/>
       </c>
-      <c r="I13" s="20">
+      <c r="I13" s="22">
         <f>IF(C13="Oui",COUNTIF(C$6:C13,"Oui"),"")</f>
         <v/>
       </c>
       <c r="J13" s="7" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>📦  FORFAIT (remplace les tarifs des lignes cochées)</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
       <c r="D14" s="7" t="n"/>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="17" t="n"/>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>Forfait global</t>
-        </is>
-      </c>
-      <c r="H14" s="25">
-        <f>IF(C14="Oui",IF(AND(OR(G14="Coût réel +15 %"),F14=""),0,N(E14)*N(F14)),0)</f>
-        <v/>
-      </c>
-      <c r="I14" s="20">
+      <c r="F14" s="18" t="n"/>
+      <c r="G14" s="19" t="inlineStr">
+        <is>
+          <t>Forfait calculé (S + O + UC)</t>
+        </is>
+      </c>
+      <c r="H14" s="26">
+        <f>IF(C14="Oui",IF(G14="Forfait calculé (S + O + UC)",IF(F14&lt;&gt;"",F14,SUM('2 Matériel'!$L$6:$L$29)),N(E14)*N(F14)),0)</f>
+        <v/>
+      </c>
+      <c r="I14" s="22">
         <f>IF(C14="Oui",COUNTIF(C$6:C14,"Oui"),"")</f>
         <v/>
       </c>
@@ -2768,52 +3069,89 @@
           <t>Forfait · intitulé et périmètre</t>
         </is>
       </c>
-      <c r="D15" s="26" t="n"/>
-      <c r="E15" s="27" t="n"/>
-      <c r="F15" s="27" t="n"/>
-      <c r="G15" s="27" t="n"/>
-      <c r="H15" s="27" t="n"/>
-      <c r="I15" s="27" t="n"/>
-      <c r="J15" s="27" t="n"/>
+      <c r="D15" s="27" t="n"/>
+      <c r="E15" s="28" t="n"/>
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="28" t="n"/>
+      <c r="H15" s="28" t="n"/>
+      <c r="I15" s="28" t="n"/>
+      <c r="J15" s="28" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Forfait calculé · jours de stand-by (S)</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Forfait habituel : 3 jours de stand-by + 2 jours d’opérations + toutes les utilisations de charge (UC). Laisser « Prix € » de la ligne forfait vide pour utiliser ce calcul, ou saisir un prix pour le remplacer.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Forfait calculé · jours d’opérations (O)</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Montant calculé des lignes « Inclus au forfait »</t>
+        </is>
+      </c>
+      <c r="C18" s="29">
+        <f>SUM('2 Matériel'!$L$6:$L$29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Comment utiliser le forfait</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="28" t="inlineStr">
-        <is>
-          <t>1. Option « Forfait » sur Oui, mode Forfait global (prix total) ou Forfait par jour (Qté = nombre de jours).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="28" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>1. Option « Forfait » sur Oui. Mode « calculé » (3 S + 2 O + UC, jours modifiables), « global » (prix total) ou « par jour » (Qté = nombre de jours).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>2. Dans l'onglet 2, mettre « Oui » dans « Inclus au forfait » sur chaque ligne couverte : elles s'affichent « incl. » sur le devis et restent sur la tool list.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="28" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="30" t="inlineStr">
         <is>
           <t>3. Écrire le périmètre ci-dessus (ex. « Location 10 jours stab + 2 XO, transport inclus »). Il apparaît sous le forfait.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="28" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="30" t="inlineStr">
         <is>
           <t>Transport : « Coût réel +15 % » n'affiche aucun montant. Choisir « Forfait » pour imposer un prix.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="D15:J15"/>
+    <mergeCell ref="D16:J18"/>
   </mergeCells>
   <dataValidations count="18">
     <dataValidation sqref="G6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="warning">
@@ -2905,7 +3243,7 @@
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
-      <c r="E1" s="29">
+      <c r="E1" s="31">
         <f>INDEX(Textes!$B$2:$C$54,MATCH("title",Textes!$A$2:$A$54,0),Listes!$H$1)</f>
         <v/>
       </c>
@@ -2916,7 +3254,7 @@
       <c r="B2" s="1" t="n"/>
       <c r="C2" s="1" t="n"/>
       <c r="D2" s="1" t="n"/>
-      <c r="E2" s="30">
+      <c r="E2" s="32">
         <f>"N° "&amp;'1 Affaire'!$C$6&amp;"   ·   "&amp;IF('1 Affaire'!$C$7="","",TEXT('1 Affaire'!$C$7,"dd/mm/yyyy"))</f>
         <v/>
       </c>
@@ -2938,1547 +3276,1547 @@
     </row>
     <row r="4" ht="8" customHeight="1"/>
     <row r="5" ht="15" customHeight="1">
-      <c r="B5" s="31">
+      <c r="B5" s="33">
         <f>UPPER(INDEX(Textes!$B$2:$C$54,MATCH("client",Textes!$A$2:$A$54,0),Listes!$H$1))</f>
         <v/>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="33">
         <f>UPPER(INDEX(Textes!$B$2:$C$54,MATCH("offer",Textes!$A$2:$A$54,0),Listes!$H$1))</f>
         <v/>
       </c>
-      <c r="G5" s="31">
+      <c r="G5" s="33">
         <f>UPPER(INDEX(Textes!$B$2:$C$54,MATCH("date",Textes!$A$2:$A$54,0),Listes!$H$1))</f>
         <v/>
       </c>
-      <c r="I5" s="31">
+      <c r="I5" s="33">
         <f>UPPER(INDEX(Textes!$B$2:$C$54,MATCH("by",Textes!$A$2:$A$54,0),Listes!$H$1))</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="19" customHeight="1">
-      <c r="B6" s="32">
+      <c r="B6" s="34">
         <f>""&amp;'1 Affaire'!$C$8</f>
         <v/>
       </c>
-      <c r="C6" s="33" t="n"/>
-      <c r="D6" s="32">
+      <c r="C6" s="35" t="n"/>
+      <c r="D6" s="34">
         <f>""&amp;'1 Affaire'!$C$6</f>
         <v/>
       </c>
-      <c r="E6" s="33" t="n"/>
-      <c r="F6" s="33" t="n"/>
-      <c r="G6" s="32">
+      <c r="E6" s="35" t="n"/>
+      <c r="F6" s="35" t="n"/>
+      <c r="G6" s="34">
         <f>IF('1 Affaire'!$C$7="","",TEXT('1 Affaire'!$C$7,"dd/mm/yyyy"))</f>
         <v/>
       </c>
-      <c r="H6" s="33" t="n"/>
-      <c r="I6" s="32">
+      <c r="H6" s="35" t="n"/>
+      <c r="I6" s="34">
         <f>""&amp;'1 Affaire'!$F$6</f>
         <v/>
       </c>
-      <c r="J6" s="33" t="n"/>
-      <c r="K6" s="33" t="n"/>
+      <c r="J6" s="35" t="n"/>
+      <c r="K6" s="35" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="B7" s="31">
+      <c r="B7" s="33">
         <f>UPPER(INDEX(Textes!$B$2:$C$54,MATCH("attn",Textes!$A$2:$A$54,0),Listes!$H$1))</f>
         <v/>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="33">
         <f>UPPER(INDEX(Textes!$B$2:$C$54,MATCH("well",Textes!$A$2:$A$54,0),Listes!$H$1))</f>
         <v/>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="33">
         <f>UPPER(INDEX(Textes!$B$2:$C$54,MATCH("rigjob",Textes!$A$2:$A$54,0),Listes!$H$1))</f>
         <v/>
       </c>
-      <c r="I7" s="31">
+      <c r="I7" s="33">
         <f>UPPER(INDEX(Textes!$B$2:$C$54,MATCH("mail",Textes!$A$2:$A$54,0),Listes!$H$1))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
-      <c r="B8" s="32">
+      <c r="B8" s="34">
         <f>""&amp;'1 Affaire'!$C$9</f>
         <v/>
       </c>
-      <c r="C8" s="33" t="n"/>
-      <c r="D8" s="32">
+      <c r="C8" s="35" t="n"/>
+      <c r="D8" s="34">
         <f>""&amp;'1 Affaire'!$C$10</f>
         <v/>
       </c>
-      <c r="E8" s="33" t="n"/>
-      <c r="F8" s="33" t="n"/>
-      <c r="G8" s="32">
+      <c r="E8" s="35" t="n"/>
+      <c r="F8" s="35" t="n"/>
+      <c r="G8" s="34">
         <f>'1 Affaire'!$C$11&amp;IF('1 Affaire'!$C$12&lt;&gt;""," · "&amp;'1 Affaire'!$C$12,"")</f>
         <v/>
       </c>
-      <c r="H8" s="33" t="n"/>
-      <c r="I8" s="32">
+      <c r="H8" s="35" t="n"/>
+      <c r="I8" s="34">
         <f>""&amp;'1 Affaire'!$F$7</f>
         <v/>
       </c>
-      <c r="J8" s="33" t="n"/>
-      <c r="K8" s="33" t="n"/>
+      <c r="J8" s="35" t="n"/>
+      <c r="K8" s="35" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="B9" s="31">
+      <c r="B9" s="33">
         <f>UPPER(INDEX(Textes!$B$2:$C$54,MATCH("po",Textes!$A$2:$A$54,0),Listes!$H$1))</f>
         <v/>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="33">
         <f>UPPER(INDEX(Textes!$B$2:$C$54,MATCH("inco",Textes!$A$2:$A$54,0),Listes!$H$1))</f>
         <v/>
       </c>
-      <c r="G9" s="31">
+      <c r="G9" s="33">
         <f>UPPER(INDEX(Textes!$B$2:$C$54,MATCH("valid",Textes!$A$2:$A$54,0),Listes!$H$1))</f>
         <v/>
       </c>
-      <c r="I9" s="31">
+      <c r="I9" s="33">
         <f>UPPER(INDEX(Textes!$B$2:$C$54,MATCH("tel",Textes!$A$2:$A$54,0),Listes!$H$1))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
-      <c r="B10" s="32">
+      <c r="B10" s="34">
         <f>""&amp;'1 Affaire'!$C$13</f>
         <v/>
       </c>
-      <c r="C10" s="33" t="n"/>
-      <c r="D10" s="32">
+      <c r="C10" s="35" t="n"/>
+      <c r="D10" s="34">
         <f>""&amp;'1 Affaire'!$F$10</f>
         <v/>
       </c>
-      <c r="E10" s="33" t="n"/>
-      <c r="F10" s="33" t="n"/>
-      <c r="G10" s="32">
+      <c r="E10" s="35" t="n"/>
+      <c r="F10" s="35" t="n"/>
+      <c r="G10" s="34">
         <f>""&amp;'1 Affaire'!$F$9</f>
         <v/>
       </c>
-      <c r="H10" s="33" t="n"/>
-      <c r="I10" s="32">
+      <c r="H10" s="35" t="n"/>
+      <c r="I10" s="34">
         <f>""&amp;'1 Affaire'!$F$8</f>
         <v/>
       </c>
-      <c r="J10" s="33" t="n"/>
-      <c r="K10" s="33" t="n"/>
+      <c r="J10" s="35" t="n"/>
+      <c r="K10" s="35" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="B11" s="31">
+      <c r="B11" s="33">
         <f>UPPER(INDEX(Textes!$B$2:$C$54,MATCH("pay",Textes!$A$2:$A$54,0),Listes!$H$1))</f>
         <v/>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="33">
         <f>UPPER(INDEX(Textes!$B$2:$C$54,MATCH("lead",Textes!$A$2:$A$54,0),Listes!$H$1))</f>
         <v/>
       </c>
-      <c r="G11" s="31">
+      <c r="G11" s="33">
         <f>UPPER(INDEX(Textes!$B$2:$C$54,MATCH("we",Textes!$A$2:$A$54,0),Listes!$H$1))</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1">
-      <c r="B12" s="32">
+      <c r="B12" s="34">
         <f>""&amp;'1 Affaire'!$F$12</f>
         <v/>
       </c>
-      <c r="C12" s="33" t="n"/>
-      <c r="D12" s="32">
+      <c r="C12" s="35" t="n"/>
+      <c r="D12" s="34">
         <f>""&amp;'1 Affaire'!$F$11</f>
         <v/>
       </c>
-      <c r="E12" s="33" t="n"/>
-      <c r="F12" s="33" t="n"/>
-      <c r="G12" s="32">
+      <c r="E12" s="35" t="n"/>
+      <c r="F12" s="35" t="n"/>
+      <c r="G12" s="34">
         <f>""&amp;'1 Affaire'!$F$13</f>
         <v/>
       </c>
-      <c r="H12" s="33" t="n"/>
+      <c r="H12" s="35" t="n"/>
     </row>
     <row r="13" ht="8" customHeight="1"/>
     <row r="14" ht="20" customHeight="1">
-      <c r="B14" s="34">
+      <c r="B14" s="36">
         <f>INDEX(Textes!$B$2:$C$54,MATCH("sec_eq",Textes!$A$2:$A$54,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="C14" s="35" t="n"/>
-      <c r="D14" s="35" t="n"/>
-      <c r="E14" s="35" t="n"/>
-      <c r="F14" s="35" t="n"/>
-      <c r="G14" s="35" t="n"/>
-      <c r="H14" s="35" t="n"/>
-      <c r="I14" s="35" t="n"/>
-      <c r="J14" s="35" t="n"/>
-      <c r="K14" s="35" t="n"/>
+      <c r="C14" s="37" t="n"/>
+      <c r="D14" s="37" t="n"/>
+      <c r="E14" s="37" t="n"/>
+      <c r="F14" s="37" t="n"/>
+      <c r="G14" s="37" t="n"/>
+      <c r="H14" s="37" t="n"/>
+      <c r="I14" s="37" t="n"/>
+      <c r="J14" s="37" t="n"/>
+      <c r="K14" s="37" t="n"/>
     </row>
     <row r="15" ht="44" customHeight="1">
-      <c r="B15" s="36">
+      <c r="B15" s="38">
         <f>INDEX(Textes!$B$2:$C$54,MATCH("h_n",Textes!$A$2:$A$54,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="C15" s="37">
+      <c r="C15" s="39">
         <f>INDEX(Textes!$B$2:$C$54,MATCH("h_desc",Textes!$A$2:$A$54,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="D15" s="36">
+      <c r="D15" s="38">
         <f>INDEX(Textes!$B$2:$C$54,MATCH("h_qty",Textes!$A$2:$A$54,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="E15" s="36">
+      <c r="E15" s="38">
         <f>INDEX(Textes!$B$2:$C$54,MATCH("h_s",Textes!$A$2:$A$54,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="F15" s="36">
+      <c r="F15" s="38">
         <f>INDEX(Textes!$B$2:$C$54,MATCH("h_o",Textes!$A$2:$A$54,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="G15" s="36">
+      <c r="G15" s="38">
         <f>INDEX(Textes!$B$2:$C$54,MATCH("h_uc",Textes!$A$2:$A$54,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="H15" s="36">
+      <c r="H15" s="38">
         <f>INDEX(Textes!$B$2:$C$54,MATCH("h_lih",Textes!$A$2:$A$54,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="I15" s="36">
+      <c r="I15" s="38">
         <f>INDEX(Textes!$B$2:$C$54,MATCH("h_insp",Textes!$A$2:$A$54,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="J15" s="36">
+      <c r="J15" s="38">
         <f>INDEX(Textes!$B$2:$C$54,MATCH("h_rest",Textes!$A$2:$A$54,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="K15" s="36">
+      <c r="K15" s="38">
         <f>INDEX(Textes!$B$2:$C$54,MATCH("h_ref",Textes!$A$2:$A$54,0),Listes!$H$1)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="21" customHeight="1">
-      <c r="B16" s="15">
+      <c r="B16" s="16">
         <f>IF('2 Matériel'!$M6&gt;0,'2 Matériel'!$A6,"")</f>
         <v/>
       </c>
-      <c r="C16" s="38">
+      <c r="C16" s="40">
         <f>IF('2 Matériel'!$M6&gt;0,'2 Matériel'!$C6,"")</f>
         <v/>
       </c>
-      <c r="D16" s="39">
+      <c r="D16" s="41">
         <f>IF('2 Matériel'!$M6&gt;0,'2 Matériel'!$M6,"")</f>
         <v/>
       </c>
-      <c r="E16" s="40">
+      <c r="E16" s="42">
         <f>IF('2 Matériel'!$M6&gt;0,IF(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$E6="","",'2 Matériel'!$E6)),"")</f>
         <v/>
       </c>
-      <c r="F16" s="40">
+      <c r="F16" s="42">
         <f>IF('2 Matériel'!$M6&gt;0,IF(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$F6="","",'2 Matériel'!$F6)),"")</f>
         <v/>
       </c>
-      <c r="G16" s="40">
+      <c r="G16" s="42">
         <f>IF('2 Matériel'!$M6&gt;0,IF(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$G6="","",'2 Matériel'!$G6)),"")</f>
         <v/>
       </c>
-      <c r="H16" s="40">
+      <c r="H16" s="42">
         <f>IF('2 Matériel'!$M6&gt;0,IF(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$H6="","",'2 Matériel'!$H6)),"")</f>
         <v/>
       </c>
-      <c r="I16" s="40">
+      <c r="I16" s="42">
         <f>IF('2 Matériel'!$M6&gt;0,IF(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$I6="","",'2 Matériel'!$I6)),"")</f>
         <v/>
       </c>
-      <c r="J16" s="40">
+      <c r="J16" s="42">
         <f>IF('2 Matériel'!$M6&gt;0,IF(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$J6="","",'2 Matériel'!$J6)),"")</f>
         <v/>
       </c>
-      <c r="K16" s="41">
-        <f>IF('2 Matériel'!$M6&gt;0,'2 Matériel'!$B6&amp;IF(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$14="Oui"),IF('2 Matériel'!$B6="","","  ·  ")&amp;INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
+      <c r="K16" s="43">
+        <f>IF('2 Matériel'!$M6&gt;0,IF(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
-      <c r="B17" s="15">
+      <c r="B17" s="16">
         <f>IF('2 Matériel'!$M7&gt;0,'2 Matériel'!$A7,"")</f>
         <v/>
       </c>
-      <c r="C17" s="38">
+      <c r="C17" s="40">
         <f>IF('2 Matériel'!$M7&gt;0,'2 Matériel'!$C7,"")</f>
         <v/>
       </c>
-      <c r="D17" s="39">
+      <c r="D17" s="41">
         <f>IF('2 Matériel'!$M7&gt;0,'2 Matériel'!$M7,"")</f>
         <v/>
       </c>
-      <c r="E17" s="40">
+      <c r="E17" s="42">
         <f>IF('2 Matériel'!$M7&gt;0,IF(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$E7="","",'2 Matériel'!$E7)),"")</f>
         <v/>
       </c>
-      <c r="F17" s="40">
+      <c r="F17" s="42">
         <f>IF('2 Matériel'!$M7&gt;0,IF(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$F7="","",'2 Matériel'!$F7)),"")</f>
         <v/>
       </c>
-      <c r="G17" s="40">
+      <c r="G17" s="42">
         <f>IF('2 Matériel'!$M7&gt;0,IF(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$G7="","",'2 Matériel'!$G7)),"")</f>
         <v/>
       </c>
-      <c r="H17" s="40">
+      <c r="H17" s="42">
         <f>IF('2 Matériel'!$M7&gt;0,IF(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$H7="","",'2 Matériel'!$H7)),"")</f>
         <v/>
       </c>
-      <c r="I17" s="40">
+      <c r="I17" s="42">
         <f>IF('2 Matériel'!$M7&gt;0,IF(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$I7="","",'2 Matériel'!$I7)),"")</f>
         <v/>
       </c>
-      <c r="J17" s="40">
+      <c r="J17" s="42">
         <f>IF('2 Matériel'!$M7&gt;0,IF(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$J7="","",'2 Matériel'!$J7)),"")</f>
         <v/>
       </c>
-      <c r="K17" s="41">
-        <f>IF('2 Matériel'!$M7&gt;0,'2 Matériel'!$B7&amp;IF(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$14="Oui"),IF('2 Matériel'!$B7="","","  ·  ")&amp;INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
+      <c r="K17" s="43">
+        <f>IF('2 Matériel'!$M7&gt;0,IF(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
-      <c r="B18" s="15">
+      <c r="B18" s="16">
         <f>IF('2 Matériel'!$M8&gt;0,'2 Matériel'!$A8,"")</f>
         <v/>
       </c>
-      <c r="C18" s="38">
+      <c r="C18" s="40">
         <f>IF('2 Matériel'!$M8&gt;0,'2 Matériel'!$C8,"")</f>
         <v/>
       </c>
-      <c r="D18" s="39">
+      <c r="D18" s="41">
         <f>IF('2 Matériel'!$M8&gt;0,'2 Matériel'!$M8,"")</f>
         <v/>
       </c>
-      <c r="E18" s="40">
+      <c r="E18" s="42">
         <f>IF('2 Matériel'!$M8&gt;0,IF(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$E8="","",'2 Matériel'!$E8)),"")</f>
         <v/>
       </c>
-      <c r="F18" s="40">
+      <c r="F18" s="42">
         <f>IF('2 Matériel'!$M8&gt;0,IF(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$F8="","",'2 Matériel'!$F8)),"")</f>
         <v/>
       </c>
-      <c r="G18" s="40">
+      <c r="G18" s="42">
         <f>IF('2 Matériel'!$M8&gt;0,IF(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$G8="","",'2 Matériel'!$G8)),"")</f>
         <v/>
       </c>
-      <c r="H18" s="40">
+      <c r="H18" s="42">
         <f>IF('2 Matériel'!$M8&gt;0,IF(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$H8="","",'2 Matériel'!$H8)),"")</f>
         <v/>
       </c>
-      <c r="I18" s="40">
+      <c r="I18" s="42">
         <f>IF('2 Matériel'!$M8&gt;0,IF(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$I8="","",'2 Matériel'!$I8)),"")</f>
         <v/>
       </c>
-      <c r="J18" s="40">
+      <c r="J18" s="42">
         <f>IF('2 Matériel'!$M8&gt;0,IF(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$J8="","",'2 Matériel'!$J8)),"")</f>
         <v/>
       </c>
-      <c r="K18" s="41">
-        <f>IF('2 Matériel'!$M8&gt;0,'2 Matériel'!$B8&amp;IF(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$14="Oui"),IF('2 Matériel'!$B8="","","  ·  ")&amp;INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
+      <c r="K18" s="43">
+        <f>IF('2 Matériel'!$M8&gt;0,IF(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="21" customHeight="1">
-      <c r="B19" s="15">
+      <c r="B19" s="16">
         <f>IF('2 Matériel'!$M9&gt;0,'2 Matériel'!$A9,"")</f>
         <v/>
       </c>
-      <c r="C19" s="38">
+      <c r="C19" s="40">
         <f>IF('2 Matériel'!$M9&gt;0,'2 Matériel'!$C9,"")</f>
         <v/>
       </c>
-      <c r="D19" s="39">
+      <c r="D19" s="41">
         <f>IF('2 Matériel'!$M9&gt;0,'2 Matériel'!$M9,"")</f>
         <v/>
       </c>
-      <c r="E19" s="40">
+      <c r="E19" s="42">
         <f>IF('2 Matériel'!$M9&gt;0,IF(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$E9="","",'2 Matériel'!$E9)),"")</f>
         <v/>
       </c>
-      <c r="F19" s="40">
+      <c r="F19" s="42">
         <f>IF('2 Matériel'!$M9&gt;0,IF(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$F9="","",'2 Matériel'!$F9)),"")</f>
         <v/>
       </c>
-      <c r="G19" s="40">
+      <c r="G19" s="42">
         <f>IF('2 Matériel'!$M9&gt;0,IF(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$G9="","",'2 Matériel'!$G9)),"")</f>
         <v/>
       </c>
-      <c r="H19" s="40">
+      <c r="H19" s="42">
         <f>IF('2 Matériel'!$M9&gt;0,IF(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$H9="","",'2 Matériel'!$H9)),"")</f>
         <v/>
       </c>
-      <c r="I19" s="40">
+      <c r="I19" s="42">
         <f>IF('2 Matériel'!$M9&gt;0,IF(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$I9="","",'2 Matériel'!$I9)),"")</f>
         <v/>
       </c>
-      <c r="J19" s="40">
+      <c r="J19" s="42">
         <f>IF('2 Matériel'!$M9&gt;0,IF(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$J9="","",'2 Matériel'!$J9)),"")</f>
         <v/>
       </c>
-      <c r="K19" s="41">
-        <f>IF('2 Matériel'!$M9&gt;0,'2 Matériel'!$B9&amp;IF(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$14="Oui"),IF('2 Matériel'!$B9="","","  ·  ")&amp;INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
+      <c r="K19" s="43">
+        <f>IF('2 Matériel'!$M9&gt;0,IF(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="21" customHeight="1">
-      <c r="B20" s="15">
+      <c r="B20" s="16">
         <f>IF('2 Matériel'!$M10&gt;0,'2 Matériel'!$A10,"")</f>
         <v/>
       </c>
-      <c r="C20" s="38">
+      <c r="C20" s="40">
         <f>IF('2 Matériel'!$M10&gt;0,'2 Matériel'!$C10,"")</f>
         <v/>
       </c>
-      <c r="D20" s="39">
+      <c r="D20" s="41">
         <f>IF('2 Matériel'!$M10&gt;0,'2 Matériel'!$M10,"")</f>
         <v/>
       </c>
-      <c r="E20" s="40">
+      <c r="E20" s="42">
         <f>IF('2 Matériel'!$M10&gt;0,IF(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$E10="","",'2 Matériel'!$E10)),"")</f>
         <v/>
       </c>
-      <c r="F20" s="40">
+      <c r="F20" s="42">
         <f>IF('2 Matériel'!$M10&gt;0,IF(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$F10="","",'2 Matériel'!$F10)),"")</f>
         <v/>
       </c>
-      <c r="G20" s="40">
+      <c r="G20" s="42">
         <f>IF('2 Matériel'!$M10&gt;0,IF(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$G10="","",'2 Matériel'!$G10)),"")</f>
         <v/>
       </c>
-      <c r="H20" s="40">
+      <c r="H20" s="42">
         <f>IF('2 Matériel'!$M10&gt;0,IF(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$H10="","",'2 Matériel'!$H10)),"")</f>
         <v/>
       </c>
-      <c r="I20" s="40">
+      <c r="I20" s="42">
         <f>IF('2 Matériel'!$M10&gt;0,IF(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$I10="","",'2 Matériel'!$I10)),"")</f>
         <v/>
       </c>
-      <c r="J20" s="40">
+      <c r="J20" s="42">
         <f>IF('2 Matériel'!$M10&gt;0,IF(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$J10="","",'2 Matériel'!$J10)),"")</f>
         <v/>
       </c>
-      <c r="K20" s="41">
-        <f>IF('2 Matériel'!$M10&gt;0,'2 Matériel'!$B10&amp;IF(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$14="Oui"),IF('2 Matériel'!$B10="","","  ·  ")&amp;INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
+      <c r="K20" s="43">
+        <f>IF('2 Matériel'!$M10&gt;0,IF(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="21" customHeight="1">
-      <c r="B21" s="15">
+      <c r="B21" s="16">
         <f>IF('2 Matériel'!$M11&gt;0,'2 Matériel'!$A11,"")</f>
         <v/>
       </c>
-      <c r="C21" s="38">
+      <c r="C21" s="40">
         <f>IF('2 Matériel'!$M11&gt;0,'2 Matériel'!$C11,"")</f>
         <v/>
       </c>
-      <c r="D21" s="39">
+      <c r="D21" s="41">
         <f>IF('2 Matériel'!$M11&gt;0,'2 Matériel'!$M11,"")</f>
         <v/>
       </c>
-      <c r="E21" s="40">
+      <c r="E21" s="42">
         <f>IF('2 Matériel'!$M11&gt;0,IF(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$E11="","",'2 Matériel'!$E11)),"")</f>
         <v/>
       </c>
-      <c r="F21" s="40">
+      <c r="F21" s="42">
         <f>IF('2 Matériel'!$M11&gt;0,IF(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$F11="","",'2 Matériel'!$F11)),"")</f>
         <v/>
       </c>
-      <c r="G21" s="40">
+      <c r="G21" s="42">
         <f>IF('2 Matériel'!$M11&gt;0,IF(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$G11="","",'2 Matériel'!$G11)),"")</f>
         <v/>
       </c>
-      <c r="H21" s="40">
+      <c r="H21" s="42">
         <f>IF('2 Matériel'!$M11&gt;0,IF(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$H11="","",'2 Matériel'!$H11)),"")</f>
         <v/>
       </c>
-      <c r="I21" s="40">
+      <c r="I21" s="42">
         <f>IF('2 Matériel'!$M11&gt;0,IF(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$I11="","",'2 Matériel'!$I11)),"")</f>
         <v/>
       </c>
-      <c r="J21" s="40">
+      <c r="J21" s="42">
         <f>IF('2 Matériel'!$M11&gt;0,IF(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$J11="","",'2 Matériel'!$J11)),"")</f>
         <v/>
       </c>
-      <c r="K21" s="41">
-        <f>IF('2 Matériel'!$M11&gt;0,'2 Matériel'!$B11&amp;IF(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$14="Oui"),IF('2 Matériel'!$B11="","","  ·  ")&amp;INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
+      <c r="K21" s="43">
+        <f>IF('2 Matériel'!$M11&gt;0,IF(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="21" customHeight="1">
-      <c r="B22" s="15">
+      <c r="B22" s="16">
         <f>IF('2 Matériel'!$M12&gt;0,'2 Matériel'!$A12,"")</f>
         <v/>
       </c>
-      <c r="C22" s="38">
+      <c r="C22" s="40">
         <f>IF('2 Matériel'!$M12&gt;0,'2 Matériel'!$C12,"")</f>
         <v/>
       </c>
-      <c r="D22" s="39">
+      <c r="D22" s="41">
         <f>IF('2 Matériel'!$M12&gt;0,'2 Matériel'!$M12,"")</f>
         <v/>
       </c>
-      <c r="E22" s="40">
+      <c r="E22" s="42">
         <f>IF('2 Matériel'!$M12&gt;0,IF(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$E12="","",'2 Matériel'!$E12)),"")</f>
         <v/>
       </c>
-      <c r="F22" s="40">
+      <c r="F22" s="42">
         <f>IF('2 Matériel'!$M12&gt;0,IF(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$F12="","",'2 Matériel'!$F12)),"")</f>
         <v/>
       </c>
-      <c r="G22" s="40">
+      <c r="G22" s="42">
         <f>IF('2 Matériel'!$M12&gt;0,IF(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$G12="","",'2 Matériel'!$G12)),"")</f>
         <v/>
       </c>
-      <c r="H22" s="40">
+      <c r="H22" s="42">
         <f>IF('2 Matériel'!$M12&gt;0,IF(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$H12="","",'2 Matériel'!$H12)),"")</f>
         <v/>
       </c>
-      <c r="I22" s="40">
+      <c r="I22" s="42">
         <f>IF('2 Matériel'!$M12&gt;0,IF(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$I12="","",'2 Matériel'!$I12)),"")</f>
         <v/>
       </c>
-      <c r="J22" s="40">
+      <c r="J22" s="42">
         <f>IF('2 Matériel'!$M12&gt;0,IF(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$J12="","",'2 Matériel'!$J12)),"")</f>
         <v/>
       </c>
-      <c r="K22" s="41">
-        <f>IF('2 Matériel'!$M12&gt;0,'2 Matériel'!$B12&amp;IF(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$14="Oui"),IF('2 Matériel'!$B12="","","  ·  ")&amp;INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
+      <c r="K22" s="43">
+        <f>IF('2 Matériel'!$M12&gt;0,IF(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="21" customHeight="1">
-      <c r="B23" s="15">
+      <c r="B23" s="16">
         <f>IF('2 Matériel'!$M13&gt;0,'2 Matériel'!$A13,"")</f>
         <v/>
       </c>
-      <c r="C23" s="38">
+      <c r="C23" s="40">
         <f>IF('2 Matériel'!$M13&gt;0,'2 Matériel'!$C13,"")</f>
         <v/>
       </c>
-      <c r="D23" s="39">
+      <c r="D23" s="41">
         <f>IF('2 Matériel'!$M13&gt;0,'2 Matériel'!$M13,"")</f>
         <v/>
       </c>
-      <c r="E23" s="40">
+      <c r="E23" s="42">
         <f>IF('2 Matériel'!$M13&gt;0,IF(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$E13="","",'2 Matériel'!$E13)),"")</f>
         <v/>
       </c>
-      <c r="F23" s="40">
+      <c r="F23" s="42">
         <f>IF('2 Matériel'!$M13&gt;0,IF(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$F13="","",'2 Matériel'!$F13)),"")</f>
         <v/>
       </c>
-      <c r="G23" s="40">
+      <c r="G23" s="42">
         <f>IF('2 Matériel'!$M13&gt;0,IF(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$G13="","",'2 Matériel'!$G13)),"")</f>
         <v/>
       </c>
-      <c r="H23" s="40">
+      <c r="H23" s="42">
         <f>IF('2 Matériel'!$M13&gt;0,IF(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$H13="","",'2 Matériel'!$H13)),"")</f>
         <v/>
       </c>
-      <c r="I23" s="40">
+      <c r="I23" s="42">
         <f>IF('2 Matériel'!$M13&gt;0,IF(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$I13="","",'2 Matériel'!$I13)),"")</f>
         <v/>
       </c>
-      <c r="J23" s="40">
+      <c r="J23" s="42">
         <f>IF('2 Matériel'!$M13&gt;0,IF(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$J13="","",'2 Matériel'!$J13)),"")</f>
         <v/>
       </c>
-      <c r="K23" s="41">
-        <f>IF('2 Matériel'!$M13&gt;0,'2 Matériel'!$B13&amp;IF(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$14="Oui"),IF('2 Matériel'!$B13="","","  ·  ")&amp;INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
+      <c r="K23" s="43">
+        <f>IF('2 Matériel'!$M13&gt;0,IF(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="21" customHeight="1">
-      <c r="B24" s="15">
+      <c r="B24" s="16">
         <f>IF('2 Matériel'!$M14&gt;0,'2 Matériel'!$A14,"")</f>
         <v/>
       </c>
-      <c r="C24" s="38">
+      <c r="C24" s="40">
         <f>IF('2 Matériel'!$M14&gt;0,'2 Matériel'!$C14,"")</f>
         <v/>
       </c>
-      <c r="D24" s="39">
+      <c r="D24" s="41">
         <f>IF('2 Matériel'!$M14&gt;0,'2 Matériel'!$M14,"")</f>
         <v/>
       </c>
-      <c r="E24" s="40">
+      <c r="E24" s="42">
         <f>IF('2 Matériel'!$M14&gt;0,IF(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$E14="","",'2 Matériel'!$E14)),"")</f>
         <v/>
       </c>
-      <c r="F24" s="40">
+      <c r="F24" s="42">
         <f>IF('2 Matériel'!$M14&gt;0,IF(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$F14="","",'2 Matériel'!$F14)),"")</f>
         <v/>
       </c>
-      <c r="G24" s="40">
+      <c r="G24" s="42">
         <f>IF('2 Matériel'!$M14&gt;0,IF(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$G14="","",'2 Matériel'!$G14)),"")</f>
         <v/>
       </c>
-      <c r="H24" s="40">
+      <c r="H24" s="42">
         <f>IF('2 Matériel'!$M14&gt;0,IF(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$H14="","",'2 Matériel'!$H14)),"")</f>
         <v/>
       </c>
-      <c r="I24" s="40">
+      <c r="I24" s="42">
         <f>IF('2 Matériel'!$M14&gt;0,IF(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$I14="","",'2 Matériel'!$I14)),"")</f>
         <v/>
       </c>
-      <c r="J24" s="40">
+      <c r="J24" s="42">
         <f>IF('2 Matériel'!$M14&gt;0,IF(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$J14="","",'2 Matériel'!$J14)),"")</f>
         <v/>
       </c>
-      <c r="K24" s="41">
-        <f>IF('2 Matériel'!$M14&gt;0,'2 Matériel'!$B14&amp;IF(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$14="Oui"),IF('2 Matériel'!$B14="","","  ·  ")&amp;INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
+      <c r="K24" s="43">
+        <f>IF('2 Matériel'!$M14&gt;0,IF(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1">
-      <c r="B25" s="15">
+      <c r="B25" s="16">
         <f>IF('2 Matériel'!$M15&gt;0,'2 Matériel'!$A15,"")</f>
         <v/>
       </c>
-      <c r="C25" s="38">
+      <c r="C25" s="40">
         <f>IF('2 Matériel'!$M15&gt;0,'2 Matériel'!$C15,"")</f>
         <v/>
       </c>
-      <c r="D25" s="39">
+      <c r="D25" s="41">
         <f>IF('2 Matériel'!$M15&gt;0,'2 Matériel'!$M15,"")</f>
         <v/>
       </c>
-      <c r="E25" s="40">
+      <c r="E25" s="42">
         <f>IF('2 Matériel'!$M15&gt;0,IF(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$E15="","",'2 Matériel'!$E15)),"")</f>
         <v/>
       </c>
-      <c r="F25" s="40">
+      <c r="F25" s="42">
         <f>IF('2 Matériel'!$M15&gt;0,IF(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$F15="","",'2 Matériel'!$F15)),"")</f>
         <v/>
       </c>
-      <c r="G25" s="40">
+      <c r="G25" s="42">
         <f>IF('2 Matériel'!$M15&gt;0,IF(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$G15="","",'2 Matériel'!$G15)),"")</f>
         <v/>
       </c>
-      <c r="H25" s="40">
+      <c r="H25" s="42">
         <f>IF('2 Matériel'!$M15&gt;0,IF(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$H15="","",'2 Matériel'!$H15)),"")</f>
         <v/>
       </c>
-      <c r="I25" s="40">
+      <c r="I25" s="42">
         <f>IF('2 Matériel'!$M15&gt;0,IF(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$I15="","",'2 Matériel'!$I15)),"")</f>
         <v/>
       </c>
-      <c r="J25" s="40">
+      <c r="J25" s="42">
         <f>IF('2 Matériel'!$M15&gt;0,IF(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$J15="","",'2 Matériel'!$J15)),"")</f>
         <v/>
       </c>
-      <c r="K25" s="41">
-        <f>IF('2 Matériel'!$M15&gt;0,'2 Matériel'!$B15&amp;IF(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$14="Oui"),IF('2 Matériel'!$B15="","","  ·  ")&amp;INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
+      <c r="K25" s="43">
+        <f>IF('2 Matériel'!$M15&gt;0,IF(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="21" customHeight="1">
-      <c r="B26" s="15">
+      <c r="B26" s="16">
         <f>IF('2 Matériel'!$M16&gt;0,'2 Matériel'!$A16,"")</f>
         <v/>
       </c>
-      <c r="C26" s="38">
+      <c r="C26" s="40">
         <f>IF('2 Matériel'!$M16&gt;0,'2 Matériel'!$C16,"")</f>
         <v/>
       </c>
-      <c r="D26" s="39">
+      <c r="D26" s="41">
         <f>IF('2 Matériel'!$M16&gt;0,'2 Matériel'!$M16,"")</f>
         <v/>
       </c>
-      <c r="E26" s="40">
+      <c r="E26" s="42">
         <f>IF('2 Matériel'!$M16&gt;0,IF(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$E16="","",'2 Matériel'!$E16)),"")</f>
         <v/>
       </c>
-      <c r="F26" s="40">
+      <c r="F26" s="42">
         <f>IF('2 Matériel'!$M16&gt;0,IF(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$F16="","",'2 Matériel'!$F16)),"")</f>
         <v/>
       </c>
-      <c r="G26" s="40">
+      <c r="G26" s="42">
         <f>IF('2 Matériel'!$M16&gt;0,IF(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$G16="","",'2 Matériel'!$G16)),"")</f>
         <v/>
       </c>
-      <c r="H26" s="40">
+      <c r="H26" s="42">
         <f>IF('2 Matériel'!$M16&gt;0,IF(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$H16="","",'2 Matériel'!$H16)),"")</f>
         <v/>
       </c>
-      <c r="I26" s="40">
+      <c r="I26" s="42">
         <f>IF('2 Matériel'!$M16&gt;0,IF(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$I16="","",'2 Matériel'!$I16)),"")</f>
         <v/>
       </c>
-      <c r="J26" s="40">
+      <c r="J26" s="42">
         <f>IF('2 Matériel'!$M16&gt;0,IF(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$J16="","",'2 Matériel'!$J16)),"")</f>
         <v/>
       </c>
-      <c r="K26" s="41">
-        <f>IF('2 Matériel'!$M16&gt;0,'2 Matériel'!$B16&amp;IF(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$14="Oui"),IF('2 Matériel'!$B16="","","  ·  ")&amp;INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
+      <c r="K26" s="43">
+        <f>IF('2 Matériel'!$M16&gt;0,IF(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="21" customHeight="1">
-      <c r="B27" s="15">
+      <c r="B27" s="16">
         <f>IF('2 Matériel'!$M17&gt;0,'2 Matériel'!$A17,"")</f>
         <v/>
       </c>
-      <c r="C27" s="38">
+      <c r="C27" s="40">
         <f>IF('2 Matériel'!$M17&gt;0,'2 Matériel'!$C17,"")</f>
         <v/>
       </c>
-      <c r="D27" s="39">
+      <c r="D27" s="41">
         <f>IF('2 Matériel'!$M17&gt;0,'2 Matériel'!$M17,"")</f>
         <v/>
       </c>
-      <c r="E27" s="40">
+      <c r="E27" s="42">
         <f>IF('2 Matériel'!$M17&gt;0,IF(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$E17="","",'2 Matériel'!$E17)),"")</f>
         <v/>
       </c>
-      <c r="F27" s="40">
+      <c r="F27" s="42">
         <f>IF('2 Matériel'!$M17&gt;0,IF(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$F17="","",'2 Matériel'!$F17)),"")</f>
         <v/>
       </c>
-      <c r="G27" s="40">
+      <c r="G27" s="42">
         <f>IF('2 Matériel'!$M17&gt;0,IF(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$G17="","",'2 Matériel'!$G17)),"")</f>
         <v/>
       </c>
-      <c r="H27" s="40">
+      <c r="H27" s="42">
         <f>IF('2 Matériel'!$M17&gt;0,IF(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$H17="","",'2 Matériel'!$H17)),"")</f>
         <v/>
       </c>
-      <c r="I27" s="40">
+      <c r="I27" s="42">
         <f>IF('2 Matériel'!$M17&gt;0,IF(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$I17="","",'2 Matériel'!$I17)),"")</f>
         <v/>
       </c>
-      <c r="J27" s="40">
+      <c r="J27" s="42">
         <f>IF('2 Matériel'!$M17&gt;0,IF(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$J17="","",'2 Matériel'!$J17)),"")</f>
         <v/>
       </c>
-      <c r="K27" s="41">
-        <f>IF('2 Matériel'!$M17&gt;0,'2 Matériel'!$B17&amp;IF(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$14="Oui"),IF('2 Matériel'!$B17="","","  ·  ")&amp;INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
+      <c r="K27" s="43">
+        <f>IF('2 Matériel'!$M17&gt;0,IF(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="21" customHeight="1">
-      <c r="B28" s="15">
+      <c r="B28" s="16">
         <f>IF('2 Matériel'!$M18&gt;0,'2 Matériel'!$A18,"")</f>
         <v/>
       </c>
-      <c r="C28" s="38">
+      <c r="C28" s="40">
         <f>IF('2 Matériel'!$M18&gt;0,'2 Matériel'!$C18,"")</f>
         <v/>
       </c>
-      <c r="D28" s="39">
+      <c r="D28" s="41">
         <f>IF('2 Matériel'!$M18&gt;0,'2 Matériel'!$M18,"")</f>
         <v/>
       </c>
-      <c r="E28" s="40">
+      <c r="E28" s="42">
         <f>IF('2 Matériel'!$M18&gt;0,IF(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$E18="","",'2 Matériel'!$E18)),"")</f>
         <v/>
       </c>
-      <c r="F28" s="40">
+      <c r="F28" s="42">
         <f>IF('2 Matériel'!$M18&gt;0,IF(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$F18="","",'2 Matériel'!$F18)),"")</f>
         <v/>
       </c>
-      <c r="G28" s="40">
+      <c r="G28" s="42">
         <f>IF('2 Matériel'!$M18&gt;0,IF(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$G18="","",'2 Matériel'!$G18)),"")</f>
         <v/>
       </c>
-      <c r="H28" s="40">
+      <c r="H28" s="42">
         <f>IF('2 Matériel'!$M18&gt;0,IF(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$H18="","",'2 Matériel'!$H18)),"")</f>
         <v/>
       </c>
-      <c r="I28" s="40">
+      <c r="I28" s="42">
         <f>IF('2 Matériel'!$M18&gt;0,IF(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$I18="","",'2 Matériel'!$I18)),"")</f>
         <v/>
       </c>
-      <c r="J28" s="40">
+      <c r="J28" s="42">
         <f>IF('2 Matériel'!$M18&gt;0,IF(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$J18="","",'2 Matériel'!$J18)),"")</f>
         <v/>
       </c>
-      <c r="K28" s="41">
-        <f>IF('2 Matériel'!$M18&gt;0,'2 Matériel'!$B18&amp;IF(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$14="Oui"),IF('2 Matériel'!$B18="","","  ·  ")&amp;INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
+      <c r="K28" s="43">
+        <f>IF('2 Matériel'!$M18&gt;0,IF(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="21" customHeight="1">
-      <c r="B29" s="15">
+      <c r="B29" s="16">
         <f>IF('2 Matériel'!$M19&gt;0,'2 Matériel'!$A19,"")</f>
         <v/>
       </c>
-      <c r="C29" s="38">
+      <c r="C29" s="40">
         <f>IF('2 Matériel'!$M19&gt;0,'2 Matériel'!$C19,"")</f>
         <v/>
       </c>
-      <c r="D29" s="39">
+      <c r="D29" s="41">
         <f>IF('2 Matériel'!$M19&gt;0,'2 Matériel'!$M19,"")</f>
         <v/>
       </c>
-      <c r="E29" s="40">
+      <c r="E29" s="42">
         <f>IF('2 Matériel'!$M19&gt;0,IF(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$E19="","",'2 Matériel'!$E19)),"")</f>
         <v/>
       </c>
-      <c r="F29" s="40">
+      <c r="F29" s="42">
         <f>IF('2 Matériel'!$M19&gt;0,IF(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$F19="","",'2 Matériel'!$F19)),"")</f>
         <v/>
       </c>
-      <c r="G29" s="40">
+      <c r="G29" s="42">
         <f>IF('2 Matériel'!$M19&gt;0,IF(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$G19="","",'2 Matériel'!$G19)),"")</f>
         <v/>
       </c>
-      <c r="H29" s="40">
+      <c r="H29" s="42">
         <f>IF('2 Matériel'!$M19&gt;0,IF(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$H19="","",'2 Matériel'!$H19)),"")</f>
         <v/>
       </c>
-      <c r="I29" s="40">
+      <c r="I29" s="42">
         <f>IF('2 Matériel'!$M19&gt;0,IF(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$I19="","",'2 Matériel'!$I19)),"")</f>
         <v/>
       </c>
-      <c r="J29" s="40">
+      <c r="J29" s="42">
         <f>IF('2 Matériel'!$M19&gt;0,IF(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$J19="","",'2 Matériel'!$J19)),"")</f>
         <v/>
       </c>
-      <c r="K29" s="41">
-        <f>IF('2 Matériel'!$M19&gt;0,'2 Matériel'!$B19&amp;IF(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$14="Oui"),IF('2 Matériel'!$B19="","","  ·  ")&amp;INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
+      <c r="K29" s="43">
+        <f>IF('2 Matériel'!$M19&gt;0,IF(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="30" hidden="1" outlineLevel="1" ht="21" customHeight="1">
-      <c r="B30" s="15">
+      <c r="B30" s="16">
         <f>IF('2 Matériel'!$M20&gt;0,'2 Matériel'!$A20,"")</f>
         <v/>
       </c>
-      <c r="C30" s="38">
+      <c r="C30" s="40">
         <f>IF('2 Matériel'!$M20&gt;0,'2 Matériel'!$C20,"")</f>
         <v/>
       </c>
-      <c r="D30" s="39">
+      <c r="D30" s="41">
         <f>IF('2 Matériel'!$M20&gt;0,'2 Matériel'!$M20,"")</f>
         <v/>
       </c>
-      <c r="E30" s="40">
+      <c r="E30" s="42">
         <f>IF('2 Matériel'!$M20&gt;0,IF(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$E20="","",'2 Matériel'!$E20)),"")</f>
         <v/>
       </c>
-      <c r="F30" s="40">
+      <c r="F30" s="42">
         <f>IF('2 Matériel'!$M20&gt;0,IF(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$F20="","",'2 Matériel'!$F20)),"")</f>
         <v/>
       </c>
-      <c r="G30" s="40">
+      <c r="G30" s="42">
         <f>IF('2 Matériel'!$M20&gt;0,IF(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$G20="","",'2 Matériel'!$G20)),"")</f>
         <v/>
       </c>
-      <c r="H30" s="40">
+      <c r="H30" s="42">
         <f>IF('2 Matériel'!$M20&gt;0,IF(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$H20="","",'2 Matériel'!$H20)),"")</f>
         <v/>
       </c>
-      <c r="I30" s="40">
+      <c r="I30" s="42">
         <f>IF('2 Matériel'!$M20&gt;0,IF(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$I20="","",'2 Matériel'!$I20)),"")</f>
         <v/>
       </c>
-      <c r="J30" s="40">
+      <c r="J30" s="42">
         <f>IF('2 Matériel'!$M20&gt;0,IF(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$J20="","",'2 Matériel'!$J20)),"")</f>
         <v/>
       </c>
-      <c r="K30" s="41">
-        <f>IF('2 Matériel'!$M20&gt;0,'2 Matériel'!$B20&amp;IF(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$14="Oui"),IF('2 Matériel'!$B20="","","  ·  ")&amp;INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
+      <c r="K30" s="43">
+        <f>IF('2 Matériel'!$M20&gt;0,IF(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="31" hidden="1" outlineLevel="1" ht="21" customHeight="1">
-      <c r="B31" s="15">
+      <c r="B31" s="16">
         <f>IF('2 Matériel'!$M21&gt;0,'2 Matériel'!$A21,"")</f>
         <v/>
       </c>
-      <c r="C31" s="38">
+      <c r="C31" s="40">
         <f>IF('2 Matériel'!$M21&gt;0,'2 Matériel'!$C21,"")</f>
         <v/>
       </c>
-      <c r="D31" s="39">
+      <c r="D31" s="41">
         <f>IF('2 Matériel'!$M21&gt;0,'2 Matériel'!$M21,"")</f>
         <v/>
       </c>
-      <c r="E31" s="40">
+      <c r="E31" s="42">
         <f>IF('2 Matériel'!$M21&gt;0,IF(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$E21="","",'2 Matériel'!$E21)),"")</f>
         <v/>
       </c>
-      <c r="F31" s="40">
+      <c r="F31" s="42">
         <f>IF('2 Matériel'!$M21&gt;0,IF(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$F21="","",'2 Matériel'!$F21)),"")</f>
         <v/>
       </c>
-      <c r="G31" s="40">
+      <c r="G31" s="42">
         <f>IF('2 Matériel'!$M21&gt;0,IF(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$G21="","",'2 Matériel'!$G21)),"")</f>
         <v/>
       </c>
-      <c r="H31" s="40">
+      <c r="H31" s="42">
         <f>IF('2 Matériel'!$M21&gt;0,IF(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$H21="","",'2 Matériel'!$H21)),"")</f>
         <v/>
       </c>
-      <c r="I31" s="40">
+      <c r="I31" s="42">
         <f>IF('2 Matériel'!$M21&gt;0,IF(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$I21="","",'2 Matériel'!$I21)),"")</f>
         <v/>
       </c>
-      <c r="J31" s="40">
+      <c r="J31" s="42">
         <f>IF('2 Matériel'!$M21&gt;0,IF(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$J21="","",'2 Matériel'!$J21)),"")</f>
         <v/>
       </c>
-      <c r="K31" s="41">
-        <f>IF('2 Matériel'!$M21&gt;0,'2 Matériel'!$B21&amp;IF(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$14="Oui"),IF('2 Matériel'!$B21="","","  ·  ")&amp;INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
+      <c r="K31" s="43">
+        <f>IF('2 Matériel'!$M21&gt;0,IF(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="32" hidden="1" outlineLevel="1" ht="21" customHeight="1">
-      <c r="B32" s="15">
+      <c r="B32" s="16">
         <f>IF('2 Matériel'!$M22&gt;0,'2 Matériel'!$A22,"")</f>
         <v/>
       </c>
-      <c r="C32" s="38">
+      <c r="C32" s="40">
         <f>IF('2 Matériel'!$M22&gt;0,'2 Matériel'!$C22,"")</f>
         <v/>
       </c>
-      <c r="D32" s="39">
+      <c r="D32" s="41">
         <f>IF('2 Matériel'!$M22&gt;0,'2 Matériel'!$M22,"")</f>
         <v/>
       </c>
-      <c r="E32" s="40">
+      <c r="E32" s="42">
         <f>IF('2 Matériel'!$M22&gt;0,IF(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$E22="","",'2 Matériel'!$E22)),"")</f>
         <v/>
       </c>
-      <c r="F32" s="40">
+      <c r="F32" s="42">
         <f>IF('2 Matériel'!$M22&gt;0,IF(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$F22="","",'2 Matériel'!$F22)),"")</f>
         <v/>
       </c>
-      <c r="G32" s="40">
+      <c r="G32" s="42">
         <f>IF('2 Matériel'!$M22&gt;0,IF(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$G22="","",'2 Matériel'!$G22)),"")</f>
         <v/>
       </c>
-      <c r="H32" s="40">
+      <c r="H32" s="42">
         <f>IF('2 Matériel'!$M22&gt;0,IF(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$H22="","",'2 Matériel'!$H22)),"")</f>
         <v/>
       </c>
-      <c r="I32" s="40">
+      <c r="I32" s="42">
         <f>IF('2 Matériel'!$M22&gt;0,IF(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$I22="","",'2 Matériel'!$I22)),"")</f>
         <v/>
       </c>
-      <c r="J32" s="40">
+      <c r="J32" s="42">
         <f>IF('2 Matériel'!$M22&gt;0,IF(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$J22="","",'2 Matériel'!$J22)),"")</f>
         <v/>
       </c>
-      <c r="K32" s="41">
-        <f>IF('2 Matériel'!$M22&gt;0,'2 Matériel'!$B22&amp;IF(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$14="Oui"),IF('2 Matériel'!$B22="","","  ·  ")&amp;INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
+      <c r="K32" s="43">
+        <f>IF('2 Matériel'!$M22&gt;0,IF(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="33" hidden="1" outlineLevel="1" ht="21" customHeight="1">
-      <c r="B33" s="15">
+      <c r="B33" s="16">
         <f>IF('2 Matériel'!$M23&gt;0,'2 Matériel'!$A23,"")</f>
         <v/>
       </c>
-      <c r="C33" s="38">
+      <c r="C33" s="40">
         <f>IF('2 Matériel'!$M23&gt;0,'2 Matériel'!$C23,"")</f>
         <v/>
       </c>
-      <c r="D33" s="39">
+      <c r="D33" s="41">
         <f>IF('2 Matériel'!$M23&gt;0,'2 Matériel'!$M23,"")</f>
         <v/>
       </c>
-      <c r="E33" s="40">
+      <c r="E33" s="42">
         <f>IF('2 Matériel'!$M23&gt;0,IF(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$E23="","",'2 Matériel'!$E23)),"")</f>
         <v/>
       </c>
-      <c r="F33" s="40">
+      <c r="F33" s="42">
         <f>IF('2 Matériel'!$M23&gt;0,IF(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$F23="","",'2 Matériel'!$F23)),"")</f>
         <v/>
       </c>
-      <c r="G33" s="40">
+      <c r="G33" s="42">
         <f>IF('2 Matériel'!$M23&gt;0,IF(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$G23="","",'2 Matériel'!$G23)),"")</f>
         <v/>
       </c>
-      <c r="H33" s="40">
+      <c r="H33" s="42">
         <f>IF('2 Matériel'!$M23&gt;0,IF(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$H23="","",'2 Matériel'!$H23)),"")</f>
         <v/>
       </c>
-      <c r="I33" s="40">
+      <c r="I33" s="42">
         <f>IF('2 Matériel'!$M23&gt;0,IF(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$I23="","",'2 Matériel'!$I23)),"")</f>
         <v/>
       </c>
-      <c r="J33" s="40">
+      <c r="J33" s="42">
         <f>IF('2 Matériel'!$M23&gt;0,IF(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$J23="","",'2 Matériel'!$J23)),"")</f>
         <v/>
       </c>
-      <c r="K33" s="41">
-        <f>IF('2 Matériel'!$M23&gt;0,'2 Matériel'!$B23&amp;IF(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$14="Oui"),IF('2 Matériel'!$B23="","","  ·  ")&amp;INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
+      <c r="K33" s="43">
+        <f>IF('2 Matériel'!$M23&gt;0,IF(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="34" hidden="1" outlineLevel="1" ht="21" customHeight="1">
-      <c r="B34" s="15">
+      <c r="B34" s="16">
         <f>IF('2 Matériel'!$M24&gt;0,'2 Matériel'!$A24,"")</f>
         <v/>
       </c>
-      <c r="C34" s="38">
+      <c r="C34" s="40">
         <f>IF('2 Matériel'!$M24&gt;0,'2 Matériel'!$C24,"")</f>
         <v/>
       </c>
-      <c r="D34" s="39">
+      <c r="D34" s="41">
         <f>IF('2 Matériel'!$M24&gt;0,'2 Matériel'!$M24,"")</f>
         <v/>
       </c>
-      <c r="E34" s="40">
+      <c r="E34" s="42">
         <f>IF('2 Matériel'!$M24&gt;0,IF(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$E24="","",'2 Matériel'!$E24)),"")</f>
         <v/>
       </c>
-      <c r="F34" s="40">
+      <c r="F34" s="42">
         <f>IF('2 Matériel'!$M24&gt;0,IF(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$F24="","",'2 Matériel'!$F24)),"")</f>
         <v/>
       </c>
-      <c r="G34" s="40">
+      <c r="G34" s="42">
         <f>IF('2 Matériel'!$M24&gt;0,IF(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$G24="","",'2 Matériel'!$G24)),"")</f>
         <v/>
       </c>
-      <c r="H34" s="40">
+      <c r="H34" s="42">
         <f>IF('2 Matériel'!$M24&gt;0,IF(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$H24="","",'2 Matériel'!$H24)),"")</f>
         <v/>
       </c>
-      <c r="I34" s="40">
+      <c r="I34" s="42">
         <f>IF('2 Matériel'!$M24&gt;0,IF(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$I24="","",'2 Matériel'!$I24)),"")</f>
         <v/>
       </c>
-      <c r="J34" s="40">
+      <c r="J34" s="42">
         <f>IF('2 Matériel'!$M24&gt;0,IF(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$J24="","",'2 Matériel'!$J24)),"")</f>
         <v/>
       </c>
-      <c r="K34" s="41">
-        <f>IF('2 Matériel'!$M24&gt;0,'2 Matériel'!$B24&amp;IF(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$14="Oui"),IF('2 Matériel'!$B24="","","  ·  ")&amp;INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
+      <c r="K34" s="43">
+        <f>IF('2 Matériel'!$M24&gt;0,IF(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="35" hidden="1" outlineLevel="1" ht="21" customHeight="1">
-      <c r="B35" s="15">
+      <c r="B35" s="16">
         <f>IF('2 Matériel'!$M25&gt;0,'2 Matériel'!$A25,"")</f>
         <v/>
       </c>
-      <c r="C35" s="38">
+      <c r="C35" s="40">
         <f>IF('2 Matériel'!$M25&gt;0,'2 Matériel'!$C25,"")</f>
         <v/>
       </c>
-      <c r="D35" s="39">
+      <c r="D35" s="41">
         <f>IF('2 Matériel'!$M25&gt;0,'2 Matériel'!$M25,"")</f>
         <v/>
       </c>
-      <c r="E35" s="40">
+      <c r="E35" s="42">
         <f>IF('2 Matériel'!$M25&gt;0,IF(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$E25="","",'2 Matériel'!$E25)),"")</f>
         <v/>
       </c>
-      <c r="F35" s="40">
+      <c r="F35" s="42">
         <f>IF('2 Matériel'!$M25&gt;0,IF(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$F25="","",'2 Matériel'!$F25)),"")</f>
         <v/>
       </c>
-      <c r="G35" s="40">
+      <c r="G35" s="42">
         <f>IF('2 Matériel'!$M25&gt;0,IF(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$G25="","",'2 Matériel'!$G25)),"")</f>
         <v/>
       </c>
-      <c r="H35" s="40">
+      <c r="H35" s="42">
         <f>IF('2 Matériel'!$M25&gt;0,IF(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$H25="","",'2 Matériel'!$H25)),"")</f>
         <v/>
       </c>
-      <c r="I35" s="40">
+      <c r="I35" s="42">
         <f>IF('2 Matériel'!$M25&gt;0,IF(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$I25="","",'2 Matériel'!$I25)),"")</f>
         <v/>
       </c>
-      <c r="J35" s="40">
+      <c r="J35" s="42">
         <f>IF('2 Matériel'!$M25&gt;0,IF(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$J25="","",'2 Matériel'!$J25)),"")</f>
         <v/>
       </c>
-      <c r="K35" s="41">
-        <f>IF('2 Matériel'!$M25&gt;0,'2 Matériel'!$B25&amp;IF(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$14="Oui"),IF('2 Matériel'!$B25="","","  ·  ")&amp;INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
+      <c r="K35" s="43">
+        <f>IF('2 Matériel'!$M25&gt;0,IF(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="36" hidden="1" outlineLevel="1" ht="21" customHeight="1">
-      <c r="B36" s="15">
+      <c r="B36" s="16">
         <f>IF('2 Matériel'!$M26&gt;0,'2 Matériel'!$A26,"")</f>
         <v/>
       </c>
-      <c r="C36" s="38">
+      <c r="C36" s="40">
         <f>IF('2 Matériel'!$M26&gt;0,'2 Matériel'!$C26,"")</f>
         <v/>
       </c>
-      <c r="D36" s="39">
+      <c r="D36" s="41">
         <f>IF('2 Matériel'!$M26&gt;0,'2 Matériel'!$M26,"")</f>
         <v/>
       </c>
-      <c r="E36" s="40">
+      <c r="E36" s="42">
         <f>IF('2 Matériel'!$M26&gt;0,IF(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$E26="","",'2 Matériel'!$E26)),"")</f>
         <v/>
       </c>
-      <c r="F36" s="40">
+      <c r="F36" s="42">
         <f>IF('2 Matériel'!$M26&gt;0,IF(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$F26="","",'2 Matériel'!$F26)),"")</f>
         <v/>
       </c>
-      <c r="G36" s="40">
+      <c r="G36" s="42">
         <f>IF('2 Matériel'!$M26&gt;0,IF(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$G26="","",'2 Matériel'!$G26)),"")</f>
         <v/>
       </c>
-      <c r="H36" s="40">
+      <c r="H36" s="42">
         <f>IF('2 Matériel'!$M26&gt;0,IF(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$H26="","",'2 Matériel'!$H26)),"")</f>
         <v/>
       </c>
-      <c r="I36" s="40">
+      <c r="I36" s="42">
         <f>IF('2 Matériel'!$M26&gt;0,IF(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$I26="","",'2 Matériel'!$I26)),"")</f>
         <v/>
       </c>
-      <c r="J36" s="40">
+      <c r="J36" s="42">
         <f>IF('2 Matériel'!$M26&gt;0,IF(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$J26="","",'2 Matériel'!$J26)),"")</f>
         <v/>
       </c>
-      <c r="K36" s="41">
-        <f>IF('2 Matériel'!$M26&gt;0,'2 Matériel'!$B26&amp;IF(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$14="Oui"),IF('2 Matériel'!$B26="","","  ·  ")&amp;INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
+      <c r="K36" s="43">
+        <f>IF('2 Matériel'!$M26&gt;0,IF(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="37" hidden="1" outlineLevel="1" ht="21" customHeight="1">
-      <c r="B37" s="15">
+      <c r="B37" s="16">
         <f>IF('2 Matériel'!$M27&gt;0,'2 Matériel'!$A27,"")</f>
         <v/>
       </c>
-      <c r="C37" s="38">
+      <c r="C37" s="40">
         <f>IF('2 Matériel'!$M27&gt;0,'2 Matériel'!$C27,"")</f>
         <v/>
       </c>
-      <c r="D37" s="39">
+      <c r="D37" s="41">
         <f>IF('2 Matériel'!$M27&gt;0,'2 Matériel'!$M27,"")</f>
         <v/>
       </c>
-      <c r="E37" s="40">
+      <c r="E37" s="42">
         <f>IF('2 Matériel'!$M27&gt;0,IF(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$E27="","",'2 Matériel'!$E27)),"")</f>
         <v/>
       </c>
-      <c r="F37" s="40">
+      <c r="F37" s="42">
         <f>IF('2 Matériel'!$M27&gt;0,IF(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$F27="","",'2 Matériel'!$F27)),"")</f>
         <v/>
       </c>
-      <c r="G37" s="40">
+      <c r="G37" s="42">
         <f>IF('2 Matériel'!$M27&gt;0,IF(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$G27="","",'2 Matériel'!$G27)),"")</f>
         <v/>
       </c>
-      <c r="H37" s="40">
+      <c r="H37" s="42">
         <f>IF('2 Matériel'!$M27&gt;0,IF(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$H27="","",'2 Matériel'!$H27)),"")</f>
         <v/>
       </c>
-      <c r="I37" s="40">
+      <c r="I37" s="42">
         <f>IF('2 Matériel'!$M27&gt;0,IF(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$I27="","",'2 Matériel'!$I27)),"")</f>
         <v/>
       </c>
-      <c r="J37" s="40">
+      <c r="J37" s="42">
         <f>IF('2 Matériel'!$M27&gt;0,IF(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$J27="","",'2 Matériel'!$J27)),"")</f>
         <v/>
       </c>
-      <c r="K37" s="41">
-        <f>IF('2 Matériel'!$M27&gt;0,'2 Matériel'!$B27&amp;IF(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$14="Oui"),IF('2 Matériel'!$B27="","","  ·  ")&amp;INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
+      <c r="K37" s="43">
+        <f>IF('2 Matériel'!$M27&gt;0,IF(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="38" hidden="1" outlineLevel="1" ht="21" customHeight="1">
-      <c r="B38" s="15">
+      <c r="B38" s="16">
         <f>IF('2 Matériel'!$M28&gt;0,'2 Matériel'!$A28,"")</f>
         <v/>
       </c>
-      <c r="C38" s="38">
+      <c r="C38" s="40">
         <f>IF('2 Matériel'!$M28&gt;0,'2 Matériel'!$C28,"")</f>
         <v/>
       </c>
-      <c r="D38" s="39">
+      <c r="D38" s="41">
         <f>IF('2 Matériel'!$M28&gt;0,'2 Matériel'!$M28,"")</f>
         <v/>
       </c>
-      <c r="E38" s="40">
+      <c r="E38" s="42">
         <f>IF('2 Matériel'!$M28&gt;0,IF(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$E28="","",'2 Matériel'!$E28)),"")</f>
         <v/>
       </c>
-      <c r="F38" s="40">
+      <c r="F38" s="42">
         <f>IF('2 Matériel'!$M28&gt;0,IF(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$F28="","",'2 Matériel'!$F28)),"")</f>
         <v/>
       </c>
-      <c r="G38" s="40">
+      <c r="G38" s="42">
         <f>IF('2 Matériel'!$M28&gt;0,IF(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$G28="","",'2 Matériel'!$G28)),"")</f>
         <v/>
       </c>
-      <c r="H38" s="40">
+      <c r="H38" s="42">
         <f>IF('2 Matériel'!$M28&gt;0,IF(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$H28="","",'2 Matériel'!$H28)),"")</f>
         <v/>
       </c>
-      <c r="I38" s="40">
+      <c r="I38" s="42">
         <f>IF('2 Matériel'!$M28&gt;0,IF(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$I28="","",'2 Matériel'!$I28)),"")</f>
         <v/>
       </c>
-      <c r="J38" s="40">
+      <c r="J38" s="42">
         <f>IF('2 Matériel'!$M28&gt;0,IF(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$J28="","",'2 Matériel'!$J28)),"")</f>
         <v/>
       </c>
-      <c r="K38" s="41">
-        <f>IF('2 Matériel'!$M28&gt;0,'2 Matériel'!$B28&amp;IF(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$14="Oui"),IF('2 Matériel'!$B28="","","  ·  ")&amp;INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
+      <c r="K38" s="43">
+        <f>IF('2 Matériel'!$M28&gt;0,IF(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="39" hidden="1" outlineLevel="1" ht="21" customHeight="1">
-      <c r="B39" s="15">
+      <c r="B39" s="16">
         <f>IF('2 Matériel'!$M29&gt;0,'2 Matériel'!$A29,"")</f>
         <v/>
       </c>
-      <c r="C39" s="38">
+      <c r="C39" s="40">
         <f>IF('2 Matériel'!$M29&gt;0,'2 Matériel'!$C29,"")</f>
         <v/>
       </c>
-      <c r="D39" s="39">
+      <c r="D39" s="41">
         <f>IF('2 Matériel'!$M29&gt;0,'2 Matériel'!$M29,"")</f>
         <v/>
       </c>
-      <c r="E39" s="40">
+      <c r="E39" s="42">
         <f>IF('2 Matériel'!$M29&gt;0,IF(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$E29="","",'2 Matériel'!$E29)),"")</f>
         <v/>
       </c>
-      <c r="F39" s="40">
+      <c r="F39" s="42">
         <f>IF('2 Matériel'!$M29&gt;0,IF(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$F29="","",'2 Matériel'!$F29)),"")</f>
         <v/>
       </c>
-      <c r="G39" s="40">
+      <c r="G39" s="42">
         <f>IF('2 Matériel'!$M29&gt;0,IF(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$G29="","",'2 Matériel'!$G29)),"")</f>
         <v/>
       </c>
-      <c r="H39" s="40">
+      <c r="H39" s="42">
         <f>IF('2 Matériel'!$M29&gt;0,IF(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$H29="","",'2 Matériel'!$H29)),"")</f>
         <v/>
       </c>
-      <c r="I39" s="40">
+      <c r="I39" s="42">
         <f>IF('2 Matériel'!$M29&gt;0,IF(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$I29="","",'2 Matériel'!$I29)),"")</f>
         <v/>
       </c>
-      <c r="J39" s="40">
+      <c r="J39" s="42">
         <f>IF('2 Matériel'!$M29&gt;0,IF(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl",Textes!$A$2:$A$54,0),Listes!$H$1),IF('2 Matériel'!$J29="","",'2 Matériel'!$J29)),"")</f>
         <v/>
       </c>
-      <c r="K39" s="41">
-        <f>IF('2 Matériel'!$M29&gt;0,'2 Matériel'!$B29&amp;IF(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$14="Oui"),IF('2 Matériel'!$B29="","","  ·  ")&amp;INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
+      <c r="K39" s="43">
+        <f>IF('2 Matériel'!$M29&gt;0,IF(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$14="Oui"),INDEX(Textes!$B$2:$C$54,MATCH("incl_long",Textes!$A$2:$A$54,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="B40" s="42">
+      <c r="B40" s="44">
         <f>IF(SUM('2 Matériel'!$M$20:$M$29)&gt;0,"⚠  Des lignes de matériel au-delà de la ligne 14 sont masquées : cliquer sur le [+] dans la marge gauche pour les afficher.","")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="10" customHeight="1"/>
     <row r="42" ht="20" customHeight="1">
-      <c r="B42" s="34">
+      <c r="B42" s="36">
         <f>INDEX(Textes!$B$2:$C$54,MATCH("sec_opt",Textes!$A$2:$A$54,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="C42" s="35" t="n"/>
-      <c r="D42" s="35" t="n"/>
-      <c r="E42" s="35" t="n"/>
-      <c r="F42" s="35" t="n"/>
-      <c r="G42" s="35" t="n"/>
-      <c r="H42" s="35" t="n"/>
-      <c r="I42" s="35" t="n"/>
-      <c r="J42" s="35" t="n"/>
-      <c r="K42" s="35" t="n"/>
+      <c r="C42" s="37" t="n"/>
+      <c r="D42" s="37" t="n"/>
+      <c r="E42" s="37" t="n"/>
+      <c r="F42" s="37" t="n"/>
+      <c r="G42" s="37" t="n"/>
+      <c r="H42" s="37" t="n"/>
+      <c r="I42" s="37" t="n"/>
+      <c r="J42" s="37" t="n"/>
+      <c r="K42" s="37" t="n"/>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="B43" s="43" t="n"/>
-      <c r="C43" s="44">
+      <c r="B43" s="45" t="n"/>
+      <c r="C43" s="46">
         <f>INDEX(Textes!$B$2:$C$54,MATCH("h_label",Textes!$A$2:$A$54,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="D43" s="43">
+      <c r="D43" s="45">
         <f>INDEX(Textes!$B$2:$C$54,MATCH("h_qty",Textes!$A$2:$A$54,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="E43" s="43">
+      <c r="E43" s="45">
         <f>INDEX(Textes!$B$2:$C$54,MATCH("h_unit",Textes!$A$2:$A$54,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="F43" s="43">
+      <c r="F43" s="45">
         <f>INDEX(Textes!$B$2:$C$54,MATCH("h_pu",Textes!$A$2:$A$54,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="G43" s="43">
+      <c r="G43" s="45">
         <f>INDEX(Textes!$B$2:$C$54,MATCH("h_tot",Textes!$A$2:$A$54,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="H43" s="44">
+      <c r="H43" s="46">
         <f>INDEX(Textes!$B$2:$C$54,MATCH("h_det",Textes!$A$2:$A$54,0),Listes!$H$1)</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="21" customHeight="1">
-      <c r="C44" s="45">
+      <c r="C44" s="47">
         <f>IF(ISNUMBER(MATCH(1,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$D$6:$D$14,MATCH(1,'3 Options'!$I$6:$I$14,0))&lt;&gt;"",INDEX('3 Options'!$D$6:$D$14,MATCH(1,'3 Options'!$I$6:$I$14,0)),CHOOSE(MATCH(1,'3 Options'!$I$6:$I$14,0),INDEX(Textes!$B$2:$C$54,MATCH("op_day",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("op_mob",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("tight",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("tr_mob",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("tr_dem",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("free",Textes!$A$2:$A$54,0),Listes!$H$1)&amp;" 1",INDEX(Textes!$B$2:$C$54,MATCH("free",Textes!$A$2:$A$54,0),Listes!$H$1)&amp;" 2",INDEX(Textes!$B$2:$C$54,MATCH("free",Textes!$A$2:$A$54,0),Listes!$H$1)&amp;" 3",INDEX(Textes!$B$2:$C$54,MATCH("forfait",Textes!$A$2:$A$54,0),Listes!$H$1))),"")</f>
         <v/>
       </c>
-      <c r="D44" s="39">
-        <f>IF(ISNUMBER(MATCH(1,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(1,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",INDEX('3 Options'!$E$6:$E$14,MATCH(1,'3 Options'!$I$6:$I$14,0))),"")</f>
-        <v/>
-      </c>
-      <c r="E44" s="39">
-        <f>IF(ISNUMBER(MATCH(1,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(1,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",INDEX('3 Options'!$G$6:$G$14,MATCH(1,'3 Options'!$I$6:$I$14,0))),"")</f>
-        <v/>
-      </c>
-      <c r="F44" s="40">
-        <f>IF(ISNUMBER(MATCH(1,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(1,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %",INDEX(Textes!$B$2:$C$54,MATCH("at_cost",Textes!$A$2:$A$54,0),Listes!$H$1),IF(INDEX('3 Options'!$F$6:$F$14,MATCH(1,'3 Options'!$I$6:$I$14,0))="","",INDEX('3 Options'!$F$6:$F$14,MATCH(1,'3 Options'!$I$6:$I$14,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="G44" s="46">
+      <c r="D44" s="41">
+        <f>IF(ISNUMBER(MATCH(1,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(1,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",IF(AND(MATCH(1,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$G$14="Forfait calculé (S + O + UC)"),1,INDEX('3 Options'!$E$6:$E$14,MATCH(1,'3 Options'!$I$6:$I$14,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="41">
+        <f>IF(ISNUMBER(MATCH(1,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(1,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",IF(AND(MATCH(1,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$G$14="Forfait calculé (S + O + UC)"),INDEX(Textes!$B$2:$C$54,MATCH("lump",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX('3 Options'!$G$6:$G$14,MATCH(1,'3 Options'!$I$6:$I$14,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="F44" s="42">
+        <f>IF(ISNUMBER(MATCH(1,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(1,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %",INDEX(Textes!$B$2:$C$54,MATCH("at_cost",Textes!$A$2:$A$54,0),Listes!$H$1),IF(AND(MATCH(1,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$G$14="Forfait calculé (S + O + UC)"),IF('3 Options'!$F$14="",SUM('2 Matériel'!$L$6:$L$29),'3 Options'!$F$14),IF(INDEX('3 Options'!$F$6:$F$14,MATCH(1,'3 Options'!$I$6:$I$14,0))="","",INDEX('3 Options'!$F$6:$F$14,MATCH(1,'3 Options'!$I$6:$I$14,0))))),"")</f>
+        <v/>
+      </c>
+      <c r="G44" s="48">
         <f>IF(ISNUMBER(MATCH(1,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(1,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","—",INDEX('3 Options'!$H$6:$H$14,MATCH(1,'3 Options'!$I$6:$I$14,0))),"")</f>
         <v/>
       </c>
-      <c r="H44" s="47">
-        <f>IF(ISNUMBER(MATCH(1,'3 Options'!$I$6:$I$14,0)),IF(AND(MATCH(1,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$D$15&lt;&gt;""),'3 Options'!$D$15,IF(OR(MATCH(1,'3 Options'!$I$6:$I$14,0)=4,MATCH(1,'3 Options'!$I$6:$I$14,0)=5),INDEX(Textes!$B$2:$C$54,MATCH("tr_note",Textes!$A$2:$A$54,0),Listes!$H$1),"")),"")</f>
+      <c r="H44" s="49">
+        <f>IF(ISNUMBER(MATCH(1,'3 Options'!$I$6:$I$14,0)),IF(MATCH(1,'3 Options'!$I$6:$I$14,0)=9,IF('3 Options'!$G$14="Forfait calculé (S + O + UC)",IF(Listes!$H$1=1,'3 Options'!$C$16&amp;" j stand-by + "&amp;'3 Options'!$C$17&amp;" j opérations + UC",'3 Options'!$C$16&amp;" stand-by days + "&amp;'3 Options'!$C$17&amp;" operation days + UC")&amp;IF('3 Options'!$D$15&lt;&gt;"","  ·  "&amp;'3 Options'!$D$15,""),'3 Options'!$D$15),IF(OR(MATCH(1,'3 Options'!$I$6:$I$14,0)=4,MATCH(1,'3 Options'!$I$6:$I$14,0)=5),INDEX(Textes!$B$2:$C$54,MATCH("tr_note",Textes!$A$2:$A$54,0),Listes!$H$1),"")),"")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="21" customHeight="1">
-      <c r="C45" s="45">
+      <c r="C45" s="47">
         <f>IF(ISNUMBER(MATCH(2,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$D$6:$D$14,MATCH(2,'3 Options'!$I$6:$I$14,0))&lt;&gt;"",INDEX('3 Options'!$D$6:$D$14,MATCH(2,'3 Options'!$I$6:$I$14,0)),CHOOSE(MATCH(2,'3 Options'!$I$6:$I$14,0),INDEX(Textes!$B$2:$C$54,MATCH("op_day",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("op_mob",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("tight",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("tr_mob",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("tr_dem",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("free",Textes!$A$2:$A$54,0),Listes!$H$1)&amp;" 1",INDEX(Textes!$B$2:$C$54,MATCH("free",Textes!$A$2:$A$54,0),Listes!$H$1)&amp;" 2",INDEX(Textes!$B$2:$C$54,MATCH("free",Textes!$A$2:$A$54,0),Listes!$H$1)&amp;" 3",INDEX(Textes!$B$2:$C$54,MATCH("forfait",Textes!$A$2:$A$54,0),Listes!$H$1))),"")</f>
         <v/>
       </c>
-      <c r="D45" s="39">
-        <f>IF(ISNUMBER(MATCH(2,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(2,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",INDEX('3 Options'!$E$6:$E$14,MATCH(2,'3 Options'!$I$6:$I$14,0))),"")</f>
-        <v/>
-      </c>
-      <c r="E45" s="39">
-        <f>IF(ISNUMBER(MATCH(2,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(2,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",INDEX('3 Options'!$G$6:$G$14,MATCH(2,'3 Options'!$I$6:$I$14,0))),"")</f>
-        <v/>
-      </c>
-      <c r="F45" s="40">
-        <f>IF(ISNUMBER(MATCH(2,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(2,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %",INDEX(Textes!$B$2:$C$54,MATCH("at_cost",Textes!$A$2:$A$54,0),Listes!$H$1),IF(INDEX('3 Options'!$F$6:$F$14,MATCH(2,'3 Options'!$I$6:$I$14,0))="","",INDEX('3 Options'!$F$6:$F$14,MATCH(2,'3 Options'!$I$6:$I$14,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="G45" s="46">
+      <c r="D45" s="41">
+        <f>IF(ISNUMBER(MATCH(2,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(2,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",IF(AND(MATCH(2,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$G$14="Forfait calculé (S + O + UC)"),1,INDEX('3 Options'!$E$6:$E$14,MATCH(2,'3 Options'!$I$6:$I$14,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="E45" s="41">
+        <f>IF(ISNUMBER(MATCH(2,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(2,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",IF(AND(MATCH(2,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$G$14="Forfait calculé (S + O + UC)"),INDEX(Textes!$B$2:$C$54,MATCH("lump",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX('3 Options'!$G$6:$G$14,MATCH(2,'3 Options'!$I$6:$I$14,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="F45" s="42">
+        <f>IF(ISNUMBER(MATCH(2,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(2,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %",INDEX(Textes!$B$2:$C$54,MATCH("at_cost",Textes!$A$2:$A$54,0),Listes!$H$1),IF(AND(MATCH(2,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$G$14="Forfait calculé (S + O + UC)"),IF('3 Options'!$F$14="",SUM('2 Matériel'!$L$6:$L$29),'3 Options'!$F$14),IF(INDEX('3 Options'!$F$6:$F$14,MATCH(2,'3 Options'!$I$6:$I$14,0))="","",INDEX('3 Options'!$F$6:$F$14,MATCH(2,'3 Options'!$I$6:$I$14,0))))),"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="48">
         <f>IF(ISNUMBER(MATCH(2,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(2,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","—",INDEX('3 Options'!$H$6:$H$14,MATCH(2,'3 Options'!$I$6:$I$14,0))),"")</f>
         <v/>
       </c>
-      <c r="H45" s="47">
-        <f>IF(ISNUMBER(MATCH(2,'3 Options'!$I$6:$I$14,0)),IF(AND(MATCH(2,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$D$15&lt;&gt;""),'3 Options'!$D$15,IF(OR(MATCH(2,'3 Options'!$I$6:$I$14,0)=4,MATCH(2,'3 Options'!$I$6:$I$14,0)=5),INDEX(Textes!$B$2:$C$54,MATCH("tr_note",Textes!$A$2:$A$54,0),Listes!$H$1),"")),"")</f>
+      <c r="H45" s="49">
+        <f>IF(ISNUMBER(MATCH(2,'3 Options'!$I$6:$I$14,0)),IF(MATCH(2,'3 Options'!$I$6:$I$14,0)=9,IF('3 Options'!$G$14="Forfait calculé (S + O + UC)",IF(Listes!$H$1=1,'3 Options'!$C$16&amp;" j stand-by + "&amp;'3 Options'!$C$17&amp;" j opérations + UC",'3 Options'!$C$16&amp;" stand-by days + "&amp;'3 Options'!$C$17&amp;" operation days + UC")&amp;IF('3 Options'!$D$15&lt;&gt;"","  ·  "&amp;'3 Options'!$D$15,""),'3 Options'!$D$15),IF(OR(MATCH(2,'3 Options'!$I$6:$I$14,0)=4,MATCH(2,'3 Options'!$I$6:$I$14,0)=5),INDEX(Textes!$B$2:$C$54,MATCH("tr_note",Textes!$A$2:$A$54,0),Listes!$H$1),"")),"")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="21" customHeight="1">
-      <c r="C46" s="45">
+      <c r="C46" s="47">
         <f>IF(ISNUMBER(MATCH(3,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$D$6:$D$14,MATCH(3,'3 Options'!$I$6:$I$14,0))&lt;&gt;"",INDEX('3 Options'!$D$6:$D$14,MATCH(3,'3 Options'!$I$6:$I$14,0)),CHOOSE(MATCH(3,'3 Options'!$I$6:$I$14,0),INDEX(Textes!$B$2:$C$54,MATCH("op_day",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("op_mob",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("tight",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("tr_mob",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("tr_dem",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("free",Textes!$A$2:$A$54,0),Listes!$H$1)&amp;" 1",INDEX(Textes!$B$2:$C$54,MATCH("free",Textes!$A$2:$A$54,0),Listes!$H$1)&amp;" 2",INDEX(Textes!$B$2:$C$54,MATCH("free",Textes!$A$2:$A$54,0),Listes!$H$1)&amp;" 3",INDEX(Textes!$B$2:$C$54,MATCH("forfait",Textes!$A$2:$A$54,0),Listes!$H$1))),"")</f>
         <v/>
       </c>
-      <c r="D46" s="39">
-        <f>IF(ISNUMBER(MATCH(3,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(3,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",INDEX('3 Options'!$E$6:$E$14,MATCH(3,'3 Options'!$I$6:$I$14,0))),"")</f>
-        <v/>
-      </c>
-      <c r="E46" s="39">
-        <f>IF(ISNUMBER(MATCH(3,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(3,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",INDEX('3 Options'!$G$6:$G$14,MATCH(3,'3 Options'!$I$6:$I$14,0))),"")</f>
-        <v/>
-      </c>
-      <c r="F46" s="40">
-        <f>IF(ISNUMBER(MATCH(3,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(3,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %",INDEX(Textes!$B$2:$C$54,MATCH("at_cost",Textes!$A$2:$A$54,0),Listes!$H$1),IF(INDEX('3 Options'!$F$6:$F$14,MATCH(3,'3 Options'!$I$6:$I$14,0))="","",INDEX('3 Options'!$F$6:$F$14,MATCH(3,'3 Options'!$I$6:$I$14,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="G46" s="46">
+      <c r="D46" s="41">
+        <f>IF(ISNUMBER(MATCH(3,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(3,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",IF(AND(MATCH(3,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$G$14="Forfait calculé (S + O + UC)"),1,INDEX('3 Options'!$E$6:$E$14,MATCH(3,'3 Options'!$I$6:$I$14,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="E46" s="41">
+        <f>IF(ISNUMBER(MATCH(3,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(3,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",IF(AND(MATCH(3,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$G$14="Forfait calculé (S + O + UC)"),INDEX(Textes!$B$2:$C$54,MATCH("lump",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX('3 Options'!$G$6:$G$14,MATCH(3,'3 Options'!$I$6:$I$14,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="F46" s="42">
+        <f>IF(ISNUMBER(MATCH(3,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(3,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %",INDEX(Textes!$B$2:$C$54,MATCH("at_cost",Textes!$A$2:$A$54,0),Listes!$H$1),IF(AND(MATCH(3,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$G$14="Forfait calculé (S + O + UC)"),IF('3 Options'!$F$14="",SUM('2 Matériel'!$L$6:$L$29),'3 Options'!$F$14),IF(INDEX('3 Options'!$F$6:$F$14,MATCH(3,'3 Options'!$I$6:$I$14,0))="","",INDEX('3 Options'!$F$6:$F$14,MATCH(3,'3 Options'!$I$6:$I$14,0))))),"")</f>
+        <v/>
+      </c>
+      <c r="G46" s="48">
         <f>IF(ISNUMBER(MATCH(3,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(3,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","—",INDEX('3 Options'!$H$6:$H$14,MATCH(3,'3 Options'!$I$6:$I$14,0))),"")</f>
         <v/>
       </c>
-      <c r="H46" s="47">
-        <f>IF(ISNUMBER(MATCH(3,'3 Options'!$I$6:$I$14,0)),IF(AND(MATCH(3,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$D$15&lt;&gt;""),'3 Options'!$D$15,IF(OR(MATCH(3,'3 Options'!$I$6:$I$14,0)=4,MATCH(3,'3 Options'!$I$6:$I$14,0)=5),INDEX(Textes!$B$2:$C$54,MATCH("tr_note",Textes!$A$2:$A$54,0),Listes!$H$1),"")),"")</f>
+      <c r="H46" s="49">
+        <f>IF(ISNUMBER(MATCH(3,'3 Options'!$I$6:$I$14,0)),IF(MATCH(3,'3 Options'!$I$6:$I$14,0)=9,IF('3 Options'!$G$14="Forfait calculé (S + O + UC)",IF(Listes!$H$1=1,'3 Options'!$C$16&amp;" j stand-by + "&amp;'3 Options'!$C$17&amp;" j opérations + UC",'3 Options'!$C$16&amp;" stand-by days + "&amp;'3 Options'!$C$17&amp;" operation days + UC")&amp;IF('3 Options'!$D$15&lt;&gt;"","  ·  "&amp;'3 Options'!$D$15,""),'3 Options'!$D$15),IF(OR(MATCH(3,'3 Options'!$I$6:$I$14,0)=4,MATCH(3,'3 Options'!$I$6:$I$14,0)=5),INDEX(Textes!$B$2:$C$54,MATCH("tr_note",Textes!$A$2:$A$54,0),Listes!$H$1),"")),"")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="21" customHeight="1">
-      <c r="C47" s="45">
+      <c r="C47" s="47">
         <f>IF(ISNUMBER(MATCH(4,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$D$6:$D$14,MATCH(4,'3 Options'!$I$6:$I$14,0))&lt;&gt;"",INDEX('3 Options'!$D$6:$D$14,MATCH(4,'3 Options'!$I$6:$I$14,0)),CHOOSE(MATCH(4,'3 Options'!$I$6:$I$14,0),INDEX(Textes!$B$2:$C$54,MATCH("op_day",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("op_mob",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("tight",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("tr_mob",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("tr_dem",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("free",Textes!$A$2:$A$54,0),Listes!$H$1)&amp;" 1",INDEX(Textes!$B$2:$C$54,MATCH("free",Textes!$A$2:$A$54,0),Listes!$H$1)&amp;" 2",INDEX(Textes!$B$2:$C$54,MATCH("free",Textes!$A$2:$A$54,0),Listes!$H$1)&amp;" 3",INDEX(Textes!$B$2:$C$54,MATCH("forfait",Textes!$A$2:$A$54,0),Listes!$H$1))),"")</f>
         <v/>
       </c>
-      <c r="D47" s="39">
-        <f>IF(ISNUMBER(MATCH(4,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(4,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",INDEX('3 Options'!$E$6:$E$14,MATCH(4,'3 Options'!$I$6:$I$14,0))),"")</f>
-        <v/>
-      </c>
-      <c r="E47" s="39">
-        <f>IF(ISNUMBER(MATCH(4,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(4,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",INDEX('3 Options'!$G$6:$G$14,MATCH(4,'3 Options'!$I$6:$I$14,0))),"")</f>
-        <v/>
-      </c>
-      <c r="F47" s="40">
-        <f>IF(ISNUMBER(MATCH(4,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(4,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %",INDEX(Textes!$B$2:$C$54,MATCH("at_cost",Textes!$A$2:$A$54,0),Listes!$H$1),IF(INDEX('3 Options'!$F$6:$F$14,MATCH(4,'3 Options'!$I$6:$I$14,0))="","",INDEX('3 Options'!$F$6:$F$14,MATCH(4,'3 Options'!$I$6:$I$14,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="G47" s="46">
+      <c r="D47" s="41">
+        <f>IF(ISNUMBER(MATCH(4,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(4,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",IF(AND(MATCH(4,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$G$14="Forfait calculé (S + O + UC)"),1,INDEX('3 Options'!$E$6:$E$14,MATCH(4,'3 Options'!$I$6:$I$14,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="E47" s="41">
+        <f>IF(ISNUMBER(MATCH(4,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(4,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",IF(AND(MATCH(4,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$G$14="Forfait calculé (S + O + UC)"),INDEX(Textes!$B$2:$C$54,MATCH("lump",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX('3 Options'!$G$6:$G$14,MATCH(4,'3 Options'!$I$6:$I$14,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="F47" s="42">
+        <f>IF(ISNUMBER(MATCH(4,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(4,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %",INDEX(Textes!$B$2:$C$54,MATCH("at_cost",Textes!$A$2:$A$54,0),Listes!$H$1),IF(AND(MATCH(4,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$G$14="Forfait calculé (S + O + UC)"),IF('3 Options'!$F$14="",SUM('2 Matériel'!$L$6:$L$29),'3 Options'!$F$14),IF(INDEX('3 Options'!$F$6:$F$14,MATCH(4,'3 Options'!$I$6:$I$14,0))="","",INDEX('3 Options'!$F$6:$F$14,MATCH(4,'3 Options'!$I$6:$I$14,0))))),"")</f>
+        <v/>
+      </c>
+      <c r="G47" s="48">
         <f>IF(ISNUMBER(MATCH(4,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(4,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","—",INDEX('3 Options'!$H$6:$H$14,MATCH(4,'3 Options'!$I$6:$I$14,0))),"")</f>
         <v/>
       </c>
-      <c r="H47" s="47">
-        <f>IF(ISNUMBER(MATCH(4,'3 Options'!$I$6:$I$14,0)),IF(AND(MATCH(4,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$D$15&lt;&gt;""),'3 Options'!$D$15,IF(OR(MATCH(4,'3 Options'!$I$6:$I$14,0)=4,MATCH(4,'3 Options'!$I$6:$I$14,0)=5),INDEX(Textes!$B$2:$C$54,MATCH("tr_note",Textes!$A$2:$A$54,0),Listes!$H$1),"")),"")</f>
+      <c r="H47" s="49">
+        <f>IF(ISNUMBER(MATCH(4,'3 Options'!$I$6:$I$14,0)),IF(MATCH(4,'3 Options'!$I$6:$I$14,0)=9,IF('3 Options'!$G$14="Forfait calculé (S + O + UC)",IF(Listes!$H$1=1,'3 Options'!$C$16&amp;" j stand-by + "&amp;'3 Options'!$C$17&amp;" j opérations + UC",'3 Options'!$C$16&amp;" stand-by days + "&amp;'3 Options'!$C$17&amp;" operation days + UC")&amp;IF('3 Options'!$D$15&lt;&gt;"","  ·  "&amp;'3 Options'!$D$15,""),'3 Options'!$D$15),IF(OR(MATCH(4,'3 Options'!$I$6:$I$14,0)=4,MATCH(4,'3 Options'!$I$6:$I$14,0)=5),INDEX(Textes!$B$2:$C$54,MATCH("tr_note",Textes!$A$2:$A$54,0),Listes!$H$1),"")),"")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="21" customHeight="1">
-      <c r="C48" s="45">
+      <c r="C48" s="47">
         <f>IF(ISNUMBER(MATCH(5,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$D$6:$D$14,MATCH(5,'3 Options'!$I$6:$I$14,0))&lt;&gt;"",INDEX('3 Options'!$D$6:$D$14,MATCH(5,'3 Options'!$I$6:$I$14,0)),CHOOSE(MATCH(5,'3 Options'!$I$6:$I$14,0),INDEX(Textes!$B$2:$C$54,MATCH("op_day",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("op_mob",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("tight",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("tr_mob",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("tr_dem",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("free",Textes!$A$2:$A$54,0),Listes!$H$1)&amp;" 1",INDEX(Textes!$B$2:$C$54,MATCH("free",Textes!$A$2:$A$54,0),Listes!$H$1)&amp;" 2",INDEX(Textes!$B$2:$C$54,MATCH("free",Textes!$A$2:$A$54,0),Listes!$H$1)&amp;" 3",INDEX(Textes!$B$2:$C$54,MATCH("forfait",Textes!$A$2:$A$54,0),Listes!$H$1))),"")</f>
         <v/>
       </c>
-      <c r="D48" s="39">
-        <f>IF(ISNUMBER(MATCH(5,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(5,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",INDEX('3 Options'!$E$6:$E$14,MATCH(5,'3 Options'!$I$6:$I$14,0))),"")</f>
-        <v/>
-      </c>
-      <c r="E48" s="39">
-        <f>IF(ISNUMBER(MATCH(5,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(5,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",INDEX('3 Options'!$G$6:$G$14,MATCH(5,'3 Options'!$I$6:$I$14,0))),"")</f>
-        <v/>
-      </c>
-      <c r="F48" s="40">
-        <f>IF(ISNUMBER(MATCH(5,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(5,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %",INDEX(Textes!$B$2:$C$54,MATCH("at_cost",Textes!$A$2:$A$54,0),Listes!$H$1),IF(INDEX('3 Options'!$F$6:$F$14,MATCH(5,'3 Options'!$I$6:$I$14,0))="","",INDEX('3 Options'!$F$6:$F$14,MATCH(5,'3 Options'!$I$6:$I$14,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="G48" s="46">
+      <c r="D48" s="41">
+        <f>IF(ISNUMBER(MATCH(5,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(5,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",IF(AND(MATCH(5,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$G$14="Forfait calculé (S + O + UC)"),1,INDEX('3 Options'!$E$6:$E$14,MATCH(5,'3 Options'!$I$6:$I$14,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="E48" s="41">
+        <f>IF(ISNUMBER(MATCH(5,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(5,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",IF(AND(MATCH(5,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$G$14="Forfait calculé (S + O + UC)"),INDEX(Textes!$B$2:$C$54,MATCH("lump",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX('3 Options'!$G$6:$G$14,MATCH(5,'3 Options'!$I$6:$I$14,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="F48" s="42">
+        <f>IF(ISNUMBER(MATCH(5,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(5,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %",INDEX(Textes!$B$2:$C$54,MATCH("at_cost",Textes!$A$2:$A$54,0),Listes!$H$1),IF(AND(MATCH(5,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$G$14="Forfait calculé (S + O + UC)"),IF('3 Options'!$F$14="",SUM('2 Matériel'!$L$6:$L$29),'3 Options'!$F$14),IF(INDEX('3 Options'!$F$6:$F$14,MATCH(5,'3 Options'!$I$6:$I$14,0))="","",INDEX('3 Options'!$F$6:$F$14,MATCH(5,'3 Options'!$I$6:$I$14,0))))),"")</f>
+        <v/>
+      </c>
+      <c r="G48" s="48">
         <f>IF(ISNUMBER(MATCH(5,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(5,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","—",INDEX('3 Options'!$H$6:$H$14,MATCH(5,'3 Options'!$I$6:$I$14,0))),"")</f>
         <v/>
       </c>
-      <c r="H48" s="47">
-        <f>IF(ISNUMBER(MATCH(5,'3 Options'!$I$6:$I$14,0)),IF(AND(MATCH(5,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$D$15&lt;&gt;""),'3 Options'!$D$15,IF(OR(MATCH(5,'3 Options'!$I$6:$I$14,0)=4,MATCH(5,'3 Options'!$I$6:$I$14,0)=5),INDEX(Textes!$B$2:$C$54,MATCH("tr_note",Textes!$A$2:$A$54,0),Listes!$H$1),"")),"")</f>
+      <c r="H48" s="49">
+        <f>IF(ISNUMBER(MATCH(5,'3 Options'!$I$6:$I$14,0)),IF(MATCH(5,'3 Options'!$I$6:$I$14,0)=9,IF('3 Options'!$G$14="Forfait calculé (S + O + UC)",IF(Listes!$H$1=1,'3 Options'!$C$16&amp;" j stand-by + "&amp;'3 Options'!$C$17&amp;" j opérations + UC",'3 Options'!$C$16&amp;" stand-by days + "&amp;'3 Options'!$C$17&amp;" operation days + UC")&amp;IF('3 Options'!$D$15&lt;&gt;"","  ·  "&amp;'3 Options'!$D$15,""),'3 Options'!$D$15),IF(OR(MATCH(5,'3 Options'!$I$6:$I$14,0)=4,MATCH(5,'3 Options'!$I$6:$I$14,0)=5),INDEX(Textes!$B$2:$C$54,MATCH("tr_note",Textes!$A$2:$A$54,0),Listes!$H$1),"")),"")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="21" customHeight="1">
-      <c r="C49" s="45">
+      <c r="C49" s="47">
         <f>IF(ISNUMBER(MATCH(6,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$D$6:$D$14,MATCH(6,'3 Options'!$I$6:$I$14,0))&lt;&gt;"",INDEX('3 Options'!$D$6:$D$14,MATCH(6,'3 Options'!$I$6:$I$14,0)),CHOOSE(MATCH(6,'3 Options'!$I$6:$I$14,0),INDEX(Textes!$B$2:$C$54,MATCH("op_day",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("op_mob",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("tight",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("tr_mob",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("tr_dem",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("free",Textes!$A$2:$A$54,0),Listes!$H$1)&amp;" 1",INDEX(Textes!$B$2:$C$54,MATCH("free",Textes!$A$2:$A$54,0),Listes!$H$1)&amp;" 2",INDEX(Textes!$B$2:$C$54,MATCH("free",Textes!$A$2:$A$54,0),Listes!$H$1)&amp;" 3",INDEX(Textes!$B$2:$C$54,MATCH("forfait",Textes!$A$2:$A$54,0),Listes!$H$1))),"")</f>
         <v/>
       </c>
-      <c r="D49" s="39">
-        <f>IF(ISNUMBER(MATCH(6,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(6,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",INDEX('3 Options'!$E$6:$E$14,MATCH(6,'3 Options'!$I$6:$I$14,0))),"")</f>
-        <v/>
-      </c>
-      <c r="E49" s="39">
-        <f>IF(ISNUMBER(MATCH(6,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(6,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",INDEX('3 Options'!$G$6:$G$14,MATCH(6,'3 Options'!$I$6:$I$14,0))),"")</f>
-        <v/>
-      </c>
-      <c r="F49" s="40">
-        <f>IF(ISNUMBER(MATCH(6,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(6,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %",INDEX(Textes!$B$2:$C$54,MATCH("at_cost",Textes!$A$2:$A$54,0),Listes!$H$1),IF(INDEX('3 Options'!$F$6:$F$14,MATCH(6,'3 Options'!$I$6:$I$14,0))="","",INDEX('3 Options'!$F$6:$F$14,MATCH(6,'3 Options'!$I$6:$I$14,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="G49" s="46">
+      <c r="D49" s="41">
+        <f>IF(ISNUMBER(MATCH(6,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(6,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",IF(AND(MATCH(6,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$G$14="Forfait calculé (S + O + UC)"),1,INDEX('3 Options'!$E$6:$E$14,MATCH(6,'3 Options'!$I$6:$I$14,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="E49" s="41">
+        <f>IF(ISNUMBER(MATCH(6,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(6,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",IF(AND(MATCH(6,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$G$14="Forfait calculé (S + O + UC)"),INDEX(Textes!$B$2:$C$54,MATCH("lump",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX('3 Options'!$G$6:$G$14,MATCH(6,'3 Options'!$I$6:$I$14,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="F49" s="42">
+        <f>IF(ISNUMBER(MATCH(6,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(6,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %",INDEX(Textes!$B$2:$C$54,MATCH("at_cost",Textes!$A$2:$A$54,0),Listes!$H$1),IF(AND(MATCH(6,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$G$14="Forfait calculé (S + O + UC)"),IF('3 Options'!$F$14="",SUM('2 Matériel'!$L$6:$L$29),'3 Options'!$F$14),IF(INDEX('3 Options'!$F$6:$F$14,MATCH(6,'3 Options'!$I$6:$I$14,0))="","",INDEX('3 Options'!$F$6:$F$14,MATCH(6,'3 Options'!$I$6:$I$14,0))))),"")</f>
+        <v/>
+      </c>
+      <c r="G49" s="48">
         <f>IF(ISNUMBER(MATCH(6,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(6,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","—",INDEX('3 Options'!$H$6:$H$14,MATCH(6,'3 Options'!$I$6:$I$14,0))),"")</f>
         <v/>
       </c>
-      <c r="H49" s="47">
-        <f>IF(ISNUMBER(MATCH(6,'3 Options'!$I$6:$I$14,0)),IF(AND(MATCH(6,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$D$15&lt;&gt;""),'3 Options'!$D$15,IF(OR(MATCH(6,'3 Options'!$I$6:$I$14,0)=4,MATCH(6,'3 Options'!$I$6:$I$14,0)=5),INDEX(Textes!$B$2:$C$54,MATCH("tr_note",Textes!$A$2:$A$54,0),Listes!$H$1),"")),"")</f>
+      <c r="H49" s="49">
+        <f>IF(ISNUMBER(MATCH(6,'3 Options'!$I$6:$I$14,0)),IF(MATCH(6,'3 Options'!$I$6:$I$14,0)=9,IF('3 Options'!$G$14="Forfait calculé (S + O + UC)",IF(Listes!$H$1=1,'3 Options'!$C$16&amp;" j stand-by + "&amp;'3 Options'!$C$17&amp;" j opérations + UC",'3 Options'!$C$16&amp;" stand-by days + "&amp;'3 Options'!$C$17&amp;" operation days + UC")&amp;IF('3 Options'!$D$15&lt;&gt;"","  ·  "&amp;'3 Options'!$D$15,""),'3 Options'!$D$15),IF(OR(MATCH(6,'3 Options'!$I$6:$I$14,0)=4,MATCH(6,'3 Options'!$I$6:$I$14,0)=5),INDEX(Textes!$B$2:$C$54,MATCH("tr_note",Textes!$A$2:$A$54,0),Listes!$H$1),"")),"")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="21" customHeight="1">
-      <c r="C50" s="45">
+      <c r="C50" s="47">
         <f>IF(ISNUMBER(MATCH(7,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$D$6:$D$14,MATCH(7,'3 Options'!$I$6:$I$14,0))&lt;&gt;"",INDEX('3 Options'!$D$6:$D$14,MATCH(7,'3 Options'!$I$6:$I$14,0)),CHOOSE(MATCH(7,'3 Options'!$I$6:$I$14,0),INDEX(Textes!$B$2:$C$54,MATCH("op_day",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("op_mob",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("tight",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("tr_mob",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("tr_dem",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("free",Textes!$A$2:$A$54,0),Listes!$H$1)&amp;" 1",INDEX(Textes!$B$2:$C$54,MATCH("free",Textes!$A$2:$A$54,0),Listes!$H$1)&amp;" 2",INDEX(Textes!$B$2:$C$54,MATCH("free",Textes!$A$2:$A$54,0),Listes!$H$1)&amp;" 3",INDEX(Textes!$B$2:$C$54,MATCH("forfait",Textes!$A$2:$A$54,0),Listes!$H$1))),"")</f>
         <v/>
       </c>
-      <c r="D50" s="39">
-        <f>IF(ISNUMBER(MATCH(7,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(7,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",INDEX('3 Options'!$E$6:$E$14,MATCH(7,'3 Options'!$I$6:$I$14,0))),"")</f>
-        <v/>
-      </c>
-      <c r="E50" s="39">
-        <f>IF(ISNUMBER(MATCH(7,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(7,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",INDEX('3 Options'!$G$6:$G$14,MATCH(7,'3 Options'!$I$6:$I$14,0))),"")</f>
-        <v/>
-      </c>
-      <c r="F50" s="40">
-        <f>IF(ISNUMBER(MATCH(7,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(7,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %",INDEX(Textes!$B$2:$C$54,MATCH("at_cost",Textes!$A$2:$A$54,0),Listes!$H$1),IF(INDEX('3 Options'!$F$6:$F$14,MATCH(7,'3 Options'!$I$6:$I$14,0))="","",INDEX('3 Options'!$F$6:$F$14,MATCH(7,'3 Options'!$I$6:$I$14,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="G50" s="46">
+      <c r="D50" s="41">
+        <f>IF(ISNUMBER(MATCH(7,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(7,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",IF(AND(MATCH(7,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$G$14="Forfait calculé (S + O + UC)"),1,INDEX('3 Options'!$E$6:$E$14,MATCH(7,'3 Options'!$I$6:$I$14,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="E50" s="41">
+        <f>IF(ISNUMBER(MATCH(7,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(7,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",IF(AND(MATCH(7,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$G$14="Forfait calculé (S + O + UC)"),INDEX(Textes!$B$2:$C$54,MATCH("lump",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX('3 Options'!$G$6:$G$14,MATCH(7,'3 Options'!$I$6:$I$14,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="F50" s="42">
+        <f>IF(ISNUMBER(MATCH(7,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(7,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %",INDEX(Textes!$B$2:$C$54,MATCH("at_cost",Textes!$A$2:$A$54,0),Listes!$H$1),IF(AND(MATCH(7,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$G$14="Forfait calculé (S + O + UC)"),IF('3 Options'!$F$14="",SUM('2 Matériel'!$L$6:$L$29),'3 Options'!$F$14),IF(INDEX('3 Options'!$F$6:$F$14,MATCH(7,'3 Options'!$I$6:$I$14,0))="","",INDEX('3 Options'!$F$6:$F$14,MATCH(7,'3 Options'!$I$6:$I$14,0))))),"")</f>
+        <v/>
+      </c>
+      <c r="G50" s="48">
         <f>IF(ISNUMBER(MATCH(7,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(7,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","—",INDEX('3 Options'!$H$6:$H$14,MATCH(7,'3 Options'!$I$6:$I$14,0))),"")</f>
         <v/>
       </c>
-      <c r="H50" s="47">
-        <f>IF(ISNUMBER(MATCH(7,'3 Options'!$I$6:$I$14,0)),IF(AND(MATCH(7,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$D$15&lt;&gt;""),'3 Options'!$D$15,IF(OR(MATCH(7,'3 Options'!$I$6:$I$14,0)=4,MATCH(7,'3 Options'!$I$6:$I$14,0)=5),INDEX(Textes!$B$2:$C$54,MATCH("tr_note",Textes!$A$2:$A$54,0),Listes!$H$1),"")),"")</f>
+      <c r="H50" s="49">
+        <f>IF(ISNUMBER(MATCH(7,'3 Options'!$I$6:$I$14,0)),IF(MATCH(7,'3 Options'!$I$6:$I$14,0)=9,IF('3 Options'!$G$14="Forfait calculé (S + O + UC)",IF(Listes!$H$1=1,'3 Options'!$C$16&amp;" j stand-by + "&amp;'3 Options'!$C$17&amp;" j opérations + UC",'3 Options'!$C$16&amp;" stand-by days + "&amp;'3 Options'!$C$17&amp;" operation days + UC")&amp;IF('3 Options'!$D$15&lt;&gt;"","  ·  "&amp;'3 Options'!$D$15,""),'3 Options'!$D$15),IF(OR(MATCH(7,'3 Options'!$I$6:$I$14,0)=4,MATCH(7,'3 Options'!$I$6:$I$14,0)=5),INDEX(Textes!$B$2:$C$54,MATCH("tr_note",Textes!$A$2:$A$54,0),Listes!$H$1),"")),"")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="21" customHeight="1">
-      <c r="C51" s="45">
+      <c r="C51" s="47">
         <f>IF(ISNUMBER(MATCH(8,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$D$6:$D$14,MATCH(8,'3 Options'!$I$6:$I$14,0))&lt;&gt;"",INDEX('3 Options'!$D$6:$D$14,MATCH(8,'3 Options'!$I$6:$I$14,0)),CHOOSE(MATCH(8,'3 Options'!$I$6:$I$14,0),INDEX(Textes!$B$2:$C$54,MATCH("op_day",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("op_mob",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("tight",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("tr_mob",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("tr_dem",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("free",Textes!$A$2:$A$54,0),Listes!$H$1)&amp;" 1",INDEX(Textes!$B$2:$C$54,MATCH("free",Textes!$A$2:$A$54,0),Listes!$H$1)&amp;" 2",INDEX(Textes!$B$2:$C$54,MATCH("free",Textes!$A$2:$A$54,0),Listes!$H$1)&amp;" 3",INDEX(Textes!$B$2:$C$54,MATCH("forfait",Textes!$A$2:$A$54,0),Listes!$H$1))),"")</f>
         <v/>
       </c>
-      <c r="D51" s="39">
-        <f>IF(ISNUMBER(MATCH(8,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(8,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",INDEX('3 Options'!$E$6:$E$14,MATCH(8,'3 Options'!$I$6:$I$14,0))),"")</f>
-        <v/>
-      </c>
-      <c r="E51" s="39">
-        <f>IF(ISNUMBER(MATCH(8,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(8,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",INDEX('3 Options'!$G$6:$G$14,MATCH(8,'3 Options'!$I$6:$I$14,0))),"")</f>
-        <v/>
-      </c>
-      <c r="F51" s="40">
-        <f>IF(ISNUMBER(MATCH(8,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(8,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %",INDEX(Textes!$B$2:$C$54,MATCH("at_cost",Textes!$A$2:$A$54,0),Listes!$H$1),IF(INDEX('3 Options'!$F$6:$F$14,MATCH(8,'3 Options'!$I$6:$I$14,0))="","",INDEX('3 Options'!$F$6:$F$14,MATCH(8,'3 Options'!$I$6:$I$14,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="G51" s="46">
+      <c r="D51" s="41">
+        <f>IF(ISNUMBER(MATCH(8,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(8,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",IF(AND(MATCH(8,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$G$14="Forfait calculé (S + O + UC)"),1,INDEX('3 Options'!$E$6:$E$14,MATCH(8,'3 Options'!$I$6:$I$14,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="E51" s="41">
+        <f>IF(ISNUMBER(MATCH(8,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(8,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",IF(AND(MATCH(8,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$G$14="Forfait calculé (S + O + UC)"),INDEX(Textes!$B$2:$C$54,MATCH("lump",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX('3 Options'!$G$6:$G$14,MATCH(8,'3 Options'!$I$6:$I$14,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="F51" s="42">
+        <f>IF(ISNUMBER(MATCH(8,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(8,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %",INDEX(Textes!$B$2:$C$54,MATCH("at_cost",Textes!$A$2:$A$54,0),Listes!$H$1),IF(AND(MATCH(8,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$G$14="Forfait calculé (S + O + UC)"),IF('3 Options'!$F$14="",SUM('2 Matériel'!$L$6:$L$29),'3 Options'!$F$14),IF(INDEX('3 Options'!$F$6:$F$14,MATCH(8,'3 Options'!$I$6:$I$14,0))="","",INDEX('3 Options'!$F$6:$F$14,MATCH(8,'3 Options'!$I$6:$I$14,0))))),"")</f>
+        <v/>
+      </c>
+      <c r="G51" s="48">
         <f>IF(ISNUMBER(MATCH(8,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(8,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","—",INDEX('3 Options'!$H$6:$H$14,MATCH(8,'3 Options'!$I$6:$I$14,0))),"")</f>
         <v/>
       </c>
-      <c r="H51" s="47">
-        <f>IF(ISNUMBER(MATCH(8,'3 Options'!$I$6:$I$14,0)),IF(AND(MATCH(8,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$D$15&lt;&gt;""),'3 Options'!$D$15,IF(OR(MATCH(8,'3 Options'!$I$6:$I$14,0)=4,MATCH(8,'3 Options'!$I$6:$I$14,0)=5),INDEX(Textes!$B$2:$C$54,MATCH("tr_note",Textes!$A$2:$A$54,0),Listes!$H$1),"")),"")</f>
+      <c r="H51" s="49">
+        <f>IF(ISNUMBER(MATCH(8,'3 Options'!$I$6:$I$14,0)),IF(MATCH(8,'3 Options'!$I$6:$I$14,0)=9,IF('3 Options'!$G$14="Forfait calculé (S + O + UC)",IF(Listes!$H$1=1,'3 Options'!$C$16&amp;" j stand-by + "&amp;'3 Options'!$C$17&amp;" j opérations + UC",'3 Options'!$C$16&amp;" stand-by days + "&amp;'3 Options'!$C$17&amp;" operation days + UC")&amp;IF('3 Options'!$D$15&lt;&gt;"","  ·  "&amp;'3 Options'!$D$15,""),'3 Options'!$D$15),IF(OR(MATCH(8,'3 Options'!$I$6:$I$14,0)=4,MATCH(8,'3 Options'!$I$6:$I$14,0)=5),INDEX(Textes!$B$2:$C$54,MATCH("tr_note",Textes!$A$2:$A$54,0),Listes!$H$1),"")),"")</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="21" customHeight="1">
-      <c r="C52" s="45">
+      <c r="C52" s="47">
         <f>IF(ISNUMBER(MATCH(9,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$D$6:$D$14,MATCH(9,'3 Options'!$I$6:$I$14,0))&lt;&gt;"",INDEX('3 Options'!$D$6:$D$14,MATCH(9,'3 Options'!$I$6:$I$14,0)),CHOOSE(MATCH(9,'3 Options'!$I$6:$I$14,0),INDEX(Textes!$B$2:$C$54,MATCH("op_day",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("op_mob",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("tight",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("tr_mob",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("tr_dem",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX(Textes!$B$2:$C$54,MATCH("free",Textes!$A$2:$A$54,0),Listes!$H$1)&amp;" 1",INDEX(Textes!$B$2:$C$54,MATCH("free",Textes!$A$2:$A$54,0),Listes!$H$1)&amp;" 2",INDEX(Textes!$B$2:$C$54,MATCH("free",Textes!$A$2:$A$54,0),Listes!$H$1)&amp;" 3",INDEX(Textes!$B$2:$C$54,MATCH("forfait",Textes!$A$2:$A$54,0),Listes!$H$1))),"")</f>
         <v/>
       </c>
-      <c r="D52" s="39">
-        <f>IF(ISNUMBER(MATCH(9,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(9,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",INDEX('3 Options'!$E$6:$E$14,MATCH(9,'3 Options'!$I$6:$I$14,0))),"")</f>
-        <v/>
-      </c>
-      <c r="E52" s="39">
-        <f>IF(ISNUMBER(MATCH(9,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(9,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",INDEX('3 Options'!$G$6:$G$14,MATCH(9,'3 Options'!$I$6:$I$14,0))),"")</f>
-        <v/>
-      </c>
-      <c r="F52" s="40">
-        <f>IF(ISNUMBER(MATCH(9,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(9,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %",INDEX(Textes!$B$2:$C$54,MATCH("at_cost",Textes!$A$2:$A$54,0),Listes!$H$1),IF(INDEX('3 Options'!$F$6:$F$14,MATCH(9,'3 Options'!$I$6:$I$14,0))="","",INDEX('3 Options'!$F$6:$F$14,MATCH(9,'3 Options'!$I$6:$I$14,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="G52" s="46">
+      <c r="D52" s="41">
+        <f>IF(ISNUMBER(MATCH(9,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(9,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",IF(AND(MATCH(9,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$G$14="Forfait calculé (S + O + UC)"),1,INDEX('3 Options'!$E$6:$E$14,MATCH(9,'3 Options'!$I$6:$I$14,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="E52" s="41">
+        <f>IF(ISNUMBER(MATCH(9,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(9,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","",IF(AND(MATCH(9,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$G$14="Forfait calculé (S + O + UC)"),INDEX(Textes!$B$2:$C$54,MATCH("lump",Textes!$A$2:$A$54,0),Listes!$H$1),INDEX('3 Options'!$G$6:$G$14,MATCH(9,'3 Options'!$I$6:$I$14,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="F52" s="42">
+        <f>IF(ISNUMBER(MATCH(9,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(9,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %",INDEX(Textes!$B$2:$C$54,MATCH("at_cost",Textes!$A$2:$A$54,0),Listes!$H$1),IF(AND(MATCH(9,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$G$14="Forfait calculé (S + O + UC)"),IF('3 Options'!$F$14="",SUM('2 Matériel'!$L$6:$L$29),'3 Options'!$F$14),IF(INDEX('3 Options'!$F$6:$F$14,MATCH(9,'3 Options'!$I$6:$I$14,0))="","",INDEX('3 Options'!$F$6:$F$14,MATCH(9,'3 Options'!$I$6:$I$14,0))))),"")</f>
+        <v/>
+      </c>
+      <c r="G52" s="48">
         <f>IF(ISNUMBER(MATCH(9,'3 Options'!$I$6:$I$14,0)),IF(INDEX('3 Options'!$G$6:$G$14,MATCH(9,'3 Options'!$I$6:$I$14,0))="Coût réel +15 %","—",INDEX('3 Options'!$H$6:$H$14,MATCH(9,'3 Options'!$I$6:$I$14,0))),"")</f>
         <v/>
       </c>
-      <c r="H52" s="47">
-        <f>IF(ISNUMBER(MATCH(9,'3 Options'!$I$6:$I$14,0)),IF(AND(MATCH(9,'3 Options'!$I$6:$I$14,0)=9,'3 Options'!$D$15&lt;&gt;""),'3 Options'!$D$15,IF(OR(MATCH(9,'3 Options'!$I$6:$I$14,0)=4,MATCH(9,'3 Options'!$I$6:$I$14,0)=5),INDEX(Textes!$B$2:$C$54,MATCH("tr_note",Textes!$A$2:$A$54,0),Listes!$H$1),"")),"")</f>
+      <c r="H52" s="49">
+        <f>IF(ISNUMBER(MATCH(9,'3 Options'!$I$6:$I$14,0)),IF(MATCH(9,'3 Options'!$I$6:$I$14,0)=9,IF('3 Options'!$G$14="Forfait calculé (S + O + UC)",IF(Listes!$H$1=1,'3 Options'!$C$16&amp;" j stand-by + "&amp;'3 Options'!$C$17&amp;" j opérations + UC",'3 Options'!$C$16&amp;" stand-by days + "&amp;'3 Options'!$C$17&amp;" operation days + UC")&amp;IF('3 Options'!$D$15&lt;&gt;"","  ·  "&amp;'3 Options'!$D$15,""),'3 Options'!$D$15),IF(OR(MATCH(9,'3 Options'!$I$6:$I$14,0)=4,MATCH(9,'3 Options'!$I$6:$I$14,0)=5),INDEX(Textes!$B$2:$C$54,MATCH("tr_note",Textes!$A$2:$A$54,0),Listes!$H$1),"")),"")</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="8" customHeight="1"/>
     <row r="54" ht="18" customHeight="1">
-      <c r="C54" s="48">
+      <c r="C54" s="50">
         <f>IF('1 Affaire'!$F$25="Oui",IF(Listes!$H$1=1,"Basée sur "&amp;'1 Affaire'!$C$25&amp;" j de stand-by et "&amp;'1 Affaire'!$C$26&amp;" j d'opérations. Les options « €/jour » sont comptées sur les jours d’opérations. Hors valeur de remplacement, inspection, restocking et transport au coût réel.","Based on "&amp;'1 Affaire'!$C$25&amp;" stand-by days and "&amp;'1 Affaire'!$C$26&amp;" operation days. Option day rates are counted on operation days. Excluding replacement value, inspection, restocking and transport at cost."),"")</f>
         <v/>
       </c>
-      <c r="H54" s="49">
+      <c r="H54" s="51">
         <f>IF('1 Affaire'!$F$25="Oui",INDEX(Textes!$B$2:$C$54,MATCH("est",Textes!$A$2:$A$54,0),Listes!$H$1),"")</f>
         <v/>
       </c>
     </row>
     <row r="55" ht="30" customHeight="1">
-      <c r="H55" s="50">
+      <c r="H55" s="52">
         <f>IF('1 Affaire'!$F$25="Oui",SUM('2 Matériel'!$O$6:$O$29)+SUM('3 Options'!$H$6:$H$14)-SUMPRODUCT(('3 Options'!$C$6:$C$14="Oui")*ISNUMBER(SEARCH("€/jour",'3 Options'!$G$6:$G$14))*'3 Options'!$E$6:$E$14*'3 Options'!$F$6:$F$14)+SUMPRODUCT(('3 Options'!$C$6:$C$14="Oui")*ISNUMBER(SEARCH("€/jour",'3 Options'!$G$6:$G$14))*'3 Options'!$E$6:$E$14*'3 Options'!$F$6:$F$14)*N('1 Affaire'!$C$26),"")</f>
         <v/>
       </c>
     </row>
     <row r="56" ht="8" customHeight="1"/>
     <row r="57" ht="20" customHeight="1">
-      <c r="B57" s="34">
+      <c r="B57" s="36">
         <f>INDEX(Textes!$B$2:$C$54,MATCH("sec_cond",Textes!$A$2:$A$54,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="C57" s="35" t="n"/>
-      <c r="D57" s="35" t="n"/>
-      <c r="E57" s="35" t="n"/>
-      <c r="F57" s="35" t="n"/>
-      <c r="G57" s="35" t="n"/>
-      <c r="H57" s="35" t="n"/>
-      <c r="I57" s="35" t="n"/>
-      <c r="J57" s="35" t="n"/>
-      <c r="K57" s="35" t="n"/>
+      <c r="C57" s="37" t="n"/>
+      <c r="D57" s="37" t="n"/>
+      <c r="E57" s="37" t="n"/>
+      <c r="F57" s="37" t="n"/>
+      <c r="G57" s="37" t="n"/>
+      <c r="H57" s="37" t="n"/>
+      <c r="I57" s="37" t="n"/>
+      <c r="J57" s="37" t="n"/>
+      <c r="K57" s="37" t="n"/>
     </row>
     <row r="58" ht="66" customHeight="1">
-      <c r="B58" s="51" t="inlineStr">
+      <c r="B58" s="53" t="inlineStr">
         <is>
           <t>La location s'entend depuis le jour de départ de la base d'origine jusqu'à son retour au même endroit.
 Le Wear Charge s'applique pour toute usure liée à un usage normal des équipements. En cas de dommages plus importants liés à un usage anormal, la valeur de remplacement sera facturée sur documentation.
@@ -4488,7 +4826,7 @@
       </c>
     </row>
     <row r="59" ht="66" customHeight="1">
-      <c r="B59" s="52" t="inlineStr">
+      <c r="B59" s="54" t="inlineStr">
         <is>
           <t>The rental is from the day of departure from the base of origin until its return to the same place.
 Wear Charge applies to all wear and tear related to normal use of equipment. In case of greater damage due to abnormal use, the replacement value will be charged based on supporting documentation.
@@ -4499,70 +4837,70 @@
     </row>
     <row r="60" ht="10" customHeight="1"/>
     <row r="61">
-      <c r="B61" s="53">
+      <c r="B61" s="55">
         <f>INDEX(Textes!$B$2:$C$54,MATCH("accept",Textes!$A$2:$A$54,0),Listes!$H$1)</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="16" customHeight="1">
-      <c r="B62" s="54">
+      <c r="B62" s="56">
         <f>INDEX(Textes!$B$2:$C$54,MATCH("sig_name",Textes!$A$2:$A$54,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="C62" s="55" t="n"/>
-      <c r="D62" s="56" t="n"/>
-      <c r="E62" s="54">
+      <c r="C62" s="57" t="n"/>
+      <c r="D62" s="58" t="n"/>
+      <c r="E62" s="56">
         <f>INDEX(Textes!$B$2:$C$54,MATCH("sig_date",Textes!$A$2:$A$54,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="F62" s="55" t="n"/>
-      <c r="G62" s="56" t="n"/>
-      <c r="H62" s="54">
+      <c r="F62" s="57" t="n"/>
+      <c r="G62" s="58" t="n"/>
+      <c r="H62" s="56">
         <f>INDEX(Textes!$B$2:$C$54,MATCH("sig_sig",Textes!$A$2:$A$54,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="I62" s="55" t="n"/>
-      <c r="J62" s="55" t="n"/>
-      <c r="K62" s="56" t="n"/>
+      <c r="I62" s="57" t="n"/>
+      <c r="J62" s="57" t="n"/>
+      <c r="K62" s="58" t="n"/>
     </row>
     <row r="63" ht="16" customHeight="1">
-      <c r="B63" s="57" t="n"/>
-      <c r="C63" s="58" t="n"/>
-      <c r="D63" s="59" t="n"/>
-      <c r="E63" s="57" t="n"/>
-      <c r="F63" s="58" t="n"/>
-      <c r="G63" s="59" t="n"/>
-      <c r="H63" s="57" t="n"/>
-      <c r="I63" s="58" t="n"/>
-      <c r="J63" s="58" t="n"/>
-      <c r="K63" s="59" t="n"/>
+      <c r="B63" s="59" t="n"/>
+      <c r="C63" s="60" t="n"/>
+      <c r="D63" s="61" t="n"/>
+      <c r="E63" s="59" t="n"/>
+      <c r="F63" s="60" t="n"/>
+      <c r="G63" s="61" t="n"/>
+      <c r="H63" s="59" t="n"/>
+      <c r="I63" s="60" t="n"/>
+      <c r="J63" s="60" t="n"/>
+      <c r="K63" s="61" t="n"/>
     </row>
     <row r="64" ht="16" customHeight="1">
-      <c r="B64" s="57" t="n"/>
-      <c r="C64" s="58" t="n"/>
-      <c r="D64" s="59" t="n"/>
-      <c r="E64" s="57" t="n"/>
-      <c r="F64" s="58" t="n"/>
-      <c r="G64" s="59" t="n"/>
-      <c r="H64" s="57" t="n"/>
-      <c r="I64" s="58" t="n"/>
-      <c r="J64" s="58" t="n"/>
-      <c r="K64" s="59" t="n"/>
+      <c r="B64" s="59" t="n"/>
+      <c r="C64" s="60" t="n"/>
+      <c r="D64" s="61" t="n"/>
+      <c r="E64" s="59" t="n"/>
+      <c r="F64" s="60" t="n"/>
+      <c r="G64" s="61" t="n"/>
+      <c r="H64" s="59" t="n"/>
+      <c r="I64" s="60" t="n"/>
+      <c r="J64" s="60" t="n"/>
+      <c r="K64" s="61" t="n"/>
     </row>
     <row r="65" ht="16" customHeight="1">
-      <c r="B65" s="60" t="n"/>
-      <c r="C65" s="33" t="n"/>
-      <c r="D65" s="61" t="n"/>
-      <c r="E65" s="60" t="n"/>
-      <c r="F65" s="33" t="n"/>
-      <c r="G65" s="61" t="n"/>
-      <c r="H65" s="60" t="n"/>
-      <c r="I65" s="33" t="n"/>
-      <c r="J65" s="33" t="n"/>
-      <c r="K65" s="61" t="n"/>
+      <c r="B65" s="62" t="n"/>
+      <c r="C65" s="35" t="n"/>
+      <c r="D65" s="63" t="n"/>
+      <c r="E65" s="62" t="n"/>
+      <c r="F65" s="35" t="n"/>
+      <c r="G65" s="63" t="n"/>
+      <c r="H65" s="62" t="n"/>
+      <c r="I65" s="35" t="n"/>
+      <c r="J65" s="35" t="n"/>
+      <c r="K65" s="63" t="n"/>
     </row>
     <row r="67">
-      <c r="B67" s="62" t="inlineStr">
+      <c r="B67" s="64" t="inlineStr">
         <is>
           <t>ENEDRIL · Z-Induspal · 3 Av. des Lacs · 64140 LONS (France) · SIRET 79464246200020 · TVA FR11794642462</t>
         </is>
@@ -4701,7 +5039,7 @@
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
       <c r="E1" s="1" t="n"/>
-      <c r="F1" s="29" t="inlineStr">
+      <c r="F1" s="31" t="inlineStr">
         <is>
           <t>TOOL LIST  ·  LISTE DE MATÉRIEL</t>
         </is>
@@ -4713,7 +5051,7 @@
       <c r="C2" s="1" t="n"/>
       <c r="D2" s="1" t="n"/>
       <c r="E2" s="1" t="n"/>
-      <c r="F2" s="30">
+      <c r="F2" s="32">
         <f>"N° "&amp;'1 Affaire'!$C$18&amp;IF('1 Affaire'!$C$12="","","   ·   Dossier "&amp;'1 Affaire'!$C$12)</f>
         <v/>
       </c>
@@ -4740,153 +5078,153 @@
     </row>
     <row r="4" ht="8" customHeight="1"/>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>CLIENT</t>
         </is>
       </c>
-      <c r="E5" s="31" t="inlineStr">
+      <c r="E5" s="33" t="inlineStr">
         <is>
           <t>DOSSIER N°</t>
         </is>
       </c>
-      <c r="I5" s="31" t="inlineStr">
+      <c r="I5" s="33" t="inlineStr">
         <is>
           <t>RIG / PUITS</t>
         </is>
       </c>
-      <c r="L5" s="31" t="inlineStr">
+      <c r="L5" s="33" t="inlineStr">
         <is>
           <t>A / AT (DESTINATION)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="19" customHeight="1">
-      <c r="A6" s="32">
+      <c r="A6" s="34">
         <f>""&amp;'1 Affaire'!$C$8</f>
         <v/>
       </c>
-      <c r="B6" s="33" t="n"/>
-      <c r="C6" s="33" t="n"/>
-      <c r="D6" s="33" t="n"/>
-      <c r="E6" s="32">
+      <c r="B6" s="35" t="n"/>
+      <c r="C6" s="35" t="n"/>
+      <c r="D6" s="35" t="n"/>
+      <c r="E6" s="34">
         <f>""&amp;'1 Affaire'!$C$12</f>
         <v/>
       </c>
-      <c r="F6" s="33" t="n"/>
-      <c r="G6" s="33" t="n"/>
-      <c r="H6" s="33" t="n"/>
-      <c r="I6" s="32">
+      <c r="F6" s="35" t="n"/>
+      <c r="G6" s="35" t="n"/>
+      <c r="H6" s="35" t="n"/>
+      <c r="I6" s="34">
         <f>'1 Affaire'!$C$11&amp;IF('1 Affaire'!$C$10&lt;&gt;""," · "&amp;'1 Affaire'!$C$10,"")</f>
         <v/>
       </c>
-      <c r="J6" s="33" t="n"/>
-      <c r="K6" s="33" t="n"/>
-      <c r="L6" s="32">
+      <c r="J6" s="35" t="n"/>
+      <c r="K6" s="35" t="n"/>
+      <c r="L6" s="34">
         <f>""&amp;'1 Affaire'!$C$22</f>
         <v/>
       </c>
-      <c r="M6" s="33" t="n"/>
-      <c r="N6" s="33" t="n"/>
-      <c r="O6" s="33" t="n"/>
-      <c r="P6" s="33" t="n"/>
-      <c r="Q6" s="33" t="n"/>
-      <c r="R6" s="33" t="n"/>
+      <c r="M6" s="35" t="n"/>
+      <c r="N6" s="35" t="n"/>
+      <c r="O6" s="35" t="n"/>
+      <c r="P6" s="35" t="n"/>
+      <c r="Q6" s="35" t="n"/>
+      <c r="R6" s="35" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="31" t="inlineStr">
+      <c r="A7" s="33" t="inlineStr">
         <is>
           <t>DATE DE DÉPART</t>
         </is>
       </c>
-      <c r="E7" s="31" t="inlineStr">
+      <c r="E7" s="33" t="inlineStr">
         <is>
           <t>FAITE LE</t>
         </is>
       </c>
-      <c r="I7" s="31" t="inlineStr">
+      <c r="I7" s="33" t="inlineStr">
         <is>
           <t>FAITE PAR</t>
         </is>
       </c>
-      <c r="L7" s="31" t="inlineStr">
+      <c r="L7" s="33" t="inlineStr">
         <is>
           <t>RÉVISÉE LE · PAR</t>
         </is>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
-      <c r="A8" s="32">
+      <c r="A8" s="34">
         <f>IF('1 Affaire'!$C$21="","",TEXT('1 Affaire'!$C$21,"dd/mm/yyyy"))</f>
         <v/>
       </c>
-      <c r="B8" s="33" t="n"/>
-      <c r="C8" s="33" t="n"/>
-      <c r="D8" s="33" t="n"/>
-      <c r="E8" s="32">
+      <c r="B8" s="35" t="n"/>
+      <c r="C8" s="35" t="n"/>
+      <c r="D8" s="35" t="n"/>
+      <c r="E8" s="34">
         <f>IF('1 Affaire'!$C$19="","",TEXT('1 Affaire'!$C$19,"dd/mm/yyyy"))</f>
         <v/>
       </c>
-      <c r="F8" s="33" t="n"/>
-      <c r="G8" s="33" t="n"/>
-      <c r="H8" s="33" t="n"/>
-      <c r="I8" s="32">
+      <c r="F8" s="35" t="n"/>
+      <c r="G8" s="35" t="n"/>
+      <c r="H8" s="35" t="n"/>
+      <c r="I8" s="34">
         <f>""&amp;'1 Affaire'!$C$20</f>
         <v/>
       </c>
-      <c r="J8" s="33" t="n"/>
-      <c r="K8" s="33" t="n"/>
-      <c r="L8" s="32">
+      <c r="J8" s="35" t="n"/>
+      <c r="K8" s="35" t="n"/>
+      <c r="L8" s="34">
         <f>IF('1 Affaire'!$F$18="","",TEXT('1 Affaire'!$F$18,"dd/mm/yyyy")&amp;"  ·  "&amp;'1 Affaire'!$F$19)</f>
         <v/>
       </c>
-      <c r="M8" s="33" t="n"/>
-      <c r="N8" s="33" t="n"/>
-      <c r="O8" s="33" t="n"/>
-      <c r="P8" s="33" t="n"/>
-      <c r="Q8" s="33" t="n"/>
-      <c r="R8" s="33" t="n"/>
+      <c r="M8" s="35" t="n"/>
+      <c r="N8" s="35" t="n"/>
+      <c r="O8" s="35" t="n"/>
+      <c r="P8" s="35" t="n"/>
+      <c r="Q8" s="35" t="n"/>
+      <c r="R8" s="35" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>DESCRIPTION GÉNÉRALE</t>
         </is>
       </c>
-      <c r="L9" s="31" t="inlineStr">
+      <c r="L9" s="33" t="inlineStr">
         <is>
           <t>COLISAGE</t>
         </is>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
-      <c r="A10" s="32">
+      <c r="A10" s="34">
         <f>""&amp;'1 Affaire'!$C$14</f>
         <v/>
       </c>
-      <c r="B10" s="33" t="n"/>
-      <c r="C10" s="33" t="n"/>
-      <c r="D10" s="33" t="n"/>
-      <c r="E10" s="33" t="n"/>
-      <c r="F10" s="33" t="n"/>
-      <c r="G10" s="33" t="n"/>
-      <c r="H10" s="33" t="n"/>
-      <c r="I10" s="33" t="n"/>
-      <c r="J10" s="33" t="n"/>
-      <c r="K10" s="33" t="n"/>
-      <c r="L10" s="32">
+      <c r="B10" s="35" t="n"/>
+      <c r="C10" s="35" t="n"/>
+      <c r="D10" s="35" t="n"/>
+      <c r="E10" s="35" t="n"/>
+      <c r="F10" s="35" t="n"/>
+      <c r="G10" s="35" t="n"/>
+      <c r="H10" s="35" t="n"/>
+      <c r="I10" s="35" t="n"/>
+      <c r="J10" s="35" t="n"/>
+      <c r="K10" s="35" t="n"/>
+      <c r="L10" s="34">
         <f>""&amp;'1 Affaire'!$F$20</f>
         <v/>
       </c>
-      <c r="M10" s="33" t="n"/>
-      <c r="N10" s="33" t="n"/>
-      <c r="O10" s="33" t="n"/>
-      <c r="P10" s="33" t="n"/>
-      <c r="Q10" s="33" t="n"/>
-      <c r="R10" s="33" t="n"/>
+      <c r="M10" s="35" t="n"/>
+      <c r="N10" s="35" t="n"/>
+      <c r="O10" s="35" t="n"/>
+      <c r="P10" s="35" t="n"/>
+      <c r="Q10" s="35" t="n"/>
+      <c r="R10" s="35" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="63" t="inlineStr">
+      <c r="A11" s="65" t="inlineStr">
         <is>
           <t>Toute modification par rapport à la liste ci-dessous doit être évitée, et impérativement signalée si pas le choix.</t>
         </is>
@@ -4894,7 +5232,7 @@
     </row>
     <row r="12" ht="4" customHeight="1"/>
     <row r="13">
-      <c r="A13" s="64" t="inlineStr">
+      <c r="A13" s="66" t="inlineStr">
         <is>
           <t>ÉQUIPEMENT</t>
         </is>
@@ -4902,30 +5240,30 @@
       <c r="B13" s="1" t="n"/>
       <c r="C13" s="1" t="n"/>
       <c r="D13" s="1" t="n"/>
-      <c r="E13" s="65" t="inlineStr">
+      <c r="E13" s="67" t="inlineStr">
         <is>
           <t>RELEVÉS · MEASUREMENTS (in / pouces)</t>
         </is>
       </c>
-      <c r="F13" s="35" t="n"/>
-      <c r="G13" s="35" t="n"/>
-      <c r="H13" s="35" t="n"/>
-      <c r="I13" s="35" t="n"/>
-      <c r="J13" s="64" t="inlineStr">
+      <c r="F13" s="37" t="n"/>
+      <c r="G13" s="37" t="n"/>
+      <c r="H13" s="37" t="n"/>
+      <c r="I13" s="37" t="n"/>
+      <c r="J13" s="66" t="inlineStr">
         <is>
           <t>STOCK ET REMARQUES</t>
         </is>
       </c>
       <c r="K13" s="1" t="n"/>
-      <c r="L13" s="65" t="inlineStr">
+      <c r="L13" s="67" t="inlineStr">
         <is>
           <t>AVANCEMENT PRÉPARATION</t>
         </is>
       </c>
-      <c r="M13" s="35" t="n"/>
-      <c r="N13" s="35" t="n"/>
-      <c r="O13" s="35" t="n"/>
-      <c r="P13" s="64" t="inlineStr">
+      <c r="M13" s="37" t="n"/>
+      <c r="N13" s="37" t="n"/>
+      <c r="O13" s="37" t="n"/>
+      <c r="P13" s="66" t="inlineStr">
         <is>
           <t>CONTRÔLE SUPERVISEUR</t>
         </is>
@@ -4934,1437 +5272,1317 @@
       <c r="R13" s="1" t="n"/>
     </row>
     <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="36" t="inlineStr">
+      <c r="A14" s="38" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B14" s="36" t="inlineStr">
-        <is>
-          <t>Ligne
-devis</t>
-        </is>
-      </c>
-      <c r="C14" s="36" t="inlineStr">
+      <c r="B14" s="38" t="inlineStr">
+        <is>
+          <t>Référence
+(PL)</t>
+        </is>
+      </c>
+      <c r="C14" s="38" t="inlineStr">
         <is>
           <t>Serial Number</t>
         </is>
       </c>
-      <c r="D14" s="36" t="inlineStr">
+      <c r="D14" s="38" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E14" s="36" t="inlineStr">
+      <c r="E14" s="38" t="inlineStr">
         <is>
           <t>OD</t>
         </is>
       </c>
-      <c r="F14" s="36" t="inlineStr">
+      <c r="F14" s="38" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="G14" s="36" t="inlineStr">
+      <c r="G14" s="38" t="inlineStr">
         <is>
           <t>Ouverture
 blades</t>
         </is>
       </c>
-      <c r="H14" s="36" t="inlineStr">
+      <c r="H14" s="38" t="inlineStr">
         <is>
           <t>Ouverture max
 couteaux</t>
         </is>
       </c>
-      <c r="I14" s="36" t="inlineStr">
+      <c r="I14" s="38" t="inlineStr">
         <is>
           <t>Taille / test
 confirmé</t>
         </is>
       </c>
-      <c r="J14" s="36" t="inlineStr">
+      <c r="J14" s="38" t="inlineStr">
         <is>
           <t>Stock
 @CC</t>
         </is>
       </c>
-      <c r="K14" s="36" t="inlineStr">
+      <c r="K14" s="38" t="inlineStr">
         <is>
           <t>Commentaire</t>
         </is>
       </c>
-      <c r="L14" s="36" t="inlineStr">
+      <c r="L14" s="38" t="inlineStr">
         <is>
           <t>Prêt à
 partir</t>
         </is>
       </c>
-      <c r="M14" s="36" t="inlineStr">
+      <c r="M14" s="38" t="inlineStr">
         <is>
           <t>Le</t>
         </is>
       </c>
-      <c r="N14" s="36" t="inlineStr">
+      <c r="N14" s="38" t="inlineStr">
         <is>
           <t>Par</t>
         </is>
       </c>
-      <c r="O14" s="36" t="inlineStr">
+      <c r="O14" s="38" t="inlineStr">
         <is>
           <t>Colisage
 (n° colis)</t>
         </is>
       </c>
-      <c r="P14" s="36" t="inlineStr">
+      <c r="P14" s="38" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="Q14" s="36" t="inlineStr">
+      <c r="Q14" s="38" t="inlineStr">
         <is>
           <t>Le</t>
         </is>
       </c>
-      <c r="R14" s="36" t="inlineStr">
+      <c r="R14" s="38" t="inlineStr">
         <is>
           <t>Par</t>
         </is>
       </c>
-      <c r="T14" s="66" t="inlineStr">
+      <c r="T14" s="68" t="inlineStr">
         <is>
           <t>ptr</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="15">
+    <row r="15" ht="27" customHeight="1">
+      <c r="A15" s="16">
         <f>IF(1&lt;=SUM('2 Matériel'!$M$6:$M$29),1,"")</f>
         <v/>
       </c>
-      <c r="B15" s="67">
-        <f>IF(A15="","",INDEX('2 Matériel'!$A$6:$A$29,$T15)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T15)&gt;1,"  ("&amp;(A15-INDEX('2 Matériel'!$N$6:$N$29,$T15)+INDEX('2 Matériel'!$M$6:$M$29,$T15))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T15)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C15" s="68" t="n"/>
-      <c r="D15" s="38">
-        <f>IF(A15="","",INDEX('2 Matériel'!$C$6:$C$29,$T15))</f>
-        <v/>
-      </c>
-      <c r="E15" s="69" t="n"/>
-      <c r="F15" s="69" t="n"/>
-      <c r="G15" s="69" t="n"/>
-      <c r="H15" s="69" t="n"/>
-      <c r="I15" s="70" t="n"/>
-      <c r="J15" s="70" t="n"/>
-      <c r="K15" s="68" t="n"/>
-      <c r="L15" s="70" t="n"/>
-      <c r="M15" s="71" t="n"/>
-      <c r="N15" s="70" t="n"/>
-      <c r="O15" s="70" t="n"/>
-      <c r="P15" s="70" t="n"/>
-      <c r="Q15" s="71" t="n"/>
-      <c r="R15" s="70" t="n"/>
-      <c r="T15" s="72">
+      <c r="B15" s="69" t="n"/>
+      <c r="C15" s="70" t="n"/>
+      <c r="D15" s="71">
+        <f>IF(A15="","",INDEX('2 Matériel'!$C$6:$C$29,$T15)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T15)&gt;1,"  ("&amp;(A15-INDEX('2 Matériel'!$N$6:$N$29,$T15)+INDEX('2 Matériel'!$M$6:$M$29,$T15))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T15)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T15)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T15),""))</f>
+        <v/>
+      </c>
+      <c r="E15" s="72" t="n"/>
+      <c r="F15" s="72" t="n"/>
+      <c r="G15" s="72" t="n"/>
+      <c r="H15" s="72" t="n"/>
+      <c r="I15" s="69" t="n"/>
+      <c r="J15" s="69" t="n"/>
+      <c r="K15" s="70" t="n"/>
+      <c r="L15" s="69" t="n"/>
+      <c r="M15" s="73" t="n"/>
+      <c r="N15" s="69" t="n"/>
+      <c r="O15" s="69" t="n"/>
+      <c r="P15" s="69" t="n"/>
+      <c r="Q15" s="73" t="n"/>
+      <c r="R15" s="69" t="n"/>
+      <c r="T15" s="74">
         <f>IF(A15="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A15)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="15">
+    <row r="16" ht="27" customHeight="1">
+      <c r="A16" s="16">
         <f>IF(2&lt;=SUM('2 Matériel'!$M$6:$M$29),2,"")</f>
         <v/>
       </c>
-      <c r="B16" s="67">
-        <f>IF(A16="","",INDEX('2 Matériel'!$A$6:$A$29,$T16)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T16)&gt;1,"  ("&amp;(A16-INDEX('2 Matériel'!$N$6:$N$29,$T16)+INDEX('2 Matériel'!$M$6:$M$29,$T16))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T16)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C16" s="68" t="n"/>
-      <c r="D16" s="38">
-        <f>IF(A16="","",INDEX('2 Matériel'!$C$6:$C$29,$T16))</f>
-        <v/>
-      </c>
-      <c r="E16" s="69" t="n"/>
-      <c r="F16" s="69" t="n"/>
-      <c r="G16" s="69" t="n"/>
-      <c r="H16" s="69" t="n"/>
-      <c r="I16" s="70" t="n"/>
-      <c r="J16" s="70" t="n"/>
-      <c r="K16" s="68" t="n"/>
-      <c r="L16" s="70" t="n"/>
-      <c r="M16" s="71" t="n"/>
-      <c r="N16" s="70" t="n"/>
-      <c r="O16" s="70" t="n"/>
-      <c r="P16" s="70" t="n"/>
-      <c r="Q16" s="71" t="n"/>
-      <c r="R16" s="70" t="n"/>
-      <c r="T16" s="72">
+      <c r="B16" s="69" t="n"/>
+      <c r="C16" s="70" t="n"/>
+      <c r="D16" s="71">
+        <f>IF(A16="","",INDEX('2 Matériel'!$C$6:$C$29,$T16)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T16)&gt;1,"  ("&amp;(A16-INDEX('2 Matériel'!$N$6:$N$29,$T16)+INDEX('2 Matériel'!$M$6:$M$29,$T16))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T16)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T16)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T16),""))</f>
+        <v/>
+      </c>
+      <c r="E16" s="72" t="n"/>
+      <c r="F16" s="72" t="n"/>
+      <c r="G16" s="72" t="n"/>
+      <c r="H16" s="72" t="n"/>
+      <c r="I16" s="69" t="n"/>
+      <c r="J16" s="69" t="n"/>
+      <c r="K16" s="70" t="n"/>
+      <c r="L16" s="69" t="n"/>
+      <c r="M16" s="73" t="n"/>
+      <c r="N16" s="69" t="n"/>
+      <c r="O16" s="69" t="n"/>
+      <c r="P16" s="69" t="n"/>
+      <c r="Q16" s="73" t="n"/>
+      <c r="R16" s="69" t="n"/>
+      <c r="T16" s="74">
         <f>IF(A16="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A16)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="15">
+    <row r="17" ht="27" customHeight="1">
+      <c r="A17" s="16">
         <f>IF(3&lt;=SUM('2 Matériel'!$M$6:$M$29),3,"")</f>
         <v/>
       </c>
-      <c r="B17" s="67">
-        <f>IF(A17="","",INDEX('2 Matériel'!$A$6:$A$29,$T17)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T17)&gt;1,"  ("&amp;(A17-INDEX('2 Matériel'!$N$6:$N$29,$T17)+INDEX('2 Matériel'!$M$6:$M$29,$T17))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T17)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C17" s="68" t="n"/>
-      <c r="D17" s="38">
-        <f>IF(A17="","",INDEX('2 Matériel'!$C$6:$C$29,$T17))</f>
-        <v/>
-      </c>
-      <c r="E17" s="69" t="n"/>
-      <c r="F17" s="69" t="n"/>
-      <c r="G17" s="69" t="n"/>
-      <c r="H17" s="69" t="n"/>
-      <c r="I17" s="70" t="n"/>
-      <c r="J17" s="70" t="n"/>
-      <c r="K17" s="68" t="n"/>
-      <c r="L17" s="70" t="n"/>
-      <c r="M17" s="71" t="n"/>
-      <c r="N17" s="70" t="n"/>
-      <c r="O17" s="70" t="n"/>
-      <c r="P17" s="70" t="n"/>
-      <c r="Q17" s="71" t="n"/>
-      <c r="R17" s="70" t="n"/>
-      <c r="T17" s="72">
+      <c r="B17" s="69" t="n"/>
+      <c r="C17" s="70" t="n"/>
+      <c r="D17" s="71">
+        <f>IF(A17="","",INDEX('2 Matériel'!$C$6:$C$29,$T17)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T17)&gt;1,"  ("&amp;(A17-INDEX('2 Matériel'!$N$6:$N$29,$T17)+INDEX('2 Matériel'!$M$6:$M$29,$T17))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T17)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T17)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T17),""))</f>
+        <v/>
+      </c>
+      <c r="E17" s="72" t="n"/>
+      <c r="F17" s="72" t="n"/>
+      <c r="G17" s="72" t="n"/>
+      <c r="H17" s="72" t="n"/>
+      <c r="I17" s="69" t="n"/>
+      <c r="J17" s="69" t="n"/>
+      <c r="K17" s="70" t="n"/>
+      <c r="L17" s="69" t="n"/>
+      <c r="M17" s="73" t="n"/>
+      <c r="N17" s="69" t="n"/>
+      <c r="O17" s="69" t="n"/>
+      <c r="P17" s="69" t="n"/>
+      <c r="Q17" s="73" t="n"/>
+      <c r="R17" s="69" t="n"/>
+      <c r="T17" s="74">
         <f>IF(A17="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A17)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="15">
+    <row r="18" ht="27" customHeight="1">
+      <c r="A18" s="16">
         <f>IF(4&lt;=SUM('2 Matériel'!$M$6:$M$29),4,"")</f>
         <v/>
       </c>
-      <c r="B18" s="67">
-        <f>IF(A18="","",INDEX('2 Matériel'!$A$6:$A$29,$T18)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T18)&gt;1,"  ("&amp;(A18-INDEX('2 Matériel'!$N$6:$N$29,$T18)+INDEX('2 Matériel'!$M$6:$M$29,$T18))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T18)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C18" s="68" t="n"/>
-      <c r="D18" s="38">
-        <f>IF(A18="","",INDEX('2 Matériel'!$C$6:$C$29,$T18))</f>
-        <v/>
-      </c>
-      <c r="E18" s="69" t="n"/>
-      <c r="F18" s="69" t="n"/>
-      <c r="G18" s="69" t="n"/>
-      <c r="H18" s="69" t="n"/>
-      <c r="I18" s="70" t="n"/>
-      <c r="J18" s="70" t="n"/>
-      <c r="K18" s="68" t="n"/>
-      <c r="L18" s="70" t="n"/>
-      <c r="M18" s="71" t="n"/>
-      <c r="N18" s="70" t="n"/>
-      <c r="O18" s="70" t="n"/>
-      <c r="P18" s="70" t="n"/>
-      <c r="Q18" s="71" t="n"/>
-      <c r="R18" s="70" t="n"/>
-      <c r="T18" s="72">
+      <c r="B18" s="69" t="n"/>
+      <c r="C18" s="70" t="n"/>
+      <c r="D18" s="71">
+        <f>IF(A18="","",INDEX('2 Matériel'!$C$6:$C$29,$T18)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T18)&gt;1,"  ("&amp;(A18-INDEX('2 Matériel'!$N$6:$N$29,$T18)+INDEX('2 Matériel'!$M$6:$M$29,$T18))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T18)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T18)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T18),""))</f>
+        <v/>
+      </c>
+      <c r="E18" s="72" t="n"/>
+      <c r="F18" s="72" t="n"/>
+      <c r="G18" s="72" t="n"/>
+      <c r="H18" s="72" t="n"/>
+      <c r="I18" s="69" t="n"/>
+      <c r="J18" s="69" t="n"/>
+      <c r="K18" s="70" t="n"/>
+      <c r="L18" s="69" t="n"/>
+      <c r="M18" s="73" t="n"/>
+      <c r="N18" s="69" t="n"/>
+      <c r="O18" s="69" t="n"/>
+      <c r="P18" s="69" t="n"/>
+      <c r="Q18" s="73" t="n"/>
+      <c r="R18" s="69" t="n"/>
+      <c r="T18" s="74">
         <f>IF(A18="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A18)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="15">
+    <row r="19" ht="27" customHeight="1">
+      <c r="A19" s="16">
         <f>IF(5&lt;=SUM('2 Matériel'!$M$6:$M$29),5,"")</f>
         <v/>
       </c>
-      <c r="B19" s="67">
-        <f>IF(A19="","",INDEX('2 Matériel'!$A$6:$A$29,$T19)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T19)&gt;1,"  ("&amp;(A19-INDEX('2 Matériel'!$N$6:$N$29,$T19)+INDEX('2 Matériel'!$M$6:$M$29,$T19))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T19)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C19" s="68" t="n"/>
-      <c r="D19" s="38">
-        <f>IF(A19="","",INDEX('2 Matériel'!$C$6:$C$29,$T19))</f>
-        <v/>
-      </c>
-      <c r="E19" s="69" t="n"/>
-      <c r="F19" s="69" t="n"/>
-      <c r="G19" s="69" t="n"/>
-      <c r="H19" s="69" t="n"/>
-      <c r="I19" s="70" t="n"/>
-      <c r="J19" s="70" t="n"/>
-      <c r="K19" s="68" t="n"/>
-      <c r="L19" s="70" t="n"/>
-      <c r="M19" s="71" t="n"/>
-      <c r="N19" s="70" t="n"/>
-      <c r="O19" s="70" t="n"/>
-      <c r="P19" s="70" t="n"/>
-      <c r="Q19" s="71" t="n"/>
-      <c r="R19" s="70" t="n"/>
-      <c r="T19" s="72">
+      <c r="B19" s="69" t="n"/>
+      <c r="C19" s="70" t="n"/>
+      <c r="D19" s="71">
+        <f>IF(A19="","",INDEX('2 Matériel'!$C$6:$C$29,$T19)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T19)&gt;1,"  ("&amp;(A19-INDEX('2 Matériel'!$N$6:$N$29,$T19)+INDEX('2 Matériel'!$M$6:$M$29,$T19))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T19)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T19)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T19),""))</f>
+        <v/>
+      </c>
+      <c r="E19" s="72" t="n"/>
+      <c r="F19" s="72" t="n"/>
+      <c r="G19" s="72" t="n"/>
+      <c r="H19" s="72" t="n"/>
+      <c r="I19" s="69" t="n"/>
+      <c r="J19" s="69" t="n"/>
+      <c r="K19" s="70" t="n"/>
+      <c r="L19" s="69" t="n"/>
+      <c r="M19" s="73" t="n"/>
+      <c r="N19" s="69" t="n"/>
+      <c r="O19" s="69" t="n"/>
+      <c r="P19" s="69" t="n"/>
+      <c r="Q19" s="73" t="n"/>
+      <c r="R19" s="69" t="n"/>
+      <c r="T19" s="74">
         <f>IF(A19="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A19)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="15">
+    <row r="20" ht="27" customHeight="1">
+      <c r="A20" s="16">
         <f>IF(6&lt;=SUM('2 Matériel'!$M$6:$M$29),6,"")</f>
         <v/>
       </c>
-      <c r="B20" s="67">
-        <f>IF(A20="","",INDEX('2 Matériel'!$A$6:$A$29,$T20)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T20)&gt;1,"  ("&amp;(A20-INDEX('2 Matériel'!$N$6:$N$29,$T20)+INDEX('2 Matériel'!$M$6:$M$29,$T20))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T20)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C20" s="68" t="n"/>
-      <c r="D20" s="38">
-        <f>IF(A20="","",INDEX('2 Matériel'!$C$6:$C$29,$T20))</f>
-        <v/>
-      </c>
-      <c r="E20" s="69" t="n"/>
-      <c r="F20" s="69" t="n"/>
-      <c r="G20" s="69" t="n"/>
-      <c r="H20" s="69" t="n"/>
-      <c r="I20" s="70" t="n"/>
-      <c r="J20" s="70" t="n"/>
-      <c r="K20" s="68" t="n"/>
-      <c r="L20" s="70" t="n"/>
-      <c r="M20" s="71" t="n"/>
-      <c r="N20" s="70" t="n"/>
-      <c r="O20" s="70" t="n"/>
-      <c r="P20" s="70" t="n"/>
-      <c r="Q20" s="71" t="n"/>
-      <c r="R20" s="70" t="n"/>
-      <c r="T20" s="72">
+      <c r="B20" s="69" t="n"/>
+      <c r="C20" s="70" t="n"/>
+      <c r="D20" s="71">
+        <f>IF(A20="","",INDEX('2 Matériel'!$C$6:$C$29,$T20)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T20)&gt;1,"  ("&amp;(A20-INDEX('2 Matériel'!$N$6:$N$29,$T20)+INDEX('2 Matériel'!$M$6:$M$29,$T20))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T20)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T20)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T20),""))</f>
+        <v/>
+      </c>
+      <c r="E20" s="72" t="n"/>
+      <c r="F20" s="72" t="n"/>
+      <c r="G20" s="72" t="n"/>
+      <c r="H20" s="72" t="n"/>
+      <c r="I20" s="69" t="n"/>
+      <c r="J20" s="69" t="n"/>
+      <c r="K20" s="70" t="n"/>
+      <c r="L20" s="69" t="n"/>
+      <c r="M20" s="73" t="n"/>
+      <c r="N20" s="69" t="n"/>
+      <c r="O20" s="69" t="n"/>
+      <c r="P20" s="69" t="n"/>
+      <c r="Q20" s="73" t="n"/>
+      <c r="R20" s="69" t="n"/>
+      <c r="T20" s="74">
         <f>IF(A20="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A20)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="15">
+    <row r="21" ht="27" customHeight="1">
+      <c r="A21" s="16">
         <f>IF(7&lt;=SUM('2 Matériel'!$M$6:$M$29),7,"")</f>
         <v/>
       </c>
-      <c r="B21" s="67">
-        <f>IF(A21="","",INDEX('2 Matériel'!$A$6:$A$29,$T21)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T21)&gt;1,"  ("&amp;(A21-INDEX('2 Matériel'!$N$6:$N$29,$T21)+INDEX('2 Matériel'!$M$6:$M$29,$T21))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T21)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C21" s="68" t="n"/>
-      <c r="D21" s="38">
-        <f>IF(A21="","",INDEX('2 Matériel'!$C$6:$C$29,$T21))</f>
-        <v/>
-      </c>
-      <c r="E21" s="69" t="n"/>
-      <c r="F21" s="69" t="n"/>
-      <c r="G21" s="69" t="n"/>
-      <c r="H21" s="69" t="n"/>
-      <c r="I21" s="70" t="n"/>
-      <c r="J21" s="70" t="n"/>
-      <c r="K21" s="68" t="n"/>
-      <c r="L21" s="70" t="n"/>
-      <c r="M21" s="71" t="n"/>
-      <c r="N21" s="70" t="n"/>
-      <c r="O21" s="70" t="n"/>
-      <c r="P21" s="70" t="n"/>
-      <c r="Q21" s="71" t="n"/>
-      <c r="R21" s="70" t="n"/>
-      <c r="T21" s="72">
+      <c r="B21" s="69" t="n"/>
+      <c r="C21" s="70" t="n"/>
+      <c r="D21" s="71">
+        <f>IF(A21="","",INDEX('2 Matériel'!$C$6:$C$29,$T21)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T21)&gt;1,"  ("&amp;(A21-INDEX('2 Matériel'!$N$6:$N$29,$T21)+INDEX('2 Matériel'!$M$6:$M$29,$T21))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T21)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T21)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T21),""))</f>
+        <v/>
+      </c>
+      <c r="E21" s="72" t="n"/>
+      <c r="F21" s="72" t="n"/>
+      <c r="G21" s="72" t="n"/>
+      <c r="H21" s="72" t="n"/>
+      <c r="I21" s="69" t="n"/>
+      <c r="J21" s="69" t="n"/>
+      <c r="K21" s="70" t="n"/>
+      <c r="L21" s="69" t="n"/>
+      <c r="M21" s="73" t="n"/>
+      <c r="N21" s="69" t="n"/>
+      <c r="O21" s="69" t="n"/>
+      <c r="P21" s="69" t="n"/>
+      <c r="Q21" s="73" t="n"/>
+      <c r="R21" s="69" t="n"/>
+      <c r="T21" s="74">
         <f>IF(A21="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A21)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="15">
+    <row r="22" ht="27" customHeight="1">
+      <c r="A22" s="16">
         <f>IF(8&lt;=SUM('2 Matériel'!$M$6:$M$29),8,"")</f>
         <v/>
       </c>
-      <c r="B22" s="67">
-        <f>IF(A22="","",INDEX('2 Matériel'!$A$6:$A$29,$T22)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T22)&gt;1,"  ("&amp;(A22-INDEX('2 Matériel'!$N$6:$N$29,$T22)+INDEX('2 Matériel'!$M$6:$M$29,$T22))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T22)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C22" s="68" t="n"/>
-      <c r="D22" s="38">
-        <f>IF(A22="","",INDEX('2 Matériel'!$C$6:$C$29,$T22))</f>
-        <v/>
-      </c>
-      <c r="E22" s="69" t="n"/>
-      <c r="F22" s="69" t="n"/>
-      <c r="G22" s="69" t="n"/>
-      <c r="H22" s="69" t="n"/>
-      <c r="I22" s="70" t="n"/>
-      <c r="J22" s="70" t="n"/>
-      <c r="K22" s="68" t="n"/>
-      <c r="L22" s="70" t="n"/>
-      <c r="M22" s="71" t="n"/>
-      <c r="N22" s="70" t="n"/>
-      <c r="O22" s="70" t="n"/>
-      <c r="P22" s="70" t="n"/>
-      <c r="Q22" s="71" t="n"/>
-      <c r="R22" s="70" t="n"/>
-      <c r="T22" s="72">
+      <c r="B22" s="69" t="n"/>
+      <c r="C22" s="70" t="n"/>
+      <c r="D22" s="71">
+        <f>IF(A22="","",INDEX('2 Matériel'!$C$6:$C$29,$T22)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T22)&gt;1,"  ("&amp;(A22-INDEX('2 Matériel'!$N$6:$N$29,$T22)+INDEX('2 Matériel'!$M$6:$M$29,$T22))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T22)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T22)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T22),""))</f>
+        <v/>
+      </c>
+      <c r="E22" s="72" t="n"/>
+      <c r="F22" s="72" t="n"/>
+      <c r="G22" s="72" t="n"/>
+      <c r="H22" s="72" t="n"/>
+      <c r="I22" s="69" t="n"/>
+      <c r="J22" s="69" t="n"/>
+      <c r="K22" s="70" t="n"/>
+      <c r="L22" s="69" t="n"/>
+      <c r="M22" s="73" t="n"/>
+      <c r="N22" s="69" t="n"/>
+      <c r="O22" s="69" t="n"/>
+      <c r="P22" s="69" t="n"/>
+      <c r="Q22" s="73" t="n"/>
+      <c r="R22" s="69" t="n"/>
+      <c r="T22" s="74">
         <f>IF(A22="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A22)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="15">
+    <row r="23" ht="27" customHeight="1">
+      <c r="A23" s="16">
         <f>IF(9&lt;=SUM('2 Matériel'!$M$6:$M$29),9,"")</f>
         <v/>
       </c>
-      <c r="B23" s="67">
-        <f>IF(A23="","",INDEX('2 Matériel'!$A$6:$A$29,$T23)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T23)&gt;1,"  ("&amp;(A23-INDEX('2 Matériel'!$N$6:$N$29,$T23)+INDEX('2 Matériel'!$M$6:$M$29,$T23))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T23)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C23" s="68" t="n"/>
-      <c r="D23" s="38">
-        <f>IF(A23="","",INDEX('2 Matériel'!$C$6:$C$29,$T23))</f>
-        <v/>
-      </c>
-      <c r="E23" s="69" t="n"/>
-      <c r="F23" s="69" t="n"/>
-      <c r="G23" s="69" t="n"/>
-      <c r="H23" s="69" t="n"/>
-      <c r="I23" s="70" t="n"/>
-      <c r="J23" s="70" t="n"/>
-      <c r="K23" s="68" t="n"/>
-      <c r="L23" s="70" t="n"/>
-      <c r="M23" s="71" t="n"/>
-      <c r="N23" s="70" t="n"/>
-      <c r="O23" s="70" t="n"/>
-      <c r="P23" s="70" t="n"/>
-      <c r="Q23" s="71" t="n"/>
-      <c r="R23" s="70" t="n"/>
-      <c r="T23" s="72">
+      <c r="B23" s="69" t="n"/>
+      <c r="C23" s="70" t="n"/>
+      <c r="D23" s="71">
+        <f>IF(A23="","",INDEX('2 Matériel'!$C$6:$C$29,$T23)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T23)&gt;1,"  ("&amp;(A23-INDEX('2 Matériel'!$N$6:$N$29,$T23)+INDEX('2 Matériel'!$M$6:$M$29,$T23))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T23)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T23)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T23),""))</f>
+        <v/>
+      </c>
+      <c r="E23" s="72" t="n"/>
+      <c r="F23" s="72" t="n"/>
+      <c r="G23" s="72" t="n"/>
+      <c r="H23" s="72" t="n"/>
+      <c r="I23" s="69" t="n"/>
+      <c r="J23" s="69" t="n"/>
+      <c r="K23" s="70" t="n"/>
+      <c r="L23" s="69" t="n"/>
+      <c r="M23" s="73" t="n"/>
+      <c r="N23" s="69" t="n"/>
+      <c r="O23" s="69" t="n"/>
+      <c r="P23" s="69" t="n"/>
+      <c r="Q23" s="73" t="n"/>
+      <c r="R23" s="69" t="n"/>
+      <c r="T23" s="74">
         <f>IF(A23="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A23)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="15">
+    <row r="24" ht="27" customHeight="1">
+      <c r="A24" s="16">
         <f>IF(10&lt;=SUM('2 Matériel'!$M$6:$M$29),10,"")</f>
         <v/>
       </c>
-      <c r="B24" s="67">
-        <f>IF(A24="","",INDEX('2 Matériel'!$A$6:$A$29,$T24)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T24)&gt;1,"  ("&amp;(A24-INDEX('2 Matériel'!$N$6:$N$29,$T24)+INDEX('2 Matériel'!$M$6:$M$29,$T24))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T24)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C24" s="68" t="n"/>
-      <c r="D24" s="38">
-        <f>IF(A24="","",INDEX('2 Matériel'!$C$6:$C$29,$T24))</f>
-        <v/>
-      </c>
-      <c r="E24" s="69" t="n"/>
-      <c r="F24" s="69" t="n"/>
-      <c r="G24" s="69" t="n"/>
-      <c r="H24" s="69" t="n"/>
-      <c r="I24" s="70" t="n"/>
-      <c r="J24" s="70" t="n"/>
-      <c r="K24" s="68" t="n"/>
-      <c r="L24" s="70" t="n"/>
-      <c r="M24" s="71" t="n"/>
-      <c r="N24" s="70" t="n"/>
-      <c r="O24" s="70" t="n"/>
-      <c r="P24" s="70" t="n"/>
-      <c r="Q24" s="71" t="n"/>
-      <c r="R24" s="70" t="n"/>
-      <c r="T24" s="72">
+      <c r="B24" s="69" t="n"/>
+      <c r="C24" s="70" t="n"/>
+      <c r="D24" s="71">
+        <f>IF(A24="","",INDEX('2 Matériel'!$C$6:$C$29,$T24)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T24)&gt;1,"  ("&amp;(A24-INDEX('2 Matériel'!$N$6:$N$29,$T24)+INDEX('2 Matériel'!$M$6:$M$29,$T24))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T24)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T24)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T24),""))</f>
+        <v/>
+      </c>
+      <c r="E24" s="72" t="n"/>
+      <c r="F24" s="72" t="n"/>
+      <c r="G24" s="72" t="n"/>
+      <c r="H24" s="72" t="n"/>
+      <c r="I24" s="69" t="n"/>
+      <c r="J24" s="69" t="n"/>
+      <c r="K24" s="70" t="n"/>
+      <c r="L24" s="69" t="n"/>
+      <c r="M24" s="73" t="n"/>
+      <c r="N24" s="69" t="n"/>
+      <c r="O24" s="69" t="n"/>
+      <c r="P24" s="69" t="n"/>
+      <c r="Q24" s="73" t="n"/>
+      <c r="R24" s="69" t="n"/>
+      <c r="T24" s="74">
         <f>IF(A24="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A24)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="15">
+    <row r="25" ht="27" customHeight="1">
+      <c r="A25" s="16">
         <f>IF(11&lt;=SUM('2 Matériel'!$M$6:$M$29),11,"")</f>
         <v/>
       </c>
-      <c r="B25" s="67">
-        <f>IF(A25="","",INDEX('2 Matériel'!$A$6:$A$29,$T25)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T25)&gt;1,"  ("&amp;(A25-INDEX('2 Matériel'!$N$6:$N$29,$T25)+INDEX('2 Matériel'!$M$6:$M$29,$T25))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T25)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C25" s="68" t="n"/>
-      <c r="D25" s="38">
-        <f>IF(A25="","",INDEX('2 Matériel'!$C$6:$C$29,$T25))</f>
-        <v/>
-      </c>
-      <c r="E25" s="69" t="n"/>
-      <c r="F25" s="69" t="n"/>
-      <c r="G25" s="69" t="n"/>
-      <c r="H25" s="69" t="n"/>
-      <c r="I25" s="70" t="n"/>
-      <c r="J25" s="70" t="n"/>
-      <c r="K25" s="68" t="n"/>
-      <c r="L25" s="70" t="n"/>
-      <c r="M25" s="71" t="n"/>
-      <c r="N25" s="70" t="n"/>
-      <c r="O25" s="70" t="n"/>
-      <c r="P25" s="70" t="n"/>
-      <c r="Q25" s="71" t="n"/>
-      <c r="R25" s="70" t="n"/>
-      <c r="T25" s="72">
+      <c r="B25" s="69" t="n"/>
+      <c r="C25" s="70" t="n"/>
+      <c r="D25" s="71">
+        <f>IF(A25="","",INDEX('2 Matériel'!$C$6:$C$29,$T25)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T25)&gt;1,"  ("&amp;(A25-INDEX('2 Matériel'!$N$6:$N$29,$T25)+INDEX('2 Matériel'!$M$6:$M$29,$T25))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T25)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T25)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T25),""))</f>
+        <v/>
+      </c>
+      <c r="E25" s="72" t="n"/>
+      <c r="F25" s="72" t="n"/>
+      <c r="G25" s="72" t="n"/>
+      <c r="H25" s="72" t="n"/>
+      <c r="I25" s="69" t="n"/>
+      <c r="J25" s="69" t="n"/>
+      <c r="K25" s="70" t="n"/>
+      <c r="L25" s="69" t="n"/>
+      <c r="M25" s="73" t="n"/>
+      <c r="N25" s="69" t="n"/>
+      <c r="O25" s="69" t="n"/>
+      <c r="P25" s="69" t="n"/>
+      <c r="Q25" s="73" t="n"/>
+      <c r="R25" s="69" t="n"/>
+      <c r="T25" s="74">
         <f>IF(A25="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A25)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="15">
+    <row r="26" ht="27" customHeight="1">
+      <c r="A26" s="16">
         <f>IF(12&lt;=SUM('2 Matériel'!$M$6:$M$29),12,"")</f>
         <v/>
       </c>
-      <c r="B26" s="67">
-        <f>IF(A26="","",INDEX('2 Matériel'!$A$6:$A$29,$T26)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T26)&gt;1,"  ("&amp;(A26-INDEX('2 Matériel'!$N$6:$N$29,$T26)+INDEX('2 Matériel'!$M$6:$M$29,$T26))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T26)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C26" s="68" t="n"/>
-      <c r="D26" s="38">
-        <f>IF(A26="","",INDEX('2 Matériel'!$C$6:$C$29,$T26))</f>
-        <v/>
-      </c>
-      <c r="E26" s="69" t="n"/>
-      <c r="F26" s="69" t="n"/>
-      <c r="G26" s="69" t="n"/>
-      <c r="H26" s="69" t="n"/>
-      <c r="I26" s="70" t="n"/>
-      <c r="J26" s="70" t="n"/>
-      <c r="K26" s="68" t="n"/>
-      <c r="L26" s="70" t="n"/>
-      <c r="M26" s="71" t="n"/>
-      <c r="N26" s="70" t="n"/>
-      <c r="O26" s="70" t="n"/>
-      <c r="P26" s="70" t="n"/>
-      <c r="Q26" s="71" t="n"/>
-      <c r="R26" s="70" t="n"/>
-      <c r="T26" s="72">
+      <c r="B26" s="69" t="n"/>
+      <c r="C26" s="70" t="n"/>
+      <c r="D26" s="71">
+        <f>IF(A26="","",INDEX('2 Matériel'!$C$6:$C$29,$T26)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T26)&gt;1,"  ("&amp;(A26-INDEX('2 Matériel'!$N$6:$N$29,$T26)+INDEX('2 Matériel'!$M$6:$M$29,$T26))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T26)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T26)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T26),""))</f>
+        <v/>
+      </c>
+      <c r="E26" s="72" t="n"/>
+      <c r="F26" s="72" t="n"/>
+      <c r="G26" s="72" t="n"/>
+      <c r="H26" s="72" t="n"/>
+      <c r="I26" s="69" t="n"/>
+      <c r="J26" s="69" t="n"/>
+      <c r="K26" s="70" t="n"/>
+      <c r="L26" s="69" t="n"/>
+      <c r="M26" s="73" t="n"/>
+      <c r="N26" s="69" t="n"/>
+      <c r="O26" s="69" t="n"/>
+      <c r="P26" s="69" t="n"/>
+      <c r="Q26" s="73" t="n"/>
+      <c r="R26" s="69" t="n"/>
+      <c r="T26" s="74">
         <f>IF(A26="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A26)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="15">
+    <row r="27" ht="27" customHeight="1">
+      <c r="A27" s="16">
         <f>IF(13&lt;=SUM('2 Matériel'!$M$6:$M$29),13,"")</f>
         <v/>
       </c>
-      <c r="B27" s="67">
-        <f>IF(A27="","",INDEX('2 Matériel'!$A$6:$A$29,$T27)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T27)&gt;1,"  ("&amp;(A27-INDEX('2 Matériel'!$N$6:$N$29,$T27)+INDEX('2 Matériel'!$M$6:$M$29,$T27))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T27)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C27" s="68" t="n"/>
-      <c r="D27" s="38">
-        <f>IF(A27="","",INDEX('2 Matériel'!$C$6:$C$29,$T27))</f>
-        <v/>
-      </c>
-      <c r="E27" s="69" t="n"/>
-      <c r="F27" s="69" t="n"/>
-      <c r="G27" s="69" t="n"/>
-      <c r="H27" s="69" t="n"/>
-      <c r="I27" s="70" t="n"/>
-      <c r="J27" s="70" t="n"/>
-      <c r="K27" s="68" t="n"/>
-      <c r="L27" s="70" t="n"/>
-      <c r="M27" s="71" t="n"/>
-      <c r="N27" s="70" t="n"/>
-      <c r="O27" s="70" t="n"/>
-      <c r="P27" s="70" t="n"/>
-      <c r="Q27" s="71" t="n"/>
-      <c r="R27" s="70" t="n"/>
-      <c r="T27" s="72">
+      <c r="B27" s="69" t="n"/>
+      <c r="C27" s="70" t="n"/>
+      <c r="D27" s="71">
+        <f>IF(A27="","",INDEX('2 Matériel'!$C$6:$C$29,$T27)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T27)&gt;1,"  ("&amp;(A27-INDEX('2 Matériel'!$N$6:$N$29,$T27)+INDEX('2 Matériel'!$M$6:$M$29,$T27))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T27)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T27)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T27),""))</f>
+        <v/>
+      </c>
+      <c r="E27" s="72" t="n"/>
+      <c r="F27" s="72" t="n"/>
+      <c r="G27" s="72" t="n"/>
+      <c r="H27" s="72" t="n"/>
+      <c r="I27" s="69" t="n"/>
+      <c r="J27" s="69" t="n"/>
+      <c r="K27" s="70" t="n"/>
+      <c r="L27" s="69" t="n"/>
+      <c r="M27" s="73" t="n"/>
+      <c r="N27" s="69" t="n"/>
+      <c r="O27" s="69" t="n"/>
+      <c r="P27" s="69" t="n"/>
+      <c r="Q27" s="73" t="n"/>
+      <c r="R27" s="69" t="n"/>
+      <c r="T27" s="74">
         <f>IF(A27="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A27)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="15">
+    <row r="28" ht="27" customHeight="1">
+      <c r="A28" s="16">
         <f>IF(14&lt;=SUM('2 Matériel'!$M$6:$M$29),14,"")</f>
         <v/>
       </c>
-      <c r="B28" s="67">
-        <f>IF(A28="","",INDEX('2 Matériel'!$A$6:$A$29,$T28)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T28)&gt;1,"  ("&amp;(A28-INDEX('2 Matériel'!$N$6:$N$29,$T28)+INDEX('2 Matériel'!$M$6:$M$29,$T28))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T28)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C28" s="68" t="n"/>
-      <c r="D28" s="38">
-        <f>IF(A28="","",INDEX('2 Matériel'!$C$6:$C$29,$T28))</f>
-        <v/>
-      </c>
-      <c r="E28" s="69" t="n"/>
-      <c r="F28" s="69" t="n"/>
-      <c r="G28" s="69" t="n"/>
-      <c r="H28" s="69" t="n"/>
-      <c r="I28" s="70" t="n"/>
-      <c r="J28" s="70" t="n"/>
-      <c r="K28" s="68" t="n"/>
-      <c r="L28" s="70" t="n"/>
-      <c r="M28" s="71" t="n"/>
-      <c r="N28" s="70" t="n"/>
-      <c r="O28" s="70" t="n"/>
-      <c r="P28" s="70" t="n"/>
-      <c r="Q28" s="71" t="n"/>
-      <c r="R28" s="70" t="n"/>
-      <c r="T28" s="72">
+      <c r="B28" s="69" t="n"/>
+      <c r="C28" s="70" t="n"/>
+      <c r="D28" s="71">
+        <f>IF(A28="","",INDEX('2 Matériel'!$C$6:$C$29,$T28)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T28)&gt;1,"  ("&amp;(A28-INDEX('2 Matériel'!$N$6:$N$29,$T28)+INDEX('2 Matériel'!$M$6:$M$29,$T28))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T28)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T28)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T28),""))</f>
+        <v/>
+      </c>
+      <c r="E28" s="72" t="n"/>
+      <c r="F28" s="72" t="n"/>
+      <c r="G28" s="72" t="n"/>
+      <c r="H28" s="72" t="n"/>
+      <c r="I28" s="69" t="n"/>
+      <c r="J28" s="69" t="n"/>
+      <c r="K28" s="70" t="n"/>
+      <c r="L28" s="69" t="n"/>
+      <c r="M28" s="73" t="n"/>
+      <c r="N28" s="69" t="n"/>
+      <c r="O28" s="69" t="n"/>
+      <c r="P28" s="69" t="n"/>
+      <c r="Q28" s="73" t="n"/>
+      <c r="R28" s="69" t="n"/>
+      <c r="T28" s="74">
         <f>IF(A28="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A28)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="15">
+    <row r="29" ht="27" customHeight="1">
+      <c r="A29" s="16">
         <f>IF(15&lt;=SUM('2 Matériel'!$M$6:$M$29),15,"")</f>
         <v/>
       </c>
-      <c r="B29" s="67">
-        <f>IF(A29="","",INDEX('2 Matériel'!$A$6:$A$29,$T29)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T29)&gt;1,"  ("&amp;(A29-INDEX('2 Matériel'!$N$6:$N$29,$T29)+INDEX('2 Matériel'!$M$6:$M$29,$T29))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T29)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C29" s="68" t="n"/>
-      <c r="D29" s="38">
-        <f>IF(A29="","",INDEX('2 Matériel'!$C$6:$C$29,$T29))</f>
-        <v/>
-      </c>
-      <c r="E29" s="69" t="n"/>
-      <c r="F29" s="69" t="n"/>
-      <c r="G29" s="69" t="n"/>
-      <c r="H29" s="69" t="n"/>
-      <c r="I29" s="70" t="n"/>
-      <c r="J29" s="70" t="n"/>
-      <c r="K29" s="68" t="n"/>
-      <c r="L29" s="70" t="n"/>
-      <c r="M29" s="71" t="n"/>
-      <c r="N29" s="70" t="n"/>
-      <c r="O29" s="70" t="n"/>
-      <c r="P29" s="70" t="n"/>
-      <c r="Q29" s="71" t="n"/>
-      <c r="R29" s="70" t="n"/>
-      <c r="T29" s="72">
+      <c r="B29" s="69" t="n"/>
+      <c r="C29" s="70" t="n"/>
+      <c r="D29" s="71">
+        <f>IF(A29="","",INDEX('2 Matériel'!$C$6:$C$29,$T29)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T29)&gt;1,"  ("&amp;(A29-INDEX('2 Matériel'!$N$6:$N$29,$T29)+INDEX('2 Matériel'!$M$6:$M$29,$T29))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T29)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T29)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T29),""))</f>
+        <v/>
+      </c>
+      <c r="E29" s="72" t="n"/>
+      <c r="F29" s="72" t="n"/>
+      <c r="G29" s="72" t="n"/>
+      <c r="H29" s="72" t="n"/>
+      <c r="I29" s="69" t="n"/>
+      <c r="J29" s="69" t="n"/>
+      <c r="K29" s="70" t="n"/>
+      <c r="L29" s="69" t="n"/>
+      <c r="M29" s="73" t="n"/>
+      <c r="N29" s="69" t="n"/>
+      <c r="O29" s="69" t="n"/>
+      <c r="P29" s="69" t="n"/>
+      <c r="Q29" s="73" t="n"/>
+      <c r="R29" s="69" t="n"/>
+      <c r="T29" s="74">
         <f>IF(A29="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A29)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="15">
+    <row r="30" ht="27" customHeight="1">
+      <c r="A30" s="16">
         <f>IF(16&lt;=SUM('2 Matériel'!$M$6:$M$29),16,"")</f>
         <v/>
       </c>
-      <c r="B30" s="67">
-        <f>IF(A30="","",INDEX('2 Matériel'!$A$6:$A$29,$T30)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T30)&gt;1,"  ("&amp;(A30-INDEX('2 Matériel'!$N$6:$N$29,$T30)+INDEX('2 Matériel'!$M$6:$M$29,$T30))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T30)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C30" s="68" t="n"/>
-      <c r="D30" s="38">
-        <f>IF(A30="","",INDEX('2 Matériel'!$C$6:$C$29,$T30))</f>
-        <v/>
-      </c>
-      <c r="E30" s="69" t="n"/>
-      <c r="F30" s="69" t="n"/>
-      <c r="G30" s="69" t="n"/>
-      <c r="H30" s="69" t="n"/>
-      <c r="I30" s="70" t="n"/>
-      <c r="J30" s="70" t="n"/>
-      <c r="K30" s="68" t="n"/>
-      <c r="L30" s="70" t="n"/>
-      <c r="M30" s="71" t="n"/>
-      <c r="N30" s="70" t="n"/>
-      <c r="O30" s="70" t="n"/>
-      <c r="P30" s="70" t="n"/>
-      <c r="Q30" s="71" t="n"/>
-      <c r="R30" s="70" t="n"/>
-      <c r="T30" s="72">
+      <c r="B30" s="69" t="n"/>
+      <c r="C30" s="70" t="n"/>
+      <c r="D30" s="71">
+        <f>IF(A30="","",INDEX('2 Matériel'!$C$6:$C$29,$T30)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T30)&gt;1,"  ("&amp;(A30-INDEX('2 Matériel'!$N$6:$N$29,$T30)+INDEX('2 Matériel'!$M$6:$M$29,$T30))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T30)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T30)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T30),""))</f>
+        <v/>
+      </c>
+      <c r="E30" s="72" t="n"/>
+      <c r="F30" s="72" t="n"/>
+      <c r="G30" s="72" t="n"/>
+      <c r="H30" s="72" t="n"/>
+      <c r="I30" s="69" t="n"/>
+      <c r="J30" s="69" t="n"/>
+      <c r="K30" s="70" t="n"/>
+      <c r="L30" s="69" t="n"/>
+      <c r="M30" s="73" t="n"/>
+      <c r="N30" s="69" t="n"/>
+      <c r="O30" s="69" t="n"/>
+      <c r="P30" s="69" t="n"/>
+      <c r="Q30" s="73" t="n"/>
+      <c r="R30" s="69" t="n"/>
+      <c r="T30" s="74">
         <f>IF(A30="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A30)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="15">
+    <row r="31" ht="27" customHeight="1">
+      <c r="A31" s="16">
         <f>IF(17&lt;=SUM('2 Matériel'!$M$6:$M$29),17,"")</f>
         <v/>
       </c>
-      <c r="B31" s="67">
-        <f>IF(A31="","",INDEX('2 Matériel'!$A$6:$A$29,$T31)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T31)&gt;1,"  ("&amp;(A31-INDEX('2 Matériel'!$N$6:$N$29,$T31)+INDEX('2 Matériel'!$M$6:$M$29,$T31))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T31)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C31" s="68" t="n"/>
-      <c r="D31" s="38">
-        <f>IF(A31="","",INDEX('2 Matériel'!$C$6:$C$29,$T31))</f>
-        <v/>
-      </c>
-      <c r="E31" s="69" t="n"/>
-      <c r="F31" s="69" t="n"/>
-      <c r="G31" s="69" t="n"/>
-      <c r="H31" s="69" t="n"/>
-      <c r="I31" s="70" t="n"/>
-      <c r="J31" s="70" t="n"/>
-      <c r="K31" s="68" t="n"/>
-      <c r="L31" s="70" t="n"/>
-      <c r="M31" s="71" t="n"/>
-      <c r="N31" s="70" t="n"/>
-      <c r="O31" s="70" t="n"/>
-      <c r="P31" s="70" t="n"/>
-      <c r="Q31" s="71" t="n"/>
-      <c r="R31" s="70" t="n"/>
-      <c r="T31" s="72">
+      <c r="B31" s="69" t="n"/>
+      <c r="C31" s="70" t="n"/>
+      <c r="D31" s="71">
+        <f>IF(A31="","",INDEX('2 Matériel'!$C$6:$C$29,$T31)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T31)&gt;1,"  ("&amp;(A31-INDEX('2 Matériel'!$N$6:$N$29,$T31)+INDEX('2 Matériel'!$M$6:$M$29,$T31))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T31)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T31)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T31),""))</f>
+        <v/>
+      </c>
+      <c r="E31" s="72" t="n"/>
+      <c r="F31" s="72" t="n"/>
+      <c r="G31" s="72" t="n"/>
+      <c r="H31" s="72" t="n"/>
+      <c r="I31" s="69" t="n"/>
+      <c r="J31" s="69" t="n"/>
+      <c r="K31" s="70" t="n"/>
+      <c r="L31" s="69" t="n"/>
+      <c r="M31" s="73" t="n"/>
+      <c r="N31" s="69" t="n"/>
+      <c r="O31" s="69" t="n"/>
+      <c r="P31" s="69" t="n"/>
+      <c r="Q31" s="73" t="n"/>
+      <c r="R31" s="69" t="n"/>
+      <c r="T31" s="74">
         <f>IF(A31="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A31)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="15">
+    <row r="32" ht="27" customHeight="1">
+      <c r="A32" s="16">
         <f>IF(18&lt;=SUM('2 Matériel'!$M$6:$M$29),18,"")</f>
         <v/>
       </c>
-      <c r="B32" s="67">
-        <f>IF(A32="","",INDEX('2 Matériel'!$A$6:$A$29,$T32)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T32)&gt;1,"  ("&amp;(A32-INDEX('2 Matériel'!$N$6:$N$29,$T32)+INDEX('2 Matériel'!$M$6:$M$29,$T32))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T32)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C32" s="68" t="n"/>
-      <c r="D32" s="38">
-        <f>IF(A32="","",INDEX('2 Matériel'!$C$6:$C$29,$T32))</f>
-        <v/>
-      </c>
-      <c r="E32" s="69" t="n"/>
-      <c r="F32" s="69" t="n"/>
-      <c r="G32" s="69" t="n"/>
-      <c r="H32" s="69" t="n"/>
-      <c r="I32" s="70" t="n"/>
-      <c r="J32" s="70" t="n"/>
-      <c r="K32" s="68" t="n"/>
-      <c r="L32" s="70" t="n"/>
-      <c r="M32" s="71" t="n"/>
-      <c r="N32" s="70" t="n"/>
-      <c r="O32" s="70" t="n"/>
-      <c r="P32" s="70" t="n"/>
-      <c r="Q32" s="71" t="n"/>
-      <c r="R32" s="70" t="n"/>
-      <c r="T32" s="72">
+      <c r="B32" s="69" t="n"/>
+      <c r="C32" s="70" t="n"/>
+      <c r="D32" s="71">
+        <f>IF(A32="","",INDEX('2 Matériel'!$C$6:$C$29,$T32)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T32)&gt;1,"  ("&amp;(A32-INDEX('2 Matériel'!$N$6:$N$29,$T32)+INDEX('2 Matériel'!$M$6:$M$29,$T32))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T32)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T32)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T32),""))</f>
+        <v/>
+      </c>
+      <c r="E32" s="72" t="n"/>
+      <c r="F32" s="72" t="n"/>
+      <c r="G32" s="72" t="n"/>
+      <c r="H32" s="72" t="n"/>
+      <c r="I32" s="69" t="n"/>
+      <c r="J32" s="69" t="n"/>
+      <c r="K32" s="70" t="n"/>
+      <c r="L32" s="69" t="n"/>
+      <c r="M32" s="73" t="n"/>
+      <c r="N32" s="69" t="n"/>
+      <c r="O32" s="69" t="n"/>
+      <c r="P32" s="69" t="n"/>
+      <c r="Q32" s="73" t="n"/>
+      <c r="R32" s="69" t="n"/>
+      <c r="T32" s="74">
         <f>IF(A32="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A32)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="15">
+    <row r="33" ht="27" customHeight="1">
+      <c r="A33" s="16">
         <f>IF(19&lt;=SUM('2 Matériel'!$M$6:$M$29),19,"")</f>
         <v/>
       </c>
-      <c r="B33" s="67">
-        <f>IF(A33="","",INDEX('2 Matériel'!$A$6:$A$29,$T33)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T33)&gt;1,"  ("&amp;(A33-INDEX('2 Matériel'!$N$6:$N$29,$T33)+INDEX('2 Matériel'!$M$6:$M$29,$T33))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T33)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C33" s="68" t="n"/>
-      <c r="D33" s="38">
-        <f>IF(A33="","",INDEX('2 Matériel'!$C$6:$C$29,$T33))</f>
-        <v/>
-      </c>
-      <c r="E33" s="69" t="n"/>
-      <c r="F33" s="69" t="n"/>
-      <c r="G33" s="69" t="n"/>
-      <c r="H33" s="69" t="n"/>
-      <c r="I33" s="70" t="n"/>
-      <c r="J33" s="70" t="n"/>
-      <c r="K33" s="68" t="n"/>
-      <c r="L33" s="70" t="n"/>
-      <c r="M33" s="71" t="n"/>
-      <c r="N33" s="70" t="n"/>
-      <c r="O33" s="70" t="n"/>
-      <c r="P33" s="70" t="n"/>
-      <c r="Q33" s="71" t="n"/>
-      <c r="R33" s="70" t="n"/>
-      <c r="T33" s="72">
+      <c r="B33" s="69" t="n"/>
+      <c r="C33" s="70" t="n"/>
+      <c r="D33" s="71">
+        <f>IF(A33="","",INDEX('2 Matériel'!$C$6:$C$29,$T33)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T33)&gt;1,"  ("&amp;(A33-INDEX('2 Matériel'!$N$6:$N$29,$T33)+INDEX('2 Matériel'!$M$6:$M$29,$T33))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T33)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T33)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T33),""))</f>
+        <v/>
+      </c>
+      <c r="E33" s="72" t="n"/>
+      <c r="F33" s="72" t="n"/>
+      <c r="G33" s="72" t="n"/>
+      <c r="H33" s="72" t="n"/>
+      <c r="I33" s="69" t="n"/>
+      <c r="J33" s="69" t="n"/>
+      <c r="K33" s="70" t="n"/>
+      <c r="L33" s="69" t="n"/>
+      <c r="M33" s="73" t="n"/>
+      <c r="N33" s="69" t="n"/>
+      <c r="O33" s="69" t="n"/>
+      <c r="P33" s="69" t="n"/>
+      <c r="Q33" s="73" t="n"/>
+      <c r="R33" s="69" t="n"/>
+      <c r="T33" s="74">
         <f>IF(A33="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A33)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="15">
+    <row r="34" ht="27" customHeight="1">
+      <c r="A34" s="16">
         <f>IF(20&lt;=SUM('2 Matériel'!$M$6:$M$29),20,"")</f>
         <v/>
       </c>
-      <c r="B34" s="67">
-        <f>IF(A34="","",INDEX('2 Matériel'!$A$6:$A$29,$T34)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T34)&gt;1,"  ("&amp;(A34-INDEX('2 Matériel'!$N$6:$N$29,$T34)+INDEX('2 Matériel'!$M$6:$M$29,$T34))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T34)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C34" s="68" t="n"/>
-      <c r="D34" s="38">
-        <f>IF(A34="","",INDEX('2 Matériel'!$C$6:$C$29,$T34))</f>
-        <v/>
-      </c>
-      <c r="E34" s="69" t="n"/>
-      <c r="F34" s="69" t="n"/>
-      <c r="G34" s="69" t="n"/>
-      <c r="H34" s="69" t="n"/>
-      <c r="I34" s="70" t="n"/>
-      <c r="J34" s="70" t="n"/>
-      <c r="K34" s="68" t="n"/>
-      <c r="L34" s="70" t="n"/>
-      <c r="M34" s="71" t="n"/>
-      <c r="N34" s="70" t="n"/>
-      <c r="O34" s="70" t="n"/>
-      <c r="P34" s="70" t="n"/>
-      <c r="Q34" s="71" t="n"/>
-      <c r="R34" s="70" t="n"/>
-      <c r="T34" s="72">
+      <c r="B34" s="69" t="n"/>
+      <c r="C34" s="70" t="n"/>
+      <c r="D34" s="71">
+        <f>IF(A34="","",INDEX('2 Matériel'!$C$6:$C$29,$T34)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T34)&gt;1,"  ("&amp;(A34-INDEX('2 Matériel'!$N$6:$N$29,$T34)+INDEX('2 Matériel'!$M$6:$M$29,$T34))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T34)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T34)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T34),""))</f>
+        <v/>
+      </c>
+      <c r="E34" s="72" t="n"/>
+      <c r="F34" s="72" t="n"/>
+      <c r="G34" s="72" t="n"/>
+      <c r="H34" s="72" t="n"/>
+      <c r="I34" s="69" t="n"/>
+      <c r="J34" s="69" t="n"/>
+      <c r="K34" s="70" t="n"/>
+      <c r="L34" s="69" t="n"/>
+      <c r="M34" s="73" t="n"/>
+      <c r="N34" s="69" t="n"/>
+      <c r="O34" s="69" t="n"/>
+      <c r="P34" s="69" t="n"/>
+      <c r="Q34" s="73" t="n"/>
+      <c r="R34" s="69" t="n"/>
+      <c r="T34" s="74">
         <f>IF(A34="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A34)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="35" hidden="1" outlineLevel="1" ht="24" customHeight="1">
-      <c r="A35" s="15">
+    <row r="35" hidden="1" outlineLevel="1" ht="27" customHeight="1">
+      <c r="A35" s="16">
         <f>IF(21&lt;=SUM('2 Matériel'!$M$6:$M$29),21,"")</f>
         <v/>
       </c>
-      <c r="B35" s="67">
-        <f>IF(A35="","",INDEX('2 Matériel'!$A$6:$A$29,$T35)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T35)&gt;1,"  ("&amp;(A35-INDEX('2 Matériel'!$N$6:$N$29,$T35)+INDEX('2 Matériel'!$M$6:$M$29,$T35))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T35)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C35" s="68" t="n"/>
-      <c r="D35" s="38">
-        <f>IF(A35="","",INDEX('2 Matériel'!$C$6:$C$29,$T35))</f>
-        <v/>
-      </c>
-      <c r="E35" s="69" t="n"/>
-      <c r="F35" s="69" t="n"/>
-      <c r="G35" s="69" t="n"/>
-      <c r="H35" s="69" t="n"/>
-      <c r="I35" s="70" t="n"/>
-      <c r="J35" s="70" t="n"/>
-      <c r="K35" s="68" t="n"/>
-      <c r="L35" s="70" t="n"/>
-      <c r="M35" s="71" t="n"/>
-      <c r="N35" s="70" t="n"/>
-      <c r="O35" s="70" t="n"/>
-      <c r="P35" s="70" t="n"/>
-      <c r="Q35" s="71" t="n"/>
-      <c r="R35" s="70" t="n"/>
-      <c r="T35" s="72">
+      <c r="B35" s="69" t="n"/>
+      <c r="C35" s="70" t="n"/>
+      <c r="D35" s="71">
+        <f>IF(A35="","",INDEX('2 Matériel'!$C$6:$C$29,$T35)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T35)&gt;1,"  ("&amp;(A35-INDEX('2 Matériel'!$N$6:$N$29,$T35)+INDEX('2 Matériel'!$M$6:$M$29,$T35))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T35)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T35)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T35),""))</f>
+        <v/>
+      </c>
+      <c r="E35" s="72" t="n"/>
+      <c r="F35" s="72" t="n"/>
+      <c r="G35" s="72" t="n"/>
+      <c r="H35" s="72" t="n"/>
+      <c r="I35" s="69" t="n"/>
+      <c r="J35" s="69" t="n"/>
+      <c r="K35" s="70" t="n"/>
+      <c r="L35" s="69" t="n"/>
+      <c r="M35" s="73" t="n"/>
+      <c r="N35" s="69" t="n"/>
+      <c r="O35" s="69" t="n"/>
+      <c r="P35" s="69" t="n"/>
+      <c r="Q35" s="73" t="n"/>
+      <c r="R35" s="69" t="n"/>
+      <c r="T35" s="74">
         <f>IF(A35="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A35)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="36" hidden="1" outlineLevel="1" ht="24" customHeight="1">
-      <c r="A36" s="15">
+    <row r="36" hidden="1" outlineLevel="1" ht="27" customHeight="1">
+      <c r="A36" s="16">
         <f>IF(22&lt;=SUM('2 Matériel'!$M$6:$M$29),22,"")</f>
         <v/>
       </c>
-      <c r="B36" s="67">
-        <f>IF(A36="","",INDEX('2 Matériel'!$A$6:$A$29,$T36)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T36)&gt;1,"  ("&amp;(A36-INDEX('2 Matériel'!$N$6:$N$29,$T36)+INDEX('2 Matériel'!$M$6:$M$29,$T36))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T36)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C36" s="68" t="n"/>
-      <c r="D36" s="38">
-        <f>IF(A36="","",INDEX('2 Matériel'!$C$6:$C$29,$T36))</f>
-        <v/>
-      </c>
-      <c r="E36" s="69" t="n"/>
-      <c r="F36" s="69" t="n"/>
-      <c r="G36" s="69" t="n"/>
-      <c r="H36" s="69" t="n"/>
-      <c r="I36" s="70" t="n"/>
-      <c r="J36" s="70" t="n"/>
-      <c r="K36" s="68" t="n"/>
-      <c r="L36" s="70" t="n"/>
-      <c r="M36" s="71" t="n"/>
-      <c r="N36" s="70" t="n"/>
-      <c r="O36" s="70" t="n"/>
-      <c r="P36" s="70" t="n"/>
-      <c r="Q36" s="71" t="n"/>
-      <c r="R36" s="70" t="n"/>
-      <c r="T36" s="72">
+      <c r="B36" s="69" t="n"/>
+      <c r="C36" s="70" t="n"/>
+      <c r="D36" s="71">
+        <f>IF(A36="","",INDEX('2 Matériel'!$C$6:$C$29,$T36)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T36)&gt;1,"  ("&amp;(A36-INDEX('2 Matériel'!$N$6:$N$29,$T36)+INDEX('2 Matériel'!$M$6:$M$29,$T36))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T36)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T36)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T36),""))</f>
+        <v/>
+      </c>
+      <c r="E36" s="72" t="n"/>
+      <c r="F36" s="72" t="n"/>
+      <c r="G36" s="72" t="n"/>
+      <c r="H36" s="72" t="n"/>
+      <c r="I36" s="69" t="n"/>
+      <c r="J36" s="69" t="n"/>
+      <c r="K36" s="70" t="n"/>
+      <c r="L36" s="69" t="n"/>
+      <c r="M36" s="73" t="n"/>
+      <c r="N36" s="69" t="n"/>
+      <c r="O36" s="69" t="n"/>
+      <c r="P36" s="69" t="n"/>
+      <c r="Q36" s="73" t="n"/>
+      <c r="R36" s="69" t="n"/>
+      <c r="T36" s="74">
         <f>IF(A36="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A36)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="37" hidden="1" outlineLevel="1" ht="24" customHeight="1">
-      <c r="A37" s="15">
+    <row r="37" hidden="1" outlineLevel="1" ht="27" customHeight="1">
+      <c r="A37" s="16">
         <f>IF(23&lt;=SUM('2 Matériel'!$M$6:$M$29),23,"")</f>
         <v/>
       </c>
-      <c r="B37" s="67">
-        <f>IF(A37="","",INDEX('2 Matériel'!$A$6:$A$29,$T37)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T37)&gt;1,"  ("&amp;(A37-INDEX('2 Matériel'!$N$6:$N$29,$T37)+INDEX('2 Matériel'!$M$6:$M$29,$T37))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T37)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C37" s="68" t="n"/>
-      <c r="D37" s="38">
-        <f>IF(A37="","",INDEX('2 Matériel'!$C$6:$C$29,$T37))</f>
-        <v/>
-      </c>
-      <c r="E37" s="69" t="n"/>
-      <c r="F37" s="69" t="n"/>
-      <c r="G37" s="69" t="n"/>
-      <c r="H37" s="69" t="n"/>
-      <c r="I37" s="70" t="n"/>
-      <c r="J37" s="70" t="n"/>
-      <c r="K37" s="68" t="n"/>
-      <c r="L37" s="70" t="n"/>
-      <c r="M37" s="71" t="n"/>
-      <c r="N37" s="70" t="n"/>
-      <c r="O37" s="70" t="n"/>
-      <c r="P37" s="70" t="n"/>
-      <c r="Q37" s="71" t="n"/>
-      <c r="R37" s="70" t="n"/>
-      <c r="T37" s="72">
+      <c r="B37" s="69" t="n"/>
+      <c r="C37" s="70" t="n"/>
+      <c r="D37" s="71">
+        <f>IF(A37="","",INDEX('2 Matériel'!$C$6:$C$29,$T37)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T37)&gt;1,"  ("&amp;(A37-INDEX('2 Matériel'!$N$6:$N$29,$T37)+INDEX('2 Matériel'!$M$6:$M$29,$T37))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T37)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T37)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T37),""))</f>
+        <v/>
+      </c>
+      <c r="E37" s="72" t="n"/>
+      <c r="F37" s="72" t="n"/>
+      <c r="G37" s="72" t="n"/>
+      <c r="H37" s="72" t="n"/>
+      <c r="I37" s="69" t="n"/>
+      <c r="J37" s="69" t="n"/>
+      <c r="K37" s="70" t="n"/>
+      <c r="L37" s="69" t="n"/>
+      <c r="M37" s="73" t="n"/>
+      <c r="N37" s="69" t="n"/>
+      <c r="O37" s="69" t="n"/>
+      <c r="P37" s="69" t="n"/>
+      <c r="Q37" s="73" t="n"/>
+      <c r="R37" s="69" t="n"/>
+      <c r="T37" s="74">
         <f>IF(A37="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A37)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="38" hidden="1" outlineLevel="1" ht="24" customHeight="1">
-      <c r="A38" s="15">
+    <row r="38" hidden="1" outlineLevel="1" ht="27" customHeight="1">
+      <c r="A38" s="16">
         <f>IF(24&lt;=SUM('2 Matériel'!$M$6:$M$29),24,"")</f>
         <v/>
       </c>
-      <c r="B38" s="67">
-        <f>IF(A38="","",INDEX('2 Matériel'!$A$6:$A$29,$T38)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T38)&gt;1,"  ("&amp;(A38-INDEX('2 Matériel'!$N$6:$N$29,$T38)+INDEX('2 Matériel'!$M$6:$M$29,$T38))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T38)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C38" s="68" t="n"/>
-      <c r="D38" s="38">
-        <f>IF(A38="","",INDEX('2 Matériel'!$C$6:$C$29,$T38))</f>
-        <v/>
-      </c>
-      <c r="E38" s="69" t="n"/>
-      <c r="F38" s="69" t="n"/>
-      <c r="G38" s="69" t="n"/>
-      <c r="H38" s="69" t="n"/>
-      <c r="I38" s="70" t="n"/>
-      <c r="J38" s="70" t="n"/>
-      <c r="K38" s="68" t="n"/>
-      <c r="L38" s="70" t="n"/>
-      <c r="M38" s="71" t="n"/>
-      <c r="N38" s="70" t="n"/>
-      <c r="O38" s="70" t="n"/>
-      <c r="P38" s="70" t="n"/>
-      <c r="Q38" s="71" t="n"/>
-      <c r="R38" s="70" t="n"/>
-      <c r="T38" s="72">
+      <c r="B38" s="69" t="n"/>
+      <c r="C38" s="70" t="n"/>
+      <c r="D38" s="71">
+        <f>IF(A38="","",INDEX('2 Matériel'!$C$6:$C$29,$T38)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T38)&gt;1,"  ("&amp;(A38-INDEX('2 Matériel'!$N$6:$N$29,$T38)+INDEX('2 Matériel'!$M$6:$M$29,$T38))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T38)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T38)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T38),""))</f>
+        <v/>
+      </c>
+      <c r="E38" s="72" t="n"/>
+      <c r="F38" s="72" t="n"/>
+      <c r="G38" s="72" t="n"/>
+      <c r="H38" s="72" t="n"/>
+      <c r="I38" s="69" t="n"/>
+      <c r="J38" s="69" t="n"/>
+      <c r="K38" s="70" t="n"/>
+      <c r="L38" s="69" t="n"/>
+      <c r="M38" s="73" t="n"/>
+      <c r="N38" s="69" t="n"/>
+      <c r="O38" s="69" t="n"/>
+      <c r="P38" s="69" t="n"/>
+      <c r="Q38" s="73" t="n"/>
+      <c r="R38" s="69" t="n"/>
+      <c r="T38" s="74">
         <f>IF(A38="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A38)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="39" hidden="1" outlineLevel="1" ht="24" customHeight="1">
-      <c r="A39" s="15">
+    <row r="39" hidden="1" outlineLevel="1" ht="27" customHeight="1">
+      <c r="A39" s="16">
         <f>IF(25&lt;=SUM('2 Matériel'!$M$6:$M$29),25,"")</f>
         <v/>
       </c>
-      <c r="B39" s="67">
-        <f>IF(A39="","",INDEX('2 Matériel'!$A$6:$A$29,$T39)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T39)&gt;1,"  ("&amp;(A39-INDEX('2 Matériel'!$N$6:$N$29,$T39)+INDEX('2 Matériel'!$M$6:$M$29,$T39))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T39)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C39" s="68" t="n"/>
-      <c r="D39" s="38">
-        <f>IF(A39="","",INDEX('2 Matériel'!$C$6:$C$29,$T39))</f>
-        <v/>
-      </c>
-      <c r="E39" s="69" t="n"/>
-      <c r="F39" s="69" t="n"/>
-      <c r="G39" s="69" t="n"/>
-      <c r="H39" s="69" t="n"/>
-      <c r="I39" s="70" t="n"/>
-      <c r="J39" s="70" t="n"/>
-      <c r="K39" s="68" t="n"/>
-      <c r="L39" s="70" t="n"/>
-      <c r="M39" s="71" t="n"/>
-      <c r="N39" s="70" t="n"/>
-      <c r="O39" s="70" t="n"/>
-      <c r="P39" s="70" t="n"/>
-      <c r="Q39" s="71" t="n"/>
-      <c r="R39" s="70" t="n"/>
-      <c r="T39" s="72">
+      <c r="B39" s="69" t="n"/>
+      <c r="C39" s="70" t="n"/>
+      <c r="D39" s="71">
+        <f>IF(A39="","",INDEX('2 Matériel'!$C$6:$C$29,$T39)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T39)&gt;1,"  ("&amp;(A39-INDEX('2 Matériel'!$N$6:$N$29,$T39)+INDEX('2 Matériel'!$M$6:$M$29,$T39))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T39)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T39)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T39),""))</f>
+        <v/>
+      </c>
+      <c r="E39" s="72" t="n"/>
+      <c r="F39" s="72" t="n"/>
+      <c r="G39" s="72" t="n"/>
+      <c r="H39" s="72" t="n"/>
+      <c r="I39" s="69" t="n"/>
+      <c r="J39" s="69" t="n"/>
+      <c r="K39" s="70" t="n"/>
+      <c r="L39" s="69" t="n"/>
+      <c r="M39" s="73" t="n"/>
+      <c r="N39" s="69" t="n"/>
+      <c r="O39" s="69" t="n"/>
+      <c r="P39" s="69" t="n"/>
+      <c r="Q39" s="73" t="n"/>
+      <c r="R39" s="69" t="n"/>
+      <c r="T39" s="74">
         <f>IF(A39="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A39)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="40" hidden="1" outlineLevel="1" ht="24" customHeight="1">
-      <c r="A40" s="15">
+    <row r="40" hidden="1" outlineLevel="1" ht="27" customHeight="1">
+      <c r="A40" s="16">
         <f>IF(26&lt;=SUM('2 Matériel'!$M$6:$M$29),26,"")</f>
         <v/>
       </c>
-      <c r="B40" s="67">
-        <f>IF(A40="","",INDEX('2 Matériel'!$A$6:$A$29,$T40)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T40)&gt;1,"  ("&amp;(A40-INDEX('2 Matériel'!$N$6:$N$29,$T40)+INDEX('2 Matériel'!$M$6:$M$29,$T40))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T40)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C40" s="68" t="n"/>
-      <c r="D40" s="38">
-        <f>IF(A40="","",INDEX('2 Matériel'!$C$6:$C$29,$T40))</f>
-        <v/>
-      </c>
-      <c r="E40" s="69" t="n"/>
-      <c r="F40" s="69" t="n"/>
-      <c r="G40" s="69" t="n"/>
-      <c r="H40" s="69" t="n"/>
-      <c r="I40" s="70" t="n"/>
-      <c r="J40" s="70" t="n"/>
-      <c r="K40" s="68" t="n"/>
-      <c r="L40" s="70" t="n"/>
-      <c r="M40" s="71" t="n"/>
-      <c r="N40" s="70" t="n"/>
-      <c r="O40" s="70" t="n"/>
-      <c r="P40" s="70" t="n"/>
-      <c r="Q40" s="71" t="n"/>
-      <c r="R40" s="70" t="n"/>
-      <c r="T40" s="72">
+      <c r="B40" s="69" t="n"/>
+      <c r="C40" s="70" t="n"/>
+      <c r="D40" s="71">
+        <f>IF(A40="","",INDEX('2 Matériel'!$C$6:$C$29,$T40)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T40)&gt;1,"  ("&amp;(A40-INDEX('2 Matériel'!$N$6:$N$29,$T40)+INDEX('2 Matériel'!$M$6:$M$29,$T40))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T40)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T40)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T40),""))</f>
+        <v/>
+      </c>
+      <c r="E40" s="72" t="n"/>
+      <c r="F40" s="72" t="n"/>
+      <c r="G40" s="72" t="n"/>
+      <c r="H40" s="72" t="n"/>
+      <c r="I40" s="69" t="n"/>
+      <c r="J40" s="69" t="n"/>
+      <c r="K40" s="70" t="n"/>
+      <c r="L40" s="69" t="n"/>
+      <c r="M40" s="73" t="n"/>
+      <c r="N40" s="69" t="n"/>
+      <c r="O40" s="69" t="n"/>
+      <c r="P40" s="69" t="n"/>
+      <c r="Q40" s="73" t="n"/>
+      <c r="R40" s="69" t="n"/>
+      <c r="T40" s="74">
         <f>IF(A40="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A40)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="41" hidden="1" outlineLevel="1" ht="24" customHeight="1">
-      <c r="A41" s="15">
+    <row r="41" hidden="1" outlineLevel="1" ht="27" customHeight="1">
+      <c r="A41" s="16">
         <f>IF(27&lt;=SUM('2 Matériel'!$M$6:$M$29),27,"")</f>
         <v/>
       </c>
-      <c r="B41" s="67">
-        <f>IF(A41="","",INDEX('2 Matériel'!$A$6:$A$29,$T41)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T41)&gt;1,"  ("&amp;(A41-INDEX('2 Matériel'!$N$6:$N$29,$T41)+INDEX('2 Matériel'!$M$6:$M$29,$T41))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T41)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C41" s="68" t="n"/>
-      <c r="D41" s="38">
-        <f>IF(A41="","",INDEX('2 Matériel'!$C$6:$C$29,$T41))</f>
-        <v/>
-      </c>
-      <c r="E41" s="69" t="n"/>
-      <c r="F41" s="69" t="n"/>
-      <c r="G41" s="69" t="n"/>
-      <c r="H41" s="69" t="n"/>
-      <c r="I41" s="70" t="n"/>
-      <c r="J41" s="70" t="n"/>
-      <c r="K41" s="68" t="n"/>
-      <c r="L41" s="70" t="n"/>
-      <c r="M41" s="71" t="n"/>
-      <c r="N41" s="70" t="n"/>
-      <c r="O41" s="70" t="n"/>
-      <c r="P41" s="70" t="n"/>
-      <c r="Q41" s="71" t="n"/>
-      <c r="R41" s="70" t="n"/>
-      <c r="T41" s="72">
+      <c r="B41" s="69" t="n"/>
+      <c r="C41" s="70" t="n"/>
+      <c r="D41" s="71">
+        <f>IF(A41="","",INDEX('2 Matériel'!$C$6:$C$29,$T41)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T41)&gt;1,"  ("&amp;(A41-INDEX('2 Matériel'!$N$6:$N$29,$T41)+INDEX('2 Matériel'!$M$6:$M$29,$T41))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T41)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T41)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T41),""))</f>
+        <v/>
+      </c>
+      <c r="E41" s="72" t="n"/>
+      <c r="F41" s="72" t="n"/>
+      <c r="G41" s="72" t="n"/>
+      <c r="H41" s="72" t="n"/>
+      <c r="I41" s="69" t="n"/>
+      <c r="J41" s="69" t="n"/>
+      <c r="K41" s="70" t="n"/>
+      <c r="L41" s="69" t="n"/>
+      <c r="M41" s="73" t="n"/>
+      <c r="N41" s="69" t="n"/>
+      <c r="O41" s="69" t="n"/>
+      <c r="P41" s="69" t="n"/>
+      <c r="Q41" s="73" t="n"/>
+      <c r="R41" s="69" t="n"/>
+      <c r="T41" s="74">
         <f>IF(A41="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A41)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="42" hidden="1" outlineLevel="1" ht="24" customHeight="1">
-      <c r="A42" s="15">
+    <row r="42" hidden="1" outlineLevel="1" ht="27" customHeight="1">
+      <c r="A42" s="16">
         <f>IF(28&lt;=SUM('2 Matériel'!$M$6:$M$29),28,"")</f>
         <v/>
       </c>
-      <c r="B42" s="67">
-        <f>IF(A42="","",INDEX('2 Matériel'!$A$6:$A$29,$T42)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T42)&gt;1,"  ("&amp;(A42-INDEX('2 Matériel'!$N$6:$N$29,$T42)+INDEX('2 Matériel'!$M$6:$M$29,$T42))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T42)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C42" s="68" t="n"/>
-      <c r="D42" s="38">
-        <f>IF(A42="","",INDEX('2 Matériel'!$C$6:$C$29,$T42))</f>
-        <v/>
-      </c>
-      <c r="E42" s="69" t="n"/>
-      <c r="F42" s="69" t="n"/>
-      <c r="G42" s="69" t="n"/>
-      <c r="H42" s="69" t="n"/>
-      <c r="I42" s="70" t="n"/>
-      <c r="J42" s="70" t="n"/>
-      <c r="K42" s="68" t="n"/>
-      <c r="L42" s="70" t="n"/>
-      <c r="M42" s="71" t="n"/>
-      <c r="N42" s="70" t="n"/>
-      <c r="O42" s="70" t="n"/>
-      <c r="P42" s="70" t="n"/>
-      <c r="Q42" s="71" t="n"/>
-      <c r="R42" s="70" t="n"/>
-      <c r="T42" s="72">
+      <c r="B42" s="69" t="n"/>
+      <c r="C42" s="70" t="n"/>
+      <c r="D42" s="71">
+        <f>IF(A42="","",INDEX('2 Matériel'!$C$6:$C$29,$T42)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T42)&gt;1,"  ("&amp;(A42-INDEX('2 Matériel'!$N$6:$N$29,$T42)+INDEX('2 Matériel'!$M$6:$M$29,$T42))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T42)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T42)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T42),""))</f>
+        <v/>
+      </c>
+      <c r="E42" s="72" t="n"/>
+      <c r="F42" s="72" t="n"/>
+      <c r="G42" s="72" t="n"/>
+      <c r="H42" s="72" t="n"/>
+      <c r="I42" s="69" t="n"/>
+      <c r="J42" s="69" t="n"/>
+      <c r="K42" s="70" t="n"/>
+      <c r="L42" s="69" t="n"/>
+      <c r="M42" s="73" t="n"/>
+      <c r="N42" s="69" t="n"/>
+      <c r="O42" s="69" t="n"/>
+      <c r="P42" s="69" t="n"/>
+      <c r="Q42" s="73" t="n"/>
+      <c r="R42" s="69" t="n"/>
+      <c r="T42" s="74">
         <f>IF(A42="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A42)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="43" hidden="1" outlineLevel="1" ht="24" customHeight="1">
-      <c r="A43" s="15">
+    <row r="43" hidden="1" outlineLevel="1" ht="27" customHeight="1">
+      <c r="A43" s="16">
         <f>IF(29&lt;=SUM('2 Matériel'!$M$6:$M$29),29,"")</f>
         <v/>
       </c>
-      <c r="B43" s="67">
-        <f>IF(A43="","",INDEX('2 Matériel'!$A$6:$A$29,$T43)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T43)&gt;1,"  ("&amp;(A43-INDEX('2 Matériel'!$N$6:$N$29,$T43)+INDEX('2 Matériel'!$M$6:$M$29,$T43))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T43)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C43" s="68" t="n"/>
-      <c r="D43" s="38">
-        <f>IF(A43="","",INDEX('2 Matériel'!$C$6:$C$29,$T43))</f>
-        <v/>
-      </c>
-      <c r="E43" s="69" t="n"/>
-      <c r="F43" s="69" t="n"/>
-      <c r="G43" s="69" t="n"/>
-      <c r="H43" s="69" t="n"/>
-      <c r="I43" s="70" t="n"/>
-      <c r="J43" s="70" t="n"/>
-      <c r="K43" s="68" t="n"/>
-      <c r="L43" s="70" t="n"/>
-      <c r="M43" s="71" t="n"/>
-      <c r="N43" s="70" t="n"/>
-      <c r="O43" s="70" t="n"/>
-      <c r="P43" s="70" t="n"/>
-      <c r="Q43" s="71" t="n"/>
-      <c r="R43" s="70" t="n"/>
-      <c r="T43" s="72">
+      <c r="B43" s="69" t="n"/>
+      <c r="C43" s="70" t="n"/>
+      <c r="D43" s="71">
+        <f>IF(A43="","",INDEX('2 Matériel'!$C$6:$C$29,$T43)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T43)&gt;1,"  ("&amp;(A43-INDEX('2 Matériel'!$N$6:$N$29,$T43)+INDEX('2 Matériel'!$M$6:$M$29,$T43))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T43)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T43)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T43),""))</f>
+        <v/>
+      </c>
+      <c r="E43" s="72" t="n"/>
+      <c r="F43" s="72" t="n"/>
+      <c r="G43" s="72" t="n"/>
+      <c r="H43" s="72" t="n"/>
+      <c r="I43" s="69" t="n"/>
+      <c r="J43" s="69" t="n"/>
+      <c r="K43" s="70" t="n"/>
+      <c r="L43" s="69" t="n"/>
+      <c r="M43" s="73" t="n"/>
+      <c r="N43" s="69" t="n"/>
+      <c r="O43" s="69" t="n"/>
+      <c r="P43" s="69" t="n"/>
+      <c r="Q43" s="73" t="n"/>
+      <c r="R43" s="69" t="n"/>
+      <c r="T43" s="74">
         <f>IF(A43="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A43)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="44" hidden="1" outlineLevel="1" ht="24" customHeight="1">
-      <c r="A44" s="15">
+    <row r="44" hidden="1" outlineLevel="1" ht="27" customHeight="1">
+      <c r="A44" s="16">
         <f>IF(30&lt;=SUM('2 Matériel'!$M$6:$M$29),30,"")</f>
         <v/>
       </c>
-      <c r="B44" s="67">
-        <f>IF(A44="","",INDEX('2 Matériel'!$A$6:$A$29,$T44)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T44)&gt;1,"  ("&amp;(A44-INDEX('2 Matériel'!$N$6:$N$29,$T44)+INDEX('2 Matériel'!$M$6:$M$29,$T44))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T44)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C44" s="68" t="n"/>
-      <c r="D44" s="38">
-        <f>IF(A44="","",INDEX('2 Matériel'!$C$6:$C$29,$T44))</f>
-        <v/>
-      </c>
-      <c r="E44" s="69" t="n"/>
-      <c r="F44" s="69" t="n"/>
-      <c r="G44" s="69" t="n"/>
-      <c r="H44" s="69" t="n"/>
-      <c r="I44" s="70" t="n"/>
-      <c r="J44" s="70" t="n"/>
-      <c r="K44" s="68" t="n"/>
-      <c r="L44" s="70" t="n"/>
-      <c r="M44" s="71" t="n"/>
-      <c r="N44" s="70" t="n"/>
-      <c r="O44" s="70" t="n"/>
-      <c r="P44" s="70" t="n"/>
-      <c r="Q44" s="71" t="n"/>
-      <c r="R44" s="70" t="n"/>
-      <c r="T44" s="72">
+      <c r="B44" s="69" t="n"/>
+      <c r="C44" s="70" t="n"/>
+      <c r="D44" s="71">
+        <f>IF(A44="","",INDEX('2 Matériel'!$C$6:$C$29,$T44)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T44)&gt;1,"  ("&amp;(A44-INDEX('2 Matériel'!$N$6:$N$29,$T44)+INDEX('2 Matériel'!$M$6:$M$29,$T44))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T44)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T44)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T44),""))</f>
+        <v/>
+      </c>
+      <c r="E44" s="72" t="n"/>
+      <c r="F44" s="72" t="n"/>
+      <c r="G44" s="72" t="n"/>
+      <c r="H44" s="72" t="n"/>
+      <c r="I44" s="69" t="n"/>
+      <c r="J44" s="69" t="n"/>
+      <c r="K44" s="70" t="n"/>
+      <c r="L44" s="69" t="n"/>
+      <c r="M44" s="73" t="n"/>
+      <c r="N44" s="69" t="n"/>
+      <c r="O44" s="69" t="n"/>
+      <c r="P44" s="69" t="n"/>
+      <c r="Q44" s="73" t="n"/>
+      <c r="R44" s="69" t="n"/>
+      <c r="T44" s="74">
         <f>IF(A44="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A44)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="45" hidden="1" outlineLevel="1" ht="24" customHeight="1">
-      <c r="A45" s="15">
+    <row r="45" hidden="1" outlineLevel="1" ht="27" customHeight="1">
+      <c r="A45" s="16">
         <f>IF(31&lt;=SUM('2 Matériel'!$M$6:$M$29),31,"")</f>
         <v/>
       </c>
-      <c r="B45" s="67">
-        <f>IF(A45="","",INDEX('2 Matériel'!$A$6:$A$29,$T45)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T45)&gt;1,"  ("&amp;(A45-INDEX('2 Matériel'!$N$6:$N$29,$T45)+INDEX('2 Matériel'!$M$6:$M$29,$T45))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T45)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C45" s="68" t="n"/>
-      <c r="D45" s="38">
-        <f>IF(A45="","",INDEX('2 Matériel'!$C$6:$C$29,$T45))</f>
-        <v/>
-      </c>
-      <c r="E45" s="69" t="n"/>
-      <c r="F45" s="69" t="n"/>
-      <c r="G45" s="69" t="n"/>
-      <c r="H45" s="69" t="n"/>
-      <c r="I45" s="70" t="n"/>
-      <c r="J45" s="70" t="n"/>
-      <c r="K45" s="68" t="n"/>
-      <c r="L45" s="70" t="n"/>
-      <c r="M45" s="71" t="n"/>
-      <c r="N45" s="70" t="n"/>
-      <c r="O45" s="70" t="n"/>
-      <c r="P45" s="70" t="n"/>
-      <c r="Q45" s="71" t="n"/>
-      <c r="R45" s="70" t="n"/>
-      <c r="T45" s="72">
+      <c r="B45" s="69" t="n"/>
+      <c r="C45" s="70" t="n"/>
+      <c r="D45" s="71">
+        <f>IF(A45="","",INDEX('2 Matériel'!$C$6:$C$29,$T45)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T45)&gt;1,"  ("&amp;(A45-INDEX('2 Matériel'!$N$6:$N$29,$T45)+INDEX('2 Matériel'!$M$6:$M$29,$T45))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T45)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T45)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T45),""))</f>
+        <v/>
+      </c>
+      <c r="E45" s="72" t="n"/>
+      <c r="F45" s="72" t="n"/>
+      <c r="G45" s="72" t="n"/>
+      <c r="H45" s="72" t="n"/>
+      <c r="I45" s="69" t="n"/>
+      <c r="J45" s="69" t="n"/>
+      <c r="K45" s="70" t="n"/>
+      <c r="L45" s="69" t="n"/>
+      <c r="M45" s="73" t="n"/>
+      <c r="N45" s="69" t="n"/>
+      <c r="O45" s="69" t="n"/>
+      <c r="P45" s="69" t="n"/>
+      <c r="Q45" s="73" t="n"/>
+      <c r="R45" s="69" t="n"/>
+      <c r="T45" s="74">
         <f>IF(A45="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A45)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="46" hidden="1" outlineLevel="1" ht="24" customHeight="1">
-      <c r="A46" s="15">
+    <row r="46" hidden="1" outlineLevel="1" ht="27" customHeight="1">
+      <c r="A46" s="16">
         <f>IF(32&lt;=SUM('2 Matériel'!$M$6:$M$29),32,"")</f>
         <v/>
       </c>
-      <c r="B46" s="67">
-        <f>IF(A46="","",INDEX('2 Matériel'!$A$6:$A$29,$T46)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T46)&gt;1,"  ("&amp;(A46-INDEX('2 Matériel'!$N$6:$N$29,$T46)+INDEX('2 Matériel'!$M$6:$M$29,$T46))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T46)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C46" s="68" t="n"/>
-      <c r="D46" s="38">
-        <f>IF(A46="","",INDEX('2 Matériel'!$C$6:$C$29,$T46))</f>
-        <v/>
-      </c>
-      <c r="E46" s="69" t="n"/>
-      <c r="F46" s="69" t="n"/>
-      <c r="G46" s="69" t="n"/>
-      <c r="H46" s="69" t="n"/>
-      <c r="I46" s="70" t="n"/>
-      <c r="J46" s="70" t="n"/>
-      <c r="K46" s="68" t="n"/>
-      <c r="L46" s="70" t="n"/>
-      <c r="M46" s="71" t="n"/>
-      <c r="N46" s="70" t="n"/>
-      <c r="O46" s="70" t="n"/>
-      <c r="P46" s="70" t="n"/>
-      <c r="Q46" s="71" t="n"/>
-      <c r="R46" s="70" t="n"/>
-      <c r="T46" s="72">
+      <c r="B46" s="69" t="n"/>
+      <c r="C46" s="70" t="n"/>
+      <c r="D46" s="71">
+        <f>IF(A46="","",INDEX('2 Matériel'!$C$6:$C$29,$T46)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T46)&gt;1,"  ("&amp;(A46-INDEX('2 Matériel'!$N$6:$N$29,$T46)+INDEX('2 Matériel'!$M$6:$M$29,$T46))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T46)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T46)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T46),""))</f>
+        <v/>
+      </c>
+      <c r="E46" s="72" t="n"/>
+      <c r="F46" s="72" t="n"/>
+      <c r="G46" s="72" t="n"/>
+      <c r="H46" s="72" t="n"/>
+      <c r="I46" s="69" t="n"/>
+      <c r="J46" s="69" t="n"/>
+      <c r="K46" s="70" t="n"/>
+      <c r="L46" s="69" t="n"/>
+      <c r="M46" s="73" t="n"/>
+      <c r="N46" s="69" t="n"/>
+      <c r="O46" s="69" t="n"/>
+      <c r="P46" s="69" t="n"/>
+      <c r="Q46" s="73" t="n"/>
+      <c r="R46" s="69" t="n"/>
+      <c r="T46" s="74">
         <f>IF(A46="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A46)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="47" hidden="1" outlineLevel="1" ht="24" customHeight="1">
-      <c r="A47" s="15">
+    <row r="47" hidden="1" outlineLevel="1" ht="27" customHeight="1">
+      <c r="A47" s="16">
         <f>IF(33&lt;=SUM('2 Matériel'!$M$6:$M$29),33,"")</f>
         <v/>
       </c>
-      <c r="B47" s="67">
-        <f>IF(A47="","",INDEX('2 Matériel'!$A$6:$A$29,$T47)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T47)&gt;1,"  ("&amp;(A47-INDEX('2 Matériel'!$N$6:$N$29,$T47)+INDEX('2 Matériel'!$M$6:$M$29,$T47))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T47)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C47" s="68" t="n"/>
-      <c r="D47" s="38">
-        <f>IF(A47="","",INDEX('2 Matériel'!$C$6:$C$29,$T47))</f>
-        <v/>
-      </c>
-      <c r="E47" s="69" t="n"/>
-      <c r="F47" s="69" t="n"/>
-      <c r="G47" s="69" t="n"/>
-      <c r="H47" s="69" t="n"/>
-      <c r="I47" s="70" t="n"/>
-      <c r="J47" s="70" t="n"/>
-      <c r="K47" s="68" t="n"/>
-      <c r="L47" s="70" t="n"/>
-      <c r="M47" s="71" t="n"/>
-      <c r="N47" s="70" t="n"/>
-      <c r="O47" s="70" t="n"/>
-      <c r="P47" s="70" t="n"/>
-      <c r="Q47" s="71" t="n"/>
-      <c r="R47" s="70" t="n"/>
-      <c r="T47" s="72">
+      <c r="B47" s="69" t="n"/>
+      <c r="C47" s="70" t="n"/>
+      <c r="D47" s="71">
+        <f>IF(A47="","",INDEX('2 Matériel'!$C$6:$C$29,$T47)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T47)&gt;1,"  ("&amp;(A47-INDEX('2 Matériel'!$N$6:$N$29,$T47)+INDEX('2 Matériel'!$M$6:$M$29,$T47))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T47)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T47)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T47),""))</f>
+        <v/>
+      </c>
+      <c r="E47" s="72" t="n"/>
+      <c r="F47" s="72" t="n"/>
+      <c r="G47" s="72" t="n"/>
+      <c r="H47" s="72" t="n"/>
+      <c r="I47" s="69" t="n"/>
+      <c r="J47" s="69" t="n"/>
+      <c r="K47" s="70" t="n"/>
+      <c r="L47" s="69" t="n"/>
+      <c r="M47" s="73" t="n"/>
+      <c r="N47" s="69" t="n"/>
+      <c r="O47" s="69" t="n"/>
+      <c r="P47" s="69" t="n"/>
+      <c r="Q47" s="73" t="n"/>
+      <c r="R47" s="69" t="n"/>
+      <c r="T47" s="74">
         <f>IF(A47="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A47)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="48" hidden="1" outlineLevel="1" ht="24" customHeight="1">
-      <c r="A48" s="15">
+    <row r="48" hidden="1" outlineLevel="1" ht="27" customHeight="1">
+      <c r="A48" s="16">
         <f>IF(34&lt;=SUM('2 Matériel'!$M$6:$M$29),34,"")</f>
         <v/>
       </c>
-      <c r="B48" s="67">
-        <f>IF(A48="","",INDEX('2 Matériel'!$A$6:$A$29,$T48)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T48)&gt;1,"  ("&amp;(A48-INDEX('2 Matériel'!$N$6:$N$29,$T48)+INDEX('2 Matériel'!$M$6:$M$29,$T48))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T48)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C48" s="68" t="n"/>
-      <c r="D48" s="38">
-        <f>IF(A48="","",INDEX('2 Matériel'!$C$6:$C$29,$T48))</f>
-        <v/>
-      </c>
-      <c r="E48" s="69" t="n"/>
-      <c r="F48" s="69" t="n"/>
-      <c r="G48" s="69" t="n"/>
-      <c r="H48" s="69" t="n"/>
-      <c r="I48" s="70" t="n"/>
-      <c r="J48" s="70" t="n"/>
-      <c r="K48" s="68" t="n"/>
-      <c r="L48" s="70" t="n"/>
-      <c r="M48" s="71" t="n"/>
-      <c r="N48" s="70" t="n"/>
-      <c r="O48" s="70" t="n"/>
-      <c r="P48" s="70" t="n"/>
-      <c r="Q48" s="71" t="n"/>
-      <c r="R48" s="70" t="n"/>
-      <c r="T48" s="72">
+      <c r="B48" s="69" t="n"/>
+      <c r="C48" s="70" t="n"/>
+      <c r="D48" s="71">
+        <f>IF(A48="","",INDEX('2 Matériel'!$C$6:$C$29,$T48)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T48)&gt;1,"  ("&amp;(A48-INDEX('2 Matériel'!$N$6:$N$29,$T48)+INDEX('2 Matériel'!$M$6:$M$29,$T48))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T48)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T48)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T48),""))</f>
+        <v/>
+      </c>
+      <c r="E48" s="72" t="n"/>
+      <c r="F48" s="72" t="n"/>
+      <c r="G48" s="72" t="n"/>
+      <c r="H48" s="72" t="n"/>
+      <c r="I48" s="69" t="n"/>
+      <c r="J48" s="69" t="n"/>
+      <c r="K48" s="70" t="n"/>
+      <c r="L48" s="69" t="n"/>
+      <c r="M48" s="73" t="n"/>
+      <c r="N48" s="69" t="n"/>
+      <c r="O48" s="69" t="n"/>
+      <c r="P48" s="69" t="n"/>
+      <c r="Q48" s="73" t="n"/>
+      <c r="R48" s="69" t="n"/>
+      <c r="T48" s="74">
         <f>IF(A48="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A48)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="49" hidden="1" outlineLevel="1" ht="24" customHeight="1">
-      <c r="A49" s="15">
+    <row r="49" hidden="1" outlineLevel="1" ht="27" customHeight="1">
+      <c r="A49" s="16">
         <f>IF(35&lt;=SUM('2 Matériel'!$M$6:$M$29),35,"")</f>
         <v/>
       </c>
-      <c r="B49" s="67">
-        <f>IF(A49="","",INDEX('2 Matériel'!$A$6:$A$29,$T49)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T49)&gt;1,"  ("&amp;(A49-INDEX('2 Matériel'!$N$6:$N$29,$T49)+INDEX('2 Matériel'!$M$6:$M$29,$T49))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T49)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C49" s="68" t="n"/>
-      <c r="D49" s="38">
-        <f>IF(A49="","",INDEX('2 Matériel'!$C$6:$C$29,$T49))</f>
-        <v/>
-      </c>
-      <c r="E49" s="69" t="n"/>
-      <c r="F49" s="69" t="n"/>
-      <c r="G49" s="69" t="n"/>
-      <c r="H49" s="69" t="n"/>
-      <c r="I49" s="70" t="n"/>
-      <c r="J49" s="70" t="n"/>
-      <c r="K49" s="68" t="n"/>
-      <c r="L49" s="70" t="n"/>
-      <c r="M49" s="71" t="n"/>
-      <c r="N49" s="70" t="n"/>
-      <c r="O49" s="70" t="n"/>
-      <c r="P49" s="70" t="n"/>
-      <c r="Q49" s="71" t="n"/>
-      <c r="R49" s="70" t="n"/>
-      <c r="T49" s="72">
+      <c r="B49" s="69" t="n"/>
+      <c r="C49" s="70" t="n"/>
+      <c r="D49" s="71">
+        <f>IF(A49="","",INDEX('2 Matériel'!$C$6:$C$29,$T49)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T49)&gt;1,"  ("&amp;(A49-INDEX('2 Matériel'!$N$6:$N$29,$T49)+INDEX('2 Matériel'!$M$6:$M$29,$T49))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T49)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T49)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T49),""))</f>
+        <v/>
+      </c>
+      <c r="E49" s="72" t="n"/>
+      <c r="F49" s="72" t="n"/>
+      <c r="G49" s="72" t="n"/>
+      <c r="H49" s="72" t="n"/>
+      <c r="I49" s="69" t="n"/>
+      <c r="J49" s="69" t="n"/>
+      <c r="K49" s="70" t="n"/>
+      <c r="L49" s="69" t="n"/>
+      <c r="M49" s="73" t="n"/>
+      <c r="N49" s="69" t="n"/>
+      <c r="O49" s="69" t="n"/>
+      <c r="P49" s="69" t="n"/>
+      <c r="Q49" s="73" t="n"/>
+      <c r="R49" s="69" t="n"/>
+      <c r="T49" s="74">
         <f>IF(A49="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A49)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="50" hidden="1" outlineLevel="1" ht="24" customHeight="1">
-      <c r="A50" s="15">
+    <row r="50" hidden="1" outlineLevel="1" ht="27" customHeight="1">
+      <c r="A50" s="16">
         <f>IF(36&lt;=SUM('2 Matériel'!$M$6:$M$29),36,"")</f>
         <v/>
       </c>
-      <c r="B50" s="67">
-        <f>IF(A50="","",INDEX('2 Matériel'!$A$6:$A$29,$T50)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T50)&gt;1,"  ("&amp;(A50-INDEX('2 Matériel'!$N$6:$N$29,$T50)+INDEX('2 Matériel'!$M$6:$M$29,$T50))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T50)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C50" s="68" t="n"/>
-      <c r="D50" s="38">
-        <f>IF(A50="","",INDEX('2 Matériel'!$C$6:$C$29,$T50))</f>
-        <v/>
-      </c>
-      <c r="E50" s="69" t="n"/>
-      <c r="F50" s="69" t="n"/>
-      <c r="G50" s="69" t="n"/>
-      <c r="H50" s="69" t="n"/>
-      <c r="I50" s="70" t="n"/>
-      <c r="J50" s="70" t="n"/>
-      <c r="K50" s="68" t="n"/>
-      <c r="L50" s="70" t="n"/>
-      <c r="M50" s="71" t="n"/>
-      <c r="N50" s="70" t="n"/>
-      <c r="O50" s="70" t="n"/>
-      <c r="P50" s="70" t="n"/>
-      <c r="Q50" s="71" t="n"/>
-      <c r="R50" s="70" t="n"/>
-      <c r="T50" s="72">
+      <c r="B50" s="69" t="n"/>
+      <c r="C50" s="70" t="n"/>
+      <c r="D50" s="71">
+        <f>IF(A50="","",INDEX('2 Matériel'!$C$6:$C$29,$T50)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T50)&gt;1,"  ("&amp;(A50-INDEX('2 Matériel'!$N$6:$N$29,$T50)+INDEX('2 Matériel'!$M$6:$M$29,$T50))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T50)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T50)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T50),""))</f>
+        <v/>
+      </c>
+      <c r="E50" s="72" t="n"/>
+      <c r="F50" s="72" t="n"/>
+      <c r="G50" s="72" t="n"/>
+      <c r="H50" s="72" t="n"/>
+      <c r="I50" s="69" t="n"/>
+      <c r="J50" s="69" t="n"/>
+      <c r="K50" s="70" t="n"/>
+      <c r="L50" s="69" t="n"/>
+      <c r="M50" s="73" t="n"/>
+      <c r="N50" s="69" t="n"/>
+      <c r="O50" s="69" t="n"/>
+      <c r="P50" s="69" t="n"/>
+      <c r="Q50" s="73" t="n"/>
+      <c r="R50" s="69" t="n"/>
+      <c r="T50" s="74">
         <f>IF(A50="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A50)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="51" hidden="1" outlineLevel="1" ht="24" customHeight="1">
-      <c r="A51" s="15">
+    <row r="51" hidden="1" outlineLevel="1" ht="27" customHeight="1">
+      <c r="A51" s="16">
         <f>IF(37&lt;=SUM('2 Matériel'!$M$6:$M$29),37,"")</f>
         <v/>
       </c>
-      <c r="B51" s="67">
-        <f>IF(A51="","",INDEX('2 Matériel'!$A$6:$A$29,$T51)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T51)&gt;1,"  ("&amp;(A51-INDEX('2 Matériel'!$N$6:$N$29,$T51)+INDEX('2 Matériel'!$M$6:$M$29,$T51))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T51)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C51" s="68" t="n"/>
-      <c r="D51" s="38">
-        <f>IF(A51="","",INDEX('2 Matériel'!$C$6:$C$29,$T51))</f>
-        <v/>
-      </c>
-      <c r="E51" s="69" t="n"/>
-      <c r="F51" s="69" t="n"/>
-      <c r="G51" s="69" t="n"/>
-      <c r="H51" s="69" t="n"/>
-      <c r="I51" s="70" t="n"/>
-      <c r="J51" s="70" t="n"/>
-      <c r="K51" s="68" t="n"/>
-      <c r="L51" s="70" t="n"/>
-      <c r="M51" s="71" t="n"/>
-      <c r="N51" s="70" t="n"/>
-      <c r="O51" s="70" t="n"/>
-      <c r="P51" s="70" t="n"/>
-      <c r="Q51" s="71" t="n"/>
-      <c r="R51" s="70" t="n"/>
-      <c r="T51" s="72">
+      <c r="B51" s="69" t="n"/>
+      <c r="C51" s="70" t="n"/>
+      <c r="D51" s="71">
+        <f>IF(A51="","",INDEX('2 Matériel'!$C$6:$C$29,$T51)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T51)&gt;1,"  ("&amp;(A51-INDEX('2 Matériel'!$N$6:$N$29,$T51)+INDEX('2 Matériel'!$M$6:$M$29,$T51))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T51)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T51)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T51),""))</f>
+        <v/>
+      </c>
+      <c r="E51" s="72" t="n"/>
+      <c r="F51" s="72" t="n"/>
+      <c r="G51" s="72" t="n"/>
+      <c r="H51" s="72" t="n"/>
+      <c r="I51" s="69" t="n"/>
+      <c r="J51" s="69" t="n"/>
+      <c r="K51" s="70" t="n"/>
+      <c r="L51" s="69" t="n"/>
+      <c r="M51" s="73" t="n"/>
+      <c r="N51" s="69" t="n"/>
+      <c r="O51" s="69" t="n"/>
+      <c r="P51" s="69" t="n"/>
+      <c r="Q51" s="73" t="n"/>
+      <c r="R51" s="69" t="n"/>
+      <c r="T51" s="74">
         <f>IF(A51="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A51)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="52" hidden="1" outlineLevel="1" ht="24" customHeight="1">
-      <c r="A52" s="15">
+    <row r="52" hidden="1" outlineLevel="1" ht="27" customHeight="1">
+      <c r="A52" s="16">
         <f>IF(38&lt;=SUM('2 Matériel'!$M$6:$M$29),38,"")</f>
         <v/>
       </c>
-      <c r="B52" s="67">
-        <f>IF(A52="","",INDEX('2 Matériel'!$A$6:$A$29,$T52)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T52)&gt;1,"  ("&amp;(A52-INDEX('2 Matériel'!$N$6:$N$29,$T52)+INDEX('2 Matériel'!$M$6:$M$29,$T52))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T52)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C52" s="68" t="n"/>
-      <c r="D52" s="38">
-        <f>IF(A52="","",INDEX('2 Matériel'!$C$6:$C$29,$T52))</f>
-        <v/>
-      </c>
-      <c r="E52" s="69" t="n"/>
-      <c r="F52" s="69" t="n"/>
-      <c r="G52" s="69" t="n"/>
-      <c r="H52" s="69" t="n"/>
-      <c r="I52" s="70" t="n"/>
-      <c r="J52" s="70" t="n"/>
-      <c r="K52" s="68" t="n"/>
-      <c r="L52" s="70" t="n"/>
-      <c r="M52" s="71" t="n"/>
-      <c r="N52" s="70" t="n"/>
-      <c r="O52" s="70" t="n"/>
-      <c r="P52" s="70" t="n"/>
-      <c r="Q52" s="71" t="n"/>
-      <c r="R52" s="70" t="n"/>
-      <c r="T52" s="72">
+      <c r="B52" s="69" t="n"/>
+      <c r="C52" s="70" t="n"/>
+      <c r="D52" s="71">
+        <f>IF(A52="","",INDEX('2 Matériel'!$C$6:$C$29,$T52)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T52)&gt;1,"  ("&amp;(A52-INDEX('2 Matériel'!$N$6:$N$29,$T52)+INDEX('2 Matériel'!$M$6:$M$29,$T52))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T52)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T52)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T52),""))</f>
+        <v/>
+      </c>
+      <c r="E52" s="72" t="n"/>
+      <c r="F52" s="72" t="n"/>
+      <c r="G52" s="72" t="n"/>
+      <c r="H52" s="72" t="n"/>
+      <c r="I52" s="69" t="n"/>
+      <c r="J52" s="69" t="n"/>
+      <c r="K52" s="70" t="n"/>
+      <c r="L52" s="69" t="n"/>
+      <c r="M52" s="73" t="n"/>
+      <c r="N52" s="69" t="n"/>
+      <c r="O52" s="69" t="n"/>
+      <c r="P52" s="69" t="n"/>
+      <c r="Q52" s="73" t="n"/>
+      <c r="R52" s="69" t="n"/>
+      <c r="T52" s="74">
         <f>IF(A52="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A52)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="53" hidden="1" outlineLevel="1" ht="24" customHeight="1">
-      <c r="A53" s="15">
+    <row r="53" hidden="1" outlineLevel="1" ht="27" customHeight="1">
+      <c r="A53" s="16">
         <f>IF(39&lt;=SUM('2 Matériel'!$M$6:$M$29),39,"")</f>
         <v/>
       </c>
-      <c r="B53" s="67">
-        <f>IF(A53="","",INDEX('2 Matériel'!$A$6:$A$29,$T53)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T53)&gt;1,"  ("&amp;(A53-INDEX('2 Matériel'!$N$6:$N$29,$T53)+INDEX('2 Matériel'!$M$6:$M$29,$T53))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T53)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C53" s="68" t="n"/>
-      <c r="D53" s="38">
-        <f>IF(A53="","",INDEX('2 Matériel'!$C$6:$C$29,$T53))</f>
-        <v/>
-      </c>
-      <c r="E53" s="69" t="n"/>
-      <c r="F53" s="69" t="n"/>
-      <c r="G53" s="69" t="n"/>
-      <c r="H53" s="69" t="n"/>
-      <c r="I53" s="70" t="n"/>
-      <c r="J53" s="70" t="n"/>
-      <c r="K53" s="68" t="n"/>
-      <c r="L53" s="70" t="n"/>
-      <c r="M53" s="71" t="n"/>
-      <c r="N53" s="70" t="n"/>
-      <c r="O53" s="70" t="n"/>
-      <c r="P53" s="70" t="n"/>
-      <c r="Q53" s="71" t="n"/>
-      <c r="R53" s="70" t="n"/>
-      <c r="T53" s="72">
+      <c r="B53" s="69" t="n"/>
+      <c r="C53" s="70" t="n"/>
+      <c r="D53" s="71">
+        <f>IF(A53="","",INDEX('2 Matériel'!$C$6:$C$29,$T53)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T53)&gt;1,"  ("&amp;(A53-INDEX('2 Matériel'!$N$6:$N$29,$T53)+INDEX('2 Matériel'!$M$6:$M$29,$T53))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T53)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T53)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T53),""))</f>
+        <v/>
+      </c>
+      <c r="E53" s="72" t="n"/>
+      <c r="F53" s="72" t="n"/>
+      <c r="G53" s="72" t="n"/>
+      <c r="H53" s="72" t="n"/>
+      <c r="I53" s="69" t="n"/>
+      <c r="J53" s="69" t="n"/>
+      <c r="K53" s="70" t="n"/>
+      <c r="L53" s="69" t="n"/>
+      <c r="M53" s="73" t="n"/>
+      <c r="N53" s="69" t="n"/>
+      <c r="O53" s="69" t="n"/>
+      <c r="P53" s="69" t="n"/>
+      <c r="Q53" s="73" t="n"/>
+      <c r="R53" s="69" t="n"/>
+      <c r="T53" s="74">
         <f>IF(A53="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A53)+1)</f>
         <v/>
       </c>
     </row>
-    <row r="54" hidden="1" outlineLevel="1" ht="24" customHeight="1">
-      <c r="A54" s="15">
+    <row r="54" hidden="1" outlineLevel="1" ht="27" customHeight="1">
+      <c r="A54" s="16">
         <f>IF(40&lt;=SUM('2 Matériel'!$M$6:$M$29),40,"")</f>
         <v/>
       </c>
-      <c r="B54" s="67">
-        <f>IF(A54="","",INDEX('2 Matériel'!$A$6:$A$29,$T54)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T54)&gt;1,"  ("&amp;(A54-INDEX('2 Matériel'!$N$6:$N$29,$T54)+INDEX('2 Matériel'!$M$6:$M$29,$T54))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T54)&amp;")",""))</f>
-        <v/>
-      </c>
-      <c r="C54" s="68" t="n"/>
-      <c r="D54" s="38">
-        <f>IF(A54="","",INDEX('2 Matériel'!$C$6:$C$29,$T54))</f>
-        <v/>
-      </c>
-      <c r="E54" s="69" t="n"/>
-      <c r="F54" s="69" t="n"/>
-      <c r="G54" s="69" t="n"/>
-      <c r="H54" s="69" t="n"/>
-      <c r="I54" s="70" t="n"/>
-      <c r="J54" s="70" t="n"/>
-      <c r="K54" s="68" t="n"/>
-      <c r="L54" s="70" t="n"/>
-      <c r="M54" s="71" t="n"/>
-      <c r="N54" s="70" t="n"/>
-      <c r="O54" s="70" t="n"/>
-      <c r="P54" s="70" t="n"/>
-      <c r="Q54" s="71" t="n"/>
-      <c r="R54" s="70" t="n"/>
-      <c r="T54" s="72">
+      <c r="B54" s="69" t="n"/>
+      <c r="C54" s="70" t="n"/>
+      <c r="D54" s="71">
+        <f>IF(A54="","",INDEX('2 Matériel'!$C$6:$C$29,$T54)&amp;IF(INDEX('2 Matériel'!$M$6:$M$29,$T54)&gt;1,"  ("&amp;(A54-INDEX('2 Matériel'!$N$6:$N$29,$T54)+INDEX('2 Matériel'!$M$6:$M$29,$T54))&amp;"/"&amp;INDEX('2 Matériel'!$M$6:$M$29,$T54)&amp;")","")&amp;IF(INDEX('2 Matériel'!$B$6:$B$29,$T54)&lt;&gt;"",CHAR(10)&amp;"→ "&amp;INDEX('2 Matériel'!$B$6:$B$29,$T54),""))</f>
+        <v/>
+      </c>
+      <c r="E54" s="72" t="n"/>
+      <c r="F54" s="72" t="n"/>
+      <c r="G54" s="72" t="n"/>
+      <c r="H54" s="72" t="n"/>
+      <c r="I54" s="69" t="n"/>
+      <c r="J54" s="69" t="n"/>
+      <c r="K54" s="70" t="n"/>
+      <c r="L54" s="69" t="n"/>
+      <c r="M54" s="73" t="n"/>
+      <c r="N54" s="69" t="n"/>
+      <c r="O54" s="69" t="n"/>
+      <c r="P54" s="69" t="n"/>
+      <c r="Q54" s="73" t="n"/>
+      <c r="R54" s="69" t="n"/>
+      <c r="T54" s="74">
         <f>IF(A54="","",COUNTIF('2 Matériel'!$N$6:$N$29,"&lt;"&amp;A54)+1)</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="42">
+      <c r="A55" s="44">
         <f>IF(SUM('2 Matériel'!$M$6:$M$29)&gt;20,"⚠  "&amp;(SUM('2 Matériel'!$M$6:$M$29)-20)&amp;" ligne(s) au-delà de la ligne 20 sont masquées : cliquer sur le [+] dans la marge gauche pour les afficher.","")</f>
         <v/>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="64" t="inlineStr">
+      <c r="A57" s="66" t="inlineStr">
         <is>
           <t>COLISAGE  ·  PACKING</t>
         </is>
@@ -6388,421 +6606,421 @@
       <c r="R57" s="1" t="n"/>
     </row>
     <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="36" t="inlineStr">
+      <c r="A58" s="38" t="inlineStr">
         <is>
           <t>Colis</t>
         </is>
       </c>
-      <c r="B58" s="73" t="n"/>
-      <c r="C58" s="36" t="inlineStr">
+      <c r="B58" s="75" t="n"/>
+      <c r="C58" s="38" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="D58" s="36" t="inlineStr">
+      <c r="D58" s="38" t="inlineStr">
         <is>
           <t>Contenu (items de la tool list)</t>
         </is>
       </c>
-      <c r="E58" s="36" t="inlineStr">
+      <c r="E58" s="38" t="inlineStr">
         <is>
           <t>L (cm)</t>
         </is>
       </c>
-      <c r="F58" s="36" t="inlineStr">
+      <c r="F58" s="38" t="inlineStr">
         <is>
           <t>l (cm)</t>
         </is>
       </c>
-      <c r="G58" s="36" t="inlineStr">
+      <c r="G58" s="38" t="inlineStr">
         <is>
           <t>h (cm)</t>
         </is>
       </c>
-      <c r="H58" s="36" t="inlineStr">
+      <c r="H58" s="38" t="inlineStr">
         <is>
           <t>Poids (kg)</t>
         </is>
       </c>
-      <c r="I58" s="36" t="inlineStr">
+      <c r="I58" s="38" t="inlineStr">
         <is>
           <t>Volume (m³)</t>
         </is>
       </c>
-      <c r="J58" s="36" t="inlineStr">
+      <c r="J58" s="38" t="inlineStr">
         <is>
           <t>Remarques</t>
         </is>
       </c>
-      <c r="K58" s="73" t="n"/>
+      <c r="K58" s="75" t="n"/>
     </row>
     <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="74" t="inlineStr">
+      <c r="A59" s="76" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="B59" s="33" t="n"/>
-      <c r="C59" s="75" t="n"/>
-      <c r="D59" s="76">
+      <c r="B59" s="35" t="n"/>
+      <c r="C59" s="77" t="n"/>
+      <c r="D59" s="78">
         <f t="array" ref="D59">_xlfn.TEXTJOIN(", ",TRUE,IF($O$15:$O$54=$A59,$A$15:$A$54,""))</f>
         <v/>
       </c>
-      <c r="E59" s="77" t="n"/>
-      <c r="F59" s="77" t="n"/>
-      <c r="G59" s="77" t="n"/>
-      <c r="H59" s="78" t="n"/>
-      <c r="I59" s="79">
+      <c r="E59" s="79" t="n"/>
+      <c r="F59" s="79" t="n"/>
+      <c r="G59" s="79" t="n"/>
+      <c r="H59" s="80" t="n"/>
+      <c r="I59" s="81">
         <f>IF(COUNT(E59:G59)=3,E59*F59*G59/1000000,"")</f>
         <v/>
       </c>
-      <c r="J59" s="80" t="n"/>
-      <c r="K59" s="33" t="n"/>
+      <c r="J59" s="82" t="n"/>
+      <c r="K59" s="35" t="n"/>
     </row>
     <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="74" t="inlineStr">
+      <c r="A60" s="76" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="B60" s="33" t="n"/>
-      <c r="C60" s="75" t="n"/>
-      <c r="D60" s="76">
+      <c r="B60" s="35" t="n"/>
+      <c r="C60" s="77" t="n"/>
+      <c r="D60" s="78">
         <f t="array" ref="D60">_xlfn.TEXTJOIN(", ",TRUE,IF($O$15:$O$54=$A60,$A$15:$A$54,""))</f>
         <v/>
       </c>
-      <c r="E60" s="77" t="n"/>
-      <c r="F60" s="77" t="n"/>
-      <c r="G60" s="77" t="n"/>
-      <c r="H60" s="78" t="n"/>
-      <c r="I60" s="79">
+      <c r="E60" s="79" t="n"/>
+      <c r="F60" s="79" t="n"/>
+      <c r="G60" s="79" t="n"/>
+      <c r="H60" s="80" t="n"/>
+      <c r="I60" s="81">
         <f>IF(COUNT(E60:G60)=3,E60*F60*G60/1000000,"")</f>
         <v/>
       </c>
-      <c r="J60" s="80" t="n"/>
-      <c r="K60" s="33" t="n"/>
+      <c r="J60" s="82" t="n"/>
+      <c r="K60" s="35" t="n"/>
     </row>
     <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="74" t="inlineStr">
+      <c r="A61" s="76" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="B61" s="33" t="n"/>
-      <c r="C61" s="75" t="n"/>
-      <c r="D61" s="76">
+      <c r="B61" s="35" t="n"/>
+      <c r="C61" s="77" t="n"/>
+      <c r="D61" s="78">
         <f t="array" ref="D61">_xlfn.TEXTJOIN(", ",TRUE,IF($O$15:$O$54=$A61,$A$15:$A$54,""))</f>
         <v/>
       </c>
-      <c r="E61" s="77" t="n"/>
-      <c r="F61" s="77" t="n"/>
-      <c r="G61" s="77" t="n"/>
-      <c r="H61" s="78" t="n"/>
-      <c r="I61" s="79">
+      <c r="E61" s="79" t="n"/>
+      <c r="F61" s="79" t="n"/>
+      <c r="G61" s="79" t="n"/>
+      <c r="H61" s="80" t="n"/>
+      <c r="I61" s="81">
         <f>IF(COUNT(E61:G61)=3,E61*F61*G61/1000000,"")</f>
         <v/>
       </c>
-      <c r="J61" s="80" t="n"/>
-      <c r="K61" s="33" t="n"/>
+      <c r="J61" s="82" t="n"/>
+      <c r="K61" s="35" t="n"/>
     </row>
     <row r="62" ht="22" customHeight="1">
-      <c r="A62" s="74" t="inlineStr">
+      <c r="A62" s="76" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="B62" s="33" t="n"/>
-      <c r="C62" s="75" t="n"/>
-      <c r="D62" s="76">
+      <c r="B62" s="35" t="n"/>
+      <c r="C62" s="77" t="n"/>
+      <c r="D62" s="78">
         <f t="array" ref="D62">_xlfn.TEXTJOIN(", ",TRUE,IF($O$15:$O$54=$A62,$A$15:$A$54,""))</f>
         <v/>
       </c>
-      <c r="E62" s="77" t="n"/>
-      <c r="F62" s="77" t="n"/>
-      <c r="G62" s="77" t="n"/>
-      <c r="H62" s="78" t="n"/>
-      <c r="I62" s="79">
+      <c r="E62" s="79" t="n"/>
+      <c r="F62" s="79" t="n"/>
+      <c r="G62" s="79" t="n"/>
+      <c r="H62" s="80" t="n"/>
+      <c r="I62" s="81">
         <f>IF(COUNT(E62:G62)=3,E62*F62*G62/1000000,"")</f>
         <v/>
       </c>
-      <c r="J62" s="80" t="n"/>
-      <c r="K62" s="33" t="n"/>
+      <c r="J62" s="82" t="n"/>
+      <c r="K62" s="35" t="n"/>
     </row>
     <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="74" t="inlineStr">
+      <c r="A63" s="76" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="B63" s="33" t="n"/>
-      <c r="C63" s="75" t="n"/>
-      <c r="D63" s="76">
+      <c r="B63" s="35" t="n"/>
+      <c r="C63" s="77" t="n"/>
+      <c r="D63" s="78">
         <f t="array" ref="D63">_xlfn.TEXTJOIN(", ",TRUE,IF($O$15:$O$54=$A63,$A$15:$A$54,""))</f>
         <v/>
       </c>
-      <c r="E63" s="77" t="n"/>
-      <c r="F63" s="77" t="n"/>
-      <c r="G63" s="77" t="n"/>
-      <c r="H63" s="78" t="n"/>
-      <c r="I63" s="79">
+      <c r="E63" s="79" t="n"/>
+      <c r="F63" s="79" t="n"/>
+      <c r="G63" s="79" t="n"/>
+      <c r="H63" s="80" t="n"/>
+      <c r="I63" s="81">
         <f>IF(COUNT(E63:G63)=3,E63*F63*G63/1000000,"")</f>
         <v/>
       </c>
-      <c r="J63" s="80" t="n"/>
-      <c r="K63" s="33" t="n"/>
+      <c r="J63" s="82" t="n"/>
+      <c r="K63" s="35" t="n"/>
     </row>
     <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="74" t="inlineStr">
+      <c r="A64" s="76" t="inlineStr">
         <is>
           <t>P6</t>
         </is>
       </c>
-      <c r="B64" s="33" t="n"/>
-      <c r="C64" s="75" t="n"/>
-      <c r="D64" s="76">
+      <c r="B64" s="35" t="n"/>
+      <c r="C64" s="77" t="n"/>
+      <c r="D64" s="78">
         <f t="array" ref="D64">_xlfn.TEXTJOIN(", ",TRUE,IF($O$15:$O$54=$A64,$A$15:$A$54,""))</f>
         <v/>
       </c>
-      <c r="E64" s="77" t="n"/>
-      <c r="F64" s="77" t="n"/>
-      <c r="G64" s="77" t="n"/>
-      <c r="H64" s="78" t="n"/>
-      <c r="I64" s="79">
+      <c r="E64" s="79" t="n"/>
+      <c r="F64" s="79" t="n"/>
+      <c r="G64" s="79" t="n"/>
+      <c r="H64" s="80" t="n"/>
+      <c r="I64" s="81">
         <f>IF(COUNT(E64:G64)=3,E64*F64*G64/1000000,"")</f>
         <v/>
       </c>
-      <c r="J64" s="80" t="n"/>
-      <c r="K64" s="33" t="n"/>
+      <c r="J64" s="82" t="n"/>
+      <c r="K64" s="35" t="n"/>
     </row>
     <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="74" t="inlineStr">
+      <c r="A65" s="76" t="inlineStr">
         <is>
           <t>P7</t>
         </is>
       </c>
-      <c r="B65" s="33" t="n"/>
-      <c r="C65" s="75" t="n"/>
-      <c r="D65" s="76">
+      <c r="B65" s="35" t="n"/>
+      <c r="C65" s="77" t="n"/>
+      <c r="D65" s="78">
         <f t="array" ref="D65">_xlfn.TEXTJOIN(", ",TRUE,IF($O$15:$O$54=$A65,$A$15:$A$54,""))</f>
         <v/>
       </c>
-      <c r="E65" s="77" t="n"/>
-      <c r="F65" s="77" t="n"/>
-      <c r="G65" s="77" t="n"/>
-      <c r="H65" s="78" t="n"/>
-      <c r="I65" s="79">
+      <c r="E65" s="79" t="n"/>
+      <c r="F65" s="79" t="n"/>
+      <c r="G65" s="79" t="n"/>
+      <c r="H65" s="80" t="n"/>
+      <c r="I65" s="81">
         <f>IF(COUNT(E65:G65)=3,E65*F65*G65/1000000,"")</f>
         <v/>
       </c>
-      <c r="J65" s="80" t="n"/>
-      <c r="K65" s="33" t="n"/>
+      <c r="J65" s="82" t="n"/>
+      <c r="K65" s="35" t="n"/>
     </row>
     <row r="66" ht="22" customHeight="1">
-      <c r="A66" s="74" t="inlineStr">
+      <c r="A66" s="76" t="inlineStr">
         <is>
           <t>P8</t>
         </is>
       </c>
-      <c r="B66" s="33" t="n"/>
-      <c r="C66" s="75" t="n"/>
-      <c r="D66" s="76">
+      <c r="B66" s="35" t="n"/>
+      <c r="C66" s="77" t="n"/>
+      <c r="D66" s="78">
         <f t="array" ref="D66">_xlfn.TEXTJOIN(", ",TRUE,IF($O$15:$O$54=$A66,$A$15:$A$54,""))</f>
         <v/>
       </c>
-      <c r="E66" s="77" t="n"/>
-      <c r="F66" s="77" t="n"/>
-      <c r="G66" s="77" t="n"/>
-      <c r="H66" s="78" t="n"/>
-      <c r="I66" s="79">
+      <c r="E66" s="79" t="n"/>
+      <c r="F66" s="79" t="n"/>
+      <c r="G66" s="79" t="n"/>
+      <c r="H66" s="80" t="n"/>
+      <c r="I66" s="81">
         <f>IF(COUNT(E66:G66)=3,E66*F66*G66/1000000,"")</f>
         <v/>
       </c>
-      <c r="J66" s="80" t="n"/>
-      <c r="K66" s="33" t="n"/>
+      <c r="J66" s="82" t="n"/>
+      <c r="K66" s="35" t="n"/>
     </row>
     <row r="67" ht="22" customHeight="1">
-      <c r="A67" s="74" t="inlineStr">
+      <c r="A67" s="76" t="inlineStr">
         <is>
           <t>P9</t>
         </is>
       </c>
-      <c r="B67" s="33" t="n"/>
-      <c r="C67" s="75" t="n"/>
-      <c r="D67" s="76">
+      <c r="B67" s="35" t="n"/>
+      <c r="C67" s="77" t="n"/>
+      <c r="D67" s="78">
         <f t="array" ref="D67">_xlfn.TEXTJOIN(", ",TRUE,IF($O$15:$O$54=$A67,$A$15:$A$54,""))</f>
         <v/>
       </c>
-      <c r="E67" s="77" t="n"/>
-      <c r="F67" s="77" t="n"/>
-      <c r="G67" s="77" t="n"/>
-      <c r="H67" s="78" t="n"/>
-      <c r="I67" s="79">
+      <c r="E67" s="79" t="n"/>
+      <c r="F67" s="79" t="n"/>
+      <c r="G67" s="79" t="n"/>
+      <c r="H67" s="80" t="n"/>
+      <c r="I67" s="81">
         <f>IF(COUNT(E67:G67)=3,E67*F67*G67/1000000,"")</f>
         <v/>
       </c>
-      <c r="J67" s="80" t="n"/>
-      <c r="K67" s="33" t="n"/>
+      <c r="J67" s="82" t="n"/>
+      <c r="K67" s="35" t="n"/>
     </row>
     <row r="68" ht="22" customHeight="1">
-      <c r="A68" s="74" t="inlineStr">
+      <c r="A68" s="76" t="inlineStr">
         <is>
           <t>P10</t>
         </is>
       </c>
-      <c r="B68" s="33" t="n"/>
-      <c r="C68" s="75" t="n"/>
-      <c r="D68" s="76">
+      <c r="B68" s="35" t="n"/>
+      <c r="C68" s="77" t="n"/>
+      <c r="D68" s="78">
         <f t="array" ref="D68">_xlfn.TEXTJOIN(", ",TRUE,IF($O$15:$O$54=$A68,$A$15:$A$54,""))</f>
         <v/>
       </c>
-      <c r="E68" s="77" t="n"/>
-      <c r="F68" s="77" t="n"/>
-      <c r="G68" s="77" t="n"/>
-      <c r="H68" s="78" t="n"/>
-      <c r="I68" s="79">
+      <c r="E68" s="79" t="n"/>
+      <c r="F68" s="79" t="n"/>
+      <c r="G68" s="79" t="n"/>
+      <c r="H68" s="80" t="n"/>
+      <c r="I68" s="81">
         <f>IF(COUNT(E68:G68)=3,E68*F68*G68/1000000,"")</f>
         <v/>
       </c>
-      <c r="J68" s="80" t="n"/>
-      <c r="K68" s="33" t="n"/>
+      <c r="J68" s="82" t="n"/>
+      <c r="K68" s="35" t="n"/>
     </row>
     <row r="69" ht="22" customHeight="1">
-      <c r="A69" s="74" t="inlineStr">
+      <c r="A69" s="76" t="inlineStr">
         <is>
           <t>Loose</t>
         </is>
       </c>
-      <c r="B69" s="33" t="n"/>
-      <c r="C69" s="81" t="inlineStr">
+      <c r="B69" s="35" t="n"/>
+      <c r="C69" s="83" t="inlineStr">
         <is>
           <t>Loose (vrac)</t>
         </is>
       </c>
-      <c r="D69" s="76">
+      <c r="D69" s="78">
         <f t="array" ref="D69">_xlfn.TEXTJOIN(", ",TRUE,IF($O$15:$O$54=$A69,$A$15:$A$54,""))</f>
         <v/>
       </c>
-      <c r="E69" s="33" t="n"/>
-      <c r="F69" s="33" t="n"/>
-      <c r="G69" s="33" t="n"/>
-      <c r="H69" s="78" t="n"/>
-      <c r="I69" s="33" t="n"/>
-      <c r="J69" s="33" t="n"/>
-      <c r="K69" s="33" t="n"/>
+      <c r="E69" s="35" t="n"/>
+      <c r="F69" s="35" t="n"/>
+      <c r="G69" s="35" t="n"/>
+      <c r="H69" s="80" t="n"/>
+      <c r="I69" s="35" t="n"/>
+      <c r="J69" s="35" t="n"/>
+      <c r="K69" s="35" t="n"/>
     </row>
     <row r="70" ht="22" customHeight="1">
-      <c r="A70" s="82">
+      <c r="A70" s="84">
         <f>"TOTAL  ·  "&amp;COUNTA(C59:C68)&amp;" colis  ·  "&amp;SUM('2 Matériel'!$M$6:$M$29)&amp;" outil(s)"</f>
         <v/>
       </c>
-      <c r="B70" s="83" t="n"/>
-      <c r="C70" s="83" t="n"/>
-      <c r="D70" s="83" t="n"/>
-      <c r="E70" s="83" t="n"/>
-      <c r="F70" s="83" t="n"/>
-      <c r="G70" s="83" t="n"/>
-      <c r="H70" s="84">
+      <c r="B70" s="85" t="n"/>
+      <c r="C70" s="85" t="n"/>
+      <c r="D70" s="85" t="n"/>
+      <c r="E70" s="85" t="n"/>
+      <c r="F70" s="85" t="n"/>
+      <c r="G70" s="85" t="n"/>
+      <c r="H70" s="86">
         <f>SUM(H59:H69)</f>
         <v/>
       </c>
-      <c r="I70" s="85">
+      <c r="I70" s="87">
         <f>SUM(I59:I68)</f>
         <v/>
       </c>
-      <c r="J70" s="86" t="n"/>
-      <c r="K70" s="86" t="n"/>
+      <c r="J70" s="88" t="n"/>
+      <c r="K70" s="88" t="n"/>
     </row>
     <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="87" t="inlineStr">
+      <c r="A72" s="89" t="inlineStr">
         <is>
           <t>PRÉPARÉ PAR · Nom, date, signature</t>
         </is>
       </c>
-      <c r="B72" s="55" t="n"/>
-      <c r="C72" s="55" t="n"/>
-      <c r="D72" s="56" t="n"/>
-      <c r="E72" s="87" t="inlineStr">
+      <c r="B72" s="57" t="n"/>
+      <c r="C72" s="57" t="n"/>
+      <c r="D72" s="58" t="n"/>
+      <c r="E72" s="89" t="inlineStr">
         <is>
           <t>CONTRÔLÉ PAR (superviseur) · Nom, date, signature</t>
         </is>
       </c>
-      <c r="F72" s="55" t="n"/>
-      <c r="G72" s="55" t="n"/>
-      <c r="H72" s="55" t="n"/>
-      <c r="I72" s="55" t="n"/>
-      <c r="J72" s="55" t="n"/>
-      <c r="K72" s="56" t="n"/>
-      <c r="L72" s="87" t="inlineStr">
+      <c r="F72" s="57" t="n"/>
+      <c r="G72" s="57" t="n"/>
+      <c r="H72" s="57" t="n"/>
+      <c r="I72" s="57" t="n"/>
+      <c r="J72" s="57" t="n"/>
+      <c r="K72" s="58" t="n"/>
+      <c r="L72" s="89" t="inlineStr">
         <is>
           <t>COLISAGE VÉRIFIÉ PAR · Nom, date</t>
         </is>
       </c>
-      <c r="M72" s="55" t="n"/>
-      <c r="N72" s="55" t="n"/>
-      <c r="O72" s="55" t="n"/>
-      <c r="P72" s="55" t="n"/>
-      <c r="Q72" s="55" t="n"/>
-      <c r="R72" s="56" t="n"/>
+      <c r="M72" s="57" t="n"/>
+      <c r="N72" s="57" t="n"/>
+      <c r="O72" s="57" t="n"/>
+      <c r="P72" s="57" t="n"/>
+      <c r="Q72" s="57" t="n"/>
+      <c r="R72" s="58" t="n"/>
     </row>
     <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="57" t="n"/>
-      <c r="B73" s="58" t="n"/>
-      <c r="C73" s="58" t="n"/>
-      <c r="D73" s="59" t="n"/>
-      <c r="E73" s="57" t="n"/>
-      <c r="F73" s="58" t="n"/>
-      <c r="G73" s="58" t="n"/>
-      <c r="H73" s="58" t="n"/>
-      <c r="I73" s="58" t="n"/>
-      <c r="J73" s="58" t="n"/>
-      <c r="K73" s="59" t="n"/>
-      <c r="L73" s="57" t="n"/>
-      <c r="M73" s="58" t="n"/>
-      <c r="N73" s="58" t="n"/>
-      <c r="O73" s="58" t="n"/>
-      <c r="P73" s="58" t="n"/>
-      <c r="Q73" s="58" t="n"/>
-      <c r="R73" s="59" t="n"/>
+      <c r="A73" s="59" t="n"/>
+      <c r="B73" s="60" t="n"/>
+      <c r="C73" s="60" t="n"/>
+      <c r="D73" s="61" t="n"/>
+      <c r="E73" s="59" t="n"/>
+      <c r="F73" s="60" t="n"/>
+      <c r="G73" s="60" t="n"/>
+      <c r="H73" s="60" t="n"/>
+      <c r="I73" s="60" t="n"/>
+      <c r="J73" s="60" t="n"/>
+      <c r="K73" s="61" t="n"/>
+      <c r="L73" s="59" t="n"/>
+      <c r="M73" s="60" t="n"/>
+      <c r="N73" s="60" t="n"/>
+      <c r="O73" s="60" t="n"/>
+      <c r="P73" s="60" t="n"/>
+      <c r="Q73" s="60" t="n"/>
+      <c r="R73" s="61" t="n"/>
     </row>
     <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="57" t="n"/>
-      <c r="B74" s="58" t="n"/>
-      <c r="C74" s="58" t="n"/>
-      <c r="D74" s="59" t="n"/>
-      <c r="E74" s="57" t="n"/>
-      <c r="F74" s="58" t="n"/>
-      <c r="G74" s="58" t="n"/>
-      <c r="H74" s="58" t="n"/>
-      <c r="I74" s="58" t="n"/>
-      <c r="J74" s="58" t="n"/>
-      <c r="K74" s="59" t="n"/>
-      <c r="L74" s="57" t="n"/>
-      <c r="M74" s="58" t="n"/>
-      <c r="N74" s="58" t="n"/>
-      <c r="O74" s="58" t="n"/>
-      <c r="P74" s="58" t="n"/>
-      <c r="Q74" s="58" t="n"/>
-      <c r="R74" s="59" t="n"/>
+      <c r="A74" s="59" t="n"/>
+      <c r="B74" s="60" t="n"/>
+      <c r="C74" s="60" t="n"/>
+      <c r="D74" s="61" t="n"/>
+      <c r="E74" s="59" t="n"/>
+      <c r="F74" s="60" t="n"/>
+      <c r="G74" s="60" t="n"/>
+      <c r="H74" s="60" t="n"/>
+      <c r="I74" s="60" t="n"/>
+      <c r="J74" s="60" t="n"/>
+      <c r="K74" s="61" t="n"/>
+      <c r="L74" s="59" t="n"/>
+      <c r="M74" s="60" t="n"/>
+      <c r="N74" s="60" t="n"/>
+      <c r="O74" s="60" t="n"/>
+      <c r="P74" s="60" t="n"/>
+      <c r="Q74" s="60" t="n"/>
+      <c r="R74" s="61" t="n"/>
     </row>
     <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="60" t="n"/>
-      <c r="B75" s="33" t="n"/>
-      <c r="C75" s="33" t="n"/>
-      <c r="D75" s="61" t="n"/>
-      <c r="E75" s="60" t="n"/>
-      <c r="F75" s="33" t="n"/>
-      <c r="G75" s="33" t="n"/>
-      <c r="H75" s="33" t="n"/>
-      <c r="I75" s="33" t="n"/>
-      <c r="J75" s="33" t="n"/>
-      <c r="K75" s="61" t="n"/>
-      <c r="L75" s="60" t="n"/>
-      <c r="M75" s="33" t="n"/>
-      <c r="N75" s="33" t="n"/>
-      <c r="O75" s="33" t="n"/>
-      <c r="P75" s="33" t="n"/>
-      <c r="Q75" s="33" t="n"/>
-      <c r="R75" s="61" t="n"/>
+      <c r="A75" s="62" t="n"/>
+      <c r="B75" s="35" t="n"/>
+      <c r="C75" s="35" t="n"/>
+      <c r="D75" s="63" t="n"/>
+      <c r="E75" s="62" t="n"/>
+      <c r="F75" s="35" t="n"/>
+      <c r="G75" s="35" t="n"/>
+      <c r="H75" s="35" t="n"/>
+      <c r="I75" s="35" t="n"/>
+      <c r="J75" s="35" t="n"/>
+      <c r="K75" s="63" t="n"/>
+      <c r="L75" s="62" t="n"/>
+      <c r="M75" s="35" t="n"/>
+      <c r="N75" s="35" t="n"/>
+      <c r="O75" s="35" t="n"/>
+      <c r="P75" s="35" t="n"/>
+      <c r="Q75" s="35" t="n"/>
+      <c r="R75" s="63" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="57">
@@ -6947,11 +7165,341 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000A4FA0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:I44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="2" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="D1" s="90">
+        <f>"Réf. : "&amp;'1 Affaire'!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="D2" s="91">
+        <f>IF(Listes!$H$1=1,"Date : ","Date: ")&amp;IF('1 Affaire'!$C$7="","",TEXT('1 Affaire'!$C$7,"dd/mm/yyyy"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="D3" s="91">
+        <f>IF(Listes!$H$1=1,"Validité : ","Valid: ")&amp;'1 Affaire'!$F$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="D4" s="91">
+        <f>IF(Listes!$H$1=1,"Contact : ","Contact: ")&amp;'1 Affaire'!$F$6&amp;IF('1 Affaire'!$F$7="","","  ·  "&amp;'1 Affaire'!$F$7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1"/>
+    <row r="6" ht="30" customHeight="1"/>
+    <row r="7">
+      <c r="B7" s="92">
+        <f>UPPER(IF(Listes!$H$1=1,"Dossier commercial","Commercial folder"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="B8" s="93">
+        <f>UPPER(IF('1 Affaire'!$C$31="Commerciale",IF(Listes!$H$1=1,"Proposition commerciale","Commercial proposal"),IF(Listes!$H$1=1,"Proposition technique et commerciale","Technical and commercial proposal")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1"/>
+    <row r="10" ht="4" customHeight="1">
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="16" customHeight="1"/>
+    <row r="12" ht="20" customHeight="1">
+      <c r="B12" s="94" t="inlineStr">
+        <is>
+          <t>CLIENT</t>
+        </is>
+      </c>
+      <c r="C12" s="37" t="n"/>
+      <c r="D12" s="94" t="inlineStr">
+        <is>
+          <t>PROJET · PROJECT</t>
+        </is>
+      </c>
+      <c r="E12" s="37" t="n"/>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="B13" s="95">
+        <f>""&amp;'1 Affaire'!$C$8</f>
+        <v/>
+      </c>
+      <c r="C13" s="75" t="n"/>
+      <c r="D13" s="95">
+        <f>IF('1 Affaire'!$C$32&lt;&gt;"",'1 Affaire'!$C$32,'1 Affaire'!$C$10)</f>
+        <v/>
+      </c>
+      <c r="E13" s="75" t="n"/>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="B14" s="75" t="n"/>
+      <c r="C14" s="75" t="n"/>
+      <c r="D14" s="75" t="n"/>
+      <c r="E14" s="75" t="n"/>
+    </row>
+    <row r="15" ht="16" customHeight="1"/>
+    <row r="16" ht="20" customHeight="1">
+      <c r="B16" s="96">
+        <f>UPPER(IF(Listes!$H$1=1,"Résumé du projet","Project summary"))</f>
+        <v/>
+      </c>
+      <c r="C16" s="1" t="n"/>
+      <c r="D16" s="1" t="n"/>
+      <c r="E16" s="1" t="n"/>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="B17" s="97">
+        <f>UPPER(IF(Listes!$H$1=1,"Type de prestation","Service type"))</f>
+        <v/>
+      </c>
+      <c r="D17" s="97">
+        <f>UPPER(IF(Listes!$H$1=1,"Périmètre du contrat","Contract scope"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="98">
+        <f>""&amp;'1 Affaire'!$C$29</f>
+        <v/>
+      </c>
+      <c r="C18" s="35" t="n"/>
+      <c r="D18" s="98">
+        <f>""&amp;'1 Affaire'!$C$30</f>
+        <v/>
+      </c>
+      <c r="E18" s="35" t="n"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="B19" s="97">
+        <f>UPPER(IF(Listes!$H$1=1,"Lieu","Location"))</f>
+        <v/>
+      </c>
+      <c r="D19" s="97">
+        <f>UPPER(IF(Listes!$H$1=1,"Type de proposition","Proposal type"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="98">
+        <f>""&amp;'1 Affaire'!$C$10</f>
+        <v/>
+      </c>
+      <c r="C20" s="35" t="n"/>
+      <c r="D20" s="98">
+        <f>""&amp;'1 Affaire'!$C$31</f>
+        <v/>
+      </c>
+      <c r="E20" s="35" t="n"/>
+    </row>
+    <row r="21" ht="14" customHeight="1"/>
+    <row r="22" ht="20" customHeight="1">
+      <c r="B22" s="96">
+        <f>UPPER(IF(Listes!$H$1=1,"Contenu du dossier","Folder contents"))</f>
+        <v/>
+      </c>
+      <c r="C22" s="1" t="n"/>
+      <c r="D22" s="1" t="n"/>
+      <c r="E22" s="1" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="99">
+        <f>IFERROR("1     "&amp;INDEX($H$40:$H$44,MATCH(1,$I$40:$I$44,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C23" s="35" t="n"/>
+      <c r="D23" s="35" t="n"/>
+      <c r="E23" s="35" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="B24" s="99">
+        <f>IFERROR("2     "&amp;INDEX($H$40:$H$44,MATCH(2,$I$40:$I$44,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C24" s="35" t="n"/>
+      <c r="D24" s="35" t="n"/>
+      <c r="E24" s="35" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="B25" s="99">
+        <f>IFERROR("3     "&amp;INDEX($H$40:$H$44,MATCH(3,$I$40:$I$44,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C25" s="35" t="n"/>
+      <c r="D25" s="35" t="n"/>
+      <c r="E25" s="35" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="B26" s="99">
+        <f>IFERROR("4     "&amp;INDEX($H$40:$H$44,MATCH(4,$I$40:$I$44,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C26" s="35" t="n"/>
+      <c r="D26" s="35" t="n"/>
+      <c r="E26" s="35" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="B27" s="99">
+        <f>IFERROR("5     "&amp;INDEX($H$40:$H$44,MATCH(5,$I$40:$I$44,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C27" s="35" t="n"/>
+      <c r="D27" s="35" t="n"/>
+      <c r="E27" s="35" t="n"/>
+    </row>
+    <row r="28" ht="16" customHeight="1"/>
+    <row r="29" ht="26" customHeight="1">
+      <c r="B29" s="100">
+        <f>IF(Listes!$H$1=1,"Offre valable ","Offer valid for ")&amp;'1 Affaire'!$F$9&amp;"   ·   Incoterm "&amp;'1 Affaire'!$F$10</f>
+        <v/>
+      </c>
+      <c r="C29" s="101" t="n"/>
+      <c r="D29" s="101" t="n"/>
+      <c r="E29" s="101" t="n"/>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="B36" s="102" t="inlineStr">
+        <is>
+          <t>ENEDRIL · Z-Induspal · 3 Av. des Lacs · 64140 LONS (France) · SIRET 79464246200020 · TVA FR11794642462</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="G40" s="74">
+        <f>'1 Affaire'!$F$29</f>
+        <v/>
+      </c>
+      <c r="H40" s="74">
+        <f>IF(Listes!$H$1=1,"Présentation de l’entreprise","Company presentation")</f>
+        <v/>
+      </c>
+      <c r="I40" s="74">
+        <f>IF(G40="Oui",COUNTIF(G$40:G40,"Oui"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="G41" s="74">
+        <f>'1 Affaire'!$F$30</f>
+        <v/>
+      </c>
+      <c r="H41" s="74">
+        <f>IF(Listes!$H$1=1,"Nos engagements : politique QHSE et RSE","Our commitments: QHSE and CSR policy")</f>
+        <v/>
+      </c>
+      <c r="I41" s="74">
+        <f>IF(G41="Oui",COUNTIF(G$40:G41,"Oui"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="G42" s="74">
+        <f>'1 Affaire'!$F$31</f>
+        <v/>
+      </c>
+      <c r="H42" s="74">
+        <f>IF(Listes!$H$1=1,"Certificat ISO 9001","ISO 9001 certificate")</f>
+        <v/>
+      </c>
+      <c r="I42" s="74">
+        <f>IF(G42="Oui",COUNTIF(G$40:G42,"Oui"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="G43" s="74">
+        <f>'1 Affaire'!$F$32</f>
+        <v/>
+      </c>
+      <c r="H43" s="74">
+        <f>IF(Listes!$H$1=1,"Proposition technique","Technical proposal")</f>
+        <v/>
+      </c>
+      <c r="I43" s="74">
+        <f>IF(G43="Oui",COUNTIF(G$40:G43,"Oui"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="G44" s="74">
+        <f>"Oui"</f>
+        <v/>
+      </c>
+      <c r="H44" s="74">
+        <f>IF(Listes!$H$1=1,"Proposition commerciale (devis)","Commercial proposal (quotation)")</f>
+        <v/>
+      </c>
+      <c r="I44" s="74">
+        <f>IF(G44="Oui",COUNTIF(G$40:G44,"Oui"),"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="27">
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="B13:C14"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="B8:E9"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="D13:E14"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="009FB6CE"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:S12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6969,436 +7517,488 @@
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="30" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="88" t="inlineStr">
+      <c r="A1" s="103" t="inlineStr">
         <is>
           <t>Contact Enedril</t>
         </is>
       </c>
-      <c r="B1" s="88" t="inlineStr">
+      <c r="B1" s="103" t="inlineStr">
         <is>
           <t>E-mail</t>
         </is>
       </c>
-      <c r="D1" s="88" t="inlineStr">
+      <c r="D1" s="103" t="inlineStr">
         <is>
           <t>Incoterm</t>
         </is>
       </c>
-      <c r="E1" s="88" t="inlineStr">
+      <c r="E1" s="103" t="inlineStr">
         <is>
           <t>Validité</t>
         </is>
       </c>
-      <c r="F1" s="88" t="inlineStr">
+      <c r="F1" s="103" t="inlineStr">
         <is>
           <t>Règlement</t>
         </is>
       </c>
-      <c r="G1" s="88" t="inlineStr">
+      <c r="G1" s="103" t="inlineStr">
         <is>
           <t>Oui / Non</t>
         </is>
       </c>
-      <c r="H1" s="89">
+      <c r="H1" s="104">
         <f>IF('1 Affaire'!$F$14="EN",2,1)</f>
         <v/>
       </c>
-      <c r="I1" s="88" t="inlineStr">
+      <c r="I1" s="103" t="inlineStr">
         <is>
           <t>Poste opérateur</t>
         </is>
       </c>
-      <c r="J1" s="88" t="inlineStr">
+      <c r="J1" s="103" t="inlineStr">
         <is>
           <t>Support de colisage</t>
         </is>
       </c>
-      <c r="K1" s="88" t="inlineStr">
+      <c r="K1" s="103" t="inlineStr">
         <is>
           <t>N° de colis</t>
         </is>
       </c>
-      <c r="L1" s="88" t="inlineStr">
+      <c r="L1" s="103" t="inlineStr">
         <is>
           <t>Unité</t>
         </is>
       </c>
-      <c r="M1" s="88" t="inlineStr">
+      <c r="M1" s="103" t="inlineStr">
         <is>
           <t>Mode transport</t>
         </is>
       </c>
-      <c r="N1" s="88" t="inlineStr">
+      <c r="N1" s="103" t="inlineStr">
         <is>
           <t>Mode forfait</t>
         </is>
       </c>
-      <c r="O1" s="88" t="inlineStr">
+      <c r="O1" s="103" t="inlineStr">
         <is>
           <t>Langue</t>
         </is>
       </c>
-      <c r="P1" s="88" t="inlineStr">
+      <c r="P1" s="103" t="inlineStr">
         <is>
           <t>Statut</t>
         </is>
       </c>
-      <c r="Q1" s="88" t="inlineStr">
+      <c r="Q1" s="103" t="inlineStr">
         <is>
           <t>Test / Taille</t>
         </is>
       </c>
+      <c r="R1" s="103" t="inlineStr">
+        <is>
+          <t>Type de prestation</t>
+        </is>
+      </c>
+      <c r="S1" s="103" t="inlineStr">
+        <is>
+          <t>Type de proposition</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="90" t="inlineStr">
+      <c r="A2" s="105" t="inlineStr">
         <is>
           <t>Fabien JACQUOT</t>
         </is>
       </c>
-      <c r="B2" s="90" t="inlineStr">
+      <c r="B2" s="105" t="inlineStr">
         <is>
           <t>fjacquot@enedril.fr</t>
         </is>
       </c>
-      <c r="D2" s="90" t="inlineStr">
+      <c r="D2" s="105" t="inlineStr">
         <is>
           <t>EXW Lons</t>
         </is>
       </c>
-      <c r="E2" s="90" t="inlineStr">
+      <c r="E2" s="105" t="inlineStr">
         <is>
           <t>15 jours / 15 days</t>
         </is>
       </c>
-      <c r="F2" s="90" t="inlineStr">
+      <c r="F2" s="105" t="inlineStr">
         <is>
           <t>30 jours date de facture / 30 days invoice date</t>
         </is>
       </c>
-      <c r="G2" s="90" t="inlineStr">
+      <c r="G2" s="105" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="H2" s="91" t="inlineStr">
+      <c r="H2" s="106" t="inlineStr">
         <is>
           <t>← index de langue (1 = FR, 2 = EN), ne pas modifier</t>
         </is>
       </c>
-      <c r="I2" s="90" t="inlineStr">
+      <c r="I2" s="105" t="inlineStr">
         <is>
           <t>DD</t>
         </is>
       </c>
-      <c r="J2" s="90" t="inlineStr">
+      <c r="J2" s="105" t="inlineStr">
         <is>
           <t>Palette</t>
         </is>
       </c>
-      <c r="K2" s="90" t="inlineStr">
+      <c r="K2" s="105" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="L2" s="90" t="inlineStr">
+      <c r="L2" s="105" t="inlineStr">
         <is>
           <t>forfait</t>
         </is>
       </c>
-      <c r="M2" s="90" t="inlineStr">
+      <c r="M2" s="105" t="inlineStr">
         <is>
           <t>Coût réel +15 %</t>
         </is>
       </c>
-      <c r="N2" s="90" t="inlineStr">
+      <c r="N2" s="105" t="inlineStr">
+        <is>
+          <t>Forfait calculé (S + O + UC)</t>
+        </is>
+      </c>
+      <c r="O2" s="105" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="P2" s="105" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q2" s="105" t="inlineStr">
+        <is>
+          <t>Taille OK</t>
+        </is>
+      </c>
+      <c r="R2" s="105" t="inlineStr">
+        <is>
+          <t>Location d’outils de fishing</t>
+        </is>
+      </c>
+      <c r="S2" s="105" t="inlineStr">
+        <is>
+          <t>Technique et commerciale</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="105" t="inlineStr">
+        <is>
+          <t>Alexis ESTINES</t>
+        </is>
+      </c>
+      <c r="B3" s="105" t="inlineStr">
+        <is>
+          <t>aestines@enedril.fr</t>
+        </is>
+      </c>
+      <c r="D3" s="105" t="inlineStr">
+        <is>
+          <t>FCA Lons</t>
+        </is>
+      </c>
+      <c r="E3" s="105" t="inlineStr">
+        <is>
+          <t>30 jours / 30 days</t>
+        </is>
+      </c>
+      <c r="F3" s="105" t="inlineStr">
+        <is>
+          <t>30 jours fin de mois / 30 days end of month</t>
+        </is>
+      </c>
+      <c r="G3" s="105" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I3" s="105" t="inlineStr">
+        <is>
+          <t>MWD</t>
+        </is>
+      </c>
+      <c r="J3" s="105" t="inlineStr">
+        <is>
+          <t>Fishing basket</t>
+        </is>
+      </c>
+      <c r="K3" s="105" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L3" s="105" t="inlineStr">
+        <is>
+          <t>€/jour</t>
+        </is>
+      </c>
+      <c r="M3" s="105" t="inlineStr">
+        <is>
+          <t>Forfait</t>
+        </is>
+      </c>
+      <c r="N3" s="105" t="inlineStr">
         <is>
           <t>Forfait global</t>
         </is>
       </c>
-      <c r="O2" s="90" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="P2" s="90" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="Q2" s="90" t="inlineStr">
-        <is>
-          <t>Taille OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="90" t="inlineStr">
-        <is>
-          <t>Alexis ESTINES</t>
-        </is>
-      </c>
-      <c r="B3" s="90" t="inlineStr">
-        <is>
-          <t>aestines@enedril.fr</t>
-        </is>
-      </c>
-      <c r="D3" s="90" t="inlineStr">
-        <is>
-          <t>FCA Lons</t>
-        </is>
-      </c>
-      <c r="E3" s="90" t="inlineStr">
-        <is>
-          <t>30 jours / 30 days</t>
-        </is>
-      </c>
-      <c r="F3" s="90" t="inlineStr">
-        <is>
-          <t>30 jours fin de mois / 30 days end of month</t>
-        </is>
-      </c>
-      <c r="G3" s="90" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I3" s="90" t="inlineStr">
-        <is>
-          <t>MWD</t>
-        </is>
-      </c>
-      <c r="J3" s="90" t="inlineStr">
-        <is>
-          <t>Fishing basket</t>
-        </is>
-      </c>
-      <c r="K3" s="90" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="L3" s="90" t="inlineStr">
-        <is>
-          <t>€/jour</t>
-        </is>
-      </c>
-      <c r="M3" s="90" t="inlineStr">
-        <is>
-          <t>Forfait</t>
-        </is>
-      </c>
-      <c r="N3" s="90" t="inlineStr">
+      <c r="O3" s="105" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="P3" s="105" t="inlineStr">
+        <is>
+          <t>En cours</t>
+        </is>
+      </c>
+      <c r="Q3" s="105" t="inlineStr">
+        <is>
+          <t>Test OK</t>
+        </is>
+      </c>
+      <c r="R3" s="105" t="inlineStr">
+        <is>
+          <t>Forage dirigé et MWD</t>
+        </is>
+      </c>
+      <c r="S3" s="105" t="inlineStr">
+        <is>
+          <t>Commerciale</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="105" t="inlineStr">
+        <is>
+          <t>Paul HYNDERICK</t>
+        </is>
+      </c>
+      <c r="B4" s="105" t="inlineStr">
+        <is>
+          <t>phynderick@enedril.fr</t>
+        </is>
+      </c>
+      <c r="D4" s="105" t="inlineStr">
+        <is>
+          <t>DAP</t>
+        </is>
+      </c>
+      <c r="E4" s="105" t="inlineStr">
+        <is>
+          <t>60 jours / 60 days</t>
+        </is>
+      </c>
+      <c r="F4" s="105" t="inlineStr">
+        <is>
+          <t>45 jours fin de mois / 45 days end of month</t>
+        </is>
+      </c>
+      <c r="I4" s="105" t="inlineStr">
+        <is>
+          <t>Opérateur outils</t>
+        </is>
+      </c>
+      <c r="J4" s="105" t="inlineStr">
+        <is>
+          <t>Caisse</t>
+        </is>
+      </c>
+      <c r="K4" s="105" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L4" s="105" t="inlineStr">
+        <is>
+          <t>€/jour/pers</t>
+        </is>
+      </c>
+      <c r="N4" s="105" t="inlineStr">
         <is>
           <t>Forfait par jour</t>
         </is>
       </c>
-      <c r="O3" s="90" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="P3" s="90" t="inlineStr">
-        <is>
-          <t>En cours</t>
-        </is>
-      </c>
-      <c r="Q3" s="90" t="inlineStr">
-        <is>
-          <t>Test OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="90" t="inlineStr">
-        <is>
-          <t>Paul HYNDERICK</t>
-        </is>
-      </c>
-      <c r="B4" s="90" t="inlineStr">
-        <is>
-          <t>phynderick@enedril.fr</t>
-        </is>
-      </c>
-      <c r="D4" s="90" t="inlineStr">
-        <is>
-          <t>DAP</t>
-        </is>
-      </c>
-      <c r="E4" s="90" t="inlineStr">
-        <is>
-          <t>60 jours / 60 days</t>
-        </is>
-      </c>
-      <c r="F4" s="90" t="inlineStr">
-        <is>
-          <t>45 jours fin de mois / 45 days end of month</t>
-        </is>
-      </c>
-      <c r="I4" s="90" t="inlineStr">
-        <is>
-          <t>Opérateur outils</t>
-        </is>
-      </c>
-      <c r="J4" s="90" t="inlineStr">
-        <is>
-          <t>Caisse</t>
-        </is>
-      </c>
-      <c r="K4" s="90" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="L4" s="90" t="inlineStr">
-        <is>
-          <t>€/jour/pers</t>
-        </is>
-      </c>
-      <c r="Q4" s="90" t="inlineStr">
+      <c r="Q4" s="105" t="inlineStr">
         <is>
           <t>Taille + test OK</t>
         </is>
       </c>
+      <c r="R4" s="105" t="inlineStr">
+        <is>
+          <t>Workover</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="90" t="inlineStr">
+      <c r="A5" s="105" t="inlineStr">
         <is>
           <t>Céline CARDONA</t>
         </is>
       </c>
-      <c r="B5" s="90" t="inlineStr">
+      <c r="B5" s="105" t="inlineStr">
         <is>
           <t>ccardona@enedril.fr</t>
         </is>
       </c>
-      <c r="D5" s="90" t="inlineStr">
+      <c r="D5" s="105" t="inlineStr">
         <is>
           <t>DDP</t>
         </is>
       </c>
-      <c r="E5" s="90" t="inlineStr">
+      <c r="E5" s="105" t="inlineStr">
         <is>
           <t>90 jours / 90 days</t>
         </is>
       </c>
-      <c r="F5" s="90" t="inlineStr">
+      <c r="F5" s="105" t="inlineStr">
         <is>
           <t>À la commande / Upon order</t>
         </is>
       </c>
-      <c r="I5" s="90" t="inlineStr">
+      <c r="I5" s="105" t="inlineStr">
         <is>
           <t>Superviseur fishing</t>
         </is>
       </c>
-      <c r="J5" s="90" t="inlineStr">
+      <c r="J5" s="105" t="inlineStr">
         <is>
           <t>Loose (vrac)</t>
         </is>
       </c>
-      <c r="K5" s="90" t="inlineStr">
+      <c r="K5" s="105" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="L5" s="90" t="inlineStr">
+      <c r="L5" s="105" t="inlineStr">
         <is>
           <t>€/pers</t>
         </is>
       </c>
-      <c r="Q5" s="90" t="inlineStr">
+      <c r="Q5" s="105" t="inlineStr">
         <is>
           <t>À contrôler</t>
         </is>
       </c>
+      <c r="R5" s="105" t="inlineStr">
+        <is>
+          <t>Plug &amp; Abandonment</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="90" t="inlineStr">
+      <c r="A6" s="105" t="inlineStr">
         <is>
           <t>Koen MONDELAERS</t>
         </is>
       </c>
-      <c r="B6" s="90" t="inlineStr">
+      <c r="B6" s="105" t="inlineStr">
         <is>
           <t>kmondelaers@enedril.fr</t>
         </is>
       </c>
-      <c r="D6" s="90" t="inlineStr">
+      <c r="D6" s="105" t="inlineStr">
         <is>
           <t>FOB</t>
         </is>
       </c>
-      <c r="I6" s="90" t="inlineStr">
+      <c r="I6" s="105" t="inlineStr">
         <is>
           <t>Mécanicien</t>
         </is>
       </c>
-      <c r="K6" s="90" t="inlineStr">
+      <c r="K6" s="105" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="L6" s="90" t="inlineStr">
+      <c r="L6" s="105" t="inlineStr">
         <is>
           <t>€/unité</t>
         </is>
       </c>
+      <c r="R6" s="105" t="inlineStr">
+        <is>
+          <t>Fishing, workover et forage dirigé</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="90" t="inlineStr">
+      <c r="A7" s="105" t="inlineStr">
         <is>
           <t>Luigi LIBERATORE</t>
         </is>
       </c>
-      <c r="B7" s="90" t="inlineStr">
+      <c r="B7" s="105" t="inlineStr">
         <is>
           <t>lliberatore@enedril.fr</t>
         </is>
       </c>
-      <c r="K7" s="90" t="inlineStr">
+      <c r="K7" s="105" t="inlineStr">
         <is>
           <t>P6</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="K8" s="90" t="inlineStr">
+      <c r="K8" s="105" t="inlineStr">
         <is>
           <t>P7</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="K9" s="90" t="inlineStr">
+      <c r="K9" s="105" t="inlineStr">
         <is>
           <t>P8</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>Pour ajouter un contact, une validité, etc. : écrire à la suite dans la colonne (les listes déroulantes lisent les 12 premières lignes).</t>
         </is>
       </c>
-      <c r="K10" s="90" t="inlineStr">
+      <c r="K10" s="105" t="inlineStr">
         <is>
           <t>P9</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="K11" s="90" t="inlineStr">
+      <c r="K11" s="105" t="inlineStr">
         <is>
           <t>P10</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="K12" s="90" t="inlineStr">
+      <c r="K12" s="105" t="inlineStr">
         <is>
           <t>Loose</t>
         </is>
@@ -7410,7 +8010,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="009FB6CE"/>
@@ -7426,375 +8026,375 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="88" t="inlineStr">
+      <c r="A1" s="103" t="inlineStr">
         <is>
           <t>Clé</t>
         </is>
       </c>
-      <c r="B1" s="88" t="inlineStr">
+      <c r="B1" s="103" t="inlineStr">
         <is>
           <t>Français</t>
         </is>
       </c>
-      <c r="C1" s="88" t="inlineStr">
+      <c r="C1" s="103" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="92" t="inlineStr">
+      <c r="A2" s="107" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B2" s="92" t="inlineStr">
+      <c r="B2" s="107" t="inlineStr">
         <is>
           <t>OFFRE DE LOCATION</t>
         </is>
       </c>
-      <c r="C2" s="92" t="inlineStr">
+      <c r="C2" s="107" t="inlineStr">
         <is>
           <t>EQUIPMENT RENTAL QUOTATION</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="92" t="inlineStr">
+      <c r="A3" s="107" t="inlineStr">
         <is>
           <t>client</t>
         </is>
       </c>
-      <c r="B3" s="92" t="inlineStr">
+      <c r="B3" s="107" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="C3" s="92" t="inlineStr">
+      <c r="C3" s="107" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="92" t="inlineStr">
+      <c r="A4" s="107" t="inlineStr">
         <is>
           <t>attn</t>
         </is>
       </c>
-      <c r="B4" s="92" t="inlineStr">
+      <c r="B4" s="107" t="inlineStr">
         <is>
           <t>À l'attention de</t>
         </is>
       </c>
-      <c r="C4" s="92" t="inlineStr">
+      <c r="C4" s="107" t="inlineStr">
         <is>
           <t>Attention</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="92" t="inlineStr">
+      <c r="A5" s="107" t="inlineStr">
         <is>
           <t>well</t>
         </is>
       </c>
-      <c r="B5" s="92" t="inlineStr">
+      <c r="B5" s="107" t="inlineStr">
         <is>
           <t>Puits / Chantier</t>
         </is>
       </c>
-      <c r="C5" s="92" t="inlineStr">
+      <c r="C5" s="107" t="inlineStr">
         <is>
           <t>Well / Location</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="92" t="inlineStr">
+      <c r="A6" s="107" t="inlineStr">
         <is>
           <t>rigjob</t>
         </is>
       </c>
-      <c r="B6" s="92" t="inlineStr">
+      <c r="B6" s="107" t="inlineStr">
         <is>
           <t>Rig · Dossier</t>
         </is>
       </c>
-      <c r="C6" s="92" t="inlineStr">
+      <c r="C6" s="107" t="inlineStr">
         <is>
           <t>Rig · Job N°</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="92" t="inlineStr">
+      <c r="A7" s="107" t="inlineStr">
         <is>
           <t>po</t>
         </is>
       </c>
-      <c r="B7" s="92" t="inlineStr">
+      <c r="B7" s="107" t="inlineStr">
         <is>
           <t>PO client</t>
         </is>
       </c>
-      <c r="C7" s="92" t="inlineStr">
+      <c r="C7" s="107" t="inlineStr">
         <is>
           <t>Client PO</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="92" t="inlineStr">
+      <c r="A8" s="107" t="inlineStr">
         <is>
           <t>offer</t>
         </is>
       </c>
-      <c r="B8" s="92" t="inlineStr">
+      <c r="B8" s="107" t="inlineStr">
         <is>
           <t>N° d'offre</t>
         </is>
       </c>
-      <c r="C8" s="92" t="inlineStr">
+      <c r="C8" s="107" t="inlineStr">
         <is>
           <t>Offer N°</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="92" t="inlineStr">
+      <c r="A9" s="107" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B9" s="92" t="inlineStr">
+      <c r="B9" s="107" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C9" s="92" t="inlineStr">
+      <c r="C9" s="107" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="92" t="inlineStr">
+      <c r="A10" s="107" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="B10" s="92" t="inlineStr">
+      <c r="B10" s="107" t="inlineStr">
         <is>
           <t>Validité de l'offre</t>
         </is>
       </c>
-      <c r="C10" s="92" t="inlineStr">
+      <c r="C10" s="107" t="inlineStr">
         <is>
           <t>Validity</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="92" t="inlineStr">
+      <c r="A11" s="107" t="inlineStr">
         <is>
           <t>inco</t>
         </is>
       </c>
-      <c r="B11" s="92" t="inlineStr">
+      <c r="B11" s="107" t="inlineStr">
         <is>
           <t>Incoterm</t>
         </is>
       </c>
-      <c r="C11" s="92" t="inlineStr">
+      <c r="C11" s="107" t="inlineStr">
         <is>
           <t>Incoterm</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="92" t="inlineStr">
+      <c r="A12" s="107" t="inlineStr">
         <is>
           <t>lead</t>
         </is>
       </c>
-      <c r="B12" s="92" t="inlineStr">
+      <c r="B12" s="107" t="inlineStr">
         <is>
           <t>Délai de mise à dispo</t>
         </is>
       </c>
-      <c r="C12" s="92" t="inlineStr">
+      <c r="C12" s="107" t="inlineStr">
         <is>
           <t>Lead time</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="92" t="inlineStr">
+      <c r="A13" s="107" t="inlineStr">
         <is>
           <t>pay</t>
         </is>
       </c>
-      <c r="B13" s="92" t="inlineStr">
+      <c r="B13" s="107" t="inlineStr">
         <is>
           <t>Conditions de règlement</t>
         </is>
       </c>
-      <c r="C13" s="92" t="inlineStr">
+      <c r="C13" s="107" t="inlineStr">
         <is>
           <t>Payment terms</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="92" t="inlineStr">
+      <c r="A14" s="107" t="inlineStr">
         <is>
           <t>we</t>
         </is>
       </c>
-      <c r="B14" s="92" t="inlineStr">
+      <c r="B14" s="107" t="inlineStr">
         <is>
           <t>Facturation WE et jours fériés</t>
         </is>
       </c>
-      <c r="C14" s="92" t="inlineStr">
+      <c r="C14" s="107" t="inlineStr">
         <is>
           <t>Weekend &amp; holiday billing</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="92" t="inlineStr">
+      <c r="A15" s="107" t="inlineStr">
         <is>
           <t>by</t>
         </is>
       </c>
-      <c r="B15" s="92" t="inlineStr">
+      <c r="B15" s="107" t="inlineStr">
         <is>
           <t>Établi par</t>
         </is>
       </c>
-      <c r="C15" s="92" t="inlineStr">
+      <c r="C15" s="107" t="inlineStr">
         <is>
           <t>Established by</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="92" t="inlineStr">
+      <c r="A16" s="107" t="inlineStr">
         <is>
           <t>mail</t>
         </is>
       </c>
-      <c r="B16" s="92" t="inlineStr">
+      <c r="B16" s="107" t="inlineStr">
         <is>
           <t>E-mail</t>
         </is>
       </c>
-      <c r="C16" s="92" t="inlineStr">
+      <c r="C16" s="107" t="inlineStr">
         <is>
           <t>E-mail</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="92" t="inlineStr">
+      <c r="A17" s="107" t="inlineStr">
         <is>
           <t>tel</t>
         </is>
       </c>
-      <c r="B17" s="92" t="inlineStr">
+      <c r="B17" s="107" t="inlineStr">
         <is>
           <t>Téléphone</t>
         </is>
       </c>
-      <c r="C17" s="92" t="inlineStr">
+      <c r="C17" s="107" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="92" t="inlineStr">
+      <c r="A18" s="107" t="inlineStr">
         <is>
           <t>sec_eq</t>
         </is>
       </c>
-      <c r="B18" s="92" t="inlineStr">
+      <c r="B18" s="107" t="inlineStr">
         <is>
           <t>MATÉRIEL</t>
         </is>
       </c>
-      <c r="C18" s="92" t="inlineStr">
+      <c r="C18" s="107" t="inlineStr">
         <is>
           <t>EQUIPMENT</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="92" t="inlineStr">
+      <c r="A19" s="107" t="inlineStr">
         <is>
           <t>h_n</t>
         </is>
       </c>
-      <c r="B19" s="92" t="inlineStr">
+      <c r="B19" s="107" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C19" s="92" t="inlineStr">
+      <c r="C19" s="107" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="92" t="inlineStr">
+      <c r="A20" s="107" t="inlineStr">
         <is>
           <t>h_desc</t>
         </is>
       </c>
-      <c r="B20" s="92" t="inlineStr">
+      <c r="B20" s="107" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C20" s="92" t="inlineStr">
+      <c r="C20" s="107" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="92" t="inlineStr">
+      <c r="A21" s="107" t="inlineStr">
         <is>
           <t>h_qty</t>
         </is>
       </c>
-      <c r="B21" s="92" t="inlineStr">
+      <c r="B21" s="107" t="inlineStr">
         <is>
           <t>Qté</t>
         </is>
       </c>
-      <c r="C21" s="92" t="inlineStr">
+      <c r="C21" s="107" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="92" t="inlineStr">
+      <c r="A22" s="107" t="inlineStr">
         <is>
           <t>h_s</t>
         </is>
       </c>
-      <c r="B22" s="92" t="inlineStr">
+      <c r="B22" s="107" t="inlineStr">
         <is>
           <t>Stand-by (S)
 € / jour / item</t>
         </is>
       </c>
-      <c r="C22" s="92" t="inlineStr">
+      <c r="C22" s="107" t="inlineStr">
         <is>
           <t>Stand-by (S)
 daily rate / item</t>
@@ -7802,18 +8402,18 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="92" t="inlineStr">
+      <c r="A23" s="107" t="inlineStr">
         <is>
           <t>h_o</t>
         </is>
       </c>
-      <c r="B23" s="92" t="inlineStr">
+      <c r="B23" s="107" t="inlineStr">
         <is>
           <t>Opérations (O)
 € / jour / item</t>
         </is>
       </c>
-      <c r="C23" s="92" t="inlineStr">
+      <c r="C23" s="107" t="inlineStr">
         <is>
           <t>Operations (O)
 daily rate / item</t>
@@ -7821,19 +8421,19 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="92" t="inlineStr">
+      <c r="A24" s="107" t="inlineStr">
         <is>
           <t>h_uc</t>
         </is>
       </c>
-      <c r="B24" s="92" t="inlineStr">
+      <c r="B24" s="107" t="inlineStr">
         <is>
           <t>Utilisation
 Charge (UC)
 € / item</t>
         </is>
       </c>
-      <c r="C24" s="92" t="inlineStr">
+      <c r="C24" s="107" t="inlineStr">
         <is>
           <t>Utilisation
 Charge (UC)
@@ -7842,18 +8442,18 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="92" t="inlineStr">
+      <c r="A25" s="107" t="inlineStr">
         <is>
           <t>h_lih</t>
         </is>
       </c>
-      <c r="B25" s="92" t="inlineStr">
+      <c r="B25" s="107" t="inlineStr">
         <is>
           <t>Valeur de remplacement
 (LIH / DBR) € / item</t>
         </is>
       </c>
-      <c r="C25" s="92" t="inlineStr">
+      <c r="C25" s="107" t="inlineStr">
         <is>
           <t>Replacement value
 (LIH / DBR) per item</t>
@@ -7861,18 +8461,18 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="92" t="inlineStr">
+      <c r="A26" s="107" t="inlineStr">
         <is>
           <t>h_insp</t>
         </is>
       </c>
-      <c r="B26" s="92" t="inlineStr">
+      <c r="B26" s="107" t="inlineStr">
         <is>
           <t>Inspection
 € / item</t>
         </is>
       </c>
-      <c r="C26" s="92" t="inlineStr">
+      <c r="C26" s="107" t="inlineStr">
         <is>
           <t>Inspection
 per item</t>
@@ -7880,18 +8480,18 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="92" t="inlineStr">
+      <c r="A27" s="107" t="inlineStr">
         <is>
           <t>h_rest</t>
         </is>
       </c>
-      <c r="B27" s="92" t="inlineStr">
+      <c r="B27" s="107" t="inlineStr">
         <is>
           <t>Restocking
 €</t>
         </is>
       </c>
-      <c r="C27" s="92" t="inlineStr">
+      <c r="C27" s="107" t="inlineStr">
         <is>
           <t>Restocking
 charge</t>
@@ -7899,459 +8499,459 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="92" t="inlineStr">
+      <c r="A28" s="107" t="inlineStr">
         <is>
           <t>h_ref</t>
         </is>
       </c>
-      <c r="B28" s="92" t="inlineStr">
-        <is>
-          <t>Réf PL / instructions</t>
-        </is>
-      </c>
-      <c r="C28" s="92" t="inlineStr">
-        <is>
-          <t>PL ref / instructions</t>
+      <c r="B28" s="107" t="inlineStr">
+        <is>
+          <t>Remarques</t>
+        </is>
+      </c>
+      <c r="C28" s="107" t="inlineStr">
+        <is>
+          <t>Remarks</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="92" t="inlineStr">
+      <c r="A29" s="107" t="inlineStr">
         <is>
           <t>incl</t>
         </is>
       </c>
-      <c r="B29" s="92" t="inlineStr">
+      <c r="B29" s="107" t="inlineStr">
         <is>
           <t>incl.</t>
         </is>
       </c>
-      <c r="C29" s="92" t="inlineStr">
+      <c r="C29" s="107" t="inlineStr">
         <is>
           <t>incl.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="92" t="inlineStr">
+      <c r="A30" s="107" t="inlineStr">
         <is>
           <t>incl_long</t>
         </is>
       </c>
-      <c r="B30" s="92" t="inlineStr">
+      <c r="B30" s="107" t="inlineStr">
         <is>
           <t>Inclus au forfait</t>
         </is>
       </c>
-      <c r="C30" s="92" t="inlineStr">
+      <c r="C30" s="107" t="inlineStr">
         <is>
           <t>Included in lump sum</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="92" t="inlineStr">
+      <c r="A31" s="107" t="inlineStr">
         <is>
           <t>sec_opt</t>
         </is>
       </c>
-      <c r="B31" s="92" t="inlineStr">
+      <c r="B31" s="107" t="inlineStr">
         <is>
           <t>PRESTATIONS ET OPTIONS</t>
         </is>
       </c>
-      <c r="C31" s="92" t="inlineStr">
+      <c r="C31" s="107" t="inlineStr">
         <is>
           <t>SERVICES AND OPTIONS</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="92" t="inlineStr">
+      <c r="A32" s="107" t="inlineStr">
         <is>
           <t>h_label</t>
         </is>
       </c>
-      <c r="B32" s="92" t="inlineStr">
+      <c r="B32" s="107" t="inlineStr">
         <is>
           <t>Prestation</t>
         </is>
       </c>
-      <c r="C32" s="92" t="inlineStr">
+      <c r="C32" s="107" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="92" t="inlineStr">
+      <c r="A33" s="107" t="inlineStr">
         <is>
           <t>h_unit</t>
         </is>
       </c>
-      <c r="B33" s="92" t="inlineStr">
+      <c r="B33" s="107" t="inlineStr">
         <is>
           <t>Unité</t>
         </is>
       </c>
-      <c r="C33" s="92" t="inlineStr">
+      <c r="C33" s="107" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="92" t="inlineStr">
+      <c r="A34" s="107" t="inlineStr">
         <is>
           <t>h_pu</t>
         </is>
       </c>
-      <c r="B34" s="92" t="inlineStr">
+      <c r="B34" s="107" t="inlineStr">
         <is>
           <t>Prix unitaire €</t>
         </is>
       </c>
-      <c r="C34" s="92" t="inlineStr">
+      <c r="C34" s="107" t="inlineStr">
         <is>
           <t>Unit price €</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="92" t="inlineStr">
+      <c r="A35" s="107" t="inlineStr">
         <is>
           <t>h_tot</t>
         </is>
       </c>
-      <c r="B35" s="92" t="inlineStr">
+      <c r="B35" s="107" t="inlineStr">
         <is>
           <t>Total €</t>
         </is>
       </c>
-      <c r="C35" s="92" t="inlineStr">
+      <c r="C35" s="107" t="inlineStr">
         <is>
           <t>Total €</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="92" t="inlineStr">
+      <c r="A36" s="107" t="inlineStr">
         <is>
           <t>h_det</t>
         </is>
       </c>
-      <c r="B36" s="92" t="inlineStr">
+      <c r="B36" s="107" t="inlineStr">
         <is>
           <t>Détail</t>
         </is>
       </c>
-      <c r="C36" s="92" t="inlineStr">
+      <c r="C36" s="107" t="inlineStr">
         <is>
           <t>Details</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="92" t="inlineStr">
+      <c r="A37" s="107" t="inlineStr">
         <is>
           <t>op_day</t>
         </is>
       </c>
-      <c r="B37" s="92" t="inlineStr">
+      <c r="B37" s="107" t="inlineStr">
         <is>
           <t>Opérateur · tarif journalier</t>
         </is>
       </c>
-      <c r="C37" s="92" t="inlineStr">
+      <c r="C37" s="107" t="inlineStr">
         <is>
           <t>Operator · daily rate</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="92" t="inlineStr">
+      <c r="A38" s="107" t="inlineStr">
         <is>
           <t>op_mob</t>
         </is>
       </c>
-      <c r="B38" s="92" t="inlineStr">
+      <c r="B38" s="107" t="inlineStr">
         <is>
           <t>Opérateur · Mob / Demob</t>
         </is>
       </c>
-      <c r="C38" s="92" t="inlineStr">
+      <c r="C38" s="107" t="inlineStr">
         <is>
           <t>Operator · Mob / Demob</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="92" t="inlineStr">
+      <c r="A39" s="107" t="inlineStr">
         <is>
           <t>tight</t>
         </is>
       </c>
-      <c r="B39" s="92" t="inlineStr">
+      <c r="B39" s="107" t="inlineStr">
         <is>
           <t>Serrage · Make-up (forfait)</t>
         </is>
       </c>
-      <c r="C39" s="92" t="inlineStr">
+      <c r="C39" s="107" t="inlineStr">
         <is>
           <t>Tong &amp; make-up service (lump sum)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="92" t="inlineStr">
+      <c r="A40" s="107" t="inlineStr">
         <is>
           <t>tr_mob</t>
         </is>
       </c>
-      <c r="B40" s="92" t="inlineStr">
+      <c r="B40" s="107" t="inlineStr">
         <is>
           <t>Transport MOB (Lons → chantier)</t>
         </is>
       </c>
-      <c r="C40" s="92" t="inlineStr">
+      <c r="C40" s="107" t="inlineStr">
         <is>
           <t>Transport MOB (Lons → site)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="92" t="inlineStr">
+      <c r="A41" s="107" t="inlineStr">
         <is>
           <t>tr_dem</t>
         </is>
       </c>
-      <c r="B41" s="92" t="inlineStr">
+      <c r="B41" s="107" t="inlineStr">
         <is>
           <t>Transport DEMOB (chantier → Lons)</t>
         </is>
       </c>
-      <c r="C41" s="92" t="inlineStr">
+      <c r="C41" s="107" t="inlineStr">
         <is>
           <t>Transport DEMOB (site → Lons)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="92" t="inlineStr">
+      <c r="A42" s="107" t="inlineStr">
         <is>
           <t>free</t>
         </is>
       </c>
-      <c r="B42" s="92" t="inlineStr">
+      <c r="B42" s="107" t="inlineStr">
         <is>
           <t>Option</t>
         </is>
       </c>
-      <c r="C42" s="92" t="inlineStr">
+      <c r="C42" s="107" t="inlineStr">
         <is>
           <t>Option</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="92" t="inlineStr">
+      <c r="A43" s="107" t="inlineStr">
         <is>
           <t>forfait</t>
         </is>
       </c>
-      <c r="B43" s="92" t="inlineStr">
+      <c r="B43" s="107" t="inlineStr">
         <is>
           <t>Forfait</t>
         </is>
       </c>
-      <c r="C43" s="92" t="inlineStr">
+      <c r="C43" s="107" t="inlineStr">
         <is>
           <t>Lump sum</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="92" t="inlineStr">
+      <c r="A44" s="107" t="inlineStr">
         <is>
           <t>at_cost</t>
         </is>
       </c>
-      <c r="B44" s="92" t="inlineStr">
+      <c r="B44" s="107" t="inlineStr">
         <is>
           <t>au coût réel +15 %</t>
         </is>
       </c>
-      <c r="C44" s="92" t="inlineStr">
+      <c r="C44" s="107" t="inlineStr">
         <is>
           <t>at cost +15%</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="92" t="inlineStr">
+      <c r="A45" s="107" t="inlineStr">
         <is>
           <t>tr_note</t>
         </is>
       </c>
-      <c r="B45" s="92" t="inlineStr">
+      <c r="B45" s="107" t="inlineStr">
         <is>
           <t>Transport organisé par Enedril</t>
         </is>
       </c>
-      <c r="C45" s="92" t="inlineStr">
+      <c r="C45" s="107" t="inlineStr">
         <is>
           <t>Transport organised by Enedril</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="92" t="inlineStr">
+      <c r="A46" s="107" t="inlineStr">
         <is>
           <t>est</t>
         </is>
       </c>
-      <c r="B46" s="92" t="inlineStr">
+      <c r="B46" s="107" t="inlineStr">
         <is>
           <t>ESTIMATION BUDGÉTAIRE HT (indicative)</t>
         </is>
       </c>
-      <c r="C46" s="92" t="inlineStr">
+      <c r="C46" s="107" t="inlineStr">
         <is>
           <t>BUDGET ESTIMATE EXCL. VAT (indicative)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="92" t="inlineStr">
+      <c r="A47" s="107" t="inlineStr">
         <is>
           <t>est_note</t>
         </is>
       </c>
-      <c r="B47" s="92" t="inlineStr">
+      <c r="B47" s="107" t="inlineStr">
         <is>
           <t>Basée sur %s j de stand-by et %s j d'opérations. Hors valeur de remplacement, inspection, restocking et transport au coût réel.</t>
         </is>
       </c>
-      <c r="C47" s="92" t="inlineStr">
+      <c r="C47" s="107" t="inlineStr">
         <is>
           <t>Based on %s stand-by days and %s operation days. Excluding replacement value, inspection, restocking and transport at cost.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="92" t="inlineStr">
+      <c r="A48" s="107" t="inlineStr">
         <is>
           <t>sec_cond</t>
         </is>
       </c>
-      <c r="B48" s="92" t="inlineStr">
+      <c r="B48" s="107" t="inlineStr">
         <is>
           <t>CONDITIONS PARTICULIÈRES · SPECIFIC CONDITIONS</t>
         </is>
       </c>
-      <c r="C48" s="92" t="inlineStr">
+      <c r="C48" s="107" t="inlineStr">
         <is>
           <t>SPECIFIC CONDITIONS · CONDITIONS PARTICULIÈRES</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="92" t="inlineStr">
+      <c r="A49" s="107" t="inlineStr">
         <is>
           <t>accept</t>
         </is>
       </c>
-      <c r="B49" s="92" t="inlineStr">
+      <c r="B49" s="107" t="inlineStr">
         <is>
           <t>BON POUR ACCORD</t>
         </is>
       </c>
-      <c r="C49" s="92" t="inlineStr">
+      <c r="C49" s="107" t="inlineStr">
         <is>
           <t>ACCEPTED BY</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="92" t="inlineStr">
+      <c r="A50" s="107" t="inlineStr">
         <is>
           <t>sig_name</t>
         </is>
       </c>
-      <c r="B50" s="92" t="inlineStr">
+      <c r="B50" s="107" t="inlineStr">
         <is>
           <t>Nom et qualité</t>
         </is>
       </c>
-      <c r="C50" s="92" t="inlineStr">
+      <c r="C50" s="107" t="inlineStr">
         <is>
           <t>Name and title</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="92" t="inlineStr">
+      <c r="A51" s="107" t="inlineStr">
         <is>
           <t>sig_date</t>
         </is>
       </c>
-      <c r="B51" s="92" t="inlineStr">
+      <c r="B51" s="107" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C51" s="92" t="inlineStr">
+      <c r="C51" s="107" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="92" t="inlineStr">
+      <c r="A52" s="107" t="inlineStr">
         <is>
           <t>sig_sig</t>
         </is>
       </c>
-      <c r="B52" s="92" t="inlineStr">
+      <c r="B52" s="107" t="inlineStr">
         <is>
           <t>Signature et cachet</t>
         </is>
       </c>
-      <c r="C52" s="92" t="inlineStr">
+      <c r="C52" s="107" t="inlineStr">
         <is>
           <t>Signature and stamp</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="92" t="inlineStr">
+      <c r="A53" s="107" t="inlineStr">
         <is>
           <t>per_day</t>
         </is>
       </c>
-      <c r="B53" s="92" t="inlineStr">
+      <c r="B53" s="107" t="inlineStr">
         <is>
           <t>€/jour</t>
         </is>
       </c>
-      <c r="C53" s="92" t="inlineStr">
+      <c r="C53" s="107" t="inlineStr">
         <is>
           <t>€/day</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="92" t="inlineStr">
+      <c r="A54" s="107" t="inlineStr">
         <is>
           <t>lump</t>
         </is>
       </c>
-      <c r="B54" s="92" t="inlineStr">
+      <c r="B54" s="107" t="inlineStr">
         <is>
           <t>forfait</t>
         </is>
       </c>
-      <c r="C54" s="92" t="inlineStr">
+      <c r="C54" s="107" t="inlineStr">
         <is>
           <t>lump sum</t>
         </is>

--- a/devis_2027/Devis_Enedril_2027.xlsx
+++ b/devis_2027/Devis_Enedril_2027.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Textes" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'4 Devis'!$A$1:$L$68</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'4 Devis'!$A$1:$L$66</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -175,20 +175,8 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="000A4FA0"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="0008203F"/>
-      <sz val="19"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="000A4FA0"/>
-      <sz val="24"/>
+      <color rgb="000B1B2E"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -198,7 +186,19 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="000B1B2E"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="0008203F"/>
       <sz val="10"/>
     </font>
     <font>
@@ -289,7 +289,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border/>
     <border>
       <left style="thin">
         <color rgb="00D5DEE8"/>
@@ -316,6 +315,7 @@
         <color rgb="00D5DEE8"/>
       </left>
     </border>
+    <border/>
     <border>
       <right style="thin">
         <color rgb="00D5DEE8"/>
@@ -341,7 +341,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -449,35 +449,28 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom" indent="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="167" fontId="27" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -486,9 +479,10 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -509,7 +503,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="8">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -561,17 +555,26 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="000A4FA0"/>
+          <bgColor rgb="000A4FA0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="0008203F"/>
+          <bgColor rgb="0008203F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="00EAF6FD"/>
           <bgColor rgb="00EAF6FD"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thick">
-          <color rgb="0000AEEF"/>
-        </left>
-      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1113,12 +1116,6 @@
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Rig</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="n"/>
       <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Délai de mise à dispo</t>
@@ -1191,24 +1188,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1230,7 +1226,6 @@
       <c r="L1" s="1" t="n"/>
       <c r="M1" s="1" t="n"/>
       <c r="N1" s="1" t="n"/>
-      <c r="O1" s="1" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="1" t="n"/>
@@ -1251,7 +1246,6 @@
       <c r="L2" s="1" t="n"/>
       <c r="M2" s="1" t="n"/>
       <c r="N2" s="1" t="n"/>
-      <c r="O2" s="1" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1">
       <c r="A3" s="4" t="n"/>
@@ -1268,7 +1262,6 @@
       <c r="L3" s="4" t="n"/>
       <c r="M3" s="4" t="n"/>
       <c r="N3" s="4" t="n"/>
-      <c r="O3" s="4" t="n"/>
     </row>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
@@ -1293,63 +1286,58 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Note pour la tool list</t>
-        </is>
-      </c>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
           <t>Stand-by (S)
 € / jour</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>Opérations (O)
 € / jour</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>UC
 € / item</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="H5" s="11" t="inlineStr">
         <is>
           <t>LIH / DBR
 € / item</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="I5" s="11" t="inlineStr">
         <is>
           <t>Inspection
 € / item</t>
         </is>
       </c>
-      <c r="K5" s="11" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr">
         <is>
           <t>Restocking
 €</t>
         </is>
       </c>
-      <c r="L5" s="11" t="inlineStr">
+      <c r="K5" s="11" t="inlineStr">
         <is>
           <t>Inclus au
 forfait ?</t>
         </is>
       </c>
-      <c r="M5" s="12" t="inlineStr">
+      <c r="L5" s="12" t="inlineStr">
         <is>
           <t>Lignes
 tool list</t>
         </is>
       </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>Cumul</t>
+        </is>
+      </c>
       <c r="N5" s="12" t="inlineStr">
-        <is>
-          <t>Cumul</t>
-        </is>
-      </c>
-      <c r="O5" s="12" t="inlineStr">
         <is>
           <t>Forfait
 € (calc.)</t>
@@ -1358,728 +1346,704 @@
     </row>
     <row r="6" ht="21" customHeight="1">
       <c r="A6" s="13">
-        <f>IF(AND(M6&gt;0,B6&lt;&gt;"Oui"),COUNTIFS(M$6:M6,"&gt;0",B$6:B6,"&lt;&gt;Oui"),"")</f>
+        <f>IF(AND(L6&gt;0,B6&lt;&gt;"Oui"),COUNTIFS(L$6:L6,"&gt;0",B$6:B6,"&lt;&gt;Oui"),"")</f>
         <v/>
       </c>
       <c r="B6" s="14" t="n"/>
       <c r="C6" s="7" t="n"/>
       <c r="D6" s="15" t="n"/>
-      <c r="E6" s="7" t="n"/>
+      <c r="E6" s="16" t="n"/>
       <c r="F6" s="16" t="n"/>
       <c r="G6" s="16" t="n"/>
       <c r="H6" s="16" t="n"/>
       <c r="I6" s="16" t="n"/>
       <c r="J6" s="16" t="n"/>
-      <c r="K6" s="16" t="n"/>
-      <c r="L6" s="14" t="n"/>
-      <c r="M6" s="17">
+      <c r="K6" s="14" t="n"/>
+      <c r="L6" s="17">
         <f>IF($C6="",0,IF($B6="Oui",1,IF(N($D6)&gt;0,INT($D6),1)))</f>
         <v/>
       </c>
-      <c r="N6" s="18">
-        <f>SUM(M$6:M6)</f>
-        <v/>
-      </c>
-      <c r="O6" s="19">
-        <f>IF(AND(M6&gt;0,B6&lt;&gt;"Oui",L6="Oui"),M6*(N(F6)*N('3 Options'!$C$18)+N(G6)*N('3 Options'!$C$19)+N(H6)),0)</f>
+      <c r="M6" s="18">
+        <f>SUM(L$6:L6)</f>
+        <v/>
+      </c>
+      <c r="N6" s="19">
+        <f>IF(AND(L6&gt;0,B6&lt;&gt;"Oui",K6="Oui"),L6*(N(E6)*N('3 Options'!$C$15)+N(F6)*N('3 Options'!$C$16)+N(G6)),0)</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="21" customHeight="1">
       <c r="A7" s="13">
-        <f>IF(AND(M7&gt;0,B7&lt;&gt;"Oui"),COUNTIFS(M$6:M7,"&gt;0",B$6:B7,"&lt;&gt;Oui"),"")</f>
+        <f>IF(AND(L7&gt;0,B7&lt;&gt;"Oui"),COUNTIFS(L$6:L7,"&gt;0",B$6:B7,"&lt;&gt;Oui"),"")</f>
         <v/>
       </c>
       <c r="B7" s="14" t="n"/>
       <c r="C7" s="7" t="n"/>
       <c r="D7" s="15" t="n"/>
-      <c r="E7" s="7" t="n"/>
+      <c r="E7" s="16" t="n"/>
       <c r="F7" s="16" t="n"/>
       <c r="G7" s="16" t="n"/>
       <c r="H7" s="16" t="n"/>
       <c r="I7" s="16" t="n"/>
       <c r="J7" s="16" t="n"/>
-      <c r="K7" s="16" t="n"/>
-      <c r="L7" s="14" t="n"/>
-      <c r="M7" s="17">
+      <c r="K7" s="14" t="n"/>
+      <c r="L7" s="17">
         <f>IF($C7="",0,IF($B7="Oui",1,IF(N($D7)&gt;0,INT($D7),1)))</f>
         <v/>
       </c>
-      <c r="N7" s="18">
-        <f>SUM(M$6:M7)</f>
-        <v/>
-      </c>
-      <c r="O7" s="19">
-        <f>IF(AND(M7&gt;0,B7&lt;&gt;"Oui",L7="Oui"),M7*(N(F7)*N('3 Options'!$C$18)+N(G7)*N('3 Options'!$C$19)+N(H7)),0)</f>
+      <c r="M7" s="18">
+        <f>SUM(L$6:L7)</f>
+        <v/>
+      </c>
+      <c r="N7" s="19">
+        <f>IF(AND(L7&gt;0,B7&lt;&gt;"Oui",K7="Oui"),L7*(N(E7)*N('3 Options'!$C$15)+N(F7)*N('3 Options'!$C$16)+N(G7)),0)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="21" customHeight="1">
       <c r="A8" s="13">
-        <f>IF(AND(M8&gt;0,B8&lt;&gt;"Oui"),COUNTIFS(M$6:M8,"&gt;0",B$6:B8,"&lt;&gt;Oui"),"")</f>
+        <f>IF(AND(L8&gt;0,B8&lt;&gt;"Oui"),COUNTIFS(L$6:L8,"&gt;0",B$6:B8,"&lt;&gt;Oui"),"")</f>
         <v/>
       </c>
       <c r="B8" s="14" t="n"/>
       <c r="C8" s="7" t="n"/>
       <c r="D8" s="15" t="n"/>
-      <c r="E8" s="7" t="n"/>
+      <c r="E8" s="16" t="n"/>
       <c r="F8" s="16" t="n"/>
       <c r="G8" s="16" t="n"/>
       <c r="H8" s="16" t="n"/>
       <c r="I8" s="16" t="n"/>
       <c r="J8" s="16" t="n"/>
-      <c r="K8" s="16" t="n"/>
-      <c r="L8" s="14" t="n"/>
-      <c r="M8" s="17">
+      <c r="K8" s="14" t="n"/>
+      <c r="L8" s="17">
         <f>IF($C8="",0,IF($B8="Oui",1,IF(N($D8)&gt;0,INT($D8),1)))</f>
         <v/>
       </c>
-      <c r="N8" s="18">
-        <f>SUM(M$6:M8)</f>
-        <v/>
-      </c>
-      <c r="O8" s="19">
-        <f>IF(AND(M8&gt;0,B8&lt;&gt;"Oui",L8="Oui"),M8*(N(F8)*N('3 Options'!$C$18)+N(G8)*N('3 Options'!$C$19)+N(H8)),0)</f>
+      <c r="M8" s="18">
+        <f>SUM(L$6:L8)</f>
+        <v/>
+      </c>
+      <c r="N8" s="19">
+        <f>IF(AND(L8&gt;0,B8&lt;&gt;"Oui",K8="Oui"),L8*(N(E8)*N('3 Options'!$C$15)+N(F8)*N('3 Options'!$C$16)+N(G8)),0)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="21" customHeight="1">
       <c r="A9" s="13">
-        <f>IF(AND(M9&gt;0,B9&lt;&gt;"Oui"),COUNTIFS(M$6:M9,"&gt;0",B$6:B9,"&lt;&gt;Oui"),"")</f>
+        <f>IF(AND(L9&gt;0,B9&lt;&gt;"Oui"),COUNTIFS(L$6:L9,"&gt;0",B$6:B9,"&lt;&gt;Oui"),"")</f>
         <v/>
       </c>
       <c r="B9" s="14" t="n"/>
       <c r="C9" s="7" t="n"/>
       <c r="D9" s="15" t="n"/>
-      <c r="E9" s="7" t="n"/>
+      <c r="E9" s="16" t="n"/>
       <c r="F9" s="16" t="n"/>
       <c r="G9" s="16" t="n"/>
       <c r="H9" s="16" t="n"/>
       <c r="I9" s="16" t="n"/>
       <c r="J9" s="16" t="n"/>
-      <c r="K9" s="16" t="n"/>
-      <c r="L9" s="14" t="n"/>
-      <c r="M9" s="17">
+      <c r="K9" s="14" t="n"/>
+      <c r="L9" s="17">
         <f>IF($C9="",0,IF($B9="Oui",1,IF(N($D9)&gt;0,INT($D9),1)))</f>
         <v/>
       </c>
-      <c r="N9" s="18">
-        <f>SUM(M$6:M9)</f>
-        <v/>
-      </c>
-      <c r="O9" s="19">
-        <f>IF(AND(M9&gt;0,B9&lt;&gt;"Oui",L9="Oui"),M9*(N(F9)*N('3 Options'!$C$18)+N(G9)*N('3 Options'!$C$19)+N(H9)),0)</f>
+      <c r="M9" s="18">
+        <f>SUM(L$6:L9)</f>
+        <v/>
+      </c>
+      <c r="N9" s="19">
+        <f>IF(AND(L9&gt;0,B9&lt;&gt;"Oui",K9="Oui"),L9*(N(E9)*N('3 Options'!$C$15)+N(F9)*N('3 Options'!$C$16)+N(G9)),0)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="21" customHeight="1">
       <c r="A10" s="13">
-        <f>IF(AND(M10&gt;0,B10&lt;&gt;"Oui"),COUNTIFS(M$6:M10,"&gt;0",B$6:B10,"&lt;&gt;Oui"),"")</f>
+        <f>IF(AND(L10&gt;0,B10&lt;&gt;"Oui"),COUNTIFS(L$6:L10,"&gt;0",B$6:B10,"&lt;&gt;Oui"),"")</f>
         <v/>
       </c>
       <c r="B10" s="14" t="n"/>
       <c r="C10" s="7" t="n"/>
       <c r="D10" s="15" t="n"/>
-      <c r="E10" s="7" t="n"/>
+      <c r="E10" s="16" t="n"/>
       <c r="F10" s="16" t="n"/>
       <c r="G10" s="16" t="n"/>
       <c r="H10" s="16" t="n"/>
       <c r="I10" s="16" t="n"/>
       <c r="J10" s="16" t="n"/>
-      <c r="K10" s="16" t="n"/>
-      <c r="L10" s="14" t="n"/>
-      <c r="M10" s="17">
+      <c r="K10" s="14" t="n"/>
+      <c r="L10" s="17">
         <f>IF($C10="",0,IF($B10="Oui",1,IF(N($D10)&gt;0,INT($D10),1)))</f>
         <v/>
       </c>
-      <c r="N10" s="18">
-        <f>SUM(M$6:M10)</f>
-        <v/>
-      </c>
-      <c r="O10" s="19">
-        <f>IF(AND(M10&gt;0,B10&lt;&gt;"Oui",L10="Oui"),M10*(N(F10)*N('3 Options'!$C$18)+N(G10)*N('3 Options'!$C$19)+N(H10)),0)</f>
+      <c r="M10" s="18">
+        <f>SUM(L$6:L10)</f>
+        <v/>
+      </c>
+      <c r="N10" s="19">
+        <f>IF(AND(L10&gt;0,B10&lt;&gt;"Oui",K10="Oui"),L10*(N(E10)*N('3 Options'!$C$15)+N(F10)*N('3 Options'!$C$16)+N(G10)),0)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="21" customHeight="1">
       <c r="A11" s="13">
-        <f>IF(AND(M11&gt;0,B11&lt;&gt;"Oui"),COUNTIFS(M$6:M11,"&gt;0",B$6:B11,"&lt;&gt;Oui"),"")</f>
+        <f>IF(AND(L11&gt;0,B11&lt;&gt;"Oui"),COUNTIFS(L$6:L11,"&gt;0",B$6:B11,"&lt;&gt;Oui"),"")</f>
         <v/>
       </c>
       <c r="B11" s="14" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="15" t="n"/>
-      <c r="E11" s="7" t="n"/>
+      <c r="E11" s="16" t="n"/>
       <c r="F11" s="16" t="n"/>
       <c r="G11" s="16" t="n"/>
       <c r="H11" s="16" t="n"/>
       <c r="I11" s="16" t="n"/>
       <c r="J11" s="16" t="n"/>
-      <c r="K11" s="16" t="n"/>
-      <c r="L11" s="14" t="n"/>
-      <c r="M11" s="17">
+      <c r="K11" s="14" t="n"/>
+      <c r="L11" s="17">
         <f>IF($C11="",0,IF($B11="Oui",1,IF(N($D11)&gt;0,INT($D11),1)))</f>
         <v/>
       </c>
-      <c r="N11" s="18">
-        <f>SUM(M$6:M11)</f>
-        <v/>
-      </c>
-      <c r="O11" s="19">
-        <f>IF(AND(M11&gt;0,B11&lt;&gt;"Oui",L11="Oui"),M11*(N(F11)*N('3 Options'!$C$18)+N(G11)*N('3 Options'!$C$19)+N(H11)),0)</f>
+      <c r="M11" s="18">
+        <f>SUM(L$6:L11)</f>
+        <v/>
+      </c>
+      <c r="N11" s="19">
+        <f>IF(AND(L11&gt;0,B11&lt;&gt;"Oui",K11="Oui"),L11*(N(E11)*N('3 Options'!$C$15)+N(F11)*N('3 Options'!$C$16)+N(G11)),0)</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="21" customHeight="1">
       <c r="A12" s="13">
-        <f>IF(AND(M12&gt;0,B12&lt;&gt;"Oui"),COUNTIFS(M$6:M12,"&gt;0",B$6:B12,"&lt;&gt;Oui"),"")</f>
+        <f>IF(AND(L12&gt;0,B12&lt;&gt;"Oui"),COUNTIFS(L$6:L12,"&gt;0",B$6:B12,"&lt;&gt;Oui"),"")</f>
         <v/>
       </c>
       <c r="B12" s="14" t="n"/>
       <c r="C12" s="7" t="n"/>
       <c r="D12" s="15" t="n"/>
-      <c r="E12" s="7" t="n"/>
+      <c r="E12" s="16" t="n"/>
       <c r="F12" s="16" t="n"/>
       <c r="G12" s="16" t="n"/>
       <c r="H12" s="16" t="n"/>
       <c r="I12" s="16" t="n"/>
       <c r="J12" s="16" t="n"/>
-      <c r="K12" s="16" t="n"/>
-      <c r="L12" s="14" t="n"/>
-      <c r="M12" s="17">
+      <c r="K12" s="14" t="n"/>
+      <c r="L12" s="17">
         <f>IF($C12="",0,IF($B12="Oui",1,IF(N($D12)&gt;0,INT($D12),1)))</f>
         <v/>
       </c>
-      <c r="N12" s="18">
-        <f>SUM(M$6:M12)</f>
-        <v/>
-      </c>
-      <c r="O12" s="19">
-        <f>IF(AND(M12&gt;0,B12&lt;&gt;"Oui",L12="Oui"),M12*(N(F12)*N('3 Options'!$C$18)+N(G12)*N('3 Options'!$C$19)+N(H12)),0)</f>
+      <c r="M12" s="18">
+        <f>SUM(L$6:L12)</f>
+        <v/>
+      </c>
+      <c r="N12" s="19">
+        <f>IF(AND(L12&gt;0,B12&lt;&gt;"Oui",K12="Oui"),L12*(N(E12)*N('3 Options'!$C$15)+N(F12)*N('3 Options'!$C$16)+N(G12)),0)</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="21" customHeight="1">
       <c r="A13" s="13">
-        <f>IF(AND(M13&gt;0,B13&lt;&gt;"Oui"),COUNTIFS(M$6:M13,"&gt;0",B$6:B13,"&lt;&gt;Oui"),"")</f>
+        <f>IF(AND(L13&gt;0,B13&lt;&gt;"Oui"),COUNTIFS(L$6:L13,"&gt;0",B$6:B13,"&lt;&gt;Oui"),"")</f>
         <v/>
       </c>
       <c r="B13" s="14" t="n"/>
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="15" t="n"/>
-      <c r="E13" s="7" t="n"/>
+      <c r="E13" s="16" t="n"/>
       <c r="F13" s="16" t="n"/>
       <c r="G13" s="16" t="n"/>
       <c r="H13" s="16" t="n"/>
       <c r="I13" s="16" t="n"/>
       <c r="J13" s="16" t="n"/>
-      <c r="K13" s="16" t="n"/>
-      <c r="L13" s="14" t="n"/>
-      <c r="M13" s="17">
+      <c r="K13" s="14" t="n"/>
+      <c r="L13" s="17">
         <f>IF($C13="",0,IF($B13="Oui",1,IF(N($D13)&gt;0,INT($D13),1)))</f>
         <v/>
       </c>
-      <c r="N13" s="18">
-        <f>SUM(M$6:M13)</f>
-        <v/>
-      </c>
-      <c r="O13" s="19">
-        <f>IF(AND(M13&gt;0,B13&lt;&gt;"Oui",L13="Oui"),M13*(N(F13)*N('3 Options'!$C$18)+N(G13)*N('3 Options'!$C$19)+N(H13)),0)</f>
+      <c r="M13" s="18">
+        <f>SUM(L$6:L13)</f>
+        <v/>
+      </c>
+      <c r="N13" s="19">
+        <f>IF(AND(L13&gt;0,B13&lt;&gt;"Oui",K13="Oui"),L13*(N(E13)*N('3 Options'!$C$15)+N(F13)*N('3 Options'!$C$16)+N(G13)),0)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="21" customHeight="1">
       <c r="A14" s="13">
-        <f>IF(AND(M14&gt;0,B14&lt;&gt;"Oui"),COUNTIFS(M$6:M14,"&gt;0",B$6:B14,"&lt;&gt;Oui"),"")</f>
+        <f>IF(AND(L14&gt;0,B14&lt;&gt;"Oui"),COUNTIFS(L$6:L14,"&gt;0",B$6:B14,"&lt;&gt;Oui"),"")</f>
         <v/>
       </c>
       <c r="B14" s="14" t="n"/>
       <c r="C14" s="7" t="n"/>
       <c r="D14" s="15" t="n"/>
-      <c r="E14" s="7" t="n"/>
+      <c r="E14" s="16" t="n"/>
       <c r="F14" s="16" t="n"/>
       <c r="G14" s="16" t="n"/>
       <c r="H14" s="16" t="n"/>
       <c r="I14" s="16" t="n"/>
       <c r="J14" s="16" t="n"/>
-      <c r="K14" s="16" t="n"/>
-      <c r="L14" s="14" t="n"/>
-      <c r="M14" s="17">
+      <c r="K14" s="14" t="n"/>
+      <c r="L14" s="17">
         <f>IF($C14="",0,IF($B14="Oui",1,IF(N($D14)&gt;0,INT($D14),1)))</f>
         <v/>
       </c>
-      <c r="N14" s="18">
-        <f>SUM(M$6:M14)</f>
-        <v/>
-      </c>
-      <c r="O14" s="19">
-        <f>IF(AND(M14&gt;0,B14&lt;&gt;"Oui",L14="Oui"),M14*(N(F14)*N('3 Options'!$C$18)+N(G14)*N('3 Options'!$C$19)+N(H14)),0)</f>
+      <c r="M14" s="18">
+        <f>SUM(L$6:L14)</f>
+        <v/>
+      </c>
+      <c r="N14" s="19">
+        <f>IF(AND(L14&gt;0,B14&lt;&gt;"Oui",K14="Oui"),L14*(N(E14)*N('3 Options'!$C$15)+N(F14)*N('3 Options'!$C$16)+N(G14)),0)</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="21" customHeight="1">
       <c r="A15" s="13">
-        <f>IF(AND(M15&gt;0,B15&lt;&gt;"Oui"),COUNTIFS(M$6:M15,"&gt;0",B$6:B15,"&lt;&gt;Oui"),"")</f>
+        <f>IF(AND(L15&gt;0,B15&lt;&gt;"Oui"),COUNTIFS(L$6:L15,"&gt;0",B$6:B15,"&lt;&gt;Oui"),"")</f>
         <v/>
       </c>
       <c r="B15" s="14" t="n"/>
       <c r="C15" s="7" t="n"/>
       <c r="D15" s="15" t="n"/>
-      <c r="E15" s="7" t="n"/>
+      <c r="E15" s="16" t="n"/>
       <c r="F15" s="16" t="n"/>
       <c r="G15" s="16" t="n"/>
       <c r="H15" s="16" t="n"/>
       <c r="I15" s="16" t="n"/>
       <c r="J15" s="16" t="n"/>
-      <c r="K15" s="16" t="n"/>
-      <c r="L15" s="14" t="n"/>
-      <c r="M15" s="17">
+      <c r="K15" s="14" t="n"/>
+      <c r="L15" s="17">
         <f>IF($C15="",0,IF($B15="Oui",1,IF(N($D15)&gt;0,INT($D15),1)))</f>
         <v/>
       </c>
-      <c r="N15" s="18">
-        <f>SUM(M$6:M15)</f>
-        <v/>
-      </c>
-      <c r="O15" s="19">
-        <f>IF(AND(M15&gt;0,B15&lt;&gt;"Oui",L15="Oui"),M15*(N(F15)*N('3 Options'!$C$18)+N(G15)*N('3 Options'!$C$19)+N(H15)),0)</f>
+      <c r="M15" s="18">
+        <f>SUM(L$6:L15)</f>
+        <v/>
+      </c>
+      <c r="N15" s="19">
+        <f>IF(AND(L15&gt;0,B15&lt;&gt;"Oui",K15="Oui"),L15*(N(E15)*N('3 Options'!$C$15)+N(F15)*N('3 Options'!$C$16)+N(G15)),0)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="21" customHeight="1">
       <c r="A16" s="13">
-        <f>IF(AND(M16&gt;0,B16&lt;&gt;"Oui"),COUNTIFS(M$6:M16,"&gt;0",B$6:B16,"&lt;&gt;Oui"),"")</f>
+        <f>IF(AND(L16&gt;0,B16&lt;&gt;"Oui"),COUNTIFS(L$6:L16,"&gt;0",B$6:B16,"&lt;&gt;Oui"),"")</f>
         <v/>
       </c>
       <c r="B16" s="14" t="n"/>
       <c r="C16" s="7" t="n"/>
       <c r="D16" s="15" t="n"/>
-      <c r="E16" s="7" t="n"/>
+      <c r="E16" s="16" t="n"/>
       <c r="F16" s="16" t="n"/>
       <c r="G16" s="16" t="n"/>
       <c r="H16" s="16" t="n"/>
       <c r="I16" s="16" t="n"/>
       <c r="J16" s="16" t="n"/>
-      <c r="K16" s="16" t="n"/>
-      <c r="L16" s="14" t="n"/>
-      <c r="M16" s="17">
+      <c r="K16" s="14" t="n"/>
+      <c r="L16" s="17">
         <f>IF($C16="",0,IF($B16="Oui",1,IF(N($D16)&gt;0,INT($D16),1)))</f>
         <v/>
       </c>
-      <c r="N16" s="18">
-        <f>SUM(M$6:M16)</f>
-        <v/>
-      </c>
-      <c r="O16" s="19">
-        <f>IF(AND(M16&gt;0,B16&lt;&gt;"Oui",L16="Oui"),M16*(N(F16)*N('3 Options'!$C$18)+N(G16)*N('3 Options'!$C$19)+N(H16)),0)</f>
+      <c r="M16" s="18">
+        <f>SUM(L$6:L16)</f>
+        <v/>
+      </c>
+      <c r="N16" s="19">
+        <f>IF(AND(L16&gt;0,B16&lt;&gt;"Oui",K16="Oui"),L16*(N(E16)*N('3 Options'!$C$15)+N(F16)*N('3 Options'!$C$16)+N(G16)),0)</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="13">
-        <f>IF(AND(M17&gt;0,B17&lt;&gt;"Oui"),COUNTIFS(M$6:M17,"&gt;0",B$6:B17,"&lt;&gt;Oui"),"")</f>
+        <f>IF(AND(L17&gt;0,B17&lt;&gt;"Oui"),COUNTIFS(L$6:L17,"&gt;0",B$6:B17,"&lt;&gt;Oui"),"")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="n"/>
       <c r="C17" s="7" t="n"/>
       <c r="D17" s="15" t="n"/>
-      <c r="E17" s="7" t="n"/>
+      <c r="E17" s="16" t="n"/>
       <c r="F17" s="16" t="n"/>
       <c r="G17" s="16" t="n"/>
       <c r="H17" s="16" t="n"/>
       <c r="I17" s="16" t="n"/>
       <c r="J17" s="16" t="n"/>
-      <c r="K17" s="16" t="n"/>
-      <c r="L17" s="14" t="n"/>
-      <c r="M17" s="17">
+      <c r="K17" s="14" t="n"/>
+      <c r="L17" s="17">
         <f>IF($C17="",0,IF($B17="Oui",1,IF(N($D17)&gt;0,INT($D17),1)))</f>
         <v/>
       </c>
-      <c r="N17" s="18">
-        <f>SUM(M$6:M17)</f>
-        <v/>
-      </c>
-      <c r="O17" s="19">
-        <f>IF(AND(M17&gt;0,B17&lt;&gt;"Oui",L17="Oui"),M17*(N(F17)*N('3 Options'!$C$18)+N(G17)*N('3 Options'!$C$19)+N(H17)),0)</f>
+      <c r="M17" s="18">
+        <f>SUM(L$6:L17)</f>
+        <v/>
+      </c>
+      <c r="N17" s="19">
+        <f>IF(AND(L17&gt;0,B17&lt;&gt;"Oui",K17="Oui"),L17*(N(E17)*N('3 Options'!$C$15)+N(F17)*N('3 Options'!$C$16)+N(G17)),0)</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
       <c r="A18" s="13">
-        <f>IF(AND(M18&gt;0,B18&lt;&gt;"Oui"),COUNTIFS(M$6:M18,"&gt;0",B$6:B18,"&lt;&gt;Oui"),"")</f>
+        <f>IF(AND(L18&gt;0,B18&lt;&gt;"Oui"),COUNTIFS(L$6:L18,"&gt;0",B$6:B18,"&lt;&gt;Oui"),"")</f>
         <v/>
       </c>
       <c r="B18" s="14" t="n"/>
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="15" t="n"/>
-      <c r="E18" s="7" t="n"/>
+      <c r="E18" s="16" t="n"/>
       <c r="F18" s="16" t="n"/>
       <c r="G18" s="16" t="n"/>
       <c r="H18" s="16" t="n"/>
       <c r="I18" s="16" t="n"/>
       <c r="J18" s="16" t="n"/>
-      <c r="K18" s="16" t="n"/>
-      <c r="L18" s="14" t="n"/>
-      <c r="M18" s="17">
+      <c r="K18" s="14" t="n"/>
+      <c r="L18" s="17">
         <f>IF($C18="",0,IF($B18="Oui",1,IF(N($D18)&gt;0,INT($D18),1)))</f>
         <v/>
       </c>
-      <c r="N18" s="18">
-        <f>SUM(M$6:M18)</f>
-        <v/>
-      </c>
-      <c r="O18" s="19">
-        <f>IF(AND(M18&gt;0,B18&lt;&gt;"Oui",L18="Oui"),M18*(N(F18)*N('3 Options'!$C$18)+N(G18)*N('3 Options'!$C$19)+N(H18)),0)</f>
+      <c r="M18" s="18">
+        <f>SUM(L$6:L18)</f>
+        <v/>
+      </c>
+      <c r="N18" s="19">
+        <f>IF(AND(L18&gt;0,B18&lt;&gt;"Oui",K18="Oui"),L18*(N(E18)*N('3 Options'!$C$15)+N(F18)*N('3 Options'!$C$16)+N(G18)),0)</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="21" customHeight="1">
       <c r="A19" s="13">
-        <f>IF(AND(M19&gt;0,B19&lt;&gt;"Oui"),COUNTIFS(M$6:M19,"&gt;0",B$6:B19,"&lt;&gt;Oui"),"")</f>
+        <f>IF(AND(L19&gt;0,B19&lt;&gt;"Oui"),COUNTIFS(L$6:L19,"&gt;0",B$6:B19,"&lt;&gt;Oui"),"")</f>
         <v/>
       </c>
       <c r="B19" s="14" t="n"/>
       <c r="C19" s="7" t="n"/>
       <c r="D19" s="15" t="n"/>
-      <c r="E19" s="7" t="n"/>
+      <c r="E19" s="16" t="n"/>
       <c r="F19" s="16" t="n"/>
       <c r="G19" s="16" t="n"/>
       <c r="H19" s="16" t="n"/>
       <c r="I19" s="16" t="n"/>
       <c r="J19" s="16" t="n"/>
-      <c r="K19" s="16" t="n"/>
-      <c r="L19" s="14" t="n"/>
-      <c r="M19" s="17">
+      <c r="K19" s="14" t="n"/>
+      <c r="L19" s="17">
         <f>IF($C19="",0,IF($B19="Oui",1,IF(N($D19)&gt;0,INT($D19),1)))</f>
         <v/>
       </c>
-      <c r="N19" s="18">
-        <f>SUM(M$6:M19)</f>
-        <v/>
-      </c>
-      <c r="O19" s="19">
-        <f>IF(AND(M19&gt;0,B19&lt;&gt;"Oui",L19="Oui"),M19*(N(F19)*N('3 Options'!$C$18)+N(G19)*N('3 Options'!$C$19)+N(H19)),0)</f>
+      <c r="M19" s="18">
+        <f>SUM(L$6:L19)</f>
+        <v/>
+      </c>
+      <c r="N19" s="19">
+        <f>IF(AND(L19&gt;0,B19&lt;&gt;"Oui",K19="Oui"),L19*(N(E19)*N('3 Options'!$C$15)+N(F19)*N('3 Options'!$C$16)+N(G19)),0)</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="21" customHeight="1">
       <c r="A20" s="13">
-        <f>IF(AND(M20&gt;0,B20&lt;&gt;"Oui"),COUNTIFS(M$6:M20,"&gt;0",B$6:B20,"&lt;&gt;Oui"),"")</f>
+        <f>IF(AND(L20&gt;0,B20&lt;&gt;"Oui"),COUNTIFS(L$6:L20,"&gt;0",B$6:B20,"&lt;&gt;Oui"),"")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="n"/>
       <c r="C20" s="7" t="n"/>
       <c r="D20" s="15" t="n"/>
-      <c r="E20" s="7" t="n"/>
+      <c r="E20" s="16" t="n"/>
       <c r="F20" s="16" t="n"/>
       <c r="G20" s="16" t="n"/>
       <c r="H20" s="16" t="n"/>
       <c r="I20" s="16" t="n"/>
       <c r="J20" s="16" t="n"/>
-      <c r="K20" s="16" t="n"/>
-      <c r="L20" s="14" t="n"/>
-      <c r="M20" s="17">
+      <c r="K20" s="14" t="n"/>
+      <c r="L20" s="17">
         <f>IF($C20="",0,IF($B20="Oui",1,IF(N($D20)&gt;0,INT($D20),1)))</f>
         <v/>
       </c>
-      <c r="N20" s="18">
-        <f>SUM(M$6:M20)</f>
-        <v/>
-      </c>
-      <c r="O20" s="19">
-        <f>IF(AND(M20&gt;0,B20&lt;&gt;"Oui",L20="Oui"),M20*(N(F20)*N('3 Options'!$C$18)+N(G20)*N('3 Options'!$C$19)+N(H20)),0)</f>
+      <c r="M20" s="18">
+        <f>SUM(L$6:L20)</f>
+        <v/>
+      </c>
+      <c r="N20" s="19">
+        <f>IF(AND(L20&gt;0,B20&lt;&gt;"Oui",K20="Oui"),L20*(N(E20)*N('3 Options'!$C$15)+N(F20)*N('3 Options'!$C$16)+N(G20)),0)</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="21" customHeight="1">
       <c r="A21" s="13">
-        <f>IF(AND(M21&gt;0,B21&lt;&gt;"Oui"),COUNTIFS(M$6:M21,"&gt;0",B$6:B21,"&lt;&gt;Oui"),"")</f>
+        <f>IF(AND(L21&gt;0,B21&lt;&gt;"Oui"),COUNTIFS(L$6:L21,"&gt;0",B$6:B21,"&lt;&gt;Oui"),"")</f>
         <v/>
       </c>
       <c r="B21" s="14" t="n"/>
       <c r="C21" s="7" t="n"/>
       <c r="D21" s="15" t="n"/>
-      <c r="E21" s="7" t="n"/>
+      <c r="E21" s="16" t="n"/>
       <c r="F21" s="16" t="n"/>
       <c r="G21" s="16" t="n"/>
       <c r="H21" s="16" t="n"/>
       <c r="I21" s="16" t="n"/>
       <c r="J21" s="16" t="n"/>
-      <c r="K21" s="16" t="n"/>
-      <c r="L21" s="14" t="n"/>
-      <c r="M21" s="17">
+      <c r="K21" s="14" t="n"/>
+      <c r="L21" s="17">
         <f>IF($C21="",0,IF($B21="Oui",1,IF(N($D21)&gt;0,INT($D21),1)))</f>
         <v/>
       </c>
-      <c r="N21" s="18">
-        <f>SUM(M$6:M21)</f>
-        <v/>
-      </c>
-      <c r="O21" s="19">
-        <f>IF(AND(M21&gt;0,B21&lt;&gt;"Oui",L21="Oui"),M21*(N(F21)*N('3 Options'!$C$18)+N(G21)*N('3 Options'!$C$19)+N(H21)),0)</f>
+      <c r="M21" s="18">
+        <f>SUM(L$6:L21)</f>
+        <v/>
+      </c>
+      <c r="N21" s="19">
+        <f>IF(AND(L21&gt;0,B21&lt;&gt;"Oui",K21="Oui"),L21*(N(E21)*N('3 Options'!$C$15)+N(F21)*N('3 Options'!$C$16)+N(G21)),0)</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="21" customHeight="1">
       <c r="A22" s="13">
-        <f>IF(AND(M22&gt;0,B22&lt;&gt;"Oui"),COUNTIFS(M$6:M22,"&gt;0",B$6:B22,"&lt;&gt;Oui"),"")</f>
+        <f>IF(AND(L22&gt;0,B22&lt;&gt;"Oui"),COUNTIFS(L$6:L22,"&gt;0",B$6:B22,"&lt;&gt;Oui"),"")</f>
         <v/>
       </c>
       <c r="B22" s="14" t="n"/>
       <c r="C22" s="7" t="n"/>
       <c r="D22" s="15" t="n"/>
-      <c r="E22" s="7" t="n"/>
+      <c r="E22" s="16" t="n"/>
       <c r="F22" s="16" t="n"/>
       <c r="G22" s="16" t="n"/>
       <c r="H22" s="16" t="n"/>
       <c r="I22" s="16" t="n"/>
       <c r="J22" s="16" t="n"/>
-      <c r="K22" s="16" t="n"/>
-      <c r="L22" s="14" t="n"/>
-      <c r="M22" s="17">
+      <c r="K22" s="14" t="n"/>
+      <c r="L22" s="17">
         <f>IF($C22="",0,IF($B22="Oui",1,IF(N($D22)&gt;0,INT($D22),1)))</f>
         <v/>
       </c>
-      <c r="N22" s="18">
-        <f>SUM(M$6:M22)</f>
-        <v/>
-      </c>
-      <c r="O22" s="19">
-        <f>IF(AND(M22&gt;0,B22&lt;&gt;"Oui",L22="Oui"),M22*(N(F22)*N('3 Options'!$C$18)+N(G22)*N('3 Options'!$C$19)+N(H22)),0)</f>
+      <c r="M22" s="18">
+        <f>SUM(L$6:L22)</f>
+        <v/>
+      </c>
+      <c r="N22" s="19">
+        <f>IF(AND(L22&gt;0,B22&lt;&gt;"Oui",K22="Oui"),L22*(N(E22)*N('3 Options'!$C$15)+N(F22)*N('3 Options'!$C$16)+N(G22)),0)</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="21" customHeight="1">
       <c r="A23" s="13">
-        <f>IF(AND(M23&gt;0,B23&lt;&gt;"Oui"),COUNTIFS(M$6:M23,"&gt;0",B$6:B23,"&lt;&gt;Oui"),"")</f>
+        <f>IF(AND(L23&gt;0,B23&lt;&gt;"Oui"),COUNTIFS(L$6:L23,"&gt;0",B$6:B23,"&lt;&gt;Oui"),"")</f>
         <v/>
       </c>
       <c r="B23" s="14" t="n"/>
       <c r="C23" s="7" t="n"/>
       <c r="D23" s="15" t="n"/>
-      <c r="E23" s="7" t="n"/>
+      <c r="E23" s="16" t="n"/>
       <c r="F23" s="16" t="n"/>
       <c r="G23" s="16" t="n"/>
       <c r="H23" s="16" t="n"/>
       <c r="I23" s="16" t="n"/>
       <c r="J23" s="16" t="n"/>
-      <c r="K23" s="16" t="n"/>
-      <c r="L23" s="14" t="n"/>
-      <c r="M23" s="17">
+      <c r="K23" s="14" t="n"/>
+      <c r="L23" s="17">
         <f>IF($C23="",0,IF($B23="Oui",1,IF(N($D23)&gt;0,INT($D23),1)))</f>
         <v/>
       </c>
-      <c r="N23" s="18">
-        <f>SUM(M$6:M23)</f>
-        <v/>
-      </c>
-      <c r="O23" s="19">
-        <f>IF(AND(M23&gt;0,B23&lt;&gt;"Oui",L23="Oui"),M23*(N(F23)*N('3 Options'!$C$18)+N(G23)*N('3 Options'!$C$19)+N(H23)),0)</f>
+      <c r="M23" s="18">
+        <f>SUM(L$6:L23)</f>
+        <v/>
+      </c>
+      <c r="N23" s="19">
+        <f>IF(AND(L23&gt;0,B23&lt;&gt;"Oui",K23="Oui"),L23*(N(E23)*N('3 Options'!$C$15)+N(F23)*N('3 Options'!$C$16)+N(G23)),0)</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="21" customHeight="1">
       <c r="A24" s="13">
-        <f>IF(AND(M24&gt;0,B24&lt;&gt;"Oui"),COUNTIFS(M$6:M24,"&gt;0",B$6:B24,"&lt;&gt;Oui"),"")</f>
+        <f>IF(AND(L24&gt;0,B24&lt;&gt;"Oui"),COUNTIFS(L$6:L24,"&gt;0",B$6:B24,"&lt;&gt;Oui"),"")</f>
         <v/>
       </c>
       <c r="B24" s="14" t="n"/>
       <c r="C24" s="7" t="n"/>
       <c r="D24" s="15" t="n"/>
-      <c r="E24" s="7" t="n"/>
+      <c r="E24" s="16" t="n"/>
       <c r="F24" s="16" t="n"/>
       <c r="G24" s="16" t="n"/>
       <c r="H24" s="16" t="n"/>
       <c r="I24" s="16" t="n"/>
       <c r="J24" s="16" t="n"/>
-      <c r="K24" s="16" t="n"/>
-      <c r="L24" s="14" t="n"/>
-      <c r="M24" s="17">
+      <c r="K24" s="14" t="n"/>
+      <c r="L24" s="17">
         <f>IF($C24="",0,IF($B24="Oui",1,IF(N($D24)&gt;0,INT($D24),1)))</f>
         <v/>
       </c>
-      <c r="N24" s="18">
-        <f>SUM(M$6:M24)</f>
-        <v/>
-      </c>
-      <c r="O24" s="19">
-        <f>IF(AND(M24&gt;0,B24&lt;&gt;"Oui",L24="Oui"),M24*(N(F24)*N('3 Options'!$C$18)+N(G24)*N('3 Options'!$C$19)+N(H24)),0)</f>
+      <c r="M24" s="18">
+        <f>SUM(L$6:L24)</f>
+        <v/>
+      </c>
+      <c r="N24" s="19">
+        <f>IF(AND(L24&gt;0,B24&lt;&gt;"Oui",K24="Oui"),L24*(N(E24)*N('3 Options'!$C$15)+N(F24)*N('3 Options'!$C$16)+N(G24)),0)</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1">
       <c r="A25" s="13">
-        <f>IF(AND(M25&gt;0,B25&lt;&gt;"Oui"),COUNTIFS(M$6:M25,"&gt;0",B$6:B25,"&lt;&gt;Oui"),"")</f>
+        <f>IF(AND(L25&gt;0,B25&lt;&gt;"Oui"),COUNTIFS(L$6:L25,"&gt;0",B$6:B25,"&lt;&gt;Oui"),"")</f>
         <v/>
       </c>
       <c r="B25" s="14" t="n"/>
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="15" t="n"/>
-      <c r="E25" s="7" t="n"/>
+      <c r="E25" s="16" t="n"/>
       <c r="F25" s="16" t="n"/>
       <c r="G25" s="16" t="n"/>
       <c r="H25" s="16" t="n"/>
       <c r="I25" s="16" t="n"/>
       <c r="J25" s="16" t="n"/>
-      <c r="K25" s="16" t="n"/>
-      <c r="L25" s="14" t="n"/>
-      <c r="M25" s="17">
+      <c r="K25" s="14" t="n"/>
+      <c r="L25" s="17">
         <f>IF($C25="",0,IF($B25="Oui",1,IF(N($D25)&gt;0,INT($D25),1)))</f>
         <v/>
       </c>
-      <c r="N25" s="18">
-        <f>SUM(M$6:M25)</f>
-        <v/>
-      </c>
-      <c r="O25" s="19">
-        <f>IF(AND(M25&gt;0,B25&lt;&gt;"Oui",L25="Oui"),M25*(N(F25)*N('3 Options'!$C$18)+N(G25)*N('3 Options'!$C$19)+N(H25)),0)</f>
+      <c r="M25" s="18">
+        <f>SUM(L$6:L25)</f>
+        <v/>
+      </c>
+      <c r="N25" s="19">
+        <f>IF(AND(L25&gt;0,B25&lt;&gt;"Oui",K25="Oui"),L25*(N(E25)*N('3 Options'!$C$15)+N(F25)*N('3 Options'!$C$16)+N(G25)),0)</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="21" customHeight="1">
       <c r="A26" s="13">
-        <f>IF(AND(M26&gt;0,B26&lt;&gt;"Oui"),COUNTIFS(M$6:M26,"&gt;0",B$6:B26,"&lt;&gt;Oui"),"")</f>
+        <f>IF(AND(L26&gt;0,B26&lt;&gt;"Oui"),COUNTIFS(L$6:L26,"&gt;0",B$6:B26,"&lt;&gt;Oui"),"")</f>
         <v/>
       </c>
       <c r="B26" s="14" t="n"/>
       <c r="C26" s="7" t="n"/>
       <c r="D26" s="15" t="n"/>
-      <c r="E26" s="7" t="n"/>
+      <c r="E26" s="16" t="n"/>
       <c r="F26" s="16" t="n"/>
       <c r="G26" s="16" t="n"/>
       <c r="H26" s="16" t="n"/>
       <c r="I26" s="16" t="n"/>
       <c r="J26" s="16" t="n"/>
-      <c r="K26" s="16" t="n"/>
-      <c r="L26" s="14" t="n"/>
-      <c r="M26" s="17">
+      <c r="K26" s="14" t="n"/>
+      <c r="L26" s="17">
         <f>IF($C26="",0,IF($B26="Oui",1,IF(N($D26)&gt;0,INT($D26),1)))</f>
         <v/>
       </c>
-      <c r="N26" s="18">
-        <f>SUM(M$6:M26)</f>
-        <v/>
-      </c>
-      <c r="O26" s="19">
-        <f>IF(AND(M26&gt;0,B26&lt;&gt;"Oui",L26="Oui"),M26*(N(F26)*N('3 Options'!$C$18)+N(G26)*N('3 Options'!$C$19)+N(H26)),0)</f>
+      <c r="M26" s="18">
+        <f>SUM(L$6:L26)</f>
+        <v/>
+      </c>
+      <c r="N26" s="19">
+        <f>IF(AND(L26&gt;0,B26&lt;&gt;"Oui",K26="Oui"),L26*(N(E26)*N('3 Options'!$C$15)+N(F26)*N('3 Options'!$C$16)+N(G26)),0)</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="21" customHeight="1">
       <c r="A27" s="13">
-        <f>IF(AND(M27&gt;0,B27&lt;&gt;"Oui"),COUNTIFS(M$6:M27,"&gt;0",B$6:B27,"&lt;&gt;Oui"),"")</f>
+        <f>IF(AND(L27&gt;0,B27&lt;&gt;"Oui"),COUNTIFS(L$6:L27,"&gt;0",B$6:B27,"&lt;&gt;Oui"),"")</f>
         <v/>
       </c>
       <c r="B27" s="14" t="n"/>
       <c r="C27" s="7" t="n"/>
       <c r="D27" s="15" t="n"/>
-      <c r="E27" s="7" t="n"/>
+      <c r="E27" s="16" t="n"/>
       <c r="F27" s="16" t="n"/>
       <c r="G27" s="16" t="n"/>
       <c r="H27" s="16" t="n"/>
       <c r="I27" s="16" t="n"/>
       <c r="J27" s="16" t="n"/>
-      <c r="K27" s="16" t="n"/>
-      <c r="L27" s="14" t="n"/>
-      <c r="M27" s="17">
+      <c r="K27" s="14" t="n"/>
+      <c r="L27" s="17">
         <f>IF($C27="",0,IF($B27="Oui",1,IF(N($D27)&gt;0,INT($D27),1)))</f>
         <v/>
       </c>
-      <c r="N27" s="18">
-        <f>SUM(M$6:M27)</f>
-        <v/>
-      </c>
-      <c r="O27" s="19">
-        <f>IF(AND(M27&gt;0,B27&lt;&gt;"Oui",L27="Oui"),M27*(N(F27)*N('3 Options'!$C$18)+N(G27)*N('3 Options'!$C$19)+N(H27)),0)</f>
+      <c r="M27" s="18">
+        <f>SUM(L$6:L27)</f>
+        <v/>
+      </c>
+      <c r="N27" s="19">
+        <f>IF(AND(L27&gt;0,B27&lt;&gt;"Oui",K27="Oui"),L27*(N(E27)*N('3 Options'!$C$15)+N(F27)*N('3 Options'!$C$16)+N(G27)),0)</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="21" customHeight="1">
       <c r="A28" s="13">
-        <f>IF(AND(M28&gt;0,B28&lt;&gt;"Oui"),COUNTIFS(M$6:M28,"&gt;0",B$6:B28,"&lt;&gt;Oui"),"")</f>
+        <f>IF(AND(L28&gt;0,B28&lt;&gt;"Oui"),COUNTIFS(L$6:L28,"&gt;0",B$6:B28,"&lt;&gt;Oui"),"")</f>
         <v/>
       </c>
       <c r="B28" s="14" t="n"/>
       <c r="C28" s="7" t="n"/>
       <c r="D28" s="15" t="n"/>
-      <c r="E28" s="7" t="n"/>
+      <c r="E28" s="16" t="n"/>
       <c r="F28" s="16" t="n"/>
       <c r="G28" s="16" t="n"/>
       <c r="H28" s="16" t="n"/>
       <c r="I28" s="16" t="n"/>
       <c r="J28" s="16" t="n"/>
-      <c r="K28" s="16" t="n"/>
-      <c r="L28" s="14" t="n"/>
-      <c r="M28" s="17">
+      <c r="K28" s="14" t="n"/>
+      <c r="L28" s="17">
         <f>IF($C28="",0,IF($B28="Oui",1,IF(N($D28)&gt;0,INT($D28),1)))</f>
         <v/>
       </c>
-      <c r="N28" s="18">
-        <f>SUM(M$6:M28)</f>
-        <v/>
-      </c>
-      <c r="O28" s="19">
-        <f>IF(AND(M28&gt;0,B28&lt;&gt;"Oui",L28="Oui"),M28*(N(F28)*N('3 Options'!$C$18)+N(G28)*N('3 Options'!$C$19)+N(H28)),0)</f>
+      <c r="M28" s="18">
+        <f>SUM(L$6:L28)</f>
+        <v/>
+      </c>
+      <c r="N28" s="19">
+        <f>IF(AND(L28&gt;0,B28&lt;&gt;"Oui",K28="Oui"),L28*(N(E28)*N('3 Options'!$C$15)+N(F28)*N('3 Options'!$C$16)+N(G28)),0)</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="21" customHeight="1">
       <c r="A29" s="13">
-        <f>IF(AND(M29&gt;0,B29&lt;&gt;"Oui"),COUNTIFS(M$6:M29,"&gt;0",B$6:B29,"&lt;&gt;Oui"),"")</f>
+        <f>IF(AND(L29&gt;0,B29&lt;&gt;"Oui"),COUNTIFS(L$6:L29,"&gt;0",B$6:B29,"&lt;&gt;Oui"),"")</f>
         <v/>
       </c>
       <c r="B29" s="14" t="n"/>
       <c r="C29" s="7" t="n"/>
       <c r="D29" s="15" t="n"/>
-      <c r="E29" s="7" t="n"/>
+      <c r="E29" s="16" t="n"/>
       <c r="F29" s="16" t="n"/>
       <c r="G29" s="16" t="n"/>
       <c r="H29" s="16" t="n"/>
       <c r="I29" s="16" t="n"/>
       <c r="J29" s="16" t="n"/>
-      <c r="K29" s="16" t="n"/>
-      <c r="L29" s="14" t="n"/>
-      <c r="M29" s="17">
+      <c r="K29" s="14" t="n"/>
+      <c r="L29" s="17">
         <f>IF($C29="",0,IF($B29="Oui",1,IF(N($D29)&gt;0,INT($D29),1)))</f>
         <v/>
       </c>
-      <c r="N29" s="18">
-        <f>SUM(M$6:M29)</f>
-        <v/>
-      </c>
-      <c r="O29" s="19">
-        <f>IF(AND(M29&gt;0,B29&lt;&gt;"Oui",L29="Oui"),M29*(N(F29)*N('3 Options'!$C$18)+N(G29)*N('3 Options'!$C$19)+N(H29)),0)</f>
+      <c r="M29" s="18">
+        <f>SUM(L$6:L29)</f>
+        <v/>
+      </c>
+      <c r="N29" s="19">
+        <f>IF(AND(L29&gt;0,B29&lt;&gt;"Oui",K29="Oui"),L29*(N(E29)*N('3 Options'!$C$15)+N(F29)*N('3 Options'!$C$16)+N(G29)),0)</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="C31" s="20">
-        <f>SUM(M6:M29)&amp;" ligne(s) sur la tool list  ·  "&amp;COUNTIFS(M6:M29,"&gt;0",B6:B29,"&lt;&gt;Oui")&amp;" outil(s) au devis"</f>
+        <f>SUM(L6:L29)&amp;" ligne(s) sur la tool list  ·  "&amp;COUNTIFS(L6:L29,"&gt;0",B6:B29,"&lt;&gt;Oui")&amp;" outil(s) au devis"</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>Pour la tool list : copier les colonnes B à E (Bannière, Description, Qté, Note) et les coller dans le classeur « Tool List » (sans les prix).</t>
+          <t>Pour la tool list : copier les colonnes B à D (Bannière, Description, Qté) et les coller dans le classeur « Tool List » (sans les prix).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>Le devis affiche les 14 premières lignes (les suivantes sont repliées dans l’onglet 4, avec une alerte). Colonnes grises (M à O) : calculs, ne pas modifier.</t>
+          <t>Le devis affiche les 14 premières lignes (les suivantes sont repliées dans l’onglet 4, avec une alerte). Colonnes grises (L à N) : calculs, ne pas modifier.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A6:L29">
+  <conditionalFormatting sqref="A6:K29">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$B6="Oui"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="L6:L29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="stop">
+    <dataValidation sqref="K6:K29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="stop">
       <formula1>=Listes!$G$2:$G$12</formula1>
     </dataValidation>
     <dataValidation sqref="B6:B29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="stop">
@@ -2102,7 +2066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2113,8 +2077,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="36" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2130,14 +2092,12 @@
       <c r="F1" s="1" t="n"/>
       <c r="G1" s="1" t="n"/>
       <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Une option sur « Non » disparaît du devis. Le forfait s'affiche à part, en grand, sous la liste du matériel. Le transport reste activé par défaut.</t>
+          <t>Une option sur « Non » disparaît du devis. Serrage, transport et opérateurs s'affichent chacun dans leur bloc ; le forfait dans un bandeau final.</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>
@@ -2146,8 +2106,6 @@
       <c r="F2" s="1" t="n"/>
       <c r="G2" s="1" t="n"/>
       <c r="H2" s="1" t="n"/>
-      <c r="I2" s="1" t="n"/>
-      <c r="J2" s="1" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1">
       <c r="A3" s="4" t="n"/>
@@ -2158,8 +2116,6 @@
       <c r="F3" s="4" t="n"/>
       <c r="G3" s="4" t="n"/>
       <c r="H3" s="4" t="n"/>
-      <c r="I3" s="4" t="n"/>
-      <c r="J3" s="4" t="n"/>
     </row>
     <row r="5" ht="28" customHeight="1">
       <c r="B5" s="11" t="inlineStr">
@@ -2195,16 +2151,6 @@
       <c r="H5" s="11" t="inlineStr">
         <is>
           <t>Total €</t>
-        </is>
-      </c>
-      <c r="I5" s="12" t="inlineStr">
-        <is>
-          <t>Rang</t>
-        </is>
-      </c>
-      <c r="J5" s="12" t="inlineStr">
-        <is>
-          <t>Détail affiché sur le devis</t>
         </is>
       </c>
     </row>
@@ -2233,11 +2179,6 @@
         <f>IF(C6="Oui",IF(AND(G6="Coût réel +15 %",F6=""),0,N(E6)*N(F6)),0)</f>
         <v/>
       </c>
-      <c r="I6" s="18">
-        <f>IF(C6="Oui",COUNTIF(C$6:C6,"Oui"),"")</f>
-        <v/>
-      </c>
-      <c r="J6" s="7" t="n"/>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="B7" s="22" t="inlineStr">
@@ -2264,16 +2205,11 @@
         <f>IF(C7="Oui",IF(AND(G7="Coût réel +15 %",F7=""),0,N(E7)*N(F7)),0)</f>
         <v/>
       </c>
-      <c r="I7" s="18">
-        <f>IF(C7="Oui",COUNTIF(C$6:C7,"Oui"),"")</f>
-        <v/>
-      </c>
-      <c r="J7" s="7" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>🔧  Serrage · Make-up</t>
+          <t>🔧  Serrage · prix par serrage (Qté = nombre de serrages)</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
@@ -2288,18 +2224,13 @@
       <c r="F8" s="16" t="n"/>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>forfait</t>
+          <t>€/serrage</t>
         </is>
       </c>
       <c r="H8" s="23">
         <f>IF(C8="Oui",IF(AND(G8="Coût réel +15 %",F8=""),0,N(E8)*N(F8)),0)</f>
         <v/>
       </c>
-      <c r="I8" s="18">
-        <f>IF(C8="Oui",COUNTIF(C$6:C8,"Oui"),"")</f>
-        <v/>
-      </c>
-      <c r="J8" s="7" t="n"/>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="B9" s="22" t="inlineStr">
@@ -2326,11 +2257,6 @@
         <f>IF(C9="Oui",IF(AND(G9="Coût réel +15 %",F9=""),0,N(E9)*N(F9)),0)</f>
         <v/>
       </c>
-      <c r="I9" s="18">
-        <f>IF(C9="Oui",COUNTIF(C$6:C9,"Oui"),"")</f>
-        <v/>
-      </c>
-      <c r="J9" s="7" t="n"/>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="B10" s="22" t="inlineStr">
@@ -2357,78 +2283,24 @@
         <f>IF(C10="Oui",IF(AND(G10="Coût réel +15 %",F10=""),0,N(E10)*N(F10)),0)</f>
         <v/>
       </c>
-      <c r="I10" s="18">
-        <f>IF(C10="Oui",COUNTIF(C$6:C10,"Oui"),"")</f>
-        <v/>
-      </c>
-      <c r="J10" s="7" t="n"/>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="B11" s="22" t="inlineStr">
-        <is>
-          <t>➕  Option libre 1</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="16" t="n"/>
-      <c r="G11" s="14" t="inlineStr">
-        <is>
-          <t>forfait</t>
-        </is>
-      </c>
-      <c r="H11" s="23">
-        <f>IF(C11="Oui",IF(AND(G11="Coût réel +15 %",F11=""),0,N(E11)*N(F11)),0)</f>
-        <v/>
-      </c>
-      <c r="I11" s="18">
-        <f>IF(C11="Oui",COUNTIF(C$6:C11,"Oui"),"")</f>
-        <v/>
-      </c>
-      <c r="J11" s="7" t="n"/>
-    </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="B12" s="22" t="inlineStr">
-        <is>
-          <t>➕  Option libre 2</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="16" t="n"/>
-      <c r="G12" s="14" t="inlineStr">
-        <is>
-          <t>forfait</t>
-        </is>
-      </c>
-      <c r="H12" s="23">
-        <f>IF(C12="Oui",IF(AND(G12="Coût réel +15 %",F12=""),0,N(E12)*N(F12)),0)</f>
-        <v/>
-      </c>
-      <c r="I12" s="18">
-        <f>IF(C12="Oui",COUNTIF(C$6:C12,"Oui"),"")</f>
-        <v/>
-      </c>
-      <c r="J12" s="7" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>📦  FORFAIT · bandeau final du devis, avec son coût</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="n"/>
+      <c r="D12" s="1" t="n"/>
+      <c r="E12" s="1" t="n"/>
+      <c r="F12" s="1" t="n"/>
+      <c r="G12" s="1" t="n"/>
+      <c r="H12" s="1" t="n"/>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>➕  Option libre 3</t>
+          <t>Forfait</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
@@ -2443,145 +2315,90 @@
       <c r="F13" s="16" t="n"/>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>forfait</t>
+          <t>Forfait calculé (S + O + UC)</t>
         </is>
       </c>
       <c r="H13" s="23">
-        <f>IF(C13="Oui",IF(AND(G13="Coût réel +15 %",F13=""),0,N(E13)*N(F13)),0)</f>
-        <v/>
-      </c>
-      <c r="I13" s="18">
-        <f>IF(C13="Oui",COUNTIF(C$6:C13,"Oui"),"")</f>
-        <v/>
-      </c>
-      <c r="J13" s="7" t="n"/>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>📦  FORFAIT · bloc détaché, affiché en grand sous la liste du matériel</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="n"/>
-      <c r="D15" s="1" t="n"/>
-      <c r="E15" s="1" t="n"/>
-      <c r="F15" s="1" t="n"/>
-      <c r="G15" s="1" t="n"/>
-      <c r="H15" s="1" t="n"/>
-      <c r="I15" s="1" t="n"/>
-      <c r="J15" s="1" t="n"/>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="B16" s="22" t="inlineStr">
-        <is>
-          <t>Forfait</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="16" t="n"/>
-      <c r="G16" s="14" t="inlineStr">
-        <is>
-          <t>Forfait calculé (S + O + UC)</t>
-        </is>
-      </c>
-      <c r="H16" s="23">
-        <f>IF(C16="Oui",IF(G16="Forfait calculé (S + O + UC)",IF(F16&lt;&gt;"",F16,C20),N(E16)*N(F16)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
+        <f>IF(C13="Oui",IF(G13="Forfait calculé (S + O + UC)",IF(F13&lt;&gt;"",F13,C17),N(E13)*N(F13)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Périmètre affiché sous le forfait</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="24" t="n"/>
+      <c r="F14" s="24" t="n"/>
+      <c r="G14" s="24" t="n"/>
+      <c r="H14" s="24" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Forfait calculé · jours de stand-by (S)</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="25" t="inlineStr">
+        <is>
+          <t>Forfait habituel : 3 jours de stand-by + 2 jours d’opérations + toutes les utilisations de charge (UC), sur les lignes « Inclus au forfait » de l’onglet 2. Laisser « Prix € » vide pour utiliser ce calcul, ou saisir un prix pour le remplacer. Qté sert pour le mode « par jour » (nombre de jours).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Forfait calculé · jours d’opérations (O)</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Périmètre affiché sous le forfait</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="24" t="n"/>
-      <c r="F17" s="24" t="n"/>
-      <c r="G17" s="24" t="n"/>
-      <c r="H17" s="24" t="n"/>
-      <c r="I17" s="24" t="n"/>
-      <c r="J17" s="24" t="n"/>
-    </row>
-    <row r="18">
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Forfait calculé · jours de stand-by (S)</t>
-        </is>
-      </c>
-      <c r="C18" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" s="25" t="inlineStr">
-        <is>
-          <t>Forfait habituel : 3 jours de stand-by + 2 jours d’opérations + toutes les utilisations de charge (UC), sur les lignes « Inclus au forfait » de l’onglet 2. Laisser « Prix € » vide pour utiliser ce calcul, ou saisir un prix pour le remplacer. Qté sert pour le mode « par jour » (nombre de jours).</t>
-        </is>
+          <t>Montant calculé des lignes « Inclus au forfait »</t>
+        </is>
+      </c>
+      <c r="C17" s="26">
+        <f>SUM('2 Matériel'!$N$6:$N$29)</f>
+        <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>Forfait calculé · jours d’opérations (O)</t>
-        </is>
-      </c>
-      <c r="C19" s="15" t="n">
-        <v>2</v>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>Rappels</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>Montant calculé des lignes « Inclus au forfait »</t>
-        </is>
-      </c>
-      <c r="C20" s="26">
-        <f>SUM('2 Matériel'!$O$6:$O$29)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="20" t="inlineStr">
-        <is>
-          <t>Rappels</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="27" t="inlineStr">
+      <c r="B20" s="27" t="inlineStr">
         <is>
           <t>Transport « Coût réel +15 % » : aucun montant affiché. Choisir « Forfait » pour imposer un prix.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="27" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="27" t="inlineStr">
         <is>
           <t>Lignes couvertes par le forfait : mettre « Oui » dans « Inclus au forfait » (onglet 2). Elles s’affichent « incl. » sur le devis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="27" t="inlineStr">
-        <is>
-          <t>Une option libre : écrire son intitulé, son unité et son prix, puis « Oui ».</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B15:J15"/>
-    <mergeCell ref="D17:J17"/>
-    <mergeCell ref="D18:J20"/>
+    <mergeCell ref="D15:H17"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="B12:H12"/>
   </mergeCells>
-  <dataValidations count="18">
+  <dataValidations count="12">
     <dataValidation sqref="C6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="stop">
       <formula1>=Listes!$G$2:$G$12</formula1>
     </dataValidation>
@@ -2612,28 +2429,10 @@
     <dataValidation sqref="G10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="stop">
       <formula1>=Listes!$M$2:$M$12</formula1>
     </dataValidation>
-    <dataValidation sqref="C11" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="stop">
-      <formula1>=Listes!$G$2:$G$12</formula1>
-    </dataValidation>
-    <dataValidation sqref="G11" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="warning">
-      <formula1>=Listes!$L$2:$L$12</formula1>
-    </dataValidation>
-    <dataValidation sqref="C12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="stop">
-      <formula1>=Listes!$G$2:$G$12</formula1>
-    </dataValidation>
-    <dataValidation sqref="G12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="warning">
-      <formula1>=Listes!$L$2:$L$12</formula1>
-    </dataValidation>
     <dataValidation sqref="C13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="stop">
       <formula1>=Listes!$G$2:$G$12</formula1>
     </dataValidation>
-    <dataValidation sqref="G13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="warning">
-      <formula1>=Listes!$L$2:$L$12</formula1>
-    </dataValidation>
-    <dataValidation sqref="C16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="stop">
-      <formula1>=Listes!$G$2:$G$12</formula1>
-    </dataValidation>
-    <dataValidation sqref="G16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="stop">
+    <dataValidation sqref="G13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="stop">
       <formula1>=Listes!$N$2:$N$12</formula1>
     </dataValidation>
   </dataValidations>
@@ -2649,7 +2448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -2673,7 +2472,7 @@
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
       <c r="E1" s="28">
-        <f>INDEX(Textes!$B$2:$C$52,MATCH("title",Textes!$A$2:$A$52,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$55,MATCH("title",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="L1" s="1" t="n"/>
@@ -2706,19 +2505,19 @@
     <row r="4" ht="8" customHeight="1"/>
     <row r="5" ht="15" customHeight="1">
       <c r="B5" s="30">
-        <f>UPPER(INDEX(Textes!$B$2:$C$52,MATCH("client",Textes!$A$2:$A$52,0),Listes!$H$1))</f>
+        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("client",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
         <v/>
       </c>
       <c r="D5" s="30">
-        <f>UPPER(INDEX(Textes!$B$2:$C$52,MATCH("offer",Textes!$A$2:$A$52,0),Listes!$H$1))</f>
+        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("offer",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
         <v/>
       </c>
       <c r="G5" s="30">
-        <f>UPPER(INDEX(Textes!$B$2:$C$52,MATCH("date",Textes!$A$2:$A$52,0),Listes!$H$1))</f>
+        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("date",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
         <v/>
       </c>
       <c r="I5" s="30">
-        <f>UPPER(INDEX(Textes!$B$2:$C$52,MATCH("by",Textes!$A$2:$A$52,0),Listes!$H$1))</f>
+        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("by",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
         <v/>
       </c>
     </row>
@@ -2748,19 +2547,19 @@
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="B7" s="30">
-        <f>UPPER(INDEX(Textes!$B$2:$C$52,MATCH("attn",Textes!$A$2:$A$52,0),Listes!$H$1))</f>
+        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("attn",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
         <v/>
       </c>
       <c r="D7" s="30">
-        <f>UPPER(INDEX(Textes!$B$2:$C$52,MATCH("well",Textes!$A$2:$A$52,0),Listes!$H$1))</f>
+        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("well",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
         <v/>
       </c>
       <c r="G7" s="30">
-        <f>UPPER(INDEX(Textes!$B$2:$C$52,MATCH("rig",Textes!$A$2:$A$52,0),Listes!$H$1))</f>
+        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("inco",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
         <v/>
       </c>
       <c r="I7" s="30">
-        <f>UPPER(INDEX(Textes!$B$2:$C$52,MATCH("mail",Textes!$A$2:$A$52,0),Listes!$H$1))</f>
+        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("mail",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
         <v/>
       </c>
     </row>
@@ -2777,7 +2576,7 @@
       <c r="E8" s="32" t="n"/>
       <c r="F8" s="32" t="n"/>
       <c r="G8" s="31">
-        <f>""&amp;'1 Affaire'!$C$11</f>
+        <f>""&amp;'1 Affaire'!$F$10</f>
         <v/>
       </c>
       <c r="H8" s="32" t="n"/>
@@ -2790,36 +2589,36 @@
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="B9" s="30">
-        <f>UPPER(INDEX(Textes!$B$2:$C$52,MATCH("inco",Textes!$A$2:$A$52,0),Listes!$H$1))</f>
+        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("valid",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
         <v/>
       </c>
       <c r="D9" s="30">
-        <f>UPPER(INDEX(Textes!$B$2:$C$52,MATCH("valid",Textes!$A$2:$A$52,0),Listes!$H$1))</f>
+        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("lead",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
         <v/>
       </c>
       <c r="G9" s="30">
-        <f>UPPER(INDEX(Textes!$B$2:$C$52,MATCH("lead",Textes!$A$2:$A$52,0),Listes!$H$1))</f>
+        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("we",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
         <v/>
       </c>
       <c r="I9" s="30">
-        <f>UPPER(INDEX(Textes!$B$2:$C$52,MATCH("tel",Textes!$A$2:$A$52,0),Listes!$H$1))</f>
+        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("tel",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
       <c r="B10" s="31">
-        <f>""&amp;'1 Affaire'!$F$10</f>
+        <f>""&amp;'1 Affaire'!$F$9</f>
         <v/>
       </c>
       <c r="C10" s="32" t="n"/>
       <c r="D10" s="31">
-        <f>""&amp;'1 Affaire'!$F$9</f>
+        <f>""&amp;'1 Affaire'!$F$11</f>
         <v/>
       </c>
       <c r="E10" s="32" t="n"/>
       <c r="F10" s="32" t="n"/>
       <c r="G10" s="31">
-        <f>""&amp;'1 Affaire'!$F$11</f>
+        <f>""&amp;'1 Affaire'!$F$13</f>
         <v/>
       </c>
       <c r="H10" s="32" t="n"/>
@@ -2832,11 +2631,7 @@
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="B11" s="30">
-        <f>UPPER(INDEX(Textes!$B$2:$C$52,MATCH("pay",Textes!$A$2:$A$52,0),Listes!$H$1))</f>
-        <v/>
-      </c>
-      <c r="D11" s="30">
-        <f>UPPER(INDEX(Textes!$B$2:$C$52,MATCH("we",Textes!$A$2:$A$52,0),Listes!$H$1))</f>
+        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("pay",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
         <v/>
       </c>
     </row>
@@ -2846,17 +2641,11 @@
         <v/>
       </c>
       <c r="C12" s="32" t="n"/>
-      <c r="D12" s="31">
-        <f>""&amp;'1 Affaire'!$F$13</f>
-        <v/>
-      </c>
-      <c r="E12" s="32" t="n"/>
-      <c r="F12" s="32" t="n"/>
     </row>
     <row r="13" ht="8" customHeight="1"/>
     <row r="14" ht="20" customHeight="1">
       <c r="B14" s="33">
-        <f>INDEX(Textes!$B$2:$C$52,MATCH("sec_eq",Textes!$A$2:$A$52,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$55,MATCH("sec_eq",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="C14" s="34" t="n"/>
@@ -2871,1479 +2660,1421 @@
     </row>
     <row r="15" ht="44" customHeight="1">
       <c r="B15" s="35">
-        <f>INDEX(Textes!$B$2:$C$52,MATCH("h_n",Textes!$A$2:$A$52,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_n",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="C15" s="36">
-        <f>INDEX(Textes!$B$2:$C$52,MATCH("h_desc",Textes!$A$2:$A$52,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_desc",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="D15" s="35">
-        <f>INDEX(Textes!$B$2:$C$52,MATCH("h_qty",Textes!$A$2:$A$52,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_qty",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="E15" s="35">
-        <f>INDEX(Textes!$B$2:$C$52,MATCH("h_s",Textes!$A$2:$A$52,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_s",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="F15" s="35">
-        <f>INDEX(Textes!$B$2:$C$52,MATCH("h_o",Textes!$A$2:$A$52,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_o",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="G15" s="35">
-        <f>INDEX(Textes!$B$2:$C$52,MATCH("h_uc",Textes!$A$2:$A$52,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_uc",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="H15" s="35">
-        <f>INDEX(Textes!$B$2:$C$52,MATCH("h_lih",Textes!$A$2:$A$52,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_lih",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="I15" s="35">
-        <f>INDEX(Textes!$B$2:$C$52,MATCH("h_insp",Textes!$A$2:$A$52,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_insp",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="J15" s="35">
-        <f>INDEX(Textes!$B$2:$C$52,MATCH("h_rest",Textes!$A$2:$A$52,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_rest",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="K15" s="35">
-        <f>INDEX(Textes!$B$2:$C$52,MATCH("h_ref",Textes!$A$2:$A$52,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_ref",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="21" customHeight="1">
       <c r="B16" s="13">
-        <f>IF(AND('2 Matériel'!$M6&gt;0,NOT('2 Matériel'!$B6="Oui")),'2 Matériel'!$A6,"")</f>
+        <f>IF(AND('2 Matériel'!$L6&gt;0,NOT('2 Matériel'!$B6="Oui")),'2 Matériel'!$A6,"")</f>
         <v/>
       </c>
       <c r="C16" s="37">
-        <f>IF('2 Matériel'!$M6&gt;0,IF('2 Matériel'!$B6="Oui",UPPER('2 Matériel'!$C6),'2 Matériel'!$C6),"")</f>
+        <f>IF('2 Matériel'!$L6&gt;0,IF('2 Matériel'!$B6="Oui",UPPER('2 Matériel'!$C6),'2 Matériel'!$C6),"")</f>
         <v/>
       </c>
       <c r="D16" s="38">
-        <f>IF(AND('2 Matériel'!$M6&gt;0,NOT('2 Matériel'!$B6="Oui")),'2 Matériel'!$M6,"")</f>
+        <f>IF(AND('2 Matériel'!$L6&gt;0,NOT('2 Matériel'!$B6="Oui")),'2 Matériel'!$L6,"")</f>
         <v/>
       </c>
       <c r="E16" s="39">
-        <f>IF(AND('2 Matériel'!$M6&gt;0,NOT('2 Matériel'!$B6="Oui")),IF(AND('2 Matériel'!$L6="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$F6="","",'2 Matériel'!$F6)),"")</f>
+        <f>IF(AND('2 Matériel'!$L6&gt;0,NOT('2 Matériel'!$B6="Oui")),IF(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E6="","",'2 Matériel'!$E6)),"")</f>
         <v/>
       </c>
       <c r="F16" s="39">
-        <f>IF(AND('2 Matériel'!$M6&gt;0,NOT('2 Matériel'!$B6="Oui")),IF(AND('2 Matériel'!$L6="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$G6="","",'2 Matériel'!$G6)),"")</f>
+        <f>IF(AND('2 Matériel'!$L6&gt;0,NOT('2 Matériel'!$B6="Oui")),IF(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F6="","",'2 Matériel'!$F6)),"")</f>
         <v/>
       </c>
       <c r="G16" s="39">
-        <f>IF(AND('2 Matériel'!$M6&gt;0,NOT('2 Matériel'!$B6="Oui")),IF(AND('2 Matériel'!$L6="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$H6="","",'2 Matériel'!$H6)),"")</f>
+        <f>IF(AND('2 Matériel'!$L6&gt;0,NOT('2 Matériel'!$B6="Oui")),IF(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G6="","",'2 Matériel'!$G6)),"")</f>
         <v/>
       </c>
       <c r="H16" s="39">
-        <f>IF(AND('2 Matériel'!$M6&gt;0,NOT('2 Matériel'!$B6="Oui")),IF(AND('2 Matériel'!$L6="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$I6="","",'2 Matériel'!$I6)),"")</f>
+        <f>IF(AND('2 Matériel'!$L6&gt;0,NOT('2 Matériel'!$B6="Oui")),IF(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H6="","",'2 Matériel'!$H6)),"")</f>
         <v/>
       </c>
       <c r="I16" s="39">
-        <f>IF(AND('2 Matériel'!$M6&gt;0,NOT('2 Matériel'!$B6="Oui")),IF(AND('2 Matériel'!$L6="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$J6="","",'2 Matériel'!$J6)),"")</f>
+        <f>IF(AND('2 Matériel'!$L6&gt;0,NOT('2 Matériel'!$B6="Oui")),IF(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I6="","",'2 Matériel'!$I6)),"")</f>
         <v/>
       </c>
       <c r="J16" s="39">
-        <f>IF(AND('2 Matériel'!$M6&gt;0,NOT('2 Matériel'!$B6="Oui")),IF(AND('2 Matériel'!$L6="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$K6="","",'2 Matériel'!$K6)),"")</f>
+        <f>IF(AND('2 Matériel'!$L6&gt;0,NOT('2 Matériel'!$B6="Oui")),IF(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J6="","",'2 Matériel'!$J6)),"")</f>
         <v/>
       </c>
       <c r="K16" s="40">
-        <f>IF(AND('2 Matériel'!$M6&gt;0,NOT('2 Matériel'!$B6="Oui")),IF(AND('2 Matériel'!$L6="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl_long",Textes!$A$2:$A$52,0),Listes!$H$1),""),"")</f>
+        <f>IF(AND('2 Matériel'!$L6&gt;0,NOT('2 Matériel'!$B6="Oui")),IF(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
       <c r="M16" s="41">
-        <f>IF(AND('2 Matériel'!$M6&gt;0,'2 Matériel'!$B6="Oui"),1,0)</f>
+        <f>IF(AND('2 Matériel'!$L6&gt;0,'2 Matériel'!$B6="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
       <c r="B17" s="13">
-        <f>IF(AND('2 Matériel'!$M7&gt;0,NOT('2 Matériel'!$B7="Oui")),'2 Matériel'!$A7,"")</f>
+        <f>IF(AND('2 Matériel'!$L7&gt;0,NOT('2 Matériel'!$B7="Oui")),'2 Matériel'!$A7,"")</f>
         <v/>
       </c>
       <c r="C17" s="37">
-        <f>IF('2 Matériel'!$M7&gt;0,IF('2 Matériel'!$B7="Oui",UPPER('2 Matériel'!$C7),'2 Matériel'!$C7),"")</f>
+        <f>IF('2 Matériel'!$L7&gt;0,IF('2 Matériel'!$B7="Oui",UPPER('2 Matériel'!$C7),'2 Matériel'!$C7),"")</f>
         <v/>
       </c>
       <c r="D17" s="38">
-        <f>IF(AND('2 Matériel'!$M7&gt;0,NOT('2 Matériel'!$B7="Oui")),'2 Matériel'!$M7,"")</f>
+        <f>IF(AND('2 Matériel'!$L7&gt;0,NOT('2 Matériel'!$B7="Oui")),'2 Matériel'!$L7,"")</f>
         <v/>
       </c>
       <c r="E17" s="39">
-        <f>IF(AND('2 Matériel'!$M7&gt;0,NOT('2 Matériel'!$B7="Oui")),IF(AND('2 Matériel'!$L7="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$F7="","",'2 Matériel'!$F7)),"")</f>
+        <f>IF(AND('2 Matériel'!$L7&gt;0,NOT('2 Matériel'!$B7="Oui")),IF(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E7="","",'2 Matériel'!$E7)),"")</f>
         <v/>
       </c>
       <c r="F17" s="39">
-        <f>IF(AND('2 Matériel'!$M7&gt;0,NOT('2 Matériel'!$B7="Oui")),IF(AND('2 Matériel'!$L7="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$G7="","",'2 Matériel'!$G7)),"")</f>
+        <f>IF(AND('2 Matériel'!$L7&gt;0,NOT('2 Matériel'!$B7="Oui")),IF(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F7="","",'2 Matériel'!$F7)),"")</f>
         <v/>
       </c>
       <c r="G17" s="39">
-        <f>IF(AND('2 Matériel'!$M7&gt;0,NOT('2 Matériel'!$B7="Oui")),IF(AND('2 Matériel'!$L7="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$H7="","",'2 Matériel'!$H7)),"")</f>
+        <f>IF(AND('2 Matériel'!$L7&gt;0,NOT('2 Matériel'!$B7="Oui")),IF(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G7="","",'2 Matériel'!$G7)),"")</f>
         <v/>
       </c>
       <c r="H17" s="39">
-        <f>IF(AND('2 Matériel'!$M7&gt;0,NOT('2 Matériel'!$B7="Oui")),IF(AND('2 Matériel'!$L7="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$I7="","",'2 Matériel'!$I7)),"")</f>
+        <f>IF(AND('2 Matériel'!$L7&gt;0,NOT('2 Matériel'!$B7="Oui")),IF(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H7="","",'2 Matériel'!$H7)),"")</f>
         <v/>
       </c>
       <c r="I17" s="39">
-        <f>IF(AND('2 Matériel'!$M7&gt;0,NOT('2 Matériel'!$B7="Oui")),IF(AND('2 Matériel'!$L7="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$J7="","",'2 Matériel'!$J7)),"")</f>
+        <f>IF(AND('2 Matériel'!$L7&gt;0,NOT('2 Matériel'!$B7="Oui")),IF(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I7="","",'2 Matériel'!$I7)),"")</f>
         <v/>
       </c>
       <c r="J17" s="39">
-        <f>IF(AND('2 Matériel'!$M7&gt;0,NOT('2 Matériel'!$B7="Oui")),IF(AND('2 Matériel'!$L7="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$K7="","",'2 Matériel'!$K7)),"")</f>
+        <f>IF(AND('2 Matériel'!$L7&gt;0,NOT('2 Matériel'!$B7="Oui")),IF(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J7="","",'2 Matériel'!$J7)),"")</f>
         <v/>
       </c>
       <c r="K17" s="40">
-        <f>IF(AND('2 Matériel'!$M7&gt;0,NOT('2 Matériel'!$B7="Oui")),IF(AND('2 Matériel'!$L7="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl_long",Textes!$A$2:$A$52,0),Listes!$H$1),""),"")</f>
+        <f>IF(AND('2 Matériel'!$L7&gt;0,NOT('2 Matériel'!$B7="Oui")),IF(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
       <c r="M17" s="41">
-        <f>IF(AND('2 Matériel'!$M7&gt;0,'2 Matériel'!$B7="Oui"),1,0)</f>
+        <f>IF(AND('2 Matériel'!$L7&gt;0,'2 Matériel'!$B7="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
       <c r="B18" s="13">
-        <f>IF(AND('2 Matériel'!$M8&gt;0,NOT('2 Matériel'!$B8="Oui")),'2 Matériel'!$A8,"")</f>
+        <f>IF(AND('2 Matériel'!$L8&gt;0,NOT('2 Matériel'!$B8="Oui")),'2 Matériel'!$A8,"")</f>
         <v/>
       </c>
       <c r="C18" s="37">
-        <f>IF('2 Matériel'!$M8&gt;0,IF('2 Matériel'!$B8="Oui",UPPER('2 Matériel'!$C8),'2 Matériel'!$C8),"")</f>
+        <f>IF('2 Matériel'!$L8&gt;0,IF('2 Matériel'!$B8="Oui",UPPER('2 Matériel'!$C8),'2 Matériel'!$C8),"")</f>
         <v/>
       </c>
       <c r="D18" s="38">
-        <f>IF(AND('2 Matériel'!$M8&gt;0,NOT('2 Matériel'!$B8="Oui")),'2 Matériel'!$M8,"")</f>
+        <f>IF(AND('2 Matériel'!$L8&gt;0,NOT('2 Matériel'!$B8="Oui")),'2 Matériel'!$L8,"")</f>
         <v/>
       </c>
       <c r="E18" s="39">
-        <f>IF(AND('2 Matériel'!$M8&gt;0,NOT('2 Matériel'!$B8="Oui")),IF(AND('2 Matériel'!$L8="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$F8="","",'2 Matériel'!$F8)),"")</f>
+        <f>IF(AND('2 Matériel'!$L8&gt;0,NOT('2 Matériel'!$B8="Oui")),IF(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E8="","",'2 Matériel'!$E8)),"")</f>
         <v/>
       </c>
       <c r="F18" s="39">
-        <f>IF(AND('2 Matériel'!$M8&gt;0,NOT('2 Matériel'!$B8="Oui")),IF(AND('2 Matériel'!$L8="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$G8="","",'2 Matériel'!$G8)),"")</f>
+        <f>IF(AND('2 Matériel'!$L8&gt;0,NOT('2 Matériel'!$B8="Oui")),IF(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F8="","",'2 Matériel'!$F8)),"")</f>
         <v/>
       </c>
       <c r="G18" s="39">
-        <f>IF(AND('2 Matériel'!$M8&gt;0,NOT('2 Matériel'!$B8="Oui")),IF(AND('2 Matériel'!$L8="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$H8="","",'2 Matériel'!$H8)),"")</f>
+        <f>IF(AND('2 Matériel'!$L8&gt;0,NOT('2 Matériel'!$B8="Oui")),IF(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G8="","",'2 Matériel'!$G8)),"")</f>
         <v/>
       </c>
       <c r="H18" s="39">
-        <f>IF(AND('2 Matériel'!$M8&gt;0,NOT('2 Matériel'!$B8="Oui")),IF(AND('2 Matériel'!$L8="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$I8="","",'2 Matériel'!$I8)),"")</f>
+        <f>IF(AND('2 Matériel'!$L8&gt;0,NOT('2 Matériel'!$B8="Oui")),IF(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H8="","",'2 Matériel'!$H8)),"")</f>
         <v/>
       </c>
       <c r="I18" s="39">
-        <f>IF(AND('2 Matériel'!$M8&gt;0,NOT('2 Matériel'!$B8="Oui")),IF(AND('2 Matériel'!$L8="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$J8="","",'2 Matériel'!$J8)),"")</f>
+        <f>IF(AND('2 Matériel'!$L8&gt;0,NOT('2 Matériel'!$B8="Oui")),IF(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I8="","",'2 Matériel'!$I8)),"")</f>
         <v/>
       </c>
       <c r="J18" s="39">
-        <f>IF(AND('2 Matériel'!$M8&gt;0,NOT('2 Matériel'!$B8="Oui")),IF(AND('2 Matériel'!$L8="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$K8="","",'2 Matériel'!$K8)),"")</f>
+        <f>IF(AND('2 Matériel'!$L8&gt;0,NOT('2 Matériel'!$B8="Oui")),IF(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J8="","",'2 Matériel'!$J8)),"")</f>
         <v/>
       </c>
       <c r="K18" s="40">
-        <f>IF(AND('2 Matériel'!$M8&gt;0,NOT('2 Matériel'!$B8="Oui")),IF(AND('2 Matériel'!$L8="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl_long",Textes!$A$2:$A$52,0),Listes!$H$1),""),"")</f>
+        <f>IF(AND('2 Matériel'!$L8&gt;0,NOT('2 Matériel'!$B8="Oui")),IF(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
       <c r="M18" s="41">
-        <f>IF(AND('2 Matériel'!$M8&gt;0,'2 Matériel'!$B8="Oui"),1,0)</f>
+        <f>IF(AND('2 Matériel'!$L8&gt;0,'2 Matériel'!$B8="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="21" customHeight="1">
       <c r="B19" s="13">
-        <f>IF(AND('2 Matériel'!$M9&gt;0,NOT('2 Matériel'!$B9="Oui")),'2 Matériel'!$A9,"")</f>
+        <f>IF(AND('2 Matériel'!$L9&gt;0,NOT('2 Matériel'!$B9="Oui")),'2 Matériel'!$A9,"")</f>
         <v/>
       </c>
       <c r="C19" s="37">
-        <f>IF('2 Matériel'!$M9&gt;0,IF('2 Matériel'!$B9="Oui",UPPER('2 Matériel'!$C9),'2 Matériel'!$C9),"")</f>
+        <f>IF('2 Matériel'!$L9&gt;0,IF('2 Matériel'!$B9="Oui",UPPER('2 Matériel'!$C9),'2 Matériel'!$C9),"")</f>
         <v/>
       </c>
       <c r="D19" s="38">
-        <f>IF(AND('2 Matériel'!$M9&gt;0,NOT('2 Matériel'!$B9="Oui")),'2 Matériel'!$M9,"")</f>
+        <f>IF(AND('2 Matériel'!$L9&gt;0,NOT('2 Matériel'!$B9="Oui")),'2 Matériel'!$L9,"")</f>
         <v/>
       </c>
       <c r="E19" s="39">
-        <f>IF(AND('2 Matériel'!$M9&gt;0,NOT('2 Matériel'!$B9="Oui")),IF(AND('2 Matériel'!$L9="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$F9="","",'2 Matériel'!$F9)),"")</f>
+        <f>IF(AND('2 Matériel'!$L9&gt;0,NOT('2 Matériel'!$B9="Oui")),IF(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E9="","",'2 Matériel'!$E9)),"")</f>
         <v/>
       </c>
       <c r="F19" s="39">
-        <f>IF(AND('2 Matériel'!$M9&gt;0,NOT('2 Matériel'!$B9="Oui")),IF(AND('2 Matériel'!$L9="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$G9="","",'2 Matériel'!$G9)),"")</f>
+        <f>IF(AND('2 Matériel'!$L9&gt;0,NOT('2 Matériel'!$B9="Oui")),IF(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F9="","",'2 Matériel'!$F9)),"")</f>
         <v/>
       </c>
       <c r="G19" s="39">
-        <f>IF(AND('2 Matériel'!$M9&gt;0,NOT('2 Matériel'!$B9="Oui")),IF(AND('2 Matériel'!$L9="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$H9="","",'2 Matériel'!$H9)),"")</f>
+        <f>IF(AND('2 Matériel'!$L9&gt;0,NOT('2 Matériel'!$B9="Oui")),IF(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G9="","",'2 Matériel'!$G9)),"")</f>
         <v/>
       </c>
       <c r="H19" s="39">
-        <f>IF(AND('2 Matériel'!$M9&gt;0,NOT('2 Matériel'!$B9="Oui")),IF(AND('2 Matériel'!$L9="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$I9="","",'2 Matériel'!$I9)),"")</f>
+        <f>IF(AND('2 Matériel'!$L9&gt;0,NOT('2 Matériel'!$B9="Oui")),IF(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H9="","",'2 Matériel'!$H9)),"")</f>
         <v/>
       </c>
       <c r="I19" s="39">
-        <f>IF(AND('2 Matériel'!$M9&gt;0,NOT('2 Matériel'!$B9="Oui")),IF(AND('2 Matériel'!$L9="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$J9="","",'2 Matériel'!$J9)),"")</f>
+        <f>IF(AND('2 Matériel'!$L9&gt;0,NOT('2 Matériel'!$B9="Oui")),IF(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I9="","",'2 Matériel'!$I9)),"")</f>
         <v/>
       </c>
       <c r="J19" s="39">
-        <f>IF(AND('2 Matériel'!$M9&gt;0,NOT('2 Matériel'!$B9="Oui")),IF(AND('2 Matériel'!$L9="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$K9="","",'2 Matériel'!$K9)),"")</f>
+        <f>IF(AND('2 Matériel'!$L9&gt;0,NOT('2 Matériel'!$B9="Oui")),IF(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J9="","",'2 Matériel'!$J9)),"")</f>
         <v/>
       </c>
       <c r="K19" s="40">
-        <f>IF(AND('2 Matériel'!$M9&gt;0,NOT('2 Matériel'!$B9="Oui")),IF(AND('2 Matériel'!$L9="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl_long",Textes!$A$2:$A$52,0),Listes!$H$1),""),"")</f>
+        <f>IF(AND('2 Matériel'!$L9&gt;0,NOT('2 Matériel'!$B9="Oui")),IF(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
       <c r="M19" s="41">
-        <f>IF(AND('2 Matériel'!$M9&gt;0,'2 Matériel'!$B9="Oui"),1,0)</f>
+        <f>IF(AND('2 Matériel'!$L9&gt;0,'2 Matériel'!$B9="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="21" customHeight="1">
       <c r="B20" s="13">
-        <f>IF(AND('2 Matériel'!$M10&gt;0,NOT('2 Matériel'!$B10="Oui")),'2 Matériel'!$A10,"")</f>
+        <f>IF(AND('2 Matériel'!$L10&gt;0,NOT('2 Matériel'!$B10="Oui")),'2 Matériel'!$A10,"")</f>
         <v/>
       </c>
       <c r="C20" s="37">
-        <f>IF('2 Matériel'!$M10&gt;0,IF('2 Matériel'!$B10="Oui",UPPER('2 Matériel'!$C10),'2 Matériel'!$C10),"")</f>
+        <f>IF('2 Matériel'!$L10&gt;0,IF('2 Matériel'!$B10="Oui",UPPER('2 Matériel'!$C10),'2 Matériel'!$C10),"")</f>
         <v/>
       </c>
       <c r="D20" s="38">
-        <f>IF(AND('2 Matériel'!$M10&gt;0,NOT('2 Matériel'!$B10="Oui")),'2 Matériel'!$M10,"")</f>
+        <f>IF(AND('2 Matériel'!$L10&gt;0,NOT('2 Matériel'!$B10="Oui")),'2 Matériel'!$L10,"")</f>
         <v/>
       </c>
       <c r="E20" s="39">
-        <f>IF(AND('2 Matériel'!$M10&gt;0,NOT('2 Matériel'!$B10="Oui")),IF(AND('2 Matériel'!$L10="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$F10="","",'2 Matériel'!$F10)),"")</f>
+        <f>IF(AND('2 Matériel'!$L10&gt;0,NOT('2 Matériel'!$B10="Oui")),IF(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E10="","",'2 Matériel'!$E10)),"")</f>
         <v/>
       </c>
       <c r="F20" s="39">
-        <f>IF(AND('2 Matériel'!$M10&gt;0,NOT('2 Matériel'!$B10="Oui")),IF(AND('2 Matériel'!$L10="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$G10="","",'2 Matériel'!$G10)),"")</f>
+        <f>IF(AND('2 Matériel'!$L10&gt;0,NOT('2 Matériel'!$B10="Oui")),IF(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F10="","",'2 Matériel'!$F10)),"")</f>
         <v/>
       </c>
       <c r="G20" s="39">
-        <f>IF(AND('2 Matériel'!$M10&gt;0,NOT('2 Matériel'!$B10="Oui")),IF(AND('2 Matériel'!$L10="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$H10="","",'2 Matériel'!$H10)),"")</f>
+        <f>IF(AND('2 Matériel'!$L10&gt;0,NOT('2 Matériel'!$B10="Oui")),IF(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G10="","",'2 Matériel'!$G10)),"")</f>
         <v/>
       </c>
       <c r="H20" s="39">
-        <f>IF(AND('2 Matériel'!$M10&gt;0,NOT('2 Matériel'!$B10="Oui")),IF(AND('2 Matériel'!$L10="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$I10="","",'2 Matériel'!$I10)),"")</f>
+        <f>IF(AND('2 Matériel'!$L10&gt;0,NOT('2 Matériel'!$B10="Oui")),IF(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H10="","",'2 Matériel'!$H10)),"")</f>
         <v/>
       </c>
       <c r="I20" s="39">
-        <f>IF(AND('2 Matériel'!$M10&gt;0,NOT('2 Matériel'!$B10="Oui")),IF(AND('2 Matériel'!$L10="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$J10="","",'2 Matériel'!$J10)),"")</f>
+        <f>IF(AND('2 Matériel'!$L10&gt;0,NOT('2 Matériel'!$B10="Oui")),IF(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I10="","",'2 Matériel'!$I10)),"")</f>
         <v/>
       </c>
       <c r="J20" s="39">
-        <f>IF(AND('2 Matériel'!$M10&gt;0,NOT('2 Matériel'!$B10="Oui")),IF(AND('2 Matériel'!$L10="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$K10="","",'2 Matériel'!$K10)),"")</f>
+        <f>IF(AND('2 Matériel'!$L10&gt;0,NOT('2 Matériel'!$B10="Oui")),IF(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J10="","",'2 Matériel'!$J10)),"")</f>
         <v/>
       </c>
       <c r="K20" s="40">
-        <f>IF(AND('2 Matériel'!$M10&gt;0,NOT('2 Matériel'!$B10="Oui")),IF(AND('2 Matériel'!$L10="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl_long",Textes!$A$2:$A$52,0),Listes!$H$1),""),"")</f>
+        <f>IF(AND('2 Matériel'!$L10&gt;0,NOT('2 Matériel'!$B10="Oui")),IF(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
       <c r="M20" s="41">
-        <f>IF(AND('2 Matériel'!$M10&gt;0,'2 Matériel'!$B10="Oui"),1,0)</f>
+        <f>IF(AND('2 Matériel'!$L10&gt;0,'2 Matériel'!$B10="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="21" customHeight="1">
       <c r="B21" s="13">
-        <f>IF(AND('2 Matériel'!$M11&gt;0,NOT('2 Matériel'!$B11="Oui")),'2 Matériel'!$A11,"")</f>
+        <f>IF(AND('2 Matériel'!$L11&gt;0,NOT('2 Matériel'!$B11="Oui")),'2 Matériel'!$A11,"")</f>
         <v/>
       </c>
       <c r="C21" s="37">
-        <f>IF('2 Matériel'!$M11&gt;0,IF('2 Matériel'!$B11="Oui",UPPER('2 Matériel'!$C11),'2 Matériel'!$C11),"")</f>
+        <f>IF('2 Matériel'!$L11&gt;0,IF('2 Matériel'!$B11="Oui",UPPER('2 Matériel'!$C11),'2 Matériel'!$C11),"")</f>
         <v/>
       </c>
       <c r="D21" s="38">
-        <f>IF(AND('2 Matériel'!$M11&gt;0,NOT('2 Matériel'!$B11="Oui")),'2 Matériel'!$M11,"")</f>
+        <f>IF(AND('2 Matériel'!$L11&gt;0,NOT('2 Matériel'!$B11="Oui")),'2 Matériel'!$L11,"")</f>
         <v/>
       </c>
       <c r="E21" s="39">
-        <f>IF(AND('2 Matériel'!$M11&gt;0,NOT('2 Matériel'!$B11="Oui")),IF(AND('2 Matériel'!$L11="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$F11="","",'2 Matériel'!$F11)),"")</f>
+        <f>IF(AND('2 Matériel'!$L11&gt;0,NOT('2 Matériel'!$B11="Oui")),IF(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E11="","",'2 Matériel'!$E11)),"")</f>
         <v/>
       </c>
       <c r="F21" s="39">
-        <f>IF(AND('2 Matériel'!$M11&gt;0,NOT('2 Matériel'!$B11="Oui")),IF(AND('2 Matériel'!$L11="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$G11="","",'2 Matériel'!$G11)),"")</f>
+        <f>IF(AND('2 Matériel'!$L11&gt;0,NOT('2 Matériel'!$B11="Oui")),IF(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F11="","",'2 Matériel'!$F11)),"")</f>
         <v/>
       </c>
       <c r="G21" s="39">
-        <f>IF(AND('2 Matériel'!$M11&gt;0,NOT('2 Matériel'!$B11="Oui")),IF(AND('2 Matériel'!$L11="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$H11="","",'2 Matériel'!$H11)),"")</f>
+        <f>IF(AND('2 Matériel'!$L11&gt;0,NOT('2 Matériel'!$B11="Oui")),IF(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G11="","",'2 Matériel'!$G11)),"")</f>
         <v/>
       </c>
       <c r="H21" s="39">
-        <f>IF(AND('2 Matériel'!$M11&gt;0,NOT('2 Matériel'!$B11="Oui")),IF(AND('2 Matériel'!$L11="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$I11="","",'2 Matériel'!$I11)),"")</f>
+        <f>IF(AND('2 Matériel'!$L11&gt;0,NOT('2 Matériel'!$B11="Oui")),IF(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H11="","",'2 Matériel'!$H11)),"")</f>
         <v/>
       </c>
       <c r="I21" s="39">
-        <f>IF(AND('2 Matériel'!$M11&gt;0,NOT('2 Matériel'!$B11="Oui")),IF(AND('2 Matériel'!$L11="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$J11="","",'2 Matériel'!$J11)),"")</f>
+        <f>IF(AND('2 Matériel'!$L11&gt;0,NOT('2 Matériel'!$B11="Oui")),IF(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I11="","",'2 Matériel'!$I11)),"")</f>
         <v/>
       </c>
       <c r="J21" s="39">
-        <f>IF(AND('2 Matériel'!$M11&gt;0,NOT('2 Matériel'!$B11="Oui")),IF(AND('2 Matériel'!$L11="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$K11="","",'2 Matériel'!$K11)),"")</f>
+        <f>IF(AND('2 Matériel'!$L11&gt;0,NOT('2 Matériel'!$B11="Oui")),IF(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J11="","",'2 Matériel'!$J11)),"")</f>
         <v/>
       </c>
       <c r="K21" s="40">
-        <f>IF(AND('2 Matériel'!$M11&gt;0,NOT('2 Matériel'!$B11="Oui")),IF(AND('2 Matériel'!$L11="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl_long",Textes!$A$2:$A$52,0),Listes!$H$1),""),"")</f>
+        <f>IF(AND('2 Matériel'!$L11&gt;0,NOT('2 Matériel'!$B11="Oui")),IF(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
       <c r="M21" s="41">
-        <f>IF(AND('2 Matériel'!$M11&gt;0,'2 Matériel'!$B11="Oui"),1,0)</f>
+        <f>IF(AND('2 Matériel'!$L11&gt;0,'2 Matériel'!$B11="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="21" customHeight="1">
       <c r="B22" s="13">
-        <f>IF(AND('2 Matériel'!$M12&gt;0,NOT('2 Matériel'!$B12="Oui")),'2 Matériel'!$A12,"")</f>
+        <f>IF(AND('2 Matériel'!$L12&gt;0,NOT('2 Matériel'!$B12="Oui")),'2 Matériel'!$A12,"")</f>
         <v/>
       </c>
       <c r="C22" s="37">
-        <f>IF('2 Matériel'!$M12&gt;0,IF('2 Matériel'!$B12="Oui",UPPER('2 Matériel'!$C12),'2 Matériel'!$C12),"")</f>
+        <f>IF('2 Matériel'!$L12&gt;0,IF('2 Matériel'!$B12="Oui",UPPER('2 Matériel'!$C12),'2 Matériel'!$C12),"")</f>
         <v/>
       </c>
       <c r="D22" s="38">
-        <f>IF(AND('2 Matériel'!$M12&gt;0,NOT('2 Matériel'!$B12="Oui")),'2 Matériel'!$M12,"")</f>
+        <f>IF(AND('2 Matériel'!$L12&gt;0,NOT('2 Matériel'!$B12="Oui")),'2 Matériel'!$L12,"")</f>
         <v/>
       </c>
       <c r="E22" s="39">
-        <f>IF(AND('2 Matériel'!$M12&gt;0,NOT('2 Matériel'!$B12="Oui")),IF(AND('2 Matériel'!$L12="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$F12="","",'2 Matériel'!$F12)),"")</f>
+        <f>IF(AND('2 Matériel'!$L12&gt;0,NOT('2 Matériel'!$B12="Oui")),IF(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E12="","",'2 Matériel'!$E12)),"")</f>
         <v/>
       </c>
       <c r="F22" s="39">
-        <f>IF(AND('2 Matériel'!$M12&gt;0,NOT('2 Matériel'!$B12="Oui")),IF(AND('2 Matériel'!$L12="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$G12="","",'2 Matériel'!$G12)),"")</f>
+        <f>IF(AND('2 Matériel'!$L12&gt;0,NOT('2 Matériel'!$B12="Oui")),IF(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F12="","",'2 Matériel'!$F12)),"")</f>
         <v/>
       </c>
       <c r="G22" s="39">
-        <f>IF(AND('2 Matériel'!$M12&gt;0,NOT('2 Matériel'!$B12="Oui")),IF(AND('2 Matériel'!$L12="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$H12="","",'2 Matériel'!$H12)),"")</f>
+        <f>IF(AND('2 Matériel'!$L12&gt;0,NOT('2 Matériel'!$B12="Oui")),IF(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G12="","",'2 Matériel'!$G12)),"")</f>
         <v/>
       </c>
       <c r="H22" s="39">
-        <f>IF(AND('2 Matériel'!$M12&gt;0,NOT('2 Matériel'!$B12="Oui")),IF(AND('2 Matériel'!$L12="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$I12="","",'2 Matériel'!$I12)),"")</f>
+        <f>IF(AND('2 Matériel'!$L12&gt;0,NOT('2 Matériel'!$B12="Oui")),IF(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H12="","",'2 Matériel'!$H12)),"")</f>
         <v/>
       </c>
       <c r="I22" s="39">
-        <f>IF(AND('2 Matériel'!$M12&gt;0,NOT('2 Matériel'!$B12="Oui")),IF(AND('2 Matériel'!$L12="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$J12="","",'2 Matériel'!$J12)),"")</f>
+        <f>IF(AND('2 Matériel'!$L12&gt;0,NOT('2 Matériel'!$B12="Oui")),IF(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I12="","",'2 Matériel'!$I12)),"")</f>
         <v/>
       </c>
       <c r="J22" s="39">
-        <f>IF(AND('2 Matériel'!$M12&gt;0,NOT('2 Matériel'!$B12="Oui")),IF(AND('2 Matériel'!$L12="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$K12="","",'2 Matériel'!$K12)),"")</f>
+        <f>IF(AND('2 Matériel'!$L12&gt;0,NOT('2 Matériel'!$B12="Oui")),IF(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J12="","",'2 Matériel'!$J12)),"")</f>
         <v/>
       </c>
       <c r="K22" s="40">
-        <f>IF(AND('2 Matériel'!$M12&gt;0,NOT('2 Matériel'!$B12="Oui")),IF(AND('2 Matériel'!$L12="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl_long",Textes!$A$2:$A$52,0),Listes!$H$1),""),"")</f>
+        <f>IF(AND('2 Matériel'!$L12&gt;0,NOT('2 Matériel'!$B12="Oui")),IF(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
       <c r="M22" s="41">
-        <f>IF(AND('2 Matériel'!$M12&gt;0,'2 Matériel'!$B12="Oui"),1,0)</f>
+        <f>IF(AND('2 Matériel'!$L12&gt;0,'2 Matériel'!$B12="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="21" customHeight="1">
       <c r="B23" s="13">
-        <f>IF(AND('2 Matériel'!$M13&gt;0,NOT('2 Matériel'!$B13="Oui")),'2 Matériel'!$A13,"")</f>
+        <f>IF(AND('2 Matériel'!$L13&gt;0,NOT('2 Matériel'!$B13="Oui")),'2 Matériel'!$A13,"")</f>
         <v/>
       </c>
       <c r="C23" s="37">
-        <f>IF('2 Matériel'!$M13&gt;0,IF('2 Matériel'!$B13="Oui",UPPER('2 Matériel'!$C13),'2 Matériel'!$C13),"")</f>
+        <f>IF('2 Matériel'!$L13&gt;0,IF('2 Matériel'!$B13="Oui",UPPER('2 Matériel'!$C13),'2 Matériel'!$C13),"")</f>
         <v/>
       </c>
       <c r="D23" s="38">
-        <f>IF(AND('2 Matériel'!$M13&gt;0,NOT('2 Matériel'!$B13="Oui")),'2 Matériel'!$M13,"")</f>
+        <f>IF(AND('2 Matériel'!$L13&gt;0,NOT('2 Matériel'!$B13="Oui")),'2 Matériel'!$L13,"")</f>
         <v/>
       </c>
       <c r="E23" s="39">
-        <f>IF(AND('2 Matériel'!$M13&gt;0,NOT('2 Matériel'!$B13="Oui")),IF(AND('2 Matériel'!$L13="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$F13="","",'2 Matériel'!$F13)),"")</f>
+        <f>IF(AND('2 Matériel'!$L13&gt;0,NOT('2 Matériel'!$B13="Oui")),IF(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E13="","",'2 Matériel'!$E13)),"")</f>
         <v/>
       </c>
       <c r="F23" s="39">
-        <f>IF(AND('2 Matériel'!$M13&gt;0,NOT('2 Matériel'!$B13="Oui")),IF(AND('2 Matériel'!$L13="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$G13="","",'2 Matériel'!$G13)),"")</f>
+        <f>IF(AND('2 Matériel'!$L13&gt;0,NOT('2 Matériel'!$B13="Oui")),IF(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F13="","",'2 Matériel'!$F13)),"")</f>
         <v/>
       </c>
       <c r="G23" s="39">
-        <f>IF(AND('2 Matériel'!$M13&gt;0,NOT('2 Matériel'!$B13="Oui")),IF(AND('2 Matériel'!$L13="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$H13="","",'2 Matériel'!$H13)),"")</f>
+        <f>IF(AND('2 Matériel'!$L13&gt;0,NOT('2 Matériel'!$B13="Oui")),IF(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G13="","",'2 Matériel'!$G13)),"")</f>
         <v/>
       </c>
       <c r="H23" s="39">
-        <f>IF(AND('2 Matériel'!$M13&gt;0,NOT('2 Matériel'!$B13="Oui")),IF(AND('2 Matériel'!$L13="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$I13="","",'2 Matériel'!$I13)),"")</f>
+        <f>IF(AND('2 Matériel'!$L13&gt;0,NOT('2 Matériel'!$B13="Oui")),IF(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H13="","",'2 Matériel'!$H13)),"")</f>
         <v/>
       </c>
       <c r="I23" s="39">
-        <f>IF(AND('2 Matériel'!$M13&gt;0,NOT('2 Matériel'!$B13="Oui")),IF(AND('2 Matériel'!$L13="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$J13="","",'2 Matériel'!$J13)),"")</f>
+        <f>IF(AND('2 Matériel'!$L13&gt;0,NOT('2 Matériel'!$B13="Oui")),IF(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I13="","",'2 Matériel'!$I13)),"")</f>
         <v/>
       </c>
       <c r="J23" s="39">
-        <f>IF(AND('2 Matériel'!$M13&gt;0,NOT('2 Matériel'!$B13="Oui")),IF(AND('2 Matériel'!$L13="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$K13="","",'2 Matériel'!$K13)),"")</f>
+        <f>IF(AND('2 Matériel'!$L13&gt;0,NOT('2 Matériel'!$B13="Oui")),IF(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J13="","",'2 Matériel'!$J13)),"")</f>
         <v/>
       </c>
       <c r="K23" s="40">
-        <f>IF(AND('2 Matériel'!$M13&gt;0,NOT('2 Matériel'!$B13="Oui")),IF(AND('2 Matériel'!$L13="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl_long",Textes!$A$2:$A$52,0),Listes!$H$1),""),"")</f>
+        <f>IF(AND('2 Matériel'!$L13&gt;0,NOT('2 Matériel'!$B13="Oui")),IF(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
       <c r="M23" s="41">
-        <f>IF(AND('2 Matériel'!$M13&gt;0,'2 Matériel'!$B13="Oui"),1,0)</f>
+        <f>IF(AND('2 Matériel'!$L13&gt;0,'2 Matériel'!$B13="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="21" customHeight="1">
       <c r="B24" s="13">
-        <f>IF(AND('2 Matériel'!$M14&gt;0,NOT('2 Matériel'!$B14="Oui")),'2 Matériel'!$A14,"")</f>
+        <f>IF(AND('2 Matériel'!$L14&gt;0,NOT('2 Matériel'!$B14="Oui")),'2 Matériel'!$A14,"")</f>
         <v/>
       </c>
       <c r="C24" s="37">
-        <f>IF('2 Matériel'!$M14&gt;0,IF('2 Matériel'!$B14="Oui",UPPER('2 Matériel'!$C14),'2 Matériel'!$C14),"")</f>
+        <f>IF('2 Matériel'!$L14&gt;0,IF('2 Matériel'!$B14="Oui",UPPER('2 Matériel'!$C14),'2 Matériel'!$C14),"")</f>
         <v/>
       </c>
       <c r="D24" s="38">
-        <f>IF(AND('2 Matériel'!$M14&gt;0,NOT('2 Matériel'!$B14="Oui")),'2 Matériel'!$M14,"")</f>
+        <f>IF(AND('2 Matériel'!$L14&gt;0,NOT('2 Matériel'!$B14="Oui")),'2 Matériel'!$L14,"")</f>
         <v/>
       </c>
       <c r="E24" s="39">
-        <f>IF(AND('2 Matériel'!$M14&gt;0,NOT('2 Matériel'!$B14="Oui")),IF(AND('2 Matériel'!$L14="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$F14="","",'2 Matériel'!$F14)),"")</f>
+        <f>IF(AND('2 Matériel'!$L14&gt;0,NOT('2 Matériel'!$B14="Oui")),IF(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E14="","",'2 Matériel'!$E14)),"")</f>
         <v/>
       </c>
       <c r="F24" s="39">
-        <f>IF(AND('2 Matériel'!$M14&gt;0,NOT('2 Matériel'!$B14="Oui")),IF(AND('2 Matériel'!$L14="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$G14="","",'2 Matériel'!$G14)),"")</f>
+        <f>IF(AND('2 Matériel'!$L14&gt;0,NOT('2 Matériel'!$B14="Oui")),IF(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F14="","",'2 Matériel'!$F14)),"")</f>
         <v/>
       </c>
       <c r="G24" s="39">
-        <f>IF(AND('2 Matériel'!$M14&gt;0,NOT('2 Matériel'!$B14="Oui")),IF(AND('2 Matériel'!$L14="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$H14="","",'2 Matériel'!$H14)),"")</f>
+        <f>IF(AND('2 Matériel'!$L14&gt;0,NOT('2 Matériel'!$B14="Oui")),IF(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G14="","",'2 Matériel'!$G14)),"")</f>
         <v/>
       </c>
       <c r="H24" s="39">
-        <f>IF(AND('2 Matériel'!$M14&gt;0,NOT('2 Matériel'!$B14="Oui")),IF(AND('2 Matériel'!$L14="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$I14="","",'2 Matériel'!$I14)),"")</f>
+        <f>IF(AND('2 Matériel'!$L14&gt;0,NOT('2 Matériel'!$B14="Oui")),IF(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H14="","",'2 Matériel'!$H14)),"")</f>
         <v/>
       </c>
       <c r="I24" s="39">
-        <f>IF(AND('2 Matériel'!$M14&gt;0,NOT('2 Matériel'!$B14="Oui")),IF(AND('2 Matériel'!$L14="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$J14="","",'2 Matériel'!$J14)),"")</f>
+        <f>IF(AND('2 Matériel'!$L14&gt;0,NOT('2 Matériel'!$B14="Oui")),IF(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I14="","",'2 Matériel'!$I14)),"")</f>
         <v/>
       </c>
       <c r="J24" s="39">
-        <f>IF(AND('2 Matériel'!$M14&gt;0,NOT('2 Matériel'!$B14="Oui")),IF(AND('2 Matériel'!$L14="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$K14="","",'2 Matériel'!$K14)),"")</f>
+        <f>IF(AND('2 Matériel'!$L14&gt;0,NOT('2 Matériel'!$B14="Oui")),IF(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J14="","",'2 Matériel'!$J14)),"")</f>
         <v/>
       </c>
       <c r="K24" s="40">
-        <f>IF(AND('2 Matériel'!$M14&gt;0,NOT('2 Matériel'!$B14="Oui")),IF(AND('2 Matériel'!$L14="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl_long",Textes!$A$2:$A$52,0),Listes!$H$1),""),"")</f>
+        <f>IF(AND('2 Matériel'!$L14&gt;0,NOT('2 Matériel'!$B14="Oui")),IF(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
       <c r="M24" s="41">
-        <f>IF(AND('2 Matériel'!$M14&gt;0,'2 Matériel'!$B14="Oui"),1,0)</f>
+        <f>IF(AND('2 Matériel'!$L14&gt;0,'2 Matériel'!$B14="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1">
       <c r="B25" s="13">
-        <f>IF(AND('2 Matériel'!$M15&gt;0,NOT('2 Matériel'!$B15="Oui")),'2 Matériel'!$A15,"")</f>
+        <f>IF(AND('2 Matériel'!$L15&gt;0,NOT('2 Matériel'!$B15="Oui")),'2 Matériel'!$A15,"")</f>
         <v/>
       </c>
       <c r="C25" s="37">
-        <f>IF('2 Matériel'!$M15&gt;0,IF('2 Matériel'!$B15="Oui",UPPER('2 Matériel'!$C15),'2 Matériel'!$C15),"")</f>
+        <f>IF('2 Matériel'!$L15&gt;0,IF('2 Matériel'!$B15="Oui",UPPER('2 Matériel'!$C15),'2 Matériel'!$C15),"")</f>
         <v/>
       </c>
       <c r="D25" s="38">
-        <f>IF(AND('2 Matériel'!$M15&gt;0,NOT('2 Matériel'!$B15="Oui")),'2 Matériel'!$M15,"")</f>
+        <f>IF(AND('2 Matériel'!$L15&gt;0,NOT('2 Matériel'!$B15="Oui")),'2 Matériel'!$L15,"")</f>
         <v/>
       </c>
       <c r="E25" s="39">
-        <f>IF(AND('2 Matériel'!$M15&gt;0,NOT('2 Matériel'!$B15="Oui")),IF(AND('2 Matériel'!$L15="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$F15="","",'2 Matériel'!$F15)),"")</f>
+        <f>IF(AND('2 Matériel'!$L15&gt;0,NOT('2 Matériel'!$B15="Oui")),IF(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E15="","",'2 Matériel'!$E15)),"")</f>
         <v/>
       </c>
       <c r="F25" s="39">
-        <f>IF(AND('2 Matériel'!$M15&gt;0,NOT('2 Matériel'!$B15="Oui")),IF(AND('2 Matériel'!$L15="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$G15="","",'2 Matériel'!$G15)),"")</f>
+        <f>IF(AND('2 Matériel'!$L15&gt;0,NOT('2 Matériel'!$B15="Oui")),IF(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F15="","",'2 Matériel'!$F15)),"")</f>
         <v/>
       </c>
       <c r="G25" s="39">
-        <f>IF(AND('2 Matériel'!$M15&gt;0,NOT('2 Matériel'!$B15="Oui")),IF(AND('2 Matériel'!$L15="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$H15="","",'2 Matériel'!$H15)),"")</f>
+        <f>IF(AND('2 Matériel'!$L15&gt;0,NOT('2 Matériel'!$B15="Oui")),IF(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G15="","",'2 Matériel'!$G15)),"")</f>
         <v/>
       </c>
       <c r="H25" s="39">
-        <f>IF(AND('2 Matériel'!$M15&gt;0,NOT('2 Matériel'!$B15="Oui")),IF(AND('2 Matériel'!$L15="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$I15="","",'2 Matériel'!$I15)),"")</f>
+        <f>IF(AND('2 Matériel'!$L15&gt;0,NOT('2 Matériel'!$B15="Oui")),IF(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H15="","",'2 Matériel'!$H15)),"")</f>
         <v/>
       </c>
       <c r="I25" s="39">
-        <f>IF(AND('2 Matériel'!$M15&gt;0,NOT('2 Matériel'!$B15="Oui")),IF(AND('2 Matériel'!$L15="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$J15="","",'2 Matériel'!$J15)),"")</f>
+        <f>IF(AND('2 Matériel'!$L15&gt;0,NOT('2 Matériel'!$B15="Oui")),IF(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I15="","",'2 Matériel'!$I15)),"")</f>
         <v/>
       </c>
       <c r="J25" s="39">
-        <f>IF(AND('2 Matériel'!$M15&gt;0,NOT('2 Matériel'!$B15="Oui")),IF(AND('2 Matériel'!$L15="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$K15="","",'2 Matériel'!$K15)),"")</f>
+        <f>IF(AND('2 Matériel'!$L15&gt;0,NOT('2 Matériel'!$B15="Oui")),IF(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J15="","",'2 Matériel'!$J15)),"")</f>
         <v/>
       </c>
       <c r="K25" s="40">
-        <f>IF(AND('2 Matériel'!$M15&gt;0,NOT('2 Matériel'!$B15="Oui")),IF(AND('2 Matériel'!$L15="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl_long",Textes!$A$2:$A$52,0),Listes!$H$1),""),"")</f>
+        <f>IF(AND('2 Matériel'!$L15&gt;0,NOT('2 Matériel'!$B15="Oui")),IF(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
       <c r="M25" s="41">
-        <f>IF(AND('2 Matériel'!$M15&gt;0,'2 Matériel'!$B15="Oui"),1,0)</f>
+        <f>IF(AND('2 Matériel'!$L15&gt;0,'2 Matériel'!$B15="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="21" customHeight="1">
       <c r="B26" s="13">
-        <f>IF(AND('2 Matériel'!$M16&gt;0,NOT('2 Matériel'!$B16="Oui")),'2 Matériel'!$A16,"")</f>
+        <f>IF(AND('2 Matériel'!$L16&gt;0,NOT('2 Matériel'!$B16="Oui")),'2 Matériel'!$A16,"")</f>
         <v/>
       </c>
       <c r="C26" s="37">
-        <f>IF('2 Matériel'!$M16&gt;0,IF('2 Matériel'!$B16="Oui",UPPER('2 Matériel'!$C16),'2 Matériel'!$C16),"")</f>
+        <f>IF('2 Matériel'!$L16&gt;0,IF('2 Matériel'!$B16="Oui",UPPER('2 Matériel'!$C16),'2 Matériel'!$C16),"")</f>
         <v/>
       </c>
       <c r="D26" s="38">
-        <f>IF(AND('2 Matériel'!$M16&gt;0,NOT('2 Matériel'!$B16="Oui")),'2 Matériel'!$M16,"")</f>
+        <f>IF(AND('2 Matériel'!$L16&gt;0,NOT('2 Matériel'!$B16="Oui")),'2 Matériel'!$L16,"")</f>
         <v/>
       </c>
       <c r="E26" s="39">
-        <f>IF(AND('2 Matériel'!$M16&gt;0,NOT('2 Matériel'!$B16="Oui")),IF(AND('2 Matériel'!$L16="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$F16="","",'2 Matériel'!$F16)),"")</f>
+        <f>IF(AND('2 Matériel'!$L16&gt;0,NOT('2 Matériel'!$B16="Oui")),IF(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E16="","",'2 Matériel'!$E16)),"")</f>
         <v/>
       </c>
       <c r="F26" s="39">
-        <f>IF(AND('2 Matériel'!$M16&gt;0,NOT('2 Matériel'!$B16="Oui")),IF(AND('2 Matériel'!$L16="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$G16="","",'2 Matériel'!$G16)),"")</f>
+        <f>IF(AND('2 Matériel'!$L16&gt;0,NOT('2 Matériel'!$B16="Oui")),IF(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F16="","",'2 Matériel'!$F16)),"")</f>
         <v/>
       </c>
       <c r="G26" s="39">
-        <f>IF(AND('2 Matériel'!$M16&gt;0,NOT('2 Matériel'!$B16="Oui")),IF(AND('2 Matériel'!$L16="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$H16="","",'2 Matériel'!$H16)),"")</f>
+        <f>IF(AND('2 Matériel'!$L16&gt;0,NOT('2 Matériel'!$B16="Oui")),IF(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G16="","",'2 Matériel'!$G16)),"")</f>
         <v/>
       </c>
       <c r="H26" s="39">
-        <f>IF(AND('2 Matériel'!$M16&gt;0,NOT('2 Matériel'!$B16="Oui")),IF(AND('2 Matériel'!$L16="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$I16="","",'2 Matériel'!$I16)),"")</f>
+        <f>IF(AND('2 Matériel'!$L16&gt;0,NOT('2 Matériel'!$B16="Oui")),IF(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H16="","",'2 Matériel'!$H16)),"")</f>
         <v/>
       </c>
       <c r="I26" s="39">
-        <f>IF(AND('2 Matériel'!$M16&gt;0,NOT('2 Matériel'!$B16="Oui")),IF(AND('2 Matériel'!$L16="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$J16="","",'2 Matériel'!$J16)),"")</f>
+        <f>IF(AND('2 Matériel'!$L16&gt;0,NOT('2 Matériel'!$B16="Oui")),IF(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I16="","",'2 Matériel'!$I16)),"")</f>
         <v/>
       </c>
       <c r="J26" s="39">
-        <f>IF(AND('2 Matériel'!$M16&gt;0,NOT('2 Matériel'!$B16="Oui")),IF(AND('2 Matériel'!$L16="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$K16="","",'2 Matériel'!$K16)),"")</f>
+        <f>IF(AND('2 Matériel'!$L16&gt;0,NOT('2 Matériel'!$B16="Oui")),IF(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J16="","",'2 Matériel'!$J16)),"")</f>
         <v/>
       </c>
       <c r="K26" s="40">
-        <f>IF(AND('2 Matériel'!$M16&gt;0,NOT('2 Matériel'!$B16="Oui")),IF(AND('2 Matériel'!$L16="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl_long",Textes!$A$2:$A$52,0),Listes!$H$1),""),"")</f>
+        <f>IF(AND('2 Matériel'!$L16&gt;0,NOT('2 Matériel'!$B16="Oui")),IF(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
       <c r="M26" s="41">
-        <f>IF(AND('2 Matériel'!$M16&gt;0,'2 Matériel'!$B16="Oui"),1,0)</f>
+        <f>IF(AND('2 Matériel'!$L16&gt;0,'2 Matériel'!$B16="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="21" customHeight="1">
       <c r="B27" s="13">
-        <f>IF(AND('2 Matériel'!$M17&gt;0,NOT('2 Matériel'!$B17="Oui")),'2 Matériel'!$A17,"")</f>
+        <f>IF(AND('2 Matériel'!$L17&gt;0,NOT('2 Matériel'!$B17="Oui")),'2 Matériel'!$A17,"")</f>
         <v/>
       </c>
       <c r="C27" s="37">
-        <f>IF('2 Matériel'!$M17&gt;0,IF('2 Matériel'!$B17="Oui",UPPER('2 Matériel'!$C17),'2 Matériel'!$C17),"")</f>
+        <f>IF('2 Matériel'!$L17&gt;0,IF('2 Matériel'!$B17="Oui",UPPER('2 Matériel'!$C17),'2 Matériel'!$C17),"")</f>
         <v/>
       </c>
       <c r="D27" s="38">
-        <f>IF(AND('2 Matériel'!$M17&gt;0,NOT('2 Matériel'!$B17="Oui")),'2 Matériel'!$M17,"")</f>
+        <f>IF(AND('2 Matériel'!$L17&gt;0,NOT('2 Matériel'!$B17="Oui")),'2 Matériel'!$L17,"")</f>
         <v/>
       </c>
       <c r="E27" s="39">
-        <f>IF(AND('2 Matériel'!$M17&gt;0,NOT('2 Matériel'!$B17="Oui")),IF(AND('2 Matériel'!$L17="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$F17="","",'2 Matériel'!$F17)),"")</f>
+        <f>IF(AND('2 Matériel'!$L17&gt;0,NOT('2 Matériel'!$B17="Oui")),IF(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E17="","",'2 Matériel'!$E17)),"")</f>
         <v/>
       </c>
       <c r="F27" s="39">
-        <f>IF(AND('2 Matériel'!$M17&gt;0,NOT('2 Matériel'!$B17="Oui")),IF(AND('2 Matériel'!$L17="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$G17="","",'2 Matériel'!$G17)),"")</f>
+        <f>IF(AND('2 Matériel'!$L17&gt;0,NOT('2 Matériel'!$B17="Oui")),IF(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F17="","",'2 Matériel'!$F17)),"")</f>
         <v/>
       </c>
       <c r="G27" s="39">
-        <f>IF(AND('2 Matériel'!$M17&gt;0,NOT('2 Matériel'!$B17="Oui")),IF(AND('2 Matériel'!$L17="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$H17="","",'2 Matériel'!$H17)),"")</f>
+        <f>IF(AND('2 Matériel'!$L17&gt;0,NOT('2 Matériel'!$B17="Oui")),IF(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G17="","",'2 Matériel'!$G17)),"")</f>
         <v/>
       </c>
       <c r="H27" s="39">
-        <f>IF(AND('2 Matériel'!$M17&gt;0,NOT('2 Matériel'!$B17="Oui")),IF(AND('2 Matériel'!$L17="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$I17="","",'2 Matériel'!$I17)),"")</f>
+        <f>IF(AND('2 Matériel'!$L17&gt;0,NOT('2 Matériel'!$B17="Oui")),IF(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H17="","",'2 Matériel'!$H17)),"")</f>
         <v/>
       </c>
       <c r="I27" s="39">
-        <f>IF(AND('2 Matériel'!$M17&gt;0,NOT('2 Matériel'!$B17="Oui")),IF(AND('2 Matériel'!$L17="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$J17="","",'2 Matériel'!$J17)),"")</f>
+        <f>IF(AND('2 Matériel'!$L17&gt;0,NOT('2 Matériel'!$B17="Oui")),IF(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I17="","",'2 Matériel'!$I17)),"")</f>
         <v/>
       </c>
       <c r="J27" s="39">
-        <f>IF(AND('2 Matériel'!$M17&gt;0,NOT('2 Matériel'!$B17="Oui")),IF(AND('2 Matériel'!$L17="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$K17="","",'2 Matériel'!$K17)),"")</f>
+        <f>IF(AND('2 Matériel'!$L17&gt;0,NOT('2 Matériel'!$B17="Oui")),IF(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J17="","",'2 Matériel'!$J17)),"")</f>
         <v/>
       </c>
       <c r="K27" s="40">
-        <f>IF(AND('2 Matériel'!$M17&gt;0,NOT('2 Matériel'!$B17="Oui")),IF(AND('2 Matériel'!$L17="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl_long",Textes!$A$2:$A$52,0),Listes!$H$1),""),"")</f>
+        <f>IF(AND('2 Matériel'!$L17&gt;0,NOT('2 Matériel'!$B17="Oui")),IF(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
       <c r="M27" s="41">
-        <f>IF(AND('2 Matériel'!$M17&gt;0,'2 Matériel'!$B17="Oui"),1,0)</f>
+        <f>IF(AND('2 Matériel'!$L17&gt;0,'2 Matériel'!$B17="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="21" customHeight="1">
       <c r="B28" s="13">
-        <f>IF(AND('2 Matériel'!$M18&gt;0,NOT('2 Matériel'!$B18="Oui")),'2 Matériel'!$A18,"")</f>
+        <f>IF(AND('2 Matériel'!$L18&gt;0,NOT('2 Matériel'!$B18="Oui")),'2 Matériel'!$A18,"")</f>
         <v/>
       </c>
       <c r="C28" s="37">
-        <f>IF('2 Matériel'!$M18&gt;0,IF('2 Matériel'!$B18="Oui",UPPER('2 Matériel'!$C18),'2 Matériel'!$C18),"")</f>
+        <f>IF('2 Matériel'!$L18&gt;0,IF('2 Matériel'!$B18="Oui",UPPER('2 Matériel'!$C18),'2 Matériel'!$C18),"")</f>
         <v/>
       </c>
       <c r="D28" s="38">
-        <f>IF(AND('2 Matériel'!$M18&gt;0,NOT('2 Matériel'!$B18="Oui")),'2 Matériel'!$M18,"")</f>
+        <f>IF(AND('2 Matériel'!$L18&gt;0,NOT('2 Matériel'!$B18="Oui")),'2 Matériel'!$L18,"")</f>
         <v/>
       </c>
       <c r="E28" s="39">
-        <f>IF(AND('2 Matériel'!$M18&gt;0,NOT('2 Matériel'!$B18="Oui")),IF(AND('2 Matériel'!$L18="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$F18="","",'2 Matériel'!$F18)),"")</f>
+        <f>IF(AND('2 Matériel'!$L18&gt;0,NOT('2 Matériel'!$B18="Oui")),IF(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E18="","",'2 Matériel'!$E18)),"")</f>
         <v/>
       </c>
       <c r="F28" s="39">
-        <f>IF(AND('2 Matériel'!$M18&gt;0,NOT('2 Matériel'!$B18="Oui")),IF(AND('2 Matériel'!$L18="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$G18="","",'2 Matériel'!$G18)),"")</f>
+        <f>IF(AND('2 Matériel'!$L18&gt;0,NOT('2 Matériel'!$B18="Oui")),IF(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F18="","",'2 Matériel'!$F18)),"")</f>
         <v/>
       </c>
       <c r="G28" s="39">
-        <f>IF(AND('2 Matériel'!$M18&gt;0,NOT('2 Matériel'!$B18="Oui")),IF(AND('2 Matériel'!$L18="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$H18="","",'2 Matériel'!$H18)),"")</f>
+        <f>IF(AND('2 Matériel'!$L18&gt;0,NOT('2 Matériel'!$B18="Oui")),IF(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G18="","",'2 Matériel'!$G18)),"")</f>
         <v/>
       </c>
       <c r="H28" s="39">
-        <f>IF(AND('2 Matériel'!$M18&gt;0,NOT('2 Matériel'!$B18="Oui")),IF(AND('2 Matériel'!$L18="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$I18="","",'2 Matériel'!$I18)),"")</f>
+        <f>IF(AND('2 Matériel'!$L18&gt;0,NOT('2 Matériel'!$B18="Oui")),IF(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H18="","",'2 Matériel'!$H18)),"")</f>
         <v/>
       </c>
       <c r="I28" s="39">
-        <f>IF(AND('2 Matériel'!$M18&gt;0,NOT('2 Matériel'!$B18="Oui")),IF(AND('2 Matériel'!$L18="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$J18="","",'2 Matériel'!$J18)),"")</f>
+        <f>IF(AND('2 Matériel'!$L18&gt;0,NOT('2 Matériel'!$B18="Oui")),IF(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I18="","",'2 Matériel'!$I18)),"")</f>
         <v/>
       </c>
       <c r="J28" s="39">
-        <f>IF(AND('2 Matériel'!$M18&gt;0,NOT('2 Matériel'!$B18="Oui")),IF(AND('2 Matériel'!$L18="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$K18="","",'2 Matériel'!$K18)),"")</f>
+        <f>IF(AND('2 Matériel'!$L18&gt;0,NOT('2 Matériel'!$B18="Oui")),IF(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J18="","",'2 Matériel'!$J18)),"")</f>
         <v/>
       </c>
       <c r="K28" s="40">
-        <f>IF(AND('2 Matériel'!$M18&gt;0,NOT('2 Matériel'!$B18="Oui")),IF(AND('2 Matériel'!$L18="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl_long",Textes!$A$2:$A$52,0),Listes!$H$1),""),"")</f>
+        <f>IF(AND('2 Matériel'!$L18&gt;0,NOT('2 Matériel'!$B18="Oui")),IF(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
       <c r="M28" s="41">
-        <f>IF(AND('2 Matériel'!$M18&gt;0,'2 Matériel'!$B18="Oui"),1,0)</f>
+        <f>IF(AND('2 Matériel'!$L18&gt;0,'2 Matériel'!$B18="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="21" customHeight="1">
       <c r="B29" s="13">
-        <f>IF(AND('2 Matériel'!$M19&gt;0,NOT('2 Matériel'!$B19="Oui")),'2 Matériel'!$A19,"")</f>
+        <f>IF(AND('2 Matériel'!$L19&gt;0,NOT('2 Matériel'!$B19="Oui")),'2 Matériel'!$A19,"")</f>
         <v/>
       </c>
       <c r="C29" s="37">
-        <f>IF('2 Matériel'!$M19&gt;0,IF('2 Matériel'!$B19="Oui",UPPER('2 Matériel'!$C19),'2 Matériel'!$C19),"")</f>
+        <f>IF('2 Matériel'!$L19&gt;0,IF('2 Matériel'!$B19="Oui",UPPER('2 Matériel'!$C19),'2 Matériel'!$C19),"")</f>
         <v/>
       </c>
       <c r="D29" s="38">
-        <f>IF(AND('2 Matériel'!$M19&gt;0,NOT('2 Matériel'!$B19="Oui")),'2 Matériel'!$M19,"")</f>
+        <f>IF(AND('2 Matériel'!$L19&gt;0,NOT('2 Matériel'!$B19="Oui")),'2 Matériel'!$L19,"")</f>
         <v/>
       </c>
       <c r="E29" s="39">
-        <f>IF(AND('2 Matériel'!$M19&gt;0,NOT('2 Matériel'!$B19="Oui")),IF(AND('2 Matériel'!$L19="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$F19="","",'2 Matériel'!$F19)),"")</f>
+        <f>IF(AND('2 Matériel'!$L19&gt;0,NOT('2 Matériel'!$B19="Oui")),IF(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E19="","",'2 Matériel'!$E19)),"")</f>
         <v/>
       </c>
       <c r="F29" s="39">
-        <f>IF(AND('2 Matériel'!$M19&gt;0,NOT('2 Matériel'!$B19="Oui")),IF(AND('2 Matériel'!$L19="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$G19="","",'2 Matériel'!$G19)),"")</f>
+        <f>IF(AND('2 Matériel'!$L19&gt;0,NOT('2 Matériel'!$B19="Oui")),IF(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F19="","",'2 Matériel'!$F19)),"")</f>
         <v/>
       </c>
       <c r="G29" s="39">
-        <f>IF(AND('2 Matériel'!$M19&gt;0,NOT('2 Matériel'!$B19="Oui")),IF(AND('2 Matériel'!$L19="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$H19="","",'2 Matériel'!$H19)),"")</f>
+        <f>IF(AND('2 Matériel'!$L19&gt;0,NOT('2 Matériel'!$B19="Oui")),IF(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G19="","",'2 Matériel'!$G19)),"")</f>
         <v/>
       </c>
       <c r="H29" s="39">
-        <f>IF(AND('2 Matériel'!$M19&gt;0,NOT('2 Matériel'!$B19="Oui")),IF(AND('2 Matériel'!$L19="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$I19="","",'2 Matériel'!$I19)),"")</f>
+        <f>IF(AND('2 Matériel'!$L19&gt;0,NOT('2 Matériel'!$B19="Oui")),IF(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H19="","",'2 Matériel'!$H19)),"")</f>
         <v/>
       </c>
       <c r="I29" s="39">
-        <f>IF(AND('2 Matériel'!$M19&gt;0,NOT('2 Matériel'!$B19="Oui")),IF(AND('2 Matériel'!$L19="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$J19="","",'2 Matériel'!$J19)),"")</f>
+        <f>IF(AND('2 Matériel'!$L19&gt;0,NOT('2 Matériel'!$B19="Oui")),IF(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I19="","",'2 Matériel'!$I19)),"")</f>
         <v/>
       </c>
       <c r="J29" s="39">
-        <f>IF(AND('2 Matériel'!$M19&gt;0,NOT('2 Matériel'!$B19="Oui")),IF(AND('2 Matériel'!$L19="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$K19="","",'2 Matériel'!$K19)),"")</f>
+        <f>IF(AND('2 Matériel'!$L19&gt;0,NOT('2 Matériel'!$B19="Oui")),IF(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J19="","",'2 Matériel'!$J19)),"")</f>
         <v/>
       </c>
       <c r="K29" s="40">
-        <f>IF(AND('2 Matériel'!$M19&gt;0,NOT('2 Matériel'!$B19="Oui")),IF(AND('2 Matériel'!$L19="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl_long",Textes!$A$2:$A$52,0),Listes!$H$1),""),"")</f>
+        <f>IF(AND('2 Matériel'!$L19&gt;0,NOT('2 Matériel'!$B19="Oui")),IF(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
       <c r="M29" s="41">
-        <f>IF(AND('2 Matériel'!$M19&gt;0,'2 Matériel'!$B19="Oui"),1,0)</f>
+        <f>IF(AND('2 Matériel'!$L19&gt;0,'2 Matériel'!$B19="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
     <row r="30" hidden="1" outlineLevel="1" ht="21" customHeight="1">
       <c r="B30" s="13">
-        <f>IF(AND('2 Matériel'!$M20&gt;0,NOT('2 Matériel'!$B20="Oui")),'2 Matériel'!$A20,"")</f>
+        <f>IF(AND('2 Matériel'!$L20&gt;0,NOT('2 Matériel'!$B20="Oui")),'2 Matériel'!$A20,"")</f>
         <v/>
       </c>
       <c r="C30" s="37">
-        <f>IF('2 Matériel'!$M20&gt;0,IF('2 Matériel'!$B20="Oui",UPPER('2 Matériel'!$C20),'2 Matériel'!$C20),"")</f>
+        <f>IF('2 Matériel'!$L20&gt;0,IF('2 Matériel'!$B20="Oui",UPPER('2 Matériel'!$C20),'2 Matériel'!$C20),"")</f>
         <v/>
       </c>
       <c r="D30" s="38">
-        <f>IF(AND('2 Matériel'!$M20&gt;0,NOT('2 Matériel'!$B20="Oui")),'2 Matériel'!$M20,"")</f>
+        <f>IF(AND('2 Matériel'!$L20&gt;0,NOT('2 Matériel'!$B20="Oui")),'2 Matériel'!$L20,"")</f>
         <v/>
       </c>
       <c r="E30" s="39">
-        <f>IF(AND('2 Matériel'!$M20&gt;0,NOT('2 Matériel'!$B20="Oui")),IF(AND('2 Matériel'!$L20="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$F20="","",'2 Matériel'!$F20)),"")</f>
+        <f>IF(AND('2 Matériel'!$L20&gt;0,NOT('2 Matériel'!$B20="Oui")),IF(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E20="","",'2 Matériel'!$E20)),"")</f>
         <v/>
       </c>
       <c r="F30" s="39">
-        <f>IF(AND('2 Matériel'!$M20&gt;0,NOT('2 Matériel'!$B20="Oui")),IF(AND('2 Matériel'!$L20="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$G20="","",'2 Matériel'!$G20)),"")</f>
+        <f>IF(AND('2 Matériel'!$L20&gt;0,NOT('2 Matériel'!$B20="Oui")),IF(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F20="","",'2 Matériel'!$F20)),"")</f>
         <v/>
       </c>
       <c r="G30" s="39">
-        <f>IF(AND('2 Matériel'!$M20&gt;0,NOT('2 Matériel'!$B20="Oui")),IF(AND('2 Matériel'!$L20="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$H20="","",'2 Matériel'!$H20)),"")</f>
+        <f>IF(AND('2 Matériel'!$L20&gt;0,NOT('2 Matériel'!$B20="Oui")),IF(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G20="","",'2 Matériel'!$G20)),"")</f>
         <v/>
       </c>
       <c r="H30" s="39">
-        <f>IF(AND('2 Matériel'!$M20&gt;0,NOT('2 Matériel'!$B20="Oui")),IF(AND('2 Matériel'!$L20="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$I20="","",'2 Matériel'!$I20)),"")</f>
+        <f>IF(AND('2 Matériel'!$L20&gt;0,NOT('2 Matériel'!$B20="Oui")),IF(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H20="","",'2 Matériel'!$H20)),"")</f>
         <v/>
       </c>
       <c r="I30" s="39">
-        <f>IF(AND('2 Matériel'!$M20&gt;0,NOT('2 Matériel'!$B20="Oui")),IF(AND('2 Matériel'!$L20="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$J20="","",'2 Matériel'!$J20)),"")</f>
+        <f>IF(AND('2 Matériel'!$L20&gt;0,NOT('2 Matériel'!$B20="Oui")),IF(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I20="","",'2 Matériel'!$I20)),"")</f>
         <v/>
       </c>
       <c r="J30" s="39">
-        <f>IF(AND('2 Matériel'!$M20&gt;0,NOT('2 Matériel'!$B20="Oui")),IF(AND('2 Matériel'!$L20="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$K20="","",'2 Matériel'!$K20)),"")</f>
+        <f>IF(AND('2 Matériel'!$L20&gt;0,NOT('2 Matériel'!$B20="Oui")),IF(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J20="","",'2 Matériel'!$J20)),"")</f>
         <v/>
       </c>
       <c r="K30" s="40">
-        <f>IF(AND('2 Matériel'!$M20&gt;0,NOT('2 Matériel'!$B20="Oui")),IF(AND('2 Matériel'!$L20="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl_long",Textes!$A$2:$A$52,0),Listes!$H$1),""),"")</f>
+        <f>IF(AND('2 Matériel'!$L20&gt;0,NOT('2 Matériel'!$B20="Oui")),IF(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
       <c r="M30" s="41">
-        <f>IF(AND('2 Matériel'!$M20&gt;0,'2 Matériel'!$B20="Oui"),1,0)</f>
+        <f>IF(AND('2 Matériel'!$L20&gt;0,'2 Matériel'!$B20="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
     <row r="31" hidden="1" outlineLevel="1" ht="21" customHeight="1">
       <c r="B31" s="13">
-        <f>IF(AND('2 Matériel'!$M21&gt;0,NOT('2 Matériel'!$B21="Oui")),'2 Matériel'!$A21,"")</f>
+        <f>IF(AND('2 Matériel'!$L21&gt;0,NOT('2 Matériel'!$B21="Oui")),'2 Matériel'!$A21,"")</f>
         <v/>
       </c>
       <c r="C31" s="37">
-        <f>IF('2 Matériel'!$M21&gt;0,IF('2 Matériel'!$B21="Oui",UPPER('2 Matériel'!$C21),'2 Matériel'!$C21),"")</f>
+        <f>IF('2 Matériel'!$L21&gt;0,IF('2 Matériel'!$B21="Oui",UPPER('2 Matériel'!$C21),'2 Matériel'!$C21),"")</f>
         <v/>
       </c>
       <c r="D31" s="38">
-        <f>IF(AND('2 Matériel'!$M21&gt;0,NOT('2 Matériel'!$B21="Oui")),'2 Matériel'!$M21,"")</f>
+        <f>IF(AND('2 Matériel'!$L21&gt;0,NOT('2 Matériel'!$B21="Oui")),'2 Matériel'!$L21,"")</f>
         <v/>
       </c>
       <c r="E31" s="39">
-        <f>IF(AND('2 Matériel'!$M21&gt;0,NOT('2 Matériel'!$B21="Oui")),IF(AND('2 Matériel'!$L21="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$F21="","",'2 Matériel'!$F21)),"")</f>
+        <f>IF(AND('2 Matériel'!$L21&gt;0,NOT('2 Matériel'!$B21="Oui")),IF(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E21="","",'2 Matériel'!$E21)),"")</f>
         <v/>
       </c>
       <c r="F31" s="39">
-        <f>IF(AND('2 Matériel'!$M21&gt;0,NOT('2 Matériel'!$B21="Oui")),IF(AND('2 Matériel'!$L21="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$G21="","",'2 Matériel'!$G21)),"")</f>
+        <f>IF(AND('2 Matériel'!$L21&gt;0,NOT('2 Matériel'!$B21="Oui")),IF(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F21="","",'2 Matériel'!$F21)),"")</f>
         <v/>
       </c>
       <c r="G31" s="39">
-        <f>IF(AND('2 Matériel'!$M21&gt;0,NOT('2 Matériel'!$B21="Oui")),IF(AND('2 Matériel'!$L21="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$H21="","",'2 Matériel'!$H21)),"")</f>
+        <f>IF(AND('2 Matériel'!$L21&gt;0,NOT('2 Matériel'!$B21="Oui")),IF(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G21="","",'2 Matériel'!$G21)),"")</f>
         <v/>
       </c>
       <c r="H31" s="39">
-        <f>IF(AND('2 Matériel'!$M21&gt;0,NOT('2 Matériel'!$B21="Oui")),IF(AND('2 Matériel'!$L21="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$I21="","",'2 Matériel'!$I21)),"")</f>
+        <f>IF(AND('2 Matériel'!$L21&gt;0,NOT('2 Matériel'!$B21="Oui")),IF(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H21="","",'2 Matériel'!$H21)),"")</f>
         <v/>
       </c>
       <c r="I31" s="39">
-        <f>IF(AND('2 Matériel'!$M21&gt;0,NOT('2 Matériel'!$B21="Oui")),IF(AND('2 Matériel'!$L21="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$J21="","",'2 Matériel'!$J21)),"")</f>
+        <f>IF(AND('2 Matériel'!$L21&gt;0,NOT('2 Matériel'!$B21="Oui")),IF(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I21="","",'2 Matériel'!$I21)),"")</f>
         <v/>
       </c>
       <c r="J31" s="39">
-        <f>IF(AND('2 Matériel'!$M21&gt;0,NOT('2 Matériel'!$B21="Oui")),IF(AND('2 Matériel'!$L21="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$K21="","",'2 Matériel'!$K21)),"")</f>
+        <f>IF(AND('2 Matériel'!$L21&gt;0,NOT('2 Matériel'!$B21="Oui")),IF(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J21="","",'2 Matériel'!$J21)),"")</f>
         <v/>
       </c>
       <c r="K31" s="40">
-        <f>IF(AND('2 Matériel'!$M21&gt;0,NOT('2 Matériel'!$B21="Oui")),IF(AND('2 Matériel'!$L21="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl_long",Textes!$A$2:$A$52,0),Listes!$H$1),""),"")</f>
+        <f>IF(AND('2 Matériel'!$L21&gt;0,NOT('2 Matériel'!$B21="Oui")),IF(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
       <c r="M31" s="41">
-        <f>IF(AND('2 Matériel'!$M21&gt;0,'2 Matériel'!$B21="Oui"),1,0)</f>
+        <f>IF(AND('2 Matériel'!$L21&gt;0,'2 Matériel'!$B21="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
     <row r="32" hidden="1" outlineLevel="1" ht="21" customHeight="1">
       <c r="B32" s="13">
-        <f>IF(AND('2 Matériel'!$M22&gt;0,NOT('2 Matériel'!$B22="Oui")),'2 Matériel'!$A22,"")</f>
+        <f>IF(AND('2 Matériel'!$L22&gt;0,NOT('2 Matériel'!$B22="Oui")),'2 Matériel'!$A22,"")</f>
         <v/>
       </c>
       <c r="C32" s="37">
-        <f>IF('2 Matériel'!$M22&gt;0,IF('2 Matériel'!$B22="Oui",UPPER('2 Matériel'!$C22),'2 Matériel'!$C22),"")</f>
+        <f>IF('2 Matériel'!$L22&gt;0,IF('2 Matériel'!$B22="Oui",UPPER('2 Matériel'!$C22),'2 Matériel'!$C22),"")</f>
         <v/>
       </c>
       <c r="D32" s="38">
-        <f>IF(AND('2 Matériel'!$M22&gt;0,NOT('2 Matériel'!$B22="Oui")),'2 Matériel'!$M22,"")</f>
+        <f>IF(AND('2 Matériel'!$L22&gt;0,NOT('2 Matériel'!$B22="Oui")),'2 Matériel'!$L22,"")</f>
         <v/>
       </c>
       <c r="E32" s="39">
-        <f>IF(AND('2 Matériel'!$M22&gt;0,NOT('2 Matériel'!$B22="Oui")),IF(AND('2 Matériel'!$L22="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$F22="","",'2 Matériel'!$F22)),"")</f>
+        <f>IF(AND('2 Matériel'!$L22&gt;0,NOT('2 Matériel'!$B22="Oui")),IF(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E22="","",'2 Matériel'!$E22)),"")</f>
         <v/>
       </c>
       <c r="F32" s="39">
-        <f>IF(AND('2 Matériel'!$M22&gt;0,NOT('2 Matériel'!$B22="Oui")),IF(AND('2 Matériel'!$L22="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$G22="","",'2 Matériel'!$G22)),"")</f>
+        <f>IF(AND('2 Matériel'!$L22&gt;0,NOT('2 Matériel'!$B22="Oui")),IF(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F22="","",'2 Matériel'!$F22)),"")</f>
         <v/>
       </c>
       <c r="G32" s="39">
-        <f>IF(AND('2 Matériel'!$M22&gt;0,NOT('2 Matériel'!$B22="Oui")),IF(AND('2 Matériel'!$L22="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$H22="","",'2 Matériel'!$H22)),"")</f>
+        <f>IF(AND('2 Matériel'!$L22&gt;0,NOT('2 Matériel'!$B22="Oui")),IF(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G22="","",'2 Matériel'!$G22)),"")</f>
         <v/>
       </c>
       <c r="H32" s="39">
-        <f>IF(AND('2 Matériel'!$M22&gt;0,NOT('2 Matériel'!$B22="Oui")),IF(AND('2 Matériel'!$L22="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$I22="","",'2 Matériel'!$I22)),"")</f>
+        <f>IF(AND('2 Matériel'!$L22&gt;0,NOT('2 Matériel'!$B22="Oui")),IF(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H22="","",'2 Matériel'!$H22)),"")</f>
         <v/>
       </c>
       <c r="I32" s="39">
-        <f>IF(AND('2 Matériel'!$M22&gt;0,NOT('2 Matériel'!$B22="Oui")),IF(AND('2 Matériel'!$L22="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$J22="","",'2 Matériel'!$J22)),"")</f>
+        <f>IF(AND('2 Matériel'!$L22&gt;0,NOT('2 Matériel'!$B22="Oui")),IF(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I22="","",'2 Matériel'!$I22)),"")</f>
         <v/>
       </c>
       <c r="J32" s="39">
-        <f>IF(AND('2 Matériel'!$M22&gt;0,NOT('2 Matériel'!$B22="Oui")),IF(AND('2 Matériel'!$L22="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$K22="","",'2 Matériel'!$K22)),"")</f>
+        <f>IF(AND('2 Matériel'!$L22&gt;0,NOT('2 Matériel'!$B22="Oui")),IF(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J22="","",'2 Matériel'!$J22)),"")</f>
         <v/>
       </c>
       <c r="K32" s="40">
-        <f>IF(AND('2 Matériel'!$M22&gt;0,NOT('2 Matériel'!$B22="Oui")),IF(AND('2 Matériel'!$L22="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl_long",Textes!$A$2:$A$52,0),Listes!$H$1),""),"")</f>
+        <f>IF(AND('2 Matériel'!$L22&gt;0,NOT('2 Matériel'!$B22="Oui")),IF(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
       <c r="M32" s="41">
-        <f>IF(AND('2 Matériel'!$M22&gt;0,'2 Matériel'!$B22="Oui"),1,0)</f>
+        <f>IF(AND('2 Matériel'!$L22&gt;0,'2 Matériel'!$B22="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
     <row r="33" hidden="1" outlineLevel="1" ht="21" customHeight="1">
       <c r="B33" s="13">
-        <f>IF(AND('2 Matériel'!$M23&gt;0,NOT('2 Matériel'!$B23="Oui")),'2 Matériel'!$A23,"")</f>
+        <f>IF(AND('2 Matériel'!$L23&gt;0,NOT('2 Matériel'!$B23="Oui")),'2 Matériel'!$A23,"")</f>
         <v/>
       </c>
       <c r="C33" s="37">
-        <f>IF('2 Matériel'!$M23&gt;0,IF('2 Matériel'!$B23="Oui",UPPER('2 Matériel'!$C23),'2 Matériel'!$C23),"")</f>
+        <f>IF('2 Matériel'!$L23&gt;0,IF('2 Matériel'!$B23="Oui",UPPER('2 Matériel'!$C23),'2 Matériel'!$C23),"")</f>
         <v/>
       </c>
       <c r="D33" s="38">
-        <f>IF(AND('2 Matériel'!$M23&gt;0,NOT('2 Matériel'!$B23="Oui")),'2 Matériel'!$M23,"")</f>
+        <f>IF(AND('2 Matériel'!$L23&gt;0,NOT('2 Matériel'!$B23="Oui")),'2 Matériel'!$L23,"")</f>
         <v/>
       </c>
       <c r="E33" s="39">
-        <f>IF(AND('2 Matériel'!$M23&gt;0,NOT('2 Matériel'!$B23="Oui")),IF(AND('2 Matériel'!$L23="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$F23="","",'2 Matériel'!$F23)),"")</f>
+        <f>IF(AND('2 Matériel'!$L23&gt;0,NOT('2 Matériel'!$B23="Oui")),IF(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E23="","",'2 Matériel'!$E23)),"")</f>
         <v/>
       </c>
       <c r="F33" s="39">
-        <f>IF(AND('2 Matériel'!$M23&gt;0,NOT('2 Matériel'!$B23="Oui")),IF(AND('2 Matériel'!$L23="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$G23="","",'2 Matériel'!$G23)),"")</f>
+        <f>IF(AND('2 Matériel'!$L23&gt;0,NOT('2 Matériel'!$B23="Oui")),IF(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F23="","",'2 Matériel'!$F23)),"")</f>
         <v/>
       </c>
       <c r="G33" s="39">
-        <f>IF(AND('2 Matériel'!$M23&gt;0,NOT('2 Matériel'!$B23="Oui")),IF(AND('2 Matériel'!$L23="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$H23="","",'2 Matériel'!$H23)),"")</f>
+        <f>IF(AND('2 Matériel'!$L23&gt;0,NOT('2 Matériel'!$B23="Oui")),IF(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G23="","",'2 Matériel'!$G23)),"")</f>
         <v/>
       </c>
       <c r="H33" s="39">
-        <f>IF(AND('2 Matériel'!$M23&gt;0,NOT('2 Matériel'!$B23="Oui")),IF(AND('2 Matériel'!$L23="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$I23="","",'2 Matériel'!$I23)),"")</f>
+        <f>IF(AND('2 Matériel'!$L23&gt;0,NOT('2 Matériel'!$B23="Oui")),IF(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H23="","",'2 Matériel'!$H23)),"")</f>
         <v/>
       </c>
       <c r="I33" s="39">
-        <f>IF(AND('2 Matériel'!$M23&gt;0,NOT('2 Matériel'!$B23="Oui")),IF(AND('2 Matériel'!$L23="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$J23="","",'2 Matériel'!$J23)),"")</f>
+        <f>IF(AND('2 Matériel'!$L23&gt;0,NOT('2 Matériel'!$B23="Oui")),IF(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I23="","",'2 Matériel'!$I23)),"")</f>
         <v/>
       </c>
       <c r="J33" s="39">
-        <f>IF(AND('2 Matériel'!$M23&gt;0,NOT('2 Matériel'!$B23="Oui")),IF(AND('2 Matériel'!$L23="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$K23="","",'2 Matériel'!$K23)),"")</f>
+        <f>IF(AND('2 Matériel'!$L23&gt;0,NOT('2 Matériel'!$B23="Oui")),IF(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J23="","",'2 Matériel'!$J23)),"")</f>
         <v/>
       </c>
       <c r="K33" s="40">
-        <f>IF(AND('2 Matériel'!$M23&gt;0,NOT('2 Matériel'!$B23="Oui")),IF(AND('2 Matériel'!$L23="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl_long",Textes!$A$2:$A$52,0),Listes!$H$1),""),"")</f>
+        <f>IF(AND('2 Matériel'!$L23&gt;0,NOT('2 Matériel'!$B23="Oui")),IF(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
       <c r="M33" s="41">
-        <f>IF(AND('2 Matériel'!$M23&gt;0,'2 Matériel'!$B23="Oui"),1,0)</f>
+        <f>IF(AND('2 Matériel'!$L23&gt;0,'2 Matériel'!$B23="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
     <row r="34" hidden="1" outlineLevel="1" ht="21" customHeight="1">
       <c r="B34" s="13">
-        <f>IF(AND('2 Matériel'!$M24&gt;0,NOT('2 Matériel'!$B24="Oui")),'2 Matériel'!$A24,"")</f>
+        <f>IF(AND('2 Matériel'!$L24&gt;0,NOT('2 Matériel'!$B24="Oui")),'2 Matériel'!$A24,"")</f>
         <v/>
       </c>
       <c r="C34" s="37">
-        <f>IF('2 Matériel'!$M24&gt;0,IF('2 Matériel'!$B24="Oui",UPPER('2 Matériel'!$C24),'2 Matériel'!$C24),"")</f>
+        <f>IF('2 Matériel'!$L24&gt;0,IF('2 Matériel'!$B24="Oui",UPPER('2 Matériel'!$C24),'2 Matériel'!$C24),"")</f>
         <v/>
       </c>
       <c r="D34" s="38">
-        <f>IF(AND('2 Matériel'!$M24&gt;0,NOT('2 Matériel'!$B24="Oui")),'2 Matériel'!$M24,"")</f>
+        <f>IF(AND('2 Matériel'!$L24&gt;0,NOT('2 Matériel'!$B24="Oui")),'2 Matériel'!$L24,"")</f>
         <v/>
       </c>
       <c r="E34" s="39">
-        <f>IF(AND('2 Matériel'!$M24&gt;0,NOT('2 Matériel'!$B24="Oui")),IF(AND('2 Matériel'!$L24="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$F24="","",'2 Matériel'!$F24)),"")</f>
+        <f>IF(AND('2 Matériel'!$L24&gt;0,NOT('2 Matériel'!$B24="Oui")),IF(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E24="","",'2 Matériel'!$E24)),"")</f>
         <v/>
       </c>
       <c r="F34" s="39">
-        <f>IF(AND('2 Matériel'!$M24&gt;0,NOT('2 Matériel'!$B24="Oui")),IF(AND('2 Matériel'!$L24="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$G24="","",'2 Matériel'!$G24)),"")</f>
+        <f>IF(AND('2 Matériel'!$L24&gt;0,NOT('2 Matériel'!$B24="Oui")),IF(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F24="","",'2 Matériel'!$F24)),"")</f>
         <v/>
       </c>
       <c r="G34" s="39">
-        <f>IF(AND('2 Matériel'!$M24&gt;0,NOT('2 Matériel'!$B24="Oui")),IF(AND('2 Matériel'!$L24="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$H24="","",'2 Matériel'!$H24)),"")</f>
+        <f>IF(AND('2 Matériel'!$L24&gt;0,NOT('2 Matériel'!$B24="Oui")),IF(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G24="","",'2 Matériel'!$G24)),"")</f>
         <v/>
       </c>
       <c r="H34" s="39">
-        <f>IF(AND('2 Matériel'!$M24&gt;0,NOT('2 Matériel'!$B24="Oui")),IF(AND('2 Matériel'!$L24="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$I24="","",'2 Matériel'!$I24)),"")</f>
+        <f>IF(AND('2 Matériel'!$L24&gt;0,NOT('2 Matériel'!$B24="Oui")),IF(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H24="","",'2 Matériel'!$H24)),"")</f>
         <v/>
       </c>
       <c r="I34" s="39">
-        <f>IF(AND('2 Matériel'!$M24&gt;0,NOT('2 Matériel'!$B24="Oui")),IF(AND('2 Matériel'!$L24="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$J24="","",'2 Matériel'!$J24)),"")</f>
+        <f>IF(AND('2 Matériel'!$L24&gt;0,NOT('2 Matériel'!$B24="Oui")),IF(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I24="","",'2 Matériel'!$I24)),"")</f>
         <v/>
       </c>
       <c r="J34" s="39">
-        <f>IF(AND('2 Matériel'!$M24&gt;0,NOT('2 Matériel'!$B24="Oui")),IF(AND('2 Matériel'!$L24="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$K24="","",'2 Matériel'!$K24)),"")</f>
+        <f>IF(AND('2 Matériel'!$L24&gt;0,NOT('2 Matériel'!$B24="Oui")),IF(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J24="","",'2 Matériel'!$J24)),"")</f>
         <v/>
       </c>
       <c r="K34" s="40">
-        <f>IF(AND('2 Matériel'!$M24&gt;0,NOT('2 Matériel'!$B24="Oui")),IF(AND('2 Matériel'!$L24="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl_long",Textes!$A$2:$A$52,0),Listes!$H$1),""),"")</f>
+        <f>IF(AND('2 Matériel'!$L24&gt;0,NOT('2 Matériel'!$B24="Oui")),IF(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
       <c r="M34" s="41">
-        <f>IF(AND('2 Matériel'!$M24&gt;0,'2 Matériel'!$B24="Oui"),1,0)</f>
+        <f>IF(AND('2 Matériel'!$L24&gt;0,'2 Matériel'!$B24="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
     <row r="35" hidden="1" outlineLevel="1" ht="21" customHeight="1">
       <c r="B35" s="13">
-        <f>IF(AND('2 Matériel'!$M25&gt;0,NOT('2 Matériel'!$B25="Oui")),'2 Matériel'!$A25,"")</f>
+        <f>IF(AND('2 Matériel'!$L25&gt;0,NOT('2 Matériel'!$B25="Oui")),'2 Matériel'!$A25,"")</f>
         <v/>
       </c>
       <c r="C35" s="37">
-        <f>IF('2 Matériel'!$M25&gt;0,IF('2 Matériel'!$B25="Oui",UPPER('2 Matériel'!$C25),'2 Matériel'!$C25),"")</f>
+        <f>IF('2 Matériel'!$L25&gt;0,IF('2 Matériel'!$B25="Oui",UPPER('2 Matériel'!$C25),'2 Matériel'!$C25),"")</f>
         <v/>
       </c>
       <c r="D35" s="38">
-        <f>IF(AND('2 Matériel'!$M25&gt;0,NOT('2 Matériel'!$B25="Oui")),'2 Matériel'!$M25,"")</f>
+        <f>IF(AND('2 Matériel'!$L25&gt;0,NOT('2 Matériel'!$B25="Oui")),'2 Matériel'!$L25,"")</f>
         <v/>
       </c>
       <c r="E35" s="39">
-        <f>IF(AND('2 Matériel'!$M25&gt;0,NOT('2 Matériel'!$B25="Oui")),IF(AND('2 Matériel'!$L25="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$F25="","",'2 Matériel'!$F25)),"")</f>
+        <f>IF(AND('2 Matériel'!$L25&gt;0,NOT('2 Matériel'!$B25="Oui")),IF(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E25="","",'2 Matériel'!$E25)),"")</f>
         <v/>
       </c>
       <c r="F35" s="39">
-        <f>IF(AND('2 Matériel'!$M25&gt;0,NOT('2 Matériel'!$B25="Oui")),IF(AND('2 Matériel'!$L25="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$G25="","",'2 Matériel'!$G25)),"")</f>
+        <f>IF(AND('2 Matériel'!$L25&gt;0,NOT('2 Matériel'!$B25="Oui")),IF(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F25="","",'2 Matériel'!$F25)),"")</f>
         <v/>
       </c>
       <c r="G35" s="39">
-        <f>IF(AND('2 Matériel'!$M25&gt;0,NOT('2 Matériel'!$B25="Oui")),IF(AND('2 Matériel'!$L25="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$H25="","",'2 Matériel'!$H25)),"")</f>
+        <f>IF(AND('2 Matériel'!$L25&gt;0,NOT('2 Matériel'!$B25="Oui")),IF(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G25="","",'2 Matériel'!$G25)),"")</f>
         <v/>
       </c>
       <c r="H35" s="39">
-        <f>IF(AND('2 Matériel'!$M25&gt;0,NOT('2 Matériel'!$B25="Oui")),IF(AND('2 Matériel'!$L25="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$I25="","",'2 Matériel'!$I25)),"")</f>
+        <f>IF(AND('2 Matériel'!$L25&gt;0,NOT('2 Matériel'!$B25="Oui")),IF(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H25="","",'2 Matériel'!$H25)),"")</f>
         <v/>
       </c>
       <c r="I35" s="39">
-        <f>IF(AND('2 Matériel'!$M25&gt;0,NOT('2 Matériel'!$B25="Oui")),IF(AND('2 Matériel'!$L25="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$J25="","",'2 Matériel'!$J25)),"")</f>
+        <f>IF(AND('2 Matériel'!$L25&gt;0,NOT('2 Matériel'!$B25="Oui")),IF(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I25="","",'2 Matériel'!$I25)),"")</f>
         <v/>
       </c>
       <c r="J35" s="39">
-        <f>IF(AND('2 Matériel'!$M25&gt;0,NOT('2 Matériel'!$B25="Oui")),IF(AND('2 Matériel'!$L25="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$K25="","",'2 Matériel'!$K25)),"")</f>
+        <f>IF(AND('2 Matériel'!$L25&gt;0,NOT('2 Matériel'!$B25="Oui")),IF(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J25="","",'2 Matériel'!$J25)),"")</f>
         <v/>
       </c>
       <c r="K35" s="40">
-        <f>IF(AND('2 Matériel'!$M25&gt;0,NOT('2 Matériel'!$B25="Oui")),IF(AND('2 Matériel'!$L25="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl_long",Textes!$A$2:$A$52,0),Listes!$H$1),""),"")</f>
+        <f>IF(AND('2 Matériel'!$L25&gt;0,NOT('2 Matériel'!$B25="Oui")),IF(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
       <c r="M35" s="41">
-        <f>IF(AND('2 Matériel'!$M25&gt;0,'2 Matériel'!$B25="Oui"),1,0)</f>
+        <f>IF(AND('2 Matériel'!$L25&gt;0,'2 Matériel'!$B25="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
     <row r="36" hidden="1" outlineLevel="1" ht="21" customHeight="1">
       <c r="B36" s="13">
-        <f>IF(AND('2 Matériel'!$M26&gt;0,NOT('2 Matériel'!$B26="Oui")),'2 Matériel'!$A26,"")</f>
+        <f>IF(AND('2 Matériel'!$L26&gt;0,NOT('2 Matériel'!$B26="Oui")),'2 Matériel'!$A26,"")</f>
         <v/>
       </c>
       <c r="C36" s="37">
-        <f>IF('2 Matériel'!$M26&gt;0,IF('2 Matériel'!$B26="Oui",UPPER('2 Matériel'!$C26),'2 Matériel'!$C26),"")</f>
+        <f>IF('2 Matériel'!$L26&gt;0,IF('2 Matériel'!$B26="Oui",UPPER('2 Matériel'!$C26),'2 Matériel'!$C26),"")</f>
         <v/>
       </c>
       <c r="D36" s="38">
-        <f>IF(AND('2 Matériel'!$M26&gt;0,NOT('2 Matériel'!$B26="Oui")),'2 Matériel'!$M26,"")</f>
+        <f>IF(AND('2 Matériel'!$L26&gt;0,NOT('2 Matériel'!$B26="Oui")),'2 Matériel'!$L26,"")</f>
         <v/>
       </c>
       <c r="E36" s="39">
-        <f>IF(AND('2 Matériel'!$M26&gt;0,NOT('2 Matériel'!$B26="Oui")),IF(AND('2 Matériel'!$L26="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$F26="","",'2 Matériel'!$F26)),"")</f>
+        <f>IF(AND('2 Matériel'!$L26&gt;0,NOT('2 Matériel'!$B26="Oui")),IF(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E26="","",'2 Matériel'!$E26)),"")</f>
         <v/>
       </c>
       <c r="F36" s="39">
-        <f>IF(AND('2 Matériel'!$M26&gt;0,NOT('2 Matériel'!$B26="Oui")),IF(AND('2 Matériel'!$L26="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$G26="","",'2 Matériel'!$G26)),"")</f>
+        <f>IF(AND('2 Matériel'!$L26&gt;0,NOT('2 Matériel'!$B26="Oui")),IF(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F26="","",'2 Matériel'!$F26)),"")</f>
         <v/>
       </c>
       <c r="G36" s="39">
-        <f>IF(AND('2 Matériel'!$M26&gt;0,NOT('2 Matériel'!$B26="Oui")),IF(AND('2 Matériel'!$L26="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$H26="","",'2 Matériel'!$H26)),"")</f>
+        <f>IF(AND('2 Matériel'!$L26&gt;0,NOT('2 Matériel'!$B26="Oui")),IF(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G26="","",'2 Matériel'!$G26)),"")</f>
         <v/>
       </c>
       <c r="H36" s="39">
-        <f>IF(AND('2 Matériel'!$M26&gt;0,NOT('2 Matériel'!$B26="Oui")),IF(AND('2 Matériel'!$L26="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$I26="","",'2 Matériel'!$I26)),"")</f>
+        <f>IF(AND('2 Matériel'!$L26&gt;0,NOT('2 Matériel'!$B26="Oui")),IF(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H26="","",'2 Matériel'!$H26)),"")</f>
         <v/>
       </c>
       <c r="I36" s="39">
-        <f>IF(AND('2 Matériel'!$M26&gt;0,NOT('2 Matériel'!$B26="Oui")),IF(AND('2 Matériel'!$L26="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$J26="","",'2 Matériel'!$J26)),"")</f>
+        <f>IF(AND('2 Matériel'!$L26&gt;0,NOT('2 Matériel'!$B26="Oui")),IF(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I26="","",'2 Matériel'!$I26)),"")</f>
         <v/>
       </c>
       <c r="J36" s="39">
-        <f>IF(AND('2 Matériel'!$M26&gt;0,NOT('2 Matériel'!$B26="Oui")),IF(AND('2 Matériel'!$L26="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$K26="","",'2 Matériel'!$K26)),"")</f>
+        <f>IF(AND('2 Matériel'!$L26&gt;0,NOT('2 Matériel'!$B26="Oui")),IF(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J26="","",'2 Matériel'!$J26)),"")</f>
         <v/>
       </c>
       <c r="K36" s="40">
-        <f>IF(AND('2 Matériel'!$M26&gt;0,NOT('2 Matériel'!$B26="Oui")),IF(AND('2 Matériel'!$L26="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl_long",Textes!$A$2:$A$52,0),Listes!$H$1),""),"")</f>
+        <f>IF(AND('2 Matériel'!$L26&gt;0,NOT('2 Matériel'!$B26="Oui")),IF(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
       <c r="M36" s="41">
-        <f>IF(AND('2 Matériel'!$M26&gt;0,'2 Matériel'!$B26="Oui"),1,0)</f>
+        <f>IF(AND('2 Matériel'!$L26&gt;0,'2 Matériel'!$B26="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
     <row r="37" hidden="1" outlineLevel="1" ht="21" customHeight="1">
       <c r="B37" s="13">
-        <f>IF(AND('2 Matériel'!$M27&gt;0,NOT('2 Matériel'!$B27="Oui")),'2 Matériel'!$A27,"")</f>
+        <f>IF(AND('2 Matériel'!$L27&gt;0,NOT('2 Matériel'!$B27="Oui")),'2 Matériel'!$A27,"")</f>
         <v/>
       </c>
       <c r="C37" s="37">
-        <f>IF('2 Matériel'!$M27&gt;0,IF('2 Matériel'!$B27="Oui",UPPER('2 Matériel'!$C27),'2 Matériel'!$C27),"")</f>
+        <f>IF('2 Matériel'!$L27&gt;0,IF('2 Matériel'!$B27="Oui",UPPER('2 Matériel'!$C27),'2 Matériel'!$C27),"")</f>
         <v/>
       </c>
       <c r="D37" s="38">
-        <f>IF(AND('2 Matériel'!$M27&gt;0,NOT('2 Matériel'!$B27="Oui")),'2 Matériel'!$M27,"")</f>
+        <f>IF(AND('2 Matériel'!$L27&gt;0,NOT('2 Matériel'!$B27="Oui")),'2 Matériel'!$L27,"")</f>
         <v/>
       </c>
       <c r="E37" s="39">
-        <f>IF(AND('2 Matériel'!$M27&gt;0,NOT('2 Matériel'!$B27="Oui")),IF(AND('2 Matériel'!$L27="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$F27="","",'2 Matériel'!$F27)),"")</f>
+        <f>IF(AND('2 Matériel'!$L27&gt;0,NOT('2 Matériel'!$B27="Oui")),IF(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E27="","",'2 Matériel'!$E27)),"")</f>
         <v/>
       </c>
       <c r="F37" s="39">
-        <f>IF(AND('2 Matériel'!$M27&gt;0,NOT('2 Matériel'!$B27="Oui")),IF(AND('2 Matériel'!$L27="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$G27="","",'2 Matériel'!$G27)),"")</f>
+        <f>IF(AND('2 Matériel'!$L27&gt;0,NOT('2 Matériel'!$B27="Oui")),IF(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F27="","",'2 Matériel'!$F27)),"")</f>
         <v/>
       </c>
       <c r="G37" s="39">
-        <f>IF(AND('2 Matériel'!$M27&gt;0,NOT('2 Matériel'!$B27="Oui")),IF(AND('2 Matériel'!$L27="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$H27="","",'2 Matériel'!$H27)),"")</f>
+        <f>IF(AND('2 Matériel'!$L27&gt;0,NOT('2 Matériel'!$B27="Oui")),IF(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G27="","",'2 Matériel'!$G27)),"")</f>
         <v/>
       </c>
       <c r="H37" s="39">
-        <f>IF(AND('2 Matériel'!$M27&gt;0,NOT('2 Matériel'!$B27="Oui")),IF(AND('2 Matériel'!$L27="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$I27="","",'2 Matériel'!$I27)),"")</f>
+        <f>IF(AND('2 Matériel'!$L27&gt;0,NOT('2 Matériel'!$B27="Oui")),IF(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H27="","",'2 Matériel'!$H27)),"")</f>
         <v/>
       </c>
       <c r="I37" s="39">
-        <f>IF(AND('2 Matériel'!$M27&gt;0,NOT('2 Matériel'!$B27="Oui")),IF(AND('2 Matériel'!$L27="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$J27="","",'2 Matériel'!$J27)),"")</f>
+        <f>IF(AND('2 Matériel'!$L27&gt;0,NOT('2 Matériel'!$B27="Oui")),IF(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I27="","",'2 Matériel'!$I27)),"")</f>
         <v/>
       </c>
       <c r="J37" s="39">
-        <f>IF(AND('2 Matériel'!$M27&gt;0,NOT('2 Matériel'!$B27="Oui")),IF(AND('2 Matériel'!$L27="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$K27="","",'2 Matériel'!$K27)),"")</f>
+        <f>IF(AND('2 Matériel'!$L27&gt;0,NOT('2 Matériel'!$B27="Oui")),IF(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J27="","",'2 Matériel'!$J27)),"")</f>
         <v/>
       </c>
       <c r="K37" s="40">
-        <f>IF(AND('2 Matériel'!$M27&gt;0,NOT('2 Matériel'!$B27="Oui")),IF(AND('2 Matériel'!$L27="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl_long",Textes!$A$2:$A$52,0),Listes!$H$1),""),"")</f>
+        <f>IF(AND('2 Matériel'!$L27&gt;0,NOT('2 Matériel'!$B27="Oui")),IF(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
       <c r="M37" s="41">
-        <f>IF(AND('2 Matériel'!$M27&gt;0,'2 Matériel'!$B27="Oui"),1,0)</f>
+        <f>IF(AND('2 Matériel'!$L27&gt;0,'2 Matériel'!$B27="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
     <row r="38" hidden="1" outlineLevel="1" ht="21" customHeight="1">
       <c r="B38" s="13">
-        <f>IF(AND('2 Matériel'!$M28&gt;0,NOT('2 Matériel'!$B28="Oui")),'2 Matériel'!$A28,"")</f>
+        <f>IF(AND('2 Matériel'!$L28&gt;0,NOT('2 Matériel'!$B28="Oui")),'2 Matériel'!$A28,"")</f>
         <v/>
       </c>
       <c r="C38" s="37">
-        <f>IF('2 Matériel'!$M28&gt;0,IF('2 Matériel'!$B28="Oui",UPPER('2 Matériel'!$C28),'2 Matériel'!$C28),"")</f>
+        <f>IF('2 Matériel'!$L28&gt;0,IF('2 Matériel'!$B28="Oui",UPPER('2 Matériel'!$C28),'2 Matériel'!$C28),"")</f>
         <v/>
       </c>
       <c r="D38" s="38">
-        <f>IF(AND('2 Matériel'!$M28&gt;0,NOT('2 Matériel'!$B28="Oui")),'2 Matériel'!$M28,"")</f>
+        <f>IF(AND('2 Matériel'!$L28&gt;0,NOT('2 Matériel'!$B28="Oui")),'2 Matériel'!$L28,"")</f>
         <v/>
       </c>
       <c r="E38" s="39">
-        <f>IF(AND('2 Matériel'!$M28&gt;0,NOT('2 Matériel'!$B28="Oui")),IF(AND('2 Matériel'!$L28="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$F28="","",'2 Matériel'!$F28)),"")</f>
+        <f>IF(AND('2 Matériel'!$L28&gt;0,NOT('2 Matériel'!$B28="Oui")),IF(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E28="","",'2 Matériel'!$E28)),"")</f>
         <v/>
       </c>
       <c r="F38" s="39">
-        <f>IF(AND('2 Matériel'!$M28&gt;0,NOT('2 Matériel'!$B28="Oui")),IF(AND('2 Matériel'!$L28="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$G28="","",'2 Matériel'!$G28)),"")</f>
+        <f>IF(AND('2 Matériel'!$L28&gt;0,NOT('2 Matériel'!$B28="Oui")),IF(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F28="","",'2 Matériel'!$F28)),"")</f>
         <v/>
       </c>
       <c r="G38" s="39">
-        <f>IF(AND('2 Matériel'!$M28&gt;0,NOT('2 Matériel'!$B28="Oui")),IF(AND('2 Matériel'!$L28="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$H28="","",'2 Matériel'!$H28)),"")</f>
+        <f>IF(AND('2 Matériel'!$L28&gt;0,NOT('2 Matériel'!$B28="Oui")),IF(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G28="","",'2 Matériel'!$G28)),"")</f>
         <v/>
       </c>
       <c r="H38" s="39">
-        <f>IF(AND('2 Matériel'!$M28&gt;0,NOT('2 Matériel'!$B28="Oui")),IF(AND('2 Matériel'!$L28="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$I28="","",'2 Matériel'!$I28)),"")</f>
+        <f>IF(AND('2 Matériel'!$L28&gt;0,NOT('2 Matériel'!$B28="Oui")),IF(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H28="","",'2 Matériel'!$H28)),"")</f>
         <v/>
       </c>
       <c r="I38" s="39">
-        <f>IF(AND('2 Matériel'!$M28&gt;0,NOT('2 Matériel'!$B28="Oui")),IF(AND('2 Matériel'!$L28="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$J28="","",'2 Matériel'!$J28)),"")</f>
+        <f>IF(AND('2 Matériel'!$L28&gt;0,NOT('2 Matériel'!$B28="Oui")),IF(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I28="","",'2 Matériel'!$I28)),"")</f>
         <v/>
       </c>
       <c r="J38" s="39">
-        <f>IF(AND('2 Matériel'!$M28&gt;0,NOT('2 Matériel'!$B28="Oui")),IF(AND('2 Matériel'!$L28="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$K28="","",'2 Matériel'!$K28)),"")</f>
+        <f>IF(AND('2 Matériel'!$L28&gt;0,NOT('2 Matériel'!$B28="Oui")),IF(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J28="","",'2 Matériel'!$J28)),"")</f>
         <v/>
       </c>
       <c r="K38" s="40">
-        <f>IF(AND('2 Matériel'!$M28&gt;0,NOT('2 Matériel'!$B28="Oui")),IF(AND('2 Matériel'!$L28="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl_long",Textes!$A$2:$A$52,0),Listes!$H$1),""),"")</f>
+        <f>IF(AND('2 Matériel'!$L28&gt;0,NOT('2 Matériel'!$B28="Oui")),IF(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
       <c r="M38" s="41">
-        <f>IF(AND('2 Matériel'!$M28&gt;0,'2 Matériel'!$B28="Oui"),1,0)</f>
+        <f>IF(AND('2 Matériel'!$L28&gt;0,'2 Matériel'!$B28="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
     <row r="39" hidden="1" outlineLevel="1" ht="21" customHeight="1">
       <c r="B39" s="13">
-        <f>IF(AND('2 Matériel'!$M29&gt;0,NOT('2 Matériel'!$B29="Oui")),'2 Matériel'!$A29,"")</f>
+        <f>IF(AND('2 Matériel'!$L29&gt;0,NOT('2 Matériel'!$B29="Oui")),'2 Matériel'!$A29,"")</f>
         <v/>
       </c>
       <c r="C39" s="37">
-        <f>IF('2 Matériel'!$M29&gt;0,IF('2 Matériel'!$B29="Oui",UPPER('2 Matériel'!$C29),'2 Matériel'!$C29),"")</f>
+        <f>IF('2 Matériel'!$L29&gt;0,IF('2 Matériel'!$B29="Oui",UPPER('2 Matériel'!$C29),'2 Matériel'!$C29),"")</f>
         <v/>
       </c>
       <c r="D39" s="38">
-        <f>IF(AND('2 Matériel'!$M29&gt;0,NOT('2 Matériel'!$B29="Oui")),'2 Matériel'!$M29,"")</f>
+        <f>IF(AND('2 Matériel'!$L29&gt;0,NOT('2 Matériel'!$B29="Oui")),'2 Matériel'!$L29,"")</f>
         <v/>
       </c>
       <c r="E39" s="39">
-        <f>IF(AND('2 Matériel'!$M29&gt;0,NOT('2 Matériel'!$B29="Oui")),IF(AND('2 Matériel'!$L29="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$F29="","",'2 Matériel'!$F29)),"")</f>
+        <f>IF(AND('2 Matériel'!$L29&gt;0,NOT('2 Matériel'!$B29="Oui")),IF(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E29="","",'2 Matériel'!$E29)),"")</f>
         <v/>
       </c>
       <c r="F39" s="39">
-        <f>IF(AND('2 Matériel'!$M29&gt;0,NOT('2 Matériel'!$B29="Oui")),IF(AND('2 Matériel'!$L29="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$G29="","",'2 Matériel'!$G29)),"")</f>
+        <f>IF(AND('2 Matériel'!$L29&gt;0,NOT('2 Matériel'!$B29="Oui")),IF(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F29="","",'2 Matériel'!$F29)),"")</f>
         <v/>
       </c>
       <c r="G39" s="39">
-        <f>IF(AND('2 Matériel'!$M29&gt;0,NOT('2 Matériel'!$B29="Oui")),IF(AND('2 Matériel'!$L29="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$H29="","",'2 Matériel'!$H29)),"")</f>
+        <f>IF(AND('2 Matériel'!$L29&gt;0,NOT('2 Matériel'!$B29="Oui")),IF(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G29="","",'2 Matériel'!$G29)),"")</f>
         <v/>
       </c>
       <c r="H39" s="39">
-        <f>IF(AND('2 Matériel'!$M29&gt;0,NOT('2 Matériel'!$B29="Oui")),IF(AND('2 Matériel'!$L29="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$I29="","",'2 Matériel'!$I29)),"")</f>
+        <f>IF(AND('2 Matériel'!$L29&gt;0,NOT('2 Matériel'!$B29="Oui")),IF(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H29="","",'2 Matériel'!$H29)),"")</f>
         <v/>
       </c>
       <c r="I39" s="39">
-        <f>IF(AND('2 Matériel'!$M29&gt;0,NOT('2 Matériel'!$B29="Oui")),IF(AND('2 Matériel'!$L29="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$J29="","",'2 Matériel'!$J29)),"")</f>
+        <f>IF(AND('2 Matériel'!$L29&gt;0,NOT('2 Matériel'!$B29="Oui")),IF(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I29="","",'2 Matériel'!$I29)),"")</f>
         <v/>
       </c>
       <c r="J39" s="39">
-        <f>IF(AND('2 Matériel'!$M29&gt;0,NOT('2 Matériel'!$B29="Oui")),IF(AND('2 Matériel'!$L29="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl",Textes!$A$2:$A$52,0),Listes!$H$1),IF('2 Matériel'!$K29="","",'2 Matériel'!$K29)),"")</f>
+        <f>IF(AND('2 Matériel'!$L29&gt;0,NOT('2 Matériel'!$B29="Oui")),IF(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J29="","",'2 Matériel'!$J29)),"")</f>
         <v/>
       </c>
       <c r="K39" s="40">
-        <f>IF(AND('2 Matériel'!$M29&gt;0,NOT('2 Matériel'!$B29="Oui")),IF(AND('2 Matériel'!$L29="Oui",'3 Options'!$C$16="Oui"),INDEX(Textes!$B$2:$C$52,MATCH("incl_long",Textes!$A$2:$A$52,0),Listes!$H$1),""),"")</f>
+        <f>IF(AND('2 Matériel'!$L29&gt;0,NOT('2 Matériel'!$B29="Oui")),IF(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
         <v/>
       </c>
       <c r="M39" s="41">
-        <f>IF(AND('2 Matériel'!$M29&gt;0,'2 Matériel'!$B29="Oui"),1,0)</f>
+        <f>IF(AND('2 Matériel'!$L29&gt;0,'2 Matériel'!$B29="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="42">
-        <f>IF(SUM('2 Matériel'!$M$20:$M$29)&gt;0,"⚠  Des lignes de matériel au-delà de la ligne 14 sont masquées : cliquer sur le [+] dans la marge gauche pour les afficher.","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="10" customHeight="1"/>
-    <row r="42" ht="18" customHeight="1">
+        <f>IF(SUM('2 Matériel'!$L$20:$L$29)&gt;0,"⚠  Des lignes de matériel au-delà de la ligne 14 sont masquées : cliquer sur le [+] dans la marge gauche pour les afficher.","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="8" customHeight="1"/>
+    <row r="42" ht="20" customHeight="1">
       <c r="B42" s="43">
-        <f>IF('3 Options'!$C$16="Oui",UPPER(INDEX(Textes!$B$2:$C$52,MATCH("forfait",Textes!$A$2:$A$52,0),Listes!$H$1)),"")</f>
+        <f>IF('3 Options'!$C$8="Oui",INDEX(Textes!$B$2:$C$55,MATCH("sec_tight",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
+        <v/>
+      </c>
+      <c r="C42" s="44" t="n"/>
+      <c r="D42" s="44">
+        <f>IF('3 Options'!$C$8="Oui",INDEX(Textes!$B$2:$C$55,MATCH("h_qty",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="44">
+        <f>IF('3 Options'!$C$8="Oui",INDEX(Textes!$B$2:$C$55,MATCH("h_unit",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
+        <v/>
+      </c>
+      <c r="F42" s="44">
+        <f>IF('3 Options'!$C$8="Oui",INDEX(Textes!$B$2:$C$55,MATCH("h_pu",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
+        <v/>
+      </c>
+      <c r="G42" s="44">
+        <f>IF('3 Options'!$C$8="Oui",INDEX(Textes!$B$2:$C$55,MATCH("h_tot",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
+        <v/>
+      </c>
+      <c r="H42" s="43">
+        <f>IF('3 Options'!$C$8="Oui",INDEX(Textes!$B$2:$C$55,MATCH("h_det",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
         <v/>
       </c>
       <c r="M42" s="41">
-        <f>IF('3 Options'!$C$16="Oui",1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="40" customHeight="1">
-      <c r="B43" s="44">
-        <f>IF('3 Options'!$C$16="Oui",IF('3 Options'!$D$16&lt;&gt;"",'3 Options'!$D$16,INDEX(Textes!$B$2:$C$52,MATCH("forfait",Textes!$A$2:$A$52,0),Listes!$H$1)),"")</f>
-        <v/>
-      </c>
-      <c r="I43" s="45">
-        <f>IF('3 Options'!$C$16="Oui",'3 Options'!$H$16,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="B44" s="46">
-        <f>IF('3 Options'!$C$16="Oui",IF('3 Options'!$G$16="Forfait calculé (S + O + UC)",'3 Options'!$C$18&amp;" "&amp;SUBSTITUTE(INDEX(Textes!$B$2:$C$52,MATCH("calc_det",Textes!$A$2:$A$52,0),Listes!$H$1),"%s",'3 Options'!$C$19),IF('3 Options'!$G$16="Forfait par jour",'3 Options'!$E$16&amp;" j × "&amp;TEXT('3 Options'!$F$16,"#,##0.00")&amp;" €/j",""))&amp;IF(AND('3 Options'!$D$17&lt;&gt;"",'3 Options'!$G$16&lt;&gt;"Forfait global"),"  ·  ","")&amp;'3 Options'!$D$17,"")</f>
-        <v/>
-      </c>
-      <c r="I44" s="47">
-        <f>IF('3 Options'!$C$16="Oui",INDEX(Textes!$B$2:$C$52,MATCH("ht",Textes!$A$2:$A$52,0),Listes!$H$1),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="10" customHeight="1">
-      <c r="B45" s="48" t="n"/>
-      <c r="C45" s="48" t="n"/>
-      <c r="D45" s="48" t="n"/>
-      <c r="E45" s="48" t="n"/>
-      <c r="F45" s="48" t="n"/>
-      <c r="G45" s="48" t="n"/>
-      <c r="H45" s="48" t="n"/>
-      <c r="I45" s="48" t="n"/>
-      <c r="J45" s="48" t="n"/>
-      <c r="K45" s="48" t="n"/>
-    </row>
-    <row r="46" ht="10" customHeight="1">
-      <c r="B46" s="48" t="n"/>
-      <c r="C46" s="48" t="n"/>
-      <c r="D46" s="48" t="n"/>
-      <c r="E46" s="48" t="n"/>
-      <c r="F46" s="48" t="n"/>
-      <c r="G46" s="48" t="n"/>
-      <c r="H46" s="48" t="n"/>
-      <c r="I46" s="48" t="n"/>
-      <c r="J46" s="48" t="n"/>
-      <c r="K46" s="48" t="n"/>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="B47" s="33">
-        <f>INDEX(Textes!$B$2:$C$52,MATCH("sec_opt",Textes!$A$2:$A$52,0),Listes!$H$1)</f>
-        <v/>
-      </c>
-      <c r="C47" s="34" t="n"/>
-      <c r="D47" s="34" t="n"/>
-      <c r="E47" s="34" t="n"/>
-      <c r="F47" s="34" t="n"/>
-      <c r="G47" s="34" t="n"/>
-      <c r="H47" s="34" t="n"/>
-      <c r="I47" s="34" t="n"/>
-      <c r="J47" s="34" t="n"/>
-      <c r="K47" s="34" t="n"/>
-    </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="B48" s="49" t="n"/>
-      <c r="C48" s="50">
-        <f>INDEX(Textes!$B$2:$C$52,MATCH("h_label",Textes!$A$2:$A$52,0),Listes!$H$1)</f>
-        <v/>
-      </c>
-      <c r="D48" s="49">
-        <f>INDEX(Textes!$B$2:$C$52,MATCH("h_qty",Textes!$A$2:$A$52,0),Listes!$H$1)</f>
-        <v/>
-      </c>
-      <c r="E48" s="49">
-        <f>INDEX(Textes!$B$2:$C$52,MATCH("h_unit",Textes!$A$2:$A$52,0),Listes!$H$1)</f>
-        <v/>
-      </c>
-      <c r="F48" s="49">
-        <f>INDEX(Textes!$B$2:$C$52,MATCH("h_pu",Textes!$A$2:$A$52,0),Listes!$H$1)</f>
-        <v/>
-      </c>
-      <c r="G48" s="49">
-        <f>INDEX(Textes!$B$2:$C$52,MATCH("h_tot",Textes!$A$2:$A$52,0),Listes!$H$1)</f>
-        <v/>
-      </c>
-      <c r="H48" s="50">
-        <f>INDEX(Textes!$B$2:$C$52,MATCH("h_det",Textes!$A$2:$A$52,0),Listes!$H$1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="21" customHeight="1">
-      <c r="C49" s="51">
-        <f>IF(ISNUMBER(MATCH(1,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$D$6:$D$13,MATCH(1,'3 Options'!$I$6:$I$13,0))&lt;&gt;"",INDEX('3 Options'!$D$6:$D$13,MATCH(1,'3 Options'!$I$6:$I$13,0)),CHOOSE(MATCH(1,'3 Options'!$I$6:$I$13,0),INDEX(Textes!$B$2:$C$52,MATCH("op_day",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("op_mob",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("tight",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("tr_mob",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("tr_dem",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("free",Textes!$A$2:$A$52,0),Listes!$H$1)&amp;" 1",INDEX(Textes!$B$2:$C$52,MATCH("free",Textes!$A$2:$A$52,0),Listes!$H$1)&amp;" 2",INDEX(Textes!$B$2:$C$52,MATCH("free",Textes!$A$2:$A$52,0),Listes!$H$1)&amp;" 3")),"")</f>
-        <v/>
-      </c>
-      <c r="D49" s="38">
-        <f>IF(ISNUMBER(MATCH(1,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$G$6:$G$13,MATCH(1,'3 Options'!$I$6:$I$13,0))="Coût réel +15 %","",INDEX('3 Options'!$E$6:$E$13,MATCH(1,'3 Options'!$I$6:$I$13,0))),"")</f>
-        <v/>
-      </c>
-      <c r="E49" s="38">
-        <f>IF(ISNUMBER(MATCH(1,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$G$6:$G$13,MATCH(1,'3 Options'!$I$6:$I$13,0))="Coût réel +15 %","",INDEX('3 Options'!$G$6:$G$13,MATCH(1,'3 Options'!$I$6:$I$13,0))),"")</f>
-        <v/>
-      </c>
-      <c r="F49" s="39">
-        <f>IF(ISNUMBER(MATCH(1,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$G$6:$G$13,MATCH(1,'3 Options'!$I$6:$I$13,0))="Coût réel +15 %",INDEX(Textes!$B$2:$C$52,MATCH("at_cost",Textes!$A$2:$A$52,0),Listes!$H$1),IF(INDEX('3 Options'!$F$6:$F$13,MATCH(1,'3 Options'!$I$6:$I$13,0))="","",INDEX('3 Options'!$F$6:$F$13,MATCH(1,'3 Options'!$I$6:$I$13,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="G49" s="52">
-        <f>IF(ISNUMBER(MATCH(1,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$G$6:$G$13,MATCH(1,'3 Options'!$I$6:$I$13,0))="Coût réel +15 %","—",INDEX('3 Options'!$H$6:$H$13,MATCH(1,'3 Options'!$I$6:$I$13,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H49" s="53">
-        <f>IF(ISNUMBER(MATCH(1,'3 Options'!$I$6:$I$13,0)),IF(OR(MATCH(1,'3 Options'!$I$6:$I$13,0)=4,MATCH(1,'3 Options'!$I$6:$I$13,0)=5),INDEX(Textes!$B$2:$C$52,MATCH("tr_note",Textes!$A$2:$A$52,0),Listes!$H$1),""),"")</f>
+        <f>IF('3 Options'!$C$8="Oui",1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="21" customHeight="1">
+      <c r="C43" s="45">
+        <f>IF('3 Options'!$C$8="Oui",IF('3 Options'!$D$8&lt;&gt;"",'3 Options'!$D$8,INDEX(Textes!$B$2:$C$55,MATCH("tight",Textes!$A$2:$A$55,0),Listes!$H$1)),"")</f>
+        <v/>
+      </c>
+      <c r="D43" s="38">
+        <f>IF('3 Options'!$C$8="Oui",IF('3 Options'!$G$8="Coût réel +15 %","",'3 Options'!$E$8),"")</f>
+        <v/>
+      </c>
+      <c r="E43" s="38">
+        <f>IF('3 Options'!$C$8="Oui",IF('3 Options'!$G$8="Coût réel +15 %","",'3 Options'!$G$8),"")</f>
+        <v/>
+      </c>
+      <c r="F43" s="39">
+        <f>IF('3 Options'!$C$8="Oui",IF('3 Options'!$G$8="Coût réel +15 %",INDEX(Textes!$B$2:$C$55,MATCH("at_cost",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$F$8="","",'3 Options'!$F$8)),"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="46">
+        <f>IF('3 Options'!$C$8="Oui",IF('3 Options'!$G$8="Coût réel +15 %","—",'3 Options'!$H$8),"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="47">
+        <f>""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="8" customHeight="1"/>
+    <row r="45" ht="20" customHeight="1">
+      <c r="B45" s="43">
+        <f>IF(OR('3 Options'!$C$9="Oui",'3 Options'!$C$10="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("sec_tr",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
+        <v/>
+      </c>
+      <c r="C45" s="44" t="n"/>
+      <c r="D45" s="44">
+        <f>IF(OR('3 Options'!$C$9="Oui",'3 Options'!$C$10="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("h_qty",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
+        <v/>
+      </c>
+      <c r="E45" s="44">
+        <f>IF(OR('3 Options'!$C$9="Oui",'3 Options'!$C$10="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("h_unit",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
+        <v/>
+      </c>
+      <c r="F45" s="44">
+        <f>IF(OR('3 Options'!$C$9="Oui",'3 Options'!$C$10="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("h_pu",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="44">
+        <f>IF(OR('3 Options'!$C$9="Oui",'3 Options'!$C$10="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("h_tot",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
+        <v/>
+      </c>
+      <c r="H45" s="43">
+        <f>IF(OR('3 Options'!$C$9="Oui",'3 Options'!$C$10="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("h_det",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
+        <v/>
+      </c>
+      <c r="M45" s="41">
+        <f>IF(OR('3 Options'!$C$9="Oui",'3 Options'!$C$10="Oui"),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="21" customHeight="1">
+      <c r="C46" s="45">
+        <f>IF('3 Options'!$C$9="Oui",IF('3 Options'!$D$9&lt;&gt;"",'3 Options'!$D$9,INDEX(Textes!$B$2:$C$55,MATCH("tr_mob",Textes!$A$2:$A$55,0),Listes!$H$1)),"")</f>
+        <v/>
+      </c>
+      <c r="D46" s="38">
+        <f>IF('3 Options'!$C$9="Oui",IF('3 Options'!$G$9="Coût réel +15 %","",'3 Options'!$E$9),"")</f>
+        <v/>
+      </c>
+      <c r="E46" s="38">
+        <f>IF('3 Options'!$C$9="Oui",IF('3 Options'!$G$9="Coût réel +15 %","",'3 Options'!$G$9),"")</f>
+        <v/>
+      </c>
+      <c r="F46" s="39">
+        <f>IF('3 Options'!$C$9="Oui",IF('3 Options'!$G$9="Coût réel +15 %",INDEX(Textes!$B$2:$C$55,MATCH("at_cost",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$F$9="","",'3 Options'!$F$9)),"")</f>
+        <v/>
+      </c>
+      <c r="G46" s="46">
+        <f>IF('3 Options'!$C$9="Oui",IF('3 Options'!$G$9="Coût réel +15 %","—",'3 Options'!$H$9),"")</f>
+        <v/>
+      </c>
+      <c r="H46" s="47">
+        <f>IF('3 Options'!$C$9="Oui",INDEX(Textes!$B$2:$C$55,MATCH("tr_note",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="21" customHeight="1">
+      <c r="C47" s="45">
+        <f>IF('3 Options'!$C$10="Oui",IF('3 Options'!$D$10&lt;&gt;"",'3 Options'!$D$10,INDEX(Textes!$B$2:$C$55,MATCH("tr_dem",Textes!$A$2:$A$55,0),Listes!$H$1)),"")</f>
+        <v/>
+      </c>
+      <c r="D47" s="38">
+        <f>IF('3 Options'!$C$10="Oui",IF('3 Options'!$G$10="Coût réel +15 %","",'3 Options'!$E$10),"")</f>
+        <v/>
+      </c>
+      <c r="E47" s="38">
+        <f>IF('3 Options'!$C$10="Oui",IF('3 Options'!$G$10="Coût réel +15 %","",'3 Options'!$G$10),"")</f>
+        <v/>
+      </c>
+      <c r="F47" s="39">
+        <f>IF('3 Options'!$C$10="Oui",IF('3 Options'!$G$10="Coût réel +15 %",INDEX(Textes!$B$2:$C$55,MATCH("at_cost",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$F$10="","",'3 Options'!$F$10)),"")</f>
+        <v/>
+      </c>
+      <c r="G47" s="46">
+        <f>IF('3 Options'!$C$10="Oui",IF('3 Options'!$G$10="Coût réel +15 %","—",'3 Options'!$H$10),"")</f>
+        <v/>
+      </c>
+      <c r="H47" s="47">
+        <f>IF('3 Options'!$C$10="Oui",INDEX(Textes!$B$2:$C$55,MATCH("tr_note",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="8" customHeight="1"/>
+    <row r="49" ht="20" customHeight="1">
+      <c r="B49" s="43">
+        <f>IF(OR('3 Options'!$C$6="Oui",'3 Options'!$C$7="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("sec_op",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
+        <v/>
+      </c>
+      <c r="C49" s="44" t="n"/>
+      <c r="D49" s="44">
+        <f>IF(OR('3 Options'!$C$6="Oui",'3 Options'!$C$7="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("h_qty",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
+        <v/>
+      </c>
+      <c r="E49" s="44">
+        <f>IF(OR('3 Options'!$C$6="Oui",'3 Options'!$C$7="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("h_unit",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
+        <v/>
+      </c>
+      <c r="F49" s="44">
+        <f>IF(OR('3 Options'!$C$6="Oui",'3 Options'!$C$7="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("h_pu",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
+        <v/>
+      </c>
+      <c r="G49" s="44">
+        <f>IF(OR('3 Options'!$C$6="Oui",'3 Options'!$C$7="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("h_tot",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
+        <v/>
+      </c>
+      <c r="H49" s="43">
+        <f>IF(OR('3 Options'!$C$6="Oui",'3 Options'!$C$7="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("h_det",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
+        <v/>
+      </c>
+      <c r="M49" s="41">
+        <f>IF(OR('3 Options'!$C$6="Oui",'3 Options'!$C$7="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="21" customHeight="1">
-      <c r="C50" s="51">
-        <f>IF(ISNUMBER(MATCH(2,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$D$6:$D$13,MATCH(2,'3 Options'!$I$6:$I$13,0))&lt;&gt;"",INDEX('3 Options'!$D$6:$D$13,MATCH(2,'3 Options'!$I$6:$I$13,0)),CHOOSE(MATCH(2,'3 Options'!$I$6:$I$13,0),INDEX(Textes!$B$2:$C$52,MATCH("op_day",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("op_mob",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("tight",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("tr_mob",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("tr_dem",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("free",Textes!$A$2:$A$52,0),Listes!$H$1)&amp;" 1",INDEX(Textes!$B$2:$C$52,MATCH("free",Textes!$A$2:$A$52,0),Listes!$H$1)&amp;" 2",INDEX(Textes!$B$2:$C$52,MATCH("free",Textes!$A$2:$A$52,0),Listes!$H$1)&amp;" 3")),"")</f>
+      <c r="C50" s="45">
+        <f>IF('3 Options'!$C$6="Oui",IF('3 Options'!$D$6&lt;&gt;"",'3 Options'!$D$6,INDEX(Textes!$B$2:$C$55,MATCH("op_day",Textes!$A$2:$A$55,0),Listes!$H$1)),"")</f>
         <v/>
       </c>
       <c r="D50" s="38">
-        <f>IF(ISNUMBER(MATCH(2,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$G$6:$G$13,MATCH(2,'3 Options'!$I$6:$I$13,0))="Coût réel +15 %","",INDEX('3 Options'!$E$6:$E$13,MATCH(2,'3 Options'!$I$6:$I$13,0))),"")</f>
+        <f>IF('3 Options'!$C$6="Oui",IF('3 Options'!$G$6="Coût réel +15 %","",'3 Options'!$E$6),"")</f>
         <v/>
       </c>
       <c r="E50" s="38">
-        <f>IF(ISNUMBER(MATCH(2,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$G$6:$G$13,MATCH(2,'3 Options'!$I$6:$I$13,0))="Coût réel +15 %","",INDEX('3 Options'!$G$6:$G$13,MATCH(2,'3 Options'!$I$6:$I$13,0))),"")</f>
+        <f>IF('3 Options'!$C$6="Oui",IF('3 Options'!$G$6="Coût réel +15 %","",'3 Options'!$G$6),"")</f>
         <v/>
       </c>
       <c r="F50" s="39">
-        <f>IF(ISNUMBER(MATCH(2,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$G$6:$G$13,MATCH(2,'3 Options'!$I$6:$I$13,0))="Coût réel +15 %",INDEX(Textes!$B$2:$C$52,MATCH("at_cost",Textes!$A$2:$A$52,0),Listes!$H$1),IF(INDEX('3 Options'!$F$6:$F$13,MATCH(2,'3 Options'!$I$6:$I$13,0))="","",INDEX('3 Options'!$F$6:$F$13,MATCH(2,'3 Options'!$I$6:$I$13,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="G50" s="52">
-        <f>IF(ISNUMBER(MATCH(2,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$G$6:$G$13,MATCH(2,'3 Options'!$I$6:$I$13,0))="Coût réel +15 %","—",INDEX('3 Options'!$H$6:$H$13,MATCH(2,'3 Options'!$I$6:$I$13,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H50" s="53">
-        <f>IF(ISNUMBER(MATCH(2,'3 Options'!$I$6:$I$13,0)),IF(OR(MATCH(2,'3 Options'!$I$6:$I$13,0)=4,MATCH(2,'3 Options'!$I$6:$I$13,0)=5),INDEX(Textes!$B$2:$C$52,MATCH("tr_note",Textes!$A$2:$A$52,0),Listes!$H$1),""),"")</f>
+        <f>IF('3 Options'!$C$6="Oui",IF('3 Options'!$G$6="Coût réel +15 %",INDEX(Textes!$B$2:$C$55,MATCH("at_cost",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$F$6="","",'3 Options'!$F$6)),"")</f>
+        <v/>
+      </c>
+      <c r="G50" s="46">
+        <f>IF('3 Options'!$C$6="Oui",IF('3 Options'!$G$6="Coût réel +15 %","—",'3 Options'!$H$6),"")</f>
+        <v/>
+      </c>
+      <c r="H50" s="47">
+        <f>""</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="21" customHeight="1">
-      <c r="C51" s="51">
-        <f>IF(ISNUMBER(MATCH(3,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$D$6:$D$13,MATCH(3,'3 Options'!$I$6:$I$13,0))&lt;&gt;"",INDEX('3 Options'!$D$6:$D$13,MATCH(3,'3 Options'!$I$6:$I$13,0)),CHOOSE(MATCH(3,'3 Options'!$I$6:$I$13,0),INDEX(Textes!$B$2:$C$52,MATCH("op_day",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("op_mob",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("tight",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("tr_mob",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("tr_dem",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("free",Textes!$A$2:$A$52,0),Listes!$H$1)&amp;" 1",INDEX(Textes!$B$2:$C$52,MATCH("free",Textes!$A$2:$A$52,0),Listes!$H$1)&amp;" 2",INDEX(Textes!$B$2:$C$52,MATCH("free",Textes!$A$2:$A$52,0),Listes!$H$1)&amp;" 3")),"")</f>
+      <c r="C51" s="45">
+        <f>IF('3 Options'!$C$7="Oui",IF('3 Options'!$D$7&lt;&gt;"",'3 Options'!$D$7,INDEX(Textes!$B$2:$C$55,MATCH("op_mob",Textes!$A$2:$A$55,0),Listes!$H$1)),"")</f>
         <v/>
       </c>
       <c r="D51" s="38">
-        <f>IF(ISNUMBER(MATCH(3,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$G$6:$G$13,MATCH(3,'3 Options'!$I$6:$I$13,0))="Coût réel +15 %","",INDEX('3 Options'!$E$6:$E$13,MATCH(3,'3 Options'!$I$6:$I$13,0))),"")</f>
+        <f>IF('3 Options'!$C$7="Oui",IF('3 Options'!$G$7="Coût réel +15 %","",'3 Options'!$E$7),"")</f>
         <v/>
       </c>
       <c r="E51" s="38">
-        <f>IF(ISNUMBER(MATCH(3,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$G$6:$G$13,MATCH(3,'3 Options'!$I$6:$I$13,0))="Coût réel +15 %","",INDEX('3 Options'!$G$6:$G$13,MATCH(3,'3 Options'!$I$6:$I$13,0))),"")</f>
+        <f>IF('3 Options'!$C$7="Oui",IF('3 Options'!$G$7="Coût réel +15 %","",'3 Options'!$G$7),"")</f>
         <v/>
       </c>
       <c r="F51" s="39">
-        <f>IF(ISNUMBER(MATCH(3,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$G$6:$G$13,MATCH(3,'3 Options'!$I$6:$I$13,0))="Coût réel +15 %",INDEX(Textes!$B$2:$C$52,MATCH("at_cost",Textes!$A$2:$A$52,0),Listes!$H$1),IF(INDEX('3 Options'!$F$6:$F$13,MATCH(3,'3 Options'!$I$6:$I$13,0))="","",INDEX('3 Options'!$F$6:$F$13,MATCH(3,'3 Options'!$I$6:$I$13,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="G51" s="52">
-        <f>IF(ISNUMBER(MATCH(3,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$G$6:$G$13,MATCH(3,'3 Options'!$I$6:$I$13,0))="Coût réel +15 %","—",INDEX('3 Options'!$H$6:$H$13,MATCH(3,'3 Options'!$I$6:$I$13,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H51" s="53">
-        <f>IF(ISNUMBER(MATCH(3,'3 Options'!$I$6:$I$13,0)),IF(OR(MATCH(3,'3 Options'!$I$6:$I$13,0)=4,MATCH(3,'3 Options'!$I$6:$I$13,0)=5),INDEX(Textes!$B$2:$C$52,MATCH("tr_note",Textes!$A$2:$A$52,0),Listes!$H$1),""),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="21" customHeight="1">
-      <c r="C52" s="51">
-        <f>IF(ISNUMBER(MATCH(4,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$D$6:$D$13,MATCH(4,'3 Options'!$I$6:$I$13,0))&lt;&gt;"",INDEX('3 Options'!$D$6:$D$13,MATCH(4,'3 Options'!$I$6:$I$13,0)),CHOOSE(MATCH(4,'3 Options'!$I$6:$I$13,0),INDEX(Textes!$B$2:$C$52,MATCH("op_day",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("op_mob",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("tight",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("tr_mob",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("tr_dem",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("free",Textes!$A$2:$A$52,0),Listes!$H$1)&amp;" 1",INDEX(Textes!$B$2:$C$52,MATCH("free",Textes!$A$2:$A$52,0),Listes!$H$1)&amp;" 2",INDEX(Textes!$B$2:$C$52,MATCH("free",Textes!$A$2:$A$52,0),Listes!$H$1)&amp;" 3")),"")</f>
-        <v/>
-      </c>
-      <c r="D52" s="38">
-        <f>IF(ISNUMBER(MATCH(4,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$G$6:$G$13,MATCH(4,'3 Options'!$I$6:$I$13,0))="Coût réel +15 %","",INDEX('3 Options'!$E$6:$E$13,MATCH(4,'3 Options'!$I$6:$I$13,0))),"")</f>
-        <v/>
-      </c>
-      <c r="E52" s="38">
-        <f>IF(ISNUMBER(MATCH(4,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$G$6:$G$13,MATCH(4,'3 Options'!$I$6:$I$13,0))="Coût réel +15 %","",INDEX('3 Options'!$G$6:$G$13,MATCH(4,'3 Options'!$I$6:$I$13,0))),"")</f>
-        <v/>
-      </c>
-      <c r="F52" s="39">
-        <f>IF(ISNUMBER(MATCH(4,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$G$6:$G$13,MATCH(4,'3 Options'!$I$6:$I$13,0))="Coût réel +15 %",INDEX(Textes!$B$2:$C$52,MATCH("at_cost",Textes!$A$2:$A$52,0),Listes!$H$1),IF(INDEX('3 Options'!$F$6:$F$13,MATCH(4,'3 Options'!$I$6:$I$13,0))="","",INDEX('3 Options'!$F$6:$F$13,MATCH(4,'3 Options'!$I$6:$I$13,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="G52" s="52">
-        <f>IF(ISNUMBER(MATCH(4,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$G$6:$G$13,MATCH(4,'3 Options'!$I$6:$I$13,0))="Coût réel +15 %","—",INDEX('3 Options'!$H$6:$H$13,MATCH(4,'3 Options'!$I$6:$I$13,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H52" s="53">
-        <f>IF(ISNUMBER(MATCH(4,'3 Options'!$I$6:$I$13,0)),IF(OR(MATCH(4,'3 Options'!$I$6:$I$13,0)=4,MATCH(4,'3 Options'!$I$6:$I$13,0)=5),INDEX(Textes!$B$2:$C$52,MATCH("tr_note",Textes!$A$2:$A$52,0),Listes!$H$1),""),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="21" customHeight="1">
-      <c r="C53" s="51">
-        <f>IF(ISNUMBER(MATCH(5,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$D$6:$D$13,MATCH(5,'3 Options'!$I$6:$I$13,0))&lt;&gt;"",INDEX('3 Options'!$D$6:$D$13,MATCH(5,'3 Options'!$I$6:$I$13,0)),CHOOSE(MATCH(5,'3 Options'!$I$6:$I$13,0),INDEX(Textes!$B$2:$C$52,MATCH("op_day",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("op_mob",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("tight",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("tr_mob",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("tr_dem",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("free",Textes!$A$2:$A$52,0),Listes!$H$1)&amp;" 1",INDEX(Textes!$B$2:$C$52,MATCH("free",Textes!$A$2:$A$52,0),Listes!$H$1)&amp;" 2",INDEX(Textes!$B$2:$C$52,MATCH("free",Textes!$A$2:$A$52,0),Listes!$H$1)&amp;" 3")),"")</f>
-        <v/>
-      </c>
-      <c r="D53" s="38">
-        <f>IF(ISNUMBER(MATCH(5,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$G$6:$G$13,MATCH(5,'3 Options'!$I$6:$I$13,0))="Coût réel +15 %","",INDEX('3 Options'!$E$6:$E$13,MATCH(5,'3 Options'!$I$6:$I$13,0))),"")</f>
-        <v/>
-      </c>
-      <c r="E53" s="38">
-        <f>IF(ISNUMBER(MATCH(5,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$G$6:$G$13,MATCH(5,'3 Options'!$I$6:$I$13,0))="Coût réel +15 %","",INDEX('3 Options'!$G$6:$G$13,MATCH(5,'3 Options'!$I$6:$I$13,0))),"")</f>
-        <v/>
-      </c>
-      <c r="F53" s="39">
-        <f>IF(ISNUMBER(MATCH(5,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$G$6:$G$13,MATCH(5,'3 Options'!$I$6:$I$13,0))="Coût réel +15 %",INDEX(Textes!$B$2:$C$52,MATCH("at_cost",Textes!$A$2:$A$52,0),Listes!$H$1),IF(INDEX('3 Options'!$F$6:$F$13,MATCH(5,'3 Options'!$I$6:$I$13,0))="","",INDEX('3 Options'!$F$6:$F$13,MATCH(5,'3 Options'!$I$6:$I$13,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="G53" s="52">
-        <f>IF(ISNUMBER(MATCH(5,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$G$6:$G$13,MATCH(5,'3 Options'!$I$6:$I$13,0))="Coût réel +15 %","—",INDEX('3 Options'!$H$6:$H$13,MATCH(5,'3 Options'!$I$6:$I$13,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H53" s="53">
-        <f>IF(ISNUMBER(MATCH(5,'3 Options'!$I$6:$I$13,0)),IF(OR(MATCH(5,'3 Options'!$I$6:$I$13,0)=4,MATCH(5,'3 Options'!$I$6:$I$13,0)=5),INDEX(Textes!$B$2:$C$52,MATCH("tr_note",Textes!$A$2:$A$52,0),Listes!$H$1),""),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="21" customHeight="1">
-      <c r="C54" s="51">
-        <f>IF(ISNUMBER(MATCH(6,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$D$6:$D$13,MATCH(6,'3 Options'!$I$6:$I$13,0))&lt;&gt;"",INDEX('3 Options'!$D$6:$D$13,MATCH(6,'3 Options'!$I$6:$I$13,0)),CHOOSE(MATCH(6,'3 Options'!$I$6:$I$13,0),INDEX(Textes!$B$2:$C$52,MATCH("op_day",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("op_mob",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("tight",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("tr_mob",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("tr_dem",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("free",Textes!$A$2:$A$52,0),Listes!$H$1)&amp;" 1",INDEX(Textes!$B$2:$C$52,MATCH("free",Textes!$A$2:$A$52,0),Listes!$H$1)&amp;" 2",INDEX(Textes!$B$2:$C$52,MATCH("free",Textes!$A$2:$A$52,0),Listes!$H$1)&amp;" 3")),"")</f>
-        <v/>
-      </c>
-      <c r="D54" s="38">
-        <f>IF(ISNUMBER(MATCH(6,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$G$6:$G$13,MATCH(6,'3 Options'!$I$6:$I$13,0))="Coût réel +15 %","",INDEX('3 Options'!$E$6:$E$13,MATCH(6,'3 Options'!$I$6:$I$13,0))),"")</f>
-        <v/>
-      </c>
-      <c r="E54" s="38">
-        <f>IF(ISNUMBER(MATCH(6,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$G$6:$G$13,MATCH(6,'3 Options'!$I$6:$I$13,0))="Coût réel +15 %","",INDEX('3 Options'!$G$6:$G$13,MATCH(6,'3 Options'!$I$6:$I$13,0))),"")</f>
-        <v/>
-      </c>
-      <c r="F54" s="39">
-        <f>IF(ISNUMBER(MATCH(6,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$G$6:$G$13,MATCH(6,'3 Options'!$I$6:$I$13,0))="Coût réel +15 %",INDEX(Textes!$B$2:$C$52,MATCH("at_cost",Textes!$A$2:$A$52,0),Listes!$H$1),IF(INDEX('3 Options'!$F$6:$F$13,MATCH(6,'3 Options'!$I$6:$I$13,0))="","",INDEX('3 Options'!$F$6:$F$13,MATCH(6,'3 Options'!$I$6:$I$13,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="G54" s="52">
-        <f>IF(ISNUMBER(MATCH(6,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$G$6:$G$13,MATCH(6,'3 Options'!$I$6:$I$13,0))="Coût réel +15 %","—",INDEX('3 Options'!$H$6:$H$13,MATCH(6,'3 Options'!$I$6:$I$13,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H54" s="53">
-        <f>IF(ISNUMBER(MATCH(6,'3 Options'!$I$6:$I$13,0)),IF(OR(MATCH(6,'3 Options'!$I$6:$I$13,0)=4,MATCH(6,'3 Options'!$I$6:$I$13,0)=5),INDEX(Textes!$B$2:$C$52,MATCH("tr_note",Textes!$A$2:$A$52,0),Listes!$H$1),""),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="21" customHeight="1">
-      <c r="C55" s="51">
-        <f>IF(ISNUMBER(MATCH(7,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$D$6:$D$13,MATCH(7,'3 Options'!$I$6:$I$13,0))&lt;&gt;"",INDEX('3 Options'!$D$6:$D$13,MATCH(7,'3 Options'!$I$6:$I$13,0)),CHOOSE(MATCH(7,'3 Options'!$I$6:$I$13,0),INDEX(Textes!$B$2:$C$52,MATCH("op_day",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("op_mob",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("tight",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("tr_mob",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("tr_dem",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("free",Textes!$A$2:$A$52,0),Listes!$H$1)&amp;" 1",INDEX(Textes!$B$2:$C$52,MATCH("free",Textes!$A$2:$A$52,0),Listes!$H$1)&amp;" 2",INDEX(Textes!$B$2:$C$52,MATCH("free",Textes!$A$2:$A$52,0),Listes!$H$1)&amp;" 3")),"")</f>
-        <v/>
-      </c>
-      <c r="D55" s="38">
-        <f>IF(ISNUMBER(MATCH(7,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$G$6:$G$13,MATCH(7,'3 Options'!$I$6:$I$13,0))="Coût réel +15 %","",INDEX('3 Options'!$E$6:$E$13,MATCH(7,'3 Options'!$I$6:$I$13,0))),"")</f>
-        <v/>
-      </c>
-      <c r="E55" s="38">
-        <f>IF(ISNUMBER(MATCH(7,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$G$6:$G$13,MATCH(7,'3 Options'!$I$6:$I$13,0))="Coût réel +15 %","",INDEX('3 Options'!$G$6:$G$13,MATCH(7,'3 Options'!$I$6:$I$13,0))),"")</f>
-        <v/>
-      </c>
-      <c r="F55" s="39">
-        <f>IF(ISNUMBER(MATCH(7,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$G$6:$G$13,MATCH(7,'3 Options'!$I$6:$I$13,0))="Coût réel +15 %",INDEX(Textes!$B$2:$C$52,MATCH("at_cost",Textes!$A$2:$A$52,0),Listes!$H$1),IF(INDEX('3 Options'!$F$6:$F$13,MATCH(7,'3 Options'!$I$6:$I$13,0))="","",INDEX('3 Options'!$F$6:$F$13,MATCH(7,'3 Options'!$I$6:$I$13,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="G55" s="52">
-        <f>IF(ISNUMBER(MATCH(7,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$G$6:$G$13,MATCH(7,'3 Options'!$I$6:$I$13,0))="Coût réel +15 %","—",INDEX('3 Options'!$H$6:$H$13,MATCH(7,'3 Options'!$I$6:$I$13,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H55" s="53">
-        <f>IF(ISNUMBER(MATCH(7,'3 Options'!$I$6:$I$13,0)),IF(OR(MATCH(7,'3 Options'!$I$6:$I$13,0)=4,MATCH(7,'3 Options'!$I$6:$I$13,0)=5),INDEX(Textes!$B$2:$C$52,MATCH("tr_note",Textes!$A$2:$A$52,0),Listes!$H$1),""),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" ht="21" customHeight="1">
-      <c r="C56" s="51">
-        <f>IF(ISNUMBER(MATCH(8,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$D$6:$D$13,MATCH(8,'3 Options'!$I$6:$I$13,0))&lt;&gt;"",INDEX('3 Options'!$D$6:$D$13,MATCH(8,'3 Options'!$I$6:$I$13,0)),CHOOSE(MATCH(8,'3 Options'!$I$6:$I$13,0),INDEX(Textes!$B$2:$C$52,MATCH("op_day",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("op_mob",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("tight",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("tr_mob",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("tr_dem",Textes!$A$2:$A$52,0),Listes!$H$1),INDEX(Textes!$B$2:$C$52,MATCH("free",Textes!$A$2:$A$52,0),Listes!$H$1)&amp;" 1",INDEX(Textes!$B$2:$C$52,MATCH("free",Textes!$A$2:$A$52,0),Listes!$H$1)&amp;" 2",INDEX(Textes!$B$2:$C$52,MATCH("free",Textes!$A$2:$A$52,0),Listes!$H$1)&amp;" 3")),"")</f>
-        <v/>
-      </c>
-      <c r="D56" s="38">
-        <f>IF(ISNUMBER(MATCH(8,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$G$6:$G$13,MATCH(8,'3 Options'!$I$6:$I$13,0))="Coût réel +15 %","",INDEX('3 Options'!$E$6:$E$13,MATCH(8,'3 Options'!$I$6:$I$13,0))),"")</f>
-        <v/>
-      </c>
-      <c r="E56" s="38">
-        <f>IF(ISNUMBER(MATCH(8,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$G$6:$G$13,MATCH(8,'3 Options'!$I$6:$I$13,0))="Coût réel +15 %","",INDEX('3 Options'!$G$6:$G$13,MATCH(8,'3 Options'!$I$6:$I$13,0))),"")</f>
-        <v/>
-      </c>
-      <c r="F56" s="39">
-        <f>IF(ISNUMBER(MATCH(8,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$G$6:$G$13,MATCH(8,'3 Options'!$I$6:$I$13,0))="Coût réel +15 %",INDEX(Textes!$B$2:$C$52,MATCH("at_cost",Textes!$A$2:$A$52,0),Listes!$H$1),IF(INDEX('3 Options'!$F$6:$F$13,MATCH(8,'3 Options'!$I$6:$I$13,0))="","",INDEX('3 Options'!$F$6:$F$13,MATCH(8,'3 Options'!$I$6:$I$13,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="G56" s="52">
-        <f>IF(ISNUMBER(MATCH(8,'3 Options'!$I$6:$I$13,0)),IF(INDEX('3 Options'!$G$6:$G$13,MATCH(8,'3 Options'!$I$6:$I$13,0))="Coût réel +15 %","—",INDEX('3 Options'!$H$6:$H$13,MATCH(8,'3 Options'!$I$6:$I$13,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H56" s="53">
-        <f>IF(ISNUMBER(MATCH(8,'3 Options'!$I$6:$I$13,0)),IF(OR(MATCH(8,'3 Options'!$I$6:$I$13,0)=4,MATCH(8,'3 Options'!$I$6:$I$13,0)=5),INDEX(Textes!$B$2:$C$52,MATCH("tr_note",Textes!$A$2:$A$52,0),Listes!$H$1),""),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="10" customHeight="1"/>
-    <row r="58" ht="20" customHeight="1">
-      <c r="B58" s="33">
-        <f>INDEX(Textes!$B$2:$C$52,MATCH("sec_cond",Textes!$A$2:$A$52,0),Listes!$H$1)</f>
-        <v/>
-      </c>
-      <c r="C58" s="34" t="n"/>
-      <c r="D58" s="34" t="n"/>
-      <c r="E58" s="34" t="n"/>
-      <c r="F58" s="34" t="n"/>
-      <c r="G58" s="34" t="n"/>
-      <c r="H58" s="34" t="n"/>
-      <c r="I58" s="34" t="n"/>
-      <c r="J58" s="34" t="n"/>
-      <c r="K58" s="34" t="n"/>
-    </row>
-    <row r="59" ht="66" customHeight="1">
-      <c r="B59" s="54" t="inlineStr">
+        <f>IF('3 Options'!$C$7="Oui",IF('3 Options'!$G$7="Coût réel +15 %",INDEX(Textes!$B$2:$C$55,MATCH("at_cost",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$F$7="","",'3 Options'!$F$7)),"")</f>
+        <v/>
+      </c>
+      <c r="G51" s="46">
+        <f>IF('3 Options'!$C$7="Oui",IF('3 Options'!$G$7="Coût réel +15 %","—",'3 Options'!$H$7),"")</f>
+        <v/>
+      </c>
+      <c r="H51" s="47">
+        <f>""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="8" customHeight="1"/>
+    <row r="53" ht="40" customHeight="1">
+      <c r="B53" s="48">
+        <f>IF('3 Options'!$C$13="Oui",UPPER(INDEX(Textes!$B$2:$C$55,MATCH("forfait",Textes!$A$2:$A$55,0),Listes!$H$1))&amp;IF('3 Options'!$D$13&lt;&gt;"","   ·   "&amp;'3 Options'!$D$13,""),"")</f>
+        <v/>
+      </c>
+      <c r="I53" s="49">
+        <f>IF('3 Options'!$C$13="Oui",'3 Options'!$H$13,"")</f>
+        <v/>
+      </c>
+      <c r="M53" s="41">
+        <f>IF('3 Options'!$C$13="Oui",1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="24" customHeight="1">
+      <c r="B54" s="50">
+        <f>IF('3 Options'!$C$13="Oui",IF('3 Options'!$G$13="Forfait calculé (S + O + UC)",'3 Options'!$C$15&amp;" "&amp;SUBSTITUTE(INDEX(Textes!$B$2:$C$55,MATCH("calc_det",Textes!$A$2:$A$55,0),Listes!$H$1),"%s",'3 Options'!$C$16)&amp;"   ·   "&amp;INDEX(Textes!$B$2:$C$55,MATCH("ht",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$G$13="Forfait par jour",'3 Options'!$E$13&amp;" j × "&amp;TEXT('3 Options'!$F$13,"#,##0.00")&amp;" €/j   ·   "&amp;INDEX(Textes!$B$2:$C$55,MATCH("ht",Textes!$A$2:$A$55,0),Listes!$H$1),INDEX(Textes!$B$2:$C$55,MATCH("ht",Textes!$A$2:$A$55,0),Listes!$H$1)))&amp;IF('3 Options'!$D$14&lt;&gt;"","   ·   "&amp;'3 Options'!$D$14,""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="10" customHeight="1"/>
+    <row r="56" ht="20" customHeight="1">
+      <c r="B56" s="33">
+        <f>INDEX(Textes!$B$2:$C$55,MATCH("sec_cond",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <v/>
+      </c>
+      <c r="C56" s="34" t="n"/>
+      <c r="D56" s="34" t="n"/>
+      <c r="E56" s="34" t="n"/>
+      <c r="F56" s="34" t="n"/>
+      <c r="G56" s="34" t="n"/>
+      <c r="H56" s="34" t="n"/>
+      <c r="I56" s="34" t="n"/>
+      <c r="J56" s="34" t="n"/>
+      <c r="K56" s="34" t="n"/>
+    </row>
+    <row r="57" ht="66" customHeight="1">
+      <c r="B57" s="51" t="inlineStr">
         <is>
           <t>La location s'entend depuis le jour de départ de la base d'origine jusqu'à son retour au même endroit.
 Le Wear Charge s'applique pour toute usure liée à un usage normal des équipements. En cas de dommages plus importants liés à un usage anormal, la valeur de remplacement sera facturée sur documentation.
@@ -4352,8 +4083,8 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="66" customHeight="1">
-      <c r="B60" s="54" t="inlineStr">
+    <row r="58" ht="66" customHeight="1">
+      <c r="B58" s="51" t="inlineStr">
         <is>
           <t>The rental is from the day of departure from the base of origin until its return to the same place.
 Wear Charge applies to all wear and tear related to normal use of equipment. In case of greater damage due to abnormal use, the replacement value will be charged based on supporting documentation.
@@ -4362,131 +4093,128 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="10" customHeight="1"/>
-    <row r="62">
-      <c r="B62" s="55">
-        <f>INDEX(Textes!$B$2:$C$52,MATCH("accept",Textes!$A$2:$A$52,0),Listes!$H$1)</f>
-        <v/>
-      </c>
+    <row r="59" ht="10" customHeight="1"/>
+    <row r="60">
+      <c r="B60" s="52">
+        <f>INDEX(Textes!$B$2:$C$55,MATCH("accept",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="B61" s="53">
+        <f>INDEX(Textes!$B$2:$C$55,MATCH("sig_name",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <v/>
+      </c>
+      <c r="C61" s="54" t="n"/>
+      <c r="D61" s="55" t="n"/>
+      <c r="E61" s="53">
+        <f>INDEX(Textes!$B$2:$C$55,MATCH("sig_date",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <v/>
+      </c>
+      <c r="F61" s="54" t="n"/>
+      <c r="G61" s="55" t="n"/>
+      <c r="H61" s="53">
+        <f>INDEX(Textes!$B$2:$C$55,MATCH("sig_sig",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <v/>
+      </c>
+      <c r="I61" s="54" t="n"/>
+      <c r="J61" s="54" t="n"/>
+      <c r="K61" s="55" t="n"/>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="B62" s="56" t="n"/>
+      <c r="C62" s="57" t="n"/>
+      <c r="D62" s="58" t="n"/>
+      <c r="E62" s="56" t="n"/>
+      <c r="F62" s="57" t="n"/>
+      <c r="G62" s="58" t="n"/>
+      <c r="H62" s="56" t="n"/>
+      <c r="I62" s="57" t="n"/>
+      <c r="J62" s="57" t="n"/>
+      <c r="K62" s="58" t="n"/>
     </row>
     <row r="63" ht="16" customHeight="1">
-      <c r="B63" s="56">
-        <f>INDEX(Textes!$B$2:$C$52,MATCH("sig_name",Textes!$A$2:$A$52,0),Listes!$H$1)</f>
-        <v/>
-      </c>
+      <c r="B63" s="56" t="n"/>
       <c r="C63" s="57" t="n"/>
       <c r="D63" s="58" t="n"/>
-      <c r="E63" s="56">
-        <f>INDEX(Textes!$B$2:$C$52,MATCH("sig_date",Textes!$A$2:$A$52,0),Listes!$H$1)</f>
-        <v/>
-      </c>
+      <c r="E63" s="56" t="n"/>
       <c r="F63" s="57" t="n"/>
       <c r="G63" s="58" t="n"/>
-      <c r="H63" s="56">
-        <f>INDEX(Textes!$B$2:$C$52,MATCH("sig_sig",Textes!$A$2:$A$52,0),Listes!$H$1)</f>
-        <v/>
-      </c>
+      <c r="H63" s="56" t="n"/>
       <c r="I63" s="57" t="n"/>
       <c r="J63" s="57" t="n"/>
       <c r="K63" s="58" t="n"/>
     </row>
     <row r="64" ht="16" customHeight="1">
       <c r="B64" s="59" t="n"/>
-      <c r="C64" s="48" t="n"/>
+      <c r="C64" s="32" t="n"/>
       <c r="D64" s="60" t="n"/>
       <c r="E64" s="59" t="n"/>
-      <c r="F64" s="48" t="n"/>
+      <c r="F64" s="32" t="n"/>
       <c r="G64" s="60" t="n"/>
       <c r="H64" s="59" t="n"/>
-      <c r="I64" s="48" t="n"/>
-      <c r="J64" s="48" t="n"/>
+      <c r="I64" s="32" t="n"/>
+      <c r="J64" s="32" t="n"/>
       <c r="K64" s="60" t="n"/>
     </row>
-    <row r="65" ht="16" customHeight="1">
-      <c r="B65" s="59" t="n"/>
-      <c r="C65" s="48" t="n"/>
-      <c r="D65" s="60" t="n"/>
-      <c r="E65" s="59" t="n"/>
-      <c r="F65" s="48" t="n"/>
-      <c r="G65" s="60" t="n"/>
-      <c r="H65" s="59" t="n"/>
-      <c r="I65" s="48" t="n"/>
-      <c r="J65" s="48" t="n"/>
-      <c r="K65" s="60" t="n"/>
-    </row>
-    <row r="66" ht="16" customHeight="1">
-      <c r="B66" s="61" t="n"/>
-      <c r="C66" s="32" t="n"/>
-      <c r="D66" s="62" t="n"/>
-      <c r="E66" s="61" t="n"/>
-      <c r="F66" s="32" t="n"/>
-      <c r="G66" s="62" t="n"/>
-      <c r="H66" s="61" t="n"/>
-      <c r="I66" s="32" t="n"/>
-      <c r="J66" s="32" t="n"/>
-      <c r="K66" s="62" t="n"/>
-    </row>
-    <row r="68">
-      <c r="B68" s="63" t="inlineStr">
+    <row r="66">
+      <c r="B66" s="61" t="inlineStr">
         <is>
           <t>ENEDRIL · Z-Induspal · 3 Av. des Lacs · 64140 LONS (France) · SIRET 79464246200020 · TVA FR11794642462</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="55">
-    <mergeCell ref="H63:K66"/>
-    <mergeCell ref="D11:F11"/>
+  <mergeCells count="52">
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B40:K40"/>
-    <mergeCell ref="B68:K68"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="H48:K48"/>
+    <mergeCell ref="H47:K47"/>
+    <mergeCell ref="I53:K53"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="D7:F7"/>
+    <mergeCell ref="H42:K42"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B63:D66"/>
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="H61:K64"/>
     <mergeCell ref="I5:K5"/>
     <mergeCell ref="G10:H10"/>
-    <mergeCell ref="H53:K53"/>
+    <mergeCell ref="B42:C42"/>
     <mergeCell ref="I8:K8"/>
-    <mergeCell ref="D12:F12"/>
     <mergeCell ref="D9:F9"/>
     <mergeCell ref="G6:H6"/>
-    <mergeCell ref="B47:K47"/>
-    <mergeCell ref="H54:K54"/>
+    <mergeCell ref="B54:K54"/>
+    <mergeCell ref="H43:K43"/>
     <mergeCell ref="D8:F8"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="B62:K62"/>
-    <mergeCell ref="B59:K59"/>
-    <mergeCell ref="H55:K55"/>
+    <mergeCell ref="B66:K66"/>
     <mergeCell ref="H50:K50"/>
     <mergeCell ref="I10:K10"/>
     <mergeCell ref="D5:F5"/>
-    <mergeCell ref="E63:G66"/>
-    <mergeCell ref="H56:K56"/>
+    <mergeCell ref="B56:K56"/>
     <mergeCell ref="B58:K58"/>
-    <mergeCell ref="B43:H43"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="I9:K9"/>
     <mergeCell ref="G5:H5"/>
+    <mergeCell ref="B61:D64"/>
+    <mergeCell ref="H46:K46"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="E1:K1"/>
-    <mergeCell ref="B42:K42"/>
+    <mergeCell ref="B49:C49"/>
     <mergeCell ref="H49:K49"/>
     <mergeCell ref="H51:K51"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="B60:K60"/>
     <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B57:K57"/>
     <mergeCell ref="B14:K14"/>
-    <mergeCell ref="H52:K52"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="B53:H53"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="H45:K45"/>
+    <mergeCell ref="E61:G64"/>
     <mergeCell ref="E2:K2"/>
     <mergeCell ref="D6:F6"/>
     <mergeCell ref="I7:K7"/>
@@ -4507,19 +4235,54 @@
       <formula>E16="incl."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B42:K44">
+  <conditionalFormatting sqref="B42:K42">
     <cfRule type="expression" priority="5" dxfId="5">
-      <formula>$M$42=1</formula>
+      <formula>$M42=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B43">
-    <cfRule type="expression" priority="6" dxfId="6">
-      <formula>$M$42=1</formula>
+  <conditionalFormatting sqref="B43:K43">
+    <cfRule type="expression" priority="6" dxfId="2">
+      <formula>$C43&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B49:K56">
-    <cfRule type="expression" priority="7" dxfId="2">
-      <formula>$C49&lt;&gt;""</formula>
+  <conditionalFormatting sqref="B45:K45">
+    <cfRule type="expression" priority="7" dxfId="5">
+      <formula>$M45=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B46:K46">
+    <cfRule type="expression" priority="8" dxfId="2">
+      <formula>$C46&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B47:K47">
+    <cfRule type="expression" priority="9" dxfId="2">
+      <formula>$C47&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B49:K49">
+    <cfRule type="expression" priority="10" dxfId="5">
+      <formula>$M49=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B50:K50">
+    <cfRule type="expression" priority="11" dxfId="2">
+      <formula>$C50&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B51:K51">
+    <cfRule type="expression" priority="12" dxfId="2">
+      <formula>$C51&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B53:K53">
+    <cfRule type="expression" priority="13" dxfId="6">
+      <formula>$M$53=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B54:K54">
+    <cfRule type="expression" priority="14" dxfId="7">
+      <formula>$M$53=1</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
@@ -4566,366 +4329,366 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="64" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>Contact Enedril</t>
         </is>
       </c>
-      <c r="B1" s="64" t="inlineStr">
+      <c r="B1" s="62" t="inlineStr">
         <is>
           <t>E-mail</t>
         </is>
       </c>
-      <c r="D1" s="64" t="inlineStr">
+      <c r="D1" s="62" t="inlineStr">
         <is>
           <t>Incoterm</t>
         </is>
       </c>
-      <c r="E1" s="64" t="inlineStr">
+      <c r="E1" s="62" t="inlineStr">
         <is>
           <t>Validité</t>
         </is>
       </c>
-      <c r="F1" s="64" t="inlineStr">
+      <c r="F1" s="62" t="inlineStr">
         <is>
           <t>Règlement</t>
         </is>
       </c>
-      <c r="G1" s="64" t="inlineStr">
+      <c r="G1" s="62" t="inlineStr">
         <is>
           <t>Oui / Non</t>
         </is>
       </c>
-      <c r="H1" s="65" t="n">
+      <c r="H1" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="J1" s="64" t="inlineStr">
+      <c r="J1" s="62" t="inlineStr">
         <is>
           <t>Support de colisage</t>
         </is>
       </c>
-      <c r="K1" s="64" t="inlineStr">
+      <c r="K1" s="62" t="inlineStr">
         <is>
           <t>N° de colis</t>
         </is>
       </c>
-      <c r="L1" s="64" t="inlineStr">
+      <c r="L1" s="62" t="inlineStr">
         <is>
           <t>Unité</t>
         </is>
       </c>
-      <c r="M1" s="64" t="inlineStr">
+      <c r="M1" s="62" t="inlineStr">
         <is>
           <t>Mode transport</t>
         </is>
       </c>
-      <c r="N1" s="64" t="inlineStr">
+      <c r="N1" s="62" t="inlineStr">
         <is>
           <t>Mode forfait</t>
         </is>
       </c>
-      <c r="P1" s="64" t="inlineStr">
+      <c r="P1" s="62" t="inlineStr">
         <is>
           <t>Statut</t>
         </is>
       </c>
-      <c r="Q1" s="64" t="inlineStr">
+      <c r="Q1" s="62" t="inlineStr">
         <is>
           <t>Test / Taille</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="66" t="inlineStr">
+      <c r="A2" s="64" t="inlineStr">
         <is>
           <t>Fabien JACQUOT</t>
         </is>
       </c>
-      <c r="B2" s="66" t="inlineStr">
+      <c r="B2" s="64" t="inlineStr">
         <is>
           <t>fjacquot@enedril.fr</t>
         </is>
       </c>
-      <c r="D2" s="66" t="inlineStr">
+      <c r="D2" s="64" t="inlineStr">
         <is>
           <t>EXW Lons</t>
         </is>
       </c>
-      <c r="E2" s="66" t="inlineStr">
+      <c r="E2" s="64" t="inlineStr">
         <is>
           <t>15 jours / 15 days</t>
         </is>
       </c>
-      <c r="F2" s="66" t="inlineStr">
+      <c r="F2" s="64" t="inlineStr">
         <is>
           <t>30 jours date de facture / 30 days invoice date</t>
         </is>
       </c>
-      <c r="G2" s="66" t="inlineStr">
+      <c r="G2" s="64" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="H2" s="67" t="inlineStr">
+      <c r="H2" s="65" t="inlineStr">
         <is>
           <t>← langue du devis : 1 = français, 2 = anglais</t>
         </is>
       </c>
-      <c r="J2" s="66" t="inlineStr">
+      <c r="J2" s="64" t="inlineStr">
         <is>
           <t>Palette</t>
         </is>
       </c>
-      <c r="K2" s="66" t="inlineStr">
+      <c r="K2" s="64" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="L2" s="66" t="inlineStr">
+      <c r="L2" s="64" t="inlineStr">
         <is>
           <t>forfait</t>
         </is>
       </c>
-      <c r="M2" s="66" t="inlineStr">
+      <c r="M2" s="64" t="inlineStr">
         <is>
           <t>Coût réel +15 %</t>
         </is>
       </c>
-      <c r="N2" s="66" t="inlineStr">
+      <c r="N2" s="64" t="inlineStr">
         <is>
           <t>Forfait calculé (S + O + UC)</t>
         </is>
       </c>
-      <c r="P2" s="66" t="inlineStr">
+      <c r="P2" s="64" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="Q2" s="66" t="inlineStr">
+      <c r="Q2" s="64" t="inlineStr">
         <is>
           <t>Taille OK</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="66" t="inlineStr">
+      <c r="A3" s="64" t="inlineStr">
         <is>
           <t>Alexis ESTINES</t>
         </is>
       </c>
-      <c r="B3" s="66" t="inlineStr">
+      <c r="B3" s="64" t="inlineStr">
         <is>
           <t>aestines@enedril.fr</t>
         </is>
       </c>
-      <c r="D3" s="66" t="inlineStr">
+      <c r="D3" s="64" t="inlineStr">
         <is>
           <t>FCA Lons</t>
         </is>
       </c>
-      <c r="E3" s="66" t="inlineStr">
+      <c r="E3" s="64" t="inlineStr">
         <is>
           <t>30 jours / 30 days</t>
         </is>
       </c>
-      <c r="F3" s="66" t="inlineStr">
+      <c r="F3" s="64" t="inlineStr">
         <is>
           <t>30 jours fin de mois / 30 days end of month</t>
         </is>
       </c>
-      <c r="G3" s="66" t="inlineStr">
+      <c r="G3" s="64" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J3" s="66" t="inlineStr">
+      <c r="J3" s="64" t="inlineStr">
         <is>
           <t>Fishing basket</t>
         </is>
       </c>
-      <c r="K3" s="66" t="inlineStr">
+      <c r="K3" s="64" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L3" s="66" t="inlineStr">
+      <c r="L3" s="64" t="inlineStr">
         <is>
           <t>€/jour</t>
         </is>
       </c>
-      <c r="M3" s="66" t="inlineStr">
+      <c r="M3" s="64" t="inlineStr">
         <is>
           <t>Forfait</t>
         </is>
       </c>
-      <c r="N3" s="66" t="inlineStr">
+      <c r="N3" s="64" t="inlineStr">
         <is>
           <t>Forfait global</t>
         </is>
       </c>
-      <c r="P3" s="66" t="inlineStr">
+      <c r="P3" s="64" t="inlineStr">
         <is>
           <t>En cours</t>
         </is>
       </c>
-      <c r="Q3" s="66" t="inlineStr">
+      <c r="Q3" s="64" t="inlineStr">
         <is>
           <t>Test OK</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="66" t="inlineStr">
+      <c r="A4" s="64" t="inlineStr">
         <is>
           <t>Paul HYNDERICK</t>
         </is>
       </c>
-      <c r="B4" s="66" t="inlineStr">
+      <c r="B4" s="64" t="inlineStr">
         <is>
           <t>phynderick@enedril.fr</t>
         </is>
       </c>
-      <c r="D4" s="66" t="inlineStr">
+      <c r="D4" s="64" t="inlineStr">
         <is>
           <t>DAP</t>
         </is>
       </c>
-      <c r="E4" s="66" t="inlineStr">
+      <c r="E4" s="64" t="inlineStr">
         <is>
           <t>60 jours / 60 days</t>
         </is>
       </c>
-      <c r="F4" s="66" t="inlineStr">
+      <c r="F4" s="64" t="inlineStr">
         <is>
           <t>45 jours fin de mois / 45 days end of month</t>
         </is>
       </c>
-      <c r="J4" s="66" t="inlineStr">
+      <c r="J4" s="64" t="inlineStr">
         <is>
           <t>Caisse</t>
         </is>
       </c>
-      <c r="K4" s="66" t="inlineStr">
+      <c r="K4" s="64" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="L4" s="66" t="inlineStr">
+      <c r="L4" s="64" t="inlineStr">
         <is>
           <t>€/jour/pers</t>
         </is>
       </c>
-      <c r="N4" s="66" t="inlineStr">
+      <c r="N4" s="64" t="inlineStr">
         <is>
           <t>Forfait par jour</t>
         </is>
       </c>
-      <c r="Q4" s="66" t="inlineStr">
+      <c r="Q4" s="64" t="inlineStr">
         <is>
           <t>Taille + test OK</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="66" t="inlineStr">
+      <c r="A5" s="64" t="inlineStr">
         <is>
           <t>Céline CARDONA</t>
         </is>
       </c>
-      <c r="B5" s="66" t="inlineStr">
+      <c r="B5" s="64" t="inlineStr">
         <is>
           <t>ccardona@enedril.fr</t>
         </is>
       </c>
-      <c r="D5" s="66" t="inlineStr">
+      <c r="D5" s="64" t="inlineStr">
         <is>
           <t>DDP</t>
         </is>
       </c>
-      <c r="E5" s="66" t="inlineStr">
+      <c r="E5" s="64" t="inlineStr">
         <is>
           <t>90 jours / 90 days</t>
         </is>
       </c>
-      <c r="F5" s="66" t="inlineStr">
+      <c r="F5" s="64" t="inlineStr">
         <is>
           <t>À la commande / Upon order</t>
         </is>
       </c>
-      <c r="J5" s="66" t="inlineStr">
+      <c r="J5" s="64" t="inlineStr">
         <is>
           <t>Loose (vrac)</t>
         </is>
       </c>
-      <c r="K5" s="66" t="inlineStr">
+      <c r="K5" s="64" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="L5" s="66" t="inlineStr">
+      <c r="L5" s="64" t="inlineStr">
         <is>
           <t>€/pers</t>
         </is>
       </c>
-      <c r="Q5" s="66" t="inlineStr">
+      <c r="Q5" s="64" t="inlineStr">
         <is>
           <t>À contrôler</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="66" t="inlineStr">
+      <c r="A6" s="64" t="inlineStr">
         <is>
           <t>Koen MONDELAERS</t>
         </is>
       </c>
-      <c r="B6" s="66" t="inlineStr">
+      <c r="B6" s="64" t="inlineStr">
         <is>
           <t>kmondelaers@enedril.fr</t>
         </is>
       </c>
-      <c r="D6" s="66" t="inlineStr">
+      <c r="D6" s="64" t="inlineStr">
         <is>
           <t>FOB</t>
         </is>
       </c>
-      <c r="K6" s="66" t="inlineStr">
+      <c r="K6" s="64" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="L6" s="66" t="inlineStr">
+      <c r="L6" s="64" t="inlineStr">
         <is>
           <t>€/unité</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="66" t="inlineStr">
+      <c r="A7" s="64" t="inlineStr">
         <is>
           <t>Luigi LIBERATORE</t>
         </is>
       </c>
-      <c r="B7" s="66" t="inlineStr">
+      <c r="B7" s="64" t="inlineStr">
         <is>
           <t>lliberatore@enedril.fr</t>
         </is>
       </c>
-      <c r="K7" s="66" t="inlineStr">
+      <c r="K7" s="64" t="inlineStr">
         <is>
           <t>P6</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="K8" s="66" t="inlineStr">
+      <c r="K8" s="64" t="inlineStr">
         <is>
           <t>P7</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="K9" s="66" t="inlineStr">
+      <c r="K9" s="64" t="inlineStr">
         <is>
           <t>P8</t>
         </is>
@@ -4937,21 +4700,21 @@
           <t>Pour ajouter un contact, une validité, etc. : écrire à la suite dans la colonne (les listes déroulantes lisent les 12 premières lignes).</t>
         </is>
       </c>
-      <c r="K10" s="66" t="inlineStr">
+      <c r="K10" s="64" t="inlineStr">
         <is>
           <t>P9</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="K11" s="66" t="inlineStr">
+      <c r="K11" s="64" t="inlineStr">
         <is>
           <t>P10</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="K12" s="66" t="inlineStr">
+      <c r="K12" s="64" t="inlineStr">
         <is>
           <t>Loose</t>
         </is>
@@ -4969,7 +4732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4978,358 +4741,358 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="64" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>Clé</t>
         </is>
       </c>
-      <c r="B1" s="64" t="inlineStr">
+      <c r="B1" s="62" t="inlineStr">
         <is>
           <t>Français</t>
         </is>
       </c>
-      <c r="C1" s="64" t="inlineStr">
+      <c r="C1" s="62" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="68" t="inlineStr">
+      <c r="A2" s="66" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B2" s="68" t="inlineStr">
+      <c r="B2" s="66" t="inlineStr">
         <is>
           <t>OFFRE DE LOCATION</t>
         </is>
       </c>
-      <c r="C2" s="68" t="inlineStr">
+      <c r="C2" s="66" t="inlineStr">
         <is>
           <t>EQUIPMENT RENTAL QUOTATION</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="68" t="inlineStr">
+      <c r="A3" s="66" t="inlineStr">
         <is>
           <t>client</t>
         </is>
       </c>
-      <c r="B3" s="68" t="inlineStr">
+      <c r="B3" s="66" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="C3" s="68" t="inlineStr">
+      <c r="C3" s="66" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="68" t="inlineStr">
+      <c r="A4" s="66" t="inlineStr">
         <is>
           <t>attn</t>
         </is>
       </c>
-      <c r="B4" s="68" t="inlineStr">
+      <c r="B4" s="66" t="inlineStr">
         <is>
           <t>À l'attention de</t>
         </is>
       </c>
-      <c r="C4" s="68" t="inlineStr">
+      <c r="C4" s="66" t="inlineStr">
         <is>
           <t>Attention</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="68" t="inlineStr">
+      <c r="A5" s="66" t="inlineStr">
         <is>
           <t>well</t>
         </is>
       </c>
-      <c r="B5" s="68" t="inlineStr">
+      <c r="B5" s="66" t="inlineStr">
         <is>
           <t>Puits / Chantier</t>
         </is>
       </c>
-      <c r="C5" s="68" t="inlineStr">
+      <c r="C5" s="66" t="inlineStr">
         <is>
           <t>Well / Location</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="68" t="inlineStr">
+      <c r="A6" s="66" t="inlineStr">
         <is>
           <t>rig</t>
         </is>
       </c>
-      <c r="B6" s="68" t="inlineStr">
+      <c r="B6" s="66" t="inlineStr">
         <is>
           <t>Rig</t>
         </is>
       </c>
-      <c r="C6" s="68" t="inlineStr">
+      <c r="C6" s="66" t="inlineStr">
         <is>
           <t>Rig</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="68" t="inlineStr">
+      <c r="A7" s="66" t="inlineStr">
         <is>
           <t>offer</t>
         </is>
       </c>
-      <c r="B7" s="68" t="inlineStr">
+      <c r="B7" s="66" t="inlineStr">
         <is>
           <t>N° d'offre</t>
         </is>
       </c>
-      <c r="C7" s="68" t="inlineStr">
+      <c r="C7" s="66" t="inlineStr">
         <is>
           <t>Offer N°</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="68" t="inlineStr">
+      <c r="A8" s="66" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B8" s="68" t="inlineStr">
+      <c r="B8" s="66" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C8" s="68" t="inlineStr">
+      <c r="C8" s="66" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="68" t="inlineStr">
+      <c r="A9" s="66" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="B9" s="68" t="inlineStr">
+      <c r="B9" s="66" t="inlineStr">
         <is>
           <t>Validité de l'offre</t>
         </is>
       </c>
-      <c r="C9" s="68" t="inlineStr">
+      <c r="C9" s="66" t="inlineStr">
         <is>
           <t>Validity</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="68" t="inlineStr">
+      <c r="A10" s="66" t="inlineStr">
         <is>
           <t>inco</t>
         </is>
       </c>
-      <c r="B10" s="68" t="inlineStr">
+      <c r="B10" s="66" t="inlineStr">
         <is>
           <t>Incoterm</t>
         </is>
       </c>
-      <c r="C10" s="68" t="inlineStr">
+      <c r="C10" s="66" t="inlineStr">
         <is>
           <t>Incoterm</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="68" t="inlineStr">
+      <c r="A11" s="66" t="inlineStr">
         <is>
           <t>lead</t>
         </is>
       </c>
-      <c r="B11" s="68" t="inlineStr">
+      <c r="B11" s="66" t="inlineStr">
         <is>
           <t>Délai de mise à dispo</t>
         </is>
       </c>
-      <c r="C11" s="68" t="inlineStr">
+      <c r="C11" s="66" t="inlineStr">
         <is>
           <t>Lead time</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="68" t="inlineStr">
+      <c r="A12" s="66" t="inlineStr">
         <is>
           <t>pay</t>
         </is>
       </c>
-      <c r="B12" s="68" t="inlineStr">
+      <c r="B12" s="66" t="inlineStr">
         <is>
           <t>Conditions de règlement</t>
         </is>
       </c>
-      <c r="C12" s="68" t="inlineStr">
+      <c r="C12" s="66" t="inlineStr">
         <is>
           <t>Payment terms</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="68" t="inlineStr">
+      <c r="A13" s="66" t="inlineStr">
         <is>
           <t>we</t>
         </is>
       </c>
-      <c r="B13" s="68" t="inlineStr">
+      <c r="B13" s="66" t="inlineStr">
         <is>
           <t>Facturation WE et jours fériés</t>
         </is>
       </c>
-      <c r="C13" s="68" t="inlineStr">
+      <c r="C13" s="66" t="inlineStr">
         <is>
           <t>Weekend &amp; holiday billing</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="68" t="inlineStr">
+      <c r="A14" s="66" t="inlineStr">
         <is>
           <t>by</t>
         </is>
       </c>
-      <c r="B14" s="68" t="inlineStr">
+      <c r="B14" s="66" t="inlineStr">
         <is>
           <t>Établi par</t>
         </is>
       </c>
-      <c r="C14" s="68" t="inlineStr">
+      <c r="C14" s="66" t="inlineStr">
         <is>
           <t>Established by</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="68" t="inlineStr">
+      <c r="A15" s="66" t="inlineStr">
         <is>
           <t>mail</t>
         </is>
       </c>
-      <c r="B15" s="68" t="inlineStr">
+      <c r="B15" s="66" t="inlineStr">
         <is>
           <t>E-mail</t>
         </is>
       </c>
-      <c r="C15" s="68" t="inlineStr">
+      <c r="C15" s="66" t="inlineStr">
         <is>
           <t>E-mail</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="68" t="inlineStr">
+      <c r="A16" s="66" t="inlineStr">
         <is>
           <t>tel</t>
         </is>
       </c>
-      <c r="B16" s="68" t="inlineStr">
+      <c r="B16" s="66" t="inlineStr">
         <is>
           <t>Téléphone</t>
         </is>
       </c>
-      <c r="C16" s="68" t="inlineStr">
+      <c r="C16" s="66" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="68" t="inlineStr">
+      <c r="A17" s="66" t="inlineStr">
         <is>
           <t>sec_eq</t>
         </is>
       </c>
-      <c r="B17" s="68" t="inlineStr">
+      <c r="B17" s="66" t="inlineStr">
         <is>
           <t>MATÉRIEL</t>
         </is>
       </c>
-      <c r="C17" s="68" t="inlineStr">
+      <c r="C17" s="66" t="inlineStr">
         <is>
           <t>EQUIPMENT</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="68" t="inlineStr">
+      <c r="A18" s="66" t="inlineStr">
         <is>
           <t>h_n</t>
         </is>
       </c>
-      <c r="B18" s="68" t="inlineStr">
+      <c r="B18" s="66" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C18" s="68" t="inlineStr">
+      <c r="C18" s="66" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="68" t="inlineStr">
+      <c r="A19" s="66" t="inlineStr">
         <is>
           <t>h_desc</t>
         </is>
       </c>
-      <c r="B19" s="68" t="inlineStr">
+      <c r="B19" s="66" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C19" s="68" t="inlineStr">
+      <c r="C19" s="66" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="68" t="inlineStr">
+      <c r="A20" s="66" t="inlineStr">
         <is>
           <t>h_qty</t>
         </is>
       </c>
-      <c r="B20" s="68" t="inlineStr">
+      <c r="B20" s="66" t="inlineStr">
         <is>
           <t>Qté</t>
         </is>
       </c>
-      <c r="C20" s="68" t="inlineStr">
+      <c r="C20" s="66" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="68" t="inlineStr">
+      <c r="A21" s="66" t="inlineStr">
         <is>
           <t>h_s</t>
         </is>
       </c>
-      <c r="B21" s="68" t="inlineStr">
+      <c r="B21" s="66" t="inlineStr">
         <is>
           <t>Stand-by (S)
 € / jour / item</t>
         </is>
       </c>
-      <c r="C21" s="68" t="inlineStr">
+      <c r="C21" s="66" t="inlineStr">
         <is>
           <t>Stand-by (S)
 daily rate / item</t>
@@ -5337,18 +5100,18 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="68" t="inlineStr">
+      <c r="A22" s="66" t="inlineStr">
         <is>
           <t>h_o</t>
         </is>
       </c>
-      <c r="B22" s="68" t="inlineStr">
+      <c r="B22" s="66" t="inlineStr">
         <is>
           <t>Opérations (O)
 € / jour / item</t>
         </is>
       </c>
-      <c r="C22" s="68" t="inlineStr">
+      <c r="C22" s="66" t="inlineStr">
         <is>
           <t>Operations (O)
 daily rate / item</t>
@@ -5356,19 +5119,19 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="68" t="inlineStr">
+      <c r="A23" s="66" t="inlineStr">
         <is>
           <t>h_uc</t>
         </is>
       </c>
-      <c r="B23" s="68" t="inlineStr">
+      <c r="B23" s="66" t="inlineStr">
         <is>
           <t>Utilisation
 Charge (UC)
 € / item</t>
         </is>
       </c>
-      <c r="C23" s="68" t="inlineStr">
+      <c r="C23" s="66" t="inlineStr">
         <is>
           <t>Utilisation
 Charge (UC)
@@ -5377,18 +5140,18 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="68" t="inlineStr">
+      <c r="A24" s="66" t="inlineStr">
         <is>
           <t>h_lih</t>
         </is>
       </c>
-      <c r="B24" s="68" t="inlineStr">
+      <c r="B24" s="66" t="inlineStr">
         <is>
           <t>Valeur de remplacement
 (LIH / DBR) € / item</t>
         </is>
       </c>
-      <c r="C24" s="68" t="inlineStr">
+      <c r="C24" s="66" t="inlineStr">
         <is>
           <t>Replacement value
 (LIH / DBR) per item</t>
@@ -5396,18 +5159,18 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="68" t="inlineStr">
+      <c r="A25" s="66" t="inlineStr">
         <is>
           <t>h_insp</t>
         </is>
       </c>
-      <c r="B25" s="68" t="inlineStr">
+      <c r="B25" s="66" t="inlineStr">
         <is>
           <t>Inspection
 € / item</t>
         </is>
       </c>
-      <c r="C25" s="68" t="inlineStr">
+      <c r="C25" s="66" t="inlineStr">
         <is>
           <t>Inspection
 per item</t>
@@ -5415,18 +5178,18 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="68" t="inlineStr">
+      <c r="A26" s="66" t="inlineStr">
         <is>
           <t>h_rest</t>
         </is>
       </c>
-      <c r="B26" s="68" t="inlineStr">
+      <c r="B26" s="66" t="inlineStr">
         <is>
           <t>Restocking
 €</t>
         </is>
       </c>
-      <c r="C26" s="68" t="inlineStr">
+      <c r="C26" s="66" t="inlineStr">
         <is>
           <t>Restocking
 charge</t>
@@ -5434,444 +5197,495 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="68" t="inlineStr">
+      <c r="A27" s="66" t="inlineStr">
         <is>
           <t>h_ref</t>
         </is>
       </c>
-      <c r="B27" s="68" t="inlineStr">
+      <c r="B27" s="66" t="inlineStr">
         <is>
           <t>Remarques</t>
         </is>
       </c>
-      <c r="C27" s="68" t="inlineStr">
+      <c r="C27" s="66" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="68" t="inlineStr">
+      <c r="A28" s="66" t="inlineStr">
         <is>
           <t>incl</t>
         </is>
       </c>
-      <c r="B28" s="68" t="inlineStr">
+      <c r="B28" s="66" t="inlineStr">
         <is>
           <t>incl.</t>
         </is>
       </c>
-      <c r="C28" s="68" t="inlineStr">
+      <c r="C28" s="66" t="inlineStr">
         <is>
           <t>incl.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="68" t="inlineStr">
+      <c r="A29" s="66" t="inlineStr">
         <is>
           <t>incl_long</t>
         </is>
       </c>
-      <c r="B29" s="68" t="inlineStr">
+      <c r="B29" s="66" t="inlineStr">
         <is>
           <t>Inclus au forfait</t>
         </is>
       </c>
-      <c r="C29" s="68" t="inlineStr">
+      <c r="C29" s="66" t="inlineStr">
         <is>
           <t>Included in lump sum</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="68" t="inlineStr">
+      <c r="A30" s="66" t="inlineStr">
         <is>
           <t>sec_opt</t>
         </is>
       </c>
-      <c r="B30" s="68" t="inlineStr">
+      <c r="B30" s="66" t="inlineStr">
         <is>
           <t>PRESTATIONS ET OPTIONS</t>
         </is>
       </c>
-      <c r="C30" s="68" t="inlineStr">
+      <c r="C30" s="66" t="inlineStr">
         <is>
           <t>SERVICES AND OPTIONS</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="68" t="inlineStr">
+      <c r="A31" s="66" t="inlineStr">
         <is>
           <t>h_label</t>
         </is>
       </c>
-      <c r="B31" s="68" t="inlineStr">
+      <c r="B31" s="66" t="inlineStr">
         <is>
           <t>Prestation</t>
         </is>
       </c>
-      <c r="C31" s="68" t="inlineStr">
+      <c r="C31" s="66" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="68" t="inlineStr">
+      <c r="A32" s="66" t="inlineStr">
         <is>
           <t>h_unit</t>
         </is>
       </c>
-      <c r="B32" s="68" t="inlineStr">
+      <c r="B32" s="66" t="inlineStr">
         <is>
           <t>Unité</t>
         </is>
       </c>
-      <c r="C32" s="68" t="inlineStr">
+      <c r="C32" s="66" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="68" t="inlineStr">
+      <c r="A33" s="66" t="inlineStr">
         <is>
           <t>h_pu</t>
         </is>
       </c>
-      <c r="B33" s="68" t="inlineStr">
+      <c r="B33" s="66" t="inlineStr">
         <is>
           <t>Prix unitaire €</t>
         </is>
       </c>
-      <c r="C33" s="68" t="inlineStr">
+      <c r="C33" s="66" t="inlineStr">
         <is>
           <t>Unit price €</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="68" t="inlineStr">
+      <c r="A34" s="66" t="inlineStr">
         <is>
           <t>h_tot</t>
         </is>
       </c>
-      <c r="B34" s="68" t="inlineStr">
+      <c r="B34" s="66" t="inlineStr">
         <is>
           <t>Total €</t>
         </is>
       </c>
-      <c r="C34" s="68" t="inlineStr">
+      <c r="C34" s="66" t="inlineStr">
         <is>
           <t>Total €</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="68" t="inlineStr">
+      <c r="A35" s="66" t="inlineStr">
         <is>
           <t>h_det</t>
         </is>
       </c>
-      <c r="B35" s="68" t="inlineStr">
+      <c r="B35" s="66" t="inlineStr">
         <is>
           <t>Détail</t>
         </is>
       </c>
-      <c r="C35" s="68" t="inlineStr">
+      <c r="C35" s="66" t="inlineStr">
         <is>
           <t>Details</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="68" t="inlineStr">
+      <c r="A36" s="66" t="inlineStr">
         <is>
           <t>op_day</t>
         </is>
       </c>
-      <c r="B36" s="68" t="inlineStr">
+      <c r="B36" s="66" t="inlineStr">
         <is>
           <t>Opérateur · tarif journalier</t>
         </is>
       </c>
-      <c r="C36" s="68" t="inlineStr">
+      <c r="C36" s="66" t="inlineStr">
         <is>
           <t>Operator · daily rate</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="68" t="inlineStr">
+      <c r="A37" s="66" t="inlineStr">
         <is>
           <t>op_mob</t>
         </is>
       </c>
-      <c r="B37" s="68" t="inlineStr">
+      <c r="B37" s="66" t="inlineStr">
         <is>
           <t>Opérateur · Mob / Demob</t>
         </is>
       </c>
-      <c r="C37" s="68" t="inlineStr">
+      <c r="C37" s="66" t="inlineStr">
         <is>
           <t>Operator · Mob / Demob</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="68" t="inlineStr">
+      <c r="A38" s="66" t="inlineStr">
         <is>
           <t>tight</t>
         </is>
       </c>
-      <c r="B38" s="68" t="inlineStr">
-        <is>
-          <t>Serrage · Make-up (forfait)</t>
-        </is>
-      </c>
-      <c r="C38" s="68" t="inlineStr">
-        <is>
-          <t>Tong &amp; make-up service (lump sum)</t>
+      <c r="B38" s="66" t="inlineStr">
+        <is>
+          <t>Serrage · prix par serrage</t>
+        </is>
+      </c>
+      <c r="C38" s="66" t="inlineStr">
+        <is>
+          <t>Tong &amp; make-up service · price per make-up</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="68" t="inlineStr">
+      <c r="A39" s="66" t="inlineStr">
         <is>
           <t>tr_mob</t>
         </is>
       </c>
-      <c r="B39" s="68" t="inlineStr">
+      <c r="B39" s="66" t="inlineStr">
         <is>
           <t>Transport MOB (Lons → chantier)</t>
         </is>
       </c>
-      <c r="C39" s="68" t="inlineStr">
+      <c r="C39" s="66" t="inlineStr">
         <is>
           <t>Transport MOB (Lons → site)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="68" t="inlineStr">
+      <c r="A40" s="66" t="inlineStr">
         <is>
           <t>tr_dem</t>
         </is>
       </c>
-      <c r="B40" s="68" t="inlineStr">
+      <c r="B40" s="66" t="inlineStr">
         <is>
           <t>Transport DEMOB (chantier → Lons)</t>
         </is>
       </c>
-      <c r="C40" s="68" t="inlineStr">
+      <c r="C40" s="66" t="inlineStr">
         <is>
           <t>Transport DEMOB (site → Lons)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="68" t="inlineStr">
+      <c r="A41" s="66" t="inlineStr">
         <is>
           <t>free</t>
         </is>
       </c>
-      <c r="B41" s="68" t="inlineStr">
+      <c r="B41" s="66" t="inlineStr">
         <is>
           <t>Option</t>
         </is>
       </c>
-      <c r="C41" s="68" t="inlineStr">
+      <c r="C41" s="66" t="inlineStr">
         <is>
           <t>Option</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="68" t="inlineStr">
+      <c r="A42" s="66" t="inlineStr">
         <is>
           <t>forfait</t>
         </is>
       </c>
-      <c r="B42" s="68" t="inlineStr">
+      <c r="B42" s="66" t="inlineStr">
         <is>
           <t>Forfait</t>
         </is>
       </c>
-      <c r="C42" s="68" t="inlineStr">
+      <c r="C42" s="66" t="inlineStr">
         <is>
           <t>Lump sum</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="68" t="inlineStr">
+      <c r="A43" s="66" t="inlineStr">
         <is>
           <t>at_cost</t>
         </is>
       </c>
-      <c r="B43" s="68" t="inlineStr">
+      <c r="B43" s="66" t="inlineStr">
         <is>
           <t>au coût réel +15 %</t>
         </is>
       </c>
-      <c r="C43" s="68" t="inlineStr">
+      <c r="C43" s="66" t="inlineStr">
         <is>
           <t>at cost +15%</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="68" t="inlineStr">
+      <c r="A44" s="66" t="inlineStr">
         <is>
           <t>tr_note</t>
         </is>
       </c>
-      <c r="B44" s="68" t="inlineStr">
+      <c r="B44" s="66" t="inlineStr">
         <is>
           <t>Transport organisé par Enedril</t>
         </is>
       </c>
-      <c r="C44" s="68" t="inlineStr">
+      <c r="C44" s="66" t="inlineStr">
         <is>
           <t>Transport organised by Enedril</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="68" t="inlineStr">
+      <c r="A45" s="66" t="inlineStr">
         <is>
           <t>ht</t>
         </is>
       </c>
-      <c r="B45" s="68" t="inlineStr">
+      <c r="B45" s="66" t="inlineStr">
         <is>
           <t>€ HT</t>
         </is>
       </c>
-      <c r="C45" s="68" t="inlineStr">
+      <c r="C45" s="66" t="inlineStr">
         <is>
           <t>€ excl. VAT</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="68" t="inlineStr">
+      <c r="A46" s="66" t="inlineStr">
         <is>
           <t>calc_det</t>
         </is>
       </c>
-      <c r="B46" s="68" t="inlineStr">
+      <c r="B46" s="66" t="inlineStr">
         <is>
           <t>j stand-by + %s j opérations + utilisations de charge (UC)</t>
         </is>
       </c>
-      <c r="C46" s="68" t="inlineStr">
+      <c r="C46" s="66" t="inlineStr">
         <is>
           <t>stand-by days + %s operation days + utilisation charges (UC)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="68" t="inlineStr">
+      <c r="A47" s="66" t="inlineStr">
         <is>
           <t>sec_cond</t>
         </is>
       </c>
-      <c r="B47" s="68" t="inlineStr">
+      <c r="B47" s="66" t="inlineStr">
         <is>
           <t>CONDITIONS PARTICULIÈRES · SPECIFIC CONDITIONS</t>
         </is>
       </c>
-      <c r="C47" s="68" t="inlineStr">
+      <c r="C47" s="66" t="inlineStr">
         <is>
           <t>SPECIFIC CONDITIONS · CONDITIONS PARTICULIÈRES</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="68" t="inlineStr">
+      <c r="A48" s="66" t="inlineStr">
         <is>
           <t>accept</t>
         </is>
       </c>
-      <c r="B48" s="68" t="inlineStr">
+      <c r="B48" s="66" t="inlineStr">
         <is>
           <t>BON POUR ACCORD</t>
         </is>
       </c>
-      <c r="C48" s="68" t="inlineStr">
+      <c r="C48" s="66" t="inlineStr">
         <is>
           <t>ACCEPTED BY</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="68" t="inlineStr">
+      <c r="A49" s="66" t="inlineStr">
         <is>
           <t>sig_name</t>
         </is>
       </c>
-      <c r="B49" s="68" t="inlineStr">
+      <c r="B49" s="66" t="inlineStr">
         <is>
           <t>Nom et qualité</t>
         </is>
       </c>
-      <c r="C49" s="68" t="inlineStr">
+      <c r="C49" s="66" t="inlineStr">
         <is>
           <t>Name and title</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="68" t="inlineStr">
+      <c r="A50" s="66" t="inlineStr">
         <is>
           <t>sig_date</t>
         </is>
       </c>
-      <c r="B50" s="68" t="inlineStr">
+      <c r="B50" s="66" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C50" s="68" t="inlineStr">
+      <c r="C50" s="66" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="68" t="inlineStr">
+      <c r="A51" s="66" t="inlineStr">
         <is>
           <t>sig_sig</t>
         </is>
       </c>
-      <c r="B51" s="68" t="inlineStr">
+      <c r="B51" s="66" t="inlineStr">
         <is>
           <t>Signature et cachet</t>
         </is>
       </c>
-      <c r="C51" s="68" t="inlineStr">
+      <c r="C51" s="66" t="inlineStr">
         <is>
           <t>Signature and stamp</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="68" t="inlineStr">
+      <c r="A52" s="66" t="inlineStr">
         <is>
           <t>lump</t>
         </is>
       </c>
-      <c r="B52" s="68" t="inlineStr">
+      <c r="B52" s="66" t="inlineStr">
         <is>
           <t>forfait</t>
         </is>
       </c>
-      <c r="C52" s="68" t="inlineStr">
+      <c r="C52" s="66" t="inlineStr">
         <is>
           <t>lump sum</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="66" t="inlineStr">
+        <is>
+          <t>sec_tight</t>
+        </is>
+      </c>
+      <c r="B53" s="66" t="inlineStr">
+        <is>
+          <t>SERRAGE · TONG &amp; MAKE-UP</t>
+        </is>
+      </c>
+      <c r="C53" s="66" t="inlineStr">
+        <is>
+          <t>TONG &amp; MAKE-UP SERVICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="66" t="inlineStr">
+        <is>
+          <t>sec_tr</t>
+        </is>
+      </c>
+      <c r="B54" s="66" t="inlineStr">
+        <is>
+          <t>TRANSPORT</t>
+        </is>
+      </c>
+      <c r="C54" s="66" t="inlineStr">
+        <is>
+          <t>TRANSPORT</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="66" t="inlineStr">
+        <is>
+          <t>sec_op</t>
+        </is>
+      </c>
+      <c r="B55" s="66" t="inlineStr">
+        <is>
+          <t>OPÉRATEURS</t>
+        </is>
+      </c>
+      <c r="C55" s="66" t="inlineStr">
+        <is>
+          <t>OPERATORS</t>
         </is>
       </c>
     </row>

--- a/devis_2027/Devis_Enedril_2027.xlsx
+++ b/devis_2027/Devis_Enedril_2027.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Textes" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'4 Devis'!$A$1:$L$66</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'4 Devis'!$A$1:$K$68</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -29,7 +29,7 @@
     <numFmt numFmtId="166" formatCode="#,##0;-#,##0;;@"/>
     <numFmt numFmtId="167" formatCode="#,##0.00 &quot;€&quot;"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="35">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -142,7 +142,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="17"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -159,7 +159,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="0008203F"/>
-      <sz val="8"/>
+      <sz val="7.5"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -169,42 +169,54 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00E2231A"/>
+      <color rgb="0051647A"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000B1B2E"/>
       <sz val="9.5"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="000B1B2E"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="0051647A"/>
-      <sz val="10"/>
+      <color rgb="00E2231A"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="16"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000B1B2E"/>
+      <sz val="9.5"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="22"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="20"/>
     </font>
     <font>
       <name val="Calibri"/>
       <i val="1"/>
       <color rgb="0008203F"/>
-      <sz val="10"/>
+      <sz val="9.5"/>
     </font>
     <font>
       <name val="Calibri"/>
       <color rgb="0051647A"/>
-      <sz val="8.5"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -215,7 +227,7 @@
     <font>
       <name val="Calibri"/>
       <color rgb="0051647A"/>
-      <sz val="8"/>
+      <sz val="7.5"/>
     </font>
   </fonts>
   <fills count="8">
@@ -298,11 +310,6 @@
       </top>
     </border>
     <border>
-      <top style="thin">
-        <color rgb="00D5DEE8"/>
-      </top>
-    </border>
-    <border>
       <right style="thin">
         <color rgb="00D5DEE8"/>
       </right>
@@ -315,7 +322,6 @@
         <color rgb="00D5DEE8"/>
       </left>
     </border>
-    <border/>
     <border>
       <right style="thin">
         <color rgb="00D5DEE8"/>
@@ -337,11 +343,17 @@
         <color rgb="00D5DEE8"/>
       </bottom>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="00D5DEE8"/>
+      </top>
+    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -409,6 +421,9 @@
     <xf numFmtId="167" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -433,64 +448,76 @@
     <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -658,7 +685,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1428750" cy="323850"/>
+    <ext cx="1333500" cy="304800"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -2066,7 +2093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2371,34 +2398,52 @@
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="20" t="inlineStr">
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Afficher les prix des lignes du forfait sur le devis</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="inlineStr">
+        <is>
+          <t>Oui : chaque ligne garde ses tarifs ; Non : elles s’affichent « incl. ». Dans les deux cas le prix final du forfait apparaît dans le bandeau.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>Rappels</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="27" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="28" t="inlineStr">
         <is>
           <t>Transport « Coût réel +15 % » : aucun montant affiché. Choisir « Forfait » pour imposer un prix.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="27" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="28" t="inlineStr">
         <is>
           <t>Lignes couvertes par le forfait : mettre « Oui » dans « Inclus au forfait » (onglet 2). Elles s’affichent « incl. » sur le devis.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="D15:H17"/>
+    <mergeCell ref="D18:H18"/>
     <mergeCell ref="D14:H14"/>
     <mergeCell ref="B12:H12"/>
   </mergeCells>
-  <dataValidations count="12">
+  <dataValidations count="13">
     <dataValidation sqref="C6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="stop">
       <formula1>=Listes!$G$2:$G$12</formula1>
     </dataValidation>
@@ -2435,6 +2480,9 @@
     <dataValidation sqref="G13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="stop">
       <formula1>=Listes!$N$2:$N$12</formula1>
     </dataValidation>
+    <dataValidation sqref="C18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="stop">
+      <formula1>=Listes!$G$2:$G$12</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -2448,45 +2496,42 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:L68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
-    <col width="5" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="1.5" customWidth="1" min="12" max="12"/>
-    <col hidden="1" width="13" customWidth="1" min="13" max="13"/>
+    <col width="4.5" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="5.5" customWidth="1" min="4" max="4"/>
+    <col width="10.5" customWidth="1" min="5" max="5"/>
+    <col width="10.5" customWidth="1" min="6" max="6"/>
+    <col width="10.5" customWidth="1" min="7" max="7"/>
+    <col width="12.5" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="1.5" customWidth="1" min="11" max="11"/>
+    <col hidden="1" width="13" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="n"/>
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="28">
+      <c r="D1" s="29">
         <f>INDEX(Textes!$B$2:$C$55,MATCH("title",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="L1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="1" t="n"/>
       <c r="C2" s="1" t="n"/>
-      <c r="D2" s="1" t="n"/>
-      <c r="E2" s="29">
+      <c r="D2" s="30">
         <f>"N° "&amp;'1 Affaire'!$C$6&amp;"   ·   "&amp;IF('1 Affaire'!$C$7="","",TEXT('1 Affaire'!$C$7,"dd/mm/yyyy"))</f>
         <v/>
       </c>
-      <c r="L2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
     </row>
     <row r="3" ht="5" customHeight="1">
       <c r="A3" s="4" t="n"/>
@@ -2500,1581 +2545,1494 @@
       <c r="I3" s="4" t="n"/>
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
-      <c r="L3" s="4" t="n"/>
     </row>
     <row r="4" ht="8" customHeight="1"/>
     <row r="5" ht="15" customHeight="1">
-      <c r="B5" s="30">
+      <c r="B5" s="31">
         <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("client",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
         <v/>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("offer",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
         <v/>
       </c>
-      <c r="G5" s="30">
+      <c r="H5" s="31">
         <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("date",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
         <v/>
       </c>
-      <c r="I5" s="30">
+    </row>
+    <row r="6" ht="19" customHeight="1">
+      <c r="B6" s="32">
+        <f>""&amp;'1 Affaire'!$C$8</f>
+        <v/>
+      </c>
+      <c r="C6" s="33" t="n"/>
+      <c r="D6" s="32">
+        <f>""&amp;'1 Affaire'!$C$6</f>
+        <v/>
+      </c>
+      <c r="E6" s="33" t="n"/>
+      <c r="F6" s="33" t="n"/>
+      <c r="G6" s="33" t="n"/>
+      <c r="H6" s="32">
+        <f>IF('1 Affaire'!$C$7="","",TEXT('1 Affaire'!$C$7,"dd/mm/yyyy"))</f>
+        <v/>
+      </c>
+      <c r="I6" s="33" t="n"/>
+      <c r="J6" s="33" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="B7" s="31">
+        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("attn",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
+        <v/>
+      </c>
+      <c r="D7" s="31">
+        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("well",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
+        <v/>
+      </c>
+      <c r="H7" s="31">
         <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("by",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="19" customHeight="1">
-      <c r="B6" s="31">
-        <f>""&amp;'1 Affaire'!$C$8</f>
-        <v/>
-      </c>
-      <c r="C6" s="32" t="n"/>
-      <c r="D6" s="31">
-        <f>""&amp;'1 Affaire'!$C$6</f>
-        <v/>
-      </c>
-      <c r="E6" s="32" t="n"/>
-      <c r="F6" s="32" t="n"/>
-      <c r="G6" s="31">
-        <f>IF('1 Affaire'!$C$7="","",TEXT('1 Affaire'!$C$7,"dd/mm/yyyy"))</f>
-        <v/>
-      </c>
-      <c r="H6" s="32" t="n"/>
-      <c r="I6" s="31">
+    <row r="8" ht="19" customHeight="1">
+      <c r="B8" s="32">
+        <f>""&amp;'1 Affaire'!$C$9</f>
+        <v/>
+      </c>
+      <c r="C8" s="33" t="n"/>
+      <c r="D8" s="32">
+        <f>""&amp;'1 Affaire'!$C$10</f>
+        <v/>
+      </c>
+      <c r="E8" s="33" t="n"/>
+      <c r="F8" s="33" t="n"/>
+      <c r="G8" s="33" t="n"/>
+      <c r="H8" s="32">
         <f>""&amp;'1 Affaire'!$F$6</f>
         <v/>
       </c>
-      <c r="J6" s="32" t="n"/>
-      <c r="K6" s="32" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="B7" s="30">
-        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("attn",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
-        <v/>
-      </c>
-      <c r="D7" s="30">
-        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("well",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
-        <v/>
-      </c>
-      <c r="G7" s="30">
+      <c r="I8" s="33" t="n"/>
+      <c r="J8" s="33" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="B9" s="31">
         <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("inco",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
         <v/>
       </c>
-      <c r="I7" s="30">
+      <c r="D9" s="31">
+        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("valid",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
+        <v/>
+      </c>
+      <c r="H9" s="31">
         <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("mail",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="19" customHeight="1">
-      <c r="B8" s="31">
-        <f>""&amp;'1 Affaire'!$C$9</f>
-        <v/>
-      </c>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="31">
-        <f>""&amp;'1 Affaire'!$C$10</f>
-        <v/>
-      </c>
-      <c r="E8" s="32" t="n"/>
-      <c r="F8" s="32" t="n"/>
-      <c r="G8" s="31">
+    <row r="10" ht="19" customHeight="1">
+      <c r="B10" s="32">
         <f>""&amp;'1 Affaire'!$F$10</f>
         <v/>
       </c>
-      <c r="H8" s="32" t="n"/>
-      <c r="I8" s="31">
+      <c r="C10" s="33" t="n"/>
+      <c r="D10" s="32">
+        <f>""&amp;'1 Affaire'!$F$9</f>
+        <v/>
+      </c>
+      <c r="E10" s="33" t="n"/>
+      <c r="F10" s="33" t="n"/>
+      <c r="G10" s="33" t="n"/>
+      <c r="H10" s="32">
         <f>""&amp;'1 Affaire'!$F$7</f>
         <v/>
       </c>
-      <c r="J8" s="32" t="n"/>
-      <c r="K8" s="32" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="B9" s="30">
-        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("valid",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
-        <v/>
-      </c>
-      <c r="D9" s="30">
+      <c r="I10" s="33" t="n"/>
+      <c r="J10" s="33" t="n"/>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="B11" s="31">
         <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("lead",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
         <v/>
       </c>
-      <c r="G9" s="30">
+      <c r="D11" s="31">
         <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("we",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
         <v/>
       </c>
-      <c r="I9" s="30">
+      <c r="H11" s="31">
         <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("tel",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="19" customHeight="1">
-      <c r="B10" s="31">
-        <f>""&amp;'1 Affaire'!$F$9</f>
-        <v/>
-      </c>
-      <c r="C10" s="32" t="n"/>
-      <c r="D10" s="31">
+    <row r="12" ht="19" customHeight="1">
+      <c r="B12" s="32">
         <f>""&amp;'1 Affaire'!$F$11</f>
         <v/>
       </c>
-      <c r="E10" s="32" t="n"/>
-      <c r="F10" s="32" t="n"/>
-      <c r="G10" s="31">
+      <c r="C12" s="33" t="n"/>
+      <c r="D12" s="32">
         <f>""&amp;'1 Affaire'!$F$13</f>
         <v/>
       </c>
-      <c r="H10" s="32" t="n"/>
-      <c r="I10" s="31">
+      <c r="E12" s="33" t="n"/>
+      <c r="F12" s="33" t="n"/>
+      <c r="G12" s="33" t="n"/>
+      <c r="H12" s="32">
         <f>""&amp;'1 Affaire'!$F$8</f>
         <v/>
       </c>
-      <c r="J10" s="32" t="n"/>
-      <c r="K10" s="32" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="B11" s="30">
+      <c r="I12" s="33" t="n"/>
+      <c r="J12" s="33" t="n"/>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="B13" s="31">
         <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("pay",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="19" customHeight="1">
-      <c r="B12" s="31">
+    <row r="14" ht="19" customHeight="1">
+      <c r="B14" s="32">
         <f>""&amp;'1 Affaire'!$F$12</f>
         <v/>
       </c>
-      <c r="C12" s="32" t="n"/>
-    </row>
-    <row r="13" ht="8" customHeight="1"/>
-    <row r="14" ht="20" customHeight="1">
-      <c r="B14" s="33">
+      <c r="C14" s="33" t="n"/>
+    </row>
+    <row r="15" ht="8" customHeight="1"/>
+    <row r="16" ht="20" customHeight="1">
+      <c r="B16" s="34">
         <f>INDEX(Textes!$B$2:$C$55,MATCH("sec_eq",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="C14" s="34" t="n"/>
-      <c r="D14" s="34" t="n"/>
-      <c r="E14" s="34" t="n"/>
-      <c r="F14" s="34" t="n"/>
-      <c r="G14" s="34" t="n"/>
-      <c r="H14" s="34" t="n"/>
-      <c r="I14" s="34" t="n"/>
-      <c r="J14" s="34" t="n"/>
-      <c r="K14" s="34" t="n"/>
-    </row>
-    <row r="15" ht="44" customHeight="1">
-      <c r="B15" s="35">
+      <c r="C16" s="35" t="n"/>
+      <c r="D16" s="35" t="n"/>
+      <c r="E16" s="35" t="n"/>
+      <c r="F16" s="35" t="n"/>
+      <c r="G16" s="35" t="n"/>
+      <c r="H16" s="35" t="n"/>
+      <c r="I16" s="35" t="n"/>
+      <c r="J16" s="35" t="n"/>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="B17" s="36">
         <f>INDEX(Textes!$B$2:$C$55,MATCH("h_n",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="C15" s="36">
+      <c r="C17" s="37">
         <f>INDEX(Textes!$B$2:$C$55,MATCH("h_desc",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="D15" s="35">
+      <c r="D17" s="36">
         <f>INDEX(Textes!$B$2:$C$55,MATCH("h_qty",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="E15" s="35">
+      <c r="E17" s="36">
         <f>INDEX(Textes!$B$2:$C$55,MATCH("h_s",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="F15" s="35">
+      <c r="F17" s="36">
         <f>INDEX(Textes!$B$2:$C$55,MATCH("h_o",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="G15" s="35">
+      <c r="G17" s="36">
         <f>INDEX(Textes!$B$2:$C$55,MATCH("h_uc",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="H15" s="35">
+      <c r="H17" s="36">
         <f>INDEX(Textes!$B$2:$C$55,MATCH("h_lih",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="I15" s="35">
+      <c r="I17" s="36">
         <f>INDEX(Textes!$B$2:$C$55,MATCH("h_insp",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="J15" s="35">
+      <c r="J17" s="36">
         <f>INDEX(Textes!$B$2:$C$55,MATCH("h_rest",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="K15" s="35">
-        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_ref",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="21" customHeight="1">
-      <c r="B16" s="13">
+    </row>
+    <row r="18" ht="21" customHeight="1">
+      <c r="B18" s="38">
         <f>IF(AND('2 Matériel'!$L6&gt;0,NOT('2 Matériel'!$B6="Oui")),'2 Matériel'!$A6,"")</f>
         <v/>
       </c>
-      <c r="C16" s="37">
-        <f>IF('2 Matériel'!$L6&gt;0,IF('2 Matériel'!$B6="Oui",UPPER('2 Matériel'!$C6),'2 Matériel'!$C6),"")</f>
-        <v/>
-      </c>
-      <c r="D16" s="38">
+      <c r="C18" s="39">
+        <f>IF('2 Matériel'!$L6&gt;0,IF('2 Matériel'!$B6="Oui",UPPER('2 Matériel'!$C6),'2 Matériel'!$C6&amp;IF(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <v/>
+      </c>
+      <c r="D18" s="40">
         <f>IF(AND('2 Matériel'!$L6&gt;0,NOT('2 Matériel'!$B6="Oui")),'2 Matériel'!$L6,"")</f>
         <v/>
       </c>
-      <c r="E16" s="39">
-        <f>IF(AND('2 Matériel'!$L6&gt;0,NOT('2 Matériel'!$B6="Oui")),IF(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E6="","",'2 Matériel'!$E6)),"")</f>
-        <v/>
-      </c>
-      <c r="F16" s="39">
-        <f>IF(AND('2 Matériel'!$L6&gt;0,NOT('2 Matériel'!$B6="Oui")),IF(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F6="","",'2 Matériel'!$F6)),"")</f>
-        <v/>
-      </c>
-      <c r="G16" s="39">
-        <f>IF(AND('2 Matériel'!$L6&gt;0,NOT('2 Matériel'!$B6="Oui")),IF(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G6="","",'2 Matériel'!$G6)),"")</f>
-        <v/>
-      </c>
-      <c r="H16" s="39">
-        <f>IF(AND('2 Matériel'!$L6&gt;0,NOT('2 Matériel'!$B6="Oui")),IF(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H6="","",'2 Matériel'!$H6)),"")</f>
-        <v/>
-      </c>
-      <c r="I16" s="39">
-        <f>IF(AND('2 Matériel'!$L6&gt;0,NOT('2 Matériel'!$B6="Oui")),IF(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I6="","",'2 Matériel'!$I6)),"")</f>
-        <v/>
-      </c>
-      <c r="J16" s="39">
-        <f>IF(AND('2 Matériel'!$L6&gt;0,NOT('2 Matériel'!$B6="Oui")),IF(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J6="","",'2 Matériel'!$J6)),"")</f>
-        <v/>
-      </c>
-      <c r="K16" s="40">
-        <f>IF(AND('2 Matériel'!$L6&gt;0,NOT('2 Matériel'!$B6="Oui")),IF(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
-        <v/>
-      </c>
-      <c r="M16" s="41">
+      <c r="E18" s="41">
+        <f>IF(AND('2 Matériel'!$L6&gt;0,NOT('2 Matériel'!$B6="Oui")),IF(AND(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E6="","",'2 Matériel'!$E6)),"")</f>
+        <v/>
+      </c>
+      <c r="F18" s="41">
+        <f>IF(AND('2 Matériel'!$L6&gt;0,NOT('2 Matériel'!$B6="Oui")),IF(AND(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F6="","",'2 Matériel'!$F6)),"")</f>
+        <v/>
+      </c>
+      <c r="G18" s="41">
+        <f>IF(AND('2 Matériel'!$L6&gt;0,NOT('2 Matériel'!$B6="Oui")),IF(AND(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G6="","",'2 Matériel'!$G6)),"")</f>
+        <v/>
+      </c>
+      <c r="H18" s="41">
+        <f>IF(AND('2 Matériel'!$L6&gt;0,NOT('2 Matériel'!$B6="Oui")),IF(AND(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H6="","",'2 Matériel'!$H6)),"")</f>
+        <v/>
+      </c>
+      <c r="I18" s="41">
+        <f>IF(AND('2 Matériel'!$L6&gt;0,NOT('2 Matériel'!$B6="Oui")),IF(AND(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I6="","",'2 Matériel'!$I6)),"")</f>
+        <v/>
+      </c>
+      <c r="J18" s="41">
+        <f>IF(AND('2 Matériel'!$L6&gt;0,NOT('2 Matériel'!$B6="Oui")),IF(AND(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J6="","",'2 Matériel'!$J6)),"")</f>
+        <v/>
+      </c>
+      <c r="L18" s="42">
         <f>IF(AND('2 Matériel'!$L6&gt;0,'2 Matériel'!$B6="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="21" customHeight="1">
-      <c r="B17" s="13">
+    <row r="19" ht="21" customHeight="1">
+      <c r="B19" s="38">
         <f>IF(AND('2 Matériel'!$L7&gt;0,NOT('2 Matériel'!$B7="Oui")),'2 Matériel'!$A7,"")</f>
         <v/>
       </c>
-      <c r="C17" s="37">
-        <f>IF('2 Matériel'!$L7&gt;0,IF('2 Matériel'!$B7="Oui",UPPER('2 Matériel'!$C7),'2 Matériel'!$C7),"")</f>
-        <v/>
-      </c>
-      <c r="D17" s="38">
+      <c r="C19" s="39">
+        <f>IF('2 Matériel'!$L7&gt;0,IF('2 Matériel'!$B7="Oui",UPPER('2 Matériel'!$C7),'2 Matériel'!$C7&amp;IF(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <v/>
+      </c>
+      <c r="D19" s="40">
         <f>IF(AND('2 Matériel'!$L7&gt;0,NOT('2 Matériel'!$B7="Oui")),'2 Matériel'!$L7,"")</f>
         <v/>
       </c>
-      <c r="E17" s="39">
-        <f>IF(AND('2 Matériel'!$L7&gt;0,NOT('2 Matériel'!$B7="Oui")),IF(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E7="","",'2 Matériel'!$E7)),"")</f>
-        <v/>
-      </c>
-      <c r="F17" s="39">
-        <f>IF(AND('2 Matériel'!$L7&gt;0,NOT('2 Matériel'!$B7="Oui")),IF(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F7="","",'2 Matériel'!$F7)),"")</f>
-        <v/>
-      </c>
-      <c r="G17" s="39">
-        <f>IF(AND('2 Matériel'!$L7&gt;0,NOT('2 Matériel'!$B7="Oui")),IF(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G7="","",'2 Matériel'!$G7)),"")</f>
-        <v/>
-      </c>
-      <c r="H17" s="39">
-        <f>IF(AND('2 Matériel'!$L7&gt;0,NOT('2 Matériel'!$B7="Oui")),IF(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H7="","",'2 Matériel'!$H7)),"")</f>
-        <v/>
-      </c>
-      <c r="I17" s="39">
-        <f>IF(AND('2 Matériel'!$L7&gt;0,NOT('2 Matériel'!$B7="Oui")),IF(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I7="","",'2 Matériel'!$I7)),"")</f>
-        <v/>
-      </c>
-      <c r="J17" s="39">
-        <f>IF(AND('2 Matériel'!$L7&gt;0,NOT('2 Matériel'!$B7="Oui")),IF(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J7="","",'2 Matériel'!$J7)),"")</f>
-        <v/>
-      </c>
-      <c r="K17" s="40">
-        <f>IF(AND('2 Matériel'!$L7&gt;0,NOT('2 Matériel'!$B7="Oui")),IF(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
-        <v/>
-      </c>
-      <c r="M17" s="41">
+      <c r="E19" s="41">
+        <f>IF(AND('2 Matériel'!$L7&gt;0,NOT('2 Matériel'!$B7="Oui")),IF(AND(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E7="","",'2 Matériel'!$E7)),"")</f>
+        <v/>
+      </c>
+      <c r="F19" s="41">
+        <f>IF(AND('2 Matériel'!$L7&gt;0,NOT('2 Matériel'!$B7="Oui")),IF(AND(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F7="","",'2 Matériel'!$F7)),"")</f>
+        <v/>
+      </c>
+      <c r="G19" s="41">
+        <f>IF(AND('2 Matériel'!$L7&gt;0,NOT('2 Matériel'!$B7="Oui")),IF(AND(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G7="","",'2 Matériel'!$G7)),"")</f>
+        <v/>
+      </c>
+      <c r="H19" s="41">
+        <f>IF(AND('2 Matériel'!$L7&gt;0,NOT('2 Matériel'!$B7="Oui")),IF(AND(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H7="","",'2 Matériel'!$H7)),"")</f>
+        <v/>
+      </c>
+      <c r="I19" s="41">
+        <f>IF(AND('2 Matériel'!$L7&gt;0,NOT('2 Matériel'!$B7="Oui")),IF(AND(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I7="","",'2 Matériel'!$I7)),"")</f>
+        <v/>
+      </c>
+      <c r="J19" s="41">
+        <f>IF(AND('2 Matériel'!$L7&gt;0,NOT('2 Matériel'!$B7="Oui")),IF(AND(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J7="","",'2 Matériel'!$J7)),"")</f>
+        <v/>
+      </c>
+      <c r="L19" s="42">
         <f>IF(AND('2 Matériel'!$L7&gt;0,'2 Matériel'!$B7="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="21" customHeight="1">
-      <c r="B18" s="13">
+    <row r="20" ht="21" customHeight="1">
+      <c r="B20" s="38">
         <f>IF(AND('2 Matériel'!$L8&gt;0,NOT('2 Matériel'!$B8="Oui")),'2 Matériel'!$A8,"")</f>
         <v/>
       </c>
-      <c r="C18" s="37">
-        <f>IF('2 Matériel'!$L8&gt;0,IF('2 Matériel'!$B8="Oui",UPPER('2 Matériel'!$C8),'2 Matériel'!$C8),"")</f>
-        <v/>
-      </c>
-      <c r="D18" s="38">
+      <c r="C20" s="39">
+        <f>IF('2 Matériel'!$L8&gt;0,IF('2 Matériel'!$B8="Oui",UPPER('2 Matériel'!$C8),'2 Matériel'!$C8&amp;IF(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <v/>
+      </c>
+      <c r="D20" s="40">
         <f>IF(AND('2 Matériel'!$L8&gt;0,NOT('2 Matériel'!$B8="Oui")),'2 Matériel'!$L8,"")</f>
         <v/>
       </c>
-      <c r="E18" s="39">
-        <f>IF(AND('2 Matériel'!$L8&gt;0,NOT('2 Matériel'!$B8="Oui")),IF(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E8="","",'2 Matériel'!$E8)),"")</f>
-        <v/>
-      </c>
-      <c r="F18" s="39">
-        <f>IF(AND('2 Matériel'!$L8&gt;0,NOT('2 Matériel'!$B8="Oui")),IF(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F8="","",'2 Matériel'!$F8)),"")</f>
-        <v/>
-      </c>
-      <c r="G18" s="39">
-        <f>IF(AND('2 Matériel'!$L8&gt;0,NOT('2 Matériel'!$B8="Oui")),IF(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G8="","",'2 Matériel'!$G8)),"")</f>
-        <v/>
-      </c>
-      <c r="H18" s="39">
-        <f>IF(AND('2 Matériel'!$L8&gt;0,NOT('2 Matériel'!$B8="Oui")),IF(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H8="","",'2 Matériel'!$H8)),"")</f>
-        <v/>
-      </c>
-      <c r="I18" s="39">
-        <f>IF(AND('2 Matériel'!$L8&gt;0,NOT('2 Matériel'!$B8="Oui")),IF(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I8="","",'2 Matériel'!$I8)),"")</f>
-        <v/>
-      </c>
-      <c r="J18" s="39">
-        <f>IF(AND('2 Matériel'!$L8&gt;0,NOT('2 Matériel'!$B8="Oui")),IF(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J8="","",'2 Matériel'!$J8)),"")</f>
-        <v/>
-      </c>
-      <c r="K18" s="40">
-        <f>IF(AND('2 Matériel'!$L8&gt;0,NOT('2 Matériel'!$B8="Oui")),IF(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
-        <v/>
-      </c>
-      <c r="M18" s="41">
+      <c r="E20" s="41">
+        <f>IF(AND('2 Matériel'!$L8&gt;0,NOT('2 Matériel'!$B8="Oui")),IF(AND(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E8="","",'2 Matériel'!$E8)),"")</f>
+        <v/>
+      </c>
+      <c r="F20" s="41">
+        <f>IF(AND('2 Matériel'!$L8&gt;0,NOT('2 Matériel'!$B8="Oui")),IF(AND(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F8="","",'2 Matériel'!$F8)),"")</f>
+        <v/>
+      </c>
+      <c r="G20" s="41">
+        <f>IF(AND('2 Matériel'!$L8&gt;0,NOT('2 Matériel'!$B8="Oui")),IF(AND(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G8="","",'2 Matériel'!$G8)),"")</f>
+        <v/>
+      </c>
+      <c r="H20" s="41">
+        <f>IF(AND('2 Matériel'!$L8&gt;0,NOT('2 Matériel'!$B8="Oui")),IF(AND(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H8="","",'2 Matériel'!$H8)),"")</f>
+        <v/>
+      </c>
+      <c r="I20" s="41">
+        <f>IF(AND('2 Matériel'!$L8&gt;0,NOT('2 Matériel'!$B8="Oui")),IF(AND(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I8="","",'2 Matériel'!$I8)),"")</f>
+        <v/>
+      </c>
+      <c r="J20" s="41">
+        <f>IF(AND('2 Matériel'!$L8&gt;0,NOT('2 Matériel'!$B8="Oui")),IF(AND(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J8="","",'2 Matériel'!$J8)),"")</f>
+        <v/>
+      </c>
+      <c r="L20" s="42">
         <f>IF(AND('2 Matériel'!$L8&gt;0,'2 Matériel'!$B8="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="21" customHeight="1">
-      <c r="B19" s="13">
+    <row r="21" ht="21" customHeight="1">
+      <c r="B21" s="38">
         <f>IF(AND('2 Matériel'!$L9&gt;0,NOT('2 Matériel'!$B9="Oui")),'2 Matériel'!$A9,"")</f>
         <v/>
       </c>
-      <c r="C19" s="37">
-        <f>IF('2 Matériel'!$L9&gt;0,IF('2 Matériel'!$B9="Oui",UPPER('2 Matériel'!$C9),'2 Matériel'!$C9),"")</f>
-        <v/>
-      </c>
-      <c r="D19" s="38">
+      <c r="C21" s="39">
+        <f>IF('2 Matériel'!$L9&gt;0,IF('2 Matériel'!$B9="Oui",UPPER('2 Matériel'!$C9),'2 Matériel'!$C9&amp;IF(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <v/>
+      </c>
+      <c r="D21" s="40">
         <f>IF(AND('2 Matériel'!$L9&gt;0,NOT('2 Matériel'!$B9="Oui")),'2 Matériel'!$L9,"")</f>
         <v/>
       </c>
-      <c r="E19" s="39">
-        <f>IF(AND('2 Matériel'!$L9&gt;0,NOT('2 Matériel'!$B9="Oui")),IF(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E9="","",'2 Matériel'!$E9)),"")</f>
-        <v/>
-      </c>
-      <c r="F19" s="39">
-        <f>IF(AND('2 Matériel'!$L9&gt;0,NOT('2 Matériel'!$B9="Oui")),IF(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F9="","",'2 Matériel'!$F9)),"")</f>
-        <v/>
-      </c>
-      <c r="G19" s="39">
-        <f>IF(AND('2 Matériel'!$L9&gt;0,NOT('2 Matériel'!$B9="Oui")),IF(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G9="","",'2 Matériel'!$G9)),"")</f>
-        <v/>
-      </c>
-      <c r="H19" s="39">
-        <f>IF(AND('2 Matériel'!$L9&gt;0,NOT('2 Matériel'!$B9="Oui")),IF(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H9="","",'2 Matériel'!$H9)),"")</f>
-        <v/>
-      </c>
-      <c r="I19" s="39">
-        <f>IF(AND('2 Matériel'!$L9&gt;0,NOT('2 Matériel'!$B9="Oui")),IF(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I9="","",'2 Matériel'!$I9)),"")</f>
-        <v/>
-      </c>
-      <c r="J19" s="39">
-        <f>IF(AND('2 Matériel'!$L9&gt;0,NOT('2 Matériel'!$B9="Oui")),IF(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J9="","",'2 Matériel'!$J9)),"")</f>
-        <v/>
-      </c>
-      <c r="K19" s="40">
-        <f>IF(AND('2 Matériel'!$L9&gt;0,NOT('2 Matériel'!$B9="Oui")),IF(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
-        <v/>
-      </c>
-      <c r="M19" s="41">
+      <c r="E21" s="41">
+        <f>IF(AND('2 Matériel'!$L9&gt;0,NOT('2 Matériel'!$B9="Oui")),IF(AND(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E9="","",'2 Matériel'!$E9)),"")</f>
+        <v/>
+      </c>
+      <c r="F21" s="41">
+        <f>IF(AND('2 Matériel'!$L9&gt;0,NOT('2 Matériel'!$B9="Oui")),IF(AND(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F9="","",'2 Matériel'!$F9)),"")</f>
+        <v/>
+      </c>
+      <c r="G21" s="41">
+        <f>IF(AND('2 Matériel'!$L9&gt;0,NOT('2 Matériel'!$B9="Oui")),IF(AND(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G9="","",'2 Matériel'!$G9)),"")</f>
+        <v/>
+      </c>
+      <c r="H21" s="41">
+        <f>IF(AND('2 Matériel'!$L9&gt;0,NOT('2 Matériel'!$B9="Oui")),IF(AND(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H9="","",'2 Matériel'!$H9)),"")</f>
+        <v/>
+      </c>
+      <c r="I21" s="41">
+        <f>IF(AND('2 Matériel'!$L9&gt;0,NOT('2 Matériel'!$B9="Oui")),IF(AND(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I9="","",'2 Matériel'!$I9)),"")</f>
+        <v/>
+      </c>
+      <c r="J21" s="41">
+        <f>IF(AND('2 Matériel'!$L9&gt;0,NOT('2 Matériel'!$B9="Oui")),IF(AND(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J9="","",'2 Matériel'!$J9)),"")</f>
+        <v/>
+      </c>
+      <c r="L21" s="42">
         <f>IF(AND('2 Matériel'!$L9&gt;0,'2 Matériel'!$B9="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="21" customHeight="1">
-      <c r="B20" s="13">
+    <row r="22" ht="21" customHeight="1">
+      <c r="B22" s="38">
         <f>IF(AND('2 Matériel'!$L10&gt;0,NOT('2 Matériel'!$B10="Oui")),'2 Matériel'!$A10,"")</f>
         <v/>
       </c>
-      <c r="C20" s="37">
-        <f>IF('2 Matériel'!$L10&gt;0,IF('2 Matériel'!$B10="Oui",UPPER('2 Matériel'!$C10),'2 Matériel'!$C10),"")</f>
-        <v/>
-      </c>
-      <c r="D20" s="38">
+      <c r="C22" s="39">
+        <f>IF('2 Matériel'!$L10&gt;0,IF('2 Matériel'!$B10="Oui",UPPER('2 Matériel'!$C10),'2 Matériel'!$C10&amp;IF(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <v/>
+      </c>
+      <c r="D22" s="40">
         <f>IF(AND('2 Matériel'!$L10&gt;0,NOT('2 Matériel'!$B10="Oui")),'2 Matériel'!$L10,"")</f>
         <v/>
       </c>
-      <c r="E20" s="39">
-        <f>IF(AND('2 Matériel'!$L10&gt;0,NOT('2 Matériel'!$B10="Oui")),IF(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E10="","",'2 Matériel'!$E10)),"")</f>
-        <v/>
-      </c>
-      <c r="F20" s="39">
-        <f>IF(AND('2 Matériel'!$L10&gt;0,NOT('2 Matériel'!$B10="Oui")),IF(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F10="","",'2 Matériel'!$F10)),"")</f>
-        <v/>
-      </c>
-      <c r="G20" s="39">
-        <f>IF(AND('2 Matériel'!$L10&gt;0,NOT('2 Matériel'!$B10="Oui")),IF(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G10="","",'2 Matériel'!$G10)),"")</f>
-        <v/>
-      </c>
-      <c r="H20" s="39">
-        <f>IF(AND('2 Matériel'!$L10&gt;0,NOT('2 Matériel'!$B10="Oui")),IF(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H10="","",'2 Matériel'!$H10)),"")</f>
-        <v/>
-      </c>
-      <c r="I20" s="39">
-        <f>IF(AND('2 Matériel'!$L10&gt;0,NOT('2 Matériel'!$B10="Oui")),IF(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I10="","",'2 Matériel'!$I10)),"")</f>
-        <v/>
-      </c>
-      <c r="J20" s="39">
-        <f>IF(AND('2 Matériel'!$L10&gt;0,NOT('2 Matériel'!$B10="Oui")),IF(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J10="","",'2 Matériel'!$J10)),"")</f>
-        <v/>
-      </c>
-      <c r="K20" s="40">
-        <f>IF(AND('2 Matériel'!$L10&gt;0,NOT('2 Matériel'!$B10="Oui")),IF(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
-        <v/>
-      </c>
-      <c r="M20" s="41">
+      <c r="E22" s="41">
+        <f>IF(AND('2 Matériel'!$L10&gt;0,NOT('2 Matériel'!$B10="Oui")),IF(AND(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E10="","",'2 Matériel'!$E10)),"")</f>
+        <v/>
+      </c>
+      <c r="F22" s="41">
+        <f>IF(AND('2 Matériel'!$L10&gt;0,NOT('2 Matériel'!$B10="Oui")),IF(AND(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F10="","",'2 Matériel'!$F10)),"")</f>
+        <v/>
+      </c>
+      <c r="G22" s="41">
+        <f>IF(AND('2 Matériel'!$L10&gt;0,NOT('2 Matériel'!$B10="Oui")),IF(AND(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G10="","",'2 Matériel'!$G10)),"")</f>
+        <v/>
+      </c>
+      <c r="H22" s="41">
+        <f>IF(AND('2 Matériel'!$L10&gt;0,NOT('2 Matériel'!$B10="Oui")),IF(AND(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H10="","",'2 Matériel'!$H10)),"")</f>
+        <v/>
+      </c>
+      <c r="I22" s="41">
+        <f>IF(AND('2 Matériel'!$L10&gt;0,NOT('2 Matériel'!$B10="Oui")),IF(AND(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I10="","",'2 Matériel'!$I10)),"")</f>
+        <v/>
+      </c>
+      <c r="J22" s="41">
+        <f>IF(AND('2 Matériel'!$L10&gt;0,NOT('2 Matériel'!$B10="Oui")),IF(AND(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J10="","",'2 Matériel'!$J10)),"")</f>
+        <v/>
+      </c>
+      <c r="L22" s="42">
         <f>IF(AND('2 Matériel'!$L10&gt;0,'2 Matériel'!$B10="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="21" customHeight="1">
-      <c r="B21" s="13">
+    <row r="23" ht="21" customHeight="1">
+      <c r="B23" s="38">
         <f>IF(AND('2 Matériel'!$L11&gt;0,NOT('2 Matériel'!$B11="Oui")),'2 Matériel'!$A11,"")</f>
         <v/>
       </c>
-      <c r="C21" s="37">
-        <f>IF('2 Matériel'!$L11&gt;0,IF('2 Matériel'!$B11="Oui",UPPER('2 Matériel'!$C11),'2 Matériel'!$C11),"")</f>
-        <v/>
-      </c>
-      <c r="D21" s="38">
+      <c r="C23" s="39">
+        <f>IF('2 Matériel'!$L11&gt;0,IF('2 Matériel'!$B11="Oui",UPPER('2 Matériel'!$C11),'2 Matériel'!$C11&amp;IF(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <v/>
+      </c>
+      <c r="D23" s="40">
         <f>IF(AND('2 Matériel'!$L11&gt;0,NOT('2 Matériel'!$B11="Oui")),'2 Matériel'!$L11,"")</f>
         <v/>
       </c>
-      <c r="E21" s="39">
-        <f>IF(AND('2 Matériel'!$L11&gt;0,NOT('2 Matériel'!$B11="Oui")),IF(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E11="","",'2 Matériel'!$E11)),"")</f>
-        <v/>
-      </c>
-      <c r="F21" s="39">
-        <f>IF(AND('2 Matériel'!$L11&gt;0,NOT('2 Matériel'!$B11="Oui")),IF(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F11="","",'2 Matériel'!$F11)),"")</f>
-        <v/>
-      </c>
-      <c r="G21" s="39">
-        <f>IF(AND('2 Matériel'!$L11&gt;0,NOT('2 Matériel'!$B11="Oui")),IF(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G11="","",'2 Matériel'!$G11)),"")</f>
-        <v/>
-      </c>
-      <c r="H21" s="39">
-        <f>IF(AND('2 Matériel'!$L11&gt;0,NOT('2 Matériel'!$B11="Oui")),IF(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H11="","",'2 Matériel'!$H11)),"")</f>
-        <v/>
-      </c>
-      <c r="I21" s="39">
-        <f>IF(AND('2 Matériel'!$L11&gt;0,NOT('2 Matériel'!$B11="Oui")),IF(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I11="","",'2 Matériel'!$I11)),"")</f>
-        <v/>
-      </c>
-      <c r="J21" s="39">
-        <f>IF(AND('2 Matériel'!$L11&gt;0,NOT('2 Matériel'!$B11="Oui")),IF(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J11="","",'2 Matériel'!$J11)),"")</f>
-        <v/>
-      </c>
-      <c r="K21" s="40">
-        <f>IF(AND('2 Matériel'!$L11&gt;0,NOT('2 Matériel'!$B11="Oui")),IF(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
-        <v/>
-      </c>
-      <c r="M21" s="41">
+      <c r="E23" s="41">
+        <f>IF(AND('2 Matériel'!$L11&gt;0,NOT('2 Matériel'!$B11="Oui")),IF(AND(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E11="","",'2 Matériel'!$E11)),"")</f>
+        <v/>
+      </c>
+      <c r="F23" s="41">
+        <f>IF(AND('2 Matériel'!$L11&gt;0,NOT('2 Matériel'!$B11="Oui")),IF(AND(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F11="","",'2 Matériel'!$F11)),"")</f>
+        <v/>
+      </c>
+      <c r="G23" s="41">
+        <f>IF(AND('2 Matériel'!$L11&gt;0,NOT('2 Matériel'!$B11="Oui")),IF(AND(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G11="","",'2 Matériel'!$G11)),"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="41">
+        <f>IF(AND('2 Matériel'!$L11&gt;0,NOT('2 Matériel'!$B11="Oui")),IF(AND(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H11="","",'2 Matériel'!$H11)),"")</f>
+        <v/>
+      </c>
+      <c r="I23" s="41">
+        <f>IF(AND('2 Matériel'!$L11&gt;0,NOT('2 Matériel'!$B11="Oui")),IF(AND(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I11="","",'2 Matériel'!$I11)),"")</f>
+        <v/>
+      </c>
+      <c r="J23" s="41">
+        <f>IF(AND('2 Matériel'!$L11&gt;0,NOT('2 Matériel'!$B11="Oui")),IF(AND(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J11="","",'2 Matériel'!$J11)),"")</f>
+        <v/>
+      </c>
+      <c r="L23" s="42">
         <f>IF(AND('2 Matériel'!$L11&gt;0,'2 Matériel'!$B11="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="21" customHeight="1">
-      <c r="B22" s="13">
+    <row r="24" ht="21" customHeight="1">
+      <c r="B24" s="38">
         <f>IF(AND('2 Matériel'!$L12&gt;0,NOT('2 Matériel'!$B12="Oui")),'2 Matériel'!$A12,"")</f>
         <v/>
       </c>
-      <c r="C22" s="37">
-        <f>IF('2 Matériel'!$L12&gt;0,IF('2 Matériel'!$B12="Oui",UPPER('2 Matériel'!$C12),'2 Matériel'!$C12),"")</f>
-        <v/>
-      </c>
-      <c r="D22" s="38">
+      <c r="C24" s="39">
+        <f>IF('2 Matériel'!$L12&gt;0,IF('2 Matériel'!$B12="Oui",UPPER('2 Matériel'!$C12),'2 Matériel'!$C12&amp;IF(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <v/>
+      </c>
+      <c r="D24" s="40">
         <f>IF(AND('2 Matériel'!$L12&gt;0,NOT('2 Matériel'!$B12="Oui")),'2 Matériel'!$L12,"")</f>
         <v/>
       </c>
-      <c r="E22" s="39">
-        <f>IF(AND('2 Matériel'!$L12&gt;0,NOT('2 Matériel'!$B12="Oui")),IF(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E12="","",'2 Matériel'!$E12)),"")</f>
-        <v/>
-      </c>
-      <c r="F22" s="39">
-        <f>IF(AND('2 Matériel'!$L12&gt;0,NOT('2 Matériel'!$B12="Oui")),IF(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F12="","",'2 Matériel'!$F12)),"")</f>
-        <v/>
-      </c>
-      <c r="G22" s="39">
-        <f>IF(AND('2 Matériel'!$L12&gt;0,NOT('2 Matériel'!$B12="Oui")),IF(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G12="","",'2 Matériel'!$G12)),"")</f>
-        <v/>
-      </c>
-      <c r="H22" s="39">
-        <f>IF(AND('2 Matériel'!$L12&gt;0,NOT('2 Matériel'!$B12="Oui")),IF(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H12="","",'2 Matériel'!$H12)),"")</f>
-        <v/>
-      </c>
-      <c r="I22" s="39">
-        <f>IF(AND('2 Matériel'!$L12&gt;0,NOT('2 Matériel'!$B12="Oui")),IF(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I12="","",'2 Matériel'!$I12)),"")</f>
-        <v/>
-      </c>
-      <c r="J22" s="39">
-        <f>IF(AND('2 Matériel'!$L12&gt;0,NOT('2 Matériel'!$B12="Oui")),IF(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J12="","",'2 Matériel'!$J12)),"")</f>
-        <v/>
-      </c>
-      <c r="K22" s="40">
-        <f>IF(AND('2 Matériel'!$L12&gt;0,NOT('2 Matériel'!$B12="Oui")),IF(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
-        <v/>
-      </c>
-      <c r="M22" s="41">
+      <c r="E24" s="41">
+        <f>IF(AND('2 Matériel'!$L12&gt;0,NOT('2 Matériel'!$B12="Oui")),IF(AND(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E12="","",'2 Matériel'!$E12)),"")</f>
+        <v/>
+      </c>
+      <c r="F24" s="41">
+        <f>IF(AND('2 Matériel'!$L12&gt;0,NOT('2 Matériel'!$B12="Oui")),IF(AND(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F12="","",'2 Matériel'!$F12)),"")</f>
+        <v/>
+      </c>
+      <c r="G24" s="41">
+        <f>IF(AND('2 Matériel'!$L12&gt;0,NOT('2 Matériel'!$B12="Oui")),IF(AND(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G12="","",'2 Matériel'!$G12)),"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="41">
+        <f>IF(AND('2 Matériel'!$L12&gt;0,NOT('2 Matériel'!$B12="Oui")),IF(AND(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H12="","",'2 Matériel'!$H12)),"")</f>
+        <v/>
+      </c>
+      <c r="I24" s="41">
+        <f>IF(AND('2 Matériel'!$L12&gt;0,NOT('2 Matériel'!$B12="Oui")),IF(AND(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I12="","",'2 Matériel'!$I12)),"")</f>
+        <v/>
+      </c>
+      <c r="J24" s="41">
+        <f>IF(AND('2 Matériel'!$L12&gt;0,NOT('2 Matériel'!$B12="Oui")),IF(AND(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J12="","",'2 Matériel'!$J12)),"")</f>
+        <v/>
+      </c>
+      <c r="L24" s="42">
         <f>IF(AND('2 Matériel'!$L12&gt;0,'2 Matériel'!$B12="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="21" customHeight="1">
-      <c r="B23" s="13">
+    <row r="25" ht="21" customHeight="1">
+      <c r="B25" s="38">
         <f>IF(AND('2 Matériel'!$L13&gt;0,NOT('2 Matériel'!$B13="Oui")),'2 Matériel'!$A13,"")</f>
         <v/>
       </c>
-      <c r="C23" s="37">
-        <f>IF('2 Matériel'!$L13&gt;0,IF('2 Matériel'!$B13="Oui",UPPER('2 Matériel'!$C13),'2 Matériel'!$C13),"")</f>
-        <v/>
-      </c>
-      <c r="D23" s="38">
+      <c r="C25" s="39">
+        <f>IF('2 Matériel'!$L13&gt;0,IF('2 Matériel'!$B13="Oui",UPPER('2 Matériel'!$C13),'2 Matériel'!$C13&amp;IF(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <v/>
+      </c>
+      <c r="D25" s="40">
         <f>IF(AND('2 Matériel'!$L13&gt;0,NOT('2 Matériel'!$B13="Oui")),'2 Matériel'!$L13,"")</f>
         <v/>
       </c>
-      <c r="E23" s="39">
-        <f>IF(AND('2 Matériel'!$L13&gt;0,NOT('2 Matériel'!$B13="Oui")),IF(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E13="","",'2 Matériel'!$E13)),"")</f>
-        <v/>
-      </c>
-      <c r="F23" s="39">
-        <f>IF(AND('2 Matériel'!$L13&gt;0,NOT('2 Matériel'!$B13="Oui")),IF(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F13="","",'2 Matériel'!$F13)),"")</f>
-        <v/>
-      </c>
-      <c r="G23" s="39">
-        <f>IF(AND('2 Matériel'!$L13&gt;0,NOT('2 Matériel'!$B13="Oui")),IF(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G13="","",'2 Matériel'!$G13)),"")</f>
-        <v/>
-      </c>
-      <c r="H23" s="39">
-        <f>IF(AND('2 Matériel'!$L13&gt;0,NOT('2 Matériel'!$B13="Oui")),IF(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H13="","",'2 Matériel'!$H13)),"")</f>
-        <v/>
-      </c>
-      <c r="I23" s="39">
-        <f>IF(AND('2 Matériel'!$L13&gt;0,NOT('2 Matériel'!$B13="Oui")),IF(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I13="","",'2 Matériel'!$I13)),"")</f>
-        <v/>
-      </c>
-      <c r="J23" s="39">
-        <f>IF(AND('2 Matériel'!$L13&gt;0,NOT('2 Matériel'!$B13="Oui")),IF(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J13="","",'2 Matériel'!$J13)),"")</f>
-        <v/>
-      </c>
-      <c r="K23" s="40">
-        <f>IF(AND('2 Matériel'!$L13&gt;0,NOT('2 Matériel'!$B13="Oui")),IF(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
-        <v/>
-      </c>
-      <c r="M23" s="41">
+      <c r="E25" s="41">
+        <f>IF(AND('2 Matériel'!$L13&gt;0,NOT('2 Matériel'!$B13="Oui")),IF(AND(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E13="","",'2 Matériel'!$E13)),"")</f>
+        <v/>
+      </c>
+      <c r="F25" s="41">
+        <f>IF(AND('2 Matériel'!$L13&gt;0,NOT('2 Matériel'!$B13="Oui")),IF(AND(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F13="","",'2 Matériel'!$F13)),"")</f>
+        <v/>
+      </c>
+      <c r="G25" s="41">
+        <f>IF(AND('2 Matériel'!$L13&gt;0,NOT('2 Matériel'!$B13="Oui")),IF(AND(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G13="","",'2 Matériel'!$G13)),"")</f>
+        <v/>
+      </c>
+      <c r="H25" s="41">
+        <f>IF(AND('2 Matériel'!$L13&gt;0,NOT('2 Matériel'!$B13="Oui")),IF(AND(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H13="","",'2 Matériel'!$H13)),"")</f>
+        <v/>
+      </c>
+      <c r="I25" s="41">
+        <f>IF(AND('2 Matériel'!$L13&gt;0,NOT('2 Matériel'!$B13="Oui")),IF(AND(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I13="","",'2 Matériel'!$I13)),"")</f>
+        <v/>
+      </c>
+      <c r="J25" s="41">
+        <f>IF(AND('2 Matériel'!$L13&gt;0,NOT('2 Matériel'!$B13="Oui")),IF(AND(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J13="","",'2 Matériel'!$J13)),"")</f>
+        <v/>
+      </c>
+      <c r="L25" s="42">
         <f>IF(AND('2 Matériel'!$L13&gt;0,'2 Matériel'!$B13="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="21" customHeight="1">
-      <c r="B24" s="13">
+    <row r="26" ht="21" customHeight="1">
+      <c r="B26" s="38">
         <f>IF(AND('2 Matériel'!$L14&gt;0,NOT('2 Matériel'!$B14="Oui")),'2 Matériel'!$A14,"")</f>
         <v/>
       </c>
-      <c r="C24" s="37">
-        <f>IF('2 Matériel'!$L14&gt;0,IF('2 Matériel'!$B14="Oui",UPPER('2 Matériel'!$C14),'2 Matériel'!$C14),"")</f>
-        <v/>
-      </c>
-      <c r="D24" s="38">
+      <c r="C26" s="39">
+        <f>IF('2 Matériel'!$L14&gt;0,IF('2 Matériel'!$B14="Oui",UPPER('2 Matériel'!$C14),'2 Matériel'!$C14&amp;IF(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <v/>
+      </c>
+      <c r="D26" s="40">
         <f>IF(AND('2 Matériel'!$L14&gt;0,NOT('2 Matériel'!$B14="Oui")),'2 Matériel'!$L14,"")</f>
         <v/>
       </c>
-      <c r="E24" s="39">
-        <f>IF(AND('2 Matériel'!$L14&gt;0,NOT('2 Matériel'!$B14="Oui")),IF(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E14="","",'2 Matériel'!$E14)),"")</f>
-        <v/>
-      </c>
-      <c r="F24" s="39">
-        <f>IF(AND('2 Matériel'!$L14&gt;0,NOT('2 Matériel'!$B14="Oui")),IF(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F14="","",'2 Matériel'!$F14)),"")</f>
-        <v/>
-      </c>
-      <c r="G24" s="39">
-        <f>IF(AND('2 Matériel'!$L14&gt;0,NOT('2 Matériel'!$B14="Oui")),IF(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G14="","",'2 Matériel'!$G14)),"")</f>
-        <v/>
-      </c>
-      <c r="H24" s="39">
-        <f>IF(AND('2 Matériel'!$L14&gt;0,NOT('2 Matériel'!$B14="Oui")),IF(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H14="","",'2 Matériel'!$H14)),"")</f>
-        <v/>
-      </c>
-      <c r="I24" s="39">
-        <f>IF(AND('2 Matériel'!$L14&gt;0,NOT('2 Matériel'!$B14="Oui")),IF(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I14="","",'2 Matériel'!$I14)),"")</f>
-        <v/>
-      </c>
-      <c r="J24" s="39">
-        <f>IF(AND('2 Matériel'!$L14&gt;0,NOT('2 Matériel'!$B14="Oui")),IF(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J14="","",'2 Matériel'!$J14)),"")</f>
-        <v/>
-      </c>
-      <c r="K24" s="40">
-        <f>IF(AND('2 Matériel'!$L14&gt;0,NOT('2 Matériel'!$B14="Oui")),IF(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
-        <v/>
-      </c>
-      <c r="M24" s="41">
+      <c r="E26" s="41">
+        <f>IF(AND('2 Matériel'!$L14&gt;0,NOT('2 Matériel'!$B14="Oui")),IF(AND(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E14="","",'2 Matériel'!$E14)),"")</f>
+        <v/>
+      </c>
+      <c r="F26" s="41">
+        <f>IF(AND('2 Matériel'!$L14&gt;0,NOT('2 Matériel'!$B14="Oui")),IF(AND(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F14="","",'2 Matériel'!$F14)),"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="41">
+        <f>IF(AND('2 Matériel'!$L14&gt;0,NOT('2 Matériel'!$B14="Oui")),IF(AND(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G14="","",'2 Matériel'!$G14)),"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="41">
+        <f>IF(AND('2 Matériel'!$L14&gt;0,NOT('2 Matériel'!$B14="Oui")),IF(AND(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H14="","",'2 Matériel'!$H14)),"")</f>
+        <v/>
+      </c>
+      <c r="I26" s="41">
+        <f>IF(AND('2 Matériel'!$L14&gt;0,NOT('2 Matériel'!$B14="Oui")),IF(AND(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I14="","",'2 Matériel'!$I14)),"")</f>
+        <v/>
+      </c>
+      <c r="J26" s="41">
+        <f>IF(AND('2 Matériel'!$L14&gt;0,NOT('2 Matériel'!$B14="Oui")),IF(AND(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J14="","",'2 Matériel'!$J14)),"")</f>
+        <v/>
+      </c>
+      <c r="L26" s="42">
         <f>IF(AND('2 Matériel'!$L14&gt;0,'2 Matériel'!$B14="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="21" customHeight="1">
-      <c r="B25" s="13">
+    <row r="27" ht="21" customHeight="1">
+      <c r="B27" s="38">
         <f>IF(AND('2 Matériel'!$L15&gt;0,NOT('2 Matériel'!$B15="Oui")),'2 Matériel'!$A15,"")</f>
         <v/>
       </c>
-      <c r="C25" s="37">
-        <f>IF('2 Matériel'!$L15&gt;0,IF('2 Matériel'!$B15="Oui",UPPER('2 Matériel'!$C15),'2 Matériel'!$C15),"")</f>
-        <v/>
-      </c>
-      <c r="D25" s="38">
+      <c r="C27" s="39">
+        <f>IF('2 Matériel'!$L15&gt;0,IF('2 Matériel'!$B15="Oui",UPPER('2 Matériel'!$C15),'2 Matériel'!$C15&amp;IF(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <v/>
+      </c>
+      <c r="D27" s="40">
         <f>IF(AND('2 Matériel'!$L15&gt;0,NOT('2 Matériel'!$B15="Oui")),'2 Matériel'!$L15,"")</f>
         <v/>
       </c>
-      <c r="E25" s="39">
-        <f>IF(AND('2 Matériel'!$L15&gt;0,NOT('2 Matériel'!$B15="Oui")),IF(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E15="","",'2 Matériel'!$E15)),"")</f>
-        <v/>
-      </c>
-      <c r="F25" s="39">
-        <f>IF(AND('2 Matériel'!$L15&gt;0,NOT('2 Matériel'!$B15="Oui")),IF(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F15="","",'2 Matériel'!$F15)),"")</f>
-        <v/>
-      </c>
-      <c r="G25" s="39">
-        <f>IF(AND('2 Matériel'!$L15&gt;0,NOT('2 Matériel'!$B15="Oui")),IF(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G15="","",'2 Matériel'!$G15)),"")</f>
-        <v/>
-      </c>
-      <c r="H25" s="39">
-        <f>IF(AND('2 Matériel'!$L15&gt;0,NOT('2 Matériel'!$B15="Oui")),IF(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H15="","",'2 Matériel'!$H15)),"")</f>
-        <v/>
-      </c>
-      <c r="I25" s="39">
-        <f>IF(AND('2 Matériel'!$L15&gt;0,NOT('2 Matériel'!$B15="Oui")),IF(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I15="","",'2 Matériel'!$I15)),"")</f>
-        <v/>
-      </c>
-      <c r="J25" s="39">
-        <f>IF(AND('2 Matériel'!$L15&gt;0,NOT('2 Matériel'!$B15="Oui")),IF(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J15="","",'2 Matériel'!$J15)),"")</f>
-        <v/>
-      </c>
-      <c r="K25" s="40">
-        <f>IF(AND('2 Matériel'!$L15&gt;0,NOT('2 Matériel'!$B15="Oui")),IF(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
-        <v/>
-      </c>
-      <c r="M25" s="41">
+      <c r="E27" s="41">
+        <f>IF(AND('2 Matériel'!$L15&gt;0,NOT('2 Matériel'!$B15="Oui")),IF(AND(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E15="","",'2 Matériel'!$E15)),"")</f>
+        <v/>
+      </c>
+      <c r="F27" s="41">
+        <f>IF(AND('2 Matériel'!$L15&gt;0,NOT('2 Matériel'!$B15="Oui")),IF(AND(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F15="","",'2 Matériel'!$F15)),"")</f>
+        <v/>
+      </c>
+      <c r="G27" s="41">
+        <f>IF(AND('2 Matériel'!$L15&gt;0,NOT('2 Matériel'!$B15="Oui")),IF(AND(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G15="","",'2 Matériel'!$G15)),"")</f>
+        <v/>
+      </c>
+      <c r="H27" s="41">
+        <f>IF(AND('2 Matériel'!$L15&gt;0,NOT('2 Matériel'!$B15="Oui")),IF(AND(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H15="","",'2 Matériel'!$H15)),"")</f>
+        <v/>
+      </c>
+      <c r="I27" s="41">
+        <f>IF(AND('2 Matériel'!$L15&gt;0,NOT('2 Matériel'!$B15="Oui")),IF(AND(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I15="","",'2 Matériel'!$I15)),"")</f>
+        <v/>
+      </c>
+      <c r="J27" s="41">
+        <f>IF(AND('2 Matériel'!$L15&gt;0,NOT('2 Matériel'!$B15="Oui")),IF(AND(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J15="","",'2 Matériel'!$J15)),"")</f>
+        <v/>
+      </c>
+      <c r="L27" s="42">
         <f>IF(AND('2 Matériel'!$L15&gt;0,'2 Matériel'!$B15="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="21" customHeight="1">
-      <c r="B26" s="13">
+    <row r="28" ht="21" customHeight="1">
+      <c r="B28" s="38">
         <f>IF(AND('2 Matériel'!$L16&gt;0,NOT('2 Matériel'!$B16="Oui")),'2 Matériel'!$A16,"")</f>
         <v/>
       </c>
-      <c r="C26" s="37">
-        <f>IF('2 Matériel'!$L16&gt;0,IF('2 Matériel'!$B16="Oui",UPPER('2 Matériel'!$C16),'2 Matériel'!$C16),"")</f>
-        <v/>
-      </c>
-      <c r="D26" s="38">
+      <c r="C28" s="39">
+        <f>IF('2 Matériel'!$L16&gt;0,IF('2 Matériel'!$B16="Oui",UPPER('2 Matériel'!$C16),'2 Matériel'!$C16&amp;IF(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <v/>
+      </c>
+      <c r="D28" s="40">
         <f>IF(AND('2 Matériel'!$L16&gt;0,NOT('2 Matériel'!$B16="Oui")),'2 Matériel'!$L16,"")</f>
         <v/>
       </c>
-      <c r="E26" s="39">
-        <f>IF(AND('2 Matériel'!$L16&gt;0,NOT('2 Matériel'!$B16="Oui")),IF(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E16="","",'2 Matériel'!$E16)),"")</f>
-        <v/>
-      </c>
-      <c r="F26" s="39">
-        <f>IF(AND('2 Matériel'!$L16&gt;0,NOT('2 Matériel'!$B16="Oui")),IF(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F16="","",'2 Matériel'!$F16)),"")</f>
-        <v/>
-      </c>
-      <c r="G26" s="39">
-        <f>IF(AND('2 Matériel'!$L16&gt;0,NOT('2 Matériel'!$B16="Oui")),IF(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G16="","",'2 Matériel'!$G16)),"")</f>
-        <v/>
-      </c>
-      <c r="H26" s="39">
-        <f>IF(AND('2 Matériel'!$L16&gt;0,NOT('2 Matériel'!$B16="Oui")),IF(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H16="","",'2 Matériel'!$H16)),"")</f>
-        <v/>
-      </c>
-      <c r="I26" s="39">
-        <f>IF(AND('2 Matériel'!$L16&gt;0,NOT('2 Matériel'!$B16="Oui")),IF(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I16="","",'2 Matériel'!$I16)),"")</f>
-        <v/>
-      </c>
-      <c r="J26" s="39">
-        <f>IF(AND('2 Matériel'!$L16&gt;0,NOT('2 Matériel'!$B16="Oui")),IF(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J16="","",'2 Matériel'!$J16)),"")</f>
-        <v/>
-      </c>
-      <c r="K26" s="40">
-        <f>IF(AND('2 Matériel'!$L16&gt;0,NOT('2 Matériel'!$B16="Oui")),IF(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
-        <v/>
-      </c>
-      <c r="M26" s="41">
+      <c r="E28" s="41">
+        <f>IF(AND('2 Matériel'!$L16&gt;0,NOT('2 Matériel'!$B16="Oui")),IF(AND(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E16="","",'2 Matériel'!$E16)),"")</f>
+        <v/>
+      </c>
+      <c r="F28" s="41">
+        <f>IF(AND('2 Matériel'!$L16&gt;0,NOT('2 Matériel'!$B16="Oui")),IF(AND(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F16="","",'2 Matériel'!$F16)),"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="41">
+        <f>IF(AND('2 Matériel'!$L16&gt;0,NOT('2 Matériel'!$B16="Oui")),IF(AND(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G16="","",'2 Matériel'!$G16)),"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="41">
+        <f>IF(AND('2 Matériel'!$L16&gt;0,NOT('2 Matériel'!$B16="Oui")),IF(AND(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H16="","",'2 Matériel'!$H16)),"")</f>
+        <v/>
+      </c>
+      <c r="I28" s="41">
+        <f>IF(AND('2 Matériel'!$L16&gt;0,NOT('2 Matériel'!$B16="Oui")),IF(AND(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I16="","",'2 Matériel'!$I16)),"")</f>
+        <v/>
+      </c>
+      <c r="J28" s="41">
+        <f>IF(AND('2 Matériel'!$L16&gt;0,NOT('2 Matériel'!$B16="Oui")),IF(AND(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J16="","",'2 Matériel'!$J16)),"")</f>
+        <v/>
+      </c>
+      <c r="L28" s="42">
         <f>IF(AND('2 Matériel'!$L16&gt;0,'2 Matériel'!$B16="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="21" customHeight="1">
-      <c r="B27" s="13">
+    <row r="29" ht="21" customHeight="1">
+      <c r="B29" s="38">
         <f>IF(AND('2 Matériel'!$L17&gt;0,NOT('2 Matériel'!$B17="Oui")),'2 Matériel'!$A17,"")</f>
         <v/>
       </c>
-      <c r="C27" s="37">
-        <f>IF('2 Matériel'!$L17&gt;0,IF('2 Matériel'!$B17="Oui",UPPER('2 Matériel'!$C17),'2 Matériel'!$C17),"")</f>
-        <v/>
-      </c>
-      <c r="D27" s="38">
+      <c r="C29" s="39">
+        <f>IF('2 Matériel'!$L17&gt;0,IF('2 Matériel'!$B17="Oui",UPPER('2 Matériel'!$C17),'2 Matériel'!$C17&amp;IF(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <v/>
+      </c>
+      <c r="D29" s="40">
         <f>IF(AND('2 Matériel'!$L17&gt;0,NOT('2 Matériel'!$B17="Oui")),'2 Matériel'!$L17,"")</f>
         <v/>
       </c>
-      <c r="E27" s="39">
-        <f>IF(AND('2 Matériel'!$L17&gt;0,NOT('2 Matériel'!$B17="Oui")),IF(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E17="","",'2 Matériel'!$E17)),"")</f>
-        <v/>
-      </c>
-      <c r="F27" s="39">
-        <f>IF(AND('2 Matériel'!$L17&gt;0,NOT('2 Matériel'!$B17="Oui")),IF(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F17="","",'2 Matériel'!$F17)),"")</f>
-        <v/>
-      </c>
-      <c r="G27" s="39">
-        <f>IF(AND('2 Matériel'!$L17&gt;0,NOT('2 Matériel'!$B17="Oui")),IF(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G17="","",'2 Matériel'!$G17)),"")</f>
-        <v/>
-      </c>
-      <c r="H27" s="39">
-        <f>IF(AND('2 Matériel'!$L17&gt;0,NOT('2 Matériel'!$B17="Oui")),IF(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H17="","",'2 Matériel'!$H17)),"")</f>
-        <v/>
-      </c>
-      <c r="I27" s="39">
-        <f>IF(AND('2 Matériel'!$L17&gt;0,NOT('2 Matériel'!$B17="Oui")),IF(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I17="","",'2 Matériel'!$I17)),"")</f>
-        <v/>
-      </c>
-      <c r="J27" s="39">
-        <f>IF(AND('2 Matériel'!$L17&gt;0,NOT('2 Matériel'!$B17="Oui")),IF(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J17="","",'2 Matériel'!$J17)),"")</f>
-        <v/>
-      </c>
-      <c r="K27" s="40">
-        <f>IF(AND('2 Matériel'!$L17&gt;0,NOT('2 Matériel'!$B17="Oui")),IF(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
-        <v/>
-      </c>
-      <c r="M27" s="41">
+      <c r="E29" s="41">
+        <f>IF(AND('2 Matériel'!$L17&gt;0,NOT('2 Matériel'!$B17="Oui")),IF(AND(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E17="","",'2 Matériel'!$E17)),"")</f>
+        <v/>
+      </c>
+      <c r="F29" s="41">
+        <f>IF(AND('2 Matériel'!$L17&gt;0,NOT('2 Matériel'!$B17="Oui")),IF(AND(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F17="","",'2 Matériel'!$F17)),"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="41">
+        <f>IF(AND('2 Matériel'!$L17&gt;0,NOT('2 Matériel'!$B17="Oui")),IF(AND(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G17="","",'2 Matériel'!$G17)),"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="41">
+        <f>IF(AND('2 Matériel'!$L17&gt;0,NOT('2 Matériel'!$B17="Oui")),IF(AND(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H17="","",'2 Matériel'!$H17)),"")</f>
+        <v/>
+      </c>
+      <c r="I29" s="41">
+        <f>IF(AND('2 Matériel'!$L17&gt;0,NOT('2 Matériel'!$B17="Oui")),IF(AND(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I17="","",'2 Matériel'!$I17)),"")</f>
+        <v/>
+      </c>
+      <c r="J29" s="41">
+        <f>IF(AND('2 Matériel'!$L17&gt;0,NOT('2 Matériel'!$B17="Oui")),IF(AND(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J17="","",'2 Matériel'!$J17)),"")</f>
+        <v/>
+      </c>
+      <c r="L29" s="42">
         <f>IF(AND('2 Matériel'!$L17&gt;0,'2 Matériel'!$B17="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="21" customHeight="1">
-      <c r="B28" s="13">
+    <row r="30" ht="21" customHeight="1">
+      <c r="B30" s="38">
         <f>IF(AND('2 Matériel'!$L18&gt;0,NOT('2 Matériel'!$B18="Oui")),'2 Matériel'!$A18,"")</f>
         <v/>
       </c>
-      <c r="C28" s="37">
-        <f>IF('2 Matériel'!$L18&gt;0,IF('2 Matériel'!$B18="Oui",UPPER('2 Matériel'!$C18),'2 Matériel'!$C18),"")</f>
-        <v/>
-      </c>
-      <c r="D28" s="38">
+      <c r="C30" s="39">
+        <f>IF('2 Matériel'!$L18&gt;0,IF('2 Matériel'!$B18="Oui",UPPER('2 Matériel'!$C18),'2 Matériel'!$C18&amp;IF(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <v/>
+      </c>
+      <c r="D30" s="40">
         <f>IF(AND('2 Matériel'!$L18&gt;0,NOT('2 Matériel'!$B18="Oui")),'2 Matériel'!$L18,"")</f>
         <v/>
       </c>
-      <c r="E28" s="39">
-        <f>IF(AND('2 Matériel'!$L18&gt;0,NOT('2 Matériel'!$B18="Oui")),IF(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E18="","",'2 Matériel'!$E18)),"")</f>
-        <v/>
-      </c>
-      <c r="F28" s="39">
-        <f>IF(AND('2 Matériel'!$L18&gt;0,NOT('2 Matériel'!$B18="Oui")),IF(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F18="","",'2 Matériel'!$F18)),"")</f>
-        <v/>
-      </c>
-      <c r="G28" s="39">
-        <f>IF(AND('2 Matériel'!$L18&gt;0,NOT('2 Matériel'!$B18="Oui")),IF(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G18="","",'2 Matériel'!$G18)),"")</f>
-        <v/>
-      </c>
-      <c r="H28" s="39">
-        <f>IF(AND('2 Matériel'!$L18&gt;0,NOT('2 Matériel'!$B18="Oui")),IF(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H18="","",'2 Matériel'!$H18)),"")</f>
-        <v/>
-      </c>
-      <c r="I28" s="39">
-        <f>IF(AND('2 Matériel'!$L18&gt;0,NOT('2 Matériel'!$B18="Oui")),IF(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I18="","",'2 Matériel'!$I18)),"")</f>
-        <v/>
-      </c>
-      <c r="J28" s="39">
-        <f>IF(AND('2 Matériel'!$L18&gt;0,NOT('2 Matériel'!$B18="Oui")),IF(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J18="","",'2 Matériel'!$J18)),"")</f>
-        <v/>
-      </c>
-      <c r="K28" s="40">
-        <f>IF(AND('2 Matériel'!$L18&gt;0,NOT('2 Matériel'!$B18="Oui")),IF(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
-        <v/>
-      </c>
-      <c r="M28" s="41">
+      <c r="E30" s="41">
+        <f>IF(AND('2 Matériel'!$L18&gt;0,NOT('2 Matériel'!$B18="Oui")),IF(AND(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E18="","",'2 Matériel'!$E18)),"")</f>
+        <v/>
+      </c>
+      <c r="F30" s="41">
+        <f>IF(AND('2 Matériel'!$L18&gt;0,NOT('2 Matériel'!$B18="Oui")),IF(AND(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F18="","",'2 Matériel'!$F18)),"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="41">
+        <f>IF(AND('2 Matériel'!$L18&gt;0,NOT('2 Matériel'!$B18="Oui")),IF(AND(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G18="","",'2 Matériel'!$G18)),"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="41">
+        <f>IF(AND('2 Matériel'!$L18&gt;0,NOT('2 Matériel'!$B18="Oui")),IF(AND(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H18="","",'2 Matériel'!$H18)),"")</f>
+        <v/>
+      </c>
+      <c r="I30" s="41">
+        <f>IF(AND('2 Matériel'!$L18&gt;0,NOT('2 Matériel'!$B18="Oui")),IF(AND(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I18="","",'2 Matériel'!$I18)),"")</f>
+        <v/>
+      </c>
+      <c r="J30" s="41">
+        <f>IF(AND('2 Matériel'!$L18&gt;0,NOT('2 Matériel'!$B18="Oui")),IF(AND(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J18="","",'2 Matériel'!$J18)),"")</f>
+        <v/>
+      </c>
+      <c r="L30" s="42">
         <f>IF(AND('2 Matériel'!$L18&gt;0,'2 Matériel'!$B18="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="21" customHeight="1">
-      <c r="B29" s="13">
+    <row r="31" ht="21" customHeight="1">
+      <c r="B31" s="38">
         <f>IF(AND('2 Matériel'!$L19&gt;0,NOT('2 Matériel'!$B19="Oui")),'2 Matériel'!$A19,"")</f>
         <v/>
       </c>
-      <c r="C29" s="37">
-        <f>IF('2 Matériel'!$L19&gt;0,IF('2 Matériel'!$B19="Oui",UPPER('2 Matériel'!$C19),'2 Matériel'!$C19),"")</f>
-        <v/>
-      </c>
-      <c r="D29" s="38">
+      <c r="C31" s="39">
+        <f>IF('2 Matériel'!$L19&gt;0,IF('2 Matériel'!$B19="Oui",UPPER('2 Matériel'!$C19),'2 Matériel'!$C19&amp;IF(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <v/>
+      </c>
+      <c r="D31" s="40">
         <f>IF(AND('2 Matériel'!$L19&gt;0,NOT('2 Matériel'!$B19="Oui")),'2 Matériel'!$L19,"")</f>
         <v/>
       </c>
-      <c r="E29" s="39">
-        <f>IF(AND('2 Matériel'!$L19&gt;0,NOT('2 Matériel'!$B19="Oui")),IF(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E19="","",'2 Matériel'!$E19)),"")</f>
-        <v/>
-      </c>
-      <c r="F29" s="39">
-        <f>IF(AND('2 Matériel'!$L19&gt;0,NOT('2 Matériel'!$B19="Oui")),IF(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F19="","",'2 Matériel'!$F19)),"")</f>
-        <v/>
-      </c>
-      <c r="G29" s="39">
-        <f>IF(AND('2 Matériel'!$L19&gt;0,NOT('2 Matériel'!$B19="Oui")),IF(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G19="","",'2 Matériel'!$G19)),"")</f>
-        <v/>
-      </c>
-      <c r="H29" s="39">
-        <f>IF(AND('2 Matériel'!$L19&gt;0,NOT('2 Matériel'!$B19="Oui")),IF(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H19="","",'2 Matériel'!$H19)),"")</f>
-        <v/>
-      </c>
-      <c r="I29" s="39">
-        <f>IF(AND('2 Matériel'!$L19&gt;0,NOT('2 Matériel'!$B19="Oui")),IF(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I19="","",'2 Matériel'!$I19)),"")</f>
-        <v/>
-      </c>
-      <c r="J29" s="39">
-        <f>IF(AND('2 Matériel'!$L19&gt;0,NOT('2 Matériel'!$B19="Oui")),IF(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J19="","",'2 Matériel'!$J19)),"")</f>
-        <v/>
-      </c>
-      <c r="K29" s="40">
-        <f>IF(AND('2 Matériel'!$L19&gt;0,NOT('2 Matériel'!$B19="Oui")),IF(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
-        <v/>
-      </c>
-      <c r="M29" s="41">
+      <c r="E31" s="41">
+        <f>IF(AND('2 Matériel'!$L19&gt;0,NOT('2 Matériel'!$B19="Oui")),IF(AND(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E19="","",'2 Matériel'!$E19)),"")</f>
+        <v/>
+      </c>
+      <c r="F31" s="41">
+        <f>IF(AND('2 Matériel'!$L19&gt;0,NOT('2 Matériel'!$B19="Oui")),IF(AND(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F19="","",'2 Matériel'!$F19)),"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="41">
+        <f>IF(AND('2 Matériel'!$L19&gt;0,NOT('2 Matériel'!$B19="Oui")),IF(AND(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G19="","",'2 Matériel'!$G19)),"")</f>
+        <v/>
+      </c>
+      <c r="H31" s="41">
+        <f>IF(AND('2 Matériel'!$L19&gt;0,NOT('2 Matériel'!$B19="Oui")),IF(AND(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H19="","",'2 Matériel'!$H19)),"")</f>
+        <v/>
+      </c>
+      <c r="I31" s="41">
+        <f>IF(AND('2 Matériel'!$L19&gt;0,NOT('2 Matériel'!$B19="Oui")),IF(AND(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I19="","",'2 Matériel'!$I19)),"")</f>
+        <v/>
+      </c>
+      <c r="J31" s="41">
+        <f>IF(AND('2 Matériel'!$L19&gt;0,NOT('2 Matériel'!$B19="Oui")),IF(AND(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J19="","",'2 Matériel'!$J19)),"")</f>
+        <v/>
+      </c>
+      <c r="L31" s="42">
         <f>IF(AND('2 Matériel'!$L19&gt;0,'2 Matériel'!$B19="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
-    <row r="30" hidden="1" outlineLevel="1" ht="21" customHeight="1">
-      <c r="B30" s="13">
+    <row r="32" ht="21" customHeight="1">
+      <c r="B32" s="38">
         <f>IF(AND('2 Matériel'!$L20&gt;0,NOT('2 Matériel'!$B20="Oui")),'2 Matériel'!$A20,"")</f>
         <v/>
       </c>
-      <c r="C30" s="37">
-        <f>IF('2 Matériel'!$L20&gt;0,IF('2 Matériel'!$B20="Oui",UPPER('2 Matériel'!$C20),'2 Matériel'!$C20),"")</f>
-        <v/>
-      </c>
-      <c r="D30" s="38">
+      <c r="C32" s="39">
+        <f>IF('2 Matériel'!$L20&gt;0,IF('2 Matériel'!$B20="Oui",UPPER('2 Matériel'!$C20),'2 Matériel'!$C20&amp;IF(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <v/>
+      </c>
+      <c r="D32" s="40">
         <f>IF(AND('2 Matériel'!$L20&gt;0,NOT('2 Matériel'!$B20="Oui")),'2 Matériel'!$L20,"")</f>
         <v/>
       </c>
-      <c r="E30" s="39">
-        <f>IF(AND('2 Matériel'!$L20&gt;0,NOT('2 Matériel'!$B20="Oui")),IF(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E20="","",'2 Matériel'!$E20)),"")</f>
-        <v/>
-      </c>
-      <c r="F30" s="39">
-        <f>IF(AND('2 Matériel'!$L20&gt;0,NOT('2 Matériel'!$B20="Oui")),IF(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F20="","",'2 Matériel'!$F20)),"")</f>
-        <v/>
-      </c>
-      <c r="G30" s="39">
-        <f>IF(AND('2 Matériel'!$L20&gt;0,NOT('2 Matériel'!$B20="Oui")),IF(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G20="","",'2 Matériel'!$G20)),"")</f>
-        <v/>
-      </c>
-      <c r="H30" s="39">
-        <f>IF(AND('2 Matériel'!$L20&gt;0,NOT('2 Matériel'!$B20="Oui")),IF(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H20="","",'2 Matériel'!$H20)),"")</f>
-        <v/>
-      </c>
-      <c r="I30" s="39">
-        <f>IF(AND('2 Matériel'!$L20&gt;0,NOT('2 Matériel'!$B20="Oui")),IF(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I20="","",'2 Matériel'!$I20)),"")</f>
-        <v/>
-      </c>
-      <c r="J30" s="39">
-        <f>IF(AND('2 Matériel'!$L20&gt;0,NOT('2 Matériel'!$B20="Oui")),IF(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J20="","",'2 Matériel'!$J20)),"")</f>
-        <v/>
-      </c>
-      <c r="K30" s="40">
-        <f>IF(AND('2 Matériel'!$L20&gt;0,NOT('2 Matériel'!$B20="Oui")),IF(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
-        <v/>
-      </c>
-      <c r="M30" s="41">
+      <c r="E32" s="41">
+        <f>IF(AND('2 Matériel'!$L20&gt;0,NOT('2 Matériel'!$B20="Oui")),IF(AND(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E20="","",'2 Matériel'!$E20)),"")</f>
+        <v/>
+      </c>
+      <c r="F32" s="41">
+        <f>IF(AND('2 Matériel'!$L20&gt;0,NOT('2 Matériel'!$B20="Oui")),IF(AND(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F20="","",'2 Matériel'!$F20)),"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="41">
+        <f>IF(AND('2 Matériel'!$L20&gt;0,NOT('2 Matériel'!$B20="Oui")),IF(AND(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G20="","",'2 Matériel'!$G20)),"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="41">
+        <f>IF(AND('2 Matériel'!$L20&gt;0,NOT('2 Matériel'!$B20="Oui")),IF(AND(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H20="","",'2 Matériel'!$H20)),"")</f>
+        <v/>
+      </c>
+      <c r="I32" s="41">
+        <f>IF(AND('2 Matériel'!$L20&gt;0,NOT('2 Matériel'!$B20="Oui")),IF(AND(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I20="","",'2 Matériel'!$I20)),"")</f>
+        <v/>
+      </c>
+      <c r="J32" s="41">
+        <f>IF(AND('2 Matériel'!$L20&gt;0,NOT('2 Matériel'!$B20="Oui")),IF(AND(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J20="","",'2 Matériel'!$J20)),"")</f>
+        <v/>
+      </c>
+      <c r="L32" s="42">
         <f>IF(AND('2 Matériel'!$L20&gt;0,'2 Matériel'!$B20="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
-    <row r="31" hidden="1" outlineLevel="1" ht="21" customHeight="1">
-      <c r="B31" s="13">
+    <row r="33" ht="21" customHeight="1">
+      <c r="B33" s="38">
         <f>IF(AND('2 Matériel'!$L21&gt;0,NOT('2 Matériel'!$B21="Oui")),'2 Matériel'!$A21,"")</f>
         <v/>
       </c>
-      <c r="C31" s="37">
-        <f>IF('2 Matériel'!$L21&gt;0,IF('2 Matériel'!$B21="Oui",UPPER('2 Matériel'!$C21),'2 Matériel'!$C21),"")</f>
-        <v/>
-      </c>
-      <c r="D31" s="38">
+      <c r="C33" s="39">
+        <f>IF('2 Matériel'!$L21&gt;0,IF('2 Matériel'!$B21="Oui",UPPER('2 Matériel'!$C21),'2 Matériel'!$C21&amp;IF(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <v/>
+      </c>
+      <c r="D33" s="40">
         <f>IF(AND('2 Matériel'!$L21&gt;0,NOT('2 Matériel'!$B21="Oui")),'2 Matériel'!$L21,"")</f>
         <v/>
       </c>
-      <c r="E31" s="39">
-        <f>IF(AND('2 Matériel'!$L21&gt;0,NOT('2 Matériel'!$B21="Oui")),IF(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E21="","",'2 Matériel'!$E21)),"")</f>
-        <v/>
-      </c>
-      <c r="F31" s="39">
-        <f>IF(AND('2 Matériel'!$L21&gt;0,NOT('2 Matériel'!$B21="Oui")),IF(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F21="","",'2 Matériel'!$F21)),"")</f>
-        <v/>
-      </c>
-      <c r="G31" s="39">
-        <f>IF(AND('2 Matériel'!$L21&gt;0,NOT('2 Matériel'!$B21="Oui")),IF(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G21="","",'2 Matériel'!$G21)),"")</f>
-        <v/>
-      </c>
-      <c r="H31" s="39">
-        <f>IF(AND('2 Matériel'!$L21&gt;0,NOT('2 Matériel'!$B21="Oui")),IF(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H21="","",'2 Matériel'!$H21)),"")</f>
-        <v/>
-      </c>
-      <c r="I31" s="39">
-        <f>IF(AND('2 Matériel'!$L21&gt;0,NOT('2 Matériel'!$B21="Oui")),IF(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I21="","",'2 Matériel'!$I21)),"")</f>
-        <v/>
-      </c>
-      <c r="J31" s="39">
-        <f>IF(AND('2 Matériel'!$L21&gt;0,NOT('2 Matériel'!$B21="Oui")),IF(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J21="","",'2 Matériel'!$J21)),"")</f>
-        <v/>
-      </c>
-      <c r="K31" s="40">
-        <f>IF(AND('2 Matériel'!$L21&gt;0,NOT('2 Matériel'!$B21="Oui")),IF(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
-        <v/>
-      </c>
-      <c r="M31" s="41">
+      <c r="E33" s="41">
+        <f>IF(AND('2 Matériel'!$L21&gt;0,NOT('2 Matériel'!$B21="Oui")),IF(AND(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E21="","",'2 Matériel'!$E21)),"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="41">
+        <f>IF(AND('2 Matériel'!$L21&gt;0,NOT('2 Matériel'!$B21="Oui")),IF(AND(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F21="","",'2 Matériel'!$F21)),"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="41">
+        <f>IF(AND('2 Matériel'!$L21&gt;0,NOT('2 Matériel'!$B21="Oui")),IF(AND(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G21="","",'2 Matériel'!$G21)),"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="41">
+        <f>IF(AND('2 Matériel'!$L21&gt;0,NOT('2 Matériel'!$B21="Oui")),IF(AND(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H21="","",'2 Matériel'!$H21)),"")</f>
+        <v/>
+      </c>
+      <c r="I33" s="41">
+        <f>IF(AND('2 Matériel'!$L21&gt;0,NOT('2 Matériel'!$B21="Oui")),IF(AND(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I21="","",'2 Matériel'!$I21)),"")</f>
+        <v/>
+      </c>
+      <c r="J33" s="41">
+        <f>IF(AND('2 Matériel'!$L21&gt;0,NOT('2 Matériel'!$B21="Oui")),IF(AND(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J21="","",'2 Matériel'!$J21)),"")</f>
+        <v/>
+      </c>
+      <c r="L33" s="42">
         <f>IF(AND('2 Matériel'!$L21&gt;0,'2 Matériel'!$B21="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
-    <row r="32" hidden="1" outlineLevel="1" ht="21" customHeight="1">
-      <c r="B32" s="13">
+    <row r="34" ht="21" customHeight="1">
+      <c r="B34" s="38">
         <f>IF(AND('2 Matériel'!$L22&gt;0,NOT('2 Matériel'!$B22="Oui")),'2 Matériel'!$A22,"")</f>
         <v/>
       </c>
-      <c r="C32" s="37">
-        <f>IF('2 Matériel'!$L22&gt;0,IF('2 Matériel'!$B22="Oui",UPPER('2 Matériel'!$C22),'2 Matériel'!$C22),"")</f>
-        <v/>
-      </c>
-      <c r="D32" s="38">
+      <c r="C34" s="39">
+        <f>IF('2 Matériel'!$L22&gt;0,IF('2 Matériel'!$B22="Oui",UPPER('2 Matériel'!$C22),'2 Matériel'!$C22&amp;IF(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <v/>
+      </c>
+      <c r="D34" s="40">
         <f>IF(AND('2 Matériel'!$L22&gt;0,NOT('2 Matériel'!$B22="Oui")),'2 Matériel'!$L22,"")</f>
         <v/>
       </c>
-      <c r="E32" s="39">
-        <f>IF(AND('2 Matériel'!$L22&gt;0,NOT('2 Matériel'!$B22="Oui")),IF(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E22="","",'2 Matériel'!$E22)),"")</f>
-        <v/>
-      </c>
-      <c r="F32" s="39">
-        <f>IF(AND('2 Matériel'!$L22&gt;0,NOT('2 Matériel'!$B22="Oui")),IF(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F22="","",'2 Matériel'!$F22)),"")</f>
-        <v/>
-      </c>
-      <c r="G32" s="39">
-        <f>IF(AND('2 Matériel'!$L22&gt;0,NOT('2 Matériel'!$B22="Oui")),IF(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G22="","",'2 Matériel'!$G22)),"")</f>
-        <v/>
-      </c>
-      <c r="H32" s="39">
-        <f>IF(AND('2 Matériel'!$L22&gt;0,NOT('2 Matériel'!$B22="Oui")),IF(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H22="","",'2 Matériel'!$H22)),"")</f>
-        <v/>
-      </c>
-      <c r="I32" s="39">
-        <f>IF(AND('2 Matériel'!$L22&gt;0,NOT('2 Matériel'!$B22="Oui")),IF(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I22="","",'2 Matériel'!$I22)),"")</f>
-        <v/>
-      </c>
-      <c r="J32" s="39">
-        <f>IF(AND('2 Matériel'!$L22&gt;0,NOT('2 Matériel'!$B22="Oui")),IF(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J22="","",'2 Matériel'!$J22)),"")</f>
-        <v/>
-      </c>
-      <c r="K32" s="40">
-        <f>IF(AND('2 Matériel'!$L22&gt;0,NOT('2 Matériel'!$B22="Oui")),IF(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
-        <v/>
-      </c>
-      <c r="M32" s="41">
+      <c r="E34" s="41">
+        <f>IF(AND('2 Matériel'!$L22&gt;0,NOT('2 Matériel'!$B22="Oui")),IF(AND(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E22="","",'2 Matériel'!$E22)),"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="41">
+        <f>IF(AND('2 Matériel'!$L22&gt;0,NOT('2 Matériel'!$B22="Oui")),IF(AND(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F22="","",'2 Matériel'!$F22)),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="41">
+        <f>IF(AND('2 Matériel'!$L22&gt;0,NOT('2 Matériel'!$B22="Oui")),IF(AND(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G22="","",'2 Matériel'!$G22)),"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="41">
+        <f>IF(AND('2 Matériel'!$L22&gt;0,NOT('2 Matériel'!$B22="Oui")),IF(AND(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H22="","",'2 Matériel'!$H22)),"")</f>
+        <v/>
+      </c>
+      <c r="I34" s="41">
+        <f>IF(AND('2 Matériel'!$L22&gt;0,NOT('2 Matériel'!$B22="Oui")),IF(AND(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I22="","",'2 Matériel'!$I22)),"")</f>
+        <v/>
+      </c>
+      <c r="J34" s="41">
+        <f>IF(AND('2 Matériel'!$L22&gt;0,NOT('2 Matériel'!$B22="Oui")),IF(AND(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J22="","",'2 Matériel'!$J22)),"")</f>
+        <v/>
+      </c>
+      <c r="L34" s="42">
         <f>IF(AND('2 Matériel'!$L22&gt;0,'2 Matériel'!$B22="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
-    <row r="33" hidden="1" outlineLevel="1" ht="21" customHeight="1">
-      <c r="B33" s="13">
+    <row r="35" ht="21" customHeight="1">
+      <c r="B35" s="38">
         <f>IF(AND('2 Matériel'!$L23&gt;0,NOT('2 Matériel'!$B23="Oui")),'2 Matériel'!$A23,"")</f>
         <v/>
       </c>
-      <c r="C33" s="37">
-        <f>IF('2 Matériel'!$L23&gt;0,IF('2 Matériel'!$B23="Oui",UPPER('2 Matériel'!$C23),'2 Matériel'!$C23),"")</f>
-        <v/>
-      </c>
-      <c r="D33" s="38">
+      <c r="C35" s="39">
+        <f>IF('2 Matériel'!$L23&gt;0,IF('2 Matériel'!$B23="Oui",UPPER('2 Matériel'!$C23),'2 Matériel'!$C23&amp;IF(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <v/>
+      </c>
+      <c r="D35" s="40">
         <f>IF(AND('2 Matériel'!$L23&gt;0,NOT('2 Matériel'!$B23="Oui")),'2 Matériel'!$L23,"")</f>
         <v/>
       </c>
-      <c r="E33" s="39">
-        <f>IF(AND('2 Matériel'!$L23&gt;0,NOT('2 Matériel'!$B23="Oui")),IF(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E23="","",'2 Matériel'!$E23)),"")</f>
-        <v/>
-      </c>
-      <c r="F33" s="39">
-        <f>IF(AND('2 Matériel'!$L23&gt;0,NOT('2 Matériel'!$B23="Oui")),IF(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F23="","",'2 Matériel'!$F23)),"")</f>
-        <v/>
-      </c>
-      <c r="G33" s="39">
-        <f>IF(AND('2 Matériel'!$L23&gt;0,NOT('2 Matériel'!$B23="Oui")),IF(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G23="","",'2 Matériel'!$G23)),"")</f>
-        <v/>
-      </c>
-      <c r="H33" s="39">
-        <f>IF(AND('2 Matériel'!$L23&gt;0,NOT('2 Matériel'!$B23="Oui")),IF(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H23="","",'2 Matériel'!$H23)),"")</f>
-        <v/>
-      </c>
-      <c r="I33" s="39">
-        <f>IF(AND('2 Matériel'!$L23&gt;0,NOT('2 Matériel'!$B23="Oui")),IF(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I23="","",'2 Matériel'!$I23)),"")</f>
-        <v/>
-      </c>
-      <c r="J33" s="39">
-        <f>IF(AND('2 Matériel'!$L23&gt;0,NOT('2 Matériel'!$B23="Oui")),IF(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J23="","",'2 Matériel'!$J23)),"")</f>
-        <v/>
-      </c>
-      <c r="K33" s="40">
-        <f>IF(AND('2 Matériel'!$L23&gt;0,NOT('2 Matériel'!$B23="Oui")),IF(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
-        <v/>
-      </c>
-      <c r="M33" s="41">
+      <c r="E35" s="41">
+        <f>IF(AND('2 Matériel'!$L23&gt;0,NOT('2 Matériel'!$B23="Oui")),IF(AND(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E23="","",'2 Matériel'!$E23)),"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="41">
+        <f>IF(AND('2 Matériel'!$L23&gt;0,NOT('2 Matériel'!$B23="Oui")),IF(AND(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F23="","",'2 Matériel'!$F23)),"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="41">
+        <f>IF(AND('2 Matériel'!$L23&gt;0,NOT('2 Matériel'!$B23="Oui")),IF(AND(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G23="","",'2 Matériel'!$G23)),"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="41">
+        <f>IF(AND('2 Matériel'!$L23&gt;0,NOT('2 Matériel'!$B23="Oui")),IF(AND(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H23="","",'2 Matériel'!$H23)),"")</f>
+        <v/>
+      </c>
+      <c r="I35" s="41">
+        <f>IF(AND('2 Matériel'!$L23&gt;0,NOT('2 Matériel'!$B23="Oui")),IF(AND(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I23="","",'2 Matériel'!$I23)),"")</f>
+        <v/>
+      </c>
+      <c r="J35" s="41">
+        <f>IF(AND('2 Matériel'!$L23&gt;0,NOT('2 Matériel'!$B23="Oui")),IF(AND(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J23="","",'2 Matériel'!$J23)),"")</f>
+        <v/>
+      </c>
+      <c r="L35" s="42">
         <f>IF(AND('2 Matériel'!$L23&gt;0,'2 Matériel'!$B23="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
-    <row r="34" hidden="1" outlineLevel="1" ht="21" customHeight="1">
-      <c r="B34" s="13">
+    <row r="36" hidden="1" outlineLevel="1" ht="21" customHeight="1">
+      <c r="B36" s="38">
         <f>IF(AND('2 Matériel'!$L24&gt;0,NOT('2 Matériel'!$B24="Oui")),'2 Matériel'!$A24,"")</f>
         <v/>
       </c>
-      <c r="C34" s="37">
-        <f>IF('2 Matériel'!$L24&gt;0,IF('2 Matériel'!$B24="Oui",UPPER('2 Matériel'!$C24),'2 Matériel'!$C24),"")</f>
-        <v/>
-      </c>
-      <c r="D34" s="38">
+      <c r="C36" s="39">
+        <f>IF('2 Matériel'!$L24&gt;0,IF('2 Matériel'!$B24="Oui",UPPER('2 Matériel'!$C24),'2 Matériel'!$C24&amp;IF(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <v/>
+      </c>
+      <c r="D36" s="40">
         <f>IF(AND('2 Matériel'!$L24&gt;0,NOT('2 Matériel'!$B24="Oui")),'2 Matériel'!$L24,"")</f>
         <v/>
       </c>
-      <c r="E34" s="39">
-        <f>IF(AND('2 Matériel'!$L24&gt;0,NOT('2 Matériel'!$B24="Oui")),IF(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E24="","",'2 Matériel'!$E24)),"")</f>
-        <v/>
-      </c>
-      <c r="F34" s="39">
-        <f>IF(AND('2 Matériel'!$L24&gt;0,NOT('2 Matériel'!$B24="Oui")),IF(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F24="","",'2 Matériel'!$F24)),"")</f>
-        <v/>
-      </c>
-      <c r="G34" s="39">
-        <f>IF(AND('2 Matériel'!$L24&gt;0,NOT('2 Matériel'!$B24="Oui")),IF(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G24="","",'2 Matériel'!$G24)),"")</f>
-        <v/>
-      </c>
-      <c r="H34" s="39">
-        <f>IF(AND('2 Matériel'!$L24&gt;0,NOT('2 Matériel'!$B24="Oui")),IF(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H24="","",'2 Matériel'!$H24)),"")</f>
-        <v/>
-      </c>
-      <c r="I34" s="39">
-        <f>IF(AND('2 Matériel'!$L24&gt;0,NOT('2 Matériel'!$B24="Oui")),IF(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I24="","",'2 Matériel'!$I24)),"")</f>
-        <v/>
-      </c>
-      <c r="J34" s="39">
-        <f>IF(AND('2 Matériel'!$L24&gt;0,NOT('2 Matériel'!$B24="Oui")),IF(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J24="","",'2 Matériel'!$J24)),"")</f>
-        <v/>
-      </c>
-      <c r="K34" s="40">
-        <f>IF(AND('2 Matériel'!$L24&gt;0,NOT('2 Matériel'!$B24="Oui")),IF(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
-        <v/>
-      </c>
-      <c r="M34" s="41">
+      <c r="E36" s="41">
+        <f>IF(AND('2 Matériel'!$L24&gt;0,NOT('2 Matériel'!$B24="Oui")),IF(AND(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E24="","",'2 Matériel'!$E24)),"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="41">
+        <f>IF(AND('2 Matériel'!$L24&gt;0,NOT('2 Matériel'!$B24="Oui")),IF(AND(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F24="","",'2 Matériel'!$F24)),"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="41">
+        <f>IF(AND('2 Matériel'!$L24&gt;0,NOT('2 Matériel'!$B24="Oui")),IF(AND(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G24="","",'2 Matériel'!$G24)),"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="41">
+        <f>IF(AND('2 Matériel'!$L24&gt;0,NOT('2 Matériel'!$B24="Oui")),IF(AND(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H24="","",'2 Matériel'!$H24)),"")</f>
+        <v/>
+      </c>
+      <c r="I36" s="41">
+        <f>IF(AND('2 Matériel'!$L24&gt;0,NOT('2 Matériel'!$B24="Oui")),IF(AND(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I24="","",'2 Matériel'!$I24)),"")</f>
+        <v/>
+      </c>
+      <c r="J36" s="41">
+        <f>IF(AND('2 Matériel'!$L24&gt;0,NOT('2 Matériel'!$B24="Oui")),IF(AND(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J24="","",'2 Matériel'!$J24)),"")</f>
+        <v/>
+      </c>
+      <c r="L36" s="42">
         <f>IF(AND('2 Matériel'!$L24&gt;0,'2 Matériel'!$B24="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
-    <row r="35" hidden="1" outlineLevel="1" ht="21" customHeight="1">
-      <c r="B35" s="13">
+    <row r="37" hidden="1" outlineLevel="1" ht="21" customHeight="1">
+      <c r="B37" s="38">
         <f>IF(AND('2 Matériel'!$L25&gt;0,NOT('2 Matériel'!$B25="Oui")),'2 Matériel'!$A25,"")</f>
         <v/>
       </c>
-      <c r="C35" s="37">
-        <f>IF('2 Matériel'!$L25&gt;0,IF('2 Matériel'!$B25="Oui",UPPER('2 Matériel'!$C25),'2 Matériel'!$C25),"")</f>
-        <v/>
-      </c>
-      <c r="D35" s="38">
+      <c r="C37" s="39">
+        <f>IF('2 Matériel'!$L25&gt;0,IF('2 Matériel'!$B25="Oui",UPPER('2 Matériel'!$C25),'2 Matériel'!$C25&amp;IF(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <v/>
+      </c>
+      <c r="D37" s="40">
         <f>IF(AND('2 Matériel'!$L25&gt;0,NOT('2 Matériel'!$B25="Oui")),'2 Matériel'!$L25,"")</f>
         <v/>
       </c>
-      <c r="E35" s="39">
-        <f>IF(AND('2 Matériel'!$L25&gt;0,NOT('2 Matériel'!$B25="Oui")),IF(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E25="","",'2 Matériel'!$E25)),"")</f>
-        <v/>
-      </c>
-      <c r="F35" s="39">
-        <f>IF(AND('2 Matériel'!$L25&gt;0,NOT('2 Matériel'!$B25="Oui")),IF(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F25="","",'2 Matériel'!$F25)),"")</f>
-        <v/>
-      </c>
-      <c r="G35" s="39">
-        <f>IF(AND('2 Matériel'!$L25&gt;0,NOT('2 Matériel'!$B25="Oui")),IF(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G25="","",'2 Matériel'!$G25)),"")</f>
-        <v/>
-      </c>
-      <c r="H35" s="39">
-        <f>IF(AND('2 Matériel'!$L25&gt;0,NOT('2 Matériel'!$B25="Oui")),IF(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H25="","",'2 Matériel'!$H25)),"")</f>
-        <v/>
-      </c>
-      <c r="I35" s="39">
-        <f>IF(AND('2 Matériel'!$L25&gt;0,NOT('2 Matériel'!$B25="Oui")),IF(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I25="","",'2 Matériel'!$I25)),"")</f>
-        <v/>
-      </c>
-      <c r="J35" s="39">
-        <f>IF(AND('2 Matériel'!$L25&gt;0,NOT('2 Matériel'!$B25="Oui")),IF(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J25="","",'2 Matériel'!$J25)),"")</f>
-        <v/>
-      </c>
-      <c r="K35" s="40">
-        <f>IF(AND('2 Matériel'!$L25&gt;0,NOT('2 Matériel'!$B25="Oui")),IF(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
-        <v/>
-      </c>
-      <c r="M35" s="41">
+      <c r="E37" s="41">
+        <f>IF(AND('2 Matériel'!$L25&gt;0,NOT('2 Matériel'!$B25="Oui")),IF(AND(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E25="","",'2 Matériel'!$E25)),"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="41">
+        <f>IF(AND('2 Matériel'!$L25&gt;0,NOT('2 Matériel'!$B25="Oui")),IF(AND(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F25="","",'2 Matériel'!$F25)),"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="41">
+        <f>IF(AND('2 Matériel'!$L25&gt;0,NOT('2 Matériel'!$B25="Oui")),IF(AND(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G25="","",'2 Matériel'!$G25)),"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="41">
+        <f>IF(AND('2 Matériel'!$L25&gt;0,NOT('2 Matériel'!$B25="Oui")),IF(AND(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H25="","",'2 Matériel'!$H25)),"")</f>
+        <v/>
+      </c>
+      <c r="I37" s="41">
+        <f>IF(AND('2 Matériel'!$L25&gt;0,NOT('2 Matériel'!$B25="Oui")),IF(AND(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I25="","",'2 Matériel'!$I25)),"")</f>
+        <v/>
+      </c>
+      <c r="J37" s="41">
+        <f>IF(AND('2 Matériel'!$L25&gt;0,NOT('2 Matériel'!$B25="Oui")),IF(AND(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J25="","",'2 Matériel'!$J25)),"")</f>
+        <v/>
+      </c>
+      <c r="L37" s="42">
         <f>IF(AND('2 Matériel'!$L25&gt;0,'2 Matériel'!$B25="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
-    <row r="36" hidden="1" outlineLevel="1" ht="21" customHeight="1">
-      <c r="B36" s="13">
+    <row r="38" hidden="1" outlineLevel="1" ht="21" customHeight="1">
+      <c r="B38" s="38">
         <f>IF(AND('2 Matériel'!$L26&gt;0,NOT('2 Matériel'!$B26="Oui")),'2 Matériel'!$A26,"")</f>
         <v/>
       </c>
-      <c r="C36" s="37">
-        <f>IF('2 Matériel'!$L26&gt;0,IF('2 Matériel'!$B26="Oui",UPPER('2 Matériel'!$C26),'2 Matériel'!$C26),"")</f>
-        <v/>
-      </c>
-      <c r="D36" s="38">
+      <c r="C38" s="39">
+        <f>IF('2 Matériel'!$L26&gt;0,IF('2 Matériel'!$B26="Oui",UPPER('2 Matériel'!$C26),'2 Matériel'!$C26&amp;IF(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <v/>
+      </c>
+      <c r="D38" s="40">
         <f>IF(AND('2 Matériel'!$L26&gt;0,NOT('2 Matériel'!$B26="Oui")),'2 Matériel'!$L26,"")</f>
         <v/>
       </c>
-      <c r="E36" s="39">
-        <f>IF(AND('2 Matériel'!$L26&gt;0,NOT('2 Matériel'!$B26="Oui")),IF(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E26="","",'2 Matériel'!$E26)),"")</f>
-        <v/>
-      </c>
-      <c r="F36" s="39">
-        <f>IF(AND('2 Matériel'!$L26&gt;0,NOT('2 Matériel'!$B26="Oui")),IF(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F26="","",'2 Matériel'!$F26)),"")</f>
-        <v/>
-      </c>
-      <c r="G36" s="39">
-        <f>IF(AND('2 Matériel'!$L26&gt;0,NOT('2 Matériel'!$B26="Oui")),IF(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G26="","",'2 Matériel'!$G26)),"")</f>
-        <v/>
-      </c>
-      <c r="H36" s="39">
-        <f>IF(AND('2 Matériel'!$L26&gt;0,NOT('2 Matériel'!$B26="Oui")),IF(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H26="","",'2 Matériel'!$H26)),"")</f>
-        <v/>
-      </c>
-      <c r="I36" s="39">
-        <f>IF(AND('2 Matériel'!$L26&gt;0,NOT('2 Matériel'!$B26="Oui")),IF(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I26="","",'2 Matériel'!$I26)),"")</f>
-        <v/>
-      </c>
-      <c r="J36" s="39">
-        <f>IF(AND('2 Matériel'!$L26&gt;0,NOT('2 Matériel'!$B26="Oui")),IF(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J26="","",'2 Matériel'!$J26)),"")</f>
-        <v/>
-      </c>
-      <c r="K36" s="40">
-        <f>IF(AND('2 Matériel'!$L26&gt;0,NOT('2 Matériel'!$B26="Oui")),IF(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
-        <v/>
-      </c>
-      <c r="M36" s="41">
+      <c r="E38" s="41">
+        <f>IF(AND('2 Matériel'!$L26&gt;0,NOT('2 Matériel'!$B26="Oui")),IF(AND(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E26="","",'2 Matériel'!$E26)),"")</f>
+        <v/>
+      </c>
+      <c r="F38" s="41">
+        <f>IF(AND('2 Matériel'!$L26&gt;0,NOT('2 Matériel'!$B26="Oui")),IF(AND(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F26="","",'2 Matériel'!$F26)),"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="41">
+        <f>IF(AND('2 Matériel'!$L26&gt;0,NOT('2 Matériel'!$B26="Oui")),IF(AND(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G26="","",'2 Matériel'!$G26)),"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="41">
+        <f>IF(AND('2 Matériel'!$L26&gt;0,NOT('2 Matériel'!$B26="Oui")),IF(AND(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H26="","",'2 Matériel'!$H26)),"")</f>
+        <v/>
+      </c>
+      <c r="I38" s="41">
+        <f>IF(AND('2 Matériel'!$L26&gt;0,NOT('2 Matériel'!$B26="Oui")),IF(AND(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I26="","",'2 Matériel'!$I26)),"")</f>
+        <v/>
+      </c>
+      <c r="J38" s="41">
+        <f>IF(AND('2 Matériel'!$L26&gt;0,NOT('2 Matériel'!$B26="Oui")),IF(AND(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J26="","",'2 Matériel'!$J26)),"")</f>
+        <v/>
+      </c>
+      <c r="L38" s="42">
         <f>IF(AND('2 Matériel'!$L26&gt;0,'2 Matériel'!$B26="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
-    <row r="37" hidden="1" outlineLevel="1" ht="21" customHeight="1">
-      <c r="B37" s="13">
+    <row r="39" hidden="1" outlineLevel="1" ht="21" customHeight="1">
+      <c r="B39" s="38">
         <f>IF(AND('2 Matériel'!$L27&gt;0,NOT('2 Matériel'!$B27="Oui")),'2 Matériel'!$A27,"")</f>
         <v/>
       </c>
-      <c r="C37" s="37">
-        <f>IF('2 Matériel'!$L27&gt;0,IF('2 Matériel'!$B27="Oui",UPPER('2 Matériel'!$C27),'2 Matériel'!$C27),"")</f>
-        <v/>
-      </c>
-      <c r="D37" s="38">
+      <c r="C39" s="39">
+        <f>IF('2 Matériel'!$L27&gt;0,IF('2 Matériel'!$B27="Oui",UPPER('2 Matériel'!$C27),'2 Matériel'!$C27&amp;IF(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <v/>
+      </c>
+      <c r="D39" s="40">
         <f>IF(AND('2 Matériel'!$L27&gt;0,NOT('2 Matériel'!$B27="Oui")),'2 Matériel'!$L27,"")</f>
         <v/>
       </c>
-      <c r="E37" s="39">
-        <f>IF(AND('2 Matériel'!$L27&gt;0,NOT('2 Matériel'!$B27="Oui")),IF(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E27="","",'2 Matériel'!$E27)),"")</f>
-        <v/>
-      </c>
-      <c r="F37" s="39">
-        <f>IF(AND('2 Matériel'!$L27&gt;0,NOT('2 Matériel'!$B27="Oui")),IF(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F27="","",'2 Matériel'!$F27)),"")</f>
-        <v/>
-      </c>
-      <c r="G37" s="39">
-        <f>IF(AND('2 Matériel'!$L27&gt;0,NOT('2 Matériel'!$B27="Oui")),IF(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G27="","",'2 Matériel'!$G27)),"")</f>
-        <v/>
-      </c>
-      <c r="H37" s="39">
-        <f>IF(AND('2 Matériel'!$L27&gt;0,NOT('2 Matériel'!$B27="Oui")),IF(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H27="","",'2 Matériel'!$H27)),"")</f>
-        <v/>
-      </c>
-      <c r="I37" s="39">
-        <f>IF(AND('2 Matériel'!$L27&gt;0,NOT('2 Matériel'!$B27="Oui")),IF(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I27="","",'2 Matériel'!$I27)),"")</f>
-        <v/>
-      </c>
-      <c r="J37" s="39">
-        <f>IF(AND('2 Matériel'!$L27&gt;0,NOT('2 Matériel'!$B27="Oui")),IF(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J27="","",'2 Matériel'!$J27)),"")</f>
-        <v/>
-      </c>
-      <c r="K37" s="40">
-        <f>IF(AND('2 Matériel'!$L27&gt;0,NOT('2 Matériel'!$B27="Oui")),IF(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
-        <v/>
-      </c>
-      <c r="M37" s="41">
+      <c r="E39" s="41">
+        <f>IF(AND('2 Matériel'!$L27&gt;0,NOT('2 Matériel'!$B27="Oui")),IF(AND(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E27="","",'2 Matériel'!$E27)),"")</f>
+        <v/>
+      </c>
+      <c r="F39" s="41">
+        <f>IF(AND('2 Matériel'!$L27&gt;0,NOT('2 Matériel'!$B27="Oui")),IF(AND(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F27="","",'2 Matériel'!$F27)),"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="41">
+        <f>IF(AND('2 Matériel'!$L27&gt;0,NOT('2 Matériel'!$B27="Oui")),IF(AND(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G27="","",'2 Matériel'!$G27)),"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="41">
+        <f>IF(AND('2 Matériel'!$L27&gt;0,NOT('2 Matériel'!$B27="Oui")),IF(AND(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H27="","",'2 Matériel'!$H27)),"")</f>
+        <v/>
+      </c>
+      <c r="I39" s="41">
+        <f>IF(AND('2 Matériel'!$L27&gt;0,NOT('2 Matériel'!$B27="Oui")),IF(AND(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I27="","",'2 Matériel'!$I27)),"")</f>
+        <v/>
+      </c>
+      <c r="J39" s="41">
+        <f>IF(AND('2 Matériel'!$L27&gt;0,NOT('2 Matériel'!$B27="Oui")),IF(AND(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J27="","",'2 Matériel'!$J27)),"")</f>
+        <v/>
+      </c>
+      <c r="L39" s="42">
         <f>IF(AND('2 Matériel'!$L27&gt;0,'2 Matériel'!$B27="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
-    <row r="38" hidden="1" outlineLevel="1" ht="21" customHeight="1">
-      <c r="B38" s="13">
+    <row r="40" hidden="1" outlineLevel="1" ht="21" customHeight="1">
+      <c r="B40" s="38">
         <f>IF(AND('2 Matériel'!$L28&gt;0,NOT('2 Matériel'!$B28="Oui")),'2 Matériel'!$A28,"")</f>
         <v/>
       </c>
-      <c r="C38" s="37">
-        <f>IF('2 Matériel'!$L28&gt;0,IF('2 Matériel'!$B28="Oui",UPPER('2 Matériel'!$C28),'2 Matériel'!$C28),"")</f>
-        <v/>
-      </c>
-      <c r="D38" s="38">
+      <c r="C40" s="39">
+        <f>IF('2 Matériel'!$L28&gt;0,IF('2 Matériel'!$B28="Oui",UPPER('2 Matériel'!$C28),'2 Matériel'!$C28&amp;IF(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <v/>
+      </c>
+      <c r="D40" s="40">
         <f>IF(AND('2 Matériel'!$L28&gt;0,NOT('2 Matériel'!$B28="Oui")),'2 Matériel'!$L28,"")</f>
         <v/>
       </c>
-      <c r="E38" s="39">
-        <f>IF(AND('2 Matériel'!$L28&gt;0,NOT('2 Matériel'!$B28="Oui")),IF(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E28="","",'2 Matériel'!$E28)),"")</f>
-        <v/>
-      </c>
-      <c r="F38" s="39">
-        <f>IF(AND('2 Matériel'!$L28&gt;0,NOT('2 Matériel'!$B28="Oui")),IF(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F28="","",'2 Matériel'!$F28)),"")</f>
-        <v/>
-      </c>
-      <c r="G38" s="39">
-        <f>IF(AND('2 Matériel'!$L28&gt;0,NOT('2 Matériel'!$B28="Oui")),IF(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G28="","",'2 Matériel'!$G28)),"")</f>
-        <v/>
-      </c>
-      <c r="H38" s="39">
-        <f>IF(AND('2 Matériel'!$L28&gt;0,NOT('2 Matériel'!$B28="Oui")),IF(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H28="","",'2 Matériel'!$H28)),"")</f>
-        <v/>
-      </c>
-      <c r="I38" s="39">
-        <f>IF(AND('2 Matériel'!$L28&gt;0,NOT('2 Matériel'!$B28="Oui")),IF(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I28="","",'2 Matériel'!$I28)),"")</f>
-        <v/>
-      </c>
-      <c r="J38" s="39">
-        <f>IF(AND('2 Matériel'!$L28&gt;0,NOT('2 Matériel'!$B28="Oui")),IF(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J28="","",'2 Matériel'!$J28)),"")</f>
-        <v/>
-      </c>
-      <c r="K38" s="40">
-        <f>IF(AND('2 Matériel'!$L28&gt;0,NOT('2 Matériel'!$B28="Oui")),IF(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
-        <v/>
-      </c>
-      <c r="M38" s="41">
+      <c r="E40" s="41">
+        <f>IF(AND('2 Matériel'!$L28&gt;0,NOT('2 Matériel'!$B28="Oui")),IF(AND(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E28="","",'2 Matériel'!$E28)),"")</f>
+        <v/>
+      </c>
+      <c r="F40" s="41">
+        <f>IF(AND('2 Matériel'!$L28&gt;0,NOT('2 Matériel'!$B28="Oui")),IF(AND(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F28="","",'2 Matériel'!$F28)),"")</f>
+        <v/>
+      </c>
+      <c r="G40" s="41">
+        <f>IF(AND('2 Matériel'!$L28&gt;0,NOT('2 Matériel'!$B28="Oui")),IF(AND(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G28="","",'2 Matériel'!$G28)),"")</f>
+        <v/>
+      </c>
+      <c r="H40" s="41">
+        <f>IF(AND('2 Matériel'!$L28&gt;0,NOT('2 Matériel'!$B28="Oui")),IF(AND(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H28="","",'2 Matériel'!$H28)),"")</f>
+        <v/>
+      </c>
+      <c r="I40" s="41">
+        <f>IF(AND('2 Matériel'!$L28&gt;0,NOT('2 Matériel'!$B28="Oui")),IF(AND(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I28="","",'2 Matériel'!$I28)),"")</f>
+        <v/>
+      </c>
+      <c r="J40" s="41">
+        <f>IF(AND('2 Matériel'!$L28&gt;0,NOT('2 Matériel'!$B28="Oui")),IF(AND(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J28="","",'2 Matériel'!$J28)),"")</f>
+        <v/>
+      </c>
+      <c r="L40" s="42">
         <f>IF(AND('2 Matériel'!$L28&gt;0,'2 Matériel'!$B28="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
-    <row r="39" hidden="1" outlineLevel="1" ht="21" customHeight="1">
-      <c r="B39" s="13">
+    <row r="41" hidden="1" outlineLevel="1" ht="21" customHeight="1">
+      <c r="B41" s="38">
         <f>IF(AND('2 Matériel'!$L29&gt;0,NOT('2 Matériel'!$B29="Oui")),'2 Matériel'!$A29,"")</f>
         <v/>
       </c>
-      <c r="C39" s="37">
-        <f>IF('2 Matériel'!$L29&gt;0,IF('2 Matériel'!$B29="Oui",UPPER('2 Matériel'!$C29),'2 Matériel'!$C29),"")</f>
-        <v/>
-      </c>
-      <c r="D39" s="38">
+      <c r="C41" s="39">
+        <f>IF('2 Matériel'!$L29&gt;0,IF('2 Matériel'!$B29="Oui",UPPER('2 Matériel'!$C29),'2 Matériel'!$C29&amp;IF(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <v/>
+      </c>
+      <c r="D41" s="40">
         <f>IF(AND('2 Matériel'!$L29&gt;0,NOT('2 Matériel'!$B29="Oui")),'2 Matériel'!$L29,"")</f>
         <v/>
       </c>
-      <c r="E39" s="39">
-        <f>IF(AND('2 Matériel'!$L29&gt;0,NOT('2 Matériel'!$B29="Oui")),IF(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E29="","",'2 Matériel'!$E29)),"")</f>
-        <v/>
-      </c>
-      <c r="F39" s="39">
-        <f>IF(AND('2 Matériel'!$L29&gt;0,NOT('2 Matériel'!$B29="Oui")),IF(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F29="","",'2 Matériel'!$F29)),"")</f>
-        <v/>
-      </c>
-      <c r="G39" s="39">
-        <f>IF(AND('2 Matériel'!$L29&gt;0,NOT('2 Matériel'!$B29="Oui")),IF(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G29="","",'2 Matériel'!$G29)),"")</f>
-        <v/>
-      </c>
-      <c r="H39" s="39">
-        <f>IF(AND('2 Matériel'!$L29&gt;0,NOT('2 Matériel'!$B29="Oui")),IF(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H29="","",'2 Matériel'!$H29)),"")</f>
-        <v/>
-      </c>
-      <c r="I39" s="39">
-        <f>IF(AND('2 Matériel'!$L29&gt;0,NOT('2 Matériel'!$B29="Oui")),IF(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I29="","",'2 Matériel'!$I29)),"")</f>
-        <v/>
-      </c>
-      <c r="J39" s="39">
-        <f>IF(AND('2 Matériel'!$L29&gt;0,NOT('2 Matériel'!$B29="Oui")),IF(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J29="","",'2 Matériel'!$J29)),"")</f>
-        <v/>
-      </c>
-      <c r="K39" s="40">
-        <f>IF(AND('2 Matériel'!$L29&gt;0,NOT('2 Matériel'!$B29="Oui")),IF(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),"")</f>
-        <v/>
-      </c>
-      <c r="M39" s="41">
+      <c r="E41" s="41">
+        <f>IF(AND('2 Matériel'!$L29&gt;0,NOT('2 Matériel'!$B29="Oui")),IF(AND(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E29="","",'2 Matériel'!$E29)),"")</f>
+        <v/>
+      </c>
+      <c r="F41" s="41">
+        <f>IF(AND('2 Matériel'!$L29&gt;0,NOT('2 Matériel'!$B29="Oui")),IF(AND(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F29="","",'2 Matériel'!$F29)),"")</f>
+        <v/>
+      </c>
+      <c r="G41" s="41">
+        <f>IF(AND('2 Matériel'!$L29&gt;0,NOT('2 Matériel'!$B29="Oui")),IF(AND(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G29="","",'2 Matériel'!$G29)),"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="41">
+        <f>IF(AND('2 Matériel'!$L29&gt;0,NOT('2 Matériel'!$B29="Oui")),IF(AND(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H29="","",'2 Matériel'!$H29)),"")</f>
+        <v/>
+      </c>
+      <c r="I41" s="41">
+        <f>IF(AND('2 Matériel'!$L29&gt;0,NOT('2 Matériel'!$B29="Oui")),IF(AND(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I29="","",'2 Matériel'!$I29)),"")</f>
+        <v/>
+      </c>
+      <c r="J41" s="41">
+        <f>IF(AND('2 Matériel'!$L29&gt;0,NOT('2 Matériel'!$B29="Oui")),IF(AND(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J29="","",'2 Matériel'!$J29)),"")</f>
+        <v/>
+      </c>
+      <c r="L41" s="42">
         <f>IF(AND('2 Matériel'!$L29&gt;0,'2 Matériel'!$B29="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="B40" s="42">
-        <f>IF(SUM('2 Matériel'!$L$20:$L$29)&gt;0,"⚠  Des lignes de matériel au-delà de la ligne 14 sont masquées : cliquer sur le [+] dans la marge gauche pour les afficher.","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="8" customHeight="1"/>
-    <row r="42" ht="20" customHeight="1">
+    <row r="42" ht="18" customHeight="1">
       <c r="B42" s="43">
+        <f>IF(SUM('2 Matériel'!$L$24:$L$29)&gt;0,"⚠  Des lignes de matériel au-delà de la ligne 18 sont masquées : cliquer sur le [+] dans la marge gauche pour les afficher.","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="8" customHeight="1"/>
+    <row r="44" ht="20" customHeight="1">
+      <c r="B44" s="44">
         <f>IF('3 Options'!$C$8="Oui",INDEX(Textes!$B$2:$C$55,MATCH("sec_tight",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
         <v/>
       </c>
-      <c r="C42" s="44" t="n"/>
-      <c r="D42" s="44">
+      <c r="C44" s="45" t="n"/>
+      <c r="D44" s="45">
         <f>IF('3 Options'!$C$8="Oui",INDEX(Textes!$B$2:$C$55,MATCH("h_qty",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
         <v/>
       </c>
-      <c r="E42" s="44">
+      <c r="E44" s="46">
         <f>IF('3 Options'!$C$8="Oui",INDEX(Textes!$B$2:$C$55,MATCH("h_unit",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
         <v/>
       </c>
-      <c r="F42" s="44">
+      <c r="F44" s="46">
         <f>IF('3 Options'!$C$8="Oui",INDEX(Textes!$B$2:$C$55,MATCH("h_pu",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
         <v/>
       </c>
-      <c r="G42" s="44">
+      <c r="G44" s="45">
         <f>IF('3 Options'!$C$8="Oui",INDEX(Textes!$B$2:$C$55,MATCH("h_tot",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
         <v/>
       </c>
-      <c r="H42" s="43">
+      <c r="H44" s="44">
         <f>IF('3 Options'!$C$8="Oui",INDEX(Textes!$B$2:$C$55,MATCH("h_det",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
         <v/>
       </c>
-      <c r="M42" s="41">
+      <c r="I44" s="45" t="n"/>
+      <c r="J44" s="45" t="n"/>
+      <c r="L44" s="42">
         <f>IF('3 Options'!$C$8="Oui",1,0)</f>
         <v/>
       </c>
     </row>
-    <row r="43" ht="21" customHeight="1">
-      <c r="C43" s="45">
+    <row r="45" ht="21" customHeight="1">
+      <c r="C45" s="47">
         <f>IF('3 Options'!$C$8="Oui",IF('3 Options'!$D$8&lt;&gt;"",'3 Options'!$D$8,INDEX(Textes!$B$2:$C$55,MATCH("tight",Textes!$A$2:$A$55,0),Listes!$H$1)),"")</f>
         <v/>
       </c>
-      <c r="D43" s="38">
+      <c r="D45" s="48">
         <f>IF('3 Options'!$C$8="Oui",IF('3 Options'!$G$8="Coût réel +15 %","",'3 Options'!$E$8),"")</f>
         <v/>
       </c>
-      <c r="E43" s="38">
+      <c r="E45" s="49">
         <f>IF('3 Options'!$C$8="Oui",IF('3 Options'!$G$8="Coût réel +15 %","",'3 Options'!$G$8),"")</f>
         <v/>
       </c>
-      <c r="F43" s="39">
+      <c r="F45" s="50">
         <f>IF('3 Options'!$C$8="Oui",IF('3 Options'!$G$8="Coût réel +15 %",INDEX(Textes!$B$2:$C$55,MATCH("at_cost",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$F$8="","",'3 Options'!$F$8)),"")</f>
         <v/>
       </c>
-      <c r="G43" s="46">
+      <c r="G45" s="51">
         <f>IF('3 Options'!$C$8="Oui",IF('3 Options'!$G$8="Coût réel +15 %","—",'3 Options'!$H$8),"")</f>
         <v/>
       </c>
-      <c r="H43" s="47">
+      <c r="H45" s="52">
         <f>""</f>
         <v/>
       </c>
     </row>
-    <row r="44" ht="8" customHeight="1"/>
-    <row r="45" ht="20" customHeight="1">
-      <c r="B45" s="43">
+    <row r="46" ht="8" customHeight="1"/>
+    <row r="47" ht="20" customHeight="1">
+      <c r="B47" s="44">
         <f>IF(OR('3 Options'!$C$9="Oui",'3 Options'!$C$10="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("sec_tr",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
         <v/>
       </c>
-      <c r="C45" s="44" t="n"/>
-      <c r="D45" s="44">
+      <c r="C47" s="45" t="n"/>
+      <c r="D47" s="45">
         <f>IF(OR('3 Options'!$C$9="Oui",'3 Options'!$C$10="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("h_qty",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
         <v/>
       </c>
-      <c r="E45" s="44">
+      <c r="E47" s="46">
         <f>IF(OR('3 Options'!$C$9="Oui",'3 Options'!$C$10="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("h_unit",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
         <v/>
       </c>
-      <c r="F45" s="44">
+      <c r="F47" s="46">
         <f>IF(OR('3 Options'!$C$9="Oui",'3 Options'!$C$10="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("h_pu",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
         <v/>
       </c>
-      <c r="G45" s="44">
+      <c r="G47" s="45">
         <f>IF(OR('3 Options'!$C$9="Oui",'3 Options'!$C$10="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("h_tot",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
         <v/>
       </c>
-      <c r="H45" s="43">
+      <c r="H47" s="44">
         <f>IF(OR('3 Options'!$C$9="Oui",'3 Options'!$C$10="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("h_det",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
         <v/>
       </c>
-      <c r="M45" s="41">
+      <c r="I47" s="45" t="n"/>
+      <c r="J47" s="45" t="n"/>
+      <c r="L47" s="42">
         <f>IF(OR('3 Options'!$C$9="Oui",'3 Options'!$C$10="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
-    <row r="46" ht="21" customHeight="1">
-      <c r="C46" s="45">
+    <row r="48" ht="21" customHeight="1">
+      <c r="C48" s="47">
         <f>IF('3 Options'!$C$9="Oui",IF('3 Options'!$D$9&lt;&gt;"",'3 Options'!$D$9,INDEX(Textes!$B$2:$C$55,MATCH("tr_mob",Textes!$A$2:$A$55,0),Listes!$H$1)),"")</f>
         <v/>
       </c>
-      <c r="D46" s="38">
+      <c r="D48" s="48">
         <f>IF('3 Options'!$C$9="Oui",IF('3 Options'!$G$9="Coût réel +15 %","",'3 Options'!$E$9),"")</f>
         <v/>
       </c>
-      <c r="E46" s="38">
+      <c r="E48" s="49">
         <f>IF('3 Options'!$C$9="Oui",IF('3 Options'!$G$9="Coût réel +15 %","",'3 Options'!$G$9),"")</f>
         <v/>
       </c>
-      <c r="F46" s="39">
+      <c r="F48" s="50">
         <f>IF('3 Options'!$C$9="Oui",IF('3 Options'!$G$9="Coût réel +15 %",INDEX(Textes!$B$2:$C$55,MATCH("at_cost",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$F$9="","",'3 Options'!$F$9)),"")</f>
         <v/>
       </c>
-      <c r="G46" s="46">
+      <c r="G48" s="51">
         <f>IF('3 Options'!$C$9="Oui",IF('3 Options'!$G$9="Coût réel +15 %","—",'3 Options'!$H$9),"")</f>
         <v/>
       </c>
-      <c r="H46" s="47">
+      <c r="H48" s="52">
         <f>IF('3 Options'!$C$9="Oui",INDEX(Textes!$B$2:$C$55,MATCH("tr_note",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
         <v/>
       </c>
     </row>
-    <row r="47" ht="21" customHeight="1">
-      <c r="C47" s="45">
+    <row r="49" ht="21" customHeight="1">
+      <c r="C49" s="47">
         <f>IF('3 Options'!$C$10="Oui",IF('3 Options'!$D$10&lt;&gt;"",'3 Options'!$D$10,INDEX(Textes!$B$2:$C$55,MATCH("tr_dem",Textes!$A$2:$A$55,0),Listes!$H$1)),"")</f>
         <v/>
       </c>
-      <c r="D47" s="38">
+      <c r="D49" s="48">
         <f>IF('3 Options'!$C$10="Oui",IF('3 Options'!$G$10="Coût réel +15 %","",'3 Options'!$E$10),"")</f>
         <v/>
       </c>
-      <c r="E47" s="38">
+      <c r="E49" s="49">
         <f>IF('3 Options'!$C$10="Oui",IF('3 Options'!$G$10="Coût réel +15 %","",'3 Options'!$G$10),"")</f>
         <v/>
       </c>
-      <c r="F47" s="39">
+      <c r="F49" s="50">
         <f>IF('3 Options'!$C$10="Oui",IF('3 Options'!$G$10="Coût réel +15 %",INDEX(Textes!$B$2:$C$55,MATCH("at_cost",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$F$10="","",'3 Options'!$F$10)),"")</f>
         <v/>
       </c>
-      <c r="G47" s="46">
+      <c r="G49" s="51">
         <f>IF('3 Options'!$C$10="Oui",IF('3 Options'!$G$10="Coût réel +15 %","—",'3 Options'!$H$10),"")</f>
         <v/>
       </c>
-      <c r="H47" s="47">
+      <c r="H49" s="52">
         <f>IF('3 Options'!$C$10="Oui",INDEX(Textes!$B$2:$C$55,MATCH("tr_note",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
         <v/>
       </c>
     </row>
-    <row r="48" ht="8" customHeight="1"/>
-    <row r="49" ht="20" customHeight="1">
-      <c r="B49" s="43">
+    <row r="50" ht="8" customHeight="1"/>
+    <row r="51" ht="20" customHeight="1">
+      <c r="B51" s="44">
         <f>IF(OR('3 Options'!$C$6="Oui",'3 Options'!$C$7="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("sec_op",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
         <v/>
       </c>
-      <c r="C49" s="44" t="n"/>
-      <c r="D49" s="44">
+      <c r="C51" s="45" t="n"/>
+      <c r="D51" s="45">
         <f>IF(OR('3 Options'!$C$6="Oui",'3 Options'!$C$7="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("h_qty",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
         <v/>
       </c>
-      <c r="E49" s="44">
+      <c r="E51" s="46">
         <f>IF(OR('3 Options'!$C$6="Oui",'3 Options'!$C$7="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("h_unit",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
         <v/>
       </c>
-      <c r="F49" s="44">
+      <c r="F51" s="46">
         <f>IF(OR('3 Options'!$C$6="Oui",'3 Options'!$C$7="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("h_pu",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
         <v/>
       </c>
-      <c r="G49" s="44">
+      <c r="G51" s="45">
         <f>IF(OR('3 Options'!$C$6="Oui",'3 Options'!$C$7="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("h_tot",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
         <v/>
       </c>
-      <c r="H49" s="43">
+      <c r="H51" s="44">
         <f>IF(OR('3 Options'!$C$6="Oui",'3 Options'!$C$7="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("h_det",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
         <v/>
       </c>
-      <c r="M49" s="41">
+      <c r="I51" s="45" t="n"/>
+      <c r="J51" s="45" t="n"/>
+      <c r="L51" s="42">
         <f>IF(OR('3 Options'!$C$6="Oui",'3 Options'!$C$7="Oui"),1,0)</f>
         <v/>
       </c>
     </row>
-    <row r="50" ht="21" customHeight="1">
-      <c r="C50" s="45">
+    <row r="52" ht="21" customHeight="1">
+      <c r="C52" s="47">
         <f>IF('3 Options'!$C$6="Oui",IF('3 Options'!$D$6&lt;&gt;"",'3 Options'!$D$6,INDEX(Textes!$B$2:$C$55,MATCH("op_day",Textes!$A$2:$A$55,0),Listes!$H$1)),"")</f>
         <v/>
       </c>
-      <c r="D50" s="38">
+      <c r="D52" s="48">
         <f>IF('3 Options'!$C$6="Oui",IF('3 Options'!$G$6="Coût réel +15 %","",'3 Options'!$E$6),"")</f>
         <v/>
       </c>
-      <c r="E50" s="38">
+      <c r="E52" s="49">
         <f>IF('3 Options'!$C$6="Oui",IF('3 Options'!$G$6="Coût réel +15 %","",'3 Options'!$G$6),"")</f>
         <v/>
       </c>
-      <c r="F50" s="39">
+      <c r="F52" s="50">
         <f>IF('3 Options'!$C$6="Oui",IF('3 Options'!$G$6="Coût réel +15 %",INDEX(Textes!$B$2:$C$55,MATCH("at_cost",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$F$6="","",'3 Options'!$F$6)),"")</f>
         <v/>
       </c>
-      <c r="G50" s="46">
+      <c r="G52" s="51">
         <f>IF('3 Options'!$C$6="Oui",IF('3 Options'!$G$6="Coût réel +15 %","—",'3 Options'!$H$6),"")</f>
         <v/>
       </c>
-      <c r="H50" s="47">
+      <c r="H52" s="52">
         <f>""</f>
         <v/>
       </c>
     </row>
-    <row r="51" ht="21" customHeight="1">
-      <c r="C51" s="45">
+    <row r="53" ht="21" customHeight="1">
+      <c r="C53" s="47">
         <f>IF('3 Options'!$C$7="Oui",IF('3 Options'!$D$7&lt;&gt;"",'3 Options'!$D$7,INDEX(Textes!$B$2:$C$55,MATCH("op_mob",Textes!$A$2:$A$55,0),Listes!$H$1)),"")</f>
         <v/>
       </c>
-      <c r="D51" s="38">
+      <c r="D53" s="48">
         <f>IF('3 Options'!$C$7="Oui",IF('3 Options'!$G$7="Coût réel +15 %","",'3 Options'!$E$7),"")</f>
         <v/>
       </c>
-      <c r="E51" s="38">
+      <c r="E53" s="49">
         <f>IF('3 Options'!$C$7="Oui",IF('3 Options'!$G$7="Coût réel +15 %","",'3 Options'!$G$7),"")</f>
         <v/>
       </c>
-      <c r="F51" s="39">
+      <c r="F53" s="50">
         <f>IF('3 Options'!$C$7="Oui",IF('3 Options'!$G$7="Coût réel +15 %",INDEX(Textes!$B$2:$C$55,MATCH("at_cost",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$F$7="","",'3 Options'!$F$7)),"")</f>
         <v/>
       </c>
-      <c r="G51" s="46">
+      <c r="G53" s="51">
         <f>IF('3 Options'!$C$7="Oui",IF('3 Options'!$G$7="Coût réel +15 %","—",'3 Options'!$H$7),"")</f>
         <v/>
       </c>
-      <c r="H51" s="47">
+      <c r="H53" s="52">
         <f>""</f>
         <v/>
       </c>
     </row>
-    <row r="52" ht="8" customHeight="1"/>
-    <row r="53" ht="40" customHeight="1">
-      <c r="B53" s="48">
+    <row r="54" ht="8" customHeight="1"/>
+    <row r="55" ht="42" customHeight="1">
+      <c r="B55" s="53">
         <f>IF('3 Options'!$C$13="Oui",UPPER(INDEX(Textes!$B$2:$C$55,MATCH("forfait",Textes!$A$2:$A$55,0),Listes!$H$1))&amp;IF('3 Options'!$D$13&lt;&gt;"","   ·   "&amp;'3 Options'!$D$13,""),"")</f>
         <v/>
       </c>
-      <c r="I53" s="49">
+      <c r="H55" s="54">
         <f>IF('3 Options'!$C$13="Oui",'3 Options'!$H$13,"")</f>
         <v/>
       </c>
-      <c r="M53" s="41">
+      <c r="L55" s="42">
         <f>IF('3 Options'!$C$13="Oui",1,0)</f>
         <v/>
       </c>
     </row>
-    <row r="54" ht="24" customHeight="1">
-      <c r="B54" s="50">
+    <row r="56" ht="34" customHeight="1">
+      <c r="B56" s="55">
         <f>IF('3 Options'!$C$13="Oui",IF('3 Options'!$G$13="Forfait calculé (S + O + UC)",'3 Options'!$C$15&amp;" "&amp;SUBSTITUTE(INDEX(Textes!$B$2:$C$55,MATCH("calc_det",Textes!$A$2:$A$55,0),Listes!$H$1),"%s",'3 Options'!$C$16)&amp;"   ·   "&amp;INDEX(Textes!$B$2:$C$55,MATCH("ht",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$G$13="Forfait par jour",'3 Options'!$E$13&amp;" j × "&amp;TEXT('3 Options'!$F$13,"#,##0.00")&amp;" €/j   ·   "&amp;INDEX(Textes!$B$2:$C$55,MATCH("ht",Textes!$A$2:$A$55,0),Listes!$H$1),INDEX(Textes!$B$2:$C$55,MATCH("ht",Textes!$A$2:$A$55,0),Listes!$H$1)))&amp;IF('3 Options'!$D$14&lt;&gt;"","   ·   "&amp;'3 Options'!$D$14,""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="55" ht="10" customHeight="1"/>
-    <row r="56" ht="20" customHeight="1">
-      <c r="B56" s="33">
+    <row r="57" ht="10" customHeight="1"/>
+    <row r="58" ht="20" customHeight="1">
+      <c r="B58" s="34">
         <f>INDEX(Textes!$B$2:$C$55,MATCH("sec_cond",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="C56" s="34" t="n"/>
-      <c r="D56" s="34" t="n"/>
-      <c r="E56" s="34" t="n"/>
-      <c r="F56" s="34" t="n"/>
-      <c r="G56" s="34" t="n"/>
-      <c r="H56" s="34" t="n"/>
-      <c r="I56" s="34" t="n"/>
-      <c r="J56" s="34" t="n"/>
-      <c r="K56" s="34" t="n"/>
-    </row>
-    <row r="57" ht="66" customHeight="1">
-      <c r="B57" s="51" t="inlineStr">
+      <c r="C58" s="35" t="n"/>
+      <c r="D58" s="35" t="n"/>
+      <c r="E58" s="35" t="n"/>
+      <c r="F58" s="35" t="n"/>
+      <c r="G58" s="35" t="n"/>
+      <c r="H58" s="35" t="n"/>
+      <c r="I58" s="35" t="n"/>
+      <c r="J58" s="35" t="n"/>
+    </row>
+    <row r="59" ht="76" customHeight="1">
+      <c r="B59" s="56" t="inlineStr">
         <is>
           <t>La location s'entend depuis le jour de départ de la base d'origine jusqu'à son retour au même endroit.
 Le Wear Charge s'applique pour toute usure liée à un usage normal des équipements. En cas de dommages plus importants liés à un usage anormal, la valeur de remplacement sera facturée sur documentation.
@@ -4083,8 +4041,8 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="66" customHeight="1">
-      <c r="B58" s="51" t="inlineStr">
+    <row r="60" ht="76" customHeight="1">
+      <c r="B60" s="56" t="inlineStr">
         <is>
           <t>The rental is from the day of departure from the base of origin until its return to the same place.
 Wear Charge applies to all wear and tear related to normal use of equipment. In case of greater damage due to abnormal use, the replacement value will be charged based on supporting documentation.
@@ -4093,72 +4051,68 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="10" customHeight="1"/>
-    <row r="60">
-      <c r="B60" s="52">
+    <row r="61" ht="10" customHeight="1"/>
+    <row r="62">
+      <c r="B62" s="57">
         <f>INDEX(Textes!$B$2:$C$55,MATCH("accept",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
     </row>
-    <row r="61" ht="16" customHeight="1">
-      <c r="B61" s="53">
+    <row r="63" ht="17" customHeight="1">
+      <c r="B63" s="58">
         <f>INDEX(Textes!$B$2:$C$55,MATCH("sig_name",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="C61" s="54" t="n"/>
-      <c r="D61" s="55" t="n"/>
-      <c r="E61" s="53">
+      <c r="C63" s="59" t="n"/>
+      <c r="D63" s="58">
         <f>INDEX(Textes!$B$2:$C$55,MATCH("sig_date",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="F61" s="54" t="n"/>
-      <c r="G61" s="55" t="n"/>
-      <c r="H61" s="53">
+      <c r="E63" s="60" t="n"/>
+      <c r="F63" s="60" t="n"/>
+      <c r="G63" s="59" t="n"/>
+      <c r="H63" s="58">
         <f>INDEX(Textes!$B$2:$C$55,MATCH("sig_sig",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="I61" s="54" t="n"/>
-      <c r="J61" s="54" t="n"/>
-      <c r="K61" s="55" t="n"/>
-    </row>
-    <row r="62" ht="16" customHeight="1">
-      <c r="B62" s="56" t="n"/>
-      <c r="C62" s="57" t="n"/>
-      <c r="D62" s="58" t="n"/>
-      <c r="E62" s="56" t="n"/>
-      <c r="F62" s="57" t="n"/>
-      <c r="G62" s="58" t="n"/>
-      <c r="H62" s="56" t="n"/>
-      <c r="I62" s="57" t="n"/>
-      <c r="J62" s="57" t="n"/>
-      <c r="K62" s="58" t="n"/>
-    </row>
-    <row r="63" ht="16" customHeight="1">
-      <c r="B63" s="56" t="n"/>
-      <c r="C63" s="57" t="n"/>
-      <c r="D63" s="58" t="n"/>
-      <c r="E63" s="56" t="n"/>
-      <c r="F63" s="57" t="n"/>
-      <c r="G63" s="58" t="n"/>
-      <c r="H63" s="56" t="n"/>
-      <c r="I63" s="57" t="n"/>
-      <c r="J63" s="57" t="n"/>
-      <c r="K63" s="58" t="n"/>
-    </row>
-    <row r="64" ht="16" customHeight="1">
-      <c r="B64" s="59" t="n"/>
-      <c r="C64" s="32" t="n"/>
-      <c r="D64" s="60" t="n"/>
-      <c r="E64" s="59" t="n"/>
-      <c r="F64" s="32" t="n"/>
-      <c r="G64" s="60" t="n"/>
-      <c r="H64" s="59" t="n"/>
-      <c r="I64" s="32" t="n"/>
-      <c r="J64" s="32" t="n"/>
-      <c r="K64" s="60" t="n"/>
-    </row>
-    <row r="66">
-      <c r="B66" s="61" t="inlineStr">
+      <c r="I63" s="60" t="n"/>
+      <c r="J63" s="59" t="n"/>
+    </row>
+    <row r="64" ht="17" customHeight="1">
+      <c r="B64" s="61" t="n"/>
+      <c r="C64" s="62" t="n"/>
+      <c r="D64" s="61" t="n"/>
+      <c r="E64" s="63" t="n"/>
+      <c r="F64" s="63" t="n"/>
+      <c r="G64" s="62" t="n"/>
+      <c r="H64" s="61" t="n"/>
+      <c r="I64" s="63" t="n"/>
+      <c r="J64" s="62" t="n"/>
+    </row>
+    <row r="65" ht="17" customHeight="1">
+      <c r="B65" s="61" t="n"/>
+      <c r="C65" s="62" t="n"/>
+      <c r="D65" s="61" t="n"/>
+      <c r="E65" s="63" t="n"/>
+      <c r="F65" s="63" t="n"/>
+      <c r="G65" s="62" t="n"/>
+      <c r="H65" s="61" t="n"/>
+      <c r="I65" s="63" t="n"/>
+      <c r="J65" s="62" t="n"/>
+    </row>
+    <row r="66" ht="17" customHeight="1">
+      <c r="B66" s="64" t="n"/>
+      <c r="C66" s="65" t="n"/>
+      <c r="D66" s="64" t="n"/>
+      <c r="E66" s="33" t="n"/>
+      <c r="F66" s="33" t="n"/>
+      <c r="G66" s="65" t="n"/>
+      <c r="H66" s="64" t="n"/>
+      <c r="I66" s="33" t="n"/>
+      <c r="J66" s="65" t="n"/>
+    </row>
+    <row r="68" ht="26" customHeight="1">
+      <c r="B68" s="66" t="inlineStr">
         <is>
           <t>ENEDRIL · Z-Induspal · 3 Av. des Lacs · 64140 LONS (France) · SIRET 79464246200020 · TVA FR11794642462</t>
         </is>
@@ -4166,128 +4120,128 @@
     </row>
   </sheetData>
   <mergeCells count="52">
+    <mergeCell ref="H49:J49"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="H51:J51"/>
+    <mergeCell ref="D9:G9"/>
     <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B40:K40"/>
-    <mergeCell ref="H47:K47"/>
-    <mergeCell ref="I53:K53"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="H42:K42"/>
+    <mergeCell ref="D12:G12"/>
+    <mergeCell ref="B42:J42"/>
+    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="H52:J52"/>
+    <mergeCell ref="B60:J60"/>
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="H45:J45"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G7:H7"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="H61:K64"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="B54:K54"/>
-    <mergeCell ref="H43:K43"/>
-    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="H63:J66"/>
+    <mergeCell ref="H47:J47"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="D10:G10"/>
+    <mergeCell ref="D1:J1"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B66:K66"/>
-    <mergeCell ref="H50:K50"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="B56:K56"/>
-    <mergeCell ref="B58:K58"/>
+    <mergeCell ref="H48:J48"/>
+    <mergeCell ref="B68:J68"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="H5:J5"/>
     <mergeCell ref="B10:C10"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="B61:D64"/>
-    <mergeCell ref="H46:K46"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="B63:C66"/>
+    <mergeCell ref="D2:J2"/>
+    <mergeCell ref="D11:G11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="E1:K1"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="H49:K49"/>
-    <mergeCell ref="H51:K51"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="B60:K60"/>
+    <mergeCell ref="H53:J53"/>
+    <mergeCell ref="B16:J16"/>
+    <mergeCell ref="B62:J62"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B57:K57"/>
-    <mergeCell ref="B14:K14"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="B59:J59"/>
+    <mergeCell ref="H44:J44"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B53:H53"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="H45:K45"/>
-    <mergeCell ref="E61:G64"/>
-    <mergeCell ref="E2:K2"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="H55:J55"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="B56:J56"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="B58:J58"/>
+    <mergeCell ref="D63:G66"/>
+    <mergeCell ref="H6:J6"/>
   </mergeCells>
-  <conditionalFormatting sqref="B16:K39">
+  <conditionalFormatting sqref="B18:J41">
     <cfRule type="expression" priority="1" dxfId="1" stopIfTrue="1">
-      <formula>$M16=1</formula>
+      <formula>$L18=1</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="2">
-      <formula>$C16&lt;&gt;""</formula>
+      <formula>$C18&lt;&gt;""</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="3">
-      <formula>AND($C16&lt;&gt;"",MOD(ROW(),2)=0)</formula>
+      <formula>AND($C18&lt;&gt;"",MOD(ROW(),2)=0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E16:J39">
+  <conditionalFormatting sqref="E18:J41">
     <cfRule type="expression" priority="4" dxfId="4">
-      <formula>E16="incl."</formula>
+      <formula>E18="incl."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B42:K42">
+  <conditionalFormatting sqref="B44:J44">
     <cfRule type="expression" priority="5" dxfId="5">
-      <formula>$M42=1</formula>
+      <formula>$L44=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B43:K43">
+  <conditionalFormatting sqref="B45:J45">
     <cfRule type="expression" priority="6" dxfId="2">
-      <formula>$C43&lt;&gt;""</formula>
+      <formula>$C45&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B45:K45">
+  <conditionalFormatting sqref="B47:J47">
     <cfRule type="expression" priority="7" dxfId="5">
-      <formula>$M45=1</formula>
+      <formula>$L47=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B46:K46">
+  <conditionalFormatting sqref="B48:J48">
     <cfRule type="expression" priority="8" dxfId="2">
-      <formula>$C46&lt;&gt;""</formula>
+      <formula>$C48&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B47:K47">
+  <conditionalFormatting sqref="B49:J49">
     <cfRule type="expression" priority="9" dxfId="2">
-      <formula>$C47&lt;&gt;""</formula>
+      <formula>$C49&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B49:K49">
+  <conditionalFormatting sqref="B51:J51">
     <cfRule type="expression" priority="10" dxfId="5">
-      <formula>$M49=1</formula>
+      <formula>$L51=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B50:K50">
+  <conditionalFormatting sqref="B52:J52">
     <cfRule type="expression" priority="11" dxfId="2">
-      <formula>$C50&lt;&gt;""</formula>
+      <formula>$C52&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B51:K51">
+  <conditionalFormatting sqref="B53:J53">
     <cfRule type="expression" priority="12" dxfId="2">
-      <formula>$C51&lt;&gt;""</formula>
+      <formula>$C53&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B53:K53">
+  <conditionalFormatting sqref="B55:J55">
     <cfRule type="expression" priority="13" dxfId="6">
-      <formula>$M$53=1</formula>
+      <formula>$L55=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B54:K54">
+  <conditionalFormatting sqref="B56:J56">
     <cfRule type="expression" priority="14" dxfId="7">
-      <formula>$M$53=1</formula>
+      <formula>$L55=1</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.35" bottom="0.4" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageMargins left="0.35" right="0.35" top="0.4" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;8 Enedril · Devis &amp;P / &amp;N</oddFooter>
@@ -4297,7 +4251,7 @@
     <firstFooter/>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="40" min="0" max="16383" man="1"/>
+    <brk id="42" min="0" max="16383" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -4329,366 +4283,366 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="62" t="inlineStr">
+      <c r="A1" s="67" t="inlineStr">
         <is>
           <t>Contact Enedril</t>
         </is>
       </c>
-      <c r="B1" s="62" t="inlineStr">
+      <c r="B1" s="67" t="inlineStr">
         <is>
           <t>E-mail</t>
         </is>
       </c>
-      <c r="D1" s="62" t="inlineStr">
+      <c r="D1" s="67" t="inlineStr">
         <is>
           <t>Incoterm</t>
         </is>
       </c>
-      <c r="E1" s="62" t="inlineStr">
+      <c r="E1" s="67" t="inlineStr">
         <is>
           <t>Validité</t>
         </is>
       </c>
-      <c r="F1" s="62" t="inlineStr">
+      <c r="F1" s="67" t="inlineStr">
         <is>
           <t>Règlement</t>
         </is>
       </c>
-      <c r="G1" s="62" t="inlineStr">
+      <c r="G1" s="67" t="inlineStr">
         <is>
           <t>Oui / Non</t>
         </is>
       </c>
-      <c r="H1" s="63" t="n">
+      <c r="H1" s="68" t="n">
         <v>1</v>
       </c>
-      <c r="J1" s="62" t="inlineStr">
+      <c r="J1" s="67" t="inlineStr">
         <is>
           <t>Support de colisage</t>
         </is>
       </c>
-      <c r="K1" s="62" t="inlineStr">
+      <c r="K1" s="67" t="inlineStr">
         <is>
           <t>N° de colis</t>
         </is>
       </c>
-      <c r="L1" s="62" t="inlineStr">
+      <c r="L1" s="67" t="inlineStr">
         <is>
           <t>Unité</t>
         </is>
       </c>
-      <c r="M1" s="62" t="inlineStr">
+      <c r="M1" s="67" t="inlineStr">
         <is>
           <t>Mode transport</t>
         </is>
       </c>
-      <c r="N1" s="62" t="inlineStr">
+      <c r="N1" s="67" t="inlineStr">
         <is>
           <t>Mode forfait</t>
         </is>
       </c>
-      <c r="P1" s="62" t="inlineStr">
+      <c r="P1" s="67" t="inlineStr">
         <is>
           <t>Statut</t>
         </is>
       </c>
-      <c r="Q1" s="62" t="inlineStr">
+      <c r="Q1" s="67" t="inlineStr">
         <is>
           <t>Test / Taille</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="64" t="inlineStr">
+      <c r="A2" s="69" t="inlineStr">
         <is>
           <t>Fabien JACQUOT</t>
         </is>
       </c>
-      <c r="B2" s="64" t="inlineStr">
+      <c r="B2" s="69" t="inlineStr">
         <is>
           <t>fjacquot@enedril.fr</t>
         </is>
       </c>
-      <c r="D2" s="64" t="inlineStr">
+      <c r="D2" s="69" t="inlineStr">
         <is>
           <t>EXW Lons</t>
         </is>
       </c>
-      <c r="E2" s="64" t="inlineStr">
+      <c r="E2" s="69" t="inlineStr">
         <is>
           <t>15 jours / 15 days</t>
         </is>
       </c>
-      <c r="F2" s="64" t="inlineStr">
+      <c r="F2" s="69" t="inlineStr">
         <is>
           <t>30 jours date de facture / 30 days invoice date</t>
         </is>
       </c>
-      <c r="G2" s="64" t="inlineStr">
+      <c r="G2" s="69" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="H2" s="65" t="inlineStr">
+      <c r="H2" s="70" t="inlineStr">
         <is>
           <t>← langue du devis : 1 = français, 2 = anglais</t>
         </is>
       </c>
-      <c r="J2" s="64" t="inlineStr">
+      <c r="J2" s="69" t="inlineStr">
         <is>
           <t>Palette</t>
         </is>
       </c>
-      <c r="K2" s="64" t="inlineStr">
+      <c r="K2" s="69" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="L2" s="64" t="inlineStr">
+      <c r="L2" s="69" t="inlineStr">
         <is>
           <t>forfait</t>
         </is>
       </c>
-      <c r="M2" s="64" t="inlineStr">
+      <c r="M2" s="69" t="inlineStr">
         <is>
           <t>Coût réel +15 %</t>
         </is>
       </c>
-      <c r="N2" s="64" t="inlineStr">
+      <c r="N2" s="69" t="inlineStr">
         <is>
           <t>Forfait calculé (S + O + UC)</t>
         </is>
       </c>
-      <c r="P2" s="64" t="inlineStr">
+      <c r="P2" s="69" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="Q2" s="64" t="inlineStr">
+      <c r="Q2" s="69" t="inlineStr">
         <is>
           <t>Taille OK</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="64" t="inlineStr">
+      <c r="A3" s="69" t="inlineStr">
         <is>
           <t>Alexis ESTINES</t>
         </is>
       </c>
-      <c r="B3" s="64" t="inlineStr">
+      <c r="B3" s="69" t="inlineStr">
         <is>
           <t>aestines@enedril.fr</t>
         </is>
       </c>
-      <c r="D3" s="64" t="inlineStr">
+      <c r="D3" s="69" t="inlineStr">
         <is>
           <t>FCA Lons</t>
         </is>
       </c>
-      <c r="E3" s="64" t="inlineStr">
+      <c r="E3" s="69" t="inlineStr">
         <is>
           <t>30 jours / 30 days</t>
         </is>
       </c>
-      <c r="F3" s="64" t="inlineStr">
+      <c r="F3" s="69" t="inlineStr">
         <is>
           <t>30 jours fin de mois / 30 days end of month</t>
         </is>
       </c>
-      <c r="G3" s="64" t="inlineStr">
+      <c r="G3" s="69" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J3" s="64" t="inlineStr">
+      <c r="J3" s="69" t="inlineStr">
         <is>
           <t>Fishing basket</t>
         </is>
       </c>
-      <c r="K3" s="64" t="inlineStr">
+      <c r="K3" s="69" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L3" s="64" t="inlineStr">
+      <c r="L3" s="69" t="inlineStr">
         <is>
           <t>€/jour</t>
         </is>
       </c>
-      <c r="M3" s="64" t="inlineStr">
+      <c r="M3" s="69" t="inlineStr">
         <is>
           <t>Forfait</t>
         </is>
       </c>
-      <c r="N3" s="64" t="inlineStr">
+      <c r="N3" s="69" t="inlineStr">
         <is>
           <t>Forfait global</t>
         </is>
       </c>
-      <c r="P3" s="64" t="inlineStr">
+      <c r="P3" s="69" t="inlineStr">
         <is>
           <t>En cours</t>
         </is>
       </c>
-      <c r="Q3" s="64" t="inlineStr">
+      <c r="Q3" s="69" t="inlineStr">
         <is>
           <t>Test OK</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="64" t="inlineStr">
+      <c r="A4" s="69" t="inlineStr">
         <is>
           <t>Paul HYNDERICK</t>
         </is>
       </c>
-      <c r="B4" s="64" t="inlineStr">
+      <c r="B4" s="69" t="inlineStr">
         <is>
           <t>phynderick@enedril.fr</t>
         </is>
       </c>
-      <c r="D4" s="64" t="inlineStr">
+      <c r="D4" s="69" t="inlineStr">
         <is>
           <t>DAP</t>
         </is>
       </c>
-      <c r="E4" s="64" t="inlineStr">
+      <c r="E4" s="69" t="inlineStr">
         <is>
           <t>60 jours / 60 days</t>
         </is>
       </c>
-      <c r="F4" s="64" t="inlineStr">
+      <c r="F4" s="69" t="inlineStr">
         <is>
           <t>45 jours fin de mois / 45 days end of month</t>
         </is>
       </c>
-      <c r="J4" s="64" t="inlineStr">
+      <c r="J4" s="69" t="inlineStr">
         <is>
           <t>Caisse</t>
         </is>
       </c>
-      <c r="K4" s="64" t="inlineStr">
+      <c r="K4" s="69" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="L4" s="64" t="inlineStr">
+      <c r="L4" s="69" t="inlineStr">
         <is>
           <t>€/jour/pers</t>
         </is>
       </c>
-      <c r="N4" s="64" t="inlineStr">
+      <c r="N4" s="69" t="inlineStr">
         <is>
           <t>Forfait par jour</t>
         </is>
       </c>
-      <c r="Q4" s="64" t="inlineStr">
+      <c r="Q4" s="69" t="inlineStr">
         <is>
           <t>Taille + test OK</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="64" t="inlineStr">
+      <c r="A5" s="69" t="inlineStr">
         <is>
           <t>Céline CARDONA</t>
         </is>
       </c>
-      <c r="B5" s="64" t="inlineStr">
+      <c r="B5" s="69" t="inlineStr">
         <is>
           <t>ccardona@enedril.fr</t>
         </is>
       </c>
-      <c r="D5" s="64" t="inlineStr">
+      <c r="D5" s="69" t="inlineStr">
         <is>
           <t>DDP</t>
         </is>
       </c>
-      <c r="E5" s="64" t="inlineStr">
+      <c r="E5" s="69" t="inlineStr">
         <is>
           <t>90 jours / 90 days</t>
         </is>
       </c>
-      <c r="F5" s="64" t="inlineStr">
+      <c r="F5" s="69" t="inlineStr">
         <is>
           <t>À la commande / Upon order</t>
         </is>
       </c>
-      <c r="J5" s="64" t="inlineStr">
+      <c r="J5" s="69" t="inlineStr">
         <is>
           <t>Loose (vrac)</t>
         </is>
       </c>
-      <c r="K5" s="64" t="inlineStr">
+      <c r="K5" s="69" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="L5" s="64" t="inlineStr">
+      <c r="L5" s="69" t="inlineStr">
         <is>
           <t>€/pers</t>
         </is>
       </c>
-      <c r="Q5" s="64" t="inlineStr">
+      <c r="Q5" s="69" t="inlineStr">
         <is>
           <t>À contrôler</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="64" t="inlineStr">
+      <c r="A6" s="69" t="inlineStr">
         <is>
           <t>Koen MONDELAERS</t>
         </is>
       </c>
-      <c r="B6" s="64" t="inlineStr">
+      <c r="B6" s="69" t="inlineStr">
         <is>
           <t>kmondelaers@enedril.fr</t>
         </is>
       </c>
-      <c r="D6" s="64" t="inlineStr">
+      <c r="D6" s="69" t="inlineStr">
         <is>
           <t>FOB</t>
         </is>
       </c>
-      <c r="K6" s="64" t="inlineStr">
+      <c r="K6" s="69" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="L6" s="64" t="inlineStr">
+      <c r="L6" s="69" t="inlineStr">
         <is>
           <t>€/unité</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="64" t="inlineStr">
+      <c r="A7" s="69" t="inlineStr">
         <is>
           <t>Luigi LIBERATORE</t>
         </is>
       </c>
-      <c r="B7" s="64" t="inlineStr">
+      <c r="B7" s="69" t="inlineStr">
         <is>
           <t>lliberatore@enedril.fr</t>
         </is>
       </c>
-      <c r="K7" s="64" t="inlineStr">
+      <c r="K7" s="69" t="inlineStr">
         <is>
           <t>P6</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="K8" s="64" t="inlineStr">
+      <c r="K8" s="69" t="inlineStr">
         <is>
           <t>P7</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="K9" s="64" t="inlineStr">
+      <c r="K9" s="69" t="inlineStr">
         <is>
           <t>P8</t>
         </is>
@@ -4700,21 +4654,21 @@
           <t>Pour ajouter un contact, une validité, etc. : écrire à la suite dans la colonne (les listes déroulantes lisent les 12 premières lignes).</t>
         </is>
       </c>
-      <c r="K10" s="64" t="inlineStr">
+      <c r="K10" s="69" t="inlineStr">
         <is>
           <t>P9</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="K11" s="64" t="inlineStr">
+      <c r="K11" s="69" t="inlineStr">
         <is>
           <t>P10</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="K12" s="64" t="inlineStr">
+      <c r="K12" s="69" t="inlineStr">
         <is>
           <t>Loose</t>
         </is>
@@ -4741,358 +4695,358 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="62" t="inlineStr">
+      <c r="A1" s="67" t="inlineStr">
         <is>
           <t>Clé</t>
         </is>
       </c>
-      <c r="B1" s="62" t="inlineStr">
+      <c r="B1" s="67" t="inlineStr">
         <is>
           <t>Français</t>
         </is>
       </c>
-      <c r="C1" s="62" t="inlineStr">
+      <c r="C1" s="67" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="66" t="inlineStr">
+      <c r="A2" s="71" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B2" s="66" t="inlineStr">
+      <c r="B2" s="71" t="inlineStr">
         <is>
           <t>OFFRE DE LOCATION</t>
         </is>
       </c>
-      <c r="C2" s="66" t="inlineStr">
+      <c r="C2" s="71" t="inlineStr">
         <is>
           <t>EQUIPMENT RENTAL QUOTATION</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="66" t="inlineStr">
+      <c r="A3" s="71" t="inlineStr">
         <is>
           <t>client</t>
         </is>
       </c>
-      <c r="B3" s="66" t="inlineStr">
+      <c r="B3" s="71" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="C3" s="66" t="inlineStr">
+      <c r="C3" s="71" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="66" t="inlineStr">
+      <c r="A4" s="71" t="inlineStr">
         <is>
           <t>attn</t>
         </is>
       </c>
-      <c r="B4" s="66" t="inlineStr">
+      <c r="B4" s="71" t="inlineStr">
         <is>
           <t>À l'attention de</t>
         </is>
       </c>
-      <c r="C4" s="66" t="inlineStr">
+      <c r="C4" s="71" t="inlineStr">
         <is>
           <t>Attention</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="66" t="inlineStr">
+      <c r="A5" s="71" t="inlineStr">
         <is>
           <t>well</t>
         </is>
       </c>
-      <c r="B5" s="66" t="inlineStr">
+      <c r="B5" s="71" t="inlineStr">
         <is>
           <t>Puits / Chantier</t>
         </is>
       </c>
-      <c r="C5" s="66" t="inlineStr">
+      <c r="C5" s="71" t="inlineStr">
         <is>
           <t>Well / Location</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="66" t="inlineStr">
+      <c r="A6" s="71" t="inlineStr">
         <is>
           <t>rig</t>
         </is>
       </c>
-      <c r="B6" s="66" t="inlineStr">
+      <c r="B6" s="71" t="inlineStr">
         <is>
           <t>Rig</t>
         </is>
       </c>
-      <c r="C6" s="66" t="inlineStr">
+      <c r="C6" s="71" t="inlineStr">
         <is>
           <t>Rig</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="66" t="inlineStr">
+      <c r="A7" s="71" t="inlineStr">
         <is>
           <t>offer</t>
         </is>
       </c>
-      <c r="B7" s="66" t="inlineStr">
+      <c r="B7" s="71" t="inlineStr">
         <is>
           <t>N° d'offre</t>
         </is>
       </c>
-      <c r="C7" s="66" t="inlineStr">
+      <c r="C7" s="71" t="inlineStr">
         <is>
           <t>Offer N°</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="66" t="inlineStr">
+      <c r="A8" s="71" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B8" s="66" t="inlineStr">
+      <c r="B8" s="71" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C8" s="66" t="inlineStr">
+      <c r="C8" s="71" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="66" t="inlineStr">
+      <c r="A9" s="71" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="B9" s="66" t="inlineStr">
+      <c r="B9" s="71" t="inlineStr">
         <is>
           <t>Validité de l'offre</t>
         </is>
       </c>
-      <c r="C9" s="66" t="inlineStr">
+      <c r="C9" s="71" t="inlineStr">
         <is>
           <t>Validity</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="66" t="inlineStr">
+      <c r="A10" s="71" t="inlineStr">
         <is>
           <t>inco</t>
         </is>
       </c>
-      <c r="B10" s="66" t="inlineStr">
+      <c r="B10" s="71" t="inlineStr">
         <is>
           <t>Incoterm</t>
         </is>
       </c>
-      <c r="C10" s="66" t="inlineStr">
+      <c r="C10" s="71" t="inlineStr">
         <is>
           <t>Incoterm</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="66" t="inlineStr">
+      <c r="A11" s="71" t="inlineStr">
         <is>
           <t>lead</t>
         </is>
       </c>
-      <c r="B11" s="66" t="inlineStr">
+      <c r="B11" s="71" t="inlineStr">
         <is>
           <t>Délai de mise à dispo</t>
         </is>
       </c>
-      <c r="C11" s="66" t="inlineStr">
+      <c r="C11" s="71" t="inlineStr">
         <is>
           <t>Lead time</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="66" t="inlineStr">
+      <c r="A12" s="71" t="inlineStr">
         <is>
           <t>pay</t>
         </is>
       </c>
-      <c r="B12" s="66" t="inlineStr">
+      <c r="B12" s="71" t="inlineStr">
         <is>
           <t>Conditions de règlement</t>
         </is>
       </c>
-      <c r="C12" s="66" t="inlineStr">
+      <c r="C12" s="71" t="inlineStr">
         <is>
           <t>Payment terms</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="66" t="inlineStr">
+      <c r="A13" s="71" t="inlineStr">
         <is>
           <t>we</t>
         </is>
       </c>
-      <c r="B13" s="66" t="inlineStr">
+      <c r="B13" s="71" t="inlineStr">
         <is>
           <t>Facturation WE et jours fériés</t>
         </is>
       </c>
-      <c r="C13" s="66" t="inlineStr">
+      <c r="C13" s="71" t="inlineStr">
         <is>
           <t>Weekend &amp; holiday billing</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="66" t="inlineStr">
+      <c r="A14" s="71" t="inlineStr">
         <is>
           <t>by</t>
         </is>
       </c>
-      <c r="B14" s="66" t="inlineStr">
+      <c r="B14" s="71" t="inlineStr">
         <is>
           <t>Établi par</t>
         </is>
       </c>
-      <c r="C14" s="66" t="inlineStr">
+      <c r="C14" s="71" t="inlineStr">
         <is>
           <t>Established by</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="66" t="inlineStr">
+      <c r="A15" s="71" t="inlineStr">
         <is>
           <t>mail</t>
         </is>
       </c>
-      <c r="B15" s="66" t="inlineStr">
+      <c r="B15" s="71" t="inlineStr">
         <is>
           <t>E-mail</t>
         </is>
       </c>
-      <c r="C15" s="66" t="inlineStr">
+      <c r="C15" s="71" t="inlineStr">
         <is>
           <t>E-mail</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="66" t="inlineStr">
+      <c r="A16" s="71" t="inlineStr">
         <is>
           <t>tel</t>
         </is>
       </c>
-      <c r="B16" s="66" t="inlineStr">
+      <c r="B16" s="71" t="inlineStr">
         <is>
           <t>Téléphone</t>
         </is>
       </c>
-      <c r="C16" s="66" t="inlineStr">
+      <c r="C16" s="71" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="66" t="inlineStr">
+      <c r="A17" s="71" t="inlineStr">
         <is>
           <t>sec_eq</t>
         </is>
       </c>
-      <c r="B17" s="66" t="inlineStr">
+      <c r="B17" s="71" t="inlineStr">
         <is>
           <t>MATÉRIEL</t>
         </is>
       </c>
-      <c r="C17" s="66" t="inlineStr">
+      <c r="C17" s="71" t="inlineStr">
         <is>
           <t>EQUIPMENT</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="66" t="inlineStr">
+      <c r="A18" s="71" t="inlineStr">
         <is>
           <t>h_n</t>
         </is>
       </c>
-      <c r="B18" s="66" t="inlineStr">
+      <c r="B18" s="71" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C18" s="66" t="inlineStr">
+      <c r="C18" s="71" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="66" t="inlineStr">
+      <c r="A19" s="71" t="inlineStr">
         <is>
           <t>h_desc</t>
         </is>
       </c>
-      <c r="B19" s="66" t="inlineStr">
+      <c r="B19" s="71" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C19" s="66" t="inlineStr">
+      <c r="C19" s="71" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="66" t="inlineStr">
+      <c r="A20" s="71" t="inlineStr">
         <is>
           <t>h_qty</t>
         </is>
       </c>
-      <c r="B20" s="66" t="inlineStr">
+      <c r="B20" s="71" t="inlineStr">
         <is>
           <t>Qté</t>
         </is>
       </c>
-      <c r="C20" s="66" t="inlineStr">
+      <c r="C20" s="71" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="66" t="inlineStr">
+      <c r="A21" s="71" t="inlineStr">
         <is>
           <t>h_s</t>
         </is>
       </c>
-      <c r="B21" s="66" t="inlineStr">
+      <c r="B21" s="71" t="inlineStr">
         <is>
           <t>Stand-by (S)
 € / jour / item</t>
         </is>
       </c>
-      <c r="C21" s="66" t="inlineStr">
+      <c r="C21" s="71" t="inlineStr">
         <is>
           <t>Stand-by (S)
 daily rate / item</t>
@@ -5100,18 +5054,18 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="66" t="inlineStr">
+      <c r="A22" s="71" t="inlineStr">
         <is>
           <t>h_o</t>
         </is>
       </c>
-      <c r="B22" s="66" t="inlineStr">
+      <c r="B22" s="71" t="inlineStr">
         <is>
           <t>Opérations (O)
 € / jour / item</t>
         </is>
       </c>
-      <c r="C22" s="66" t="inlineStr">
+      <c r="C22" s="71" t="inlineStr">
         <is>
           <t>Operations (O)
 daily rate / item</t>
@@ -5119,19 +5073,19 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="66" t="inlineStr">
+      <c r="A23" s="71" t="inlineStr">
         <is>
           <t>h_uc</t>
         </is>
       </c>
-      <c r="B23" s="66" t="inlineStr">
+      <c r="B23" s="71" t="inlineStr">
         <is>
           <t>Utilisation
 Charge (UC)
 € / item</t>
         </is>
       </c>
-      <c r="C23" s="66" t="inlineStr">
+      <c r="C23" s="71" t="inlineStr">
         <is>
           <t>Utilisation
 Charge (UC)
@@ -5140,18 +5094,18 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="66" t="inlineStr">
+      <c r="A24" s="71" t="inlineStr">
         <is>
           <t>h_lih</t>
         </is>
       </c>
-      <c r="B24" s="66" t="inlineStr">
+      <c r="B24" s="71" t="inlineStr">
         <is>
           <t>Valeur de remplacement
 (LIH / DBR) € / item</t>
         </is>
       </c>
-      <c r="C24" s="66" t="inlineStr">
+      <c r="C24" s="71" t="inlineStr">
         <is>
           <t>Replacement value
 (LIH / DBR) per item</t>
@@ -5159,18 +5113,18 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="66" t="inlineStr">
+      <c r="A25" s="71" t="inlineStr">
         <is>
           <t>h_insp</t>
         </is>
       </c>
-      <c r="B25" s="66" t="inlineStr">
+      <c r="B25" s="71" t="inlineStr">
         <is>
           <t>Inspection
 € / item</t>
         </is>
       </c>
-      <c r="C25" s="66" t="inlineStr">
+      <c r="C25" s="71" t="inlineStr">
         <is>
           <t>Inspection
 per item</t>
@@ -5178,18 +5132,18 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="66" t="inlineStr">
+      <c r="A26" s="71" t="inlineStr">
         <is>
           <t>h_rest</t>
         </is>
       </c>
-      <c r="B26" s="66" t="inlineStr">
+      <c r="B26" s="71" t="inlineStr">
         <is>
           <t>Restocking
 €</t>
         </is>
       </c>
-      <c r="C26" s="66" t="inlineStr">
+      <c r="C26" s="71" t="inlineStr">
         <is>
           <t>Restocking
 charge</t>
@@ -5197,493 +5151,493 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="66" t="inlineStr">
+      <c r="A27" s="71" t="inlineStr">
         <is>
           <t>h_ref</t>
         </is>
       </c>
-      <c r="B27" s="66" t="inlineStr">
+      <c r="B27" s="71" t="inlineStr">
         <is>
           <t>Remarques</t>
         </is>
       </c>
-      <c r="C27" s="66" t="inlineStr">
+      <c r="C27" s="71" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="66" t="inlineStr">
+      <c r="A28" s="71" t="inlineStr">
         <is>
           <t>incl</t>
         </is>
       </c>
-      <c r="B28" s="66" t="inlineStr">
+      <c r="B28" s="71" t="inlineStr">
         <is>
           <t>incl.</t>
         </is>
       </c>
-      <c r="C28" s="66" t="inlineStr">
+      <c r="C28" s="71" t="inlineStr">
         <is>
           <t>incl.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="66" t="inlineStr">
+      <c r="A29" s="71" t="inlineStr">
         <is>
           <t>incl_long</t>
         </is>
       </c>
-      <c r="B29" s="66" t="inlineStr">
+      <c r="B29" s="71" t="inlineStr">
         <is>
           <t>Inclus au forfait</t>
         </is>
       </c>
-      <c r="C29" s="66" t="inlineStr">
+      <c r="C29" s="71" t="inlineStr">
         <is>
           <t>Included in lump sum</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="66" t="inlineStr">
+      <c r="A30" s="71" t="inlineStr">
         <is>
           <t>sec_opt</t>
         </is>
       </c>
-      <c r="B30" s="66" t="inlineStr">
+      <c r="B30" s="71" t="inlineStr">
         <is>
           <t>PRESTATIONS ET OPTIONS</t>
         </is>
       </c>
-      <c r="C30" s="66" t="inlineStr">
+      <c r="C30" s="71" t="inlineStr">
         <is>
           <t>SERVICES AND OPTIONS</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="66" t="inlineStr">
+      <c r="A31" s="71" t="inlineStr">
         <is>
           <t>h_label</t>
         </is>
       </c>
-      <c r="B31" s="66" t="inlineStr">
+      <c r="B31" s="71" t="inlineStr">
         <is>
           <t>Prestation</t>
         </is>
       </c>
-      <c r="C31" s="66" t="inlineStr">
+      <c r="C31" s="71" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="66" t="inlineStr">
+      <c r="A32" s="71" t="inlineStr">
         <is>
           <t>h_unit</t>
         </is>
       </c>
-      <c r="B32" s="66" t="inlineStr">
+      <c r="B32" s="71" t="inlineStr">
         <is>
           <t>Unité</t>
         </is>
       </c>
-      <c r="C32" s="66" t="inlineStr">
+      <c r="C32" s="71" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="66" t="inlineStr">
+      <c r="A33" s="71" t="inlineStr">
         <is>
           <t>h_pu</t>
         </is>
       </c>
-      <c r="B33" s="66" t="inlineStr">
+      <c r="B33" s="71" t="inlineStr">
         <is>
           <t>Prix unitaire €</t>
         </is>
       </c>
-      <c r="C33" s="66" t="inlineStr">
+      <c r="C33" s="71" t="inlineStr">
         <is>
           <t>Unit price €</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="66" t="inlineStr">
+      <c r="A34" s="71" t="inlineStr">
         <is>
           <t>h_tot</t>
         </is>
       </c>
-      <c r="B34" s="66" t="inlineStr">
+      <c r="B34" s="71" t="inlineStr">
         <is>
           <t>Total €</t>
         </is>
       </c>
-      <c r="C34" s="66" t="inlineStr">
+      <c r="C34" s="71" t="inlineStr">
         <is>
           <t>Total €</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="66" t="inlineStr">
+      <c r="A35" s="71" t="inlineStr">
         <is>
           <t>h_det</t>
         </is>
       </c>
-      <c r="B35" s="66" t="inlineStr">
+      <c r="B35" s="71" t="inlineStr">
         <is>
           <t>Détail</t>
         </is>
       </c>
-      <c r="C35" s="66" t="inlineStr">
+      <c r="C35" s="71" t="inlineStr">
         <is>
           <t>Details</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="66" t="inlineStr">
+      <c r="A36" s="71" t="inlineStr">
         <is>
           <t>op_day</t>
         </is>
       </c>
-      <c r="B36" s="66" t="inlineStr">
+      <c r="B36" s="71" t="inlineStr">
         <is>
           <t>Opérateur · tarif journalier</t>
         </is>
       </c>
-      <c r="C36" s="66" t="inlineStr">
+      <c r="C36" s="71" t="inlineStr">
         <is>
           <t>Operator · daily rate</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="66" t="inlineStr">
+      <c r="A37" s="71" t="inlineStr">
         <is>
           <t>op_mob</t>
         </is>
       </c>
-      <c r="B37" s="66" t="inlineStr">
+      <c r="B37" s="71" t="inlineStr">
         <is>
           <t>Opérateur · Mob / Demob</t>
         </is>
       </c>
-      <c r="C37" s="66" t="inlineStr">
+      <c r="C37" s="71" t="inlineStr">
         <is>
           <t>Operator · Mob / Demob</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="66" t="inlineStr">
+      <c r="A38" s="71" t="inlineStr">
         <is>
           <t>tight</t>
         </is>
       </c>
-      <c r="B38" s="66" t="inlineStr">
+      <c r="B38" s="71" t="inlineStr">
         <is>
           <t>Serrage · prix par serrage</t>
         </is>
       </c>
-      <c r="C38" s="66" t="inlineStr">
+      <c r="C38" s="71" t="inlineStr">
         <is>
           <t>Tong &amp; make-up service · price per make-up</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="66" t="inlineStr">
+      <c r="A39" s="71" t="inlineStr">
         <is>
           <t>tr_mob</t>
         </is>
       </c>
-      <c r="B39" s="66" t="inlineStr">
+      <c r="B39" s="71" t="inlineStr">
         <is>
           <t>Transport MOB (Lons → chantier)</t>
         </is>
       </c>
-      <c r="C39" s="66" t="inlineStr">
+      <c r="C39" s="71" t="inlineStr">
         <is>
           <t>Transport MOB (Lons → site)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="66" t="inlineStr">
+      <c r="A40" s="71" t="inlineStr">
         <is>
           <t>tr_dem</t>
         </is>
       </c>
-      <c r="B40" s="66" t="inlineStr">
+      <c r="B40" s="71" t="inlineStr">
         <is>
           <t>Transport DEMOB (chantier → Lons)</t>
         </is>
       </c>
-      <c r="C40" s="66" t="inlineStr">
+      <c r="C40" s="71" t="inlineStr">
         <is>
           <t>Transport DEMOB (site → Lons)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="66" t="inlineStr">
+      <c r="A41" s="71" t="inlineStr">
         <is>
           <t>free</t>
         </is>
       </c>
-      <c r="B41" s="66" t="inlineStr">
+      <c r="B41" s="71" t="inlineStr">
         <is>
           <t>Option</t>
         </is>
       </c>
-      <c r="C41" s="66" t="inlineStr">
+      <c r="C41" s="71" t="inlineStr">
         <is>
           <t>Option</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="66" t="inlineStr">
+      <c r="A42" s="71" t="inlineStr">
         <is>
           <t>forfait</t>
         </is>
       </c>
-      <c r="B42" s="66" t="inlineStr">
+      <c r="B42" s="71" t="inlineStr">
         <is>
           <t>Forfait</t>
         </is>
       </c>
-      <c r="C42" s="66" t="inlineStr">
+      <c r="C42" s="71" t="inlineStr">
         <is>
           <t>Lump sum</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="66" t="inlineStr">
+      <c r="A43" s="71" t="inlineStr">
         <is>
           <t>at_cost</t>
         </is>
       </c>
-      <c r="B43" s="66" t="inlineStr">
+      <c r="B43" s="71" t="inlineStr">
         <is>
           <t>au coût réel +15 %</t>
         </is>
       </c>
-      <c r="C43" s="66" t="inlineStr">
+      <c r="C43" s="71" t="inlineStr">
         <is>
           <t>at cost +15%</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="66" t="inlineStr">
+      <c r="A44" s="71" t="inlineStr">
         <is>
           <t>tr_note</t>
         </is>
       </c>
-      <c r="B44" s="66" t="inlineStr">
+      <c r="B44" s="71" t="inlineStr">
         <is>
           <t>Transport organisé par Enedril</t>
         </is>
       </c>
-      <c r="C44" s="66" t="inlineStr">
+      <c r="C44" s="71" t="inlineStr">
         <is>
           <t>Transport organised by Enedril</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="66" t="inlineStr">
+      <c r="A45" s="71" t="inlineStr">
         <is>
           <t>ht</t>
         </is>
       </c>
-      <c r="B45" s="66" t="inlineStr">
+      <c r="B45" s="71" t="inlineStr">
         <is>
           <t>€ HT</t>
         </is>
       </c>
-      <c r="C45" s="66" t="inlineStr">
+      <c r="C45" s="71" t="inlineStr">
         <is>
           <t>€ excl. VAT</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="66" t="inlineStr">
+      <c r="A46" s="71" t="inlineStr">
         <is>
           <t>calc_det</t>
         </is>
       </c>
-      <c r="B46" s="66" t="inlineStr">
+      <c r="B46" s="71" t="inlineStr">
         <is>
           <t>j stand-by + %s j opérations + utilisations de charge (UC)</t>
         </is>
       </c>
-      <c r="C46" s="66" t="inlineStr">
+      <c r="C46" s="71" t="inlineStr">
         <is>
           <t>stand-by days + %s operation days + utilisation charges (UC)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="66" t="inlineStr">
+      <c r="A47" s="71" t="inlineStr">
         <is>
           <t>sec_cond</t>
         </is>
       </c>
-      <c r="B47" s="66" t="inlineStr">
+      <c r="B47" s="71" t="inlineStr">
         <is>
           <t>CONDITIONS PARTICULIÈRES · SPECIFIC CONDITIONS</t>
         </is>
       </c>
-      <c r="C47" s="66" t="inlineStr">
+      <c r="C47" s="71" t="inlineStr">
         <is>
           <t>SPECIFIC CONDITIONS · CONDITIONS PARTICULIÈRES</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="66" t="inlineStr">
+      <c r="A48" s="71" t="inlineStr">
         <is>
           <t>accept</t>
         </is>
       </c>
-      <c r="B48" s="66" t="inlineStr">
+      <c r="B48" s="71" t="inlineStr">
         <is>
           <t>BON POUR ACCORD</t>
         </is>
       </c>
-      <c r="C48" s="66" t="inlineStr">
+      <c r="C48" s="71" t="inlineStr">
         <is>
           <t>ACCEPTED BY</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="66" t="inlineStr">
+      <c r="A49" s="71" t="inlineStr">
         <is>
           <t>sig_name</t>
         </is>
       </c>
-      <c r="B49" s="66" t="inlineStr">
+      <c r="B49" s="71" t="inlineStr">
         <is>
           <t>Nom et qualité</t>
         </is>
       </c>
-      <c r="C49" s="66" t="inlineStr">
+      <c r="C49" s="71" t="inlineStr">
         <is>
           <t>Name and title</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="66" t="inlineStr">
+      <c r="A50" s="71" t="inlineStr">
         <is>
           <t>sig_date</t>
         </is>
       </c>
-      <c r="B50" s="66" t="inlineStr">
+      <c r="B50" s="71" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C50" s="66" t="inlineStr">
+      <c r="C50" s="71" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="66" t="inlineStr">
+      <c r="A51" s="71" t="inlineStr">
         <is>
           <t>sig_sig</t>
         </is>
       </c>
-      <c r="B51" s="66" t="inlineStr">
+      <c r="B51" s="71" t="inlineStr">
         <is>
           <t>Signature et cachet</t>
         </is>
       </c>
-      <c r="C51" s="66" t="inlineStr">
+      <c r="C51" s="71" t="inlineStr">
         <is>
           <t>Signature and stamp</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="66" t="inlineStr">
+      <c r="A52" s="71" t="inlineStr">
         <is>
           <t>lump</t>
         </is>
       </c>
-      <c r="B52" s="66" t="inlineStr">
+      <c r="B52" s="71" t="inlineStr">
         <is>
           <t>forfait</t>
         </is>
       </c>
-      <c r="C52" s="66" t="inlineStr">
+      <c r="C52" s="71" t="inlineStr">
         <is>
           <t>lump sum</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="66" t="inlineStr">
+      <c r="A53" s="71" t="inlineStr">
         <is>
           <t>sec_tight</t>
         </is>
       </c>
-      <c r="B53" s="66" t="inlineStr">
+      <c r="B53" s="71" t="inlineStr">
         <is>
           <t>SERRAGE · TONG &amp; MAKE-UP</t>
         </is>
       </c>
-      <c r="C53" s="66" t="inlineStr">
+      <c r="C53" s="71" t="inlineStr">
         <is>
           <t>TONG &amp; MAKE-UP SERVICE</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="66" t="inlineStr">
+      <c r="A54" s="71" t="inlineStr">
         <is>
           <t>sec_tr</t>
         </is>
       </c>
-      <c r="B54" s="66" t="inlineStr">
+      <c r="B54" s="71" t="inlineStr">
         <is>
           <t>TRANSPORT</t>
         </is>
       </c>
-      <c r="C54" s="66" t="inlineStr">
+      <c r="C54" s="71" t="inlineStr">
         <is>
           <t>TRANSPORT</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="66" t="inlineStr">
+      <c r="A55" s="71" t="inlineStr">
         <is>
           <t>sec_op</t>
         </is>
       </c>
-      <c r="B55" s="66" t="inlineStr">
+      <c r="B55" s="71" t="inlineStr">
         <is>
           <t>OPÉRATEURS</t>
         </is>
       </c>
-      <c r="C55" s="66" t="inlineStr">
+      <c r="C55" s="71" t="inlineStr">
         <is>
           <t>OPERATORS</t>
         </is>

--- a/devis_2027/Devis_Enedril_2027.xlsx
+++ b/devis_2027/Devis_Enedril_2027.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 Devis" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listes" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Textes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flux" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'4 Devis'!$A$1:$K$68</definedName>
@@ -29,7 +30,7 @@
     <numFmt numFmtId="166" formatCode="#,##0;-#,##0;;@"/>
     <numFmt numFmtId="167" formatCode="#,##0.00 &quot;€&quot;"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="30">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -163,11 +164,6 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="00B8C4D2"/>
-      <sz val="7"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="0051647A"/>
       <sz val="9.5"/>
@@ -179,39 +175,14 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00E2231A"/>
-      <sz val="9"/>
+      <color rgb="00B8C4D2"/>
+      <sz val="7"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="8.5"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="000B1B2E"/>
-      <sz val="9.5"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="15"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="20"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="0008203F"/>
-      <sz val="9.5"/>
+      <color rgb="00E2231A"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -353,7 +324,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -448,65 +419,29 @@
     <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="4" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -516,7 +451,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -530,7 +465,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="7">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -558,6 +493,32 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <name val="Calibri"/>
+        <b val="1"/>
+        <color rgb="00FFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="000A4FA0"/>
+          <bgColor rgb="000A4FA0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <i val="1"/>
+        <color rgb="0008203F"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00EAF6FD"/>
+          <bgColor rgb="00EAF6FD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <border>
         <bottom style="thin">
           <color rgb="00D5DEE8"/>
@@ -578,30 +539,6 @@
         <i val="1"/>
         <color rgb="0000AEEF"/>
       </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="000A4FA0"/>
-          <bgColor rgb="000A4FA0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="0008203F"/>
-          <bgColor rgb="0008203F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00EAF6FD"/>
-          <bgColor rgb="00EAF6FD"/>
-        </patternFill>
-      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1145,35 +1082,28 @@
     <row r="11" ht="22" customHeight="1">
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Délai de mise à dispo</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="n"/>
+          <t>Conditions de règlement</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>30 jours date de facture / 30 days invoice date</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Conditions de règlement</t>
+          <t>Facturation WE et jours fériés</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>30 jours date de facture / 30 days invoice date</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>Facturation WE et jours fériés</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
           <t>Non</t>
         </is>
       </c>
     </row>
+    <row r="13" ht="22" customHeight="1"/>
     <row r="16">
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -1196,10 +1126,10 @@
     <dataValidation sqref="F10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="warning">
       <formula1>=Listes!$D$2:$D$12</formula1>
     </dataValidation>
-    <dataValidation sqref="F12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="warning">
+    <dataValidation sqref="F11" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="warning">
       <formula1>=Listes!$F$2:$F$12</formula1>
     </dataValidation>
-    <dataValidation sqref="F13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="stop">
+    <dataValidation sqref="F12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="stop">
       <formula1>=Listes!$G$2:$G$12</formula1>
     </dataValidation>
   </dataValidations>
@@ -2093,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2346,7 +2276,7 @@
         </is>
       </c>
       <c r="H13" s="23">
-        <f>IF(C13="Oui",IF(G13="Forfait calculé (S + O + UC)",IF(F13&lt;&gt;"",F13,C17),N(E13)*N(F13)),0)</f>
+        <f>IF(C13="Oui",IF(G13="Forfait calculé (S + O + UC)",IF(F13&lt;&gt;"",F13,C17+IF(AND(C19="Oui",C8="Oui"),H8,0)+IF(C20="Oui",IF(C9="Oui",H9,0)+IF(C10="Oui",H10,0),0)),N(E13)*N(F13)),0)</f>
         <v/>
       </c>
     </row>
@@ -2373,7 +2303,7 @@
       </c>
       <c r="D15" s="25" t="inlineStr">
         <is>
-          <t>Forfait habituel : 3 jours de stand-by + 2 jours d’opérations + toutes les utilisations de charge (UC), sur les lignes « Inclus au forfait » de l’onglet 2. Laisser « Prix € » vide pour utiliser ce calcul, ou saisir un prix pour le remplacer. Qté sert pour le mode « par jour » (nombre de jours).</t>
+          <t>Forfait habituel : 3 jours de stand-by + 2 jours d’opérations + toutes les utilisations de charge (UC), sur les lignes « Inclus au forfait » de l’onglet 2. Laisser « Prix € » vide pour utiliser ce calcul (plus serrage et transport si cochés), ou saisir un prix pour le remplacer. Qté sert pour le mode « par jour » (nombre de jours).</t>
         </is>
       </c>
     </row>
@@ -2411,39 +2341,75 @@
       </c>
       <c r="D18" s="27" t="inlineStr">
         <is>
-          <t>Oui : chaque ligne garde ses tarifs ; Non : elles s’affichent « incl. ». Dans les deux cas le prix final du forfait apparaît dans le bandeau.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="20" t="inlineStr">
+          <t>Oui : chaque ligne garde ses tarifs ; Non : « incl. ». Dans les deux cas le prix final du forfait apparaît dans le bandeau.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Inclure le serrage dans le forfait</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>Le prix du serrage s’ajoute au montant calculé du forfait.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Inclure le transport dans le forfait</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t>Le transport MOB et DEMOB (s’ils ont un prix forfaitaire) s’ajoute au montant calculé.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>Rappels</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="28" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="28" t="inlineStr">
         <is>
           <t>Transport « Coût réel +15 % » : aucun montant affiché. Choisir « Forfait » pour imposer un prix.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="28" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="28" t="inlineStr">
         <is>
           <t>Lignes couvertes par le forfait : mettre « Oui » dans « Inclus au forfait » (onglet 2). Elles s’affichent « incl. » sur le devis.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D14:H14"/>
     <mergeCell ref="D15:H17"/>
     <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="B12:H12"/>
   </mergeCells>
-  <dataValidations count="13">
+  <dataValidations count="15">
     <dataValidation sqref="C6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="stop">
       <formula1>=Listes!$G$2:$G$12</formula1>
     </dataValidation>
@@ -2483,6 +2449,12 @@
     <dataValidation sqref="C18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="stop">
       <formula1>=Listes!$G$2:$G$12</formula1>
     </dataValidation>
+    <dataValidation sqref="C19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="stop">
+      <formula1>=Listes!$G$2:$G$12</formula1>
+    </dataValidation>
+    <dataValidation sqref="C20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur" error="Choisir une valeur de la liste." type="list" errorStyle="stop">
+      <formula1>=Listes!$G$2:$G$12</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -2496,7 +2468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L68"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -2511,6 +2483,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="1.5" customWidth="1" min="11" max="11"/>
     <col hidden="1" width="13" customWidth="1" min="12" max="12"/>
+    <col hidden="1" width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -2651,7 +2624,7 @@
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="B11" s="31">
-        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("lead",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
+        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("pay",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
         <v/>
       </c>
       <c r="D11" s="31">
@@ -2670,7 +2643,7 @@
       </c>
       <c r="C12" s="33" t="n"/>
       <c r="D12" s="32">
-        <f>""&amp;'1 Affaire'!$F$13</f>
+        <f>""&amp;'1 Affaire'!$F$12</f>
         <v/>
       </c>
       <c r="E12" s="33" t="n"/>
@@ -2683,1340 +2656,1906 @@
       <c r="I12" s="33" t="n"/>
       <c r="J12" s="33" t="n"/>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="B13" s="31">
-        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("pay",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="19" customHeight="1">
-      <c r="B14" s="32">
-        <f>""&amp;'1 Affaire'!$F$12</f>
-        <v/>
-      </c>
-      <c r="C14" s="33" t="n"/>
-    </row>
-    <row r="15" ht="8" customHeight="1"/>
-    <row r="16" ht="20" customHeight="1">
-      <c r="B16" s="34">
+    <row r="13" ht="8" customHeight="1"/>
+    <row r="14" ht="20" customHeight="1">
+      <c r="B14" s="34">
         <f>INDEX(Textes!$B$2:$C$55,MATCH("sec_eq",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="C16" s="35" t="n"/>
-      <c r="D16" s="35" t="n"/>
-      <c r="E16" s="35" t="n"/>
-      <c r="F16" s="35" t="n"/>
-      <c r="G16" s="35" t="n"/>
-      <c r="H16" s="35" t="n"/>
-      <c r="I16" s="35" t="n"/>
-      <c r="J16" s="35" t="n"/>
-    </row>
-    <row r="17" ht="46" customHeight="1">
-      <c r="B17" s="36">
+      <c r="C14" s="35" t="n"/>
+      <c r="D14" s="35" t="n"/>
+      <c r="E14" s="35" t="n"/>
+      <c r="F14" s="35" t="n"/>
+      <c r="G14" s="35" t="n"/>
+      <c r="H14" s="35" t="n"/>
+      <c r="I14" s="35" t="n"/>
+      <c r="J14" s="35" t="n"/>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="B15" s="36">
         <f>INDEX(Textes!$B$2:$C$55,MATCH("h_n",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="C17" s="37">
+      <c r="C15" s="37">
         <f>INDEX(Textes!$B$2:$C$55,MATCH("h_desc",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="D17" s="36">
+      <c r="D15" s="36">
         <f>INDEX(Textes!$B$2:$C$55,MATCH("h_qty",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="E17" s="36">
+      <c r="E15" s="36">
         <f>INDEX(Textes!$B$2:$C$55,MATCH("h_s",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="F17" s="36">
+      <c r="F15" s="36">
         <f>INDEX(Textes!$B$2:$C$55,MATCH("h_o",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="G17" s="36">
+      <c r="G15" s="36">
         <f>INDEX(Textes!$B$2:$C$55,MATCH("h_uc",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="H17" s="36">
+      <c r="H15" s="36">
         <f>INDEX(Textes!$B$2:$C$55,MATCH("h_lih",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="I17" s="36">
+      <c r="I15" s="36">
         <f>INDEX(Textes!$B$2:$C$55,MATCH("h_insp",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="J17" s="36">
+      <c r="J15" s="36">
         <f>INDEX(Textes!$B$2:$C$55,MATCH("h_rest",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="21" customHeight="1">
+    <row r="16" ht="22" customHeight="1">
+      <c r="B16" s="38">
+        <f>IF($L16="","",INDEX(Flux!$D$2:$D$35,$L16))</f>
+        <v/>
+      </c>
+      <c r="C16" s="39">
+        <f>IF($L16="","",INDEX(Flux!$E$2:$E$35,$L16))</f>
+        <v/>
+      </c>
+      <c r="D16" s="40">
+        <f>IF($L16="","",INDEX(Flux!$F$2:$F$35,$L16))</f>
+        <v/>
+      </c>
+      <c r="E16" s="41">
+        <f>IF($L16="","",INDEX(Flux!$G$2:$G$35,$L16))</f>
+        <v/>
+      </c>
+      <c r="F16" s="41">
+        <f>IF($L16="","",INDEX(Flux!$H$2:$H$35,$L16))</f>
+        <v/>
+      </c>
+      <c r="G16" s="41">
+        <f>IF($L16="","",INDEX(Flux!$I$2:$I$35,$L16))</f>
+        <v/>
+      </c>
+      <c r="H16" s="41">
+        <f>IF($L16="","",INDEX(Flux!$J$2:$J$35,$L16))</f>
+        <v/>
+      </c>
+      <c r="I16" s="41">
+        <f>IF($L16="","",INDEX(Flux!$K$2:$K$35,$L16))</f>
+        <v/>
+      </c>
+      <c r="J16" s="41">
+        <f>IF($L16="","",INDEX(Flux!$L$2:$L$35,$L16))</f>
+        <v/>
+      </c>
+      <c r="L16" s="42">
+        <f>IFERROR(MATCH(1,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M16" s="42">
+        <f>IF(L16="","",INDEX(Flux!$C$2:$C$35,L16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="38">
+        <f>IF($L17="","",INDEX(Flux!$D$2:$D$35,$L17))</f>
+        <v/>
+      </c>
+      <c r="C17" s="39">
+        <f>IF($L17="","",INDEX(Flux!$E$2:$E$35,$L17))</f>
+        <v/>
+      </c>
+      <c r="D17" s="40">
+        <f>IF($L17="","",INDEX(Flux!$F$2:$F$35,$L17))</f>
+        <v/>
+      </c>
+      <c r="E17" s="41">
+        <f>IF($L17="","",INDEX(Flux!$G$2:$G$35,$L17))</f>
+        <v/>
+      </c>
+      <c r="F17" s="41">
+        <f>IF($L17="","",INDEX(Flux!$H$2:$H$35,$L17))</f>
+        <v/>
+      </c>
+      <c r="G17" s="41">
+        <f>IF($L17="","",INDEX(Flux!$I$2:$I$35,$L17))</f>
+        <v/>
+      </c>
+      <c r="H17" s="41">
+        <f>IF($L17="","",INDEX(Flux!$J$2:$J$35,$L17))</f>
+        <v/>
+      </c>
+      <c r="I17" s="41">
+        <f>IF($L17="","",INDEX(Flux!$K$2:$K$35,$L17))</f>
+        <v/>
+      </c>
+      <c r="J17" s="41">
+        <f>IF($L17="","",INDEX(Flux!$L$2:$L$35,$L17))</f>
+        <v/>
+      </c>
+      <c r="L17" s="42">
+        <f>IFERROR(MATCH(2,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M17" s="42">
+        <f>IF(L17="","",INDEX(Flux!$C$2:$C$35,L17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
       <c r="B18" s="38">
-        <f>IF(AND('2 Matériel'!$L6&gt;0,NOT('2 Matériel'!$B6="Oui")),'2 Matériel'!$A6,"")</f>
+        <f>IF($L18="","",INDEX(Flux!$D$2:$D$35,$L18))</f>
         <v/>
       </c>
       <c r="C18" s="39">
-        <f>IF('2 Matériel'!$L6&gt;0,IF('2 Matériel'!$B6="Oui",UPPER('2 Matériel'!$C6),'2 Matériel'!$C6&amp;IF(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <f>IF($L18="","",INDEX(Flux!$E$2:$E$35,$L18))</f>
         <v/>
       </c>
       <c r="D18" s="40">
-        <f>IF(AND('2 Matériel'!$L6&gt;0,NOT('2 Matériel'!$B6="Oui")),'2 Matériel'!$L6,"")</f>
+        <f>IF($L18="","",INDEX(Flux!$F$2:$F$35,$L18))</f>
         <v/>
       </c>
       <c r="E18" s="41">
-        <f>IF(AND('2 Matériel'!$L6&gt;0,NOT('2 Matériel'!$B6="Oui")),IF(AND(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E6="","",'2 Matériel'!$E6)),"")</f>
+        <f>IF($L18="","",INDEX(Flux!$G$2:$G$35,$L18))</f>
         <v/>
       </c>
       <c r="F18" s="41">
-        <f>IF(AND('2 Matériel'!$L6&gt;0,NOT('2 Matériel'!$B6="Oui")),IF(AND(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F6="","",'2 Matériel'!$F6)),"")</f>
+        <f>IF($L18="","",INDEX(Flux!$H$2:$H$35,$L18))</f>
         <v/>
       </c>
       <c r="G18" s="41">
-        <f>IF(AND('2 Matériel'!$L6&gt;0,NOT('2 Matériel'!$B6="Oui")),IF(AND(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G6="","",'2 Matériel'!$G6)),"")</f>
+        <f>IF($L18="","",INDEX(Flux!$I$2:$I$35,$L18))</f>
         <v/>
       </c>
       <c r="H18" s="41">
-        <f>IF(AND('2 Matériel'!$L6&gt;0,NOT('2 Matériel'!$B6="Oui")),IF(AND(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H6="","",'2 Matériel'!$H6)),"")</f>
+        <f>IF($L18="","",INDEX(Flux!$J$2:$J$35,$L18))</f>
         <v/>
       </c>
       <c r="I18" s="41">
-        <f>IF(AND('2 Matériel'!$L6&gt;0,NOT('2 Matériel'!$B6="Oui")),IF(AND(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I6="","",'2 Matériel'!$I6)),"")</f>
+        <f>IF($L18="","",INDEX(Flux!$K$2:$K$35,$L18))</f>
         <v/>
       </c>
       <c r="J18" s="41">
-        <f>IF(AND('2 Matériel'!$L6&gt;0,NOT('2 Matériel'!$B6="Oui")),IF(AND(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J6="","",'2 Matériel'!$J6)),"")</f>
+        <f>IF($L18="","",INDEX(Flux!$L$2:$L$35,$L18))</f>
         <v/>
       </c>
       <c r="L18" s="42">
-        <f>IF(AND('2 Matériel'!$L6&gt;0,'2 Matériel'!$B6="Oui"),1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="21" customHeight="1">
+        <f>IFERROR(MATCH(3,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M18" s="42">
+        <f>IF(L18="","",INDEX(Flux!$C$2:$C$35,L18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
       <c r="B19" s="38">
-        <f>IF(AND('2 Matériel'!$L7&gt;0,NOT('2 Matériel'!$B7="Oui")),'2 Matériel'!$A7,"")</f>
+        <f>IF($L19="","",INDEX(Flux!$D$2:$D$35,$L19))</f>
         <v/>
       </c>
       <c r="C19" s="39">
-        <f>IF('2 Matériel'!$L7&gt;0,IF('2 Matériel'!$B7="Oui",UPPER('2 Matériel'!$C7),'2 Matériel'!$C7&amp;IF(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <f>IF($L19="","",INDEX(Flux!$E$2:$E$35,$L19))</f>
         <v/>
       </c>
       <c r="D19" s="40">
-        <f>IF(AND('2 Matériel'!$L7&gt;0,NOT('2 Matériel'!$B7="Oui")),'2 Matériel'!$L7,"")</f>
+        <f>IF($L19="","",INDEX(Flux!$F$2:$F$35,$L19))</f>
         <v/>
       </c>
       <c r="E19" s="41">
-        <f>IF(AND('2 Matériel'!$L7&gt;0,NOT('2 Matériel'!$B7="Oui")),IF(AND(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E7="","",'2 Matériel'!$E7)),"")</f>
+        <f>IF($L19="","",INDEX(Flux!$G$2:$G$35,$L19))</f>
         <v/>
       </c>
       <c r="F19" s="41">
-        <f>IF(AND('2 Matériel'!$L7&gt;0,NOT('2 Matériel'!$B7="Oui")),IF(AND(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F7="","",'2 Matériel'!$F7)),"")</f>
+        <f>IF($L19="","",INDEX(Flux!$H$2:$H$35,$L19))</f>
         <v/>
       </c>
       <c r="G19" s="41">
-        <f>IF(AND('2 Matériel'!$L7&gt;0,NOT('2 Matériel'!$B7="Oui")),IF(AND(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G7="","",'2 Matériel'!$G7)),"")</f>
+        <f>IF($L19="","",INDEX(Flux!$I$2:$I$35,$L19))</f>
         <v/>
       </c>
       <c r="H19" s="41">
-        <f>IF(AND('2 Matériel'!$L7&gt;0,NOT('2 Matériel'!$B7="Oui")),IF(AND(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H7="","",'2 Matériel'!$H7)),"")</f>
+        <f>IF($L19="","",INDEX(Flux!$J$2:$J$35,$L19))</f>
         <v/>
       </c>
       <c r="I19" s="41">
-        <f>IF(AND('2 Matériel'!$L7&gt;0,NOT('2 Matériel'!$B7="Oui")),IF(AND(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I7="","",'2 Matériel'!$I7)),"")</f>
+        <f>IF($L19="","",INDEX(Flux!$K$2:$K$35,$L19))</f>
         <v/>
       </c>
       <c r="J19" s="41">
-        <f>IF(AND('2 Matériel'!$L7&gt;0,NOT('2 Matériel'!$B7="Oui")),IF(AND(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J7="","",'2 Matériel'!$J7)),"")</f>
+        <f>IF($L19="","",INDEX(Flux!$L$2:$L$35,$L19))</f>
         <v/>
       </c>
       <c r="L19" s="42">
-        <f>IF(AND('2 Matériel'!$L7&gt;0,'2 Matériel'!$B7="Oui"),1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="21" customHeight="1">
+        <f>IFERROR(MATCH(4,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M19" s="42">
+        <f>IF(L19="","",INDEX(Flux!$C$2:$C$35,L19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
       <c r="B20" s="38">
-        <f>IF(AND('2 Matériel'!$L8&gt;0,NOT('2 Matériel'!$B8="Oui")),'2 Matériel'!$A8,"")</f>
+        <f>IF($L20="","",INDEX(Flux!$D$2:$D$35,$L20))</f>
         <v/>
       </c>
       <c r="C20" s="39">
-        <f>IF('2 Matériel'!$L8&gt;0,IF('2 Matériel'!$B8="Oui",UPPER('2 Matériel'!$C8),'2 Matériel'!$C8&amp;IF(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <f>IF($L20="","",INDEX(Flux!$E$2:$E$35,$L20))</f>
         <v/>
       </c>
       <c r="D20" s="40">
-        <f>IF(AND('2 Matériel'!$L8&gt;0,NOT('2 Matériel'!$B8="Oui")),'2 Matériel'!$L8,"")</f>
+        <f>IF($L20="","",INDEX(Flux!$F$2:$F$35,$L20))</f>
         <v/>
       </c>
       <c r="E20" s="41">
-        <f>IF(AND('2 Matériel'!$L8&gt;0,NOT('2 Matériel'!$B8="Oui")),IF(AND(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E8="","",'2 Matériel'!$E8)),"")</f>
+        <f>IF($L20="","",INDEX(Flux!$G$2:$G$35,$L20))</f>
         <v/>
       </c>
       <c r="F20" s="41">
-        <f>IF(AND('2 Matériel'!$L8&gt;0,NOT('2 Matériel'!$B8="Oui")),IF(AND(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F8="","",'2 Matériel'!$F8)),"")</f>
+        <f>IF($L20="","",INDEX(Flux!$H$2:$H$35,$L20))</f>
         <v/>
       </c>
       <c r="G20" s="41">
-        <f>IF(AND('2 Matériel'!$L8&gt;0,NOT('2 Matériel'!$B8="Oui")),IF(AND(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G8="","",'2 Matériel'!$G8)),"")</f>
+        <f>IF($L20="","",INDEX(Flux!$I$2:$I$35,$L20))</f>
         <v/>
       </c>
       <c r="H20" s="41">
-        <f>IF(AND('2 Matériel'!$L8&gt;0,NOT('2 Matériel'!$B8="Oui")),IF(AND(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H8="","",'2 Matériel'!$H8)),"")</f>
+        <f>IF($L20="","",INDEX(Flux!$J$2:$J$35,$L20))</f>
         <v/>
       </c>
       <c r="I20" s="41">
-        <f>IF(AND('2 Matériel'!$L8&gt;0,NOT('2 Matériel'!$B8="Oui")),IF(AND(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I8="","",'2 Matériel'!$I8)),"")</f>
+        <f>IF($L20="","",INDEX(Flux!$K$2:$K$35,$L20))</f>
         <v/>
       </c>
       <c r="J20" s="41">
-        <f>IF(AND('2 Matériel'!$L8&gt;0,NOT('2 Matériel'!$B8="Oui")),IF(AND(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J8="","",'2 Matériel'!$J8)),"")</f>
+        <f>IF($L20="","",INDEX(Flux!$L$2:$L$35,$L20))</f>
         <v/>
       </c>
       <c r="L20" s="42">
-        <f>IF(AND('2 Matériel'!$L8&gt;0,'2 Matériel'!$B8="Oui"),1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="21" customHeight="1">
+        <f>IFERROR(MATCH(5,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M20" s="42">
+        <f>IF(L20="","",INDEX(Flux!$C$2:$C$35,L20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
       <c r="B21" s="38">
-        <f>IF(AND('2 Matériel'!$L9&gt;0,NOT('2 Matériel'!$B9="Oui")),'2 Matériel'!$A9,"")</f>
+        <f>IF($L21="","",INDEX(Flux!$D$2:$D$35,$L21))</f>
         <v/>
       </c>
       <c r="C21" s="39">
-        <f>IF('2 Matériel'!$L9&gt;0,IF('2 Matériel'!$B9="Oui",UPPER('2 Matériel'!$C9),'2 Matériel'!$C9&amp;IF(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <f>IF($L21="","",INDEX(Flux!$E$2:$E$35,$L21))</f>
         <v/>
       </c>
       <c r="D21" s="40">
-        <f>IF(AND('2 Matériel'!$L9&gt;0,NOT('2 Matériel'!$B9="Oui")),'2 Matériel'!$L9,"")</f>
+        <f>IF($L21="","",INDEX(Flux!$F$2:$F$35,$L21))</f>
         <v/>
       </c>
       <c r="E21" s="41">
-        <f>IF(AND('2 Matériel'!$L9&gt;0,NOT('2 Matériel'!$B9="Oui")),IF(AND(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E9="","",'2 Matériel'!$E9)),"")</f>
+        <f>IF($L21="","",INDEX(Flux!$G$2:$G$35,$L21))</f>
         <v/>
       </c>
       <c r="F21" s="41">
-        <f>IF(AND('2 Matériel'!$L9&gt;0,NOT('2 Matériel'!$B9="Oui")),IF(AND(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F9="","",'2 Matériel'!$F9)),"")</f>
+        <f>IF($L21="","",INDEX(Flux!$H$2:$H$35,$L21))</f>
         <v/>
       </c>
       <c r="G21" s="41">
-        <f>IF(AND('2 Matériel'!$L9&gt;0,NOT('2 Matériel'!$B9="Oui")),IF(AND(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G9="","",'2 Matériel'!$G9)),"")</f>
+        <f>IF($L21="","",INDEX(Flux!$I$2:$I$35,$L21))</f>
         <v/>
       </c>
       <c r="H21" s="41">
-        <f>IF(AND('2 Matériel'!$L9&gt;0,NOT('2 Matériel'!$B9="Oui")),IF(AND(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H9="","",'2 Matériel'!$H9)),"")</f>
+        <f>IF($L21="","",INDEX(Flux!$J$2:$J$35,$L21))</f>
         <v/>
       </c>
       <c r="I21" s="41">
-        <f>IF(AND('2 Matériel'!$L9&gt;0,NOT('2 Matériel'!$B9="Oui")),IF(AND(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I9="","",'2 Matériel'!$I9)),"")</f>
+        <f>IF($L21="","",INDEX(Flux!$K$2:$K$35,$L21))</f>
         <v/>
       </c>
       <c r="J21" s="41">
-        <f>IF(AND('2 Matériel'!$L9&gt;0,NOT('2 Matériel'!$B9="Oui")),IF(AND(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J9="","",'2 Matériel'!$J9)),"")</f>
+        <f>IF($L21="","",INDEX(Flux!$L$2:$L$35,$L21))</f>
         <v/>
       </c>
       <c r="L21" s="42">
-        <f>IF(AND('2 Matériel'!$L9&gt;0,'2 Matériel'!$B9="Oui"),1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="21" customHeight="1">
+        <f>IFERROR(MATCH(6,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M21" s="42">
+        <f>IF(L21="","",INDEX(Flux!$C$2:$C$35,L21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
       <c r="B22" s="38">
-        <f>IF(AND('2 Matériel'!$L10&gt;0,NOT('2 Matériel'!$B10="Oui")),'2 Matériel'!$A10,"")</f>
+        <f>IF($L22="","",INDEX(Flux!$D$2:$D$35,$L22))</f>
         <v/>
       </c>
       <c r="C22" s="39">
-        <f>IF('2 Matériel'!$L10&gt;0,IF('2 Matériel'!$B10="Oui",UPPER('2 Matériel'!$C10),'2 Matériel'!$C10&amp;IF(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <f>IF($L22="","",INDEX(Flux!$E$2:$E$35,$L22))</f>
         <v/>
       </c>
       <c r="D22" s="40">
-        <f>IF(AND('2 Matériel'!$L10&gt;0,NOT('2 Matériel'!$B10="Oui")),'2 Matériel'!$L10,"")</f>
+        <f>IF($L22="","",INDEX(Flux!$F$2:$F$35,$L22))</f>
         <v/>
       </c>
       <c r="E22" s="41">
-        <f>IF(AND('2 Matériel'!$L10&gt;0,NOT('2 Matériel'!$B10="Oui")),IF(AND(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E10="","",'2 Matériel'!$E10)),"")</f>
+        <f>IF($L22="","",INDEX(Flux!$G$2:$G$35,$L22))</f>
         <v/>
       </c>
       <c r="F22" s="41">
-        <f>IF(AND('2 Matériel'!$L10&gt;0,NOT('2 Matériel'!$B10="Oui")),IF(AND(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F10="","",'2 Matériel'!$F10)),"")</f>
+        <f>IF($L22="","",INDEX(Flux!$H$2:$H$35,$L22))</f>
         <v/>
       </c>
       <c r="G22" s="41">
-        <f>IF(AND('2 Matériel'!$L10&gt;0,NOT('2 Matériel'!$B10="Oui")),IF(AND(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G10="","",'2 Matériel'!$G10)),"")</f>
+        <f>IF($L22="","",INDEX(Flux!$I$2:$I$35,$L22))</f>
         <v/>
       </c>
       <c r="H22" s="41">
-        <f>IF(AND('2 Matériel'!$L10&gt;0,NOT('2 Matériel'!$B10="Oui")),IF(AND(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H10="","",'2 Matériel'!$H10)),"")</f>
+        <f>IF($L22="","",INDEX(Flux!$J$2:$J$35,$L22))</f>
         <v/>
       </c>
       <c r="I22" s="41">
-        <f>IF(AND('2 Matériel'!$L10&gt;0,NOT('2 Matériel'!$B10="Oui")),IF(AND(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I10="","",'2 Matériel'!$I10)),"")</f>
+        <f>IF($L22="","",INDEX(Flux!$K$2:$K$35,$L22))</f>
         <v/>
       </c>
       <c r="J22" s="41">
-        <f>IF(AND('2 Matériel'!$L10&gt;0,NOT('2 Matériel'!$B10="Oui")),IF(AND(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J10="","",'2 Matériel'!$J10)),"")</f>
+        <f>IF($L22="","",INDEX(Flux!$L$2:$L$35,$L22))</f>
         <v/>
       </c>
       <c r="L22" s="42">
-        <f>IF(AND('2 Matériel'!$L10&gt;0,'2 Matériel'!$B10="Oui"),1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="21" customHeight="1">
+        <f>IFERROR(MATCH(7,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M22" s="42">
+        <f>IF(L22="","",INDEX(Flux!$C$2:$C$35,L22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
       <c r="B23" s="38">
-        <f>IF(AND('2 Matériel'!$L11&gt;0,NOT('2 Matériel'!$B11="Oui")),'2 Matériel'!$A11,"")</f>
+        <f>IF($L23="","",INDEX(Flux!$D$2:$D$35,$L23))</f>
         <v/>
       </c>
       <c r="C23" s="39">
-        <f>IF('2 Matériel'!$L11&gt;0,IF('2 Matériel'!$B11="Oui",UPPER('2 Matériel'!$C11),'2 Matériel'!$C11&amp;IF(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <f>IF($L23="","",INDEX(Flux!$E$2:$E$35,$L23))</f>
         <v/>
       </c>
       <c r="D23" s="40">
-        <f>IF(AND('2 Matériel'!$L11&gt;0,NOT('2 Matériel'!$B11="Oui")),'2 Matériel'!$L11,"")</f>
+        <f>IF($L23="","",INDEX(Flux!$F$2:$F$35,$L23))</f>
         <v/>
       </c>
       <c r="E23" s="41">
-        <f>IF(AND('2 Matériel'!$L11&gt;0,NOT('2 Matériel'!$B11="Oui")),IF(AND(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E11="","",'2 Matériel'!$E11)),"")</f>
+        <f>IF($L23="","",INDEX(Flux!$G$2:$G$35,$L23))</f>
         <v/>
       </c>
       <c r="F23" s="41">
-        <f>IF(AND('2 Matériel'!$L11&gt;0,NOT('2 Matériel'!$B11="Oui")),IF(AND(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F11="","",'2 Matériel'!$F11)),"")</f>
+        <f>IF($L23="","",INDEX(Flux!$H$2:$H$35,$L23))</f>
         <v/>
       </c>
       <c r="G23" s="41">
-        <f>IF(AND('2 Matériel'!$L11&gt;0,NOT('2 Matériel'!$B11="Oui")),IF(AND(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G11="","",'2 Matériel'!$G11)),"")</f>
+        <f>IF($L23="","",INDEX(Flux!$I$2:$I$35,$L23))</f>
         <v/>
       </c>
       <c r="H23" s="41">
-        <f>IF(AND('2 Matériel'!$L11&gt;0,NOT('2 Matériel'!$B11="Oui")),IF(AND(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H11="","",'2 Matériel'!$H11)),"")</f>
+        <f>IF($L23="","",INDEX(Flux!$J$2:$J$35,$L23))</f>
         <v/>
       </c>
       <c r="I23" s="41">
-        <f>IF(AND('2 Matériel'!$L11&gt;0,NOT('2 Matériel'!$B11="Oui")),IF(AND(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I11="","",'2 Matériel'!$I11)),"")</f>
+        <f>IF($L23="","",INDEX(Flux!$K$2:$K$35,$L23))</f>
         <v/>
       </c>
       <c r="J23" s="41">
-        <f>IF(AND('2 Matériel'!$L11&gt;0,NOT('2 Matériel'!$B11="Oui")),IF(AND(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J11="","",'2 Matériel'!$J11)),"")</f>
+        <f>IF($L23="","",INDEX(Flux!$L$2:$L$35,$L23))</f>
         <v/>
       </c>
       <c r="L23" s="42">
-        <f>IF(AND('2 Matériel'!$L11&gt;0,'2 Matériel'!$B11="Oui"),1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="21" customHeight="1">
+        <f>IFERROR(MATCH(8,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M23" s="42">
+        <f>IF(L23="","",INDEX(Flux!$C$2:$C$35,L23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
       <c r="B24" s="38">
-        <f>IF(AND('2 Matériel'!$L12&gt;0,NOT('2 Matériel'!$B12="Oui")),'2 Matériel'!$A12,"")</f>
+        <f>IF($L24="","",INDEX(Flux!$D$2:$D$35,$L24))</f>
         <v/>
       </c>
       <c r="C24" s="39">
-        <f>IF('2 Matériel'!$L12&gt;0,IF('2 Matériel'!$B12="Oui",UPPER('2 Matériel'!$C12),'2 Matériel'!$C12&amp;IF(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <f>IF($L24="","",INDEX(Flux!$E$2:$E$35,$L24))</f>
         <v/>
       </c>
       <c r="D24" s="40">
-        <f>IF(AND('2 Matériel'!$L12&gt;0,NOT('2 Matériel'!$B12="Oui")),'2 Matériel'!$L12,"")</f>
+        <f>IF($L24="","",INDEX(Flux!$F$2:$F$35,$L24))</f>
         <v/>
       </c>
       <c r="E24" s="41">
-        <f>IF(AND('2 Matériel'!$L12&gt;0,NOT('2 Matériel'!$B12="Oui")),IF(AND(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E12="","",'2 Matériel'!$E12)),"")</f>
+        <f>IF($L24="","",INDEX(Flux!$G$2:$G$35,$L24))</f>
         <v/>
       </c>
       <c r="F24" s="41">
-        <f>IF(AND('2 Matériel'!$L12&gt;0,NOT('2 Matériel'!$B12="Oui")),IF(AND(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F12="","",'2 Matériel'!$F12)),"")</f>
+        <f>IF($L24="","",INDEX(Flux!$H$2:$H$35,$L24))</f>
         <v/>
       </c>
       <c r="G24" s="41">
-        <f>IF(AND('2 Matériel'!$L12&gt;0,NOT('2 Matériel'!$B12="Oui")),IF(AND(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G12="","",'2 Matériel'!$G12)),"")</f>
+        <f>IF($L24="","",INDEX(Flux!$I$2:$I$35,$L24))</f>
         <v/>
       </c>
       <c r="H24" s="41">
-        <f>IF(AND('2 Matériel'!$L12&gt;0,NOT('2 Matériel'!$B12="Oui")),IF(AND(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H12="","",'2 Matériel'!$H12)),"")</f>
+        <f>IF($L24="","",INDEX(Flux!$J$2:$J$35,$L24))</f>
         <v/>
       </c>
       <c r="I24" s="41">
-        <f>IF(AND('2 Matériel'!$L12&gt;0,NOT('2 Matériel'!$B12="Oui")),IF(AND(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I12="","",'2 Matériel'!$I12)),"")</f>
+        <f>IF($L24="","",INDEX(Flux!$K$2:$K$35,$L24))</f>
         <v/>
       </c>
       <c r="J24" s="41">
-        <f>IF(AND('2 Matériel'!$L12&gt;0,NOT('2 Matériel'!$B12="Oui")),IF(AND(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J12="","",'2 Matériel'!$J12)),"")</f>
+        <f>IF($L24="","",INDEX(Flux!$L$2:$L$35,$L24))</f>
         <v/>
       </c>
       <c r="L24" s="42">
-        <f>IF(AND('2 Matériel'!$L12&gt;0,'2 Matériel'!$B12="Oui"),1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="21" customHeight="1">
+        <f>IFERROR(MATCH(9,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M24" s="42">
+        <f>IF(L24="","",INDEX(Flux!$C$2:$C$35,L24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
       <c r="B25" s="38">
-        <f>IF(AND('2 Matériel'!$L13&gt;0,NOT('2 Matériel'!$B13="Oui")),'2 Matériel'!$A13,"")</f>
+        <f>IF($L25="","",INDEX(Flux!$D$2:$D$35,$L25))</f>
         <v/>
       </c>
       <c r="C25" s="39">
-        <f>IF('2 Matériel'!$L13&gt;0,IF('2 Matériel'!$B13="Oui",UPPER('2 Matériel'!$C13),'2 Matériel'!$C13&amp;IF(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <f>IF($L25="","",INDEX(Flux!$E$2:$E$35,$L25))</f>
         <v/>
       </c>
       <c r="D25" s="40">
-        <f>IF(AND('2 Matériel'!$L13&gt;0,NOT('2 Matériel'!$B13="Oui")),'2 Matériel'!$L13,"")</f>
+        <f>IF($L25="","",INDEX(Flux!$F$2:$F$35,$L25))</f>
         <v/>
       </c>
       <c r="E25" s="41">
-        <f>IF(AND('2 Matériel'!$L13&gt;0,NOT('2 Matériel'!$B13="Oui")),IF(AND(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E13="","",'2 Matériel'!$E13)),"")</f>
+        <f>IF($L25="","",INDEX(Flux!$G$2:$G$35,$L25))</f>
         <v/>
       </c>
       <c r="F25" s="41">
-        <f>IF(AND('2 Matériel'!$L13&gt;0,NOT('2 Matériel'!$B13="Oui")),IF(AND(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F13="","",'2 Matériel'!$F13)),"")</f>
+        <f>IF($L25="","",INDEX(Flux!$H$2:$H$35,$L25))</f>
         <v/>
       </c>
       <c r="G25" s="41">
-        <f>IF(AND('2 Matériel'!$L13&gt;0,NOT('2 Matériel'!$B13="Oui")),IF(AND(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G13="","",'2 Matériel'!$G13)),"")</f>
+        <f>IF($L25="","",INDEX(Flux!$I$2:$I$35,$L25))</f>
         <v/>
       </c>
       <c r="H25" s="41">
-        <f>IF(AND('2 Matériel'!$L13&gt;0,NOT('2 Matériel'!$B13="Oui")),IF(AND(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H13="","",'2 Matériel'!$H13)),"")</f>
+        <f>IF($L25="","",INDEX(Flux!$J$2:$J$35,$L25))</f>
         <v/>
       </c>
       <c r="I25" s="41">
-        <f>IF(AND('2 Matériel'!$L13&gt;0,NOT('2 Matériel'!$B13="Oui")),IF(AND(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I13="","",'2 Matériel'!$I13)),"")</f>
+        <f>IF($L25="","",INDEX(Flux!$K$2:$K$35,$L25))</f>
         <v/>
       </c>
       <c r="J25" s="41">
-        <f>IF(AND('2 Matériel'!$L13&gt;0,NOT('2 Matériel'!$B13="Oui")),IF(AND(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J13="","",'2 Matériel'!$J13)),"")</f>
+        <f>IF($L25="","",INDEX(Flux!$L$2:$L$35,$L25))</f>
         <v/>
       </c>
       <c r="L25" s="42">
-        <f>IF(AND('2 Matériel'!$L13&gt;0,'2 Matériel'!$B13="Oui"),1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="21" customHeight="1">
+        <f>IFERROR(MATCH(10,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M25" s="42">
+        <f>IF(L25="","",INDEX(Flux!$C$2:$C$35,L25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
       <c r="B26" s="38">
-        <f>IF(AND('2 Matériel'!$L14&gt;0,NOT('2 Matériel'!$B14="Oui")),'2 Matériel'!$A14,"")</f>
+        <f>IF($L26="","",INDEX(Flux!$D$2:$D$35,$L26))</f>
         <v/>
       </c>
       <c r="C26" s="39">
-        <f>IF('2 Matériel'!$L14&gt;0,IF('2 Matériel'!$B14="Oui",UPPER('2 Matériel'!$C14),'2 Matériel'!$C14&amp;IF(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <f>IF($L26="","",INDEX(Flux!$E$2:$E$35,$L26))</f>
         <v/>
       </c>
       <c r="D26" s="40">
-        <f>IF(AND('2 Matériel'!$L14&gt;0,NOT('2 Matériel'!$B14="Oui")),'2 Matériel'!$L14,"")</f>
+        <f>IF($L26="","",INDEX(Flux!$F$2:$F$35,$L26))</f>
         <v/>
       </c>
       <c r="E26" s="41">
-        <f>IF(AND('2 Matériel'!$L14&gt;0,NOT('2 Matériel'!$B14="Oui")),IF(AND(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E14="","",'2 Matériel'!$E14)),"")</f>
+        <f>IF($L26="","",INDEX(Flux!$G$2:$G$35,$L26))</f>
         <v/>
       </c>
       <c r="F26" s="41">
-        <f>IF(AND('2 Matériel'!$L14&gt;0,NOT('2 Matériel'!$B14="Oui")),IF(AND(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F14="","",'2 Matériel'!$F14)),"")</f>
+        <f>IF($L26="","",INDEX(Flux!$H$2:$H$35,$L26))</f>
         <v/>
       </c>
       <c r="G26" s="41">
-        <f>IF(AND('2 Matériel'!$L14&gt;0,NOT('2 Matériel'!$B14="Oui")),IF(AND(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G14="","",'2 Matériel'!$G14)),"")</f>
+        <f>IF($L26="","",INDEX(Flux!$I$2:$I$35,$L26))</f>
         <v/>
       </c>
       <c r="H26" s="41">
-        <f>IF(AND('2 Matériel'!$L14&gt;0,NOT('2 Matériel'!$B14="Oui")),IF(AND(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H14="","",'2 Matériel'!$H14)),"")</f>
+        <f>IF($L26="","",INDEX(Flux!$J$2:$J$35,$L26))</f>
         <v/>
       </c>
       <c r="I26" s="41">
-        <f>IF(AND('2 Matériel'!$L14&gt;0,NOT('2 Matériel'!$B14="Oui")),IF(AND(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I14="","",'2 Matériel'!$I14)),"")</f>
+        <f>IF($L26="","",INDEX(Flux!$K$2:$K$35,$L26))</f>
         <v/>
       </c>
       <c r="J26" s="41">
-        <f>IF(AND('2 Matériel'!$L14&gt;0,NOT('2 Matériel'!$B14="Oui")),IF(AND(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J14="","",'2 Matériel'!$J14)),"")</f>
+        <f>IF($L26="","",INDEX(Flux!$L$2:$L$35,$L26))</f>
         <v/>
       </c>
       <c r="L26" s="42">
-        <f>IF(AND('2 Matériel'!$L14&gt;0,'2 Matériel'!$B14="Oui"),1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="21" customHeight="1">
+        <f>IFERROR(MATCH(11,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M26" s="42">
+        <f>IF(L26="","",INDEX(Flux!$C$2:$C$35,L26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
       <c r="B27" s="38">
-        <f>IF(AND('2 Matériel'!$L15&gt;0,NOT('2 Matériel'!$B15="Oui")),'2 Matériel'!$A15,"")</f>
+        <f>IF($L27="","",INDEX(Flux!$D$2:$D$35,$L27))</f>
         <v/>
       </c>
       <c r="C27" s="39">
-        <f>IF('2 Matériel'!$L15&gt;0,IF('2 Matériel'!$B15="Oui",UPPER('2 Matériel'!$C15),'2 Matériel'!$C15&amp;IF(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <f>IF($L27="","",INDEX(Flux!$E$2:$E$35,$L27))</f>
         <v/>
       </c>
       <c r="D27" s="40">
-        <f>IF(AND('2 Matériel'!$L15&gt;0,NOT('2 Matériel'!$B15="Oui")),'2 Matériel'!$L15,"")</f>
+        <f>IF($L27="","",INDEX(Flux!$F$2:$F$35,$L27))</f>
         <v/>
       </c>
       <c r="E27" s="41">
-        <f>IF(AND('2 Matériel'!$L15&gt;0,NOT('2 Matériel'!$B15="Oui")),IF(AND(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E15="","",'2 Matériel'!$E15)),"")</f>
+        <f>IF($L27="","",INDEX(Flux!$G$2:$G$35,$L27))</f>
         <v/>
       </c>
       <c r="F27" s="41">
-        <f>IF(AND('2 Matériel'!$L15&gt;0,NOT('2 Matériel'!$B15="Oui")),IF(AND(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F15="","",'2 Matériel'!$F15)),"")</f>
+        <f>IF($L27="","",INDEX(Flux!$H$2:$H$35,$L27))</f>
         <v/>
       </c>
       <c r="G27" s="41">
-        <f>IF(AND('2 Matériel'!$L15&gt;0,NOT('2 Matériel'!$B15="Oui")),IF(AND(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G15="","",'2 Matériel'!$G15)),"")</f>
+        <f>IF($L27="","",INDEX(Flux!$I$2:$I$35,$L27))</f>
         <v/>
       </c>
       <c r="H27" s="41">
-        <f>IF(AND('2 Matériel'!$L15&gt;0,NOT('2 Matériel'!$B15="Oui")),IF(AND(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H15="","",'2 Matériel'!$H15)),"")</f>
+        <f>IF($L27="","",INDEX(Flux!$J$2:$J$35,$L27))</f>
         <v/>
       </c>
       <c r="I27" s="41">
-        <f>IF(AND('2 Matériel'!$L15&gt;0,NOT('2 Matériel'!$B15="Oui")),IF(AND(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I15="","",'2 Matériel'!$I15)),"")</f>
+        <f>IF($L27="","",INDEX(Flux!$K$2:$K$35,$L27))</f>
         <v/>
       </c>
       <c r="J27" s="41">
-        <f>IF(AND('2 Matériel'!$L15&gt;0,NOT('2 Matériel'!$B15="Oui")),IF(AND(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J15="","",'2 Matériel'!$J15)),"")</f>
+        <f>IF($L27="","",INDEX(Flux!$L$2:$L$35,$L27))</f>
         <v/>
       </c>
       <c r="L27" s="42">
-        <f>IF(AND('2 Matériel'!$L15&gt;0,'2 Matériel'!$B15="Oui"),1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="21" customHeight="1">
+        <f>IFERROR(MATCH(12,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M27" s="42">
+        <f>IF(L27="","",INDEX(Flux!$C$2:$C$35,L27))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
       <c r="B28" s="38">
-        <f>IF(AND('2 Matériel'!$L16&gt;0,NOT('2 Matériel'!$B16="Oui")),'2 Matériel'!$A16,"")</f>
+        <f>IF($L28="","",INDEX(Flux!$D$2:$D$35,$L28))</f>
         <v/>
       </c>
       <c r="C28" s="39">
-        <f>IF('2 Matériel'!$L16&gt;0,IF('2 Matériel'!$B16="Oui",UPPER('2 Matériel'!$C16),'2 Matériel'!$C16&amp;IF(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <f>IF($L28="","",INDEX(Flux!$E$2:$E$35,$L28))</f>
         <v/>
       </c>
       <c r="D28" s="40">
-        <f>IF(AND('2 Matériel'!$L16&gt;0,NOT('2 Matériel'!$B16="Oui")),'2 Matériel'!$L16,"")</f>
+        <f>IF($L28="","",INDEX(Flux!$F$2:$F$35,$L28))</f>
         <v/>
       </c>
       <c r="E28" s="41">
-        <f>IF(AND('2 Matériel'!$L16&gt;0,NOT('2 Matériel'!$B16="Oui")),IF(AND(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E16="","",'2 Matériel'!$E16)),"")</f>
+        <f>IF($L28="","",INDEX(Flux!$G$2:$G$35,$L28))</f>
         <v/>
       </c>
       <c r="F28" s="41">
-        <f>IF(AND('2 Matériel'!$L16&gt;0,NOT('2 Matériel'!$B16="Oui")),IF(AND(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F16="","",'2 Matériel'!$F16)),"")</f>
+        <f>IF($L28="","",INDEX(Flux!$H$2:$H$35,$L28))</f>
         <v/>
       </c>
       <c r="G28" s="41">
-        <f>IF(AND('2 Matériel'!$L16&gt;0,NOT('2 Matériel'!$B16="Oui")),IF(AND(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G16="","",'2 Matériel'!$G16)),"")</f>
+        <f>IF($L28="","",INDEX(Flux!$I$2:$I$35,$L28))</f>
         <v/>
       </c>
       <c r="H28" s="41">
-        <f>IF(AND('2 Matériel'!$L16&gt;0,NOT('2 Matériel'!$B16="Oui")),IF(AND(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H16="","",'2 Matériel'!$H16)),"")</f>
+        <f>IF($L28="","",INDEX(Flux!$J$2:$J$35,$L28))</f>
         <v/>
       </c>
       <c r="I28" s="41">
-        <f>IF(AND('2 Matériel'!$L16&gt;0,NOT('2 Matériel'!$B16="Oui")),IF(AND(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I16="","",'2 Matériel'!$I16)),"")</f>
+        <f>IF($L28="","",INDEX(Flux!$K$2:$K$35,$L28))</f>
         <v/>
       </c>
       <c r="J28" s="41">
-        <f>IF(AND('2 Matériel'!$L16&gt;0,NOT('2 Matériel'!$B16="Oui")),IF(AND(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J16="","",'2 Matériel'!$J16)),"")</f>
+        <f>IF($L28="","",INDEX(Flux!$L$2:$L$35,$L28))</f>
         <v/>
       </c>
       <c r="L28" s="42">
-        <f>IF(AND('2 Matériel'!$L16&gt;0,'2 Matériel'!$B16="Oui"),1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="21" customHeight="1">
+        <f>IFERROR(MATCH(13,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M28" s="42">
+        <f>IF(L28="","",INDEX(Flux!$C$2:$C$35,L28))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
       <c r="B29" s="38">
-        <f>IF(AND('2 Matériel'!$L17&gt;0,NOT('2 Matériel'!$B17="Oui")),'2 Matériel'!$A17,"")</f>
+        <f>IF($L29="","",INDEX(Flux!$D$2:$D$35,$L29))</f>
         <v/>
       </c>
       <c r="C29" s="39">
-        <f>IF('2 Matériel'!$L17&gt;0,IF('2 Matériel'!$B17="Oui",UPPER('2 Matériel'!$C17),'2 Matériel'!$C17&amp;IF(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <f>IF($L29="","",INDEX(Flux!$E$2:$E$35,$L29))</f>
         <v/>
       </c>
       <c r="D29" s="40">
-        <f>IF(AND('2 Matériel'!$L17&gt;0,NOT('2 Matériel'!$B17="Oui")),'2 Matériel'!$L17,"")</f>
+        <f>IF($L29="","",INDEX(Flux!$F$2:$F$35,$L29))</f>
         <v/>
       </c>
       <c r="E29" s="41">
-        <f>IF(AND('2 Matériel'!$L17&gt;0,NOT('2 Matériel'!$B17="Oui")),IF(AND(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E17="","",'2 Matériel'!$E17)),"")</f>
+        <f>IF($L29="","",INDEX(Flux!$G$2:$G$35,$L29))</f>
         <v/>
       </c>
       <c r="F29" s="41">
-        <f>IF(AND('2 Matériel'!$L17&gt;0,NOT('2 Matériel'!$B17="Oui")),IF(AND(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F17="","",'2 Matériel'!$F17)),"")</f>
+        <f>IF($L29="","",INDEX(Flux!$H$2:$H$35,$L29))</f>
         <v/>
       </c>
       <c r="G29" s="41">
-        <f>IF(AND('2 Matériel'!$L17&gt;0,NOT('2 Matériel'!$B17="Oui")),IF(AND(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G17="","",'2 Matériel'!$G17)),"")</f>
+        <f>IF($L29="","",INDEX(Flux!$I$2:$I$35,$L29))</f>
         <v/>
       </c>
       <c r="H29" s="41">
-        <f>IF(AND('2 Matériel'!$L17&gt;0,NOT('2 Matériel'!$B17="Oui")),IF(AND(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H17="","",'2 Matériel'!$H17)),"")</f>
+        <f>IF($L29="","",INDEX(Flux!$J$2:$J$35,$L29))</f>
         <v/>
       </c>
       <c r="I29" s="41">
-        <f>IF(AND('2 Matériel'!$L17&gt;0,NOT('2 Matériel'!$B17="Oui")),IF(AND(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I17="","",'2 Matériel'!$I17)),"")</f>
+        <f>IF($L29="","",INDEX(Flux!$K$2:$K$35,$L29))</f>
         <v/>
       </c>
       <c r="J29" s="41">
-        <f>IF(AND('2 Matériel'!$L17&gt;0,NOT('2 Matériel'!$B17="Oui")),IF(AND(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J17="","",'2 Matériel'!$J17)),"")</f>
+        <f>IF($L29="","",INDEX(Flux!$L$2:$L$35,$L29))</f>
         <v/>
       </c>
       <c r="L29" s="42">
-        <f>IF(AND('2 Matériel'!$L17&gt;0,'2 Matériel'!$B17="Oui"),1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="21" customHeight="1">
+        <f>IFERROR(MATCH(14,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M29" s="42">
+        <f>IF(L29="","",INDEX(Flux!$C$2:$C$35,L29))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
       <c r="B30" s="38">
-        <f>IF(AND('2 Matériel'!$L18&gt;0,NOT('2 Matériel'!$B18="Oui")),'2 Matériel'!$A18,"")</f>
+        <f>IF($L30="","",INDEX(Flux!$D$2:$D$35,$L30))</f>
         <v/>
       </c>
       <c r="C30" s="39">
-        <f>IF('2 Matériel'!$L18&gt;0,IF('2 Matériel'!$B18="Oui",UPPER('2 Matériel'!$C18),'2 Matériel'!$C18&amp;IF(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <f>IF($L30="","",INDEX(Flux!$E$2:$E$35,$L30))</f>
         <v/>
       </c>
       <c r="D30" s="40">
-        <f>IF(AND('2 Matériel'!$L18&gt;0,NOT('2 Matériel'!$B18="Oui")),'2 Matériel'!$L18,"")</f>
+        <f>IF($L30="","",INDEX(Flux!$F$2:$F$35,$L30))</f>
         <v/>
       </c>
       <c r="E30" s="41">
-        <f>IF(AND('2 Matériel'!$L18&gt;0,NOT('2 Matériel'!$B18="Oui")),IF(AND(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E18="","",'2 Matériel'!$E18)),"")</f>
+        <f>IF($L30="","",INDEX(Flux!$G$2:$G$35,$L30))</f>
         <v/>
       </c>
       <c r="F30" s="41">
-        <f>IF(AND('2 Matériel'!$L18&gt;0,NOT('2 Matériel'!$B18="Oui")),IF(AND(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F18="","",'2 Matériel'!$F18)),"")</f>
+        <f>IF($L30="","",INDEX(Flux!$H$2:$H$35,$L30))</f>
         <v/>
       </c>
       <c r="G30" s="41">
-        <f>IF(AND('2 Matériel'!$L18&gt;0,NOT('2 Matériel'!$B18="Oui")),IF(AND(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G18="","",'2 Matériel'!$G18)),"")</f>
+        <f>IF($L30="","",INDEX(Flux!$I$2:$I$35,$L30))</f>
         <v/>
       </c>
       <c r="H30" s="41">
-        <f>IF(AND('2 Matériel'!$L18&gt;0,NOT('2 Matériel'!$B18="Oui")),IF(AND(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H18="","",'2 Matériel'!$H18)),"")</f>
+        <f>IF($L30="","",INDEX(Flux!$J$2:$J$35,$L30))</f>
         <v/>
       </c>
       <c r="I30" s="41">
-        <f>IF(AND('2 Matériel'!$L18&gt;0,NOT('2 Matériel'!$B18="Oui")),IF(AND(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I18="","",'2 Matériel'!$I18)),"")</f>
+        <f>IF($L30="","",INDEX(Flux!$K$2:$K$35,$L30))</f>
         <v/>
       </c>
       <c r="J30" s="41">
-        <f>IF(AND('2 Matériel'!$L18&gt;0,NOT('2 Matériel'!$B18="Oui")),IF(AND(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J18="","",'2 Matériel'!$J18)),"")</f>
+        <f>IF($L30="","",INDEX(Flux!$L$2:$L$35,$L30))</f>
         <v/>
       </c>
       <c r="L30" s="42">
-        <f>IF(AND('2 Matériel'!$L18&gt;0,'2 Matériel'!$B18="Oui"),1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="21" customHeight="1">
+        <f>IFERROR(MATCH(15,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M30" s="42">
+        <f>IF(L30="","",INDEX(Flux!$C$2:$C$35,L30))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
       <c r="B31" s="38">
-        <f>IF(AND('2 Matériel'!$L19&gt;0,NOT('2 Matériel'!$B19="Oui")),'2 Matériel'!$A19,"")</f>
+        <f>IF($L31="","",INDEX(Flux!$D$2:$D$35,$L31))</f>
         <v/>
       </c>
       <c r="C31" s="39">
-        <f>IF('2 Matériel'!$L19&gt;0,IF('2 Matériel'!$B19="Oui",UPPER('2 Matériel'!$C19),'2 Matériel'!$C19&amp;IF(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <f>IF($L31="","",INDEX(Flux!$E$2:$E$35,$L31))</f>
         <v/>
       </c>
       <c r="D31" s="40">
-        <f>IF(AND('2 Matériel'!$L19&gt;0,NOT('2 Matériel'!$B19="Oui")),'2 Matériel'!$L19,"")</f>
+        <f>IF($L31="","",INDEX(Flux!$F$2:$F$35,$L31))</f>
         <v/>
       </c>
       <c r="E31" s="41">
-        <f>IF(AND('2 Matériel'!$L19&gt;0,NOT('2 Matériel'!$B19="Oui")),IF(AND(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E19="","",'2 Matériel'!$E19)),"")</f>
+        <f>IF($L31="","",INDEX(Flux!$G$2:$G$35,$L31))</f>
         <v/>
       </c>
       <c r="F31" s="41">
-        <f>IF(AND('2 Matériel'!$L19&gt;0,NOT('2 Matériel'!$B19="Oui")),IF(AND(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F19="","",'2 Matériel'!$F19)),"")</f>
+        <f>IF($L31="","",INDEX(Flux!$H$2:$H$35,$L31))</f>
         <v/>
       </c>
       <c r="G31" s="41">
-        <f>IF(AND('2 Matériel'!$L19&gt;0,NOT('2 Matériel'!$B19="Oui")),IF(AND(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G19="","",'2 Matériel'!$G19)),"")</f>
+        <f>IF($L31="","",INDEX(Flux!$I$2:$I$35,$L31))</f>
         <v/>
       </c>
       <c r="H31" s="41">
-        <f>IF(AND('2 Matériel'!$L19&gt;0,NOT('2 Matériel'!$B19="Oui")),IF(AND(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H19="","",'2 Matériel'!$H19)),"")</f>
+        <f>IF($L31="","",INDEX(Flux!$J$2:$J$35,$L31))</f>
         <v/>
       </c>
       <c r="I31" s="41">
-        <f>IF(AND('2 Matériel'!$L19&gt;0,NOT('2 Matériel'!$B19="Oui")),IF(AND(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I19="","",'2 Matériel'!$I19)),"")</f>
+        <f>IF($L31="","",INDEX(Flux!$K$2:$K$35,$L31))</f>
         <v/>
       </c>
       <c r="J31" s="41">
-        <f>IF(AND('2 Matériel'!$L19&gt;0,NOT('2 Matériel'!$B19="Oui")),IF(AND(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J19="","",'2 Matériel'!$J19)),"")</f>
+        <f>IF($L31="","",INDEX(Flux!$L$2:$L$35,$L31))</f>
         <v/>
       </c>
       <c r="L31" s="42">
-        <f>IF(AND('2 Matériel'!$L19&gt;0,'2 Matériel'!$B19="Oui"),1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="21" customHeight="1">
+        <f>IFERROR(MATCH(16,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M31" s="42">
+        <f>IF(L31="","",INDEX(Flux!$C$2:$C$35,L31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
       <c r="B32" s="38">
-        <f>IF(AND('2 Matériel'!$L20&gt;0,NOT('2 Matériel'!$B20="Oui")),'2 Matériel'!$A20,"")</f>
+        <f>IF($L32="","",INDEX(Flux!$D$2:$D$35,$L32))</f>
         <v/>
       </c>
       <c r="C32" s="39">
-        <f>IF('2 Matériel'!$L20&gt;0,IF('2 Matériel'!$B20="Oui",UPPER('2 Matériel'!$C20),'2 Matériel'!$C20&amp;IF(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <f>IF($L32="","",INDEX(Flux!$E$2:$E$35,$L32))</f>
         <v/>
       </c>
       <c r="D32" s="40">
-        <f>IF(AND('2 Matériel'!$L20&gt;0,NOT('2 Matériel'!$B20="Oui")),'2 Matériel'!$L20,"")</f>
+        <f>IF($L32="","",INDEX(Flux!$F$2:$F$35,$L32))</f>
         <v/>
       </c>
       <c r="E32" s="41">
-        <f>IF(AND('2 Matériel'!$L20&gt;0,NOT('2 Matériel'!$B20="Oui")),IF(AND(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E20="","",'2 Matériel'!$E20)),"")</f>
+        <f>IF($L32="","",INDEX(Flux!$G$2:$G$35,$L32))</f>
         <v/>
       </c>
       <c r="F32" s="41">
-        <f>IF(AND('2 Matériel'!$L20&gt;0,NOT('2 Matériel'!$B20="Oui")),IF(AND(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F20="","",'2 Matériel'!$F20)),"")</f>
+        <f>IF($L32="","",INDEX(Flux!$H$2:$H$35,$L32))</f>
         <v/>
       </c>
       <c r="G32" s="41">
-        <f>IF(AND('2 Matériel'!$L20&gt;0,NOT('2 Matériel'!$B20="Oui")),IF(AND(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G20="","",'2 Matériel'!$G20)),"")</f>
+        <f>IF($L32="","",INDEX(Flux!$I$2:$I$35,$L32))</f>
         <v/>
       </c>
       <c r="H32" s="41">
-        <f>IF(AND('2 Matériel'!$L20&gt;0,NOT('2 Matériel'!$B20="Oui")),IF(AND(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H20="","",'2 Matériel'!$H20)),"")</f>
+        <f>IF($L32="","",INDEX(Flux!$J$2:$J$35,$L32))</f>
         <v/>
       </c>
       <c r="I32" s="41">
-        <f>IF(AND('2 Matériel'!$L20&gt;0,NOT('2 Matériel'!$B20="Oui")),IF(AND(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I20="","",'2 Matériel'!$I20)),"")</f>
+        <f>IF($L32="","",INDEX(Flux!$K$2:$K$35,$L32))</f>
         <v/>
       </c>
       <c r="J32" s="41">
-        <f>IF(AND('2 Matériel'!$L20&gt;0,NOT('2 Matériel'!$B20="Oui")),IF(AND(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J20="","",'2 Matériel'!$J20)),"")</f>
+        <f>IF($L32="","",INDEX(Flux!$L$2:$L$35,$L32))</f>
         <v/>
       </c>
       <c r="L32" s="42">
-        <f>IF(AND('2 Matériel'!$L20&gt;0,'2 Matériel'!$B20="Oui"),1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="21" customHeight="1">
+        <f>IFERROR(MATCH(17,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M32" s="42">
+        <f>IF(L32="","",INDEX(Flux!$C$2:$C$35,L32))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
       <c r="B33" s="38">
-        <f>IF(AND('2 Matériel'!$L21&gt;0,NOT('2 Matériel'!$B21="Oui")),'2 Matériel'!$A21,"")</f>
+        <f>IF($L33="","",INDEX(Flux!$D$2:$D$35,$L33))</f>
         <v/>
       </c>
       <c r="C33" s="39">
-        <f>IF('2 Matériel'!$L21&gt;0,IF('2 Matériel'!$B21="Oui",UPPER('2 Matériel'!$C21),'2 Matériel'!$C21&amp;IF(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <f>IF($L33="","",INDEX(Flux!$E$2:$E$35,$L33))</f>
         <v/>
       </c>
       <c r="D33" s="40">
-        <f>IF(AND('2 Matériel'!$L21&gt;0,NOT('2 Matériel'!$B21="Oui")),'2 Matériel'!$L21,"")</f>
+        <f>IF($L33="","",INDEX(Flux!$F$2:$F$35,$L33))</f>
         <v/>
       </c>
       <c r="E33" s="41">
-        <f>IF(AND('2 Matériel'!$L21&gt;0,NOT('2 Matériel'!$B21="Oui")),IF(AND(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E21="","",'2 Matériel'!$E21)),"")</f>
+        <f>IF($L33="","",INDEX(Flux!$G$2:$G$35,$L33))</f>
         <v/>
       </c>
       <c r="F33" s="41">
-        <f>IF(AND('2 Matériel'!$L21&gt;0,NOT('2 Matériel'!$B21="Oui")),IF(AND(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F21="","",'2 Matériel'!$F21)),"")</f>
+        <f>IF($L33="","",INDEX(Flux!$H$2:$H$35,$L33))</f>
         <v/>
       </c>
       <c r="G33" s="41">
-        <f>IF(AND('2 Matériel'!$L21&gt;0,NOT('2 Matériel'!$B21="Oui")),IF(AND(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G21="","",'2 Matériel'!$G21)),"")</f>
+        <f>IF($L33="","",INDEX(Flux!$I$2:$I$35,$L33))</f>
         <v/>
       </c>
       <c r="H33" s="41">
-        <f>IF(AND('2 Matériel'!$L21&gt;0,NOT('2 Matériel'!$B21="Oui")),IF(AND(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H21="","",'2 Matériel'!$H21)),"")</f>
+        <f>IF($L33="","",INDEX(Flux!$J$2:$J$35,$L33))</f>
         <v/>
       </c>
       <c r="I33" s="41">
-        <f>IF(AND('2 Matériel'!$L21&gt;0,NOT('2 Matériel'!$B21="Oui")),IF(AND(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I21="","",'2 Matériel'!$I21)),"")</f>
+        <f>IF($L33="","",INDEX(Flux!$K$2:$K$35,$L33))</f>
         <v/>
       </c>
       <c r="J33" s="41">
-        <f>IF(AND('2 Matériel'!$L21&gt;0,NOT('2 Matériel'!$B21="Oui")),IF(AND(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J21="","",'2 Matériel'!$J21)),"")</f>
+        <f>IF($L33="","",INDEX(Flux!$L$2:$L$35,$L33))</f>
         <v/>
       </c>
       <c r="L33" s="42">
-        <f>IF(AND('2 Matériel'!$L21&gt;0,'2 Matériel'!$B21="Oui"),1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="21" customHeight="1">
+        <f>IFERROR(MATCH(18,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M33" s="42">
+        <f>IF(L33="","",INDEX(Flux!$C$2:$C$35,L33))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
       <c r="B34" s="38">
-        <f>IF(AND('2 Matériel'!$L22&gt;0,NOT('2 Matériel'!$B22="Oui")),'2 Matériel'!$A22,"")</f>
+        <f>IF($L34="","",INDEX(Flux!$D$2:$D$35,$L34))</f>
         <v/>
       </c>
       <c r="C34" s="39">
-        <f>IF('2 Matériel'!$L22&gt;0,IF('2 Matériel'!$B22="Oui",UPPER('2 Matériel'!$C22),'2 Matériel'!$C22&amp;IF(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <f>IF($L34="","",INDEX(Flux!$E$2:$E$35,$L34))</f>
         <v/>
       </c>
       <c r="D34" s="40">
-        <f>IF(AND('2 Matériel'!$L22&gt;0,NOT('2 Matériel'!$B22="Oui")),'2 Matériel'!$L22,"")</f>
+        <f>IF($L34="","",INDEX(Flux!$F$2:$F$35,$L34))</f>
         <v/>
       </c>
       <c r="E34" s="41">
-        <f>IF(AND('2 Matériel'!$L22&gt;0,NOT('2 Matériel'!$B22="Oui")),IF(AND(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E22="","",'2 Matériel'!$E22)),"")</f>
+        <f>IF($L34="","",INDEX(Flux!$G$2:$G$35,$L34))</f>
         <v/>
       </c>
       <c r="F34" s="41">
-        <f>IF(AND('2 Matériel'!$L22&gt;0,NOT('2 Matériel'!$B22="Oui")),IF(AND(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F22="","",'2 Matériel'!$F22)),"")</f>
+        <f>IF($L34="","",INDEX(Flux!$H$2:$H$35,$L34))</f>
         <v/>
       </c>
       <c r="G34" s="41">
-        <f>IF(AND('2 Matériel'!$L22&gt;0,NOT('2 Matériel'!$B22="Oui")),IF(AND(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G22="","",'2 Matériel'!$G22)),"")</f>
+        <f>IF($L34="","",INDEX(Flux!$I$2:$I$35,$L34))</f>
         <v/>
       </c>
       <c r="H34" s="41">
-        <f>IF(AND('2 Matériel'!$L22&gt;0,NOT('2 Matériel'!$B22="Oui")),IF(AND(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H22="","",'2 Matériel'!$H22)),"")</f>
+        <f>IF($L34="","",INDEX(Flux!$J$2:$J$35,$L34))</f>
         <v/>
       </c>
       <c r="I34" s="41">
-        <f>IF(AND('2 Matériel'!$L22&gt;0,NOT('2 Matériel'!$B22="Oui")),IF(AND(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I22="","",'2 Matériel'!$I22)),"")</f>
+        <f>IF($L34="","",INDEX(Flux!$K$2:$K$35,$L34))</f>
         <v/>
       </c>
       <c r="J34" s="41">
-        <f>IF(AND('2 Matériel'!$L22&gt;0,NOT('2 Matériel'!$B22="Oui")),IF(AND(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J22="","",'2 Matériel'!$J22)),"")</f>
+        <f>IF($L34="","",INDEX(Flux!$L$2:$L$35,$L34))</f>
         <v/>
       </c>
       <c r="L34" s="42">
-        <f>IF(AND('2 Matériel'!$L22&gt;0,'2 Matériel'!$B22="Oui"),1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="21" customHeight="1">
+        <f>IFERROR(MATCH(19,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M34" s="42">
+        <f>IF(L34="","",INDEX(Flux!$C$2:$C$35,L34))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
       <c r="B35" s="38">
-        <f>IF(AND('2 Matériel'!$L23&gt;0,NOT('2 Matériel'!$B23="Oui")),'2 Matériel'!$A23,"")</f>
+        <f>IF($L35="","",INDEX(Flux!$D$2:$D$35,$L35))</f>
         <v/>
       </c>
       <c r="C35" s="39">
-        <f>IF('2 Matériel'!$L23&gt;0,IF('2 Matériel'!$B23="Oui",UPPER('2 Matériel'!$C23),'2 Matériel'!$C23&amp;IF(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <f>IF($L35="","",INDEX(Flux!$E$2:$E$35,$L35))</f>
         <v/>
       </c>
       <c r="D35" s="40">
-        <f>IF(AND('2 Matériel'!$L23&gt;0,NOT('2 Matériel'!$B23="Oui")),'2 Matériel'!$L23,"")</f>
+        <f>IF($L35="","",INDEX(Flux!$F$2:$F$35,$L35))</f>
         <v/>
       </c>
       <c r="E35" s="41">
-        <f>IF(AND('2 Matériel'!$L23&gt;0,NOT('2 Matériel'!$B23="Oui")),IF(AND(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E23="","",'2 Matériel'!$E23)),"")</f>
+        <f>IF($L35="","",INDEX(Flux!$G$2:$G$35,$L35))</f>
         <v/>
       </c>
       <c r="F35" s="41">
-        <f>IF(AND('2 Matériel'!$L23&gt;0,NOT('2 Matériel'!$B23="Oui")),IF(AND(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F23="","",'2 Matériel'!$F23)),"")</f>
+        <f>IF($L35="","",INDEX(Flux!$H$2:$H$35,$L35))</f>
         <v/>
       </c>
       <c r="G35" s="41">
-        <f>IF(AND('2 Matériel'!$L23&gt;0,NOT('2 Matériel'!$B23="Oui")),IF(AND(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G23="","",'2 Matériel'!$G23)),"")</f>
+        <f>IF($L35="","",INDEX(Flux!$I$2:$I$35,$L35))</f>
         <v/>
       </c>
       <c r="H35" s="41">
-        <f>IF(AND('2 Matériel'!$L23&gt;0,NOT('2 Matériel'!$B23="Oui")),IF(AND(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H23="","",'2 Matériel'!$H23)),"")</f>
+        <f>IF($L35="","",INDEX(Flux!$J$2:$J$35,$L35))</f>
         <v/>
       </c>
       <c r="I35" s="41">
-        <f>IF(AND('2 Matériel'!$L23&gt;0,NOT('2 Matériel'!$B23="Oui")),IF(AND(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I23="","",'2 Matériel'!$I23)),"")</f>
+        <f>IF($L35="","",INDEX(Flux!$K$2:$K$35,$L35))</f>
         <v/>
       </c>
       <c r="J35" s="41">
-        <f>IF(AND('2 Matériel'!$L23&gt;0,NOT('2 Matériel'!$B23="Oui")),IF(AND(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J23="","",'2 Matériel'!$J23)),"")</f>
+        <f>IF($L35="","",INDEX(Flux!$L$2:$L$35,$L35))</f>
         <v/>
       </c>
       <c r="L35" s="42">
-        <f>IF(AND('2 Matériel'!$L23&gt;0,'2 Matériel'!$B23="Oui"),1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" hidden="1" outlineLevel="1" ht="21" customHeight="1">
+        <f>IFERROR(MATCH(20,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M35" s="42">
+        <f>IF(L35="","",INDEX(Flux!$C$2:$C$35,L35))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
       <c r="B36" s="38">
-        <f>IF(AND('2 Matériel'!$L24&gt;0,NOT('2 Matériel'!$B24="Oui")),'2 Matériel'!$A24,"")</f>
+        <f>IF($L36="","",INDEX(Flux!$D$2:$D$35,$L36))</f>
         <v/>
       </c>
       <c r="C36" s="39">
-        <f>IF('2 Matériel'!$L24&gt;0,IF('2 Matériel'!$B24="Oui",UPPER('2 Matériel'!$C24),'2 Matériel'!$C24&amp;IF(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <f>IF($L36="","",INDEX(Flux!$E$2:$E$35,$L36))</f>
         <v/>
       </c>
       <c r="D36" s="40">
-        <f>IF(AND('2 Matériel'!$L24&gt;0,NOT('2 Matériel'!$B24="Oui")),'2 Matériel'!$L24,"")</f>
+        <f>IF($L36="","",INDEX(Flux!$F$2:$F$35,$L36))</f>
         <v/>
       </c>
       <c r="E36" s="41">
-        <f>IF(AND('2 Matériel'!$L24&gt;0,NOT('2 Matériel'!$B24="Oui")),IF(AND(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E24="","",'2 Matériel'!$E24)),"")</f>
+        <f>IF($L36="","",INDEX(Flux!$G$2:$G$35,$L36))</f>
         <v/>
       </c>
       <c r="F36" s="41">
-        <f>IF(AND('2 Matériel'!$L24&gt;0,NOT('2 Matériel'!$B24="Oui")),IF(AND(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F24="","",'2 Matériel'!$F24)),"")</f>
+        <f>IF($L36="","",INDEX(Flux!$H$2:$H$35,$L36))</f>
         <v/>
       </c>
       <c r="G36" s="41">
-        <f>IF(AND('2 Matériel'!$L24&gt;0,NOT('2 Matériel'!$B24="Oui")),IF(AND(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G24="","",'2 Matériel'!$G24)),"")</f>
+        <f>IF($L36="","",INDEX(Flux!$I$2:$I$35,$L36))</f>
         <v/>
       </c>
       <c r="H36" s="41">
-        <f>IF(AND('2 Matériel'!$L24&gt;0,NOT('2 Matériel'!$B24="Oui")),IF(AND(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H24="","",'2 Matériel'!$H24)),"")</f>
+        <f>IF($L36="","",INDEX(Flux!$J$2:$J$35,$L36))</f>
         <v/>
       </c>
       <c r="I36" s="41">
-        <f>IF(AND('2 Matériel'!$L24&gt;0,NOT('2 Matériel'!$B24="Oui")),IF(AND(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I24="","",'2 Matériel'!$I24)),"")</f>
+        <f>IF($L36="","",INDEX(Flux!$K$2:$K$35,$L36))</f>
         <v/>
       </c>
       <c r="J36" s="41">
-        <f>IF(AND('2 Matériel'!$L24&gt;0,NOT('2 Matériel'!$B24="Oui")),IF(AND(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J24="","",'2 Matériel'!$J24)),"")</f>
+        <f>IF($L36="","",INDEX(Flux!$L$2:$L$35,$L36))</f>
         <v/>
       </c>
       <c r="L36" s="42">
-        <f>IF(AND('2 Matériel'!$L24&gt;0,'2 Matériel'!$B24="Oui"),1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" hidden="1" outlineLevel="1" ht="21" customHeight="1">
+        <f>IFERROR(MATCH(21,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M36" s="42">
+        <f>IF(L36="","",INDEX(Flux!$C$2:$C$35,L36))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
       <c r="B37" s="38">
-        <f>IF(AND('2 Matériel'!$L25&gt;0,NOT('2 Matériel'!$B25="Oui")),'2 Matériel'!$A25,"")</f>
+        <f>IF($L37="","",INDEX(Flux!$D$2:$D$35,$L37))</f>
         <v/>
       </c>
       <c r="C37" s="39">
-        <f>IF('2 Matériel'!$L25&gt;0,IF('2 Matériel'!$B25="Oui",UPPER('2 Matériel'!$C25),'2 Matériel'!$C25&amp;IF(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <f>IF($L37="","",INDEX(Flux!$E$2:$E$35,$L37))</f>
         <v/>
       </c>
       <c r="D37" s="40">
-        <f>IF(AND('2 Matériel'!$L25&gt;0,NOT('2 Matériel'!$B25="Oui")),'2 Matériel'!$L25,"")</f>
+        <f>IF($L37="","",INDEX(Flux!$F$2:$F$35,$L37))</f>
         <v/>
       </c>
       <c r="E37" s="41">
-        <f>IF(AND('2 Matériel'!$L25&gt;0,NOT('2 Matériel'!$B25="Oui")),IF(AND(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E25="","",'2 Matériel'!$E25)),"")</f>
+        <f>IF($L37="","",INDEX(Flux!$G$2:$G$35,$L37))</f>
         <v/>
       </c>
       <c r="F37" s="41">
-        <f>IF(AND('2 Matériel'!$L25&gt;0,NOT('2 Matériel'!$B25="Oui")),IF(AND(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F25="","",'2 Matériel'!$F25)),"")</f>
+        <f>IF($L37="","",INDEX(Flux!$H$2:$H$35,$L37))</f>
         <v/>
       </c>
       <c r="G37" s="41">
-        <f>IF(AND('2 Matériel'!$L25&gt;0,NOT('2 Matériel'!$B25="Oui")),IF(AND(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G25="","",'2 Matériel'!$G25)),"")</f>
+        <f>IF($L37="","",INDEX(Flux!$I$2:$I$35,$L37))</f>
         <v/>
       </c>
       <c r="H37" s="41">
-        <f>IF(AND('2 Matériel'!$L25&gt;0,NOT('2 Matériel'!$B25="Oui")),IF(AND(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H25="","",'2 Matériel'!$H25)),"")</f>
+        <f>IF($L37="","",INDEX(Flux!$J$2:$J$35,$L37))</f>
         <v/>
       </c>
       <c r="I37" s="41">
-        <f>IF(AND('2 Matériel'!$L25&gt;0,NOT('2 Matériel'!$B25="Oui")),IF(AND(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I25="","",'2 Matériel'!$I25)),"")</f>
+        <f>IF($L37="","",INDEX(Flux!$K$2:$K$35,$L37))</f>
         <v/>
       </c>
       <c r="J37" s="41">
-        <f>IF(AND('2 Matériel'!$L25&gt;0,NOT('2 Matériel'!$B25="Oui")),IF(AND(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J25="","",'2 Matériel'!$J25)),"")</f>
+        <f>IF($L37="","",INDEX(Flux!$L$2:$L$35,$L37))</f>
         <v/>
       </c>
       <c r="L37" s="42">
-        <f>IF(AND('2 Matériel'!$L25&gt;0,'2 Matériel'!$B25="Oui"),1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" hidden="1" outlineLevel="1" ht="21" customHeight="1">
+        <f>IFERROR(MATCH(22,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M37" s="42">
+        <f>IF(L37="","",INDEX(Flux!$C$2:$C$35,L37))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
       <c r="B38" s="38">
-        <f>IF(AND('2 Matériel'!$L26&gt;0,NOT('2 Matériel'!$B26="Oui")),'2 Matériel'!$A26,"")</f>
+        <f>IF($L38="","",INDEX(Flux!$D$2:$D$35,$L38))</f>
         <v/>
       </c>
       <c r="C38" s="39">
-        <f>IF('2 Matériel'!$L26&gt;0,IF('2 Matériel'!$B26="Oui",UPPER('2 Matériel'!$C26),'2 Matériel'!$C26&amp;IF(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <f>IF($L38="","",INDEX(Flux!$E$2:$E$35,$L38))</f>
         <v/>
       </c>
       <c r="D38" s="40">
-        <f>IF(AND('2 Matériel'!$L26&gt;0,NOT('2 Matériel'!$B26="Oui")),'2 Matériel'!$L26,"")</f>
+        <f>IF($L38="","",INDEX(Flux!$F$2:$F$35,$L38))</f>
         <v/>
       </c>
       <c r="E38" s="41">
-        <f>IF(AND('2 Matériel'!$L26&gt;0,NOT('2 Matériel'!$B26="Oui")),IF(AND(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E26="","",'2 Matériel'!$E26)),"")</f>
+        <f>IF($L38="","",INDEX(Flux!$G$2:$G$35,$L38))</f>
         <v/>
       </c>
       <c r="F38" s="41">
-        <f>IF(AND('2 Matériel'!$L26&gt;0,NOT('2 Matériel'!$B26="Oui")),IF(AND(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F26="","",'2 Matériel'!$F26)),"")</f>
+        <f>IF($L38="","",INDEX(Flux!$H$2:$H$35,$L38))</f>
         <v/>
       </c>
       <c r="G38" s="41">
-        <f>IF(AND('2 Matériel'!$L26&gt;0,NOT('2 Matériel'!$B26="Oui")),IF(AND(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G26="","",'2 Matériel'!$G26)),"")</f>
+        <f>IF($L38="","",INDEX(Flux!$I$2:$I$35,$L38))</f>
         <v/>
       </c>
       <c r="H38" s="41">
-        <f>IF(AND('2 Matériel'!$L26&gt;0,NOT('2 Matériel'!$B26="Oui")),IF(AND(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H26="","",'2 Matériel'!$H26)),"")</f>
+        <f>IF($L38="","",INDEX(Flux!$J$2:$J$35,$L38))</f>
         <v/>
       </c>
       <c r="I38" s="41">
-        <f>IF(AND('2 Matériel'!$L26&gt;0,NOT('2 Matériel'!$B26="Oui")),IF(AND(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I26="","",'2 Matériel'!$I26)),"")</f>
+        <f>IF($L38="","",INDEX(Flux!$K$2:$K$35,$L38))</f>
         <v/>
       </c>
       <c r="J38" s="41">
-        <f>IF(AND('2 Matériel'!$L26&gt;0,NOT('2 Matériel'!$B26="Oui")),IF(AND(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J26="","",'2 Matériel'!$J26)),"")</f>
+        <f>IF($L38="","",INDEX(Flux!$L$2:$L$35,$L38))</f>
         <v/>
       </c>
       <c r="L38" s="42">
-        <f>IF(AND('2 Matériel'!$L26&gt;0,'2 Matériel'!$B26="Oui"),1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" hidden="1" outlineLevel="1" ht="21" customHeight="1">
+        <f>IFERROR(MATCH(23,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M38" s="42">
+        <f>IF(L38="","",INDEX(Flux!$C$2:$C$35,L38))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
       <c r="B39" s="38">
-        <f>IF(AND('2 Matériel'!$L27&gt;0,NOT('2 Matériel'!$B27="Oui")),'2 Matériel'!$A27,"")</f>
+        <f>IF($L39="","",INDEX(Flux!$D$2:$D$35,$L39))</f>
         <v/>
       </c>
       <c r="C39" s="39">
-        <f>IF('2 Matériel'!$L27&gt;0,IF('2 Matériel'!$B27="Oui",UPPER('2 Matériel'!$C27),'2 Matériel'!$C27&amp;IF(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <f>IF($L39="","",INDEX(Flux!$E$2:$E$35,$L39))</f>
         <v/>
       </c>
       <c r="D39" s="40">
-        <f>IF(AND('2 Matériel'!$L27&gt;0,NOT('2 Matériel'!$B27="Oui")),'2 Matériel'!$L27,"")</f>
+        <f>IF($L39="","",INDEX(Flux!$F$2:$F$35,$L39))</f>
         <v/>
       </c>
       <c r="E39" s="41">
-        <f>IF(AND('2 Matériel'!$L27&gt;0,NOT('2 Matériel'!$B27="Oui")),IF(AND(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E27="","",'2 Matériel'!$E27)),"")</f>
+        <f>IF($L39="","",INDEX(Flux!$G$2:$G$35,$L39))</f>
         <v/>
       </c>
       <c r="F39" s="41">
-        <f>IF(AND('2 Matériel'!$L27&gt;0,NOT('2 Matériel'!$B27="Oui")),IF(AND(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F27="","",'2 Matériel'!$F27)),"")</f>
+        <f>IF($L39="","",INDEX(Flux!$H$2:$H$35,$L39))</f>
         <v/>
       </c>
       <c r="G39" s="41">
-        <f>IF(AND('2 Matériel'!$L27&gt;0,NOT('2 Matériel'!$B27="Oui")),IF(AND(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G27="","",'2 Matériel'!$G27)),"")</f>
+        <f>IF($L39="","",INDEX(Flux!$I$2:$I$35,$L39))</f>
         <v/>
       </c>
       <c r="H39" s="41">
-        <f>IF(AND('2 Matériel'!$L27&gt;0,NOT('2 Matériel'!$B27="Oui")),IF(AND(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H27="","",'2 Matériel'!$H27)),"")</f>
+        <f>IF($L39="","",INDEX(Flux!$J$2:$J$35,$L39))</f>
         <v/>
       </c>
       <c r="I39" s="41">
-        <f>IF(AND('2 Matériel'!$L27&gt;0,NOT('2 Matériel'!$B27="Oui")),IF(AND(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I27="","",'2 Matériel'!$I27)),"")</f>
+        <f>IF($L39="","",INDEX(Flux!$K$2:$K$35,$L39))</f>
         <v/>
       </c>
       <c r="J39" s="41">
-        <f>IF(AND('2 Matériel'!$L27&gt;0,NOT('2 Matériel'!$B27="Oui")),IF(AND(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J27="","",'2 Matériel'!$J27)),"")</f>
+        <f>IF($L39="","",INDEX(Flux!$L$2:$L$35,$L39))</f>
         <v/>
       </c>
       <c r="L39" s="42">
-        <f>IF(AND('2 Matériel'!$L27&gt;0,'2 Matériel'!$B27="Oui"),1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" hidden="1" outlineLevel="1" ht="21" customHeight="1">
+        <f>IFERROR(MATCH(24,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M39" s="42">
+        <f>IF(L39="","",INDEX(Flux!$C$2:$C$35,L39))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
       <c r="B40" s="38">
-        <f>IF(AND('2 Matériel'!$L28&gt;0,NOT('2 Matériel'!$B28="Oui")),'2 Matériel'!$A28,"")</f>
+        <f>IF($L40="","",INDEX(Flux!$D$2:$D$35,$L40))</f>
         <v/>
       </c>
       <c r="C40" s="39">
-        <f>IF('2 Matériel'!$L28&gt;0,IF('2 Matériel'!$B28="Oui",UPPER('2 Matériel'!$C28),'2 Matériel'!$C28&amp;IF(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <f>IF($L40="","",INDEX(Flux!$E$2:$E$35,$L40))</f>
         <v/>
       </c>
       <c r="D40" s="40">
-        <f>IF(AND('2 Matériel'!$L28&gt;0,NOT('2 Matériel'!$B28="Oui")),'2 Matériel'!$L28,"")</f>
+        <f>IF($L40="","",INDEX(Flux!$F$2:$F$35,$L40))</f>
         <v/>
       </c>
       <c r="E40" s="41">
-        <f>IF(AND('2 Matériel'!$L28&gt;0,NOT('2 Matériel'!$B28="Oui")),IF(AND(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E28="","",'2 Matériel'!$E28)),"")</f>
+        <f>IF($L40="","",INDEX(Flux!$G$2:$G$35,$L40))</f>
         <v/>
       </c>
       <c r="F40" s="41">
-        <f>IF(AND('2 Matériel'!$L28&gt;0,NOT('2 Matériel'!$B28="Oui")),IF(AND(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F28="","",'2 Matériel'!$F28)),"")</f>
+        <f>IF($L40="","",INDEX(Flux!$H$2:$H$35,$L40))</f>
         <v/>
       </c>
       <c r="G40" s="41">
-        <f>IF(AND('2 Matériel'!$L28&gt;0,NOT('2 Matériel'!$B28="Oui")),IF(AND(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G28="","",'2 Matériel'!$G28)),"")</f>
+        <f>IF($L40="","",INDEX(Flux!$I$2:$I$35,$L40))</f>
         <v/>
       </c>
       <c r="H40" s="41">
-        <f>IF(AND('2 Matériel'!$L28&gt;0,NOT('2 Matériel'!$B28="Oui")),IF(AND(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H28="","",'2 Matériel'!$H28)),"")</f>
+        <f>IF($L40="","",INDEX(Flux!$J$2:$J$35,$L40))</f>
         <v/>
       </c>
       <c r="I40" s="41">
-        <f>IF(AND('2 Matériel'!$L28&gt;0,NOT('2 Matériel'!$B28="Oui")),IF(AND(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I28="","",'2 Matériel'!$I28)),"")</f>
+        <f>IF($L40="","",INDEX(Flux!$K$2:$K$35,$L40))</f>
         <v/>
       </c>
       <c r="J40" s="41">
-        <f>IF(AND('2 Matériel'!$L28&gt;0,NOT('2 Matériel'!$B28="Oui")),IF(AND(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J28="","",'2 Matériel'!$J28)),"")</f>
+        <f>IF($L40="","",INDEX(Flux!$L$2:$L$35,$L40))</f>
         <v/>
       </c>
       <c r="L40" s="42">
-        <f>IF(AND('2 Matériel'!$L28&gt;0,'2 Matériel'!$B28="Oui"),1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" hidden="1" outlineLevel="1" ht="21" customHeight="1">
+        <f>IFERROR(MATCH(25,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M40" s="42">
+        <f>IF(L40="","",INDEX(Flux!$C$2:$C$35,L40))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
       <c r="B41" s="38">
-        <f>IF(AND('2 Matériel'!$L29&gt;0,NOT('2 Matériel'!$B29="Oui")),'2 Matériel'!$A29,"")</f>
+        <f>IF($L41="","",INDEX(Flux!$D$2:$D$35,$L41))</f>
         <v/>
       </c>
       <c r="C41" s="39">
-        <f>IF('2 Matériel'!$L29&gt;0,IF('2 Matériel'!$B29="Oui",UPPER('2 Matériel'!$C29),'2 Matériel'!$C29&amp;IF(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")),"")</f>
+        <f>IF($L41="","",INDEX(Flux!$E$2:$E$35,$L41))</f>
         <v/>
       </c>
       <c r="D41" s="40">
-        <f>IF(AND('2 Matériel'!$L29&gt;0,NOT('2 Matériel'!$B29="Oui")),'2 Matériel'!$L29,"")</f>
+        <f>IF($L41="","",INDEX(Flux!$F$2:$F$35,$L41))</f>
         <v/>
       </c>
       <c r="E41" s="41">
-        <f>IF(AND('2 Matériel'!$L29&gt;0,NOT('2 Matériel'!$B29="Oui")),IF(AND(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E29="","",'2 Matériel'!$E29)),"")</f>
+        <f>IF($L41="","",INDEX(Flux!$G$2:$G$35,$L41))</f>
         <v/>
       </c>
       <c r="F41" s="41">
-        <f>IF(AND('2 Matériel'!$L29&gt;0,NOT('2 Matériel'!$B29="Oui")),IF(AND(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F29="","",'2 Matériel'!$F29)),"")</f>
+        <f>IF($L41="","",INDEX(Flux!$H$2:$H$35,$L41))</f>
         <v/>
       </c>
       <c r="G41" s="41">
-        <f>IF(AND('2 Matériel'!$L29&gt;0,NOT('2 Matériel'!$B29="Oui")),IF(AND(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G29="","",'2 Matériel'!$G29)),"")</f>
+        <f>IF($L41="","",INDEX(Flux!$I$2:$I$35,$L41))</f>
         <v/>
       </c>
       <c r="H41" s="41">
-        <f>IF(AND('2 Matériel'!$L29&gt;0,NOT('2 Matériel'!$B29="Oui")),IF(AND(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H29="","",'2 Matériel'!$H29)),"")</f>
+        <f>IF($L41="","",INDEX(Flux!$J$2:$J$35,$L41))</f>
         <v/>
       </c>
       <c r="I41" s="41">
-        <f>IF(AND('2 Matériel'!$L29&gt;0,NOT('2 Matériel'!$B29="Oui")),IF(AND(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I29="","",'2 Matériel'!$I29)),"")</f>
+        <f>IF($L41="","",INDEX(Flux!$K$2:$K$35,$L41))</f>
         <v/>
       </c>
       <c r="J41" s="41">
-        <f>IF(AND('2 Matériel'!$L29&gt;0,NOT('2 Matériel'!$B29="Oui")),IF(AND(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J29="","",'2 Matériel'!$J29)),"")</f>
+        <f>IF($L41="","",INDEX(Flux!$L$2:$L$35,$L41))</f>
         <v/>
       </c>
       <c r="L41" s="42">
-        <f>IF(AND('2 Matériel'!$L29&gt;0,'2 Matériel'!$B29="Oui"),1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="B42" s="43">
-        <f>IF(SUM('2 Matériel'!$L$24:$L$29)&gt;0,"⚠  Des lignes de matériel au-delà de la ligne 18 sont masquées : cliquer sur le [+] dans la marge gauche pour les afficher.","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="8" customHeight="1"/>
-    <row r="44" ht="20" customHeight="1">
-      <c r="B44" s="44">
-        <f>IF('3 Options'!$C$8="Oui",INDEX(Textes!$B$2:$C$55,MATCH("sec_tight",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
-        <v/>
-      </c>
-      <c r="C44" s="45" t="n"/>
-      <c r="D44" s="45">
-        <f>IF('3 Options'!$C$8="Oui",INDEX(Textes!$B$2:$C$55,MATCH("h_qty",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
-        <v/>
-      </c>
-      <c r="E44" s="46">
-        <f>IF('3 Options'!$C$8="Oui",INDEX(Textes!$B$2:$C$55,MATCH("h_unit",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
-        <v/>
-      </c>
-      <c r="F44" s="46">
-        <f>IF('3 Options'!$C$8="Oui",INDEX(Textes!$B$2:$C$55,MATCH("h_pu",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
-        <v/>
-      </c>
-      <c r="G44" s="45">
-        <f>IF('3 Options'!$C$8="Oui",INDEX(Textes!$B$2:$C$55,MATCH("h_tot",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
-        <v/>
-      </c>
-      <c r="H44" s="44">
-        <f>IF('3 Options'!$C$8="Oui",INDEX(Textes!$B$2:$C$55,MATCH("h_det",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
-        <v/>
-      </c>
-      <c r="I44" s="45" t="n"/>
-      <c r="J44" s="45" t="n"/>
+        <f>IFERROR(MATCH(26,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M41" s="42">
+        <f>IF(L41="","",INDEX(Flux!$C$2:$C$35,L41))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" hidden="1" outlineLevel="1" ht="22" customHeight="1">
+      <c r="B42" s="38">
+        <f>IF($L42="","",INDEX(Flux!$D$2:$D$35,$L42))</f>
+        <v/>
+      </c>
+      <c r="C42" s="39">
+        <f>IF($L42="","",INDEX(Flux!$E$2:$E$35,$L42))</f>
+        <v/>
+      </c>
+      <c r="D42" s="40">
+        <f>IF($L42="","",INDEX(Flux!$F$2:$F$35,$L42))</f>
+        <v/>
+      </c>
+      <c r="E42" s="41">
+        <f>IF($L42="","",INDEX(Flux!$G$2:$G$35,$L42))</f>
+        <v/>
+      </c>
+      <c r="F42" s="41">
+        <f>IF($L42="","",INDEX(Flux!$H$2:$H$35,$L42))</f>
+        <v/>
+      </c>
+      <c r="G42" s="41">
+        <f>IF($L42="","",INDEX(Flux!$I$2:$I$35,$L42))</f>
+        <v/>
+      </c>
+      <c r="H42" s="41">
+        <f>IF($L42="","",INDEX(Flux!$J$2:$J$35,$L42))</f>
+        <v/>
+      </c>
+      <c r="I42" s="41">
+        <f>IF($L42="","",INDEX(Flux!$K$2:$K$35,$L42))</f>
+        <v/>
+      </c>
+      <c r="J42" s="41">
+        <f>IF($L42="","",INDEX(Flux!$L$2:$L$35,$L42))</f>
+        <v/>
+      </c>
+      <c r="L42" s="42">
+        <f>IFERROR(MATCH(27,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M42" s="42">
+        <f>IF(L42="","",INDEX(Flux!$C$2:$C$35,L42))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" hidden="1" outlineLevel="1" ht="22" customHeight="1">
+      <c r="B43" s="38">
+        <f>IF($L43="","",INDEX(Flux!$D$2:$D$35,$L43))</f>
+        <v/>
+      </c>
+      <c r="C43" s="39">
+        <f>IF($L43="","",INDEX(Flux!$E$2:$E$35,$L43))</f>
+        <v/>
+      </c>
+      <c r="D43" s="40">
+        <f>IF($L43="","",INDEX(Flux!$F$2:$F$35,$L43))</f>
+        <v/>
+      </c>
+      <c r="E43" s="41">
+        <f>IF($L43="","",INDEX(Flux!$G$2:$G$35,$L43))</f>
+        <v/>
+      </c>
+      <c r="F43" s="41">
+        <f>IF($L43="","",INDEX(Flux!$H$2:$H$35,$L43))</f>
+        <v/>
+      </c>
+      <c r="G43" s="41">
+        <f>IF($L43="","",INDEX(Flux!$I$2:$I$35,$L43))</f>
+        <v/>
+      </c>
+      <c r="H43" s="41">
+        <f>IF($L43="","",INDEX(Flux!$J$2:$J$35,$L43))</f>
+        <v/>
+      </c>
+      <c r="I43" s="41">
+        <f>IF($L43="","",INDEX(Flux!$K$2:$K$35,$L43))</f>
+        <v/>
+      </c>
+      <c r="J43" s="41">
+        <f>IF($L43="","",INDEX(Flux!$L$2:$L$35,$L43))</f>
+        <v/>
+      </c>
+      <c r="L43" s="42">
+        <f>IFERROR(MATCH(28,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M43" s="42">
+        <f>IF(L43="","",INDEX(Flux!$C$2:$C$35,L43))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" hidden="1" outlineLevel="1" ht="22" customHeight="1">
+      <c r="B44" s="38">
+        <f>IF($L44="","",INDEX(Flux!$D$2:$D$35,$L44))</f>
+        <v/>
+      </c>
+      <c r="C44" s="39">
+        <f>IF($L44="","",INDEX(Flux!$E$2:$E$35,$L44))</f>
+        <v/>
+      </c>
+      <c r="D44" s="40">
+        <f>IF($L44="","",INDEX(Flux!$F$2:$F$35,$L44))</f>
+        <v/>
+      </c>
+      <c r="E44" s="41">
+        <f>IF($L44="","",INDEX(Flux!$G$2:$G$35,$L44))</f>
+        <v/>
+      </c>
+      <c r="F44" s="41">
+        <f>IF($L44="","",INDEX(Flux!$H$2:$H$35,$L44))</f>
+        <v/>
+      </c>
+      <c r="G44" s="41">
+        <f>IF($L44="","",INDEX(Flux!$I$2:$I$35,$L44))</f>
+        <v/>
+      </c>
+      <c r="H44" s="41">
+        <f>IF($L44="","",INDEX(Flux!$J$2:$J$35,$L44))</f>
+        <v/>
+      </c>
+      <c r="I44" s="41">
+        <f>IF($L44="","",INDEX(Flux!$K$2:$K$35,$L44))</f>
+        <v/>
+      </c>
+      <c r="J44" s="41">
+        <f>IF($L44="","",INDEX(Flux!$L$2:$L$35,$L44))</f>
+        <v/>
+      </c>
       <c r="L44" s="42">
-        <f>IF('3 Options'!$C$8="Oui",1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="21" customHeight="1">
-      <c r="C45" s="47">
-        <f>IF('3 Options'!$C$8="Oui",IF('3 Options'!$D$8&lt;&gt;"",'3 Options'!$D$8,INDEX(Textes!$B$2:$C$55,MATCH("tight",Textes!$A$2:$A$55,0),Listes!$H$1)),"")</f>
-        <v/>
-      </c>
-      <c r="D45" s="48">
-        <f>IF('3 Options'!$C$8="Oui",IF('3 Options'!$G$8="Coût réel +15 %","",'3 Options'!$E$8),"")</f>
-        <v/>
-      </c>
-      <c r="E45" s="49">
-        <f>IF('3 Options'!$C$8="Oui",IF('3 Options'!$G$8="Coût réel +15 %","",'3 Options'!$G$8),"")</f>
-        <v/>
-      </c>
-      <c r="F45" s="50">
-        <f>IF('3 Options'!$C$8="Oui",IF('3 Options'!$G$8="Coût réel +15 %",INDEX(Textes!$B$2:$C$55,MATCH("at_cost",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$F$8="","",'3 Options'!$F$8)),"")</f>
-        <v/>
-      </c>
-      <c r="G45" s="51">
-        <f>IF('3 Options'!$C$8="Oui",IF('3 Options'!$G$8="Coût réel +15 %","—",'3 Options'!$H$8),"")</f>
-        <v/>
-      </c>
-      <c r="H45" s="52">
-        <f>""</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="8" customHeight="1"/>
-    <row r="47" ht="20" customHeight="1">
-      <c r="B47" s="44">
-        <f>IF(OR('3 Options'!$C$9="Oui",'3 Options'!$C$10="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("sec_tr",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
-        <v/>
-      </c>
-      <c r="C47" s="45" t="n"/>
-      <c r="D47" s="45">
-        <f>IF(OR('3 Options'!$C$9="Oui",'3 Options'!$C$10="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("h_qty",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
-        <v/>
-      </c>
-      <c r="E47" s="46">
-        <f>IF(OR('3 Options'!$C$9="Oui",'3 Options'!$C$10="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("h_unit",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
-        <v/>
-      </c>
-      <c r="F47" s="46">
-        <f>IF(OR('3 Options'!$C$9="Oui",'3 Options'!$C$10="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("h_pu",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
-        <v/>
-      </c>
-      <c r="G47" s="45">
-        <f>IF(OR('3 Options'!$C$9="Oui",'3 Options'!$C$10="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("h_tot",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
-        <v/>
-      </c>
-      <c r="H47" s="44">
-        <f>IF(OR('3 Options'!$C$9="Oui",'3 Options'!$C$10="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("h_det",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
-        <v/>
-      </c>
-      <c r="I47" s="45" t="n"/>
-      <c r="J47" s="45" t="n"/>
+        <f>IFERROR(MATCH(29,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M44" s="42">
+        <f>IF(L44="","",INDEX(Flux!$C$2:$C$35,L44))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" hidden="1" outlineLevel="1" ht="22" customHeight="1">
+      <c r="B45" s="38">
+        <f>IF($L45="","",INDEX(Flux!$D$2:$D$35,$L45))</f>
+        <v/>
+      </c>
+      <c r="C45" s="39">
+        <f>IF($L45="","",INDEX(Flux!$E$2:$E$35,$L45))</f>
+        <v/>
+      </c>
+      <c r="D45" s="40">
+        <f>IF($L45="","",INDEX(Flux!$F$2:$F$35,$L45))</f>
+        <v/>
+      </c>
+      <c r="E45" s="41">
+        <f>IF($L45="","",INDEX(Flux!$G$2:$G$35,$L45))</f>
+        <v/>
+      </c>
+      <c r="F45" s="41">
+        <f>IF($L45="","",INDEX(Flux!$H$2:$H$35,$L45))</f>
+        <v/>
+      </c>
+      <c r="G45" s="41">
+        <f>IF($L45="","",INDEX(Flux!$I$2:$I$35,$L45))</f>
+        <v/>
+      </c>
+      <c r="H45" s="41">
+        <f>IF($L45="","",INDEX(Flux!$J$2:$J$35,$L45))</f>
+        <v/>
+      </c>
+      <c r="I45" s="41">
+        <f>IF($L45="","",INDEX(Flux!$K$2:$K$35,$L45))</f>
+        <v/>
+      </c>
+      <c r="J45" s="41">
+        <f>IF($L45="","",INDEX(Flux!$L$2:$L$35,$L45))</f>
+        <v/>
+      </c>
+      <c r="L45" s="42">
+        <f>IFERROR(MATCH(30,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M45" s="42">
+        <f>IF(L45="","",INDEX(Flux!$C$2:$C$35,L45))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" hidden="1" outlineLevel="1" ht="22" customHeight="1">
+      <c r="B46" s="38">
+        <f>IF($L46="","",INDEX(Flux!$D$2:$D$35,$L46))</f>
+        <v/>
+      </c>
+      <c r="C46" s="39">
+        <f>IF($L46="","",INDEX(Flux!$E$2:$E$35,$L46))</f>
+        <v/>
+      </c>
+      <c r="D46" s="40">
+        <f>IF($L46="","",INDEX(Flux!$F$2:$F$35,$L46))</f>
+        <v/>
+      </c>
+      <c r="E46" s="41">
+        <f>IF($L46="","",INDEX(Flux!$G$2:$G$35,$L46))</f>
+        <v/>
+      </c>
+      <c r="F46" s="41">
+        <f>IF($L46="","",INDEX(Flux!$H$2:$H$35,$L46))</f>
+        <v/>
+      </c>
+      <c r="G46" s="41">
+        <f>IF($L46="","",INDEX(Flux!$I$2:$I$35,$L46))</f>
+        <v/>
+      </c>
+      <c r="H46" s="41">
+        <f>IF($L46="","",INDEX(Flux!$J$2:$J$35,$L46))</f>
+        <v/>
+      </c>
+      <c r="I46" s="41">
+        <f>IF($L46="","",INDEX(Flux!$K$2:$K$35,$L46))</f>
+        <v/>
+      </c>
+      <c r="J46" s="41">
+        <f>IF($L46="","",INDEX(Flux!$L$2:$L$35,$L46))</f>
+        <v/>
+      </c>
+      <c r="L46" s="42">
+        <f>IFERROR(MATCH(31,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M46" s="42">
+        <f>IF(L46="","",INDEX(Flux!$C$2:$C$35,L46))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" hidden="1" outlineLevel="1" ht="22" customHeight="1">
+      <c r="B47" s="38">
+        <f>IF($L47="","",INDEX(Flux!$D$2:$D$35,$L47))</f>
+        <v/>
+      </c>
+      <c r="C47" s="39">
+        <f>IF($L47="","",INDEX(Flux!$E$2:$E$35,$L47))</f>
+        <v/>
+      </c>
+      <c r="D47" s="40">
+        <f>IF($L47="","",INDEX(Flux!$F$2:$F$35,$L47))</f>
+        <v/>
+      </c>
+      <c r="E47" s="41">
+        <f>IF($L47="","",INDEX(Flux!$G$2:$G$35,$L47))</f>
+        <v/>
+      </c>
+      <c r="F47" s="41">
+        <f>IF($L47="","",INDEX(Flux!$H$2:$H$35,$L47))</f>
+        <v/>
+      </c>
+      <c r="G47" s="41">
+        <f>IF($L47="","",INDEX(Flux!$I$2:$I$35,$L47))</f>
+        <v/>
+      </c>
+      <c r="H47" s="41">
+        <f>IF($L47="","",INDEX(Flux!$J$2:$J$35,$L47))</f>
+        <v/>
+      </c>
+      <c r="I47" s="41">
+        <f>IF($L47="","",INDEX(Flux!$K$2:$K$35,$L47))</f>
+        <v/>
+      </c>
+      <c r="J47" s="41">
+        <f>IF($L47="","",INDEX(Flux!$L$2:$L$35,$L47))</f>
+        <v/>
+      </c>
       <c r="L47" s="42">
-        <f>IF(OR('3 Options'!$C$9="Oui",'3 Options'!$C$10="Oui"),1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="21" customHeight="1">
-      <c r="C48" s="47">
-        <f>IF('3 Options'!$C$9="Oui",IF('3 Options'!$D$9&lt;&gt;"",'3 Options'!$D$9,INDEX(Textes!$B$2:$C$55,MATCH("tr_mob",Textes!$A$2:$A$55,0),Listes!$H$1)),"")</f>
-        <v/>
-      </c>
-      <c r="D48" s="48">
-        <f>IF('3 Options'!$C$9="Oui",IF('3 Options'!$G$9="Coût réel +15 %","",'3 Options'!$E$9),"")</f>
-        <v/>
-      </c>
-      <c r="E48" s="49">
-        <f>IF('3 Options'!$C$9="Oui",IF('3 Options'!$G$9="Coût réel +15 %","",'3 Options'!$G$9),"")</f>
-        <v/>
-      </c>
-      <c r="F48" s="50">
-        <f>IF('3 Options'!$C$9="Oui",IF('3 Options'!$G$9="Coût réel +15 %",INDEX(Textes!$B$2:$C$55,MATCH("at_cost",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$F$9="","",'3 Options'!$F$9)),"")</f>
-        <v/>
-      </c>
-      <c r="G48" s="51">
-        <f>IF('3 Options'!$C$9="Oui",IF('3 Options'!$G$9="Coût réel +15 %","—",'3 Options'!$H$9),"")</f>
-        <v/>
-      </c>
-      <c r="H48" s="52">
-        <f>IF('3 Options'!$C$9="Oui",INDEX(Textes!$B$2:$C$55,MATCH("tr_note",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="21" customHeight="1">
-      <c r="C49" s="47">
-        <f>IF('3 Options'!$C$10="Oui",IF('3 Options'!$D$10&lt;&gt;"",'3 Options'!$D$10,INDEX(Textes!$B$2:$C$55,MATCH("tr_dem",Textes!$A$2:$A$55,0),Listes!$H$1)),"")</f>
-        <v/>
-      </c>
-      <c r="D49" s="48">
-        <f>IF('3 Options'!$C$10="Oui",IF('3 Options'!$G$10="Coût réel +15 %","",'3 Options'!$E$10),"")</f>
-        <v/>
-      </c>
-      <c r="E49" s="49">
-        <f>IF('3 Options'!$C$10="Oui",IF('3 Options'!$G$10="Coût réel +15 %","",'3 Options'!$G$10),"")</f>
-        <v/>
-      </c>
-      <c r="F49" s="50">
-        <f>IF('3 Options'!$C$10="Oui",IF('3 Options'!$G$10="Coût réel +15 %",INDEX(Textes!$B$2:$C$55,MATCH("at_cost",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$F$10="","",'3 Options'!$F$10)),"")</f>
-        <v/>
-      </c>
-      <c r="G49" s="51">
-        <f>IF('3 Options'!$C$10="Oui",IF('3 Options'!$G$10="Coût réel +15 %","—",'3 Options'!$H$10),"")</f>
-        <v/>
-      </c>
-      <c r="H49" s="52">
-        <f>IF('3 Options'!$C$10="Oui",INDEX(Textes!$B$2:$C$55,MATCH("tr_note",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="8" customHeight="1"/>
-    <row r="51" ht="20" customHeight="1">
-      <c r="B51" s="44">
-        <f>IF(OR('3 Options'!$C$6="Oui",'3 Options'!$C$7="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("sec_op",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
-        <v/>
-      </c>
-      <c r="C51" s="45" t="n"/>
-      <c r="D51" s="45">
-        <f>IF(OR('3 Options'!$C$6="Oui",'3 Options'!$C$7="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("h_qty",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
-        <v/>
-      </c>
-      <c r="E51" s="46">
-        <f>IF(OR('3 Options'!$C$6="Oui",'3 Options'!$C$7="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("h_unit",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
-        <v/>
-      </c>
-      <c r="F51" s="46">
-        <f>IF(OR('3 Options'!$C$6="Oui",'3 Options'!$C$7="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("h_pu",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
-        <v/>
-      </c>
-      <c r="G51" s="45">
-        <f>IF(OR('3 Options'!$C$6="Oui",'3 Options'!$C$7="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("h_tot",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
-        <v/>
-      </c>
-      <c r="H51" s="44">
-        <f>IF(OR('3 Options'!$C$6="Oui",'3 Options'!$C$7="Oui"),INDEX(Textes!$B$2:$C$55,MATCH("h_det",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
-        <v/>
-      </c>
-      <c r="I51" s="45" t="n"/>
-      <c r="J51" s="45" t="n"/>
+        <f>IFERROR(MATCH(32,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M47" s="42">
+        <f>IF(L47="","",INDEX(Flux!$C$2:$C$35,L47))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" hidden="1" outlineLevel="1" ht="22" customHeight="1">
+      <c r="B48" s="38">
+        <f>IF($L48="","",INDEX(Flux!$D$2:$D$35,$L48))</f>
+        <v/>
+      </c>
+      <c r="C48" s="39">
+        <f>IF($L48="","",INDEX(Flux!$E$2:$E$35,$L48))</f>
+        <v/>
+      </c>
+      <c r="D48" s="40">
+        <f>IF($L48="","",INDEX(Flux!$F$2:$F$35,$L48))</f>
+        <v/>
+      </c>
+      <c r="E48" s="41">
+        <f>IF($L48="","",INDEX(Flux!$G$2:$G$35,$L48))</f>
+        <v/>
+      </c>
+      <c r="F48" s="41">
+        <f>IF($L48="","",INDEX(Flux!$H$2:$H$35,$L48))</f>
+        <v/>
+      </c>
+      <c r="G48" s="41">
+        <f>IF($L48="","",INDEX(Flux!$I$2:$I$35,$L48))</f>
+        <v/>
+      </c>
+      <c r="H48" s="41">
+        <f>IF($L48="","",INDEX(Flux!$J$2:$J$35,$L48))</f>
+        <v/>
+      </c>
+      <c r="I48" s="41">
+        <f>IF($L48="","",INDEX(Flux!$K$2:$K$35,$L48))</f>
+        <v/>
+      </c>
+      <c r="J48" s="41">
+        <f>IF($L48="","",INDEX(Flux!$L$2:$L$35,$L48))</f>
+        <v/>
+      </c>
+      <c r="L48" s="42">
+        <f>IFERROR(MATCH(33,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M48" s="42">
+        <f>IF(L48="","",INDEX(Flux!$C$2:$C$35,L48))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" hidden="1" outlineLevel="1" ht="22" customHeight="1">
+      <c r="B49" s="38">
+        <f>IF($L49="","",INDEX(Flux!$D$2:$D$35,$L49))</f>
+        <v/>
+      </c>
+      <c r="C49" s="39">
+        <f>IF($L49="","",INDEX(Flux!$E$2:$E$35,$L49))</f>
+        <v/>
+      </c>
+      <c r="D49" s="40">
+        <f>IF($L49="","",INDEX(Flux!$F$2:$F$35,$L49))</f>
+        <v/>
+      </c>
+      <c r="E49" s="41">
+        <f>IF($L49="","",INDEX(Flux!$G$2:$G$35,$L49))</f>
+        <v/>
+      </c>
+      <c r="F49" s="41">
+        <f>IF($L49="","",INDEX(Flux!$H$2:$H$35,$L49))</f>
+        <v/>
+      </c>
+      <c r="G49" s="41">
+        <f>IF($L49="","",INDEX(Flux!$I$2:$I$35,$L49))</f>
+        <v/>
+      </c>
+      <c r="H49" s="41">
+        <f>IF($L49="","",INDEX(Flux!$J$2:$J$35,$L49))</f>
+        <v/>
+      </c>
+      <c r="I49" s="41">
+        <f>IF($L49="","",INDEX(Flux!$K$2:$K$35,$L49))</f>
+        <v/>
+      </c>
+      <c r="J49" s="41">
+        <f>IF($L49="","",INDEX(Flux!$L$2:$L$35,$L49))</f>
+        <v/>
+      </c>
+      <c r="L49" s="42">
+        <f>IFERROR(MATCH(34,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M49" s="42">
+        <f>IF(L49="","",INDEX(Flux!$C$2:$C$35,L49))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" hidden="1" outlineLevel="1" ht="22" customHeight="1">
+      <c r="B50" s="38">
+        <f>IF($L50="","",INDEX(Flux!$D$2:$D$35,$L50))</f>
+        <v/>
+      </c>
+      <c r="C50" s="39">
+        <f>IF($L50="","",INDEX(Flux!$E$2:$E$35,$L50))</f>
+        <v/>
+      </c>
+      <c r="D50" s="40">
+        <f>IF($L50="","",INDEX(Flux!$F$2:$F$35,$L50))</f>
+        <v/>
+      </c>
+      <c r="E50" s="41">
+        <f>IF($L50="","",INDEX(Flux!$G$2:$G$35,$L50))</f>
+        <v/>
+      </c>
+      <c r="F50" s="41">
+        <f>IF($L50="","",INDEX(Flux!$H$2:$H$35,$L50))</f>
+        <v/>
+      </c>
+      <c r="G50" s="41">
+        <f>IF($L50="","",INDEX(Flux!$I$2:$I$35,$L50))</f>
+        <v/>
+      </c>
+      <c r="H50" s="41">
+        <f>IF($L50="","",INDEX(Flux!$J$2:$J$35,$L50))</f>
+        <v/>
+      </c>
+      <c r="I50" s="41">
+        <f>IF($L50="","",INDEX(Flux!$K$2:$K$35,$L50))</f>
+        <v/>
+      </c>
+      <c r="J50" s="41">
+        <f>IF($L50="","",INDEX(Flux!$L$2:$L$35,$L50))</f>
+        <v/>
+      </c>
+      <c r="L50" s="42">
+        <f>IFERROR(MATCH(35,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M50" s="42">
+        <f>IF(L50="","",INDEX(Flux!$C$2:$C$35,L50))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" hidden="1" outlineLevel="1" ht="22" customHeight="1">
+      <c r="B51" s="38">
+        <f>IF($L51="","",INDEX(Flux!$D$2:$D$35,$L51))</f>
+        <v/>
+      </c>
+      <c r="C51" s="39">
+        <f>IF($L51="","",INDEX(Flux!$E$2:$E$35,$L51))</f>
+        <v/>
+      </c>
+      <c r="D51" s="40">
+        <f>IF($L51="","",INDEX(Flux!$F$2:$F$35,$L51))</f>
+        <v/>
+      </c>
+      <c r="E51" s="41">
+        <f>IF($L51="","",INDEX(Flux!$G$2:$G$35,$L51))</f>
+        <v/>
+      </c>
+      <c r="F51" s="41">
+        <f>IF($L51="","",INDEX(Flux!$H$2:$H$35,$L51))</f>
+        <v/>
+      </c>
+      <c r="G51" s="41">
+        <f>IF($L51="","",INDEX(Flux!$I$2:$I$35,$L51))</f>
+        <v/>
+      </c>
+      <c r="H51" s="41">
+        <f>IF($L51="","",INDEX(Flux!$J$2:$J$35,$L51))</f>
+        <v/>
+      </c>
+      <c r="I51" s="41">
+        <f>IF($L51="","",INDEX(Flux!$K$2:$K$35,$L51))</f>
+        <v/>
+      </c>
+      <c r="J51" s="41">
+        <f>IF($L51="","",INDEX(Flux!$L$2:$L$35,$L51))</f>
+        <v/>
+      </c>
       <c r="L51" s="42">
-        <f>IF(OR('3 Options'!$C$6="Oui",'3 Options'!$C$7="Oui"),1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="21" customHeight="1">
-      <c r="C52" s="47">
-        <f>IF('3 Options'!$C$6="Oui",IF('3 Options'!$D$6&lt;&gt;"",'3 Options'!$D$6,INDEX(Textes!$B$2:$C$55,MATCH("op_day",Textes!$A$2:$A$55,0),Listes!$H$1)),"")</f>
-        <v/>
-      </c>
-      <c r="D52" s="48">
-        <f>IF('3 Options'!$C$6="Oui",IF('3 Options'!$G$6="Coût réel +15 %","",'3 Options'!$E$6),"")</f>
-        <v/>
-      </c>
-      <c r="E52" s="49">
-        <f>IF('3 Options'!$C$6="Oui",IF('3 Options'!$G$6="Coût réel +15 %","",'3 Options'!$G$6),"")</f>
-        <v/>
-      </c>
-      <c r="F52" s="50">
-        <f>IF('3 Options'!$C$6="Oui",IF('3 Options'!$G$6="Coût réel +15 %",INDEX(Textes!$B$2:$C$55,MATCH("at_cost",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$F$6="","",'3 Options'!$F$6)),"")</f>
-        <v/>
-      </c>
-      <c r="G52" s="51">
-        <f>IF('3 Options'!$C$6="Oui",IF('3 Options'!$G$6="Coût réel +15 %","—",'3 Options'!$H$6),"")</f>
-        <v/>
-      </c>
-      <c r="H52" s="52">
-        <f>""</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="21" customHeight="1">
-      <c r="C53" s="47">
-        <f>IF('3 Options'!$C$7="Oui",IF('3 Options'!$D$7&lt;&gt;"",'3 Options'!$D$7,INDEX(Textes!$B$2:$C$55,MATCH("op_mob",Textes!$A$2:$A$55,0),Listes!$H$1)),"")</f>
-        <v/>
-      </c>
-      <c r="D53" s="48">
-        <f>IF('3 Options'!$C$7="Oui",IF('3 Options'!$G$7="Coût réel +15 %","",'3 Options'!$E$7),"")</f>
-        <v/>
-      </c>
-      <c r="E53" s="49">
-        <f>IF('3 Options'!$C$7="Oui",IF('3 Options'!$G$7="Coût réel +15 %","",'3 Options'!$G$7),"")</f>
-        <v/>
-      </c>
-      <c r="F53" s="50">
-        <f>IF('3 Options'!$C$7="Oui",IF('3 Options'!$G$7="Coût réel +15 %",INDEX(Textes!$B$2:$C$55,MATCH("at_cost",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$F$7="","",'3 Options'!$F$7)),"")</f>
-        <v/>
-      </c>
-      <c r="G53" s="51">
-        <f>IF('3 Options'!$C$7="Oui",IF('3 Options'!$G$7="Coût réel +15 %","—",'3 Options'!$H$7),"")</f>
-        <v/>
-      </c>
-      <c r="H53" s="52">
-        <f>""</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="8" customHeight="1"/>
-    <row r="55" ht="42" customHeight="1">
-      <c r="B55" s="53">
-        <f>IF('3 Options'!$C$13="Oui",UPPER(INDEX(Textes!$B$2:$C$55,MATCH("forfait",Textes!$A$2:$A$55,0),Listes!$H$1))&amp;IF('3 Options'!$D$13&lt;&gt;"","   ·   "&amp;'3 Options'!$D$13,""),"")</f>
-        <v/>
-      </c>
-      <c r="H55" s="54">
-        <f>IF('3 Options'!$C$13="Oui",'3 Options'!$H$13,"")</f>
+        <f>IFERROR(MATCH(36,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M51" s="42">
+        <f>IF(L51="","",INDEX(Flux!$C$2:$C$35,L51))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" hidden="1" outlineLevel="1" ht="22" customHeight="1">
+      <c r="B52" s="38">
+        <f>IF($L52="","",INDEX(Flux!$D$2:$D$35,$L52))</f>
+        <v/>
+      </c>
+      <c r="C52" s="39">
+        <f>IF($L52="","",INDEX(Flux!$E$2:$E$35,$L52))</f>
+        <v/>
+      </c>
+      <c r="D52" s="40">
+        <f>IF($L52="","",INDEX(Flux!$F$2:$F$35,$L52))</f>
+        <v/>
+      </c>
+      <c r="E52" s="41">
+        <f>IF($L52="","",INDEX(Flux!$G$2:$G$35,$L52))</f>
+        <v/>
+      </c>
+      <c r="F52" s="41">
+        <f>IF($L52="","",INDEX(Flux!$H$2:$H$35,$L52))</f>
+        <v/>
+      </c>
+      <c r="G52" s="41">
+        <f>IF($L52="","",INDEX(Flux!$I$2:$I$35,$L52))</f>
+        <v/>
+      </c>
+      <c r="H52" s="41">
+        <f>IF($L52="","",INDEX(Flux!$J$2:$J$35,$L52))</f>
+        <v/>
+      </c>
+      <c r="I52" s="41">
+        <f>IF($L52="","",INDEX(Flux!$K$2:$K$35,$L52))</f>
+        <v/>
+      </c>
+      <c r="J52" s="41">
+        <f>IF($L52="","",INDEX(Flux!$L$2:$L$35,$L52))</f>
+        <v/>
+      </c>
+      <c r="L52" s="42">
+        <f>IFERROR(MATCH(37,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M52" s="42">
+        <f>IF(L52="","",INDEX(Flux!$C$2:$C$35,L52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" hidden="1" outlineLevel="1" ht="22" customHeight="1">
+      <c r="B53" s="38">
+        <f>IF($L53="","",INDEX(Flux!$D$2:$D$35,$L53))</f>
+        <v/>
+      </c>
+      <c r="C53" s="39">
+        <f>IF($L53="","",INDEX(Flux!$E$2:$E$35,$L53))</f>
+        <v/>
+      </c>
+      <c r="D53" s="40">
+        <f>IF($L53="","",INDEX(Flux!$F$2:$F$35,$L53))</f>
+        <v/>
+      </c>
+      <c r="E53" s="41">
+        <f>IF($L53="","",INDEX(Flux!$G$2:$G$35,$L53))</f>
+        <v/>
+      </c>
+      <c r="F53" s="41">
+        <f>IF($L53="","",INDEX(Flux!$H$2:$H$35,$L53))</f>
+        <v/>
+      </c>
+      <c r="G53" s="41">
+        <f>IF($L53="","",INDEX(Flux!$I$2:$I$35,$L53))</f>
+        <v/>
+      </c>
+      <c r="H53" s="41">
+        <f>IF($L53="","",INDEX(Flux!$J$2:$J$35,$L53))</f>
+        <v/>
+      </c>
+      <c r="I53" s="41">
+        <f>IF($L53="","",INDEX(Flux!$K$2:$K$35,$L53))</f>
+        <v/>
+      </c>
+      <c r="J53" s="41">
+        <f>IF($L53="","",INDEX(Flux!$L$2:$L$35,$L53))</f>
+        <v/>
+      </c>
+      <c r="L53" s="42">
+        <f>IFERROR(MATCH(38,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M53" s="42">
+        <f>IF(L53="","",INDEX(Flux!$C$2:$C$35,L53))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" hidden="1" outlineLevel="1" ht="22" customHeight="1">
+      <c r="B54" s="38">
+        <f>IF($L54="","",INDEX(Flux!$D$2:$D$35,$L54))</f>
+        <v/>
+      </c>
+      <c r="C54" s="39">
+        <f>IF($L54="","",INDEX(Flux!$E$2:$E$35,$L54))</f>
+        <v/>
+      </c>
+      <c r="D54" s="40">
+        <f>IF($L54="","",INDEX(Flux!$F$2:$F$35,$L54))</f>
+        <v/>
+      </c>
+      <c r="E54" s="41">
+        <f>IF($L54="","",INDEX(Flux!$G$2:$G$35,$L54))</f>
+        <v/>
+      </c>
+      <c r="F54" s="41">
+        <f>IF($L54="","",INDEX(Flux!$H$2:$H$35,$L54))</f>
+        <v/>
+      </c>
+      <c r="G54" s="41">
+        <f>IF($L54="","",INDEX(Flux!$I$2:$I$35,$L54))</f>
+        <v/>
+      </c>
+      <c r="H54" s="41">
+        <f>IF($L54="","",INDEX(Flux!$J$2:$J$35,$L54))</f>
+        <v/>
+      </c>
+      <c r="I54" s="41">
+        <f>IF($L54="","",INDEX(Flux!$K$2:$K$35,$L54))</f>
+        <v/>
+      </c>
+      <c r="J54" s="41">
+        <f>IF($L54="","",INDEX(Flux!$L$2:$L$35,$L54))</f>
+        <v/>
+      </c>
+      <c r="L54" s="42">
+        <f>IFERROR(MATCH(39,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M54" s="42">
+        <f>IF(L54="","",INDEX(Flux!$C$2:$C$35,L54))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" hidden="1" outlineLevel="1" ht="22" customHeight="1">
+      <c r="B55" s="38">
+        <f>IF($L55="","",INDEX(Flux!$D$2:$D$35,$L55))</f>
+        <v/>
+      </c>
+      <c r="C55" s="39">
+        <f>IF($L55="","",INDEX(Flux!$E$2:$E$35,$L55))</f>
+        <v/>
+      </c>
+      <c r="D55" s="40">
+        <f>IF($L55="","",INDEX(Flux!$F$2:$F$35,$L55))</f>
+        <v/>
+      </c>
+      <c r="E55" s="41">
+        <f>IF($L55="","",INDEX(Flux!$G$2:$G$35,$L55))</f>
+        <v/>
+      </c>
+      <c r="F55" s="41">
+        <f>IF($L55="","",INDEX(Flux!$H$2:$H$35,$L55))</f>
+        <v/>
+      </c>
+      <c r="G55" s="41">
+        <f>IF($L55="","",INDEX(Flux!$I$2:$I$35,$L55))</f>
+        <v/>
+      </c>
+      <c r="H55" s="41">
+        <f>IF($L55="","",INDEX(Flux!$J$2:$J$35,$L55))</f>
+        <v/>
+      </c>
+      <c r="I55" s="41">
+        <f>IF($L55="","",INDEX(Flux!$K$2:$K$35,$L55))</f>
+        <v/>
+      </c>
+      <c r="J55" s="41">
+        <f>IF($L55="","",INDEX(Flux!$L$2:$L$35,$L55))</f>
         <v/>
       </c>
       <c r="L55" s="42">
-        <f>IF('3 Options'!$C$13="Oui",1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" ht="34" customHeight="1">
-      <c r="B56" s="55">
-        <f>IF('3 Options'!$C$13="Oui",IF('3 Options'!$G$13="Forfait calculé (S + O + UC)",'3 Options'!$C$15&amp;" "&amp;SUBSTITUTE(INDEX(Textes!$B$2:$C$55,MATCH("calc_det",Textes!$A$2:$A$55,0),Listes!$H$1),"%s",'3 Options'!$C$16)&amp;"   ·   "&amp;INDEX(Textes!$B$2:$C$55,MATCH("ht",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$G$13="Forfait par jour",'3 Options'!$E$13&amp;" j × "&amp;TEXT('3 Options'!$F$13,"#,##0.00")&amp;" €/j   ·   "&amp;INDEX(Textes!$B$2:$C$55,MATCH("ht",Textes!$A$2:$A$55,0),Listes!$H$1),INDEX(Textes!$B$2:$C$55,MATCH("ht",Textes!$A$2:$A$55,0),Listes!$H$1)))&amp;IF('3 Options'!$D$14&lt;&gt;"","   ·   "&amp;'3 Options'!$D$14,""),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="10" customHeight="1"/>
+        <f>IFERROR(MATCH(40,Flux!$B$2:$B$35,0),"")</f>
+        <v/>
+      </c>
+      <c r="M55" s="42">
+        <f>IF(L55="","",INDEX(Flux!$C$2:$C$35,L55))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="B56" s="43">
+        <f>IF(MAX(Flux!$B$2:$B$35)&gt;26,"⚠  Le devis contient plus de 26 lignes : cliquer sur le [+] dans la marge gauche pour afficher les lignes masquées.","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="8" customHeight="1"/>
     <row r="58" ht="20" customHeight="1">
       <c r="B58" s="34">
         <f>INDEX(Textes!$B$2:$C$55,MATCH("sec_cond",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
@@ -4032,7 +4571,7 @@
       <c r="J58" s="35" t="n"/>
     </row>
     <row r="59" ht="76" customHeight="1">
-      <c r="B59" s="56" t="inlineStr">
+      <c r="B59" s="44" t="inlineStr">
         <is>
           <t>La location s'entend depuis le jour de départ de la base d'origine jusqu'à son retour au même endroit.
 Le Wear Charge s'applique pour toute usure liée à un usage normal des équipements. En cas de dommages plus importants liés à un usage anormal, la valeur de remplacement sera facturée sur documentation.
@@ -4042,7 +4581,7 @@
       </c>
     </row>
     <row r="60" ht="76" customHeight="1">
-      <c r="B60" s="56" t="inlineStr">
+      <c r="B60" s="44" t="inlineStr">
         <is>
           <t>The rental is from the day of departure from the base of origin until its return to the same place.
 Wear Charge applies to all wear and tear related to normal use of equipment. In case of greater damage due to abnormal use, the replacement value will be charged based on supporting documentation.
@@ -4053,101 +4592,90 @@
     </row>
     <row r="61" ht="10" customHeight="1"/>
     <row r="62">
-      <c r="B62" s="57">
+      <c r="B62" s="45">
         <f>INDEX(Textes!$B$2:$C$55,MATCH("accept",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
     </row>
     <row r="63" ht="17" customHeight="1">
-      <c r="B63" s="58">
+      <c r="B63" s="46">
         <f>INDEX(Textes!$B$2:$C$55,MATCH("sig_name",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="C63" s="59" t="n"/>
-      <c r="D63" s="58">
+      <c r="C63" s="47" t="n"/>
+      <c r="D63" s="46">
         <f>INDEX(Textes!$B$2:$C$55,MATCH("sig_date",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="E63" s="60" t="n"/>
-      <c r="F63" s="60" t="n"/>
-      <c r="G63" s="59" t="n"/>
-      <c r="H63" s="58">
+      <c r="E63" s="48" t="n"/>
+      <c r="F63" s="48" t="n"/>
+      <c r="G63" s="47" t="n"/>
+      <c r="H63" s="46">
         <f>INDEX(Textes!$B$2:$C$55,MATCH("sig_sig",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="I63" s="60" t="n"/>
-      <c r="J63" s="59" t="n"/>
+      <c r="I63" s="48" t="n"/>
+      <c r="J63" s="47" t="n"/>
     </row>
     <row r="64" ht="17" customHeight="1">
-      <c r="B64" s="61" t="n"/>
-      <c r="C64" s="62" t="n"/>
-      <c r="D64" s="61" t="n"/>
-      <c r="E64" s="63" t="n"/>
-      <c r="F64" s="63" t="n"/>
-      <c r="G64" s="62" t="n"/>
-      <c r="H64" s="61" t="n"/>
-      <c r="I64" s="63" t="n"/>
-      <c r="J64" s="62" t="n"/>
+      <c r="B64" s="49" t="n"/>
+      <c r="C64" s="50" t="n"/>
+      <c r="D64" s="49" t="n"/>
+      <c r="E64" s="51" t="n"/>
+      <c r="F64" s="51" t="n"/>
+      <c r="G64" s="50" t="n"/>
+      <c r="H64" s="49" t="n"/>
+      <c r="I64" s="51" t="n"/>
+      <c r="J64" s="50" t="n"/>
     </row>
     <row r="65" ht="17" customHeight="1">
-      <c r="B65" s="61" t="n"/>
-      <c r="C65" s="62" t="n"/>
-      <c r="D65" s="61" t="n"/>
-      <c r="E65" s="63" t="n"/>
-      <c r="F65" s="63" t="n"/>
-      <c r="G65" s="62" t="n"/>
-      <c r="H65" s="61" t="n"/>
-      <c r="I65" s="63" t="n"/>
-      <c r="J65" s="62" t="n"/>
+      <c r="B65" s="49" t="n"/>
+      <c r="C65" s="50" t="n"/>
+      <c r="D65" s="49" t="n"/>
+      <c r="E65" s="51" t="n"/>
+      <c r="F65" s="51" t="n"/>
+      <c r="G65" s="50" t="n"/>
+      <c r="H65" s="49" t="n"/>
+      <c r="I65" s="51" t="n"/>
+      <c r="J65" s="50" t="n"/>
     </row>
     <row r="66" ht="17" customHeight="1">
-      <c r="B66" s="64" t="n"/>
-      <c r="C66" s="65" t="n"/>
-      <c r="D66" s="64" t="n"/>
+      <c r="B66" s="52" t="n"/>
+      <c r="C66" s="53" t="n"/>
+      <c r="D66" s="52" t="n"/>
       <c r="E66" s="33" t="n"/>
       <c r="F66" s="33" t="n"/>
-      <c r="G66" s="65" t="n"/>
-      <c r="H66" s="64" t="n"/>
+      <c r="G66" s="53" t="n"/>
+      <c r="H66" s="52" t="n"/>
       <c r="I66" s="33" t="n"/>
-      <c r="J66" s="65" t="n"/>
+      <c r="J66" s="53" t="n"/>
     </row>
     <row r="68" ht="26" customHeight="1">
-      <c r="B68" s="66" t="inlineStr">
+      <c r="B68" s="54" t="inlineStr">
         <is>
           <t>ENEDRIL · Z-Induspal · 3 Av. des Lacs · 64140 LONS (France) · SIRET 79464246200020 · TVA FR11794642462</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="52">
-    <mergeCell ref="H49:J49"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="H51:J51"/>
+  <mergeCells count="36">
     <mergeCell ref="D9:G9"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D12:G12"/>
-    <mergeCell ref="B42:J42"/>
     <mergeCell ref="D8:G8"/>
-    <mergeCell ref="H52:J52"/>
+    <mergeCell ref="B14:J14"/>
     <mergeCell ref="B60:J60"/>
     <mergeCell ref="D5:G5"/>
     <mergeCell ref="H11:J11"/>
     <mergeCell ref="H7:J7"/>
-    <mergeCell ref="H45:J45"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="H63:J66"/>
-    <mergeCell ref="H47:J47"/>
-    <mergeCell ref="B14:C14"/>
     <mergeCell ref="H12:J12"/>
     <mergeCell ref="D10:G10"/>
     <mergeCell ref="D1:J1"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="H48:J48"/>
     <mergeCell ref="B68:J68"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B44:C44"/>
     <mergeCell ref="D6:G6"/>
     <mergeCell ref="H5:J5"/>
     <mergeCell ref="B10:C10"/>
@@ -4156,16 +4684,11 @@
     <mergeCell ref="D2:J2"/>
     <mergeCell ref="D11:G11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="H53:J53"/>
-    <mergeCell ref="B16:J16"/>
     <mergeCell ref="B62:J62"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="H10:J10"/>
     <mergeCell ref="B59:J59"/>
-    <mergeCell ref="H44:J44"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="H55:J55"/>
     <mergeCell ref="D7:G7"/>
     <mergeCell ref="B56:J56"/>
     <mergeCell ref="H9:J9"/>
@@ -4173,70 +4696,26 @@
     <mergeCell ref="D63:G66"/>
     <mergeCell ref="H6:J6"/>
   </mergeCells>
-  <conditionalFormatting sqref="B18:J41">
+  <conditionalFormatting sqref="B16:J55">
     <cfRule type="expression" priority="1" dxfId="1" stopIfTrue="1">
-      <formula>$L18=1</formula>
+      <formula>OR($M16="BAN",$M16="FB")</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="2">
-      <formula>$C18&lt;&gt;""</formula>
+    <cfRule type="expression" priority="2" dxfId="2" stopIfTrue="1">
+      <formula>$M16="HDR"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="3">
-      <formula>AND($C18&lt;&gt;"",MOD(ROW(),2)=0)</formula>
+    <cfRule type="expression" priority="3" dxfId="3" stopIfTrue="1">
+      <formula>$M16="FD"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="4">
+      <formula>OR($M16="ITM",$M16="LIN")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="5">
+      <formula>AND($M16="ITM",MOD(ROW(),2)=0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E18:J41">
-    <cfRule type="expression" priority="4" dxfId="4">
-      <formula>E18="incl."</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B44:J44">
-    <cfRule type="expression" priority="5" dxfId="5">
-      <formula>$L44=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B45:J45">
-    <cfRule type="expression" priority="6" dxfId="2">
-      <formula>$C45&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B47:J47">
-    <cfRule type="expression" priority="7" dxfId="5">
-      <formula>$L47=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B48:J48">
-    <cfRule type="expression" priority="8" dxfId="2">
-      <formula>$C48&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B49:J49">
-    <cfRule type="expression" priority="9" dxfId="2">
-      <formula>$C49&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B51:J51">
-    <cfRule type="expression" priority="10" dxfId="5">
-      <formula>$L51=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B52:J52">
-    <cfRule type="expression" priority="11" dxfId="2">
-      <formula>$C52&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B53:J53">
-    <cfRule type="expression" priority="12" dxfId="2">
-      <formula>$C53&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B55:J55">
-    <cfRule type="expression" priority="13" dxfId="6">
-      <formula>$L55=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B56:J56">
-    <cfRule type="expression" priority="14" dxfId="7">
-      <formula>$L55=1</formula>
+  <conditionalFormatting sqref="E16:J55">
+    <cfRule type="expression" priority="6" dxfId="6">
+      <formula>E16="incl."</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
@@ -4251,7 +4730,7 @@
     <firstFooter/>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="42" min="0" max="16383" man="1"/>
+    <brk id="56" min="0" max="16383" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -4283,366 +4762,366 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="67" t="inlineStr">
+      <c r="A1" s="55" t="inlineStr">
         <is>
           <t>Contact Enedril</t>
         </is>
       </c>
-      <c r="B1" s="67" t="inlineStr">
+      <c r="B1" s="55" t="inlineStr">
         <is>
           <t>E-mail</t>
         </is>
       </c>
-      <c r="D1" s="67" t="inlineStr">
+      <c r="D1" s="55" t="inlineStr">
         <is>
           <t>Incoterm</t>
         </is>
       </c>
-      <c r="E1" s="67" t="inlineStr">
+      <c r="E1" s="55" t="inlineStr">
         <is>
           <t>Validité</t>
         </is>
       </c>
-      <c r="F1" s="67" t="inlineStr">
+      <c r="F1" s="55" t="inlineStr">
         <is>
           <t>Règlement</t>
         </is>
       </c>
-      <c r="G1" s="67" t="inlineStr">
+      <c r="G1" s="55" t="inlineStr">
         <is>
           <t>Oui / Non</t>
         </is>
       </c>
-      <c r="H1" s="68" t="n">
+      <c r="H1" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="J1" s="67" t="inlineStr">
+      <c r="J1" s="55" t="inlineStr">
         <is>
           <t>Support de colisage</t>
         </is>
       </c>
-      <c r="K1" s="67" t="inlineStr">
+      <c r="K1" s="55" t="inlineStr">
         <is>
           <t>N° de colis</t>
         </is>
       </c>
-      <c r="L1" s="67" t="inlineStr">
+      <c r="L1" s="55" t="inlineStr">
         <is>
           <t>Unité</t>
         </is>
       </c>
-      <c r="M1" s="67" t="inlineStr">
+      <c r="M1" s="55" t="inlineStr">
         <is>
           <t>Mode transport</t>
         </is>
       </c>
-      <c r="N1" s="67" t="inlineStr">
+      <c r="N1" s="55" t="inlineStr">
         <is>
           <t>Mode forfait</t>
         </is>
       </c>
-      <c r="P1" s="67" t="inlineStr">
+      <c r="P1" s="55" t="inlineStr">
         <is>
           <t>Statut</t>
         </is>
       </c>
-      <c r="Q1" s="67" t="inlineStr">
+      <c r="Q1" s="55" t="inlineStr">
         <is>
           <t>Test / Taille</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="69" t="inlineStr">
+      <c r="A2" s="57" t="inlineStr">
         <is>
           <t>Fabien JACQUOT</t>
         </is>
       </c>
-      <c r="B2" s="69" t="inlineStr">
+      <c r="B2" s="57" t="inlineStr">
         <is>
           <t>fjacquot@enedril.fr</t>
         </is>
       </c>
-      <c r="D2" s="69" t="inlineStr">
+      <c r="D2" s="57" t="inlineStr">
         <is>
           <t>EXW Lons</t>
         </is>
       </c>
-      <c r="E2" s="69" t="inlineStr">
+      <c r="E2" s="57" t="inlineStr">
         <is>
           <t>15 jours / 15 days</t>
         </is>
       </c>
-      <c r="F2" s="69" t="inlineStr">
+      <c r="F2" s="57" t="inlineStr">
         <is>
           <t>30 jours date de facture / 30 days invoice date</t>
         </is>
       </c>
-      <c r="G2" s="69" t="inlineStr">
+      <c r="G2" s="57" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="H2" s="70" t="inlineStr">
+      <c r="H2" s="58" t="inlineStr">
         <is>
           <t>← langue du devis : 1 = français, 2 = anglais</t>
         </is>
       </c>
-      <c r="J2" s="69" t="inlineStr">
+      <c r="J2" s="57" t="inlineStr">
         <is>
           <t>Palette</t>
         </is>
       </c>
-      <c r="K2" s="69" t="inlineStr">
+      <c r="K2" s="57" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="L2" s="69" t="inlineStr">
+      <c r="L2" s="57" t="inlineStr">
         <is>
           <t>forfait</t>
         </is>
       </c>
-      <c r="M2" s="69" t="inlineStr">
+      <c r="M2" s="57" t="inlineStr">
         <is>
           <t>Coût réel +15 %</t>
         </is>
       </c>
-      <c r="N2" s="69" t="inlineStr">
+      <c r="N2" s="57" t="inlineStr">
         <is>
           <t>Forfait calculé (S + O + UC)</t>
         </is>
       </c>
-      <c r="P2" s="69" t="inlineStr">
+      <c r="P2" s="57" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="Q2" s="69" t="inlineStr">
+      <c r="Q2" s="57" t="inlineStr">
         <is>
           <t>Taille OK</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="69" t="inlineStr">
+      <c r="A3" s="57" t="inlineStr">
         <is>
           <t>Alexis ESTINES</t>
         </is>
       </c>
-      <c r="B3" s="69" t="inlineStr">
+      <c r="B3" s="57" t="inlineStr">
         <is>
           <t>aestines@enedril.fr</t>
         </is>
       </c>
-      <c r="D3" s="69" t="inlineStr">
+      <c r="D3" s="57" t="inlineStr">
         <is>
           <t>FCA Lons</t>
         </is>
       </c>
-      <c r="E3" s="69" t="inlineStr">
+      <c r="E3" s="57" t="inlineStr">
         <is>
           <t>30 jours / 30 days</t>
         </is>
       </c>
-      <c r="F3" s="69" t="inlineStr">
+      <c r="F3" s="57" t="inlineStr">
         <is>
           <t>30 jours fin de mois / 30 days end of month</t>
         </is>
       </c>
-      <c r="G3" s="69" t="inlineStr">
+      <c r="G3" s="57" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J3" s="69" t="inlineStr">
+      <c r="J3" s="57" t="inlineStr">
         <is>
           <t>Fishing basket</t>
         </is>
       </c>
-      <c r="K3" s="69" t="inlineStr">
+      <c r="K3" s="57" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L3" s="69" t="inlineStr">
+      <c r="L3" s="57" t="inlineStr">
         <is>
           <t>€/jour</t>
         </is>
       </c>
-      <c r="M3" s="69" t="inlineStr">
+      <c r="M3" s="57" t="inlineStr">
         <is>
           <t>Forfait</t>
         </is>
       </c>
-      <c r="N3" s="69" t="inlineStr">
+      <c r="N3" s="57" t="inlineStr">
         <is>
           <t>Forfait global</t>
         </is>
       </c>
-      <c r="P3" s="69" t="inlineStr">
+      <c r="P3" s="57" t="inlineStr">
         <is>
           <t>En cours</t>
         </is>
       </c>
-      <c r="Q3" s="69" t="inlineStr">
+      <c r="Q3" s="57" t="inlineStr">
         <is>
           <t>Test OK</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="69" t="inlineStr">
+      <c r="A4" s="57" t="inlineStr">
         <is>
           <t>Paul HYNDERICK</t>
         </is>
       </c>
-      <c r="B4" s="69" t="inlineStr">
+      <c r="B4" s="57" t="inlineStr">
         <is>
           <t>phynderick@enedril.fr</t>
         </is>
       </c>
-      <c r="D4" s="69" t="inlineStr">
+      <c r="D4" s="57" t="inlineStr">
         <is>
           <t>DAP</t>
         </is>
       </c>
-      <c r="E4" s="69" t="inlineStr">
+      <c r="E4" s="57" t="inlineStr">
         <is>
           <t>60 jours / 60 days</t>
         </is>
       </c>
-      <c r="F4" s="69" t="inlineStr">
+      <c r="F4" s="57" t="inlineStr">
         <is>
           <t>45 jours fin de mois / 45 days end of month</t>
         </is>
       </c>
-      <c r="J4" s="69" t="inlineStr">
+      <c r="J4" s="57" t="inlineStr">
         <is>
           <t>Caisse</t>
         </is>
       </c>
-      <c r="K4" s="69" t="inlineStr">
+      <c r="K4" s="57" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="L4" s="69" t="inlineStr">
+      <c r="L4" s="57" t="inlineStr">
         <is>
           <t>€/jour/pers</t>
         </is>
       </c>
-      <c r="N4" s="69" t="inlineStr">
+      <c r="N4" s="57" t="inlineStr">
         <is>
           <t>Forfait par jour</t>
         </is>
       </c>
-      <c r="Q4" s="69" t="inlineStr">
+      <c r="Q4" s="57" t="inlineStr">
         <is>
           <t>Taille + test OK</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="69" t="inlineStr">
+      <c r="A5" s="57" t="inlineStr">
         <is>
           <t>Céline CARDONA</t>
         </is>
       </c>
-      <c r="B5" s="69" t="inlineStr">
+      <c r="B5" s="57" t="inlineStr">
         <is>
           <t>ccardona@enedril.fr</t>
         </is>
       </c>
-      <c r="D5" s="69" t="inlineStr">
+      <c r="D5" s="57" t="inlineStr">
         <is>
           <t>DDP</t>
         </is>
       </c>
-      <c r="E5" s="69" t="inlineStr">
+      <c r="E5" s="57" t="inlineStr">
         <is>
           <t>90 jours / 90 days</t>
         </is>
       </c>
-      <c r="F5" s="69" t="inlineStr">
+      <c r="F5" s="57" t="inlineStr">
         <is>
           <t>À la commande / Upon order</t>
         </is>
       </c>
-      <c r="J5" s="69" t="inlineStr">
+      <c r="J5" s="57" t="inlineStr">
         <is>
           <t>Loose (vrac)</t>
         </is>
       </c>
-      <c r="K5" s="69" t="inlineStr">
+      <c r="K5" s="57" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="L5" s="69" t="inlineStr">
+      <c r="L5" s="57" t="inlineStr">
         <is>
           <t>€/pers</t>
         </is>
       </c>
-      <c r="Q5" s="69" t="inlineStr">
+      <c r="Q5" s="57" t="inlineStr">
         <is>
           <t>À contrôler</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="69" t="inlineStr">
+      <c r="A6" s="57" t="inlineStr">
         <is>
           <t>Koen MONDELAERS</t>
         </is>
       </c>
-      <c r="B6" s="69" t="inlineStr">
+      <c r="B6" s="57" t="inlineStr">
         <is>
           <t>kmondelaers@enedril.fr</t>
         </is>
       </c>
-      <c r="D6" s="69" t="inlineStr">
+      <c r="D6" s="57" t="inlineStr">
         <is>
           <t>FOB</t>
         </is>
       </c>
-      <c r="K6" s="69" t="inlineStr">
+      <c r="K6" s="57" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="L6" s="69" t="inlineStr">
+      <c r="L6" s="57" t="inlineStr">
         <is>
           <t>€/unité</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="69" t="inlineStr">
+      <c r="A7" s="57" t="inlineStr">
         <is>
           <t>Luigi LIBERATORE</t>
         </is>
       </c>
-      <c r="B7" s="69" t="inlineStr">
+      <c r="B7" s="57" t="inlineStr">
         <is>
           <t>lliberatore@enedril.fr</t>
         </is>
       </c>
-      <c r="K7" s="69" t="inlineStr">
+      <c r="K7" s="57" t="inlineStr">
         <is>
           <t>P6</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="K8" s="69" t="inlineStr">
+      <c r="K8" s="57" t="inlineStr">
         <is>
           <t>P7</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="K9" s="69" t="inlineStr">
+      <c r="K9" s="57" t="inlineStr">
         <is>
           <t>P8</t>
         </is>
@@ -4654,21 +5133,21 @@
           <t>Pour ajouter un contact, une validité, etc. : écrire à la suite dans la colonne (les listes déroulantes lisent les 12 premières lignes).</t>
         </is>
       </c>
-      <c r="K10" s="69" t="inlineStr">
+      <c r="K10" s="57" t="inlineStr">
         <is>
           <t>P9</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="K11" s="69" t="inlineStr">
+      <c r="K11" s="57" t="inlineStr">
         <is>
           <t>P10</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="K12" s="69" t="inlineStr">
+      <c r="K12" s="57" t="inlineStr">
         <is>
           <t>Loose</t>
         </is>
@@ -4695,358 +5174,358 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="67" t="inlineStr">
+      <c r="A1" s="55" t="inlineStr">
         <is>
           <t>Clé</t>
         </is>
       </c>
-      <c r="B1" s="67" t="inlineStr">
+      <c r="B1" s="55" t="inlineStr">
         <is>
           <t>Français</t>
         </is>
       </c>
-      <c r="C1" s="67" t="inlineStr">
+      <c r="C1" s="55" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="71" t="inlineStr">
+      <c r="A2" s="59" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B2" s="71" t="inlineStr">
+      <c r="B2" s="59" t="inlineStr">
         <is>
           <t>OFFRE DE LOCATION</t>
         </is>
       </c>
-      <c r="C2" s="71" t="inlineStr">
+      <c r="C2" s="59" t="inlineStr">
         <is>
           <t>EQUIPMENT RENTAL QUOTATION</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="71" t="inlineStr">
+      <c r="A3" s="59" t="inlineStr">
         <is>
           <t>client</t>
         </is>
       </c>
-      <c r="B3" s="71" t="inlineStr">
+      <c r="B3" s="59" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="C3" s="71" t="inlineStr">
+      <c r="C3" s="59" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="71" t="inlineStr">
+      <c r="A4" s="59" t="inlineStr">
         <is>
           <t>attn</t>
         </is>
       </c>
-      <c r="B4" s="71" t="inlineStr">
+      <c r="B4" s="59" t="inlineStr">
         <is>
           <t>À l'attention de</t>
         </is>
       </c>
-      <c r="C4" s="71" t="inlineStr">
+      <c r="C4" s="59" t="inlineStr">
         <is>
           <t>Attention</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="71" t="inlineStr">
+      <c r="A5" s="59" t="inlineStr">
         <is>
           <t>well</t>
         </is>
       </c>
-      <c r="B5" s="71" t="inlineStr">
+      <c r="B5" s="59" t="inlineStr">
         <is>
           <t>Puits / Chantier</t>
         </is>
       </c>
-      <c r="C5" s="71" t="inlineStr">
+      <c r="C5" s="59" t="inlineStr">
         <is>
           <t>Well / Location</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="71" t="inlineStr">
+      <c r="A6" s="59" t="inlineStr">
         <is>
           <t>rig</t>
         </is>
       </c>
-      <c r="B6" s="71" t="inlineStr">
+      <c r="B6" s="59" t="inlineStr">
         <is>
           <t>Rig</t>
         </is>
       </c>
-      <c r="C6" s="71" t="inlineStr">
+      <c r="C6" s="59" t="inlineStr">
         <is>
           <t>Rig</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="71" t="inlineStr">
+      <c r="A7" s="59" t="inlineStr">
         <is>
           <t>offer</t>
         </is>
       </c>
-      <c r="B7" s="71" t="inlineStr">
+      <c r="B7" s="59" t="inlineStr">
         <is>
           <t>N° d'offre</t>
         </is>
       </c>
-      <c r="C7" s="71" t="inlineStr">
+      <c r="C7" s="59" t="inlineStr">
         <is>
           <t>Offer N°</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="71" t="inlineStr">
+      <c r="A8" s="59" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B8" s="71" t="inlineStr">
+      <c r="B8" s="59" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C8" s="71" t="inlineStr">
+      <c r="C8" s="59" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="71" t="inlineStr">
+      <c r="A9" s="59" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="B9" s="71" t="inlineStr">
+      <c r="B9" s="59" t="inlineStr">
         <is>
           <t>Validité de l'offre</t>
         </is>
       </c>
-      <c r="C9" s="71" t="inlineStr">
+      <c r="C9" s="59" t="inlineStr">
         <is>
           <t>Validity</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="71" t="inlineStr">
+      <c r="A10" s="59" t="inlineStr">
         <is>
           <t>inco</t>
         </is>
       </c>
-      <c r="B10" s="71" t="inlineStr">
+      <c r="B10" s="59" t="inlineStr">
         <is>
           <t>Incoterm</t>
         </is>
       </c>
-      <c r="C10" s="71" t="inlineStr">
+      <c r="C10" s="59" t="inlineStr">
         <is>
           <t>Incoterm</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="71" t="inlineStr">
+      <c r="A11" s="59" t="inlineStr">
         <is>
           <t>lead</t>
         </is>
       </c>
-      <c r="B11" s="71" t="inlineStr">
+      <c r="B11" s="59" t="inlineStr">
         <is>
           <t>Délai de mise à dispo</t>
         </is>
       </c>
-      <c r="C11" s="71" t="inlineStr">
+      <c r="C11" s="59" t="inlineStr">
         <is>
           <t>Lead time</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="71" t="inlineStr">
+      <c r="A12" s="59" t="inlineStr">
         <is>
           <t>pay</t>
         </is>
       </c>
-      <c r="B12" s="71" t="inlineStr">
+      <c r="B12" s="59" t="inlineStr">
         <is>
           <t>Conditions de règlement</t>
         </is>
       </c>
-      <c r="C12" s="71" t="inlineStr">
+      <c r="C12" s="59" t="inlineStr">
         <is>
           <t>Payment terms</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="71" t="inlineStr">
+      <c r="A13" s="59" t="inlineStr">
         <is>
           <t>we</t>
         </is>
       </c>
-      <c r="B13" s="71" t="inlineStr">
+      <c r="B13" s="59" t="inlineStr">
         <is>
           <t>Facturation WE et jours fériés</t>
         </is>
       </c>
-      <c r="C13" s="71" t="inlineStr">
+      <c r="C13" s="59" t="inlineStr">
         <is>
           <t>Weekend &amp; holiday billing</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="71" t="inlineStr">
+      <c r="A14" s="59" t="inlineStr">
         <is>
           <t>by</t>
         </is>
       </c>
-      <c r="B14" s="71" t="inlineStr">
+      <c r="B14" s="59" t="inlineStr">
         <is>
           <t>Établi par</t>
         </is>
       </c>
-      <c r="C14" s="71" t="inlineStr">
+      <c r="C14" s="59" t="inlineStr">
         <is>
           <t>Established by</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="71" t="inlineStr">
+      <c r="A15" s="59" t="inlineStr">
         <is>
           <t>mail</t>
         </is>
       </c>
-      <c r="B15" s="71" t="inlineStr">
+      <c r="B15" s="59" t="inlineStr">
         <is>
           <t>E-mail</t>
         </is>
       </c>
-      <c r="C15" s="71" t="inlineStr">
+      <c r="C15" s="59" t="inlineStr">
         <is>
           <t>E-mail</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="71" t="inlineStr">
+      <c r="A16" s="59" t="inlineStr">
         <is>
           <t>tel</t>
         </is>
       </c>
-      <c r="B16" s="71" t="inlineStr">
+      <c r="B16" s="59" t="inlineStr">
         <is>
           <t>Téléphone</t>
         </is>
       </c>
-      <c r="C16" s="71" t="inlineStr">
+      <c r="C16" s="59" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="71" t="inlineStr">
+      <c r="A17" s="59" t="inlineStr">
         <is>
           <t>sec_eq</t>
         </is>
       </c>
-      <c r="B17" s="71" t="inlineStr">
+      <c r="B17" s="59" t="inlineStr">
         <is>
           <t>MATÉRIEL</t>
         </is>
       </c>
-      <c r="C17" s="71" t="inlineStr">
+      <c r="C17" s="59" t="inlineStr">
         <is>
           <t>EQUIPMENT</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="71" t="inlineStr">
+      <c r="A18" s="59" t="inlineStr">
         <is>
           <t>h_n</t>
         </is>
       </c>
-      <c r="B18" s="71" t="inlineStr">
+      <c r="B18" s="59" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C18" s="71" t="inlineStr">
+      <c r="C18" s="59" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="71" t="inlineStr">
+      <c r="A19" s="59" t="inlineStr">
         <is>
           <t>h_desc</t>
         </is>
       </c>
-      <c r="B19" s="71" t="inlineStr">
+      <c r="B19" s="59" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C19" s="71" t="inlineStr">
+      <c r="C19" s="59" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="71" t="inlineStr">
+      <c r="A20" s="59" t="inlineStr">
         <is>
           <t>h_qty</t>
         </is>
       </c>
-      <c r="B20" s="71" t="inlineStr">
+      <c r="B20" s="59" t="inlineStr">
         <is>
           <t>Qté</t>
         </is>
       </c>
-      <c r="C20" s="71" t="inlineStr">
+      <c r="C20" s="59" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="71" t="inlineStr">
+      <c r="A21" s="59" t="inlineStr">
         <is>
           <t>h_s</t>
         </is>
       </c>
-      <c r="B21" s="71" t="inlineStr">
+      <c r="B21" s="59" t="inlineStr">
         <is>
           <t>Stand-by (S)
 € / jour / item</t>
         </is>
       </c>
-      <c r="C21" s="71" t="inlineStr">
+      <c r="C21" s="59" t="inlineStr">
         <is>
           <t>Stand-by (S)
 daily rate / item</t>
@@ -5054,18 +5533,18 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="71" t="inlineStr">
+      <c r="A22" s="59" t="inlineStr">
         <is>
           <t>h_o</t>
         </is>
       </c>
-      <c r="B22" s="71" t="inlineStr">
+      <c r="B22" s="59" t="inlineStr">
         <is>
           <t>Opérations (O)
 € / jour / item</t>
         </is>
       </c>
-      <c r="C22" s="71" t="inlineStr">
+      <c r="C22" s="59" t="inlineStr">
         <is>
           <t>Operations (O)
 daily rate / item</t>
@@ -5073,19 +5552,19 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="71" t="inlineStr">
+      <c r="A23" s="59" t="inlineStr">
         <is>
           <t>h_uc</t>
         </is>
       </c>
-      <c r="B23" s="71" t="inlineStr">
+      <c r="B23" s="59" t="inlineStr">
         <is>
           <t>Utilisation
 Charge (UC)
 € / item</t>
         </is>
       </c>
-      <c r="C23" s="71" t="inlineStr">
+      <c r="C23" s="59" t="inlineStr">
         <is>
           <t>Utilisation
 Charge (UC)
@@ -5094,18 +5573,18 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="71" t="inlineStr">
+      <c r="A24" s="59" t="inlineStr">
         <is>
           <t>h_lih</t>
         </is>
       </c>
-      <c r="B24" s="71" t="inlineStr">
+      <c r="B24" s="59" t="inlineStr">
         <is>
           <t>Valeur de remplacement
 (LIH / DBR) € / item</t>
         </is>
       </c>
-      <c r="C24" s="71" t="inlineStr">
+      <c r="C24" s="59" t="inlineStr">
         <is>
           <t>Replacement value
 (LIH / DBR) per item</t>
@@ -5113,18 +5592,18 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="71" t="inlineStr">
+      <c r="A25" s="59" t="inlineStr">
         <is>
           <t>h_insp</t>
         </is>
       </c>
-      <c r="B25" s="71" t="inlineStr">
+      <c r="B25" s="59" t="inlineStr">
         <is>
           <t>Inspection
 € / item</t>
         </is>
       </c>
-      <c r="C25" s="71" t="inlineStr">
+      <c r="C25" s="59" t="inlineStr">
         <is>
           <t>Inspection
 per item</t>
@@ -5132,18 +5611,18 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="71" t="inlineStr">
+      <c r="A26" s="59" t="inlineStr">
         <is>
           <t>h_rest</t>
         </is>
       </c>
-      <c r="B26" s="71" t="inlineStr">
+      <c r="B26" s="59" t="inlineStr">
         <is>
           <t>Restocking
 €</t>
         </is>
       </c>
-      <c r="C26" s="71" t="inlineStr">
+      <c r="C26" s="59" t="inlineStr">
         <is>
           <t>Restocking
 charge</t>
@@ -5151,496 +5630,2273 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="71" t="inlineStr">
+      <c r="A27" s="59" t="inlineStr">
         <is>
           <t>h_ref</t>
         </is>
       </c>
-      <c r="B27" s="71" t="inlineStr">
+      <c r="B27" s="59" t="inlineStr">
         <is>
           <t>Remarques</t>
         </is>
       </c>
-      <c r="C27" s="71" t="inlineStr">
+      <c r="C27" s="59" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="71" t="inlineStr">
+      <c r="A28" s="59" t="inlineStr">
         <is>
           <t>incl</t>
         </is>
       </c>
-      <c r="B28" s="71" t="inlineStr">
+      <c r="B28" s="59" t="inlineStr">
         <is>
           <t>incl.</t>
         </is>
       </c>
-      <c r="C28" s="71" t="inlineStr">
+      <c r="C28" s="59" t="inlineStr">
         <is>
           <t>incl.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="71" t="inlineStr">
+      <c r="A29" s="59" t="inlineStr">
         <is>
           <t>incl_long</t>
         </is>
       </c>
-      <c r="B29" s="71" t="inlineStr">
+      <c r="B29" s="59" t="inlineStr">
         <is>
           <t>Inclus au forfait</t>
         </is>
       </c>
-      <c r="C29" s="71" t="inlineStr">
+      <c r="C29" s="59" t="inlineStr">
         <is>
           <t>Included in lump sum</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="71" t="inlineStr">
+      <c r="A30" s="59" t="inlineStr">
         <is>
           <t>sec_opt</t>
         </is>
       </c>
-      <c r="B30" s="71" t="inlineStr">
+      <c r="B30" s="59" t="inlineStr">
         <is>
           <t>PRESTATIONS ET OPTIONS</t>
         </is>
       </c>
-      <c r="C30" s="71" t="inlineStr">
+      <c r="C30" s="59" t="inlineStr">
         <is>
           <t>SERVICES AND OPTIONS</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="71" t="inlineStr">
+      <c r="A31" s="59" t="inlineStr">
         <is>
           <t>h_label</t>
         </is>
       </c>
-      <c r="B31" s="71" t="inlineStr">
+      <c r="B31" s="59" t="inlineStr">
         <is>
           <t>Prestation</t>
         </is>
       </c>
-      <c r="C31" s="71" t="inlineStr">
+      <c r="C31" s="59" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="71" t="inlineStr">
+      <c r="A32" s="59" t="inlineStr">
         <is>
           <t>h_unit</t>
         </is>
       </c>
-      <c r="B32" s="71" t="inlineStr">
+      <c r="B32" s="59" t="inlineStr">
         <is>
           <t>Unité</t>
         </is>
       </c>
-      <c r="C32" s="71" t="inlineStr">
+      <c r="C32" s="59" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="71" t="inlineStr">
+      <c r="A33" s="59" t="inlineStr">
         <is>
           <t>h_pu</t>
         </is>
       </c>
-      <c r="B33" s="71" t="inlineStr">
+      <c r="B33" s="59" t="inlineStr">
         <is>
           <t>Prix unitaire €</t>
         </is>
       </c>
-      <c r="C33" s="71" t="inlineStr">
+      <c r="C33" s="59" t="inlineStr">
         <is>
           <t>Unit price €</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="71" t="inlineStr">
+      <c r="A34" s="59" t="inlineStr">
         <is>
           <t>h_tot</t>
         </is>
       </c>
-      <c r="B34" s="71" t="inlineStr">
+      <c r="B34" s="59" t="inlineStr">
         <is>
           <t>Total €</t>
         </is>
       </c>
-      <c r="C34" s="71" t="inlineStr">
+      <c r="C34" s="59" t="inlineStr">
         <is>
           <t>Total €</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="71" t="inlineStr">
+      <c r="A35" s="59" t="inlineStr">
         <is>
           <t>h_det</t>
         </is>
       </c>
-      <c r="B35" s="71" t="inlineStr">
+      <c r="B35" s="59" t="inlineStr">
         <is>
           <t>Détail</t>
         </is>
       </c>
-      <c r="C35" s="71" t="inlineStr">
+      <c r="C35" s="59" t="inlineStr">
         <is>
           <t>Details</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="71" t="inlineStr">
+      <c r="A36" s="59" t="inlineStr">
         <is>
           <t>op_day</t>
         </is>
       </c>
-      <c r="B36" s="71" t="inlineStr">
+      <c r="B36" s="59" t="inlineStr">
         <is>
           <t>Opérateur · tarif journalier</t>
         </is>
       </c>
-      <c r="C36" s="71" t="inlineStr">
+      <c r="C36" s="59" t="inlineStr">
         <is>
           <t>Operator · daily rate</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="71" t="inlineStr">
+      <c r="A37" s="59" t="inlineStr">
         <is>
           <t>op_mob</t>
         </is>
       </c>
-      <c r="B37" s="71" t="inlineStr">
+      <c r="B37" s="59" t="inlineStr">
         <is>
           <t>Opérateur · Mob / Demob</t>
         </is>
       </c>
-      <c r="C37" s="71" t="inlineStr">
+      <c r="C37" s="59" t="inlineStr">
         <is>
           <t>Operator · Mob / Demob</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="71" t="inlineStr">
+      <c r="A38" s="59" t="inlineStr">
         <is>
           <t>tight</t>
         </is>
       </c>
-      <c r="B38" s="71" t="inlineStr">
+      <c r="B38" s="59" t="inlineStr">
         <is>
           <t>Serrage · prix par serrage</t>
         </is>
       </c>
-      <c r="C38" s="71" t="inlineStr">
+      <c r="C38" s="59" t="inlineStr">
         <is>
           <t>Tong &amp; make-up service · price per make-up</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="71" t="inlineStr">
+      <c r="A39" s="59" t="inlineStr">
         <is>
           <t>tr_mob</t>
         </is>
       </c>
-      <c r="B39" s="71" t="inlineStr">
+      <c r="B39" s="59" t="inlineStr">
         <is>
           <t>Transport MOB (Lons → chantier)</t>
         </is>
       </c>
-      <c r="C39" s="71" t="inlineStr">
+      <c r="C39" s="59" t="inlineStr">
         <is>
           <t>Transport MOB (Lons → site)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="71" t="inlineStr">
+      <c r="A40" s="59" t="inlineStr">
         <is>
           <t>tr_dem</t>
         </is>
       </c>
-      <c r="B40" s="71" t="inlineStr">
+      <c r="B40" s="59" t="inlineStr">
         <is>
           <t>Transport DEMOB (chantier → Lons)</t>
         </is>
       </c>
-      <c r="C40" s="71" t="inlineStr">
+      <c r="C40" s="59" t="inlineStr">
         <is>
           <t>Transport DEMOB (site → Lons)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="71" t="inlineStr">
+      <c r="A41" s="59" t="inlineStr">
         <is>
           <t>free</t>
         </is>
       </c>
-      <c r="B41" s="71" t="inlineStr">
+      <c r="B41" s="59" t="inlineStr">
         <is>
           <t>Option</t>
         </is>
       </c>
-      <c r="C41" s="71" t="inlineStr">
+      <c r="C41" s="59" t="inlineStr">
         <is>
           <t>Option</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="71" t="inlineStr">
+      <c r="A42" s="59" t="inlineStr">
         <is>
           <t>forfait</t>
         </is>
       </c>
-      <c r="B42" s="71" t="inlineStr">
+      <c r="B42" s="59" t="inlineStr">
         <is>
           <t>Forfait</t>
         </is>
       </c>
-      <c r="C42" s="71" t="inlineStr">
+      <c r="C42" s="59" t="inlineStr">
         <is>
           <t>Lump sum</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="71" t="inlineStr">
+      <c r="A43" s="59" t="inlineStr">
         <is>
           <t>at_cost</t>
         </is>
       </c>
-      <c r="B43" s="71" t="inlineStr">
+      <c r="B43" s="59" t="inlineStr">
         <is>
           <t>au coût réel +15 %</t>
         </is>
       </c>
-      <c r="C43" s="71" t="inlineStr">
+      <c r="C43" s="59" t="inlineStr">
         <is>
           <t>at cost +15%</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="71" t="inlineStr">
+      <c r="A44" s="59" t="inlineStr">
         <is>
           <t>tr_note</t>
         </is>
       </c>
-      <c r="B44" s="71" t="inlineStr">
+      <c r="B44" s="59" t="inlineStr">
         <is>
           <t>Transport organisé par Enedril</t>
         </is>
       </c>
-      <c r="C44" s="71" t="inlineStr">
+      <c r="C44" s="59" t="inlineStr">
         <is>
           <t>Transport organised by Enedril</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="71" t="inlineStr">
+      <c r="A45" s="59" t="inlineStr">
         <is>
           <t>ht</t>
         </is>
       </c>
-      <c r="B45" s="71" t="inlineStr">
+      <c r="B45" s="59" t="inlineStr">
         <is>
           <t>€ HT</t>
         </is>
       </c>
-      <c r="C45" s="71" t="inlineStr">
+      <c r="C45" s="59" t="inlineStr">
         <is>
           <t>€ excl. VAT</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="71" t="inlineStr">
+      <c r="A46" s="59" t="inlineStr">
         <is>
           <t>calc_det</t>
         </is>
       </c>
-      <c r="B46" s="71" t="inlineStr">
+      <c r="B46" s="59" t="inlineStr">
         <is>
           <t>j stand-by + %s j opérations + utilisations de charge (UC)</t>
         </is>
       </c>
-      <c r="C46" s="71" t="inlineStr">
+      <c r="C46" s="59" t="inlineStr">
         <is>
           <t>stand-by days + %s operation days + utilisation charges (UC)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="71" t="inlineStr">
+      <c r="A47" s="59" t="inlineStr">
         <is>
           <t>sec_cond</t>
         </is>
       </c>
-      <c r="B47" s="71" t="inlineStr">
+      <c r="B47" s="59" t="inlineStr">
         <is>
           <t>CONDITIONS PARTICULIÈRES · SPECIFIC CONDITIONS</t>
         </is>
       </c>
-      <c r="C47" s="71" t="inlineStr">
+      <c r="C47" s="59" t="inlineStr">
         <is>
           <t>SPECIFIC CONDITIONS · CONDITIONS PARTICULIÈRES</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="71" t="inlineStr">
+      <c r="A48" s="59" t="inlineStr">
         <is>
           <t>accept</t>
         </is>
       </c>
-      <c r="B48" s="71" t="inlineStr">
+      <c r="B48" s="59" t="inlineStr">
         <is>
           <t>BON POUR ACCORD</t>
         </is>
       </c>
-      <c r="C48" s="71" t="inlineStr">
+      <c r="C48" s="59" t="inlineStr">
         <is>
           <t>ACCEPTED BY</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="71" t="inlineStr">
+      <c r="A49" s="59" t="inlineStr">
         <is>
           <t>sig_name</t>
         </is>
       </c>
-      <c r="B49" s="71" t="inlineStr">
+      <c r="B49" s="59" t="inlineStr">
         <is>
           <t>Nom et qualité</t>
         </is>
       </c>
-      <c r="C49" s="71" t="inlineStr">
+      <c r="C49" s="59" t="inlineStr">
         <is>
           <t>Name and title</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="71" t="inlineStr">
+      <c r="A50" s="59" t="inlineStr">
         <is>
           <t>sig_date</t>
         </is>
       </c>
-      <c r="B50" s="71" t="inlineStr">
+      <c r="B50" s="59" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C50" s="71" t="inlineStr">
+      <c r="C50" s="59" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="71" t="inlineStr">
+      <c r="A51" s="59" t="inlineStr">
         <is>
           <t>sig_sig</t>
         </is>
       </c>
-      <c r="B51" s="71" t="inlineStr">
+      <c r="B51" s="59" t="inlineStr">
         <is>
           <t>Signature et cachet</t>
         </is>
       </c>
-      <c r="C51" s="71" t="inlineStr">
+      <c r="C51" s="59" t="inlineStr">
         <is>
           <t>Signature and stamp</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="71" t="inlineStr">
+      <c r="A52" s="59" t="inlineStr">
         <is>
           <t>lump</t>
         </is>
       </c>
-      <c r="B52" s="71" t="inlineStr">
+      <c r="B52" s="59" t="inlineStr">
         <is>
           <t>forfait</t>
         </is>
       </c>
-      <c r="C52" s="71" t="inlineStr">
+      <c r="C52" s="59" t="inlineStr">
         <is>
           <t>lump sum</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="71" t="inlineStr">
+      <c r="A53" s="59" t="inlineStr">
         <is>
           <t>sec_tight</t>
         </is>
       </c>
-      <c r="B53" s="71" t="inlineStr">
+      <c r="B53" s="59" t="inlineStr">
         <is>
           <t>SERRAGE · TONG &amp; MAKE-UP</t>
         </is>
       </c>
-      <c r="C53" s="71" t="inlineStr">
+      <c r="C53" s="59" t="inlineStr">
         <is>
           <t>TONG &amp; MAKE-UP SERVICE</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="71" t="inlineStr">
+      <c r="A54" s="59" t="inlineStr">
         <is>
           <t>sec_tr</t>
         </is>
       </c>
-      <c r="B54" s="71" t="inlineStr">
+      <c r="B54" s="59" t="inlineStr">
         <is>
           <t>TRANSPORT</t>
         </is>
       </c>
-      <c r="C54" s="71" t="inlineStr">
+      <c r="C54" s="59" t="inlineStr">
         <is>
           <t>TRANSPORT</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="71" t="inlineStr">
+      <c r="A55" s="59" t="inlineStr">
         <is>
           <t>sec_op</t>
         </is>
       </c>
-      <c r="B55" s="71" t="inlineStr">
+      <c r="B55" s="59" t="inlineStr">
         <is>
           <t>OPÉRATEURS</t>
         </is>
       </c>
-      <c r="C55" s="71" t="inlineStr">
+      <c r="C55" s="59" t="inlineStr">
         <is>
           <t>OPERATORS</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="009FB6CE"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>rang</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>libellé</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>qté</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>v5</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>v6</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <f>IF('2 Matériel'!$L6&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="B2">
+        <f>IF(A2=1,COUNTIF(A$2:A2,1),"")</f>
+        <v/>
+      </c>
+      <c r="C2">
+        <f>IF(A2=1,IF('2 Matériel'!$B6="Oui","BAN","ITM"),"")</f>
+        <v/>
+      </c>
+      <c r="D2">
+        <f>IF(C2="ITM",'2 Matériel'!$A6,"")</f>
+        <v/>
+      </c>
+      <c r="E2">
+        <f>IF(C2="BAN",UPPER('2 Matériel'!$C6),IF(C2="ITM",'2 Matériel'!$C6&amp;IF(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <v/>
+      </c>
+      <c r="F2">
+        <f>IF(C2="ITM",'2 Matériel'!$L6,"")</f>
+        <v/>
+      </c>
+      <c r="G2">
+        <f>IF(C2="ITM",IF(AND(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E6="","",'2 Matériel'!$E6)),"")</f>
+        <v/>
+      </c>
+      <c r="H2">
+        <f>IF(C2="ITM",IF(AND(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F6="","",'2 Matériel'!$F6)),"")</f>
+        <v/>
+      </c>
+      <c r="I2">
+        <f>IF(C2="ITM",IF(AND(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G6="","",'2 Matériel'!$G6)),"")</f>
+        <v/>
+      </c>
+      <c r="J2">
+        <f>IF(C2="ITM",IF(AND(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H6="","",'2 Matériel'!$H6)),"")</f>
+        <v/>
+      </c>
+      <c r="K2">
+        <f>IF(C2="ITM",IF(AND(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I6="","",'2 Matériel'!$I6)),"")</f>
+        <v/>
+      </c>
+      <c r="L2">
+        <f>IF(C2="ITM",IF(AND(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J6="","",'2 Matériel'!$J6)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <f>IF('2 Matériel'!$L7&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="B3">
+        <f>IF(A3=1,COUNTIF(A$2:A3,1),"")</f>
+        <v/>
+      </c>
+      <c r="C3">
+        <f>IF(A3=1,IF('2 Matériel'!$B7="Oui","BAN","ITM"),"")</f>
+        <v/>
+      </c>
+      <c r="D3">
+        <f>IF(C3="ITM",'2 Matériel'!$A7,"")</f>
+        <v/>
+      </c>
+      <c r="E3">
+        <f>IF(C3="BAN",UPPER('2 Matériel'!$C7),IF(C3="ITM",'2 Matériel'!$C7&amp;IF(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <v/>
+      </c>
+      <c r="F3">
+        <f>IF(C3="ITM",'2 Matériel'!$L7,"")</f>
+        <v/>
+      </c>
+      <c r="G3">
+        <f>IF(C3="ITM",IF(AND(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E7="","",'2 Matériel'!$E7)),"")</f>
+        <v/>
+      </c>
+      <c r="H3">
+        <f>IF(C3="ITM",IF(AND(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F7="","",'2 Matériel'!$F7)),"")</f>
+        <v/>
+      </c>
+      <c r="I3">
+        <f>IF(C3="ITM",IF(AND(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G7="","",'2 Matériel'!$G7)),"")</f>
+        <v/>
+      </c>
+      <c r="J3">
+        <f>IF(C3="ITM",IF(AND(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H7="","",'2 Matériel'!$H7)),"")</f>
+        <v/>
+      </c>
+      <c r="K3">
+        <f>IF(C3="ITM",IF(AND(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I7="","",'2 Matériel'!$I7)),"")</f>
+        <v/>
+      </c>
+      <c r="L3">
+        <f>IF(C3="ITM",IF(AND(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J7="","",'2 Matériel'!$J7)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <f>IF('2 Matériel'!$L8&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="B4">
+        <f>IF(A4=1,COUNTIF(A$2:A4,1),"")</f>
+        <v/>
+      </c>
+      <c r="C4">
+        <f>IF(A4=1,IF('2 Matériel'!$B8="Oui","BAN","ITM"),"")</f>
+        <v/>
+      </c>
+      <c r="D4">
+        <f>IF(C4="ITM",'2 Matériel'!$A8,"")</f>
+        <v/>
+      </c>
+      <c r="E4">
+        <f>IF(C4="BAN",UPPER('2 Matériel'!$C8),IF(C4="ITM",'2 Matériel'!$C8&amp;IF(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <v/>
+      </c>
+      <c r="F4">
+        <f>IF(C4="ITM",'2 Matériel'!$L8,"")</f>
+        <v/>
+      </c>
+      <c r="G4">
+        <f>IF(C4="ITM",IF(AND(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E8="","",'2 Matériel'!$E8)),"")</f>
+        <v/>
+      </c>
+      <c r="H4">
+        <f>IF(C4="ITM",IF(AND(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F8="","",'2 Matériel'!$F8)),"")</f>
+        <v/>
+      </c>
+      <c r="I4">
+        <f>IF(C4="ITM",IF(AND(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G8="","",'2 Matériel'!$G8)),"")</f>
+        <v/>
+      </c>
+      <c r="J4">
+        <f>IF(C4="ITM",IF(AND(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H8="","",'2 Matériel'!$H8)),"")</f>
+        <v/>
+      </c>
+      <c r="K4">
+        <f>IF(C4="ITM",IF(AND(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I8="","",'2 Matériel'!$I8)),"")</f>
+        <v/>
+      </c>
+      <c r="L4">
+        <f>IF(C4="ITM",IF(AND(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J8="","",'2 Matériel'!$J8)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <f>IF('2 Matériel'!$L9&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="B5">
+        <f>IF(A5=1,COUNTIF(A$2:A5,1),"")</f>
+        <v/>
+      </c>
+      <c r="C5">
+        <f>IF(A5=1,IF('2 Matériel'!$B9="Oui","BAN","ITM"),"")</f>
+        <v/>
+      </c>
+      <c r="D5">
+        <f>IF(C5="ITM",'2 Matériel'!$A9,"")</f>
+        <v/>
+      </c>
+      <c r="E5">
+        <f>IF(C5="BAN",UPPER('2 Matériel'!$C9),IF(C5="ITM",'2 Matériel'!$C9&amp;IF(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <v/>
+      </c>
+      <c r="F5">
+        <f>IF(C5="ITM",'2 Matériel'!$L9,"")</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>IF(C5="ITM",IF(AND(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E9="","",'2 Matériel'!$E9)),"")</f>
+        <v/>
+      </c>
+      <c r="H5">
+        <f>IF(C5="ITM",IF(AND(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F9="","",'2 Matériel'!$F9)),"")</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>IF(C5="ITM",IF(AND(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G9="","",'2 Matériel'!$G9)),"")</f>
+        <v/>
+      </c>
+      <c r="J5">
+        <f>IF(C5="ITM",IF(AND(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H9="","",'2 Matériel'!$H9)),"")</f>
+        <v/>
+      </c>
+      <c r="K5">
+        <f>IF(C5="ITM",IF(AND(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I9="","",'2 Matériel'!$I9)),"")</f>
+        <v/>
+      </c>
+      <c r="L5">
+        <f>IF(C5="ITM",IF(AND(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J9="","",'2 Matériel'!$J9)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <f>IF('2 Matériel'!$L10&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="B6">
+        <f>IF(A6=1,COUNTIF(A$2:A6,1),"")</f>
+        <v/>
+      </c>
+      <c r="C6">
+        <f>IF(A6=1,IF('2 Matériel'!$B10="Oui","BAN","ITM"),"")</f>
+        <v/>
+      </c>
+      <c r="D6">
+        <f>IF(C6="ITM",'2 Matériel'!$A10,"")</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>IF(C6="BAN",UPPER('2 Matériel'!$C10),IF(C6="ITM",'2 Matériel'!$C10&amp;IF(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <v/>
+      </c>
+      <c r="F6">
+        <f>IF(C6="ITM",'2 Matériel'!$L10,"")</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>IF(C6="ITM",IF(AND(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E10="","",'2 Matériel'!$E10)),"")</f>
+        <v/>
+      </c>
+      <c r="H6">
+        <f>IF(C6="ITM",IF(AND(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F10="","",'2 Matériel'!$F10)),"")</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>IF(C6="ITM",IF(AND(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G10="","",'2 Matériel'!$G10)),"")</f>
+        <v/>
+      </c>
+      <c r="J6">
+        <f>IF(C6="ITM",IF(AND(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H10="","",'2 Matériel'!$H10)),"")</f>
+        <v/>
+      </c>
+      <c r="K6">
+        <f>IF(C6="ITM",IF(AND(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I10="","",'2 Matériel'!$I10)),"")</f>
+        <v/>
+      </c>
+      <c r="L6">
+        <f>IF(C6="ITM",IF(AND(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J10="","",'2 Matériel'!$J10)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <f>IF('2 Matériel'!$L11&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="B7">
+        <f>IF(A7=1,COUNTIF(A$2:A7,1),"")</f>
+        <v/>
+      </c>
+      <c r="C7">
+        <f>IF(A7=1,IF('2 Matériel'!$B11="Oui","BAN","ITM"),"")</f>
+        <v/>
+      </c>
+      <c r="D7">
+        <f>IF(C7="ITM",'2 Matériel'!$A11,"")</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>IF(C7="BAN",UPPER('2 Matériel'!$C11),IF(C7="ITM",'2 Matériel'!$C11&amp;IF(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f>IF(C7="ITM",'2 Matériel'!$L11,"")</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>IF(C7="ITM",IF(AND(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E11="","",'2 Matériel'!$E11)),"")</f>
+        <v/>
+      </c>
+      <c r="H7">
+        <f>IF(C7="ITM",IF(AND(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F11="","",'2 Matériel'!$F11)),"")</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>IF(C7="ITM",IF(AND(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G11="","",'2 Matériel'!$G11)),"")</f>
+        <v/>
+      </c>
+      <c r="J7">
+        <f>IF(C7="ITM",IF(AND(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H11="","",'2 Matériel'!$H11)),"")</f>
+        <v/>
+      </c>
+      <c r="K7">
+        <f>IF(C7="ITM",IF(AND(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I11="","",'2 Matériel'!$I11)),"")</f>
+        <v/>
+      </c>
+      <c r="L7">
+        <f>IF(C7="ITM",IF(AND(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J11="","",'2 Matériel'!$J11)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <f>IF('2 Matériel'!$L12&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="B8">
+        <f>IF(A8=1,COUNTIF(A$2:A8,1),"")</f>
+        <v/>
+      </c>
+      <c r="C8">
+        <f>IF(A8=1,IF('2 Matériel'!$B12="Oui","BAN","ITM"),"")</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>IF(C8="ITM",'2 Matériel'!$A12,"")</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>IF(C8="BAN",UPPER('2 Matériel'!$C12),IF(C8="ITM",'2 Matériel'!$C12&amp;IF(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>IF(C8="ITM",'2 Matériel'!$L12,"")</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>IF(C8="ITM",IF(AND(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E12="","",'2 Matériel'!$E12)),"")</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>IF(C8="ITM",IF(AND(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F12="","",'2 Matériel'!$F12)),"")</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IF(C8="ITM",IF(AND(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G12="","",'2 Matériel'!$G12)),"")</f>
+        <v/>
+      </c>
+      <c r="J8">
+        <f>IF(C8="ITM",IF(AND(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H12="","",'2 Matériel'!$H12)),"")</f>
+        <v/>
+      </c>
+      <c r="K8">
+        <f>IF(C8="ITM",IF(AND(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I12="","",'2 Matériel'!$I12)),"")</f>
+        <v/>
+      </c>
+      <c r="L8">
+        <f>IF(C8="ITM",IF(AND(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J12="","",'2 Matériel'!$J12)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <f>IF('2 Matériel'!$L13&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="B9">
+        <f>IF(A9=1,COUNTIF(A$2:A9,1),"")</f>
+        <v/>
+      </c>
+      <c r="C9">
+        <f>IF(A9=1,IF('2 Matériel'!$B13="Oui","BAN","ITM"),"")</f>
+        <v/>
+      </c>
+      <c r="D9">
+        <f>IF(C9="ITM",'2 Matériel'!$A13,"")</f>
+        <v/>
+      </c>
+      <c r="E9">
+        <f>IF(C9="BAN",UPPER('2 Matériel'!$C13),IF(C9="ITM",'2 Matériel'!$C13&amp;IF(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <v/>
+      </c>
+      <c r="F9">
+        <f>IF(C9="ITM",'2 Matériel'!$L13,"")</f>
+        <v/>
+      </c>
+      <c r="G9">
+        <f>IF(C9="ITM",IF(AND(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E13="","",'2 Matériel'!$E13)),"")</f>
+        <v/>
+      </c>
+      <c r="H9">
+        <f>IF(C9="ITM",IF(AND(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F13="","",'2 Matériel'!$F13)),"")</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>IF(C9="ITM",IF(AND(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G13="","",'2 Matériel'!$G13)),"")</f>
+        <v/>
+      </c>
+      <c r="J9">
+        <f>IF(C9="ITM",IF(AND(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H13="","",'2 Matériel'!$H13)),"")</f>
+        <v/>
+      </c>
+      <c r="K9">
+        <f>IF(C9="ITM",IF(AND(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I13="","",'2 Matériel'!$I13)),"")</f>
+        <v/>
+      </c>
+      <c r="L9">
+        <f>IF(C9="ITM",IF(AND(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J13="","",'2 Matériel'!$J13)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <f>IF('2 Matériel'!$L14&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="B10">
+        <f>IF(A10=1,COUNTIF(A$2:A10,1),"")</f>
+        <v/>
+      </c>
+      <c r="C10">
+        <f>IF(A10=1,IF('2 Matériel'!$B14="Oui","BAN","ITM"),"")</f>
+        <v/>
+      </c>
+      <c r="D10">
+        <f>IF(C10="ITM",'2 Matériel'!$A14,"")</f>
+        <v/>
+      </c>
+      <c r="E10">
+        <f>IF(C10="BAN",UPPER('2 Matériel'!$C14),IF(C10="ITM",'2 Matériel'!$C14&amp;IF(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f>IF(C10="ITM",'2 Matériel'!$L14,"")</f>
+        <v/>
+      </c>
+      <c r="G10">
+        <f>IF(C10="ITM",IF(AND(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E14="","",'2 Matériel'!$E14)),"")</f>
+        <v/>
+      </c>
+      <c r="H10">
+        <f>IF(C10="ITM",IF(AND(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F14="","",'2 Matériel'!$F14)),"")</f>
+        <v/>
+      </c>
+      <c r="I10">
+        <f>IF(C10="ITM",IF(AND(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G14="","",'2 Matériel'!$G14)),"")</f>
+        <v/>
+      </c>
+      <c r="J10">
+        <f>IF(C10="ITM",IF(AND(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H14="","",'2 Matériel'!$H14)),"")</f>
+        <v/>
+      </c>
+      <c r="K10">
+        <f>IF(C10="ITM",IF(AND(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I14="","",'2 Matériel'!$I14)),"")</f>
+        <v/>
+      </c>
+      <c r="L10">
+        <f>IF(C10="ITM",IF(AND(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J14="","",'2 Matériel'!$J14)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <f>IF('2 Matériel'!$L15&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="B11">
+        <f>IF(A11=1,COUNTIF(A$2:A11,1),"")</f>
+        <v/>
+      </c>
+      <c r="C11">
+        <f>IF(A11=1,IF('2 Matériel'!$B15="Oui","BAN","ITM"),"")</f>
+        <v/>
+      </c>
+      <c r="D11">
+        <f>IF(C11="ITM",'2 Matériel'!$A15,"")</f>
+        <v/>
+      </c>
+      <c r="E11">
+        <f>IF(C11="BAN",UPPER('2 Matériel'!$C15),IF(C11="ITM",'2 Matériel'!$C15&amp;IF(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <v/>
+      </c>
+      <c r="F11">
+        <f>IF(C11="ITM",'2 Matériel'!$L15,"")</f>
+        <v/>
+      </c>
+      <c r="G11">
+        <f>IF(C11="ITM",IF(AND(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E15="","",'2 Matériel'!$E15)),"")</f>
+        <v/>
+      </c>
+      <c r="H11">
+        <f>IF(C11="ITM",IF(AND(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F15="","",'2 Matériel'!$F15)),"")</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>IF(C11="ITM",IF(AND(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G15="","",'2 Matériel'!$G15)),"")</f>
+        <v/>
+      </c>
+      <c r="J11">
+        <f>IF(C11="ITM",IF(AND(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H15="","",'2 Matériel'!$H15)),"")</f>
+        <v/>
+      </c>
+      <c r="K11">
+        <f>IF(C11="ITM",IF(AND(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I15="","",'2 Matériel'!$I15)),"")</f>
+        <v/>
+      </c>
+      <c r="L11">
+        <f>IF(C11="ITM",IF(AND(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J15="","",'2 Matériel'!$J15)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <f>IF('2 Matériel'!$L16&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="B12">
+        <f>IF(A12=1,COUNTIF(A$2:A12,1),"")</f>
+        <v/>
+      </c>
+      <c r="C12">
+        <f>IF(A12=1,IF('2 Matériel'!$B16="Oui","BAN","ITM"),"")</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>IF(C12="ITM",'2 Matériel'!$A16,"")</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>IF(C12="BAN",UPPER('2 Matériel'!$C16),IF(C12="ITM",'2 Matériel'!$C16&amp;IF(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>IF(C12="ITM",'2 Matériel'!$L16,"")</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>IF(C12="ITM",IF(AND(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E16="","",'2 Matériel'!$E16)),"")</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>IF(C12="ITM",IF(AND(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F16="","",'2 Matériel'!$F16)),"")</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>IF(C12="ITM",IF(AND(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G16="","",'2 Matériel'!$G16)),"")</f>
+        <v/>
+      </c>
+      <c r="J12">
+        <f>IF(C12="ITM",IF(AND(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H16="","",'2 Matériel'!$H16)),"")</f>
+        <v/>
+      </c>
+      <c r="K12">
+        <f>IF(C12="ITM",IF(AND(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I16="","",'2 Matériel'!$I16)),"")</f>
+        <v/>
+      </c>
+      <c r="L12">
+        <f>IF(C12="ITM",IF(AND(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J16="","",'2 Matériel'!$J16)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <f>IF('2 Matériel'!$L17&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="B13">
+        <f>IF(A13=1,COUNTIF(A$2:A13,1),"")</f>
+        <v/>
+      </c>
+      <c r="C13">
+        <f>IF(A13=1,IF('2 Matériel'!$B17="Oui","BAN","ITM"),"")</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>IF(C13="ITM",'2 Matériel'!$A17,"")</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>IF(C13="BAN",UPPER('2 Matériel'!$C17),IF(C13="ITM",'2 Matériel'!$C17&amp;IF(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <v/>
+      </c>
+      <c r="F13">
+        <f>IF(C13="ITM",'2 Matériel'!$L17,"")</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>IF(C13="ITM",IF(AND(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E17="","",'2 Matériel'!$E17)),"")</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>IF(C13="ITM",IF(AND(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F17="","",'2 Matériel'!$F17)),"")</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>IF(C13="ITM",IF(AND(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G17="","",'2 Matériel'!$G17)),"")</f>
+        <v/>
+      </c>
+      <c r="J13">
+        <f>IF(C13="ITM",IF(AND(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H17="","",'2 Matériel'!$H17)),"")</f>
+        <v/>
+      </c>
+      <c r="K13">
+        <f>IF(C13="ITM",IF(AND(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I17="","",'2 Matériel'!$I17)),"")</f>
+        <v/>
+      </c>
+      <c r="L13">
+        <f>IF(C13="ITM",IF(AND(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J17="","",'2 Matériel'!$J17)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <f>IF('2 Matériel'!$L18&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="B14">
+        <f>IF(A14=1,COUNTIF(A$2:A14,1),"")</f>
+        <v/>
+      </c>
+      <c r="C14">
+        <f>IF(A14=1,IF('2 Matériel'!$B18="Oui","BAN","ITM"),"")</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>IF(C14="ITM",'2 Matériel'!$A18,"")</f>
+        <v/>
+      </c>
+      <c r="E14">
+        <f>IF(C14="BAN",UPPER('2 Matériel'!$C18),IF(C14="ITM",'2 Matériel'!$C18&amp;IF(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f>IF(C14="ITM",'2 Matériel'!$L18,"")</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>IF(C14="ITM",IF(AND(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E18="","",'2 Matériel'!$E18)),"")</f>
+        <v/>
+      </c>
+      <c r="H14">
+        <f>IF(C14="ITM",IF(AND(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F18="","",'2 Matériel'!$F18)),"")</f>
+        <v/>
+      </c>
+      <c r="I14">
+        <f>IF(C14="ITM",IF(AND(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G18="","",'2 Matériel'!$G18)),"")</f>
+        <v/>
+      </c>
+      <c r="J14">
+        <f>IF(C14="ITM",IF(AND(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H18="","",'2 Matériel'!$H18)),"")</f>
+        <v/>
+      </c>
+      <c r="K14">
+        <f>IF(C14="ITM",IF(AND(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I18="","",'2 Matériel'!$I18)),"")</f>
+        <v/>
+      </c>
+      <c r="L14">
+        <f>IF(C14="ITM",IF(AND(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J18="","",'2 Matériel'!$J18)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <f>IF('2 Matériel'!$L19&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="B15">
+        <f>IF(A15=1,COUNTIF(A$2:A15,1),"")</f>
+        <v/>
+      </c>
+      <c r="C15">
+        <f>IF(A15=1,IF('2 Matériel'!$B19="Oui","BAN","ITM"),"")</f>
+        <v/>
+      </c>
+      <c r="D15">
+        <f>IF(C15="ITM",'2 Matériel'!$A19,"")</f>
+        <v/>
+      </c>
+      <c r="E15">
+        <f>IF(C15="BAN",UPPER('2 Matériel'!$C19),IF(C15="ITM",'2 Matériel'!$C19&amp;IF(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <v/>
+      </c>
+      <c r="F15">
+        <f>IF(C15="ITM",'2 Matériel'!$L19,"")</f>
+        <v/>
+      </c>
+      <c r="G15">
+        <f>IF(C15="ITM",IF(AND(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E19="","",'2 Matériel'!$E19)),"")</f>
+        <v/>
+      </c>
+      <c r="H15">
+        <f>IF(C15="ITM",IF(AND(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F19="","",'2 Matériel'!$F19)),"")</f>
+        <v/>
+      </c>
+      <c r="I15">
+        <f>IF(C15="ITM",IF(AND(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G19="","",'2 Matériel'!$G19)),"")</f>
+        <v/>
+      </c>
+      <c r="J15">
+        <f>IF(C15="ITM",IF(AND(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H19="","",'2 Matériel'!$H19)),"")</f>
+        <v/>
+      </c>
+      <c r="K15">
+        <f>IF(C15="ITM",IF(AND(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I19="","",'2 Matériel'!$I19)),"")</f>
+        <v/>
+      </c>
+      <c r="L15">
+        <f>IF(C15="ITM",IF(AND(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J19="","",'2 Matériel'!$J19)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <f>IF('2 Matériel'!$L20&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="B16">
+        <f>IF(A16=1,COUNTIF(A$2:A16,1),"")</f>
+        <v/>
+      </c>
+      <c r="C16">
+        <f>IF(A16=1,IF('2 Matériel'!$B20="Oui","BAN","ITM"),"")</f>
+        <v/>
+      </c>
+      <c r="D16">
+        <f>IF(C16="ITM",'2 Matériel'!$A20,"")</f>
+        <v/>
+      </c>
+      <c r="E16">
+        <f>IF(C16="BAN",UPPER('2 Matériel'!$C20),IF(C16="ITM",'2 Matériel'!$C20&amp;IF(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <v/>
+      </c>
+      <c r="F16">
+        <f>IF(C16="ITM",'2 Matériel'!$L20,"")</f>
+        <v/>
+      </c>
+      <c r="G16">
+        <f>IF(C16="ITM",IF(AND(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E20="","",'2 Matériel'!$E20)),"")</f>
+        <v/>
+      </c>
+      <c r="H16">
+        <f>IF(C16="ITM",IF(AND(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F20="","",'2 Matériel'!$F20)),"")</f>
+        <v/>
+      </c>
+      <c r="I16">
+        <f>IF(C16="ITM",IF(AND(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G20="","",'2 Matériel'!$G20)),"")</f>
+        <v/>
+      </c>
+      <c r="J16">
+        <f>IF(C16="ITM",IF(AND(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H20="","",'2 Matériel'!$H20)),"")</f>
+        <v/>
+      </c>
+      <c r="K16">
+        <f>IF(C16="ITM",IF(AND(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I20="","",'2 Matériel'!$I20)),"")</f>
+        <v/>
+      </c>
+      <c r="L16">
+        <f>IF(C16="ITM",IF(AND(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J20="","",'2 Matériel'!$J20)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <f>IF('2 Matériel'!$L21&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="B17">
+        <f>IF(A17=1,COUNTIF(A$2:A17,1),"")</f>
+        <v/>
+      </c>
+      <c r="C17">
+        <f>IF(A17=1,IF('2 Matériel'!$B21="Oui","BAN","ITM"),"")</f>
+        <v/>
+      </c>
+      <c r="D17">
+        <f>IF(C17="ITM",'2 Matériel'!$A21,"")</f>
+        <v/>
+      </c>
+      <c r="E17">
+        <f>IF(C17="BAN",UPPER('2 Matériel'!$C21),IF(C17="ITM",'2 Matériel'!$C21&amp;IF(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <v/>
+      </c>
+      <c r="F17">
+        <f>IF(C17="ITM",'2 Matériel'!$L21,"")</f>
+        <v/>
+      </c>
+      <c r="G17">
+        <f>IF(C17="ITM",IF(AND(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E21="","",'2 Matériel'!$E21)),"")</f>
+        <v/>
+      </c>
+      <c r="H17">
+        <f>IF(C17="ITM",IF(AND(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F21="","",'2 Matériel'!$F21)),"")</f>
+        <v/>
+      </c>
+      <c r="I17">
+        <f>IF(C17="ITM",IF(AND(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G21="","",'2 Matériel'!$G21)),"")</f>
+        <v/>
+      </c>
+      <c r="J17">
+        <f>IF(C17="ITM",IF(AND(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H21="","",'2 Matériel'!$H21)),"")</f>
+        <v/>
+      </c>
+      <c r="K17">
+        <f>IF(C17="ITM",IF(AND(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I21="","",'2 Matériel'!$I21)),"")</f>
+        <v/>
+      </c>
+      <c r="L17">
+        <f>IF(C17="ITM",IF(AND(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J21="","",'2 Matériel'!$J21)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <f>IF('2 Matériel'!$L22&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="B18">
+        <f>IF(A18=1,COUNTIF(A$2:A18,1),"")</f>
+        <v/>
+      </c>
+      <c r="C18">
+        <f>IF(A18=1,IF('2 Matériel'!$B22="Oui","BAN","ITM"),"")</f>
+        <v/>
+      </c>
+      <c r="D18">
+        <f>IF(C18="ITM",'2 Matériel'!$A22,"")</f>
+        <v/>
+      </c>
+      <c r="E18">
+        <f>IF(C18="BAN",UPPER('2 Matériel'!$C22),IF(C18="ITM",'2 Matériel'!$C22&amp;IF(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <v/>
+      </c>
+      <c r="F18">
+        <f>IF(C18="ITM",'2 Matériel'!$L22,"")</f>
+        <v/>
+      </c>
+      <c r="G18">
+        <f>IF(C18="ITM",IF(AND(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E22="","",'2 Matériel'!$E22)),"")</f>
+        <v/>
+      </c>
+      <c r="H18">
+        <f>IF(C18="ITM",IF(AND(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F22="","",'2 Matériel'!$F22)),"")</f>
+        <v/>
+      </c>
+      <c r="I18">
+        <f>IF(C18="ITM",IF(AND(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G22="","",'2 Matériel'!$G22)),"")</f>
+        <v/>
+      </c>
+      <c r="J18">
+        <f>IF(C18="ITM",IF(AND(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H22="","",'2 Matériel'!$H22)),"")</f>
+        <v/>
+      </c>
+      <c r="K18">
+        <f>IF(C18="ITM",IF(AND(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I22="","",'2 Matériel'!$I22)),"")</f>
+        <v/>
+      </c>
+      <c r="L18">
+        <f>IF(C18="ITM",IF(AND(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J22="","",'2 Matériel'!$J22)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <f>IF('2 Matériel'!$L23&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="B19">
+        <f>IF(A19=1,COUNTIF(A$2:A19,1),"")</f>
+        <v/>
+      </c>
+      <c r="C19">
+        <f>IF(A19=1,IF('2 Matériel'!$B23="Oui","BAN","ITM"),"")</f>
+        <v/>
+      </c>
+      <c r="D19">
+        <f>IF(C19="ITM",'2 Matériel'!$A23,"")</f>
+        <v/>
+      </c>
+      <c r="E19">
+        <f>IF(C19="BAN",UPPER('2 Matériel'!$C23),IF(C19="ITM",'2 Matériel'!$C23&amp;IF(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <v/>
+      </c>
+      <c r="F19">
+        <f>IF(C19="ITM",'2 Matériel'!$L23,"")</f>
+        <v/>
+      </c>
+      <c r="G19">
+        <f>IF(C19="ITM",IF(AND(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E23="","",'2 Matériel'!$E23)),"")</f>
+        <v/>
+      </c>
+      <c r="H19">
+        <f>IF(C19="ITM",IF(AND(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F23="","",'2 Matériel'!$F23)),"")</f>
+        <v/>
+      </c>
+      <c r="I19">
+        <f>IF(C19="ITM",IF(AND(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G23="","",'2 Matériel'!$G23)),"")</f>
+        <v/>
+      </c>
+      <c r="J19">
+        <f>IF(C19="ITM",IF(AND(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H23="","",'2 Matériel'!$H23)),"")</f>
+        <v/>
+      </c>
+      <c r="K19">
+        <f>IF(C19="ITM",IF(AND(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I23="","",'2 Matériel'!$I23)),"")</f>
+        <v/>
+      </c>
+      <c r="L19">
+        <f>IF(C19="ITM",IF(AND(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J23="","",'2 Matériel'!$J23)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <f>IF('2 Matériel'!$L24&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="B20">
+        <f>IF(A20=1,COUNTIF(A$2:A20,1),"")</f>
+        <v/>
+      </c>
+      <c r="C20">
+        <f>IF(A20=1,IF('2 Matériel'!$B24="Oui","BAN","ITM"),"")</f>
+        <v/>
+      </c>
+      <c r="D20">
+        <f>IF(C20="ITM",'2 Matériel'!$A24,"")</f>
+        <v/>
+      </c>
+      <c r="E20">
+        <f>IF(C20="BAN",UPPER('2 Matériel'!$C24),IF(C20="ITM",'2 Matériel'!$C24&amp;IF(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <v/>
+      </c>
+      <c r="F20">
+        <f>IF(C20="ITM",'2 Matériel'!$L24,"")</f>
+        <v/>
+      </c>
+      <c r="G20">
+        <f>IF(C20="ITM",IF(AND(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E24="","",'2 Matériel'!$E24)),"")</f>
+        <v/>
+      </c>
+      <c r="H20">
+        <f>IF(C20="ITM",IF(AND(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F24="","",'2 Matériel'!$F24)),"")</f>
+        <v/>
+      </c>
+      <c r="I20">
+        <f>IF(C20="ITM",IF(AND(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G24="","",'2 Matériel'!$G24)),"")</f>
+        <v/>
+      </c>
+      <c r="J20">
+        <f>IF(C20="ITM",IF(AND(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H24="","",'2 Matériel'!$H24)),"")</f>
+        <v/>
+      </c>
+      <c r="K20">
+        <f>IF(C20="ITM",IF(AND(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I24="","",'2 Matériel'!$I24)),"")</f>
+        <v/>
+      </c>
+      <c r="L20">
+        <f>IF(C20="ITM",IF(AND(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J24="","",'2 Matériel'!$J24)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <f>IF('2 Matériel'!$L25&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="B21">
+        <f>IF(A21=1,COUNTIF(A$2:A21,1),"")</f>
+        <v/>
+      </c>
+      <c r="C21">
+        <f>IF(A21=1,IF('2 Matériel'!$B25="Oui","BAN","ITM"),"")</f>
+        <v/>
+      </c>
+      <c r="D21">
+        <f>IF(C21="ITM",'2 Matériel'!$A25,"")</f>
+        <v/>
+      </c>
+      <c r="E21">
+        <f>IF(C21="BAN",UPPER('2 Matériel'!$C25),IF(C21="ITM",'2 Matériel'!$C25&amp;IF(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <v/>
+      </c>
+      <c r="F21">
+        <f>IF(C21="ITM",'2 Matériel'!$L25,"")</f>
+        <v/>
+      </c>
+      <c r="G21">
+        <f>IF(C21="ITM",IF(AND(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E25="","",'2 Matériel'!$E25)),"")</f>
+        <v/>
+      </c>
+      <c r="H21">
+        <f>IF(C21="ITM",IF(AND(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F25="","",'2 Matériel'!$F25)),"")</f>
+        <v/>
+      </c>
+      <c r="I21">
+        <f>IF(C21="ITM",IF(AND(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G25="","",'2 Matériel'!$G25)),"")</f>
+        <v/>
+      </c>
+      <c r="J21">
+        <f>IF(C21="ITM",IF(AND(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H25="","",'2 Matériel'!$H25)),"")</f>
+        <v/>
+      </c>
+      <c r="K21">
+        <f>IF(C21="ITM",IF(AND(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I25="","",'2 Matériel'!$I25)),"")</f>
+        <v/>
+      </c>
+      <c r="L21">
+        <f>IF(C21="ITM",IF(AND(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J25="","",'2 Matériel'!$J25)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <f>IF('2 Matériel'!$L26&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="B22">
+        <f>IF(A22=1,COUNTIF(A$2:A22,1),"")</f>
+        <v/>
+      </c>
+      <c r="C22">
+        <f>IF(A22=1,IF('2 Matériel'!$B26="Oui","BAN","ITM"),"")</f>
+        <v/>
+      </c>
+      <c r="D22">
+        <f>IF(C22="ITM",'2 Matériel'!$A26,"")</f>
+        <v/>
+      </c>
+      <c r="E22">
+        <f>IF(C22="BAN",UPPER('2 Matériel'!$C26),IF(C22="ITM",'2 Matériel'!$C26&amp;IF(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <v/>
+      </c>
+      <c r="F22">
+        <f>IF(C22="ITM",'2 Matériel'!$L26,"")</f>
+        <v/>
+      </c>
+      <c r="G22">
+        <f>IF(C22="ITM",IF(AND(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E26="","",'2 Matériel'!$E26)),"")</f>
+        <v/>
+      </c>
+      <c r="H22">
+        <f>IF(C22="ITM",IF(AND(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F26="","",'2 Matériel'!$F26)),"")</f>
+        <v/>
+      </c>
+      <c r="I22">
+        <f>IF(C22="ITM",IF(AND(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G26="","",'2 Matériel'!$G26)),"")</f>
+        <v/>
+      </c>
+      <c r="J22">
+        <f>IF(C22="ITM",IF(AND(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H26="","",'2 Matériel'!$H26)),"")</f>
+        <v/>
+      </c>
+      <c r="K22">
+        <f>IF(C22="ITM",IF(AND(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I26="","",'2 Matériel'!$I26)),"")</f>
+        <v/>
+      </c>
+      <c r="L22">
+        <f>IF(C22="ITM",IF(AND(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J26="","",'2 Matériel'!$J26)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <f>IF('2 Matériel'!$L27&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="B23">
+        <f>IF(A23=1,COUNTIF(A$2:A23,1),"")</f>
+        <v/>
+      </c>
+      <c r="C23">
+        <f>IF(A23=1,IF('2 Matériel'!$B27="Oui","BAN","ITM"),"")</f>
+        <v/>
+      </c>
+      <c r="D23">
+        <f>IF(C23="ITM",'2 Matériel'!$A27,"")</f>
+        <v/>
+      </c>
+      <c r="E23">
+        <f>IF(C23="BAN",UPPER('2 Matériel'!$C27),IF(C23="ITM",'2 Matériel'!$C27&amp;IF(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <v/>
+      </c>
+      <c r="F23">
+        <f>IF(C23="ITM",'2 Matériel'!$L27,"")</f>
+        <v/>
+      </c>
+      <c r="G23">
+        <f>IF(C23="ITM",IF(AND(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E27="","",'2 Matériel'!$E27)),"")</f>
+        <v/>
+      </c>
+      <c r="H23">
+        <f>IF(C23="ITM",IF(AND(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F27="","",'2 Matériel'!$F27)),"")</f>
+        <v/>
+      </c>
+      <c r="I23">
+        <f>IF(C23="ITM",IF(AND(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G27="","",'2 Matériel'!$G27)),"")</f>
+        <v/>
+      </c>
+      <c r="J23">
+        <f>IF(C23="ITM",IF(AND(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H27="","",'2 Matériel'!$H27)),"")</f>
+        <v/>
+      </c>
+      <c r="K23">
+        <f>IF(C23="ITM",IF(AND(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I27="","",'2 Matériel'!$I27)),"")</f>
+        <v/>
+      </c>
+      <c r="L23">
+        <f>IF(C23="ITM",IF(AND(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J27="","",'2 Matériel'!$J27)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <f>IF('2 Matériel'!$L28&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="B24">
+        <f>IF(A24=1,COUNTIF(A$2:A24,1),"")</f>
+        <v/>
+      </c>
+      <c r="C24">
+        <f>IF(A24=1,IF('2 Matériel'!$B28="Oui","BAN","ITM"),"")</f>
+        <v/>
+      </c>
+      <c r="D24">
+        <f>IF(C24="ITM",'2 Matériel'!$A28,"")</f>
+        <v/>
+      </c>
+      <c r="E24">
+        <f>IF(C24="BAN",UPPER('2 Matériel'!$C28),IF(C24="ITM",'2 Matériel'!$C28&amp;IF(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <v/>
+      </c>
+      <c r="F24">
+        <f>IF(C24="ITM",'2 Matériel'!$L28,"")</f>
+        <v/>
+      </c>
+      <c r="G24">
+        <f>IF(C24="ITM",IF(AND(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E28="","",'2 Matériel'!$E28)),"")</f>
+        <v/>
+      </c>
+      <c r="H24">
+        <f>IF(C24="ITM",IF(AND(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F28="","",'2 Matériel'!$F28)),"")</f>
+        <v/>
+      </c>
+      <c r="I24">
+        <f>IF(C24="ITM",IF(AND(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G28="","",'2 Matériel'!$G28)),"")</f>
+        <v/>
+      </c>
+      <c r="J24">
+        <f>IF(C24="ITM",IF(AND(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H28="","",'2 Matériel'!$H28)),"")</f>
+        <v/>
+      </c>
+      <c r="K24">
+        <f>IF(C24="ITM",IF(AND(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I28="","",'2 Matériel'!$I28)),"")</f>
+        <v/>
+      </c>
+      <c r="L24">
+        <f>IF(C24="ITM",IF(AND(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J28="","",'2 Matériel'!$J28)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <f>IF('2 Matériel'!$L29&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="B25">
+        <f>IF(A25=1,COUNTIF(A$2:A25,1),"")</f>
+        <v/>
+      </c>
+      <c r="C25">
+        <f>IF(A25=1,IF('2 Matériel'!$B29="Oui","BAN","ITM"),"")</f>
+        <v/>
+      </c>
+      <c r="D25">
+        <f>IF(C25="ITM",'2 Matériel'!$A29,"")</f>
+        <v/>
+      </c>
+      <c r="E25">
+        <f>IF(C25="BAN",UPPER('2 Matériel'!$C29),IF(C25="ITM",'2 Matériel'!$C29&amp;IF(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <v/>
+      </c>
+      <c r="F25">
+        <f>IF(C25="ITM",'2 Matériel'!$L29,"")</f>
+        <v/>
+      </c>
+      <c r="G25">
+        <f>IF(C25="ITM",IF(AND(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E29="","",'2 Matériel'!$E29)),"")</f>
+        <v/>
+      </c>
+      <c r="H25">
+        <f>IF(C25="ITM",IF(AND(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F29="","",'2 Matériel'!$F29)),"")</f>
+        <v/>
+      </c>
+      <c r="I25">
+        <f>IF(C25="ITM",IF(AND(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G29="","",'2 Matériel'!$G29)),"")</f>
+        <v/>
+      </c>
+      <c r="J25">
+        <f>IF(C25="ITM",IF(AND(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H29="","",'2 Matériel'!$H29)),"")</f>
+        <v/>
+      </c>
+      <c r="K25">
+        <f>IF(C25="ITM",IF(AND(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I29="","",'2 Matériel'!$I29)),"")</f>
+        <v/>
+      </c>
+      <c r="L25">
+        <f>IF(C25="ITM",IF(AND(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J29="","",'2 Matériel'!$J29)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <f>IF('3 Options'!$C$8="Oui",1,0)</f>
+        <v/>
+      </c>
+      <c r="B26">
+        <f>IF(A26=1,COUNTIF(A$2:A26,1),"")</f>
+        <v/>
+      </c>
+      <c r="C26">
+        <f>IF(A26=1,"HDR","")</f>
+        <v/>
+      </c>
+      <c r="D26">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="E26">
+        <f>INDEX(Textes!$B$2:$C$55,MATCH("sec_tight",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <v/>
+      </c>
+      <c r="F26">
+        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_qty",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <v/>
+      </c>
+      <c r="G26">
+        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_unit",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <v/>
+      </c>
+      <c r="H26">
+        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_pu",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <v/>
+      </c>
+      <c r="I26">
+        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_tot",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <v/>
+      </c>
+      <c r="J26">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="K26">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="L26">
+        <f>""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <f>IF('3 Options'!$C$8="Oui",1,0)</f>
+        <v/>
+      </c>
+      <c r="B27">
+        <f>IF(A27=1,COUNTIF(A$2:A27,1),"")</f>
+        <v/>
+      </c>
+      <c r="C27">
+        <f>IF(A27=1,"LIN","")</f>
+        <v/>
+      </c>
+      <c r="D27">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="E27">
+        <f>IF('3 Options'!$D$8&lt;&gt;"",'3 Options'!$D$8,INDEX(Textes!$B$2:$C$55,MATCH("tight",Textes!$A$2:$A$55,0),Listes!$H$1))&amp;IF(AND('3 Options'!$C$13="Oui",'3 Options'!$C$19="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
+        <v/>
+      </c>
+      <c r="F27">
+        <f>IF('3 Options'!$G$8="Coût réel +15 %","",'3 Options'!$E$8)</f>
+        <v/>
+      </c>
+      <c r="G27">
+        <f>IF('3 Options'!$G$8="Coût réel +15 %","",'3 Options'!$G$8)</f>
+        <v/>
+      </c>
+      <c r="H27">
+        <f>IF(AND(AND('3 Options'!$C$13="Oui",'3 Options'!$C$19="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$G$8="Coût réel +15 %",INDEX(Textes!$B$2:$C$55,MATCH("at_cost",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$F$8="","",'3 Options'!$F$8)))</f>
+        <v/>
+      </c>
+      <c r="I27">
+        <f>IF(AND(AND('3 Options'!$C$13="Oui",'3 Options'!$C$19="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$G$8="Coût réel +15 %","—",'3 Options'!$H$8))</f>
+        <v/>
+      </c>
+      <c r="J27">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="K27">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="L27">
+        <f>""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <f>IF(OR('3 Options'!$C$9="Oui",'3 Options'!$C$10="Oui"),1,0)</f>
+        <v/>
+      </c>
+      <c r="B28">
+        <f>IF(A28=1,COUNTIF(A$2:A28,1),"")</f>
+        <v/>
+      </c>
+      <c r="C28">
+        <f>IF(A28=1,"HDR","")</f>
+        <v/>
+      </c>
+      <c r="D28">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="E28">
+        <f>INDEX(Textes!$B$2:$C$55,MATCH("sec_tr",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <v/>
+      </c>
+      <c r="F28">
+        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_qty",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <v/>
+      </c>
+      <c r="G28">
+        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_unit",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <v/>
+      </c>
+      <c r="H28">
+        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_pu",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <v/>
+      </c>
+      <c r="I28">
+        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_tot",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <v/>
+      </c>
+      <c r="J28">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="K28">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="L28">
+        <f>""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <f>IF('3 Options'!$C$9="Oui",1,0)</f>
+        <v/>
+      </c>
+      <c r="B29">
+        <f>IF(A29=1,COUNTIF(A$2:A29,1),"")</f>
+        <v/>
+      </c>
+      <c r="C29">
+        <f>IF(A29=1,"LIN","")</f>
+        <v/>
+      </c>
+      <c r="D29">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="E29">
+        <f>IF('3 Options'!$D$9&lt;&gt;"",'3 Options'!$D$9,INDEX(Textes!$B$2:$C$55,MATCH("tr_mob",Textes!$A$2:$A$55,0),Listes!$H$1))&amp;IF(AND('3 Options'!$C$13="Oui",'3 Options'!$C$20="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
+        <v/>
+      </c>
+      <c r="F29">
+        <f>IF('3 Options'!$G$9="Coût réel +15 %","",'3 Options'!$E$9)</f>
+        <v/>
+      </c>
+      <c r="G29">
+        <f>IF('3 Options'!$G$9="Coût réel +15 %","",'3 Options'!$G$9)</f>
+        <v/>
+      </c>
+      <c r="H29">
+        <f>IF(AND(AND('3 Options'!$C$13="Oui",'3 Options'!$C$20="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$G$9="Coût réel +15 %",INDEX(Textes!$B$2:$C$55,MATCH("at_cost",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$F$9="","",'3 Options'!$F$9)))</f>
+        <v/>
+      </c>
+      <c r="I29">
+        <f>IF(AND(AND('3 Options'!$C$13="Oui",'3 Options'!$C$20="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$G$9="Coût réel +15 %","—",'3 Options'!$H$9))</f>
+        <v/>
+      </c>
+      <c r="J29">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="K29">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="L29">
+        <f>""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <f>IF('3 Options'!$C$10="Oui",1,0)</f>
+        <v/>
+      </c>
+      <c r="B30">
+        <f>IF(A30=1,COUNTIF(A$2:A30,1),"")</f>
+        <v/>
+      </c>
+      <c r="C30">
+        <f>IF(A30=1,"LIN","")</f>
+        <v/>
+      </c>
+      <c r="D30">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="E30">
+        <f>IF('3 Options'!$D$10&lt;&gt;"",'3 Options'!$D$10,INDEX(Textes!$B$2:$C$55,MATCH("tr_dem",Textes!$A$2:$A$55,0),Listes!$H$1))&amp;IF(AND('3 Options'!$C$13="Oui",'3 Options'!$C$20="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
+        <v/>
+      </c>
+      <c r="F30">
+        <f>IF('3 Options'!$G$10="Coût réel +15 %","",'3 Options'!$E$10)</f>
+        <v/>
+      </c>
+      <c r="G30">
+        <f>IF('3 Options'!$G$10="Coût réel +15 %","",'3 Options'!$G$10)</f>
+        <v/>
+      </c>
+      <c r="H30">
+        <f>IF(AND(AND('3 Options'!$C$13="Oui",'3 Options'!$C$20="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$G$10="Coût réel +15 %",INDEX(Textes!$B$2:$C$55,MATCH("at_cost",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$F$10="","",'3 Options'!$F$10)))</f>
+        <v/>
+      </c>
+      <c r="I30">
+        <f>IF(AND(AND('3 Options'!$C$13="Oui",'3 Options'!$C$20="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$G$10="Coût réel +15 %","—",'3 Options'!$H$10))</f>
+        <v/>
+      </c>
+      <c r="J30">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="K30">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="L30">
+        <f>""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <f>IF(OR('3 Options'!$C$6="Oui",'3 Options'!$C$7="Oui"),1,0)</f>
+        <v/>
+      </c>
+      <c r="B31">
+        <f>IF(A31=1,COUNTIF(A$2:A31,1),"")</f>
+        <v/>
+      </c>
+      <c r="C31">
+        <f>IF(A31=1,"HDR","")</f>
+        <v/>
+      </c>
+      <c r="D31">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="E31">
+        <f>INDEX(Textes!$B$2:$C$55,MATCH("sec_op",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <v/>
+      </c>
+      <c r="F31">
+        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_qty",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <v/>
+      </c>
+      <c r="G31">
+        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_unit",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <v/>
+      </c>
+      <c r="H31">
+        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_pu",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <v/>
+      </c>
+      <c r="I31">
+        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_tot",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <v/>
+      </c>
+      <c r="J31">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="K31">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="L31">
+        <f>""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <f>IF('3 Options'!$C$6="Oui",1,0)</f>
+        <v/>
+      </c>
+      <c r="B32">
+        <f>IF(A32=1,COUNTIF(A$2:A32,1),"")</f>
+        <v/>
+      </c>
+      <c r="C32">
+        <f>IF(A32=1,"LIN","")</f>
+        <v/>
+      </c>
+      <c r="D32">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="E32">
+        <f>IF('3 Options'!$D$6&lt;&gt;"",'3 Options'!$D$6,INDEX(Textes!$B$2:$C$55,MATCH("op_day",Textes!$A$2:$A$55,0),Listes!$H$1))&amp;IF(FALSE,"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
+        <v/>
+      </c>
+      <c r="F32">
+        <f>IF('3 Options'!$G$6="Coût réel +15 %","",'3 Options'!$E$6)</f>
+        <v/>
+      </c>
+      <c r="G32">
+        <f>IF('3 Options'!$G$6="Coût réel +15 %","",'3 Options'!$G$6)</f>
+        <v/>
+      </c>
+      <c r="H32">
+        <f>IF(AND(FALSE,'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$G$6="Coût réel +15 %",INDEX(Textes!$B$2:$C$55,MATCH("at_cost",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$F$6="","",'3 Options'!$F$6)))</f>
+        <v/>
+      </c>
+      <c r="I32">
+        <f>IF(AND(FALSE,'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$G$6="Coût réel +15 %","—",'3 Options'!$H$6))</f>
+        <v/>
+      </c>
+      <c r="J32">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="K32">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="L32">
+        <f>""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <f>IF('3 Options'!$C$7="Oui",1,0)</f>
+        <v/>
+      </c>
+      <c r="B33">
+        <f>IF(A33=1,COUNTIF(A$2:A33,1),"")</f>
+        <v/>
+      </c>
+      <c r="C33">
+        <f>IF(A33=1,"LIN","")</f>
+        <v/>
+      </c>
+      <c r="D33">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="E33">
+        <f>IF('3 Options'!$D$7&lt;&gt;"",'3 Options'!$D$7,INDEX(Textes!$B$2:$C$55,MATCH("op_mob",Textes!$A$2:$A$55,0),Listes!$H$1))&amp;IF(FALSE,"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
+        <v/>
+      </c>
+      <c r="F33">
+        <f>IF('3 Options'!$G$7="Coût réel +15 %","",'3 Options'!$E$7)</f>
+        <v/>
+      </c>
+      <c r="G33">
+        <f>IF('3 Options'!$G$7="Coût réel +15 %","",'3 Options'!$G$7)</f>
+        <v/>
+      </c>
+      <c r="H33">
+        <f>IF(AND(FALSE,'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$G$7="Coût réel +15 %",INDEX(Textes!$B$2:$C$55,MATCH("at_cost",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$F$7="","",'3 Options'!$F$7)))</f>
+        <v/>
+      </c>
+      <c r="I33">
+        <f>IF(AND(FALSE,'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$G$7="Coût réel +15 %","—",'3 Options'!$H$7))</f>
+        <v/>
+      </c>
+      <c r="J33">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="K33">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="L33">
+        <f>""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <f>IF('3 Options'!$C$13="Oui",1,0)</f>
+        <v/>
+      </c>
+      <c r="B34">
+        <f>IF(A34=1,COUNTIF(A$2:A34,1),"")</f>
+        <v/>
+      </c>
+      <c r="C34">
+        <f>IF(A34=1,"FB","")</f>
+        <v/>
+      </c>
+      <c r="D34">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="E34">
+        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("forfait",Textes!$A$2:$A$55,0),Listes!$H$1))&amp;IF('3 Options'!$D$13&lt;&gt;"","   ·   "&amp;'3 Options'!$D$13,"")</f>
+        <v/>
+      </c>
+      <c r="F34">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="G34">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="H34">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="I34">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="J34">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="K34">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="L34">
+        <f>TEXT('3 Options'!$H$13,"#,##0.00")&amp;" € HT"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <f>IF(AND('3 Options'!$C$13="Oui",OR('3 Options'!$D$14&lt;&gt;"",'3 Options'!$G$13="Forfait par jour")),1,0)</f>
+        <v/>
+      </c>
+      <c r="B35">
+        <f>IF(A35=1,COUNTIF(A$2:A35,1),"")</f>
+        <v/>
+      </c>
+      <c r="C35">
+        <f>IF(A35=1,"FD","")</f>
+        <v/>
+      </c>
+      <c r="D35">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="E35">
+        <f>IF('3 Options'!$G$13="Forfait par jour",'3 Options'!$E$13&amp;" j × "&amp;TEXT('3 Options'!$F$13,"#,##0.00")&amp;" €/j"&amp;IF('3 Options'!$D$14&lt;&gt;"","   ·   "&amp;'3 Options'!$D$14,""),'3 Options'!$D$14)</f>
+        <v/>
+      </c>
+      <c r="F35">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="G35">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="H35">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="I35">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="J35">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="K35">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="L35">
+        <f>""</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/devis_2027/Devis_Enedril_2027.xlsx
+++ b/devis_2027/Devis_Enedril_2027.xlsx
@@ -2491,7 +2491,7 @@
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="29">
-        <f>INDEX(Textes!$B$2:$C$55,MATCH("title",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$59,MATCH("title",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="K1" s="1" t="n"/>
@@ -2522,15 +2522,15 @@
     <row r="4" ht="8" customHeight="1"/>
     <row r="5" ht="15" customHeight="1">
       <c r="B5" s="31">
-        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("client",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
+        <f>UPPER(INDEX(Textes!$B$2:$C$59,MATCH("client",Textes!$A$2:$A$59,0),Listes!$H$1))</f>
         <v/>
       </c>
       <c r="D5" s="31">
-        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("offer",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
+        <f>UPPER(INDEX(Textes!$B$2:$C$59,MATCH("offer",Textes!$A$2:$A$59,0),Listes!$H$1))</f>
         <v/>
       </c>
       <c r="H5" s="31">
-        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("date",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
+        <f>UPPER(INDEX(Textes!$B$2:$C$59,MATCH("date",Textes!$A$2:$A$59,0),Listes!$H$1))</f>
         <v/>
       </c>
     </row>
@@ -2556,15 +2556,15 @@
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="B7" s="31">
-        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("attn",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
+        <f>UPPER(INDEX(Textes!$B$2:$C$59,MATCH("attn",Textes!$A$2:$A$59,0),Listes!$H$1))</f>
         <v/>
       </c>
       <c r="D7" s="31">
-        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("well",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
+        <f>UPPER(INDEX(Textes!$B$2:$C$59,MATCH("well",Textes!$A$2:$A$59,0),Listes!$H$1))</f>
         <v/>
       </c>
       <c r="H7" s="31">
-        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("by",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
+        <f>UPPER(INDEX(Textes!$B$2:$C$59,MATCH("by",Textes!$A$2:$A$59,0),Listes!$H$1))</f>
         <v/>
       </c>
     </row>
@@ -2590,15 +2590,15 @@
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="B9" s="31">
-        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("inco",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
+        <f>UPPER(INDEX(Textes!$B$2:$C$59,MATCH("inco",Textes!$A$2:$A$59,0),Listes!$H$1))</f>
         <v/>
       </c>
       <c r="D9" s="31">
-        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("valid",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
+        <f>UPPER(INDEX(Textes!$B$2:$C$59,MATCH("valid",Textes!$A$2:$A$59,0),Listes!$H$1))</f>
         <v/>
       </c>
       <c r="H9" s="31">
-        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("mail",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
+        <f>UPPER(INDEX(Textes!$B$2:$C$59,MATCH("mail",Textes!$A$2:$A$59,0),Listes!$H$1))</f>
         <v/>
       </c>
     </row>
@@ -2624,15 +2624,15 @@
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="B11" s="31">
-        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("pay",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
+        <f>UPPER(INDEX(Textes!$B$2:$C$59,MATCH("pay",Textes!$A$2:$A$59,0),Listes!$H$1))</f>
         <v/>
       </c>
       <c r="D11" s="31">
-        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("we",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
+        <f>UPPER(INDEX(Textes!$B$2:$C$59,MATCH("we",Textes!$A$2:$A$59,0),Listes!$H$1))</f>
         <v/>
       </c>
       <c r="H11" s="31">
-        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("tel",Textes!$A$2:$A$55,0),Listes!$H$1))</f>
+        <f>UPPER(INDEX(Textes!$B$2:$C$59,MATCH("tel",Textes!$A$2:$A$59,0),Listes!$H$1))</f>
         <v/>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
     <row r="13" ht="8" customHeight="1"/>
     <row r="14" ht="20" customHeight="1">
       <c r="B14" s="34">
-        <f>INDEX(Textes!$B$2:$C$55,MATCH("sec_eq",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$59,MATCH("sec_eq",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="C14" s="35" t="n"/>
@@ -2673,39 +2673,39 @@
     </row>
     <row r="15" ht="46" customHeight="1">
       <c r="B15" s="36">
-        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_n",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$59,MATCH("h_n",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="C15" s="37">
-        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_desc",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$59,MATCH("h_desc",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="D15" s="36">
-        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_qty",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$59,MATCH("h_qty",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="E15" s="36">
-        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_s",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$59,MATCH("h_s",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="F15" s="36">
-        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_o",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$59,MATCH("h_o",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="G15" s="36">
-        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_uc",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$59,MATCH("h_uc",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="H15" s="36">
-        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_lih",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$59,MATCH("h_lih",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="I15" s="36">
-        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_insp",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$59,MATCH("h_insp",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="J15" s="36">
-        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_rest",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$59,MATCH("h_rest",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
     <row r="57" ht="8" customHeight="1"/>
     <row r="58" ht="20" customHeight="1">
       <c r="B58" s="34">
-        <f>INDEX(Textes!$B$2:$C$55,MATCH("sec_cond",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$59,MATCH("sec_cond",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="C58" s="35" t="n"/>
@@ -4570,22 +4570,24 @@
       <c r="I58" s="35" t="n"/>
       <c r="J58" s="35" t="n"/>
     </row>
-    <row r="59" ht="76" customHeight="1">
+    <row r="59" ht="92" customHeight="1">
       <c r="B59" s="44" t="inlineStr">
         <is>
           <t>La location s'entend depuis le jour de départ de la base d'origine jusqu'à son retour au même endroit.
 Le Wear Charge s'applique pour toute usure liée à un usage normal des équipements. En cas de dommages plus importants liés à un usage anormal, la valeur de remplacement sera facturée sur documentation.
 Charges additionnelles à prévoir pour le colisage d'outils destinés à une expédition en aérien ou maritime.
+Tous les transports effectués auprès d'un fournisseur pour la fourniture des équipements sont facturés au coût réel +15 % (idem pour les frais de douane, etc.).
 Conditions générales de vente disponibles sur demande ou sur notre site internet www.enedril.com</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="76" customHeight="1">
+    <row r="60" ht="92" customHeight="1">
       <c r="B60" s="44" t="inlineStr">
         <is>
           <t>The rental is from the day of departure from the base of origin until its return to the same place.
 Wear Charge applies to all wear and tear related to normal use of equipment. In case of greater damage due to abnormal use, the replacement value will be charged based on supporting documentation.
 Additional charges may apply for packing tools intended for air or ocean shipment.
+All transport carried out through a supplier for the supply of equipment is invoiced at cost +15% (same for customs fees, etc.).
 General conditions of sale available upon request or on our website www.enedril.com</t>
         </is>
       </c>
@@ -4593,25 +4595,25 @@
     <row r="61" ht="10" customHeight="1"/>
     <row r="62">
       <c r="B62" s="45">
-        <f>INDEX(Textes!$B$2:$C$55,MATCH("accept",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$59,MATCH("accept",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
     </row>
     <row r="63" ht="17" customHeight="1">
       <c r="B63" s="46">
-        <f>INDEX(Textes!$B$2:$C$55,MATCH("sig_name",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$59,MATCH("sig_name",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="C63" s="47" t="n"/>
       <c r="D63" s="46">
-        <f>INDEX(Textes!$B$2:$C$55,MATCH("sig_date",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$59,MATCH("sig_date",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="E63" s="48" t="n"/>
       <c r="F63" s="48" t="n"/>
       <c r="G63" s="47" t="n"/>
       <c r="H63" s="46">
-        <f>INDEX(Textes!$B$2:$C$55,MATCH("sig_sig",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$59,MATCH("sig_sig",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="I63" s="48" t="n"/>
@@ -5165,7 +5167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6074,49 +6076,117 @@
     <row r="53">
       <c r="A53" s="59" t="inlineStr">
         <is>
-          <t>sec_tight</t>
+          <t>days</t>
         </is>
       </c>
       <c r="B53" s="59" t="inlineStr">
         <is>
-          <t>SERRAGE · TONG &amp; MAKE-UP</t>
+          <t>JOURS</t>
         </is>
       </c>
       <c r="C53" s="59" t="inlineStr">
         <is>
-          <t>TONG &amp; MAKE-UP SERVICE</t>
+          <t>DAYS</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="59" t="inlineStr">
         <is>
-          <t>sec_tr</t>
+          <t>in_tight</t>
         </is>
       </c>
       <c r="B54" s="59" t="inlineStr">
         <is>
-          <t>TRANSPORT</t>
+          <t>serrage inclus</t>
         </is>
       </c>
       <c r="C54" s="59" t="inlineStr">
         <is>
-          <t>TRANSPORT</t>
+          <t>make-up included</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="59" t="inlineStr">
         <is>
+          <t>in_tr</t>
+        </is>
+      </c>
+      <c r="B55" s="59" t="inlineStr">
+        <is>
+          <t>transport inclus</t>
+        </is>
+      </c>
+      <c r="C55" s="59" t="inlineStr">
+        <is>
+          <t>transport included</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="59" t="inlineStr">
+        <is>
+          <t>in_both</t>
+        </is>
+      </c>
+      <c r="B56" s="59" t="inlineStr">
+        <is>
+          <t>serrage et transport inclus</t>
+        </is>
+      </c>
+      <c r="C56" s="59" t="inlineStr">
+        <is>
+          <t>make-up and transport included</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="59" t="inlineStr">
+        <is>
+          <t>sec_tight</t>
+        </is>
+      </c>
+      <c r="B57" s="59" t="inlineStr">
+        <is>
+          <t>SERRAGE · TONG &amp; MAKE-UP</t>
+        </is>
+      </c>
+      <c r="C57" s="59" t="inlineStr">
+        <is>
+          <t>TONG &amp; MAKE-UP SERVICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="59" t="inlineStr">
+        <is>
+          <t>sec_tr</t>
+        </is>
+      </c>
+      <c r="B58" s="59" t="inlineStr">
+        <is>
+          <t>TRANSPORT</t>
+        </is>
+      </c>
+      <c r="C58" s="59" t="inlineStr">
+        <is>
+          <t>TRANSPORT</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="59" t="inlineStr">
+        <is>
           <t>sec_op</t>
         </is>
       </c>
-      <c r="B55" s="59" t="inlineStr">
+      <c r="B59" s="59" t="inlineStr">
         <is>
           <t>OPÉRATEURS</t>
         </is>
       </c>
-      <c r="C55" s="59" t="inlineStr">
+      <c r="C59" s="59" t="inlineStr">
         <is>
           <t>OPERATORS</t>
         </is>
@@ -6217,7 +6287,7 @@
         <v/>
       </c>
       <c r="E2">
-        <f>IF(C2="BAN",UPPER('2 Matériel'!$C6),IF(C2="ITM",'2 Matériel'!$C6&amp;IF(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <f>IF(C2="BAN",UPPER('2 Matériel'!$C6),IF(C2="ITM",'2 Matériel'!$C6&amp;IF(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$59,MATCH("incl_long",Textes!$A$2:$A$59,0),Listes!$H$1),""),""))</f>
         <v/>
       </c>
       <c r="F2">
@@ -6225,27 +6295,27 @@
         <v/>
       </c>
       <c r="G2">
-        <f>IF(C2="ITM",IF(AND(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E6="","",'2 Matériel'!$E6)),"")</f>
+        <f>IF(C2="ITM",IF(AND(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$E6="","",'2 Matériel'!$E6)),"")</f>
         <v/>
       </c>
       <c r="H2">
-        <f>IF(C2="ITM",IF(AND(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F6="","",'2 Matériel'!$F6)),"")</f>
+        <f>IF(C2="ITM",IF(AND(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$F6="","",'2 Matériel'!$F6)),"")</f>
         <v/>
       </c>
       <c r="I2">
-        <f>IF(C2="ITM",IF(AND(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G6="","",'2 Matériel'!$G6)),"")</f>
+        <f>IF(C2="ITM",IF(AND(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$G6="","",'2 Matériel'!$G6)),"")</f>
         <v/>
       </c>
       <c r="J2">
-        <f>IF(C2="ITM",IF(AND(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H6="","",'2 Matériel'!$H6)),"")</f>
+        <f>IF(C2="ITM",IF(AND(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$H6="","",'2 Matériel'!$H6)),"")</f>
         <v/>
       </c>
       <c r="K2">
-        <f>IF(C2="ITM",IF(AND(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I6="","",'2 Matériel'!$I6)),"")</f>
+        <f>IF(C2="ITM",IF(AND(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$I6="","",'2 Matériel'!$I6)),"")</f>
         <v/>
       </c>
       <c r="L2">
-        <f>IF(C2="ITM",IF(AND(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J6="","",'2 Matériel'!$J6)),"")</f>
+        <f>IF(C2="ITM",IF(AND(AND('2 Matériel'!$K6="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$J6="","",'2 Matériel'!$J6)),"")</f>
         <v/>
       </c>
     </row>
@@ -6267,7 +6337,7 @@
         <v/>
       </c>
       <c r="E3">
-        <f>IF(C3="BAN",UPPER('2 Matériel'!$C7),IF(C3="ITM",'2 Matériel'!$C7&amp;IF(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <f>IF(C3="BAN",UPPER('2 Matériel'!$C7),IF(C3="ITM",'2 Matériel'!$C7&amp;IF(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$59,MATCH("incl_long",Textes!$A$2:$A$59,0),Listes!$H$1),""),""))</f>
         <v/>
       </c>
       <c r="F3">
@@ -6275,27 +6345,27 @@
         <v/>
       </c>
       <c r="G3">
-        <f>IF(C3="ITM",IF(AND(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E7="","",'2 Matériel'!$E7)),"")</f>
+        <f>IF(C3="ITM",IF(AND(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$E7="","",'2 Matériel'!$E7)),"")</f>
         <v/>
       </c>
       <c r="H3">
-        <f>IF(C3="ITM",IF(AND(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F7="","",'2 Matériel'!$F7)),"")</f>
+        <f>IF(C3="ITM",IF(AND(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$F7="","",'2 Matériel'!$F7)),"")</f>
         <v/>
       </c>
       <c r="I3">
-        <f>IF(C3="ITM",IF(AND(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G7="","",'2 Matériel'!$G7)),"")</f>
+        <f>IF(C3="ITM",IF(AND(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$G7="","",'2 Matériel'!$G7)),"")</f>
         <v/>
       </c>
       <c r="J3">
-        <f>IF(C3="ITM",IF(AND(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H7="","",'2 Matériel'!$H7)),"")</f>
+        <f>IF(C3="ITM",IF(AND(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$H7="","",'2 Matériel'!$H7)),"")</f>
         <v/>
       </c>
       <c r="K3">
-        <f>IF(C3="ITM",IF(AND(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I7="","",'2 Matériel'!$I7)),"")</f>
+        <f>IF(C3="ITM",IF(AND(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$I7="","",'2 Matériel'!$I7)),"")</f>
         <v/>
       </c>
       <c r="L3">
-        <f>IF(C3="ITM",IF(AND(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J7="","",'2 Matériel'!$J7)),"")</f>
+        <f>IF(C3="ITM",IF(AND(AND('2 Matériel'!$K7="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$J7="","",'2 Matériel'!$J7)),"")</f>
         <v/>
       </c>
     </row>
@@ -6317,7 +6387,7 @@
         <v/>
       </c>
       <c r="E4">
-        <f>IF(C4="BAN",UPPER('2 Matériel'!$C8),IF(C4="ITM",'2 Matériel'!$C8&amp;IF(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <f>IF(C4="BAN",UPPER('2 Matériel'!$C8),IF(C4="ITM",'2 Matériel'!$C8&amp;IF(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$59,MATCH("incl_long",Textes!$A$2:$A$59,0),Listes!$H$1),""),""))</f>
         <v/>
       </c>
       <c r="F4">
@@ -6325,27 +6395,27 @@
         <v/>
       </c>
       <c r="G4">
-        <f>IF(C4="ITM",IF(AND(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E8="","",'2 Matériel'!$E8)),"")</f>
+        <f>IF(C4="ITM",IF(AND(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$E8="","",'2 Matériel'!$E8)),"")</f>
         <v/>
       </c>
       <c r="H4">
-        <f>IF(C4="ITM",IF(AND(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F8="","",'2 Matériel'!$F8)),"")</f>
+        <f>IF(C4="ITM",IF(AND(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$F8="","",'2 Matériel'!$F8)),"")</f>
         <v/>
       </c>
       <c r="I4">
-        <f>IF(C4="ITM",IF(AND(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G8="","",'2 Matériel'!$G8)),"")</f>
+        <f>IF(C4="ITM",IF(AND(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$G8="","",'2 Matériel'!$G8)),"")</f>
         <v/>
       </c>
       <c r="J4">
-        <f>IF(C4="ITM",IF(AND(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H8="","",'2 Matériel'!$H8)),"")</f>
+        <f>IF(C4="ITM",IF(AND(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$H8="","",'2 Matériel'!$H8)),"")</f>
         <v/>
       </c>
       <c r="K4">
-        <f>IF(C4="ITM",IF(AND(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I8="","",'2 Matériel'!$I8)),"")</f>
+        <f>IF(C4="ITM",IF(AND(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$I8="","",'2 Matériel'!$I8)),"")</f>
         <v/>
       </c>
       <c r="L4">
-        <f>IF(C4="ITM",IF(AND(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J8="","",'2 Matériel'!$J8)),"")</f>
+        <f>IF(C4="ITM",IF(AND(AND('2 Matériel'!$K8="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$J8="","",'2 Matériel'!$J8)),"")</f>
         <v/>
       </c>
     </row>
@@ -6367,7 +6437,7 @@
         <v/>
       </c>
       <c r="E5">
-        <f>IF(C5="BAN",UPPER('2 Matériel'!$C9),IF(C5="ITM",'2 Matériel'!$C9&amp;IF(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <f>IF(C5="BAN",UPPER('2 Matériel'!$C9),IF(C5="ITM",'2 Matériel'!$C9&amp;IF(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$59,MATCH("incl_long",Textes!$A$2:$A$59,0),Listes!$H$1),""),""))</f>
         <v/>
       </c>
       <c r="F5">
@@ -6375,27 +6445,27 @@
         <v/>
       </c>
       <c r="G5">
-        <f>IF(C5="ITM",IF(AND(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E9="","",'2 Matériel'!$E9)),"")</f>
+        <f>IF(C5="ITM",IF(AND(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$E9="","",'2 Matériel'!$E9)),"")</f>
         <v/>
       </c>
       <c r="H5">
-        <f>IF(C5="ITM",IF(AND(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F9="","",'2 Matériel'!$F9)),"")</f>
+        <f>IF(C5="ITM",IF(AND(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$F9="","",'2 Matériel'!$F9)),"")</f>
         <v/>
       </c>
       <c r="I5">
-        <f>IF(C5="ITM",IF(AND(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G9="","",'2 Matériel'!$G9)),"")</f>
+        <f>IF(C5="ITM",IF(AND(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$G9="","",'2 Matériel'!$G9)),"")</f>
         <v/>
       </c>
       <c r="J5">
-        <f>IF(C5="ITM",IF(AND(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H9="","",'2 Matériel'!$H9)),"")</f>
+        <f>IF(C5="ITM",IF(AND(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$H9="","",'2 Matériel'!$H9)),"")</f>
         <v/>
       </c>
       <c r="K5">
-        <f>IF(C5="ITM",IF(AND(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I9="","",'2 Matériel'!$I9)),"")</f>
+        <f>IF(C5="ITM",IF(AND(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$I9="","",'2 Matériel'!$I9)),"")</f>
         <v/>
       </c>
       <c r="L5">
-        <f>IF(C5="ITM",IF(AND(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J9="","",'2 Matériel'!$J9)),"")</f>
+        <f>IF(C5="ITM",IF(AND(AND('2 Matériel'!$K9="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$J9="","",'2 Matériel'!$J9)),"")</f>
         <v/>
       </c>
     </row>
@@ -6417,7 +6487,7 @@
         <v/>
       </c>
       <c r="E6">
-        <f>IF(C6="BAN",UPPER('2 Matériel'!$C10),IF(C6="ITM",'2 Matériel'!$C10&amp;IF(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <f>IF(C6="BAN",UPPER('2 Matériel'!$C10),IF(C6="ITM",'2 Matériel'!$C10&amp;IF(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$59,MATCH("incl_long",Textes!$A$2:$A$59,0),Listes!$H$1),""),""))</f>
         <v/>
       </c>
       <c r="F6">
@@ -6425,27 +6495,27 @@
         <v/>
       </c>
       <c r="G6">
-        <f>IF(C6="ITM",IF(AND(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E10="","",'2 Matériel'!$E10)),"")</f>
+        <f>IF(C6="ITM",IF(AND(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$E10="","",'2 Matériel'!$E10)),"")</f>
         <v/>
       </c>
       <c r="H6">
-        <f>IF(C6="ITM",IF(AND(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F10="","",'2 Matériel'!$F10)),"")</f>
+        <f>IF(C6="ITM",IF(AND(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$F10="","",'2 Matériel'!$F10)),"")</f>
         <v/>
       </c>
       <c r="I6">
-        <f>IF(C6="ITM",IF(AND(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G10="","",'2 Matériel'!$G10)),"")</f>
+        <f>IF(C6="ITM",IF(AND(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$G10="","",'2 Matériel'!$G10)),"")</f>
         <v/>
       </c>
       <c r="J6">
-        <f>IF(C6="ITM",IF(AND(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H10="","",'2 Matériel'!$H10)),"")</f>
+        <f>IF(C6="ITM",IF(AND(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$H10="","",'2 Matériel'!$H10)),"")</f>
         <v/>
       </c>
       <c r="K6">
-        <f>IF(C6="ITM",IF(AND(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I10="","",'2 Matériel'!$I10)),"")</f>
+        <f>IF(C6="ITM",IF(AND(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$I10="","",'2 Matériel'!$I10)),"")</f>
         <v/>
       </c>
       <c r="L6">
-        <f>IF(C6="ITM",IF(AND(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J10="","",'2 Matériel'!$J10)),"")</f>
+        <f>IF(C6="ITM",IF(AND(AND('2 Matériel'!$K10="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$J10="","",'2 Matériel'!$J10)),"")</f>
         <v/>
       </c>
     </row>
@@ -6467,7 +6537,7 @@
         <v/>
       </c>
       <c r="E7">
-        <f>IF(C7="BAN",UPPER('2 Matériel'!$C11),IF(C7="ITM",'2 Matériel'!$C11&amp;IF(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <f>IF(C7="BAN",UPPER('2 Matériel'!$C11),IF(C7="ITM",'2 Matériel'!$C11&amp;IF(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$59,MATCH("incl_long",Textes!$A$2:$A$59,0),Listes!$H$1),""),""))</f>
         <v/>
       </c>
       <c r="F7">
@@ -6475,27 +6545,27 @@
         <v/>
       </c>
       <c r="G7">
-        <f>IF(C7="ITM",IF(AND(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E11="","",'2 Matériel'!$E11)),"")</f>
+        <f>IF(C7="ITM",IF(AND(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$E11="","",'2 Matériel'!$E11)),"")</f>
         <v/>
       </c>
       <c r="H7">
-        <f>IF(C7="ITM",IF(AND(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F11="","",'2 Matériel'!$F11)),"")</f>
+        <f>IF(C7="ITM",IF(AND(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$F11="","",'2 Matériel'!$F11)),"")</f>
         <v/>
       </c>
       <c r="I7">
-        <f>IF(C7="ITM",IF(AND(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G11="","",'2 Matériel'!$G11)),"")</f>
+        <f>IF(C7="ITM",IF(AND(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$G11="","",'2 Matériel'!$G11)),"")</f>
         <v/>
       </c>
       <c r="J7">
-        <f>IF(C7="ITM",IF(AND(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H11="","",'2 Matériel'!$H11)),"")</f>
+        <f>IF(C7="ITM",IF(AND(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$H11="","",'2 Matériel'!$H11)),"")</f>
         <v/>
       </c>
       <c r="K7">
-        <f>IF(C7="ITM",IF(AND(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I11="","",'2 Matériel'!$I11)),"")</f>
+        <f>IF(C7="ITM",IF(AND(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$I11="","",'2 Matériel'!$I11)),"")</f>
         <v/>
       </c>
       <c r="L7">
-        <f>IF(C7="ITM",IF(AND(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J11="","",'2 Matériel'!$J11)),"")</f>
+        <f>IF(C7="ITM",IF(AND(AND('2 Matériel'!$K11="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$J11="","",'2 Matériel'!$J11)),"")</f>
         <v/>
       </c>
     </row>
@@ -6517,7 +6587,7 @@
         <v/>
       </c>
       <c r="E8">
-        <f>IF(C8="BAN",UPPER('2 Matériel'!$C12),IF(C8="ITM",'2 Matériel'!$C12&amp;IF(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <f>IF(C8="BAN",UPPER('2 Matériel'!$C12),IF(C8="ITM",'2 Matériel'!$C12&amp;IF(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$59,MATCH("incl_long",Textes!$A$2:$A$59,0),Listes!$H$1),""),""))</f>
         <v/>
       </c>
       <c r="F8">
@@ -6525,27 +6595,27 @@
         <v/>
       </c>
       <c r="G8">
-        <f>IF(C8="ITM",IF(AND(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E12="","",'2 Matériel'!$E12)),"")</f>
+        <f>IF(C8="ITM",IF(AND(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$E12="","",'2 Matériel'!$E12)),"")</f>
         <v/>
       </c>
       <c r="H8">
-        <f>IF(C8="ITM",IF(AND(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F12="","",'2 Matériel'!$F12)),"")</f>
+        <f>IF(C8="ITM",IF(AND(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$F12="","",'2 Matériel'!$F12)),"")</f>
         <v/>
       </c>
       <c r="I8">
-        <f>IF(C8="ITM",IF(AND(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G12="","",'2 Matériel'!$G12)),"")</f>
+        <f>IF(C8="ITM",IF(AND(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$G12="","",'2 Matériel'!$G12)),"")</f>
         <v/>
       </c>
       <c r="J8">
-        <f>IF(C8="ITM",IF(AND(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H12="","",'2 Matériel'!$H12)),"")</f>
+        <f>IF(C8="ITM",IF(AND(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$H12="","",'2 Matériel'!$H12)),"")</f>
         <v/>
       </c>
       <c r="K8">
-        <f>IF(C8="ITM",IF(AND(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I12="","",'2 Matériel'!$I12)),"")</f>
+        <f>IF(C8="ITM",IF(AND(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$I12="","",'2 Matériel'!$I12)),"")</f>
         <v/>
       </c>
       <c r="L8">
-        <f>IF(C8="ITM",IF(AND(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J12="","",'2 Matériel'!$J12)),"")</f>
+        <f>IF(C8="ITM",IF(AND(AND('2 Matériel'!$K12="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$J12="","",'2 Matériel'!$J12)),"")</f>
         <v/>
       </c>
     </row>
@@ -6567,7 +6637,7 @@
         <v/>
       </c>
       <c r="E9">
-        <f>IF(C9="BAN",UPPER('2 Matériel'!$C13),IF(C9="ITM",'2 Matériel'!$C13&amp;IF(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <f>IF(C9="BAN",UPPER('2 Matériel'!$C13),IF(C9="ITM",'2 Matériel'!$C13&amp;IF(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$59,MATCH("incl_long",Textes!$A$2:$A$59,0),Listes!$H$1),""),""))</f>
         <v/>
       </c>
       <c r="F9">
@@ -6575,27 +6645,27 @@
         <v/>
       </c>
       <c r="G9">
-        <f>IF(C9="ITM",IF(AND(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E13="","",'2 Matériel'!$E13)),"")</f>
+        <f>IF(C9="ITM",IF(AND(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$E13="","",'2 Matériel'!$E13)),"")</f>
         <v/>
       </c>
       <c r="H9">
-        <f>IF(C9="ITM",IF(AND(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F13="","",'2 Matériel'!$F13)),"")</f>
+        <f>IF(C9="ITM",IF(AND(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$F13="","",'2 Matériel'!$F13)),"")</f>
         <v/>
       </c>
       <c r="I9">
-        <f>IF(C9="ITM",IF(AND(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G13="","",'2 Matériel'!$G13)),"")</f>
+        <f>IF(C9="ITM",IF(AND(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$G13="","",'2 Matériel'!$G13)),"")</f>
         <v/>
       </c>
       <c r="J9">
-        <f>IF(C9="ITM",IF(AND(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H13="","",'2 Matériel'!$H13)),"")</f>
+        <f>IF(C9="ITM",IF(AND(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$H13="","",'2 Matériel'!$H13)),"")</f>
         <v/>
       </c>
       <c r="K9">
-        <f>IF(C9="ITM",IF(AND(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I13="","",'2 Matériel'!$I13)),"")</f>
+        <f>IF(C9="ITM",IF(AND(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$I13="","",'2 Matériel'!$I13)),"")</f>
         <v/>
       </c>
       <c r="L9">
-        <f>IF(C9="ITM",IF(AND(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J13="","",'2 Matériel'!$J13)),"")</f>
+        <f>IF(C9="ITM",IF(AND(AND('2 Matériel'!$K13="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$J13="","",'2 Matériel'!$J13)),"")</f>
         <v/>
       </c>
     </row>
@@ -6617,7 +6687,7 @@
         <v/>
       </c>
       <c r="E10">
-        <f>IF(C10="BAN",UPPER('2 Matériel'!$C14),IF(C10="ITM",'2 Matériel'!$C14&amp;IF(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <f>IF(C10="BAN",UPPER('2 Matériel'!$C14),IF(C10="ITM",'2 Matériel'!$C14&amp;IF(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$59,MATCH("incl_long",Textes!$A$2:$A$59,0),Listes!$H$1),""),""))</f>
         <v/>
       </c>
       <c r="F10">
@@ -6625,27 +6695,27 @@
         <v/>
       </c>
       <c r="G10">
-        <f>IF(C10="ITM",IF(AND(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E14="","",'2 Matériel'!$E14)),"")</f>
+        <f>IF(C10="ITM",IF(AND(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$E14="","",'2 Matériel'!$E14)),"")</f>
         <v/>
       </c>
       <c r="H10">
-        <f>IF(C10="ITM",IF(AND(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F14="","",'2 Matériel'!$F14)),"")</f>
+        <f>IF(C10="ITM",IF(AND(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$F14="","",'2 Matériel'!$F14)),"")</f>
         <v/>
       </c>
       <c r="I10">
-        <f>IF(C10="ITM",IF(AND(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G14="","",'2 Matériel'!$G14)),"")</f>
+        <f>IF(C10="ITM",IF(AND(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$G14="","",'2 Matériel'!$G14)),"")</f>
         <v/>
       </c>
       <c r="J10">
-        <f>IF(C10="ITM",IF(AND(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H14="","",'2 Matériel'!$H14)),"")</f>
+        <f>IF(C10="ITM",IF(AND(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$H14="","",'2 Matériel'!$H14)),"")</f>
         <v/>
       </c>
       <c r="K10">
-        <f>IF(C10="ITM",IF(AND(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I14="","",'2 Matériel'!$I14)),"")</f>
+        <f>IF(C10="ITM",IF(AND(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$I14="","",'2 Matériel'!$I14)),"")</f>
         <v/>
       </c>
       <c r="L10">
-        <f>IF(C10="ITM",IF(AND(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J14="","",'2 Matériel'!$J14)),"")</f>
+        <f>IF(C10="ITM",IF(AND(AND('2 Matériel'!$K14="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$J14="","",'2 Matériel'!$J14)),"")</f>
         <v/>
       </c>
     </row>
@@ -6667,7 +6737,7 @@
         <v/>
       </c>
       <c r="E11">
-        <f>IF(C11="BAN",UPPER('2 Matériel'!$C15),IF(C11="ITM",'2 Matériel'!$C15&amp;IF(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <f>IF(C11="BAN",UPPER('2 Matériel'!$C15),IF(C11="ITM",'2 Matériel'!$C15&amp;IF(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$59,MATCH("incl_long",Textes!$A$2:$A$59,0),Listes!$H$1),""),""))</f>
         <v/>
       </c>
       <c r="F11">
@@ -6675,27 +6745,27 @@
         <v/>
       </c>
       <c r="G11">
-        <f>IF(C11="ITM",IF(AND(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E15="","",'2 Matériel'!$E15)),"")</f>
+        <f>IF(C11="ITM",IF(AND(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$E15="","",'2 Matériel'!$E15)),"")</f>
         <v/>
       </c>
       <c r="H11">
-        <f>IF(C11="ITM",IF(AND(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F15="","",'2 Matériel'!$F15)),"")</f>
+        <f>IF(C11="ITM",IF(AND(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$F15="","",'2 Matériel'!$F15)),"")</f>
         <v/>
       </c>
       <c r="I11">
-        <f>IF(C11="ITM",IF(AND(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G15="","",'2 Matériel'!$G15)),"")</f>
+        <f>IF(C11="ITM",IF(AND(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$G15="","",'2 Matériel'!$G15)),"")</f>
         <v/>
       </c>
       <c r="J11">
-        <f>IF(C11="ITM",IF(AND(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H15="","",'2 Matériel'!$H15)),"")</f>
+        <f>IF(C11="ITM",IF(AND(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$H15="","",'2 Matériel'!$H15)),"")</f>
         <v/>
       </c>
       <c r="K11">
-        <f>IF(C11="ITM",IF(AND(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I15="","",'2 Matériel'!$I15)),"")</f>
+        <f>IF(C11="ITM",IF(AND(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$I15="","",'2 Matériel'!$I15)),"")</f>
         <v/>
       </c>
       <c r="L11">
-        <f>IF(C11="ITM",IF(AND(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J15="","",'2 Matériel'!$J15)),"")</f>
+        <f>IF(C11="ITM",IF(AND(AND('2 Matériel'!$K15="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$J15="","",'2 Matériel'!$J15)),"")</f>
         <v/>
       </c>
     </row>
@@ -6717,7 +6787,7 @@
         <v/>
       </c>
       <c r="E12">
-        <f>IF(C12="BAN",UPPER('2 Matériel'!$C16),IF(C12="ITM",'2 Matériel'!$C16&amp;IF(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <f>IF(C12="BAN",UPPER('2 Matériel'!$C16),IF(C12="ITM",'2 Matériel'!$C16&amp;IF(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$59,MATCH("incl_long",Textes!$A$2:$A$59,0),Listes!$H$1),""),""))</f>
         <v/>
       </c>
       <c r="F12">
@@ -6725,27 +6795,27 @@
         <v/>
       </c>
       <c r="G12">
-        <f>IF(C12="ITM",IF(AND(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E16="","",'2 Matériel'!$E16)),"")</f>
+        <f>IF(C12="ITM",IF(AND(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$E16="","",'2 Matériel'!$E16)),"")</f>
         <v/>
       </c>
       <c r="H12">
-        <f>IF(C12="ITM",IF(AND(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F16="","",'2 Matériel'!$F16)),"")</f>
+        <f>IF(C12="ITM",IF(AND(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$F16="","",'2 Matériel'!$F16)),"")</f>
         <v/>
       </c>
       <c r="I12">
-        <f>IF(C12="ITM",IF(AND(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G16="","",'2 Matériel'!$G16)),"")</f>
+        <f>IF(C12="ITM",IF(AND(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$G16="","",'2 Matériel'!$G16)),"")</f>
         <v/>
       </c>
       <c r="J12">
-        <f>IF(C12="ITM",IF(AND(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H16="","",'2 Matériel'!$H16)),"")</f>
+        <f>IF(C12="ITM",IF(AND(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$H16="","",'2 Matériel'!$H16)),"")</f>
         <v/>
       </c>
       <c r="K12">
-        <f>IF(C12="ITM",IF(AND(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I16="","",'2 Matériel'!$I16)),"")</f>
+        <f>IF(C12="ITM",IF(AND(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$I16="","",'2 Matériel'!$I16)),"")</f>
         <v/>
       </c>
       <c r="L12">
-        <f>IF(C12="ITM",IF(AND(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J16="","",'2 Matériel'!$J16)),"")</f>
+        <f>IF(C12="ITM",IF(AND(AND('2 Matériel'!$K16="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$J16="","",'2 Matériel'!$J16)),"")</f>
         <v/>
       </c>
     </row>
@@ -6767,7 +6837,7 @@
         <v/>
       </c>
       <c r="E13">
-        <f>IF(C13="BAN",UPPER('2 Matériel'!$C17),IF(C13="ITM",'2 Matériel'!$C17&amp;IF(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <f>IF(C13="BAN",UPPER('2 Matériel'!$C17),IF(C13="ITM",'2 Matériel'!$C17&amp;IF(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$59,MATCH("incl_long",Textes!$A$2:$A$59,0),Listes!$H$1),""),""))</f>
         <v/>
       </c>
       <c r="F13">
@@ -6775,27 +6845,27 @@
         <v/>
       </c>
       <c r="G13">
-        <f>IF(C13="ITM",IF(AND(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E17="","",'2 Matériel'!$E17)),"")</f>
+        <f>IF(C13="ITM",IF(AND(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$E17="","",'2 Matériel'!$E17)),"")</f>
         <v/>
       </c>
       <c r="H13">
-        <f>IF(C13="ITM",IF(AND(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F17="","",'2 Matériel'!$F17)),"")</f>
+        <f>IF(C13="ITM",IF(AND(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$F17="","",'2 Matériel'!$F17)),"")</f>
         <v/>
       </c>
       <c r="I13">
-        <f>IF(C13="ITM",IF(AND(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G17="","",'2 Matériel'!$G17)),"")</f>
+        <f>IF(C13="ITM",IF(AND(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$G17="","",'2 Matériel'!$G17)),"")</f>
         <v/>
       </c>
       <c r="J13">
-        <f>IF(C13="ITM",IF(AND(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H17="","",'2 Matériel'!$H17)),"")</f>
+        <f>IF(C13="ITM",IF(AND(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$H17="","",'2 Matériel'!$H17)),"")</f>
         <v/>
       </c>
       <c r="K13">
-        <f>IF(C13="ITM",IF(AND(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I17="","",'2 Matériel'!$I17)),"")</f>
+        <f>IF(C13="ITM",IF(AND(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$I17="","",'2 Matériel'!$I17)),"")</f>
         <v/>
       </c>
       <c r="L13">
-        <f>IF(C13="ITM",IF(AND(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J17="","",'2 Matériel'!$J17)),"")</f>
+        <f>IF(C13="ITM",IF(AND(AND('2 Matériel'!$K17="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$J17="","",'2 Matériel'!$J17)),"")</f>
         <v/>
       </c>
     </row>
@@ -6817,7 +6887,7 @@
         <v/>
       </c>
       <c r="E14">
-        <f>IF(C14="BAN",UPPER('2 Matériel'!$C18),IF(C14="ITM",'2 Matériel'!$C18&amp;IF(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <f>IF(C14="BAN",UPPER('2 Matériel'!$C18),IF(C14="ITM",'2 Matériel'!$C18&amp;IF(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$59,MATCH("incl_long",Textes!$A$2:$A$59,0),Listes!$H$1),""),""))</f>
         <v/>
       </c>
       <c r="F14">
@@ -6825,27 +6895,27 @@
         <v/>
       </c>
       <c r="G14">
-        <f>IF(C14="ITM",IF(AND(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E18="","",'2 Matériel'!$E18)),"")</f>
+        <f>IF(C14="ITM",IF(AND(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$E18="","",'2 Matériel'!$E18)),"")</f>
         <v/>
       </c>
       <c r="H14">
-        <f>IF(C14="ITM",IF(AND(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F18="","",'2 Matériel'!$F18)),"")</f>
+        <f>IF(C14="ITM",IF(AND(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$F18="","",'2 Matériel'!$F18)),"")</f>
         <v/>
       </c>
       <c r="I14">
-        <f>IF(C14="ITM",IF(AND(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G18="","",'2 Matériel'!$G18)),"")</f>
+        <f>IF(C14="ITM",IF(AND(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$G18="","",'2 Matériel'!$G18)),"")</f>
         <v/>
       </c>
       <c r="J14">
-        <f>IF(C14="ITM",IF(AND(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H18="","",'2 Matériel'!$H18)),"")</f>
+        <f>IF(C14="ITM",IF(AND(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$H18="","",'2 Matériel'!$H18)),"")</f>
         <v/>
       </c>
       <c r="K14">
-        <f>IF(C14="ITM",IF(AND(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I18="","",'2 Matériel'!$I18)),"")</f>
+        <f>IF(C14="ITM",IF(AND(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$I18="","",'2 Matériel'!$I18)),"")</f>
         <v/>
       </c>
       <c r="L14">
-        <f>IF(C14="ITM",IF(AND(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J18="","",'2 Matériel'!$J18)),"")</f>
+        <f>IF(C14="ITM",IF(AND(AND('2 Matériel'!$K18="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$J18="","",'2 Matériel'!$J18)),"")</f>
         <v/>
       </c>
     </row>
@@ -6867,7 +6937,7 @@
         <v/>
       </c>
       <c r="E15">
-        <f>IF(C15="BAN",UPPER('2 Matériel'!$C19),IF(C15="ITM",'2 Matériel'!$C19&amp;IF(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <f>IF(C15="BAN",UPPER('2 Matériel'!$C19),IF(C15="ITM",'2 Matériel'!$C19&amp;IF(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$59,MATCH("incl_long",Textes!$A$2:$A$59,0),Listes!$H$1),""),""))</f>
         <v/>
       </c>
       <c r="F15">
@@ -6875,27 +6945,27 @@
         <v/>
       </c>
       <c r="G15">
-        <f>IF(C15="ITM",IF(AND(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E19="","",'2 Matériel'!$E19)),"")</f>
+        <f>IF(C15="ITM",IF(AND(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$E19="","",'2 Matériel'!$E19)),"")</f>
         <v/>
       </c>
       <c r="H15">
-        <f>IF(C15="ITM",IF(AND(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F19="","",'2 Matériel'!$F19)),"")</f>
+        <f>IF(C15="ITM",IF(AND(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$F19="","",'2 Matériel'!$F19)),"")</f>
         <v/>
       </c>
       <c r="I15">
-        <f>IF(C15="ITM",IF(AND(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G19="","",'2 Matériel'!$G19)),"")</f>
+        <f>IF(C15="ITM",IF(AND(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$G19="","",'2 Matériel'!$G19)),"")</f>
         <v/>
       </c>
       <c r="J15">
-        <f>IF(C15="ITM",IF(AND(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H19="","",'2 Matériel'!$H19)),"")</f>
+        <f>IF(C15="ITM",IF(AND(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$H19="","",'2 Matériel'!$H19)),"")</f>
         <v/>
       </c>
       <c r="K15">
-        <f>IF(C15="ITM",IF(AND(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I19="","",'2 Matériel'!$I19)),"")</f>
+        <f>IF(C15="ITM",IF(AND(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$I19="","",'2 Matériel'!$I19)),"")</f>
         <v/>
       </c>
       <c r="L15">
-        <f>IF(C15="ITM",IF(AND(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J19="","",'2 Matériel'!$J19)),"")</f>
+        <f>IF(C15="ITM",IF(AND(AND('2 Matériel'!$K19="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$J19="","",'2 Matériel'!$J19)),"")</f>
         <v/>
       </c>
     </row>
@@ -6917,7 +6987,7 @@
         <v/>
       </c>
       <c r="E16">
-        <f>IF(C16="BAN",UPPER('2 Matériel'!$C20),IF(C16="ITM",'2 Matériel'!$C20&amp;IF(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <f>IF(C16="BAN",UPPER('2 Matériel'!$C20),IF(C16="ITM",'2 Matériel'!$C20&amp;IF(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$59,MATCH("incl_long",Textes!$A$2:$A$59,0),Listes!$H$1),""),""))</f>
         <v/>
       </c>
       <c r="F16">
@@ -6925,27 +6995,27 @@
         <v/>
       </c>
       <c r="G16">
-        <f>IF(C16="ITM",IF(AND(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E20="","",'2 Matériel'!$E20)),"")</f>
+        <f>IF(C16="ITM",IF(AND(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$E20="","",'2 Matériel'!$E20)),"")</f>
         <v/>
       </c>
       <c r="H16">
-        <f>IF(C16="ITM",IF(AND(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F20="","",'2 Matériel'!$F20)),"")</f>
+        <f>IF(C16="ITM",IF(AND(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$F20="","",'2 Matériel'!$F20)),"")</f>
         <v/>
       </c>
       <c r="I16">
-        <f>IF(C16="ITM",IF(AND(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G20="","",'2 Matériel'!$G20)),"")</f>
+        <f>IF(C16="ITM",IF(AND(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$G20="","",'2 Matériel'!$G20)),"")</f>
         <v/>
       </c>
       <c r="J16">
-        <f>IF(C16="ITM",IF(AND(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H20="","",'2 Matériel'!$H20)),"")</f>
+        <f>IF(C16="ITM",IF(AND(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$H20="","",'2 Matériel'!$H20)),"")</f>
         <v/>
       </c>
       <c r="K16">
-        <f>IF(C16="ITM",IF(AND(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I20="","",'2 Matériel'!$I20)),"")</f>
+        <f>IF(C16="ITM",IF(AND(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$I20="","",'2 Matériel'!$I20)),"")</f>
         <v/>
       </c>
       <c r="L16">
-        <f>IF(C16="ITM",IF(AND(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J20="","",'2 Matériel'!$J20)),"")</f>
+        <f>IF(C16="ITM",IF(AND(AND('2 Matériel'!$K20="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$J20="","",'2 Matériel'!$J20)),"")</f>
         <v/>
       </c>
     </row>
@@ -6967,7 +7037,7 @@
         <v/>
       </c>
       <c r="E17">
-        <f>IF(C17="BAN",UPPER('2 Matériel'!$C21),IF(C17="ITM",'2 Matériel'!$C21&amp;IF(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <f>IF(C17="BAN",UPPER('2 Matériel'!$C21),IF(C17="ITM",'2 Matériel'!$C21&amp;IF(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$59,MATCH("incl_long",Textes!$A$2:$A$59,0),Listes!$H$1),""),""))</f>
         <v/>
       </c>
       <c r="F17">
@@ -6975,27 +7045,27 @@
         <v/>
       </c>
       <c r="G17">
-        <f>IF(C17="ITM",IF(AND(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E21="","",'2 Matériel'!$E21)),"")</f>
+        <f>IF(C17="ITM",IF(AND(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$E21="","",'2 Matériel'!$E21)),"")</f>
         <v/>
       </c>
       <c r="H17">
-        <f>IF(C17="ITM",IF(AND(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F21="","",'2 Matériel'!$F21)),"")</f>
+        <f>IF(C17="ITM",IF(AND(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$F21="","",'2 Matériel'!$F21)),"")</f>
         <v/>
       </c>
       <c r="I17">
-        <f>IF(C17="ITM",IF(AND(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G21="","",'2 Matériel'!$G21)),"")</f>
+        <f>IF(C17="ITM",IF(AND(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$G21="","",'2 Matériel'!$G21)),"")</f>
         <v/>
       </c>
       <c r="J17">
-        <f>IF(C17="ITM",IF(AND(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H21="","",'2 Matériel'!$H21)),"")</f>
+        <f>IF(C17="ITM",IF(AND(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$H21="","",'2 Matériel'!$H21)),"")</f>
         <v/>
       </c>
       <c r="K17">
-        <f>IF(C17="ITM",IF(AND(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I21="","",'2 Matériel'!$I21)),"")</f>
+        <f>IF(C17="ITM",IF(AND(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$I21="","",'2 Matériel'!$I21)),"")</f>
         <v/>
       </c>
       <c r="L17">
-        <f>IF(C17="ITM",IF(AND(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J21="","",'2 Matériel'!$J21)),"")</f>
+        <f>IF(C17="ITM",IF(AND(AND('2 Matériel'!$K21="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$J21="","",'2 Matériel'!$J21)),"")</f>
         <v/>
       </c>
     </row>
@@ -7017,7 +7087,7 @@
         <v/>
       </c>
       <c r="E18">
-        <f>IF(C18="BAN",UPPER('2 Matériel'!$C22),IF(C18="ITM",'2 Matériel'!$C22&amp;IF(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <f>IF(C18="BAN",UPPER('2 Matériel'!$C22),IF(C18="ITM",'2 Matériel'!$C22&amp;IF(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$59,MATCH("incl_long",Textes!$A$2:$A$59,0),Listes!$H$1),""),""))</f>
         <v/>
       </c>
       <c r="F18">
@@ -7025,27 +7095,27 @@
         <v/>
       </c>
       <c r="G18">
-        <f>IF(C18="ITM",IF(AND(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E22="","",'2 Matériel'!$E22)),"")</f>
+        <f>IF(C18="ITM",IF(AND(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$E22="","",'2 Matériel'!$E22)),"")</f>
         <v/>
       </c>
       <c r="H18">
-        <f>IF(C18="ITM",IF(AND(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F22="","",'2 Matériel'!$F22)),"")</f>
+        <f>IF(C18="ITM",IF(AND(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$F22="","",'2 Matériel'!$F22)),"")</f>
         <v/>
       </c>
       <c r="I18">
-        <f>IF(C18="ITM",IF(AND(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G22="","",'2 Matériel'!$G22)),"")</f>
+        <f>IF(C18="ITM",IF(AND(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$G22="","",'2 Matériel'!$G22)),"")</f>
         <v/>
       </c>
       <c r="J18">
-        <f>IF(C18="ITM",IF(AND(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H22="","",'2 Matériel'!$H22)),"")</f>
+        <f>IF(C18="ITM",IF(AND(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$H22="","",'2 Matériel'!$H22)),"")</f>
         <v/>
       </c>
       <c r="K18">
-        <f>IF(C18="ITM",IF(AND(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I22="","",'2 Matériel'!$I22)),"")</f>
+        <f>IF(C18="ITM",IF(AND(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$I22="","",'2 Matériel'!$I22)),"")</f>
         <v/>
       </c>
       <c r="L18">
-        <f>IF(C18="ITM",IF(AND(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J22="","",'2 Matériel'!$J22)),"")</f>
+        <f>IF(C18="ITM",IF(AND(AND('2 Matériel'!$K22="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$J22="","",'2 Matériel'!$J22)),"")</f>
         <v/>
       </c>
     </row>
@@ -7067,7 +7137,7 @@
         <v/>
       </c>
       <c r="E19">
-        <f>IF(C19="BAN",UPPER('2 Matériel'!$C23),IF(C19="ITM",'2 Matériel'!$C23&amp;IF(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <f>IF(C19="BAN",UPPER('2 Matériel'!$C23),IF(C19="ITM",'2 Matériel'!$C23&amp;IF(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$59,MATCH("incl_long",Textes!$A$2:$A$59,0),Listes!$H$1),""),""))</f>
         <v/>
       </c>
       <c r="F19">
@@ -7075,27 +7145,27 @@
         <v/>
       </c>
       <c r="G19">
-        <f>IF(C19="ITM",IF(AND(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E23="","",'2 Matériel'!$E23)),"")</f>
+        <f>IF(C19="ITM",IF(AND(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$E23="","",'2 Matériel'!$E23)),"")</f>
         <v/>
       </c>
       <c r="H19">
-        <f>IF(C19="ITM",IF(AND(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F23="","",'2 Matériel'!$F23)),"")</f>
+        <f>IF(C19="ITM",IF(AND(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$F23="","",'2 Matériel'!$F23)),"")</f>
         <v/>
       </c>
       <c r="I19">
-        <f>IF(C19="ITM",IF(AND(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G23="","",'2 Matériel'!$G23)),"")</f>
+        <f>IF(C19="ITM",IF(AND(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$G23="","",'2 Matériel'!$G23)),"")</f>
         <v/>
       </c>
       <c r="J19">
-        <f>IF(C19="ITM",IF(AND(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H23="","",'2 Matériel'!$H23)),"")</f>
+        <f>IF(C19="ITM",IF(AND(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$H23="","",'2 Matériel'!$H23)),"")</f>
         <v/>
       </c>
       <c r="K19">
-        <f>IF(C19="ITM",IF(AND(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I23="","",'2 Matériel'!$I23)),"")</f>
+        <f>IF(C19="ITM",IF(AND(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$I23="","",'2 Matériel'!$I23)),"")</f>
         <v/>
       </c>
       <c r="L19">
-        <f>IF(C19="ITM",IF(AND(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J23="","",'2 Matériel'!$J23)),"")</f>
+        <f>IF(C19="ITM",IF(AND(AND('2 Matériel'!$K23="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$J23="","",'2 Matériel'!$J23)),"")</f>
         <v/>
       </c>
     </row>
@@ -7117,7 +7187,7 @@
         <v/>
       </c>
       <c r="E20">
-        <f>IF(C20="BAN",UPPER('2 Matériel'!$C24),IF(C20="ITM",'2 Matériel'!$C24&amp;IF(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <f>IF(C20="BAN",UPPER('2 Matériel'!$C24),IF(C20="ITM",'2 Matériel'!$C24&amp;IF(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$59,MATCH("incl_long",Textes!$A$2:$A$59,0),Listes!$H$1),""),""))</f>
         <v/>
       </c>
       <c r="F20">
@@ -7125,27 +7195,27 @@
         <v/>
       </c>
       <c r="G20">
-        <f>IF(C20="ITM",IF(AND(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E24="","",'2 Matériel'!$E24)),"")</f>
+        <f>IF(C20="ITM",IF(AND(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$E24="","",'2 Matériel'!$E24)),"")</f>
         <v/>
       </c>
       <c r="H20">
-        <f>IF(C20="ITM",IF(AND(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F24="","",'2 Matériel'!$F24)),"")</f>
+        <f>IF(C20="ITM",IF(AND(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$F24="","",'2 Matériel'!$F24)),"")</f>
         <v/>
       </c>
       <c r="I20">
-        <f>IF(C20="ITM",IF(AND(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G24="","",'2 Matériel'!$G24)),"")</f>
+        <f>IF(C20="ITM",IF(AND(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$G24="","",'2 Matériel'!$G24)),"")</f>
         <v/>
       </c>
       <c r="J20">
-        <f>IF(C20="ITM",IF(AND(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H24="","",'2 Matériel'!$H24)),"")</f>
+        <f>IF(C20="ITM",IF(AND(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$H24="","",'2 Matériel'!$H24)),"")</f>
         <v/>
       </c>
       <c r="K20">
-        <f>IF(C20="ITM",IF(AND(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I24="","",'2 Matériel'!$I24)),"")</f>
+        <f>IF(C20="ITM",IF(AND(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$I24="","",'2 Matériel'!$I24)),"")</f>
         <v/>
       </c>
       <c r="L20">
-        <f>IF(C20="ITM",IF(AND(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J24="","",'2 Matériel'!$J24)),"")</f>
+        <f>IF(C20="ITM",IF(AND(AND('2 Matériel'!$K24="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$J24="","",'2 Matériel'!$J24)),"")</f>
         <v/>
       </c>
     </row>
@@ -7167,7 +7237,7 @@
         <v/>
       </c>
       <c r="E21">
-        <f>IF(C21="BAN",UPPER('2 Matériel'!$C25),IF(C21="ITM",'2 Matériel'!$C25&amp;IF(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <f>IF(C21="BAN",UPPER('2 Matériel'!$C25),IF(C21="ITM",'2 Matériel'!$C25&amp;IF(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$59,MATCH("incl_long",Textes!$A$2:$A$59,0),Listes!$H$1),""),""))</f>
         <v/>
       </c>
       <c r="F21">
@@ -7175,27 +7245,27 @@
         <v/>
       </c>
       <c r="G21">
-        <f>IF(C21="ITM",IF(AND(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E25="","",'2 Matériel'!$E25)),"")</f>
+        <f>IF(C21="ITM",IF(AND(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$E25="","",'2 Matériel'!$E25)),"")</f>
         <v/>
       </c>
       <c r="H21">
-        <f>IF(C21="ITM",IF(AND(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F25="","",'2 Matériel'!$F25)),"")</f>
+        <f>IF(C21="ITM",IF(AND(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$F25="","",'2 Matériel'!$F25)),"")</f>
         <v/>
       </c>
       <c r="I21">
-        <f>IF(C21="ITM",IF(AND(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G25="","",'2 Matériel'!$G25)),"")</f>
+        <f>IF(C21="ITM",IF(AND(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$G25="","",'2 Matériel'!$G25)),"")</f>
         <v/>
       </c>
       <c r="J21">
-        <f>IF(C21="ITM",IF(AND(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H25="","",'2 Matériel'!$H25)),"")</f>
+        <f>IF(C21="ITM",IF(AND(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$H25="","",'2 Matériel'!$H25)),"")</f>
         <v/>
       </c>
       <c r="K21">
-        <f>IF(C21="ITM",IF(AND(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I25="","",'2 Matériel'!$I25)),"")</f>
+        <f>IF(C21="ITM",IF(AND(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$I25="","",'2 Matériel'!$I25)),"")</f>
         <v/>
       </c>
       <c r="L21">
-        <f>IF(C21="ITM",IF(AND(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J25="","",'2 Matériel'!$J25)),"")</f>
+        <f>IF(C21="ITM",IF(AND(AND('2 Matériel'!$K25="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$J25="","",'2 Matériel'!$J25)),"")</f>
         <v/>
       </c>
     </row>
@@ -7217,7 +7287,7 @@
         <v/>
       </c>
       <c r="E22">
-        <f>IF(C22="BAN",UPPER('2 Matériel'!$C26),IF(C22="ITM",'2 Matériel'!$C26&amp;IF(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <f>IF(C22="BAN",UPPER('2 Matériel'!$C26),IF(C22="ITM",'2 Matériel'!$C26&amp;IF(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$59,MATCH("incl_long",Textes!$A$2:$A$59,0),Listes!$H$1),""),""))</f>
         <v/>
       </c>
       <c r="F22">
@@ -7225,27 +7295,27 @@
         <v/>
       </c>
       <c r="G22">
-        <f>IF(C22="ITM",IF(AND(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E26="","",'2 Matériel'!$E26)),"")</f>
+        <f>IF(C22="ITM",IF(AND(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$E26="","",'2 Matériel'!$E26)),"")</f>
         <v/>
       </c>
       <c r="H22">
-        <f>IF(C22="ITM",IF(AND(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F26="","",'2 Matériel'!$F26)),"")</f>
+        <f>IF(C22="ITM",IF(AND(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$F26="","",'2 Matériel'!$F26)),"")</f>
         <v/>
       </c>
       <c r="I22">
-        <f>IF(C22="ITM",IF(AND(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G26="","",'2 Matériel'!$G26)),"")</f>
+        <f>IF(C22="ITM",IF(AND(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$G26="","",'2 Matériel'!$G26)),"")</f>
         <v/>
       </c>
       <c r="J22">
-        <f>IF(C22="ITM",IF(AND(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H26="","",'2 Matériel'!$H26)),"")</f>
+        <f>IF(C22="ITM",IF(AND(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$H26="","",'2 Matériel'!$H26)),"")</f>
         <v/>
       </c>
       <c r="K22">
-        <f>IF(C22="ITM",IF(AND(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I26="","",'2 Matériel'!$I26)),"")</f>
+        <f>IF(C22="ITM",IF(AND(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$I26="","",'2 Matériel'!$I26)),"")</f>
         <v/>
       </c>
       <c r="L22">
-        <f>IF(C22="ITM",IF(AND(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J26="","",'2 Matériel'!$J26)),"")</f>
+        <f>IF(C22="ITM",IF(AND(AND('2 Matériel'!$K26="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$J26="","",'2 Matériel'!$J26)),"")</f>
         <v/>
       </c>
     </row>
@@ -7267,7 +7337,7 @@
         <v/>
       </c>
       <c r="E23">
-        <f>IF(C23="BAN",UPPER('2 Matériel'!$C27),IF(C23="ITM",'2 Matériel'!$C27&amp;IF(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <f>IF(C23="BAN",UPPER('2 Matériel'!$C27),IF(C23="ITM",'2 Matériel'!$C27&amp;IF(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$59,MATCH("incl_long",Textes!$A$2:$A$59,0),Listes!$H$1),""),""))</f>
         <v/>
       </c>
       <c r="F23">
@@ -7275,27 +7345,27 @@
         <v/>
       </c>
       <c r="G23">
-        <f>IF(C23="ITM",IF(AND(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E27="","",'2 Matériel'!$E27)),"")</f>
+        <f>IF(C23="ITM",IF(AND(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$E27="","",'2 Matériel'!$E27)),"")</f>
         <v/>
       </c>
       <c r="H23">
-        <f>IF(C23="ITM",IF(AND(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F27="","",'2 Matériel'!$F27)),"")</f>
+        <f>IF(C23="ITM",IF(AND(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$F27="","",'2 Matériel'!$F27)),"")</f>
         <v/>
       </c>
       <c r="I23">
-        <f>IF(C23="ITM",IF(AND(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G27="","",'2 Matériel'!$G27)),"")</f>
+        <f>IF(C23="ITM",IF(AND(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$G27="","",'2 Matériel'!$G27)),"")</f>
         <v/>
       </c>
       <c r="J23">
-        <f>IF(C23="ITM",IF(AND(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H27="","",'2 Matériel'!$H27)),"")</f>
+        <f>IF(C23="ITM",IF(AND(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$H27="","",'2 Matériel'!$H27)),"")</f>
         <v/>
       </c>
       <c r="K23">
-        <f>IF(C23="ITM",IF(AND(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I27="","",'2 Matériel'!$I27)),"")</f>
+        <f>IF(C23="ITM",IF(AND(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$I27="","",'2 Matériel'!$I27)),"")</f>
         <v/>
       </c>
       <c r="L23">
-        <f>IF(C23="ITM",IF(AND(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J27="","",'2 Matériel'!$J27)),"")</f>
+        <f>IF(C23="ITM",IF(AND(AND('2 Matériel'!$K27="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$J27="","",'2 Matériel'!$J27)),"")</f>
         <v/>
       </c>
     </row>
@@ -7317,7 +7387,7 @@
         <v/>
       </c>
       <c r="E24">
-        <f>IF(C24="BAN",UPPER('2 Matériel'!$C28),IF(C24="ITM",'2 Matériel'!$C28&amp;IF(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <f>IF(C24="BAN",UPPER('2 Matériel'!$C28),IF(C24="ITM",'2 Matériel'!$C28&amp;IF(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$59,MATCH("incl_long",Textes!$A$2:$A$59,0),Listes!$H$1),""),""))</f>
         <v/>
       </c>
       <c r="F24">
@@ -7325,27 +7395,27 @@
         <v/>
       </c>
       <c r="G24">
-        <f>IF(C24="ITM",IF(AND(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E28="","",'2 Matériel'!$E28)),"")</f>
+        <f>IF(C24="ITM",IF(AND(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$E28="","",'2 Matériel'!$E28)),"")</f>
         <v/>
       </c>
       <c r="H24">
-        <f>IF(C24="ITM",IF(AND(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F28="","",'2 Matériel'!$F28)),"")</f>
+        <f>IF(C24="ITM",IF(AND(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$F28="","",'2 Matériel'!$F28)),"")</f>
         <v/>
       </c>
       <c r="I24">
-        <f>IF(C24="ITM",IF(AND(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G28="","",'2 Matériel'!$G28)),"")</f>
+        <f>IF(C24="ITM",IF(AND(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$G28="","",'2 Matériel'!$G28)),"")</f>
         <v/>
       </c>
       <c r="J24">
-        <f>IF(C24="ITM",IF(AND(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H28="","",'2 Matériel'!$H28)),"")</f>
+        <f>IF(C24="ITM",IF(AND(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$H28="","",'2 Matériel'!$H28)),"")</f>
         <v/>
       </c>
       <c r="K24">
-        <f>IF(C24="ITM",IF(AND(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I28="","",'2 Matériel'!$I28)),"")</f>
+        <f>IF(C24="ITM",IF(AND(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$I28="","",'2 Matériel'!$I28)),"")</f>
         <v/>
       </c>
       <c r="L24">
-        <f>IF(C24="ITM",IF(AND(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J28="","",'2 Matériel'!$J28)),"")</f>
+        <f>IF(C24="ITM",IF(AND(AND('2 Matériel'!$K28="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$J28="","",'2 Matériel'!$J28)),"")</f>
         <v/>
       </c>
     </row>
@@ -7367,7 +7437,7 @@
         <v/>
       </c>
       <c r="E25">
-        <f>IF(C25="BAN",UPPER('2 Matériel'!$C29),IF(C25="ITM",'2 Matériel'!$C29&amp;IF(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),""),""))</f>
+        <f>IF(C25="BAN",UPPER('2 Matériel'!$C29),IF(C25="ITM",'2 Matériel'!$C29&amp;IF(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$59,MATCH("incl_long",Textes!$A$2:$A$59,0),Listes!$H$1),""),""))</f>
         <v/>
       </c>
       <c r="F25">
@@ -7375,27 +7445,27 @@
         <v/>
       </c>
       <c r="G25">
-        <f>IF(C25="ITM",IF(AND(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$E29="","",'2 Matériel'!$E29)),"")</f>
+        <f>IF(C25="ITM",IF(AND(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$E29="","",'2 Matériel'!$E29)),"")</f>
         <v/>
       </c>
       <c r="H25">
-        <f>IF(C25="ITM",IF(AND(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$F29="","",'2 Matériel'!$F29)),"")</f>
+        <f>IF(C25="ITM",IF(AND(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$F29="","",'2 Matériel'!$F29)),"")</f>
         <v/>
       </c>
       <c r="I25">
-        <f>IF(C25="ITM",IF(AND(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$G29="","",'2 Matériel'!$G29)),"")</f>
+        <f>IF(C25="ITM",IF(AND(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$G29="","",'2 Matériel'!$G29)),"")</f>
         <v/>
       </c>
       <c r="J25">
-        <f>IF(C25="ITM",IF(AND(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$H29="","",'2 Matériel'!$H29)),"")</f>
+        <f>IF(C25="ITM",IF(AND(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$H29="","",'2 Matériel'!$H29)),"")</f>
         <v/>
       </c>
       <c r="K25">
-        <f>IF(C25="ITM",IF(AND(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$I29="","",'2 Matériel'!$I29)),"")</f>
+        <f>IF(C25="ITM",IF(AND(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$I29="","",'2 Matériel'!$I29)),"")</f>
         <v/>
       </c>
       <c r="L25">
-        <f>IF(C25="ITM",IF(AND(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('2 Matériel'!$J29="","",'2 Matériel'!$J29)),"")</f>
+        <f>IF(C25="ITM",IF(AND(AND('2 Matériel'!$K29="Oui",'3 Options'!$C$13="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('2 Matériel'!$J29="","",'2 Matériel'!$J29)),"")</f>
         <v/>
       </c>
     </row>
@@ -7417,23 +7487,23 @@
         <v/>
       </c>
       <c r="E26">
-        <f>INDEX(Textes!$B$2:$C$55,MATCH("sec_tight",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$59,MATCH("sec_tight",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="F26">
-        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_qty",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$59,MATCH("h_qty",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="G26">
-        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_unit",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$59,MATCH("h_unit",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="H26">
-        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_pu",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$59,MATCH("h_pu",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="I26">
-        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_tot",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$59,MATCH("h_tot",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="J26">
@@ -7467,7 +7537,7 @@
         <v/>
       </c>
       <c r="E27">
-        <f>IF('3 Options'!$D$8&lt;&gt;"",'3 Options'!$D$8,INDEX(Textes!$B$2:$C$55,MATCH("tight",Textes!$A$2:$A$55,0),Listes!$H$1))&amp;IF(AND('3 Options'!$C$13="Oui",'3 Options'!$C$19="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
+        <f>IF('3 Options'!$D$8&lt;&gt;"",'3 Options'!$D$8,INDEX(Textes!$B$2:$C$59,MATCH("tight",Textes!$A$2:$A$59,0),Listes!$H$1))&amp;IF(AND('3 Options'!$C$13="Oui",'3 Options'!$C$19="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$59,MATCH("incl_long",Textes!$A$2:$A$59,0),Listes!$H$1),"")</f>
         <v/>
       </c>
       <c r="F27">
@@ -7479,11 +7549,11 @@
         <v/>
       </c>
       <c r="H27">
-        <f>IF(AND(AND('3 Options'!$C$13="Oui",'3 Options'!$C$19="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$G$8="Coût réel +15 %",INDEX(Textes!$B$2:$C$55,MATCH("at_cost",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$F$8="","",'3 Options'!$F$8)))</f>
+        <f>IF(AND(AND('3 Options'!$C$13="Oui",'3 Options'!$C$19="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('3 Options'!$G$8="Coût réel +15 %",INDEX(Textes!$B$2:$C$59,MATCH("at_cost",Textes!$A$2:$A$59,0),Listes!$H$1),IF('3 Options'!$F$8="","",'3 Options'!$F$8)))</f>
         <v/>
       </c>
       <c r="I27">
-        <f>IF(AND(AND('3 Options'!$C$13="Oui",'3 Options'!$C$19="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$G$8="Coût réel +15 %","—",'3 Options'!$H$8))</f>
+        <f>IF(AND(AND('3 Options'!$C$13="Oui",'3 Options'!$C$19="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('3 Options'!$G$8="Coût réel +15 %","—",'3 Options'!$H$8))</f>
         <v/>
       </c>
       <c r="J27">
@@ -7517,23 +7587,23 @@
         <v/>
       </c>
       <c r="E28">
-        <f>INDEX(Textes!$B$2:$C$55,MATCH("sec_tr",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$59,MATCH("sec_tr",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="F28">
-        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_qty",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$59,MATCH("h_qty",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="G28">
-        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_unit",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$59,MATCH("h_unit",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="H28">
-        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_pu",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$59,MATCH("h_pu",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="I28">
-        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_tot",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$59,MATCH("h_tot",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="J28">
@@ -7567,7 +7637,7 @@
         <v/>
       </c>
       <c r="E29">
-        <f>IF('3 Options'!$D$9&lt;&gt;"",'3 Options'!$D$9,INDEX(Textes!$B$2:$C$55,MATCH("tr_mob",Textes!$A$2:$A$55,0),Listes!$H$1))&amp;IF(AND('3 Options'!$C$13="Oui",'3 Options'!$C$20="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
+        <f>IF('3 Options'!$D$9&lt;&gt;"",'3 Options'!$D$9,INDEX(Textes!$B$2:$C$59,MATCH("tr_mob",Textes!$A$2:$A$59,0),Listes!$H$1))&amp;IF(AND('3 Options'!$C$13="Oui",'3 Options'!$C$20="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$59,MATCH("incl_long",Textes!$A$2:$A$59,0),Listes!$H$1),"")</f>
         <v/>
       </c>
       <c r="F29">
@@ -7579,11 +7649,11 @@
         <v/>
       </c>
       <c r="H29">
-        <f>IF(AND(AND('3 Options'!$C$13="Oui",'3 Options'!$C$20="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$G$9="Coût réel +15 %",INDEX(Textes!$B$2:$C$55,MATCH("at_cost",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$F$9="","",'3 Options'!$F$9)))</f>
+        <f>IF(AND(AND('3 Options'!$C$13="Oui",'3 Options'!$C$20="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('3 Options'!$G$9="Coût réel +15 %",INDEX(Textes!$B$2:$C$59,MATCH("at_cost",Textes!$A$2:$A$59,0),Listes!$H$1),IF('3 Options'!$F$9="","",'3 Options'!$F$9)))</f>
         <v/>
       </c>
       <c r="I29">
-        <f>IF(AND(AND('3 Options'!$C$13="Oui",'3 Options'!$C$20="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$G$9="Coût réel +15 %","—",'3 Options'!$H$9))</f>
+        <f>IF(AND(AND('3 Options'!$C$13="Oui",'3 Options'!$C$20="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('3 Options'!$G$9="Coût réel +15 %","—",'3 Options'!$H$9))</f>
         <v/>
       </c>
       <c r="J29">
@@ -7617,7 +7687,7 @@
         <v/>
       </c>
       <c r="E30">
-        <f>IF('3 Options'!$D$10&lt;&gt;"",'3 Options'!$D$10,INDEX(Textes!$B$2:$C$55,MATCH("tr_dem",Textes!$A$2:$A$55,0),Listes!$H$1))&amp;IF(AND('3 Options'!$C$13="Oui",'3 Options'!$C$20="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
+        <f>IF('3 Options'!$D$10&lt;&gt;"",'3 Options'!$D$10,INDEX(Textes!$B$2:$C$59,MATCH("tr_dem",Textes!$A$2:$A$59,0),Listes!$H$1))&amp;IF(AND('3 Options'!$C$13="Oui",'3 Options'!$C$20="Oui"),"  ·  "&amp;INDEX(Textes!$B$2:$C$59,MATCH("incl_long",Textes!$A$2:$A$59,0),Listes!$H$1),"")</f>
         <v/>
       </c>
       <c r="F30">
@@ -7629,11 +7699,11 @@
         <v/>
       </c>
       <c r="H30">
-        <f>IF(AND(AND('3 Options'!$C$13="Oui",'3 Options'!$C$20="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$G$10="Coût réel +15 %",INDEX(Textes!$B$2:$C$55,MATCH("at_cost",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$F$10="","",'3 Options'!$F$10)))</f>
+        <f>IF(AND(AND('3 Options'!$C$13="Oui",'3 Options'!$C$20="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('3 Options'!$G$10="Coût réel +15 %",INDEX(Textes!$B$2:$C$59,MATCH("at_cost",Textes!$A$2:$A$59,0),Listes!$H$1),IF('3 Options'!$F$10="","",'3 Options'!$F$10)))</f>
         <v/>
       </c>
       <c r="I30">
-        <f>IF(AND(AND('3 Options'!$C$13="Oui",'3 Options'!$C$20="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$G$10="Coût réel +15 %","—",'3 Options'!$H$10))</f>
+        <f>IF(AND(AND('3 Options'!$C$13="Oui",'3 Options'!$C$20="Oui"),'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('3 Options'!$G$10="Coût réel +15 %","—",'3 Options'!$H$10))</f>
         <v/>
       </c>
       <c r="J30">
@@ -7667,23 +7737,23 @@
         <v/>
       </c>
       <c r="E31">
-        <f>INDEX(Textes!$B$2:$C$55,MATCH("sec_op",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$59,MATCH("sec_op",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="F31">
-        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_qty",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$59,MATCH("h_qty",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="G31">
-        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_unit",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$59,MATCH("h_unit",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="H31">
-        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_pu",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$59,MATCH("h_pu",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="I31">
-        <f>INDEX(Textes!$B$2:$C$55,MATCH("h_tot",Textes!$A$2:$A$55,0),Listes!$H$1)</f>
+        <f>INDEX(Textes!$B$2:$C$59,MATCH("h_tot",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
       <c r="J31">
@@ -7717,7 +7787,7 @@
         <v/>
       </c>
       <c r="E32">
-        <f>IF('3 Options'!$D$6&lt;&gt;"",'3 Options'!$D$6,INDEX(Textes!$B$2:$C$55,MATCH("op_day",Textes!$A$2:$A$55,0),Listes!$H$1))&amp;IF(FALSE,"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
+        <f>IF('3 Options'!$D$6&lt;&gt;"",'3 Options'!$D$6,INDEX(Textes!$B$2:$C$59,MATCH("op_day",Textes!$A$2:$A$59,0),Listes!$H$1))&amp;IF(FALSE,"  ·  "&amp;INDEX(Textes!$B$2:$C$59,MATCH("incl_long",Textes!$A$2:$A$59,0),Listes!$H$1),"")</f>
         <v/>
       </c>
       <c r="F32">
@@ -7729,11 +7799,11 @@
         <v/>
       </c>
       <c r="H32">
-        <f>IF(AND(FALSE,'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$G$6="Coût réel +15 %",INDEX(Textes!$B$2:$C$55,MATCH("at_cost",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$F$6="","",'3 Options'!$F$6)))</f>
+        <f>IF(AND(FALSE,'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('3 Options'!$G$6="Coût réel +15 %",INDEX(Textes!$B$2:$C$59,MATCH("at_cost",Textes!$A$2:$A$59,0),Listes!$H$1),IF('3 Options'!$F$6="","",'3 Options'!$F$6)))</f>
         <v/>
       </c>
       <c r="I32">
-        <f>IF(AND(FALSE,'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$G$6="Coût réel +15 %","—",'3 Options'!$H$6))</f>
+        <f>IF(AND(FALSE,'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('3 Options'!$G$6="Coût réel +15 %","—",'3 Options'!$H$6))</f>
         <v/>
       </c>
       <c r="J32">
@@ -7767,7 +7837,7 @@
         <v/>
       </c>
       <c r="E33">
-        <f>IF('3 Options'!$D$7&lt;&gt;"",'3 Options'!$D$7,INDEX(Textes!$B$2:$C$55,MATCH("op_mob",Textes!$A$2:$A$55,0),Listes!$H$1))&amp;IF(FALSE,"  ·  "&amp;INDEX(Textes!$B$2:$C$55,MATCH("incl_long",Textes!$A$2:$A$55,0),Listes!$H$1),"")</f>
+        <f>IF('3 Options'!$D$7&lt;&gt;"",'3 Options'!$D$7,INDEX(Textes!$B$2:$C$59,MATCH("op_mob",Textes!$A$2:$A$59,0),Listes!$H$1))&amp;IF(FALSE,"  ·  "&amp;INDEX(Textes!$B$2:$C$59,MATCH("incl_long",Textes!$A$2:$A$59,0),Listes!$H$1),"")</f>
         <v/>
       </c>
       <c r="F33">
@@ -7779,11 +7849,11 @@
         <v/>
       </c>
       <c r="H33">
-        <f>IF(AND(FALSE,'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$G$7="Coût réel +15 %",INDEX(Textes!$B$2:$C$55,MATCH("at_cost",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$F$7="","",'3 Options'!$F$7)))</f>
+        <f>IF(AND(FALSE,'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('3 Options'!$G$7="Coût réel +15 %",INDEX(Textes!$B$2:$C$59,MATCH("at_cost",Textes!$A$2:$A$59,0),Listes!$H$1),IF('3 Options'!$F$7="","",'3 Options'!$F$7)))</f>
         <v/>
       </c>
       <c r="I33">
-        <f>IF(AND(FALSE,'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$55,MATCH("incl",Textes!$A$2:$A$55,0),Listes!$H$1),IF('3 Options'!$G$7="Coût réel +15 %","—",'3 Options'!$H$7))</f>
+        <f>IF(AND(FALSE,'3 Options'!$C$18&lt;&gt;"Oui"),INDEX(Textes!$B$2:$C$59,MATCH("incl",Textes!$A$2:$A$59,0),Listes!$H$1),IF('3 Options'!$G$7="Coût réel +15 %","—",'3 Options'!$H$7))</f>
         <v/>
       </c>
       <c r="J33">
@@ -7817,7 +7887,7 @@
         <v/>
       </c>
       <c r="E34">
-        <f>UPPER(INDEX(Textes!$B$2:$C$55,MATCH("forfait",Textes!$A$2:$A$55,0),Listes!$H$1))&amp;IF('3 Options'!$D$13&lt;&gt;"","   ·   "&amp;'3 Options'!$D$13,"")</f>
+        <f>UPPER(INDEX(Textes!$B$2:$C$59,MATCH("forfait",Textes!$A$2:$A$59,0),Listes!$H$1))&amp;IF(IF('3 Options'!$G$13="Forfait calculé (S + O + UC)",'3 Options'!$C$15+'3 Options'!$C$16,IF('3 Options'!$G$13="Forfait par jour",'3 Options'!$E$13,""))&lt;&gt;"","  "&amp;IF('3 Options'!$G$13="Forfait calculé (S + O + UC)",'3 Options'!$C$15+'3 Options'!$C$16,IF('3 Options'!$G$13="Forfait par jour",'3 Options'!$E$13,""))&amp;" "&amp;INDEX(Textes!$B$2:$C$59,MATCH("days",Textes!$A$2:$A$59,0),Listes!$H$1),"")&amp;IF('3 Options'!$D$13&lt;&gt;"","   ·   "&amp;'3 Options'!$D$13,"")</f>
         <v/>
       </c>
       <c r="F34">
@@ -7851,7 +7921,7 @@
     </row>
     <row r="35">
       <c r="A35">
-        <f>IF(AND('3 Options'!$C$13="Oui",OR('3 Options'!$D$14&lt;&gt;"",'3 Options'!$G$13="Forfait par jour")),1,0)</f>
+        <f>IF(AND('3 Options'!$C$13="Oui",E35&lt;&gt;""),1,0)</f>
         <v/>
       </c>
       <c r="B35">
@@ -7867,7 +7937,7 @@
         <v/>
       </c>
       <c r="E35">
-        <f>IF('3 Options'!$G$13="Forfait par jour",'3 Options'!$E$13&amp;" j × "&amp;TEXT('3 Options'!$F$13,"#,##0.00")&amp;" €/j"&amp;IF('3 Options'!$D$14&lt;&gt;"","   ·   "&amp;'3 Options'!$D$14,""),'3 Options'!$D$14)</f>
+        <f>IF(AND(AND('3 Options'!$C$8="Oui",'3 Options'!$C$19="Oui"),AND(OR('3 Options'!$C$9="Oui",'3 Options'!$C$10="Oui"),'3 Options'!$C$20="Oui")),INDEX(Textes!$B$2:$C$59,MATCH("in_both",Textes!$A$2:$A$59,0),Listes!$H$1),IF(AND('3 Options'!$C$8="Oui",'3 Options'!$C$19="Oui"),INDEX(Textes!$B$2:$C$59,MATCH("in_tight",Textes!$A$2:$A$59,0),Listes!$H$1),IF(AND(OR('3 Options'!$C$9="Oui",'3 Options'!$C$10="Oui"),'3 Options'!$C$20="Oui"),INDEX(Textes!$B$2:$C$59,MATCH("in_tr",Textes!$A$2:$A$59,0),Listes!$H$1),"")))&amp;IF(AND(IF(AND(AND('3 Options'!$C$8="Oui",'3 Options'!$C$19="Oui"),AND(OR('3 Options'!$C$9="Oui",'3 Options'!$C$10="Oui"),'3 Options'!$C$20="Oui")),INDEX(Textes!$B$2:$C$59,MATCH("in_both",Textes!$A$2:$A$59,0),Listes!$H$1),IF(AND('3 Options'!$C$8="Oui",'3 Options'!$C$19="Oui"),INDEX(Textes!$B$2:$C$59,MATCH("in_tight",Textes!$A$2:$A$59,0),Listes!$H$1),IF(AND(OR('3 Options'!$C$9="Oui",'3 Options'!$C$10="Oui"),'3 Options'!$C$20="Oui"),INDEX(Textes!$B$2:$C$59,MATCH("in_tr",Textes!$A$2:$A$59,0),Listes!$H$1),"")))&lt;&gt;"",'3 Options'!$D$14&lt;&gt;""),"   ·   ","")&amp;'3 Options'!$D$14</f>
         <v/>
       </c>
       <c r="F35">

--- a/devis_2027/Devis_Enedril_2027.xlsx
+++ b/devis_2027/Devis_Enedril_2027.xlsx
@@ -16,6 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flux" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4 Devis'!$B$15:$N$55</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'4 Devis'!$A$1:$K$68</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -409,6 +410,9 @@
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
@@ -419,6 +423,7 @@
     <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -430,10 +435,6 @@
     </xf>
     <xf numFmtId="4" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
@@ -2468,19 +2469,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:N68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
     <col width="4.5" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="5.5" customWidth="1" min="4" max="4"/>
-    <col width="10.5" customWidth="1" min="5" max="5"/>
-    <col width="10.5" customWidth="1" min="6" max="6"/>
-    <col width="10.5" customWidth="1" min="7" max="7"/>
-    <col width="12.5" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="9.5" customWidth="1" min="9" max="9"/>
+    <col width="9.5" customWidth="1" min="10" max="10"/>
     <col width="1.5" customWidth="1" min="11" max="11"/>
     <col hidden="1" width="13" customWidth="1" min="12" max="12"/>
     <col hidden="1" width="13" customWidth="1" min="13" max="13"/>
@@ -2656,1921 +2657,2096 @@
       <c r="I12" s="33" t="n"/>
       <c r="J12" s="33" t="n"/>
     </row>
-    <row r="13" ht="8" customHeight="1"/>
+    <row r="13" ht="14" customHeight="1">
+      <c r="B13" s="34">
+        <f>IF(SUBTOTAL(103,B16:B55)&lt;&gt;SUM(N16:N55),"⚠  Appuyer sur Ctrl + Alt + L pour mettre à jour les lignes du devis (matériel ou options modifiés).","")</f>
+        <v/>
+      </c>
+    </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="B14" s="34">
+      <c r="B14" s="35">
         <f>INDEX(Textes!$B$2:$C$59,MATCH("sec_eq",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="C14" s="35" t="n"/>
-      <c r="D14" s="35" t="n"/>
-      <c r="E14" s="35" t="n"/>
-      <c r="F14" s="35" t="n"/>
-      <c r="G14" s="35" t="n"/>
-      <c r="H14" s="35" t="n"/>
-      <c r="I14" s="35" t="n"/>
-      <c r="J14" s="35" t="n"/>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="36" t="n"/>
+      <c r="F14" s="36" t="n"/>
+      <c r="G14" s="36" t="n"/>
+      <c r="H14" s="36" t="n"/>
+      <c r="I14" s="36" t="n"/>
+      <c r="J14" s="36" t="n"/>
     </row>
     <row r="15" ht="46" customHeight="1">
-      <c r="B15" s="36">
+      <c r="B15" s="37">
         <f>INDEX(Textes!$B$2:$C$59,MATCH("h_n",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="C15" s="37">
+      <c r="C15" s="38">
         <f>INDEX(Textes!$B$2:$C$59,MATCH("h_desc",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="D15" s="36">
+      <c r="D15" s="37">
         <f>INDEX(Textes!$B$2:$C$59,MATCH("h_qty",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="E15" s="36">
+      <c r="E15" s="37">
         <f>INDEX(Textes!$B$2:$C$59,MATCH("h_s",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="F15" s="36">
+      <c r="F15" s="37">
         <f>INDEX(Textes!$B$2:$C$59,MATCH("h_o",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="G15" s="36">
+      <c r="G15" s="37">
         <f>INDEX(Textes!$B$2:$C$59,MATCH("h_uc",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="H15" s="36">
+      <c r="H15" s="37">
         <f>INDEX(Textes!$B$2:$C$59,MATCH("h_lih",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="I15" s="36">
+      <c r="I15" s="37">
         <f>INDEX(Textes!$B$2:$C$59,MATCH("h_insp",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="J15" s="36">
+      <c r="J15" s="37">
         <f>INDEX(Textes!$B$2:$C$59,MATCH("h_rest",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
+      <c r="L15" s="39" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="M15" s="39" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="N15" s="39" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="B16" s="38">
-        <f>IF($L16="","",INDEX(Flux!$D$2:$D$35,$L16))</f>
-        <v/>
-      </c>
-      <c r="C16" s="39">
-        <f>IF($L16="","",INDEX(Flux!$E$2:$E$35,$L16))</f>
-        <v/>
-      </c>
-      <c r="D16" s="40">
-        <f>IF($L16="","",INDEX(Flux!$F$2:$F$35,$L16))</f>
-        <v/>
-      </c>
-      <c r="E16" s="41">
-        <f>IF($L16="","",INDEX(Flux!$G$2:$G$35,$L16))</f>
-        <v/>
-      </c>
-      <c r="F16" s="41">
-        <f>IF($L16="","",INDEX(Flux!$H$2:$H$35,$L16))</f>
-        <v/>
-      </c>
-      <c r="G16" s="41">
-        <f>IF($L16="","",INDEX(Flux!$I$2:$I$35,$L16))</f>
-        <v/>
-      </c>
-      <c r="H16" s="41">
-        <f>IF($L16="","",INDEX(Flux!$J$2:$J$35,$L16))</f>
-        <v/>
-      </c>
-      <c r="I16" s="41">
-        <f>IF($L16="","",INDEX(Flux!$K$2:$K$35,$L16))</f>
-        <v/>
-      </c>
-      <c r="J16" s="41">
-        <f>IF($L16="","",INDEX(Flux!$L$2:$L$35,$L16))</f>
-        <v/>
-      </c>
-      <c r="L16" s="42">
-        <f>IFERROR(MATCH(1,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M16" s="42">
-        <f>IF(L16="","",INDEX(Flux!$C$2:$C$35,L16))</f>
+      <c r="B16" s="40">
+        <f>IF($L16=0,"",INDEX(Flux!$D$2:$D$35,$L16))</f>
+        <v/>
+      </c>
+      <c r="C16" s="41">
+        <f>IF($L16=0,"",INDEX(Flux!$E$2:$E$35,$L16))</f>
+        <v/>
+      </c>
+      <c r="D16" s="42">
+        <f>IF($L16=0,"",INDEX(Flux!$F$2:$F$35,$L16))</f>
+        <v/>
+      </c>
+      <c r="E16" s="43">
+        <f>IF($L16=0,"",INDEX(Flux!$G$2:$G$35,$L16))</f>
+        <v/>
+      </c>
+      <c r="F16" s="43">
+        <f>IF($L16=0,"",INDEX(Flux!$H$2:$H$35,$L16))</f>
+        <v/>
+      </c>
+      <c r="G16" s="43">
+        <f>IF($L16=0,"",INDEX(Flux!$I$2:$I$35,$L16))</f>
+        <v/>
+      </c>
+      <c r="H16" s="43">
+        <f>IF($L16=0,"",INDEX(Flux!$J$2:$J$35,$L16))</f>
+        <v/>
+      </c>
+      <c r="I16" s="43">
+        <f>IF($L16=0,"",INDEX(Flux!$K$2:$K$35,$L16))</f>
+        <v/>
+      </c>
+      <c r="J16" s="43">
+        <f>IF($L16=0,"",INDEX(Flux!$L$2:$L$35,$L16))</f>
+        <v/>
+      </c>
+      <c r="L16" s="39">
+        <f>IFERROR(MATCH(1,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M16" s="39">
+        <f>IF(L16=0,"",INDEX(Flux!$C$2:$C$35,L16))</f>
+        <v/>
+      </c>
+      <c r="N16" s="39">
+        <f>IF(L16&gt;0,1,0)</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="B17" s="38">
-        <f>IF($L17="","",INDEX(Flux!$D$2:$D$35,$L17))</f>
-        <v/>
-      </c>
-      <c r="C17" s="39">
-        <f>IF($L17="","",INDEX(Flux!$E$2:$E$35,$L17))</f>
-        <v/>
-      </c>
-      <c r="D17" s="40">
-        <f>IF($L17="","",INDEX(Flux!$F$2:$F$35,$L17))</f>
-        <v/>
-      </c>
-      <c r="E17" s="41">
-        <f>IF($L17="","",INDEX(Flux!$G$2:$G$35,$L17))</f>
-        <v/>
-      </c>
-      <c r="F17" s="41">
-        <f>IF($L17="","",INDEX(Flux!$H$2:$H$35,$L17))</f>
-        <v/>
-      </c>
-      <c r="G17" s="41">
-        <f>IF($L17="","",INDEX(Flux!$I$2:$I$35,$L17))</f>
-        <v/>
-      </c>
-      <c r="H17" s="41">
-        <f>IF($L17="","",INDEX(Flux!$J$2:$J$35,$L17))</f>
-        <v/>
-      </c>
-      <c r="I17" s="41">
-        <f>IF($L17="","",INDEX(Flux!$K$2:$K$35,$L17))</f>
-        <v/>
-      </c>
-      <c r="J17" s="41">
-        <f>IF($L17="","",INDEX(Flux!$L$2:$L$35,$L17))</f>
-        <v/>
-      </c>
-      <c r="L17" s="42">
-        <f>IFERROR(MATCH(2,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M17" s="42">
-        <f>IF(L17="","",INDEX(Flux!$C$2:$C$35,L17))</f>
+      <c r="B17" s="40">
+        <f>IF($L17=0,"",INDEX(Flux!$D$2:$D$35,$L17))</f>
+        <v/>
+      </c>
+      <c r="C17" s="41">
+        <f>IF($L17=0,"",INDEX(Flux!$E$2:$E$35,$L17))</f>
+        <v/>
+      </c>
+      <c r="D17" s="42">
+        <f>IF($L17=0,"",INDEX(Flux!$F$2:$F$35,$L17))</f>
+        <v/>
+      </c>
+      <c r="E17" s="43">
+        <f>IF($L17=0,"",INDEX(Flux!$G$2:$G$35,$L17))</f>
+        <v/>
+      </c>
+      <c r="F17" s="43">
+        <f>IF($L17=0,"",INDEX(Flux!$H$2:$H$35,$L17))</f>
+        <v/>
+      </c>
+      <c r="G17" s="43">
+        <f>IF($L17=0,"",INDEX(Flux!$I$2:$I$35,$L17))</f>
+        <v/>
+      </c>
+      <c r="H17" s="43">
+        <f>IF($L17=0,"",INDEX(Flux!$J$2:$J$35,$L17))</f>
+        <v/>
+      </c>
+      <c r="I17" s="43">
+        <f>IF($L17=0,"",INDEX(Flux!$K$2:$K$35,$L17))</f>
+        <v/>
+      </c>
+      <c r="J17" s="43">
+        <f>IF($L17=0,"",INDEX(Flux!$L$2:$L$35,$L17))</f>
+        <v/>
+      </c>
+      <c r="L17" s="39">
+        <f>IFERROR(MATCH(2,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M17" s="39">
+        <f>IF(L17=0,"",INDEX(Flux!$C$2:$C$35,L17))</f>
+        <v/>
+      </c>
+      <c r="N17" s="39">
+        <f>IF(L17&gt;0,1,0)</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="B18" s="38">
-        <f>IF($L18="","",INDEX(Flux!$D$2:$D$35,$L18))</f>
-        <v/>
-      </c>
-      <c r="C18" s="39">
-        <f>IF($L18="","",INDEX(Flux!$E$2:$E$35,$L18))</f>
-        <v/>
-      </c>
-      <c r="D18" s="40">
-        <f>IF($L18="","",INDEX(Flux!$F$2:$F$35,$L18))</f>
-        <v/>
-      </c>
-      <c r="E18" s="41">
-        <f>IF($L18="","",INDEX(Flux!$G$2:$G$35,$L18))</f>
-        <v/>
-      </c>
-      <c r="F18" s="41">
-        <f>IF($L18="","",INDEX(Flux!$H$2:$H$35,$L18))</f>
-        <v/>
-      </c>
-      <c r="G18" s="41">
-        <f>IF($L18="","",INDEX(Flux!$I$2:$I$35,$L18))</f>
-        <v/>
-      </c>
-      <c r="H18" s="41">
-        <f>IF($L18="","",INDEX(Flux!$J$2:$J$35,$L18))</f>
-        <v/>
-      </c>
-      <c r="I18" s="41">
-        <f>IF($L18="","",INDEX(Flux!$K$2:$K$35,$L18))</f>
-        <v/>
-      </c>
-      <c r="J18" s="41">
-        <f>IF($L18="","",INDEX(Flux!$L$2:$L$35,$L18))</f>
-        <v/>
-      </c>
-      <c r="L18" s="42">
-        <f>IFERROR(MATCH(3,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M18" s="42">
-        <f>IF(L18="","",INDEX(Flux!$C$2:$C$35,L18))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="B19" s="38">
-        <f>IF($L19="","",INDEX(Flux!$D$2:$D$35,$L19))</f>
-        <v/>
-      </c>
-      <c r="C19" s="39">
-        <f>IF($L19="","",INDEX(Flux!$E$2:$E$35,$L19))</f>
-        <v/>
-      </c>
-      <c r="D19" s="40">
-        <f>IF($L19="","",INDEX(Flux!$F$2:$F$35,$L19))</f>
-        <v/>
-      </c>
-      <c r="E19" s="41">
-        <f>IF($L19="","",INDEX(Flux!$G$2:$G$35,$L19))</f>
-        <v/>
-      </c>
-      <c r="F19" s="41">
-        <f>IF($L19="","",INDEX(Flux!$H$2:$H$35,$L19))</f>
-        <v/>
-      </c>
-      <c r="G19" s="41">
-        <f>IF($L19="","",INDEX(Flux!$I$2:$I$35,$L19))</f>
-        <v/>
-      </c>
-      <c r="H19" s="41">
-        <f>IF($L19="","",INDEX(Flux!$J$2:$J$35,$L19))</f>
-        <v/>
-      </c>
-      <c r="I19" s="41">
-        <f>IF($L19="","",INDEX(Flux!$K$2:$K$35,$L19))</f>
-        <v/>
-      </c>
-      <c r="J19" s="41">
-        <f>IF($L19="","",INDEX(Flux!$L$2:$L$35,$L19))</f>
-        <v/>
-      </c>
-      <c r="L19" s="42">
-        <f>IFERROR(MATCH(4,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M19" s="42">
-        <f>IF(L19="","",INDEX(Flux!$C$2:$C$35,L19))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="B20" s="38">
-        <f>IF($L20="","",INDEX(Flux!$D$2:$D$35,$L20))</f>
-        <v/>
-      </c>
-      <c r="C20" s="39">
-        <f>IF($L20="","",INDEX(Flux!$E$2:$E$35,$L20))</f>
-        <v/>
-      </c>
-      <c r="D20" s="40">
-        <f>IF($L20="","",INDEX(Flux!$F$2:$F$35,$L20))</f>
-        <v/>
-      </c>
-      <c r="E20" s="41">
-        <f>IF($L20="","",INDEX(Flux!$G$2:$G$35,$L20))</f>
-        <v/>
-      </c>
-      <c r="F20" s="41">
-        <f>IF($L20="","",INDEX(Flux!$H$2:$H$35,$L20))</f>
-        <v/>
-      </c>
-      <c r="G20" s="41">
-        <f>IF($L20="","",INDEX(Flux!$I$2:$I$35,$L20))</f>
-        <v/>
-      </c>
-      <c r="H20" s="41">
-        <f>IF($L20="","",INDEX(Flux!$J$2:$J$35,$L20))</f>
-        <v/>
-      </c>
-      <c r="I20" s="41">
-        <f>IF($L20="","",INDEX(Flux!$K$2:$K$35,$L20))</f>
-        <v/>
-      </c>
-      <c r="J20" s="41">
-        <f>IF($L20="","",INDEX(Flux!$L$2:$L$35,$L20))</f>
-        <v/>
-      </c>
-      <c r="L20" s="42">
-        <f>IFERROR(MATCH(5,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M20" s="42">
-        <f>IF(L20="","",INDEX(Flux!$C$2:$C$35,L20))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="B21" s="38">
-        <f>IF($L21="","",INDEX(Flux!$D$2:$D$35,$L21))</f>
-        <v/>
-      </c>
-      <c r="C21" s="39">
-        <f>IF($L21="","",INDEX(Flux!$E$2:$E$35,$L21))</f>
-        <v/>
-      </c>
-      <c r="D21" s="40">
-        <f>IF($L21="","",INDEX(Flux!$F$2:$F$35,$L21))</f>
-        <v/>
-      </c>
-      <c r="E21" s="41">
-        <f>IF($L21="","",INDEX(Flux!$G$2:$G$35,$L21))</f>
-        <v/>
-      </c>
-      <c r="F21" s="41">
-        <f>IF($L21="","",INDEX(Flux!$H$2:$H$35,$L21))</f>
-        <v/>
-      </c>
-      <c r="G21" s="41">
-        <f>IF($L21="","",INDEX(Flux!$I$2:$I$35,$L21))</f>
-        <v/>
-      </c>
-      <c r="H21" s="41">
-        <f>IF($L21="","",INDEX(Flux!$J$2:$J$35,$L21))</f>
-        <v/>
-      </c>
-      <c r="I21" s="41">
-        <f>IF($L21="","",INDEX(Flux!$K$2:$K$35,$L21))</f>
-        <v/>
-      </c>
-      <c r="J21" s="41">
-        <f>IF($L21="","",INDEX(Flux!$L$2:$L$35,$L21))</f>
-        <v/>
-      </c>
-      <c r="L21" s="42">
-        <f>IFERROR(MATCH(6,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M21" s="42">
-        <f>IF(L21="","",INDEX(Flux!$C$2:$C$35,L21))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="B22" s="38">
-        <f>IF($L22="","",INDEX(Flux!$D$2:$D$35,$L22))</f>
-        <v/>
-      </c>
-      <c r="C22" s="39">
-        <f>IF($L22="","",INDEX(Flux!$E$2:$E$35,$L22))</f>
-        <v/>
-      </c>
-      <c r="D22" s="40">
-        <f>IF($L22="","",INDEX(Flux!$F$2:$F$35,$L22))</f>
-        <v/>
-      </c>
-      <c r="E22" s="41">
-        <f>IF($L22="","",INDEX(Flux!$G$2:$G$35,$L22))</f>
-        <v/>
-      </c>
-      <c r="F22" s="41">
-        <f>IF($L22="","",INDEX(Flux!$H$2:$H$35,$L22))</f>
-        <v/>
-      </c>
-      <c r="G22" s="41">
-        <f>IF($L22="","",INDEX(Flux!$I$2:$I$35,$L22))</f>
-        <v/>
-      </c>
-      <c r="H22" s="41">
-        <f>IF($L22="","",INDEX(Flux!$J$2:$J$35,$L22))</f>
-        <v/>
-      </c>
-      <c r="I22" s="41">
-        <f>IF($L22="","",INDEX(Flux!$K$2:$K$35,$L22))</f>
-        <v/>
-      </c>
-      <c r="J22" s="41">
-        <f>IF($L22="","",INDEX(Flux!$L$2:$L$35,$L22))</f>
-        <v/>
-      </c>
-      <c r="L22" s="42">
-        <f>IFERROR(MATCH(7,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M22" s="42">
-        <f>IF(L22="","",INDEX(Flux!$C$2:$C$35,L22))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="B23" s="38">
-        <f>IF($L23="","",INDEX(Flux!$D$2:$D$35,$L23))</f>
-        <v/>
-      </c>
-      <c r="C23" s="39">
-        <f>IF($L23="","",INDEX(Flux!$E$2:$E$35,$L23))</f>
-        <v/>
-      </c>
-      <c r="D23" s="40">
-        <f>IF($L23="","",INDEX(Flux!$F$2:$F$35,$L23))</f>
-        <v/>
-      </c>
-      <c r="E23" s="41">
-        <f>IF($L23="","",INDEX(Flux!$G$2:$G$35,$L23))</f>
-        <v/>
-      </c>
-      <c r="F23" s="41">
-        <f>IF($L23="","",INDEX(Flux!$H$2:$H$35,$L23))</f>
-        <v/>
-      </c>
-      <c r="G23" s="41">
-        <f>IF($L23="","",INDEX(Flux!$I$2:$I$35,$L23))</f>
-        <v/>
-      </c>
-      <c r="H23" s="41">
-        <f>IF($L23="","",INDEX(Flux!$J$2:$J$35,$L23))</f>
-        <v/>
-      </c>
-      <c r="I23" s="41">
-        <f>IF($L23="","",INDEX(Flux!$K$2:$K$35,$L23))</f>
-        <v/>
-      </c>
-      <c r="J23" s="41">
-        <f>IF($L23="","",INDEX(Flux!$L$2:$L$35,$L23))</f>
-        <v/>
-      </c>
-      <c r="L23" s="42">
-        <f>IFERROR(MATCH(8,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M23" s="42">
-        <f>IF(L23="","",INDEX(Flux!$C$2:$C$35,L23))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="B24" s="38">
-        <f>IF($L24="","",INDEX(Flux!$D$2:$D$35,$L24))</f>
-        <v/>
-      </c>
-      <c r="C24" s="39">
-        <f>IF($L24="","",INDEX(Flux!$E$2:$E$35,$L24))</f>
-        <v/>
-      </c>
-      <c r="D24" s="40">
-        <f>IF($L24="","",INDEX(Flux!$F$2:$F$35,$L24))</f>
-        <v/>
-      </c>
-      <c r="E24" s="41">
-        <f>IF($L24="","",INDEX(Flux!$G$2:$G$35,$L24))</f>
-        <v/>
-      </c>
-      <c r="F24" s="41">
-        <f>IF($L24="","",INDEX(Flux!$H$2:$H$35,$L24))</f>
-        <v/>
-      </c>
-      <c r="G24" s="41">
-        <f>IF($L24="","",INDEX(Flux!$I$2:$I$35,$L24))</f>
-        <v/>
-      </c>
-      <c r="H24" s="41">
-        <f>IF($L24="","",INDEX(Flux!$J$2:$J$35,$L24))</f>
-        <v/>
-      </c>
-      <c r="I24" s="41">
-        <f>IF($L24="","",INDEX(Flux!$K$2:$K$35,$L24))</f>
-        <v/>
-      </c>
-      <c r="J24" s="41">
-        <f>IF($L24="","",INDEX(Flux!$L$2:$L$35,$L24))</f>
-        <v/>
-      </c>
-      <c r="L24" s="42">
-        <f>IFERROR(MATCH(9,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M24" s="42">
-        <f>IF(L24="","",INDEX(Flux!$C$2:$C$35,L24))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="B25" s="38">
-        <f>IF($L25="","",INDEX(Flux!$D$2:$D$35,$L25))</f>
-        <v/>
-      </c>
-      <c r="C25" s="39">
-        <f>IF($L25="","",INDEX(Flux!$E$2:$E$35,$L25))</f>
-        <v/>
-      </c>
-      <c r="D25" s="40">
-        <f>IF($L25="","",INDEX(Flux!$F$2:$F$35,$L25))</f>
-        <v/>
-      </c>
-      <c r="E25" s="41">
-        <f>IF($L25="","",INDEX(Flux!$G$2:$G$35,$L25))</f>
-        <v/>
-      </c>
-      <c r="F25" s="41">
-        <f>IF($L25="","",INDEX(Flux!$H$2:$H$35,$L25))</f>
-        <v/>
-      </c>
-      <c r="G25" s="41">
-        <f>IF($L25="","",INDEX(Flux!$I$2:$I$35,$L25))</f>
-        <v/>
-      </c>
-      <c r="H25" s="41">
-        <f>IF($L25="","",INDEX(Flux!$J$2:$J$35,$L25))</f>
-        <v/>
-      </c>
-      <c r="I25" s="41">
-        <f>IF($L25="","",INDEX(Flux!$K$2:$K$35,$L25))</f>
-        <v/>
-      </c>
-      <c r="J25" s="41">
-        <f>IF($L25="","",INDEX(Flux!$L$2:$L$35,$L25))</f>
-        <v/>
-      </c>
-      <c r="L25" s="42">
-        <f>IFERROR(MATCH(10,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M25" s="42">
-        <f>IF(L25="","",INDEX(Flux!$C$2:$C$35,L25))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="B26" s="38">
-        <f>IF($L26="","",INDEX(Flux!$D$2:$D$35,$L26))</f>
-        <v/>
-      </c>
-      <c r="C26" s="39">
-        <f>IF($L26="","",INDEX(Flux!$E$2:$E$35,$L26))</f>
-        <v/>
-      </c>
-      <c r="D26" s="40">
-        <f>IF($L26="","",INDEX(Flux!$F$2:$F$35,$L26))</f>
-        <v/>
-      </c>
-      <c r="E26" s="41">
-        <f>IF($L26="","",INDEX(Flux!$G$2:$G$35,$L26))</f>
-        <v/>
-      </c>
-      <c r="F26" s="41">
-        <f>IF($L26="","",INDEX(Flux!$H$2:$H$35,$L26))</f>
-        <v/>
-      </c>
-      <c r="G26" s="41">
-        <f>IF($L26="","",INDEX(Flux!$I$2:$I$35,$L26))</f>
-        <v/>
-      </c>
-      <c r="H26" s="41">
-        <f>IF($L26="","",INDEX(Flux!$J$2:$J$35,$L26))</f>
-        <v/>
-      </c>
-      <c r="I26" s="41">
-        <f>IF($L26="","",INDEX(Flux!$K$2:$K$35,$L26))</f>
-        <v/>
-      </c>
-      <c r="J26" s="41">
-        <f>IF($L26="","",INDEX(Flux!$L$2:$L$35,$L26))</f>
-        <v/>
-      </c>
-      <c r="L26" s="42">
-        <f>IFERROR(MATCH(11,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M26" s="42">
-        <f>IF(L26="","",INDEX(Flux!$C$2:$C$35,L26))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="B27" s="38">
-        <f>IF($L27="","",INDEX(Flux!$D$2:$D$35,$L27))</f>
-        <v/>
-      </c>
-      <c r="C27" s="39">
-        <f>IF($L27="","",INDEX(Flux!$E$2:$E$35,$L27))</f>
-        <v/>
-      </c>
-      <c r="D27" s="40">
-        <f>IF($L27="","",INDEX(Flux!$F$2:$F$35,$L27))</f>
-        <v/>
-      </c>
-      <c r="E27" s="41">
-        <f>IF($L27="","",INDEX(Flux!$G$2:$G$35,$L27))</f>
-        <v/>
-      </c>
-      <c r="F27" s="41">
-        <f>IF($L27="","",INDEX(Flux!$H$2:$H$35,$L27))</f>
-        <v/>
-      </c>
-      <c r="G27" s="41">
-        <f>IF($L27="","",INDEX(Flux!$I$2:$I$35,$L27))</f>
-        <v/>
-      </c>
-      <c r="H27" s="41">
-        <f>IF($L27="","",INDEX(Flux!$J$2:$J$35,$L27))</f>
-        <v/>
-      </c>
-      <c r="I27" s="41">
-        <f>IF($L27="","",INDEX(Flux!$K$2:$K$35,$L27))</f>
-        <v/>
-      </c>
-      <c r="J27" s="41">
-        <f>IF($L27="","",INDEX(Flux!$L$2:$L$35,$L27))</f>
-        <v/>
-      </c>
-      <c r="L27" s="42">
-        <f>IFERROR(MATCH(12,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M27" s="42">
-        <f>IF(L27="","",INDEX(Flux!$C$2:$C$35,L27))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="38">
-        <f>IF($L28="","",INDEX(Flux!$D$2:$D$35,$L28))</f>
-        <v/>
-      </c>
-      <c r="C28" s="39">
-        <f>IF($L28="","",INDEX(Flux!$E$2:$E$35,$L28))</f>
-        <v/>
-      </c>
-      <c r="D28" s="40">
-        <f>IF($L28="","",INDEX(Flux!$F$2:$F$35,$L28))</f>
-        <v/>
-      </c>
-      <c r="E28" s="41">
-        <f>IF($L28="","",INDEX(Flux!$G$2:$G$35,$L28))</f>
-        <v/>
-      </c>
-      <c r="F28" s="41">
-        <f>IF($L28="","",INDEX(Flux!$H$2:$H$35,$L28))</f>
-        <v/>
-      </c>
-      <c r="G28" s="41">
-        <f>IF($L28="","",INDEX(Flux!$I$2:$I$35,$L28))</f>
-        <v/>
-      </c>
-      <c r="H28" s="41">
-        <f>IF($L28="","",INDEX(Flux!$J$2:$J$35,$L28))</f>
-        <v/>
-      </c>
-      <c r="I28" s="41">
-        <f>IF($L28="","",INDEX(Flux!$K$2:$K$35,$L28))</f>
-        <v/>
-      </c>
-      <c r="J28" s="41">
-        <f>IF($L28="","",INDEX(Flux!$L$2:$L$35,$L28))</f>
-        <v/>
-      </c>
-      <c r="L28" s="42">
-        <f>IFERROR(MATCH(13,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M28" s="42">
-        <f>IF(L28="","",INDEX(Flux!$C$2:$C$35,L28))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="B29" s="38">
-        <f>IF($L29="","",INDEX(Flux!$D$2:$D$35,$L29))</f>
-        <v/>
-      </c>
-      <c r="C29" s="39">
-        <f>IF($L29="","",INDEX(Flux!$E$2:$E$35,$L29))</f>
-        <v/>
-      </c>
-      <c r="D29" s="40">
-        <f>IF($L29="","",INDEX(Flux!$F$2:$F$35,$L29))</f>
-        <v/>
-      </c>
-      <c r="E29" s="41">
-        <f>IF($L29="","",INDEX(Flux!$G$2:$G$35,$L29))</f>
-        <v/>
-      </c>
-      <c r="F29" s="41">
-        <f>IF($L29="","",INDEX(Flux!$H$2:$H$35,$L29))</f>
-        <v/>
-      </c>
-      <c r="G29" s="41">
-        <f>IF($L29="","",INDEX(Flux!$I$2:$I$35,$L29))</f>
-        <v/>
-      </c>
-      <c r="H29" s="41">
-        <f>IF($L29="","",INDEX(Flux!$J$2:$J$35,$L29))</f>
-        <v/>
-      </c>
-      <c r="I29" s="41">
-        <f>IF($L29="","",INDEX(Flux!$K$2:$K$35,$L29))</f>
-        <v/>
-      </c>
-      <c r="J29" s="41">
-        <f>IF($L29="","",INDEX(Flux!$L$2:$L$35,$L29))</f>
-        <v/>
-      </c>
-      <c r="L29" s="42">
-        <f>IFERROR(MATCH(14,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M29" s="42">
-        <f>IF(L29="","",INDEX(Flux!$C$2:$C$35,L29))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="B30" s="38">
-        <f>IF($L30="","",INDEX(Flux!$D$2:$D$35,$L30))</f>
-        <v/>
-      </c>
-      <c r="C30" s="39">
-        <f>IF($L30="","",INDEX(Flux!$E$2:$E$35,$L30))</f>
-        <v/>
-      </c>
-      <c r="D30" s="40">
-        <f>IF($L30="","",INDEX(Flux!$F$2:$F$35,$L30))</f>
-        <v/>
-      </c>
-      <c r="E30" s="41">
-        <f>IF($L30="","",INDEX(Flux!$G$2:$G$35,$L30))</f>
-        <v/>
-      </c>
-      <c r="F30" s="41">
-        <f>IF($L30="","",INDEX(Flux!$H$2:$H$35,$L30))</f>
-        <v/>
-      </c>
-      <c r="G30" s="41">
-        <f>IF($L30="","",INDEX(Flux!$I$2:$I$35,$L30))</f>
-        <v/>
-      </c>
-      <c r="H30" s="41">
-        <f>IF($L30="","",INDEX(Flux!$J$2:$J$35,$L30))</f>
-        <v/>
-      </c>
-      <c r="I30" s="41">
-        <f>IF($L30="","",INDEX(Flux!$K$2:$K$35,$L30))</f>
-        <v/>
-      </c>
-      <c r="J30" s="41">
-        <f>IF($L30="","",INDEX(Flux!$L$2:$L$35,$L30))</f>
-        <v/>
-      </c>
-      <c r="L30" s="42">
-        <f>IFERROR(MATCH(15,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M30" s="42">
-        <f>IF(L30="","",INDEX(Flux!$C$2:$C$35,L30))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="B31" s="38">
-        <f>IF($L31="","",INDEX(Flux!$D$2:$D$35,$L31))</f>
-        <v/>
-      </c>
-      <c r="C31" s="39">
-        <f>IF($L31="","",INDEX(Flux!$E$2:$E$35,$L31))</f>
-        <v/>
-      </c>
-      <c r="D31" s="40">
-        <f>IF($L31="","",INDEX(Flux!$F$2:$F$35,$L31))</f>
-        <v/>
-      </c>
-      <c r="E31" s="41">
-        <f>IF($L31="","",INDEX(Flux!$G$2:$G$35,$L31))</f>
-        <v/>
-      </c>
-      <c r="F31" s="41">
-        <f>IF($L31="","",INDEX(Flux!$H$2:$H$35,$L31))</f>
-        <v/>
-      </c>
-      <c r="G31" s="41">
-        <f>IF($L31="","",INDEX(Flux!$I$2:$I$35,$L31))</f>
-        <v/>
-      </c>
-      <c r="H31" s="41">
-        <f>IF($L31="","",INDEX(Flux!$J$2:$J$35,$L31))</f>
-        <v/>
-      </c>
-      <c r="I31" s="41">
-        <f>IF($L31="","",INDEX(Flux!$K$2:$K$35,$L31))</f>
-        <v/>
-      </c>
-      <c r="J31" s="41">
-        <f>IF($L31="","",INDEX(Flux!$L$2:$L$35,$L31))</f>
-        <v/>
-      </c>
-      <c r="L31" s="42">
-        <f>IFERROR(MATCH(16,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M31" s="42">
-        <f>IF(L31="","",INDEX(Flux!$C$2:$C$35,L31))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="B32" s="38">
-        <f>IF($L32="","",INDEX(Flux!$D$2:$D$35,$L32))</f>
-        <v/>
-      </c>
-      <c r="C32" s="39">
-        <f>IF($L32="","",INDEX(Flux!$E$2:$E$35,$L32))</f>
-        <v/>
-      </c>
-      <c r="D32" s="40">
-        <f>IF($L32="","",INDEX(Flux!$F$2:$F$35,$L32))</f>
-        <v/>
-      </c>
-      <c r="E32" s="41">
-        <f>IF($L32="","",INDEX(Flux!$G$2:$G$35,$L32))</f>
-        <v/>
-      </c>
-      <c r="F32" s="41">
-        <f>IF($L32="","",INDEX(Flux!$H$2:$H$35,$L32))</f>
-        <v/>
-      </c>
-      <c r="G32" s="41">
-        <f>IF($L32="","",INDEX(Flux!$I$2:$I$35,$L32))</f>
-        <v/>
-      </c>
-      <c r="H32" s="41">
-        <f>IF($L32="","",INDEX(Flux!$J$2:$J$35,$L32))</f>
-        <v/>
-      </c>
-      <c r="I32" s="41">
-        <f>IF($L32="","",INDEX(Flux!$K$2:$K$35,$L32))</f>
-        <v/>
-      </c>
-      <c r="J32" s="41">
-        <f>IF($L32="","",INDEX(Flux!$L$2:$L$35,$L32))</f>
-        <v/>
-      </c>
-      <c r="L32" s="42">
-        <f>IFERROR(MATCH(17,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M32" s="42">
-        <f>IF(L32="","",INDEX(Flux!$C$2:$C$35,L32))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="B33" s="38">
-        <f>IF($L33="","",INDEX(Flux!$D$2:$D$35,$L33))</f>
-        <v/>
-      </c>
-      <c r="C33" s="39">
-        <f>IF($L33="","",INDEX(Flux!$E$2:$E$35,$L33))</f>
-        <v/>
-      </c>
-      <c r="D33" s="40">
-        <f>IF($L33="","",INDEX(Flux!$F$2:$F$35,$L33))</f>
-        <v/>
-      </c>
-      <c r="E33" s="41">
-        <f>IF($L33="","",INDEX(Flux!$G$2:$G$35,$L33))</f>
-        <v/>
-      </c>
-      <c r="F33" s="41">
-        <f>IF($L33="","",INDEX(Flux!$H$2:$H$35,$L33))</f>
-        <v/>
-      </c>
-      <c r="G33" s="41">
-        <f>IF($L33="","",INDEX(Flux!$I$2:$I$35,$L33))</f>
-        <v/>
-      </c>
-      <c r="H33" s="41">
-        <f>IF($L33="","",INDEX(Flux!$J$2:$J$35,$L33))</f>
-        <v/>
-      </c>
-      <c r="I33" s="41">
-        <f>IF($L33="","",INDEX(Flux!$K$2:$K$35,$L33))</f>
-        <v/>
-      </c>
-      <c r="J33" s="41">
-        <f>IF($L33="","",INDEX(Flux!$L$2:$L$35,$L33))</f>
-        <v/>
-      </c>
-      <c r="L33" s="42">
-        <f>IFERROR(MATCH(18,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M33" s="42">
-        <f>IF(L33="","",INDEX(Flux!$C$2:$C$35,L33))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="38">
-        <f>IF($L34="","",INDEX(Flux!$D$2:$D$35,$L34))</f>
-        <v/>
-      </c>
-      <c r="C34" s="39">
-        <f>IF($L34="","",INDEX(Flux!$E$2:$E$35,$L34))</f>
-        <v/>
-      </c>
-      <c r="D34" s="40">
-        <f>IF($L34="","",INDEX(Flux!$F$2:$F$35,$L34))</f>
-        <v/>
-      </c>
-      <c r="E34" s="41">
-        <f>IF($L34="","",INDEX(Flux!$G$2:$G$35,$L34))</f>
-        <v/>
-      </c>
-      <c r="F34" s="41">
-        <f>IF($L34="","",INDEX(Flux!$H$2:$H$35,$L34))</f>
-        <v/>
-      </c>
-      <c r="G34" s="41">
-        <f>IF($L34="","",INDEX(Flux!$I$2:$I$35,$L34))</f>
-        <v/>
-      </c>
-      <c r="H34" s="41">
-        <f>IF($L34="","",INDEX(Flux!$J$2:$J$35,$L34))</f>
-        <v/>
-      </c>
-      <c r="I34" s="41">
-        <f>IF($L34="","",INDEX(Flux!$K$2:$K$35,$L34))</f>
-        <v/>
-      </c>
-      <c r="J34" s="41">
-        <f>IF($L34="","",INDEX(Flux!$L$2:$L$35,$L34))</f>
-        <v/>
-      </c>
-      <c r="L34" s="42">
-        <f>IFERROR(MATCH(19,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M34" s="42">
-        <f>IF(L34="","",INDEX(Flux!$C$2:$C$35,L34))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="B35" s="38">
-        <f>IF($L35="","",INDEX(Flux!$D$2:$D$35,$L35))</f>
-        <v/>
-      </c>
-      <c r="C35" s="39">
-        <f>IF($L35="","",INDEX(Flux!$E$2:$E$35,$L35))</f>
-        <v/>
-      </c>
-      <c r="D35" s="40">
-        <f>IF($L35="","",INDEX(Flux!$F$2:$F$35,$L35))</f>
-        <v/>
-      </c>
-      <c r="E35" s="41">
-        <f>IF($L35="","",INDEX(Flux!$G$2:$G$35,$L35))</f>
-        <v/>
-      </c>
-      <c r="F35" s="41">
-        <f>IF($L35="","",INDEX(Flux!$H$2:$H$35,$L35))</f>
-        <v/>
-      </c>
-      <c r="G35" s="41">
-        <f>IF($L35="","",INDEX(Flux!$I$2:$I$35,$L35))</f>
-        <v/>
-      </c>
-      <c r="H35" s="41">
-        <f>IF($L35="","",INDEX(Flux!$J$2:$J$35,$L35))</f>
-        <v/>
-      </c>
-      <c r="I35" s="41">
-        <f>IF($L35="","",INDEX(Flux!$K$2:$K$35,$L35))</f>
-        <v/>
-      </c>
-      <c r="J35" s="41">
-        <f>IF($L35="","",INDEX(Flux!$L$2:$L$35,$L35))</f>
-        <v/>
-      </c>
-      <c r="L35" s="42">
-        <f>IFERROR(MATCH(20,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M35" s="42">
-        <f>IF(L35="","",INDEX(Flux!$C$2:$C$35,L35))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="B36" s="38">
-        <f>IF($L36="","",INDEX(Flux!$D$2:$D$35,$L36))</f>
-        <v/>
-      </c>
-      <c r="C36" s="39">
-        <f>IF($L36="","",INDEX(Flux!$E$2:$E$35,$L36))</f>
-        <v/>
-      </c>
-      <c r="D36" s="40">
-        <f>IF($L36="","",INDEX(Flux!$F$2:$F$35,$L36))</f>
-        <v/>
-      </c>
-      <c r="E36" s="41">
-        <f>IF($L36="","",INDEX(Flux!$G$2:$G$35,$L36))</f>
-        <v/>
-      </c>
-      <c r="F36" s="41">
-        <f>IF($L36="","",INDEX(Flux!$H$2:$H$35,$L36))</f>
-        <v/>
-      </c>
-      <c r="G36" s="41">
-        <f>IF($L36="","",INDEX(Flux!$I$2:$I$35,$L36))</f>
-        <v/>
-      </c>
-      <c r="H36" s="41">
-        <f>IF($L36="","",INDEX(Flux!$J$2:$J$35,$L36))</f>
-        <v/>
-      </c>
-      <c r="I36" s="41">
-        <f>IF($L36="","",INDEX(Flux!$K$2:$K$35,$L36))</f>
-        <v/>
-      </c>
-      <c r="J36" s="41">
-        <f>IF($L36="","",INDEX(Flux!$L$2:$L$35,$L36))</f>
-        <v/>
-      </c>
-      <c r="L36" s="42">
-        <f>IFERROR(MATCH(21,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M36" s="42">
-        <f>IF(L36="","",INDEX(Flux!$C$2:$C$35,L36))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="B37" s="38">
-        <f>IF($L37="","",INDEX(Flux!$D$2:$D$35,$L37))</f>
-        <v/>
-      </c>
-      <c r="C37" s="39">
-        <f>IF($L37="","",INDEX(Flux!$E$2:$E$35,$L37))</f>
-        <v/>
-      </c>
-      <c r="D37" s="40">
-        <f>IF($L37="","",INDEX(Flux!$F$2:$F$35,$L37))</f>
-        <v/>
-      </c>
-      <c r="E37" s="41">
-        <f>IF($L37="","",INDEX(Flux!$G$2:$G$35,$L37))</f>
-        <v/>
-      </c>
-      <c r="F37" s="41">
-        <f>IF($L37="","",INDEX(Flux!$H$2:$H$35,$L37))</f>
-        <v/>
-      </c>
-      <c r="G37" s="41">
-        <f>IF($L37="","",INDEX(Flux!$I$2:$I$35,$L37))</f>
-        <v/>
-      </c>
-      <c r="H37" s="41">
-        <f>IF($L37="","",INDEX(Flux!$J$2:$J$35,$L37))</f>
-        <v/>
-      </c>
-      <c r="I37" s="41">
-        <f>IF($L37="","",INDEX(Flux!$K$2:$K$35,$L37))</f>
-        <v/>
-      </c>
-      <c r="J37" s="41">
-        <f>IF($L37="","",INDEX(Flux!$L$2:$L$35,$L37))</f>
-        <v/>
-      </c>
-      <c r="L37" s="42">
-        <f>IFERROR(MATCH(22,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M37" s="42">
-        <f>IF(L37="","",INDEX(Flux!$C$2:$C$35,L37))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="B38" s="38">
-        <f>IF($L38="","",INDEX(Flux!$D$2:$D$35,$L38))</f>
-        <v/>
-      </c>
-      <c r="C38" s="39">
-        <f>IF($L38="","",INDEX(Flux!$E$2:$E$35,$L38))</f>
-        <v/>
-      </c>
-      <c r="D38" s="40">
-        <f>IF($L38="","",INDEX(Flux!$F$2:$F$35,$L38))</f>
-        <v/>
-      </c>
-      <c r="E38" s="41">
-        <f>IF($L38="","",INDEX(Flux!$G$2:$G$35,$L38))</f>
-        <v/>
-      </c>
-      <c r="F38" s="41">
-        <f>IF($L38="","",INDEX(Flux!$H$2:$H$35,$L38))</f>
-        <v/>
-      </c>
-      <c r="G38" s="41">
-        <f>IF($L38="","",INDEX(Flux!$I$2:$I$35,$L38))</f>
-        <v/>
-      </c>
-      <c r="H38" s="41">
-        <f>IF($L38="","",INDEX(Flux!$J$2:$J$35,$L38))</f>
-        <v/>
-      </c>
-      <c r="I38" s="41">
-        <f>IF($L38="","",INDEX(Flux!$K$2:$K$35,$L38))</f>
-        <v/>
-      </c>
-      <c r="J38" s="41">
-        <f>IF($L38="","",INDEX(Flux!$L$2:$L$35,$L38))</f>
-        <v/>
-      </c>
-      <c r="L38" s="42">
-        <f>IFERROR(MATCH(23,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M38" s="42">
-        <f>IF(L38="","",INDEX(Flux!$C$2:$C$35,L38))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="B39" s="38">
-        <f>IF($L39="","",INDEX(Flux!$D$2:$D$35,$L39))</f>
-        <v/>
-      </c>
-      <c r="C39" s="39">
-        <f>IF($L39="","",INDEX(Flux!$E$2:$E$35,$L39))</f>
-        <v/>
-      </c>
-      <c r="D39" s="40">
-        <f>IF($L39="","",INDEX(Flux!$F$2:$F$35,$L39))</f>
-        <v/>
-      </c>
-      <c r="E39" s="41">
-        <f>IF($L39="","",INDEX(Flux!$G$2:$G$35,$L39))</f>
-        <v/>
-      </c>
-      <c r="F39" s="41">
-        <f>IF($L39="","",INDEX(Flux!$H$2:$H$35,$L39))</f>
-        <v/>
-      </c>
-      <c r="G39" s="41">
-        <f>IF($L39="","",INDEX(Flux!$I$2:$I$35,$L39))</f>
-        <v/>
-      </c>
-      <c r="H39" s="41">
-        <f>IF($L39="","",INDEX(Flux!$J$2:$J$35,$L39))</f>
-        <v/>
-      </c>
-      <c r="I39" s="41">
-        <f>IF($L39="","",INDEX(Flux!$K$2:$K$35,$L39))</f>
-        <v/>
-      </c>
-      <c r="J39" s="41">
-        <f>IF($L39="","",INDEX(Flux!$L$2:$L$35,$L39))</f>
-        <v/>
-      </c>
-      <c r="L39" s="42">
-        <f>IFERROR(MATCH(24,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M39" s="42">
-        <f>IF(L39="","",INDEX(Flux!$C$2:$C$35,L39))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="B40" s="38">
-        <f>IF($L40="","",INDEX(Flux!$D$2:$D$35,$L40))</f>
-        <v/>
-      </c>
-      <c r="C40" s="39">
-        <f>IF($L40="","",INDEX(Flux!$E$2:$E$35,$L40))</f>
-        <v/>
-      </c>
-      <c r="D40" s="40">
-        <f>IF($L40="","",INDEX(Flux!$F$2:$F$35,$L40))</f>
-        <v/>
-      </c>
-      <c r="E40" s="41">
-        <f>IF($L40="","",INDEX(Flux!$G$2:$G$35,$L40))</f>
-        <v/>
-      </c>
-      <c r="F40" s="41">
-        <f>IF($L40="","",INDEX(Flux!$H$2:$H$35,$L40))</f>
-        <v/>
-      </c>
-      <c r="G40" s="41">
-        <f>IF($L40="","",INDEX(Flux!$I$2:$I$35,$L40))</f>
-        <v/>
-      </c>
-      <c r="H40" s="41">
-        <f>IF($L40="","",INDEX(Flux!$J$2:$J$35,$L40))</f>
-        <v/>
-      </c>
-      <c r="I40" s="41">
-        <f>IF($L40="","",INDEX(Flux!$K$2:$K$35,$L40))</f>
-        <v/>
-      </c>
-      <c r="J40" s="41">
-        <f>IF($L40="","",INDEX(Flux!$L$2:$L$35,$L40))</f>
-        <v/>
-      </c>
-      <c r="L40" s="42">
-        <f>IFERROR(MATCH(25,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M40" s="42">
-        <f>IF(L40="","",INDEX(Flux!$C$2:$C$35,L40))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="B41" s="38">
-        <f>IF($L41="","",INDEX(Flux!$D$2:$D$35,$L41))</f>
-        <v/>
-      </c>
-      <c r="C41" s="39">
-        <f>IF($L41="","",INDEX(Flux!$E$2:$E$35,$L41))</f>
-        <v/>
-      </c>
-      <c r="D41" s="40">
-        <f>IF($L41="","",INDEX(Flux!$F$2:$F$35,$L41))</f>
-        <v/>
-      </c>
-      <c r="E41" s="41">
-        <f>IF($L41="","",INDEX(Flux!$G$2:$G$35,$L41))</f>
-        <v/>
-      </c>
-      <c r="F41" s="41">
-        <f>IF($L41="","",INDEX(Flux!$H$2:$H$35,$L41))</f>
-        <v/>
-      </c>
-      <c r="G41" s="41">
-        <f>IF($L41="","",INDEX(Flux!$I$2:$I$35,$L41))</f>
-        <v/>
-      </c>
-      <c r="H41" s="41">
-        <f>IF($L41="","",INDEX(Flux!$J$2:$J$35,$L41))</f>
-        <v/>
-      </c>
-      <c r="I41" s="41">
-        <f>IF($L41="","",INDEX(Flux!$K$2:$K$35,$L41))</f>
-        <v/>
-      </c>
-      <c r="J41" s="41">
-        <f>IF($L41="","",INDEX(Flux!$L$2:$L$35,$L41))</f>
-        <v/>
-      </c>
-      <c r="L41" s="42">
-        <f>IFERROR(MATCH(26,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M41" s="42">
-        <f>IF(L41="","",INDEX(Flux!$C$2:$C$35,L41))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" hidden="1" outlineLevel="1" ht="22" customHeight="1">
-      <c r="B42" s="38">
-        <f>IF($L42="","",INDEX(Flux!$D$2:$D$35,$L42))</f>
-        <v/>
-      </c>
-      <c r="C42" s="39">
-        <f>IF($L42="","",INDEX(Flux!$E$2:$E$35,$L42))</f>
-        <v/>
-      </c>
-      <c r="D42" s="40">
-        <f>IF($L42="","",INDEX(Flux!$F$2:$F$35,$L42))</f>
-        <v/>
-      </c>
-      <c r="E42" s="41">
-        <f>IF($L42="","",INDEX(Flux!$G$2:$G$35,$L42))</f>
-        <v/>
-      </c>
-      <c r="F42" s="41">
-        <f>IF($L42="","",INDEX(Flux!$H$2:$H$35,$L42))</f>
-        <v/>
-      </c>
-      <c r="G42" s="41">
-        <f>IF($L42="","",INDEX(Flux!$I$2:$I$35,$L42))</f>
-        <v/>
-      </c>
-      <c r="H42" s="41">
-        <f>IF($L42="","",INDEX(Flux!$J$2:$J$35,$L42))</f>
-        <v/>
-      </c>
-      <c r="I42" s="41">
-        <f>IF($L42="","",INDEX(Flux!$K$2:$K$35,$L42))</f>
-        <v/>
-      </c>
-      <c r="J42" s="41">
-        <f>IF($L42="","",INDEX(Flux!$L$2:$L$35,$L42))</f>
-        <v/>
-      </c>
-      <c r="L42" s="42">
-        <f>IFERROR(MATCH(27,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M42" s="42">
-        <f>IF(L42="","",INDEX(Flux!$C$2:$C$35,L42))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" hidden="1" outlineLevel="1" ht="22" customHeight="1">
-      <c r="B43" s="38">
-        <f>IF($L43="","",INDEX(Flux!$D$2:$D$35,$L43))</f>
-        <v/>
-      </c>
-      <c r="C43" s="39">
-        <f>IF($L43="","",INDEX(Flux!$E$2:$E$35,$L43))</f>
-        <v/>
-      </c>
-      <c r="D43" s="40">
-        <f>IF($L43="","",INDEX(Flux!$F$2:$F$35,$L43))</f>
-        <v/>
-      </c>
-      <c r="E43" s="41">
-        <f>IF($L43="","",INDEX(Flux!$G$2:$G$35,$L43))</f>
-        <v/>
-      </c>
-      <c r="F43" s="41">
-        <f>IF($L43="","",INDEX(Flux!$H$2:$H$35,$L43))</f>
-        <v/>
-      </c>
-      <c r="G43" s="41">
-        <f>IF($L43="","",INDEX(Flux!$I$2:$I$35,$L43))</f>
-        <v/>
-      </c>
-      <c r="H43" s="41">
-        <f>IF($L43="","",INDEX(Flux!$J$2:$J$35,$L43))</f>
-        <v/>
-      </c>
-      <c r="I43" s="41">
-        <f>IF($L43="","",INDEX(Flux!$K$2:$K$35,$L43))</f>
-        <v/>
-      </c>
-      <c r="J43" s="41">
-        <f>IF($L43="","",INDEX(Flux!$L$2:$L$35,$L43))</f>
-        <v/>
-      </c>
-      <c r="L43" s="42">
-        <f>IFERROR(MATCH(28,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M43" s="42">
-        <f>IF(L43="","",INDEX(Flux!$C$2:$C$35,L43))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" hidden="1" outlineLevel="1" ht="22" customHeight="1">
-      <c r="B44" s="38">
-        <f>IF($L44="","",INDEX(Flux!$D$2:$D$35,$L44))</f>
-        <v/>
-      </c>
-      <c r="C44" s="39">
-        <f>IF($L44="","",INDEX(Flux!$E$2:$E$35,$L44))</f>
-        <v/>
-      </c>
-      <c r="D44" s="40">
-        <f>IF($L44="","",INDEX(Flux!$F$2:$F$35,$L44))</f>
-        <v/>
-      </c>
-      <c r="E44" s="41">
-        <f>IF($L44="","",INDEX(Flux!$G$2:$G$35,$L44))</f>
-        <v/>
-      </c>
-      <c r="F44" s="41">
-        <f>IF($L44="","",INDEX(Flux!$H$2:$H$35,$L44))</f>
-        <v/>
-      </c>
-      <c r="G44" s="41">
-        <f>IF($L44="","",INDEX(Flux!$I$2:$I$35,$L44))</f>
-        <v/>
-      </c>
-      <c r="H44" s="41">
-        <f>IF($L44="","",INDEX(Flux!$J$2:$J$35,$L44))</f>
-        <v/>
-      </c>
-      <c r="I44" s="41">
-        <f>IF($L44="","",INDEX(Flux!$K$2:$K$35,$L44))</f>
-        <v/>
-      </c>
-      <c r="J44" s="41">
-        <f>IF($L44="","",INDEX(Flux!$L$2:$L$35,$L44))</f>
-        <v/>
-      </c>
-      <c r="L44" s="42">
-        <f>IFERROR(MATCH(29,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M44" s="42">
-        <f>IF(L44="","",INDEX(Flux!$C$2:$C$35,L44))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" hidden="1" outlineLevel="1" ht="22" customHeight="1">
-      <c r="B45" s="38">
-        <f>IF($L45="","",INDEX(Flux!$D$2:$D$35,$L45))</f>
-        <v/>
-      </c>
-      <c r="C45" s="39">
-        <f>IF($L45="","",INDEX(Flux!$E$2:$E$35,$L45))</f>
-        <v/>
-      </c>
-      <c r="D45" s="40">
-        <f>IF($L45="","",INDEX(Flux!$F$2:$F$35,$L45))</f>
-        <v/>
-      </c>
-      <c r="E45" s="41">
-        <f>IF($L45="","",INDEX(Flux!$G$2:$G$35,$L45))</f>
-        <v/>
-      </c>
-      <c r="F45" s="41">
-        <f>IF($L45="","",INDEX(Flux!$H$2:$H$35,$L45))</f>
-        <v/>
-      </c>
-      <c r="G45" s="41">
-        <f>IF($L45="","",INDEX(Flux!$I$2:$I$35,$L45))</f>
-        <v/>
-      </c>
-      <c r="H45" s="41">
-        <f>IF($L45="","",INDEX(Flux!$J$2:$J$35,$L45))</f>
-        <v/>
-      </c>
-      <c r="I45" s="41">
-        <f>IF($L45="","",INDEX(Flux!$K$2:$K$35,$L45))</f>
-        <v/>
-      </c>
-      <c r="J45" s="41">
-        <f>IF($L45="","",INDEX(Flux!$L$2:$L$35,$L45))</f>
-        <v/>
-      </c>
-      <c r="L45" s="42">
-        <f>IFERROR(MATCH(30,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M45" s="42">
-        <f>IF(L45="","",INDEX(Flux!$C$2:$C$35,L45))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" hidden="1" outlineLevel="1" ht="22" customHeight="1">
-      <c r="B46" s="38">
-        <f>IF($L46="","",INDEX(Flux!$D$2:$D$35,$L46))</f>
-        <v/>
-      </c>
-      <c r="C46" s="39">
-        <f>IF($L46="","",INDEX(Flux!$E$2:$E$35,$L46))</f>
-        <v/>
-      </c>
-      <c r="D46" s="40">
-        <f>IF($L46="","",INDEX(Flux!$F$2:$F$35,$L46))</f>
-        <v/>
-      </c>
-      <c r="E46" s="41">
-        <f>IF($L46="","",INDEX(Flux!$G$2:$G$35,$L46))</f>
-        <v/>
-      </c>
-      <c r="F46" s="41">
-        <f>IF($L46="","",INDEX(Flux!$H$2:$H$35,$L46))</f>
-        <v/>
-      </c>
-      <c r="G46" s="41">
-        <f>IF($L46="","",INDEX(Flux!$I$2:$I$35,$L46))</f>
-        <v/>
-      </c>
-      <c r="H46" s="41">
-        <f>IF($L46="","",INDEX(Flux!$J$2:$J$35,$L46))</f>
-        <v/>
-      </c>
-      <c r="I46" s="41">
-        <f>IF($L46="","",INDEX(Flux!$K$2:$K$35,$L46))</f>
-        <v/>
-      </c>
-      <c r="J46" s="41">
-        <f>IF($L46="","",INDEX(Flux!$L$2:$L$35,$L46))</f>
-        <v/>
-      </c>
-      <c r="L46" s="42">
-        <f>IFERROR(MATCH(31,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M46" s="42">
-        <f>IF(L46="","",INDEX(Flux!$C$2:$C$35,L46))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" hidden="1" outlineLevel="1" ht="22" customHeight="1">
-      <c r="B47" s="38">
-        <f>IF($L47="","",INDEX(Flux!$D$2:$D$35,$L47))</f>
-        <v/>
-      </c>
-      <c r="C47" s="39">
-        <f>IF($L47="","",INDEX(Flux!$E$2:$E$35,$L47))</f>
-        <v/>
-      </c>
-      <c r="D47" s="40">
-        <f>IF($L47="","",INDEX(Flux!$F$2:$F$35,$L47))</f>
-        <v/>
-      </c>
-      <c r="E47" s="41">
-        <f>IF($L47="","",INDEX(Flux!$G$2:$G$35,$L47))</f>
-        <v/>
-      </c>
-      <c r="F47" s="41">
-        <f>IF($L47="","",INDEX(Flux!$H$2:$H$35,$L47))</f>
-        <v/>
-      </c>
-      <c r="G47" s="41">
-        <f>IF($L47="","",INDEX(Flux!$I$2:$I$35,$L47))</f>
-        <v/>
-      </c>
-      <c r="H47" s="41">
-        <f>IF($L47="","",INDEX(Flux!$J$2:$J$35,$L47))</f>
-        <v/>
-      </c>
-      <c r="I47" s="41">
-        <f>IF($L47="","",INDEX(Flux!$K$2:$K$35,$L47))</f>
-        <v/>
-      </c>
-      <c r="J47" s="41">
-        <f>IF($L47="","",INDEX(Flux!$L$2:$L$35,$L47))</f>
-        <v/>
-      </c>
-      <c r="L47" s="42">
-        <f>IFERROR(MATCH(32,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M47" s="42">
-        <f>IF(L47="","",INDEX(Flux!$C$2:$C$35,L47))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" hidden="1" outlineLevel="1" ht="22" customHeight="1">
-      <c r="B48" s="38">
-        <f>IF($L48="","",INDEX(Flux!$D$2:$D$35,$L48))</f>
-        <v/>
-      </c>
-      <c r="C48" s="39">
-        <f>IF($L48="","",INDEX(Flux!$E$2:$E$35,$L48))</f>
-        <v/>
-      </c>
-      <c r="D48" s="40">
-        <f>IF($L48="","",INDEX(Flux!$F$2:$F$35,$L48))</f>
-        <v/>
-      </c>
-      <c r="E48" s="41">
-        <f>IF($L48="","",INDEX(Flux!$G$2:$G$35,$L48))</f>
-        <v/>
-      </c>
-      <c r="F48" s="41">
-        <f>IF($L48="","",INDEX(Flux!$H$2:$H$35,$L48))</f>
-        <v/>
-      </c>
-      <c r="G48" s="41">
-        <f>IF($L48="","",INDEX(Flux!$I$2:$I$35,$L48))</f>
-        <v/>
-      </c>
-      <c r="H48" s="41">
-        <f>IF($L48="","",INDEX(Flux!$J$2:$J$35,$L48))</f>
-        <v/>
-      </c>
-      <c r="I48" s="41">
-        <f>IF($L48="","",INDEX(Flux!$K$2:$K$35,$L48))</f>
-        <v/>
-      </c>
-      <c r="J48" s="41">
-        <f>IF($L48="","",INDEX(Flux!$L$2:$L$35,$L48))</f>
-        <v/>
-      </c>
-      <c r="L48" s="42">
-        <f>IFERROR(MATCH(33,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M48" s="42">
-        <f>IF(L48="","",INDEX(Flux!$C$2:$C$35,L48))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" hidden="1" outlineLevel="1" ht="22" customHeight="1">
-      <c r="B49" s="38">
-        <f>IF($L49="","",INDEX(Flux!$D$2:$D$35,$L49))</f>
-        <v/>
-      </c>
-      <c r="C49" s="39">
-        <f>IF($L49="","",INDEX(Flux!$E$2:$E$35,$L49))</f>
-        <v/>
-      </c>
-      <c r="D49" s="40">
-        <f>IF($L49="","",INDEX(Flux!$F$2:$F$35,$L49))</f>
-        <v/>
-      </c>
-      <c r="E49" s="41">
-        <f>IF($L49="","",INDEX(Flux!$G$2:$G$35,$L49))</f>
-        <v/>
-      </c>
-      <c r="F49" s="41">
-        <f>IF($L49="","",INDEX(Flux!$H$2:$H$35,$L49))</f>
-        <v/>
-      </c>
-      <c r="G49" s="41">
-        <f>IF($L49="","",INDEX(Flux!$I$2:$I$35,$L49))</f>
-        <v/>
-      </c>
-      <c r="H49" s="41">
-        <f>IF($L49="","",INDEX(Flux!$J$2:$J$35,$L49))</f>
-        <v/>
-      </c>
-      <c r="I49" s="41">
-        <f>IF($L49="","",INDEX(Flux!$K$2:$K$35,$L49))</f>
-        <v/>
-      </c>
-      <c r="J49" s="41">
-        <f>IF($L49="","",INDEX(Flux!$L$2:$L$35,$L49))</f>
-        <v/>
-      </c>
-      <c r="L49" s="42">
-        <f>IFERROR(MATCH(34,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M49" s="42">
-        <f>IF(L49="","",INDEX(Flux!$C$2:$C$35,L49))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" hidden="1" outlineLevel="1" ht="22" customHeight="1">
-      <c r="B50" s="38">
-        <f>IF($L50="","",INDEX(Flux!$D$2:$D$35,$L50))</f>
-        <v/>
-      </c>
-      <c r="C50" s="39">
-        <f>IF($L50="","",INDEX(Flux!$E$2:$E$35,$L50))</f>
-        <v/>
-      </c>
-      <c r="D50" s="40">
-        <f>IF($L50="","",INDEX(Flux!$F$2:$F$35,$L50))</f>
-        <v/>
-      </c>
-      <c r="E50" s="41">
-        <f>IF($L50="","",INDEX(Flux!$G$2:$G$35,$L50))</f>
-        <v/>
-      </c>
-      <c r="F50" s="41">
-        <f>IF($L50="","",INDEX(Flux!$H$2:$H$35,$L50))</f>
-        <v/>
-      </c>
-      <c r="G50" s="41">
-        <f>IF($L50="","",INDEX(Flux!$I$2:$I$35,$L50))</f>
-        <v/>
-      </c>
-      <c r="H50" s="41">
-        <f>IF($L50="","",INDEX(Flux!$J$2:$J$35,$L50))</f>
-        <v/>
-      </c>
-      <c r="I50" s="41">
-        <f>IF($L50="","",INDEX(Flux!$K$2:$K$35,$L50))</f>
-        <v/>
-      </c>
-      <c r="J50" s="41">
-        <f>IF($L50="","",INDEX(Flux!$L$2:$L$35,$L50))</f>
-        <v/>
-      </c>
-      <c r="L50" s="42">
-        <f>IFERROR(MATCH(35,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M50" s="42">
-        <f>IF(L50="","",INDEX(Flux!$C$2:$C$35,L50))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" hidden="1" outlineLevel="1" ht="22" customHeight="1">
-      <c r="B51" s="38">
-        <f>IF($L51="","",INDEX(Flux!$D$2:$D$35,$L51))</f>
-        <v/>
-      </c>
-      <c r="C51" s="39">
-        <f>IF($L51="","",INDEX(Flux!$E$2:$E$35,$L51))</f>
-        <v/>
-      </c>
-      <c r="D51" s="40">
-        <f>IF($L51="","",INDEX(Flux!$F$2:$F$35,$L51))</f>
-        <v/>
-      </c>
-      <c r="E51" s="41">
-        <f>IF($L51="","",INDEX(Flux!$G$2:$G$35,$L51))</f>
-        <v/>
-      </c>
-      <c r="F51" s="41">
-        <f>IF($L51="","",INDEX(Flux!$H$2:$H$35,$L51))</f>
-        <v/>
-      </c>
-      <c r="G51" s="41">
-        <f>IF($L51="","",INDEX(Flux!$I$2:$I$35,$L51))</f>
-        <v/>
-      </c>
-      <c r="H51" s="41">
-        <f>IF($L51="","",INDEX(Flux!$J$2:$J$35,$L51))</f>
-        <v/>
-      </c>
-      <c r="I51" s="41">
-        <f>IF($L51="","",INDEX(Flux!$K$2:$K$35,$L51))</f>
-        <v/>
-      </c>
-      <c r="J51" s="41">
-        <f>IF($L51="","",INDEX(Flux!$L$2:$L$35,$L51))</f>
-        <v/>
-      </c>
-      <c r="L51" s="42">
-        <f>IFERROR(MATCH(36,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M51" s="42">
-        <f>IF(L51="","",INDEX(Flux!$C$2:$C$35,L51))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" hidden="1" outlineLevel="1" ht="22" customHeight="1">
-      <c r="B52" s="38">
-        <f>IF($L52="","",INDEX(Flux!$D$2:$D$35,$L52))</f>
-        <v/>
-      </c>
-      <c r="C52" s="39">
-        <f>IF($L52="","",INDEX(Flux!$E$2:$E$35,$L52))</f>
-        <v/>
-      </c>
-      <c r="D52" s="40">
-        <f>IF($L52="","",INDEX(Flux!$F$2:$F$35,$L52))</f>
-        <v/>
-      </c>
-      <c r="E52" s="41">
-        <f>IF($L52="","",INDEX(Flux!$G$2:$G$35,$L52))</f>
-        <v/>
-      </c>
-      <c r="F52" s="41">
-        <f>IF($L52="","",INDEX(Flux!$H$2:$H$35,$L52))</f>
-        <v/>
-      </c>
-      <c r="G52" s="41">
-        <f>IF($L52="","",INDEX(Flux!$I$2:$I$35,$L52))</f>
-        <v/>
-      </c>
-      <c r="H52" s="41">
-        <f>IF($L52="","",INDEX(Flux!$J$2:$J$35,$L52))</f>
-        <v/>
-      </c>
-      <c r="I52" s="41">
-        <f>IF($L52="","",INDEX(Flux!$K$2:$K$35,$L52))</f>
-        <v/>
-      </c>
-      <c r="J52" s="41">
-        <f>IF($L52="","",INDEX(Flux!$L$2:$L$35,$L52))</f>
-        <v/>
-      </c>
-      <c r="L52" s="42">
-        <f>IFERROR(MATCH(37,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M52" s="42">
-        <f>IF(L52="","",INDEX(Flux!$C$2:$C$35,L52))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" hidden="1" outlineLevel="1" ht="22" customHeight="1">
-      <c r="B53" s="38">
-        <f>IF($L53="","",INDEX(Flux!$D$2:$D$35,$L53))</f>
-        <v/>
-      </c>
-      <c r="C53" s="39">
-        <f>IF($L53="","",INDEX(Flux!$E$2:$E$35,$L53))</f>
-        <v/>
-      </c>
-      <c r="D53" s="40">
-        <f>IF($L53="","",INDEX(Flux!$F$2:$F$35,$L53))</f>
-        <v/>
-      </c>
-      <c r="E53" s="41">
-        <f>IF($L53="","",INDEX(Flux!$G$2:$G$35,$L53))</f>
-        <v/>
-      </c>
-      <c r="F53" s="41">
-        <f>IF($L53="","",INDEX(Flux!$H$2:$H$35,$L53))</f>
-        <v/>
-      </c>
-      <c r="G53" s="41">
-        <f>IF($L53="","",INDEX(Flux!$I$2:$I$35,$L53))</f>
-        <v/>
-      </c>
-      <c r="H53" s="41">
-        <f>IF($L53="","",INDEX(Flux!$J$2:$J$35,$L53))</f>
-        <v/>
-      </c>
-      <c r="I53" s="41">
-        <f>IF($L53="","",INDEX(Flux!$K$2:$K$35,$L53))</f>
-        <v/>
-      </c>
-      <c r="J53" s="41">
-        <f>IF($L53="","",INDEX(Flux!$L$2:$L$35,$L53))</f>
-        <v/>
-      </c>
-      <c r="L53" s="42">
-        <f>IFERROR(MATCH(38,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M53" s="42">
-        <f>IF(L53="","",INDEX(Flux!$C$2:$C$35,L53))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" hidden="1" outlineLevel="1" ht="22" customHeight="1">
-      <c r="B54" s="38">
-        <f>IF($L54="","",INDEX(Flux!$D$2:$D$35,$L54))</f>
-        <v/>
-      </c>
-      <c r="C54" s="39">
-        <f>IF($L54="","",INDEX(Flux!$E$2:$E$35,$L54))</f>
-        <v/>
-      </c>
-      <c r="D54" s="40">
-        <f>IF($L54="","",INDEX(Flux!$F$2:$F$35,$L54))</f>
-        <v/>
-      </c>
-      <c r="E54" s="41">
-        <f>IF($L54="","",INDEX(Flux!$G$2:$G$35,$L54))</f>
-        <v/>
-      </c>
-      <c r="F54" s="41">
-        <f>IF($L54="","",INDEX(Flux!$H$2:$H$35,$L54))</f>
-        <v/>
-      </c>
-      <c r="G54" s="41">
-        <f>IF($L54="","",INDEX(Flux!$I$2:$I$35,$L54))</f>
-        <v/>
-      </c>
-      <c r="H54" s="41">
-        <f>IF($L54="","",INDEX(Flux!$J$2:$J$35,$L54))</f>
-        <v/>
-      </c>
-      <c r="I54" s="41">
-        <f>IF($L54="","",INDEX(Flux!$K$2:$K$35,$L54))</f>
-        <v/>
-      </c>
-      <c r="J54" s="41">
-        <f>IF($L54="","",INDEX(Flux!$L$2:$L$35,$L54))</f>
-        <v/>
-      </c>
-      <c r="L54" s="42">
-        <f>IFERROR(MATCH(39,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M54" s="42">
-        <f>IF(L54="","",INDEX(Flux!$C$2:$C$35,L54))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" hidden="1" outlineLevel="1" ht="22" customHeight="1">
-      <c r="B55" s="38">
-        <f>IF($L55="","",INDEX(Flux!$D$2:$D$35,$L55))</f>
-        <v/>
-      </c>
-      <c r="C55" s="39">
-        <f>IF($L55="","",INDEX(Flux!$E$2:$E$35,$L55))</f>
-        <v/>
-      </c>
-      <c r="D55" s="40">
-        <f>IF($L55="","",INDEX(Flux!$F$2:$F$35,$L55))</f>
-        <v/>
-      </c>
-      <c r="E55" s="41">
-        <f>IF($L55="","",INDEX(Flux!$G$2:$G$35,$L55))</f>
-        <v/>
-      </c>
-      <c r="F55" s="41">
-        <f>IF($L55="","",INDEX(Flux!$H$2:$H$35,$L55))</f>
-        <v/>
-      </c>
-      <c r="G55" s="41">
-        <f>IF($L55="","",INDEX(Flux!$I$2:$I$35,$L55))</f>
-        <v/>
-      </c>
-      <c r="H55" s="41">
-        <f>IF($L55="","",INDEX(Flux!$J$2:$J$35,$L55))</f>
-        <v/>
-      </c>
-      <c r="I55" s="41">
-        <f>IF($L55="","",INDEX(Flux!$K$2:$K$35,$L55))</f>
-        <v/>
-      </c>
-      <c r="J55" s="41">
-        <f>IF($L55="","",INDEX(Flux!$L$2:$L$35,$L55))</f>
-        <v/>
-      </c>
-      <c r="L55" s="42">
-        <f>IFERROR(MATCH(40,Flux!$B$2:$B$35,0),"")</f>
-        <v/>
-      </c>
-      <c r="M55" s="42">
-        <f>IF(L55="","",INDEX(Flux!$C$2:$C$35,L55))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="B56" s="43">
-        <f>IF(MAX(Flux!$B$2:$B$35)&gt;26,"⚠  Le devis contient plus de 26 lignes : cliquer sur le [+] dans la marge gauche pour afficher les lignes masquées.","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="8" customHeight="1"/>
+      <c r="B18" s="40">
+        <f>IF($L18=0,"",INDEX(Flux!$D$2:$D$35,$L18))</f>
+        <v/>
+      </c>
+      <c r="C18" s="41">
+        <f>IF($L18=0,"",INDEX(Flux!$E$2:$E$35,$L18))</f>
+        <v/>
+      </c>
+      <c r="D18" s="42">
+        <f>IF($L18=0,"",INDEX(Flux!$F$2:$F$35,$L18))</f>
+        <v/>
+      </c>
+      <c r="E18" s="43">
+        <f>IF($L18=0,"",INDEX(Flux!$G$2:$G$35,$L18))</f>
+        <v/>
+      </c>
+      <c r="F18" s="43">
+        <f>IF($L18=0,"",INDEX(Flux!$H$2:$H$35,$L18))</f>
+        <v/>
+      </c>
+      <c r="G18" s="43">
+        <f>IF($L18=0,"",INDEX(Flux!$I$2:$I$35,$L18))</f>
+        <v/>
+      </c>
+      <c r="H18" s="43">
+        <f>IF($L18=0,"",INDEX(Flux!$J$2:$J$35,$L18))</f>
+        <v/>
+      </c>
+      <c r="I18" s="43">
+        <f>IF($L18=0,"",INDEX(Flux!$K$2:$K$35,$L18))</f>
+        <v/>
+      </c>
+      <c r="J18" s="43">
+        <f>IF($L18=0,"",INDEX(Flux!$L$2:$L$35,$L18))</f>
+        <v/>
+      </c>
+      <c r="L18" s="39">
+        <f>IFERROR(MATCH(3,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M18" s="39">
+        <f>IF(L18=0,"",INDEX(Flux!$C$2:$C$35,L18))</f>
+        <v/>
+      </c>
+      <c r="N18" s="39">
+        <f>IF(L18&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" hidden="1" ht="22" customHeight="1">
+      <c r="B19" s="40">
+        <f>IF($L19=0,"",INDEX(Flux!$D$2:$D$35,$L19))</f>
+        <v/>
+      </c>
+      <c r="C19" s="41">
+        <f>IF($L19=0,"",INDEX(Flux!$E$2:$E$35,$L19))</f>
+        <v/>
+      </c>
+      <c r="D19" s="42">
+        <f>IF($L19=0,"",INDEX(Flux!$F$2:$F$35,$L19))</f>
+        <v/>
+      </c>
+      <c r="E19" s="43">
+        <f>IF($L19=0,"",INDEX(Flux!$G$2:$G$35,$L19))</f>
+        <v/>
+      </c>
+      <c r="F19" s="43">
+        <f>IF($L19=0,"",INDEX(Flux!$H$2:$H$35,$L19))</f>
+        <v/>
+      </c>
+      <c r="G19" s="43">
+        <f>IF($L19=0,"",INDEX(Flux!$I$2:$I$35,$L19))</f>
+        <v/>
+      </c>
+      <c r="H19" s="43">
+        <f>IF($L19=0,"",INDEX(Flux!$J$2:$J$35,$L19))</f>
+        <v/>
+      </c>
+      <c r="I19" s="43">
+        <f>IF($L19=0,"",INDEX(Flux!$K$2:$K$35,$L19))</f>
+        <v/>
+      </c>
+      <c r="J19" s="43">
+        <f>IF($L19=0,"",INDEX(Flux!$L$2:$L$35,$L19))</f>
+        <v/>
+      </c>
+      <c r="L19" s="39">
+        <f>IFERROR(MATCH(4,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M19" s="39">
+        <f>IF(L19=0,"",INDEX(Flux!$C$2:$C$35,L19))</f>
+        <v/>
+      </c>
+      <c r="N19" s="39">
+        <f>IF(L19&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" hidden="1" ht="22" customHeight="1">
+      <c r="B20" s="40">
+        <f>IF($L20=0,"",INDEX(Flux!$D$2:$D$35,$L20))</f>
+        <v/>
+      </c>
+      <c r="C20" s="41">
+        <f>IF($L20=0,"",INDEX(Flux!$E$2:$E$35,$L20))</f>
+        <v/>
+      </c>
+      <c r="D20" s="42">
+        <f>IF($L20=0,"",INDEX(Flux!$F$2:$F$35,$L20))</f>
+        <v/>
+      </c>
+      <c r="E20" s="43">
+        <f>IF($L20=0,"",INDEX(Flux!$G$2:$G$35,$L20))</f>
+        <v/>
+      </c>
+      <c r="F20" s="43">
+        <f>IF($L20=0,"",INDEX(Flux!$H$2:$H$35,$L20))</f>
+        <v/>
+      </c>
+      <c r="G20" s="43">
+        <f>IF($L20=0,"",INDEX(Flux!$I$2:$I$35,$L20))</f>
+        <v/>
+      </c>
+      <c r="H20" s="43">
+        <f>IF($L20=0,"",INDEX(Flux!$J$2:$J$35,$L20))</f>
+        <v/>
+      </c>
+      <c r="I20" s="43">
+        <f>IF($L20=0,"",INDEX(Flux!$K$2:$K$35,$L20))</f>
+        <v/>
+      </c>
+      <c r="J20" s="43">
+        <f>IF($L20=0,"",INDEX(Flux!$L$2:$L$35,$L20))</f>
+        <v/>
+      </c>
+      <c r="L20" s="39">
+        <f>IFERROR(MATCH(5,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M20" s="39">
+        <f>IF(L20=0,"",INDEX(Flux!$C$2:$C$35,L20))</f>
+        <v/>
+      </c>
+      <c r="N20" s="39">
+        <f>IF(L20&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" hidden="1" ht="22" customHeight="1">
+      <c r="B21" s="40">
+        <f>IF($L21=0,"",INDEX(Flux!$D$2:$D$35,$L21))</f>
+        <v/>
+      </c>
+      <c r="C21" s="41">
+        <f>IF($L21=0,"",INDEX(Flux!$E$2:$E$35,$L21))</f>
+        <v/>
+      </c>
+      <c r="D21" s="42">
+        <f>IF($L21=0,"",INDEX(Flux!$F$2:$F$35,$L21))</f>
+        <v/>
+      </c>
+      <c r="E21" s="43">
+        <f>IF($L21=0,"",INDEX(Flux!$G$2:$G$35,$L21))</f>
+        <v/>
+      </c>
+      <c r="F21" s="43">
+        <f>IF($L21=0,"",INDEX(Flux!$H$2:$H$35,$L21))</f>
+        <v/>
+      </c>
+      <c r="G21" s="43">
+        <f>IF($L21=0,"",INDEX(Flux!$I$2:$I$35,$L21))</f>
+        <v/>
+      </c>
+      <c r="H21" s="43">
+        <f>IF($L21=0,"",INDEX(Flux!$J$2:$J$35,$L21))</f>
+        <v/>
+      </c>
+      <c r="I21" s="43">
+        <f>IF($L21=0,"",INDEX(Flux!$K$2:$K$35,$L21))</f>
+        <v/>
+      </c>
+      <c r="J21" s="43">
+        <f>IF($L21=0,"",INDEX(Flux!$L$2:$L$35,$L21))</f>
+        <v/>
+      </c>
+      <c r="L21" s="39">
+        <f>IFERROR(MATCH(6,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M21" s="39">
+        <f>IF(L21=0,"",INDEX(Flux!$C$2:$C$35,L21))</f>
+        <v/>
+      </c>
+      <c r="N21" s="39">
+        <f>IF(L21&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" hidden="1" ht="22" customHeight="1">
+      <c r="B22" s="40">
+        <f>IF($L22=0,"",INDEX(Flux!$D$2:$D$35,$L22))</f>
+        <v/>
+      </c>
+      <c r="C22" s="41">
+        <f>IF($L22=0,"",INDEX(Flux!$E$2:$E$35,$L22))</f>
+        <v/>
+      </c>
+      <c r="D22" s="42">
+        <f>IF($L22=0,"",INDEX(Flux!$F$2:$F$35,$L22))</f>
+        <v/>
+      </c>
+      <c r="E22" s="43">
+        <f>IF($L22=0,"",INDEX(Flux!$G$2:$G$35,$L22))</f>
+        <v/>
+      </c>
+      <c r="F22" s="43">
+        <f>IF($L22=0,"",INDEX(Flux!$H$2:$H$35,$L22))</f>
+        <v/>
+      </c>
+      <c r="G22" s="43">
+        <f>IF($L22=0,"",INDEX(Flux!$I$2:$I$35,$L22))</f>
+        <v/>
+      </c>
+      <c r="H22" s="43">
+        <f>IF($L22=0,"",INDEX(Flux!$J$2:$J$35,$L22))</f>
+        <v/>
+      </c>
+      <c r="I22" s="43">
+        <f>IF($L22=0,"",INDEX(Flux!$K$2:$K$35,$L22))</f>
+        <v/>
+      </c>
+      <c r="J22" s="43">
+        <f>IF($L22=0,"",INDEX(Flux!$L$2:$L$35,$L22))</f>
+        <v/>
+      </c>
+      <c r="L22" s="39">
+        <f>IFERROR(MATCH(7,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M22" s="39">
+        <f>IF(L22=0,"",INDEX(Flux!$C$2:$C$35,L22))</f>
+        <v/>
+      </c>
+      <c r="N22" s="39">
+        <f>IF(L22&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" hidden="1" ht="22" customHeight="1">
+      <c r="B23" s="40">
+        <f>IF($L23=0,"",INDEX(Flux!$D$2:$D$35,$L23))</f>
+        <v/>
+      </c>
+      <c r="C23" s="41">
+        <f>IF($L23=0,"",INDEX(Flux!$E$2:$E$35,$L23))</f>
+        <v/>
+      </c>
+      <c r="D23" s="42">
+        <f>IF($L23=0,"",INDEX(Flux!$F$2:$F$35,$L23))</f>
+        <v/>
+      </c>
+      <c r="E23" s="43">
+        <f>IF($L23=0,"",INDEX(Flux!$G$2:$G$35,$L23))</f>
+        <v/>
+      </c>
+      <c r="F23" s="43">
+        <f>IF($L23=0,"",INDEX(Flux!$H$2:$H$35,$L23))</f>
+        <v/>
+      </c>
+      <c r="G23" s="43">
+        <f>IF($L23=0,"",INDEX(Flux!$I$2:$I$35,$L23))</f>
+        <v/>
+      </c>
+      <c r="H23" s="43">
+        <f>IF($L23=0,"",INDEX(Flux!$J$2:$J$35,$L23))</f>
+        <v/>
+      </c>
+      <c r="I23" s="43">
+        <f>IF($L23=0,"",INDEX(Flux!$K$2:$K$35,$L23))</f>
+        <v/>
+      </c>
+      <c r="J23" s="43">
+        <f>IF($L23=0,"",INDEX(Flux!$L$2:$L$35,$L23))</f>
+        <v/>
+      </c>
+      <c r="L23" s="39">
+        <f>IFERROR(MATCH(8,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M23" s="39">
+        <f>IF(L23=0,"",INDEX(Flux!$C$2:$C$35,L23))</f>
+        <v/>
+      </c>
+      <c r="N23" s="39">
+        <f>IF(L23&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" hidden="1" ht="22" customHeight="1">
+      <c r="B24" s="40">
+        <f>IF($L24=0,"",INDEX(Flux!$D$2:$D$35,$L24))</f>
+        <v/>
+      </c>
+      <c r="C24" s="41">
+        <f>IF($L24=0,"",INDEX(Flux!$E$2:$E$35,$L24))</f>
+        <v/>
+      </c>
+      <c r="D24" s="42">
+        <f>IF($L24=0,"",INDEX(Flux!$F$2:$F$35,$L24))</f>
+        <v/>
+      </c>
+      <c r="E24" s="43">
+        <f>IF($L24=0,"",INDEX(Flux!$G$2:$G$35,$L24))</f>
+        <v/>
+      </c>
+      <c r="F24" s="43">
+        <f>IF($L24=0,"",INDEX(Flux!$H$2:$H$35,$L24))</f>
+        <v/>
+      </c>
+      <c r="G24" s="43">
+        <f>IF($L24=0,"",INDEX(Flux!$I$2:$I$35,$L24))</f>
+        <v/>
+      </c>
+      <c r="H24" s="43">
+        <f>IF($L24=0,"",INDEX(Flux!$J$2:$J$35,$L24))</f>
+        <v/>
+      </c>
+      <c r="I24" s="43">
+        <f>IF($L24=0,"",INDEX(Flux!$K$2:$K$35,$L24))</f>
+        <v/>
+      </c>
+      <c r="J24" s="43">
+        <f>IF($L24=0,"",INDEX(Flux!$L$2:$L$35,$L24))</f>
+        <v/>
+      </c>
+      <c r="L24" s="39">
+        <f>IFERROR(MATCH(9,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M24" s="39">
+        <f>IF(L24=0,"",INDEX(Flux!$C$2:$C$35,L24))</f>
+        <v/>
+      </c>
+      <c r="N24" s="39">
+        <f>IF(L24&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" hidden="1" ht="22" customHeight="1">
+      <c r="B25" s="40">
+        <f>IF($L25=0,"",INDEX(Flux!$D$2:$D$35,$L25))</f>
+        <v/>
+      </c>
+      <c r="C25" s="41">
+        <f>IF($L25=0,"",INDEX(Flux!$E$2:$E$35,$L25))</f>
+        <v/>
+      </c>
+      <c r="D25" s="42">
+        <f>IF($L25=0,"",INDEX(Flux!$F$2:$F$35,$L25))</f>
+        <v/>
+      </c>
+      <c r="E25" s="43">
+        <f>IF($L25=0,"",INDEX(Flux!$G$2:$G$35,$L25))</f>
+        <v/>
+      </c>
+      <c r="F25" s="43">
+        <f>IF($L25=0,"",INDEX(Flux!$H$2:$H$35,$L25))</f>
+        <v/>
+      </c>
+      <c r="G25" s="43">
+        <f>IF($L25=0,"",INDEX(Flux!$I$2:$I$35,$L25))</f>
+        <v/>
+      </c>
+      <c r="H25" s="43">
+        <f>IF($L25=0,"",INDEX(Flux!$J$2:$J$35,$L25))</f>
+        <v/>
+      </c>
+      <c r="I25" s="43">
+        <f>IF($L25=0,"",INDEX(Flux!$K$2:$K$35,$L25))</f>
+        <v/>
+      </c>
+      <c r="J25" s="43">
+        <f>IF($L25=0,"",INDEX(Flux!$L$2:$L$35,$L25))</f>
+        <v/>
+      </c>
+      <c r="L25" s="39">
+        <f>IFERROR(MATCH(10,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M25" s="39">
+        <f>IF(L25=0,"",INDEX(Flux!$C$2:$C$35,L25))</f>
+        <v/>
+      </c>
+      <c r="N25" s="39">
+        <f>IF(L25&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" hidden="1" ht="22" customHeight="1">
+      <c r="B26" s="40">
+        <f>IF($L26=0,"",INDEX(Flux!$D$2:$D$35,$L26))</f>
+        <v/>
+      </c>
+      <c r="C26" s="41">
+        <f>IF($L26=0,"",INDEX(Flux!$E$2:$E$35,$L26))</f>
+        <v/>
+      </c>
+      <c r="D26" s="42">
+        <f>IF($L26=0,"",INDEX(Flux!$F$2:$F$35,$L26))</f>
+        <v/>
+      </c>
+      <c r="E26" s="43">
+        <f>IF($L26=0,"",INDEX(Flux!$G$2:$G$35,$L26))</f>
+        <v/>
+      </c>
+      <c r="F26" s="43">
+        <f>IF($L26=0,"",INDEX(Flux!$H$2:$H$35,$L26))</f>
+        <v/>
+      </c>
+      <c r="G26" s="43">
+        <f>IF($L26=0,"",INDEX(Flux!$I$2:$I$35,$L26))</f>
+        <v/>
+      </c>
+      <c r="H26" s="43">
+        <f>IF($L26=0,"",INDEX(Flux!$J$2:$J$35,$L26))</f>
+        <v/>
+      </c>
+      <c r="I26" s="43">
+        <f>IF($L26=0,"",INDEX(Flux!$K$2:$K$35,$L26))</f>
+        <v/>
+      </c>
+      <c r="J26" s="43">
+        <f>IF($L26=0,"",INDEX(Flux!$L$2:$L$35,$L26))</f>
+        <v/>
+      </c>
+      <c r="L26" s="39">
+        <f>IFERROR(MATCH(11,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M26" s="39">
+        <f>IF(L26=0,"",INDEX(Flux!$C$2:$C$35,L26))</f>
+        <v/>
+      </c>
+      <c r="N26" s="39">
+        <f>IF(L26&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" hidden="1" ht="22" customHeight="1">
+      <c r="B27" s="40">
+        <f>IF($L27=0,"",INDEX(Flux!$D$2:$D$35,$L27))</f>
+        <v/>
+      </c>
+      <c r="C27" s="41">
+        <f>IF($L27=0,"",INDEX(Flux!$E$2:$E$35,$L27))</f>
+        <v/>
+      </c>
+      <c r="D27" s="42">
+        <f>IF($L27=0,"",INDEX(Flux!$F$2:$F$35,$L27))</f>
+        <v/>
+      </c>
+      <c r="E27" s="43">
+        <f>IF($L27=0,"",INDEX(Flux!$G$2:$G$35,$L27))</f>
+        <v/>
+      </c>
+      <c r="F27" s="43">
+        <f>IF($L27=0,"",INDEX(Flux!$H$2:$H$35,$L27))</f>
+        <v/>
+      </c>
+      <c r="G27" s="43">
+        <f>IF($L27=0,"",INDEX(Flux!$I$2:$I$35,$L27))</f>
+        <v/>
+      </c>
+      <c r="H27" s="43">
+        <f>IF($L27=0,"",INDEX(Flux!$J$2:$J$35,$L27))</f>
+        <v/>
+      </c>
+      <c r="I27" s="43">
+        <f>IF($L27=0,"",INDEX(Flux!$K$2:$K$35,$L27))</f>
+        <v/>
+      </c>
+      <c r="J27" s="43">
+        <f>IF($L27=0,"",INDEX(Flux!$L$2:$L$35,$L27))</f>
+        <v/>
+      </c>
+      <c r="L27" s="39">
+        <f>IFERROR(MATCH(12,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M27" s="39">
+        <f>IF(L27=0,"",INDEX(Flux!$C$2:$C$35,L27))</f>
+        <v/>
+      </c>
+      <c r="N27" s="39">
+        <f>IF(L27&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" hidden="1" ht="22" customHeight="1">
+      <c r="B28" s="40">
+        <f>IF($L28=0,"",INDEX(Flux!$D$2:$D$35,$L28))</f>
+        <v/>
+      </c>
+      <c r="C28" s="41">
+        <f>IF($L28=0,"",INDEX(Flux!$E$2:$E$35,$L28))</f>
+        <v/>
+      </c>
+      <c r="D28" s="42">
+        <f>IF($L28=0,"",INDEX(Flux!$F$2:$F$35,$L28))</f>
+        <v/>
+      </c>
+      <c r="E28" s="43">
+        <f>IF($L28=0,"",INDEX(Flux!$G$2:$G$35,$L28))</f>
+        <v/>
+      </c>
+      <c r="F28" s="43">
+        <f>IF($L28=0,"",INDEX(Flux!$H$2:$H$35,$L28))</f>
+        <v/>
+      </c>
+      <c r="G28" s="43">
+        <f>IF($L28=0,"",INDEX(Flux!$I$2:$I$35,$L28))</f>
+        <v/>
+      </c>
+      <c r="H28" s="43">
+        <f>IF($L28=0,"",INDEX(Flux!$J$2:$J$35,$L28))</f>
+        <v/>
+      </c>
+      <c r="I28" s="43">
+        <f>IF($L28=0,"",INDEX(Flux!$K$2:$K$35,$L28))</f>
+        <v/>
+      </c>
+      <c r="J28" s="43">
+        <f>IF($L28=0,"",INDEX(Flux!$L$2:$L$35,$L28))</f>
+        <v/>
+      </c>
+      <c r="L28" s="39">
+        <f>IFERROR(MATCH(13,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M28" s="39">
+        <f>IF(L28=0,"",INDEX(Flux!$C$2:$C$35,L28))</f>
+        <v/>
+      </c>
+      <c r="N28" s="39">
+        <f>IF(L28&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" hidden="1" ht="22" customHeight="1">
+      <c r="B29" s="40">
+        <f>IF($L29=0,"",INDEX(Flux!$D$2:$D$35,$L29))</f>
+        <v/>
+      </c>
+      <c r="C29" s="41">
+        <f>IF($L29=0,"",INDEX(Flux!$E$2:$E$35,$L29))</f>
+        <v/>
+      </c>
+      <c r="D29" s="42">
+        <f>IF($L29=0,"",INDEX(Flux!$F$2:$F$35,$L29))</f>
+        <v/>
+      </c>
+      <c r="E29" s="43">
+        <f>IF($L29=0,"",INDEX(Flux!$G$2:$G$35,$L29))</f>
+        <v/>
+      </c>
+      <c r="F29" s="43">
+        <f>IF($L29=0,"",INDEX(Flux!$H$2:$H$35,$L29))</f>
+        <v/>
+      </c>
+      <c r="G29" s="43">
+        <f>IF($L29=0,"",INDEX(Flux!$I$2:$I$35,$L29))</f>
+        <v/>
+      </c>
+      <c r="H29" s="43">
+        <f>IF($L29=0,"",INDEX(Flux!$J$2:$J$35,$L29))</f>
+        <v/>
+      </c>
+      <c r="I29" s="43">
+        <f>IF($L29=0,"",INDEX(Flux!$K$2:$K$35,$L29))</f>
+        <v/>
+      </c>
+      <c r="J29" s="43">
+        <f>IF($L29=0,"",INDEX(Flux!$L$2:$L$35,$L29))</f>
+        <v/>
+      </c>
+      <c r="L29" s="39">
+        <f>IFERROR(MATCH(14,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M29" s="39">
+        <f>IF(L29=0,"",INDEX(Flux!$C$2:$C$35,L29))</f>
+        <v/>
+      </c>
+      <c r="N29" s="39">
+        <f>IF(L29&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" hidden="1" ht="22" customHeight="1">
+      <c r="B30" s="40">
+        <f>IF($L30=0,"",INDEX(Flux!$D$2:$D$35,$L30))</f>
+        <v/>
+      </c>
+      <c r="C30" s="41">
+        <f>IF($L30=0,"",INDEX(Flux!$E$2:$E$35,$L30))</f>
+        <v/>
+      </c>
+      <c r="D30" s="42">
+        <f>IF($L30=0,"",INDEX(Flux!$F$2:$F$35,$L30))</f>
+        <v/>
+      </c>
+      <c r="E30" s="43">
+        <f>IF($L30=0,"",INDEX(Flux!$G$2:$G$35,$L30))</f>
+        <v/>
+      </c>
+      <c r="F30" s="43">
+        <f>IF($L30=0,"",INDEX(Flux!$H$2:$H$35,$L30))</f>
+        <v/>
+      </c>
+      <c r="G30" s="43">
+        <f>IF($L30=0,"",INDEX(Flux!$I$2:$I$35,$L30))</f>
+        <v/>
+      </c>
+      <c r="H30" s="43">
+        <f>IF($L30=0,"",INDEX(Flux!$J$2:$J$35,$L30))</f>
+        <v/>
+      </c>
+      <c r="I30" s="43">
+        <f>IF($L30=0,"",INDEX(Flux!$K$2:$K$35,$L30))</f>
+        <v/>
+      </c>
+      <c r="J30" s="43">
+        <f>IF($L30=0,"",INDEX(Flux!$L$2:$L$35,$L30))</f>
+        <v/>
+      </c>
+      <c r="L30" s="39">
+        <f>IFERROR(MATCH(15,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M30" s="39">
+        <f>IF(L30=0,"",INDEX(Flux!$C$2:$C$35,L30))</f>
+        <v/>
+      </c>
+      <c r="N30" s="39">
+        <f>IF(L30&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" hidden="1" ht="22" customHeight="1">
+      <c r="B31" s="40">
+        <f>IF($L31=0,"",INDEX(Flux!$D$2:$D$35,$L31))</f>
+        <v/>
+      </c>
+      <c r="C31" s="41">
+        <f>IF($L31=0,"",INDEX(Flux!$E$2:$E$35,$L31))</f>
+        <v/>
+      </c>
+      <c r="D31" s="42">
+        <f>IF($L31=0,"",INDEX(Flux!$F$2:$F$35,$L31))</f>
+        <v/>
+      </c>
+      <c r="E31" s="43">
+        <f>IF($L31=0,"",INDEX(Flux!$G$2:$G$35,$L31))</f>
+        <v/>
+      </c>
+      <c r="F31" s="43">
+        <f>IF($L31=0,"",INDEX(Flux!$H$2:$H$35,$L31))</f>
+        <v/>
+      </c>
+      <c r="G31" s="43">
+        <f>IF($L31=0,"",INDEX(Flux!$I$2:$I$35,$L31))</f>
+        <v/>
+      </c>
+      <c r="H31" s="43">
+        <f>IF($L31=0,"",INDEX(Flux!$J$2:$J$35,$L31))</f>
+        <v/>
+      </c>
+      <c r="I31" s="43">
+        <f>IF($L31=0,"",INDEX(Flux!$K$2:$K$35,$L31))</f>
+        <v/>
+      </c>
+      <c r="J31" s="43">
+        <f>IF($L31=0,"",INDEX(Flux!$L$2:$L$35,$L31))</f>
+        <v/>
+      </c>
+      <c r="L31" s="39">
+        <f>IFERROR(MATCH(16,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M31" s="39">
+        <f>IF(L31=0,"",INDEX(Flux!$C$2:$C$35,L31))</f>
+        <v/>
+      </c>
+      <c r="N31" s="39">
+        <f>IF(L31&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" hidden="1" ht="22" customHeight="1">
+      <c r="B32" s="40">
+        <f>IF($L32=0,"",INDEX(Flux!$D$2:$D$35,$L32))</f>
+        <v/>
+      </c>
+      <c r="C32" s="41">
+        <f>IF($L32=0,"",INDEX(Flux!$E$2:$E$35,$L32))</f>
+        <v/>
+      </c>
+      <c r="D32" s="42">
+        <f>IF($L32=0,"",INDEX(Flux!$F$2:$F$35,$L32))</f>
+        <v/>
+      </c>
+      <c r="E32" s="43">
+        <f>IF($L32=0,"",INDEX(Flux!$G$2:$G$35,$L32))</f>
+        <v/>
+      </c>
+      <c r="F32" s="43">
+        <f>IF($L32=0,"",INDEX(Flux!$H$2:$H$35,$L32))</f>
+        <v/>
+      </c>
+      <c r="G32" s="43">
+        <f>IF($L32=0,"",INDEX(Flux!$I$2:$I$35,$L32))</f>
+        <v/>
+      </c>
+      <c r="H32" s="43">
+        <f>IF($L32=0,"",INDEX(Flux!$J$2:$J$35,$L32))</f>
+        <v/>
+      </c>
+      <c r="I32" s="43">
+        <f>IF($L32=0,"",INDEX(Flux!$K$2:$K$35,$L32))</f>
+        <v/>
+      </c>
+      <c r="J32" s="43">
+        <f>IF($L32=0,"",INDEX(Flux!$L$2:$L$35,$L32))</f>
+        <v/>
+      </c>
+      <c r="L32" s="39">
+        <f>IFERROR(MATCH(17,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M32" s="39">
+        <f>IF(L32=0,"",INDEX(Flux!$C$2:$C$35,L32))</f>
+        <v/>
+      </c>
+      <c r="N32" s="39">
+        <f>IF(L32&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" hidden="1" ht="22" customHeight="1">
+      <c r="B33" s="40">
+        <f>IF($L33=0,"",INDEX(Flux!$D$2:$D$35,$L33))</f>
+        <v/>
+      </c>
+      <c r="C33" s="41">
+        <f>IF($L33=0,"",INDEX(Flux!$E$2:$E$35,$L33))</f>
+        <v/>
+      </c>
+      <c r="D33" s="42">
+        <f>IF($L33=0,"",INDEX(Flux!$F$2:$F$35,$L33))</f>
+        <v/>
+      </c>
+      <c r="E33" s="43">
+        <f>IF($L33=0,"",INDEX(Flux!$G$2:$G$35,$L33))</f>
+        <v/>
+      </c>
+      <c r="F33" s="43">
+        <f>IF($L33=0,"",INDEX(Flux!$H$2:$H$35,$L33))</f>
+        <v/>
+      </c>
+      <c r="G33" s="43">
+        <f>IF($L33=0,"",INDEX(Flux!$I$2:$I$35,$L33))</f>
+        <v/>
+      </c>
+      <c r="H33" s="43">
+        <f>IF($L33=0,"",INDEX(Flux!$J$2:$J$35,$L33))</f>
+        <v/>
+      </c>
+      <c r="I33" s="43">
+        <f>IF($L33=0,"",INDEX(Flux!$K$2:$K$35,$L33))</f>
+        <v/>
+      </c>
+      <c r="J33" s="43">
+        <f>IF($L33=0,"",INDEX(Flux!$L$2:$L$35,$L33))</f>
+        <v/>
+      </c>
+      <c r="L33" s="39">
+        <f>IFERROR(MATCH(18,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M33" s="39">
+        <f>IF(L33=0,"",INDEX(Flux!$C$2:$C$35,L33))</f>
+        <v/>
+      </c>
+      <c r="N33" s="39">
+        <f>IF(L33&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" hidden="1" ht="22" customHeight="1">
+      <c r="B34" s="40">
+        <f>IF($L34=0,"",INDEX(Flux!$D$2:$D$35,$L34))</f>
+        <v/>
+      </c>
+      <c r="C34" s="41">
+        <f>IF($L34=0,"",INDEX(Flux!$E$2:$E$35,$L34))</f>
+        <v/>
+      </c>
+      <c r="D34" s="42">
+        <f>IF($L34=0,"",INDEX(Flux!$F$2:$F$35,$L34))</f>
+        <v/>
+      </c>
+      <c r="E34" s="43">
+        <f>IF($L34=0,"",INDEX(Flux!$G$2:$G$35,$L34))</f>
+        <v/>
+      </c>
+      <c r="F34" s="43">
+        <f>IF($L34=0,"",INDEX(Flux!$H$2:$H$35,$L34))</f>
+        <v/>
+      </c>
+      <c r="G34" s="43">
+        <f>IF($L34=0,"",INDEX(Flux!$I$2:$I$35,$L34))</f>
+        <v/>
+      </c>
+      <c r="H34" s="43">
+        <f>IF($L34=0,"",INDEX(Flux!$J$2:$J$35,$L34))</f>
+        <v/>
+      </c>
+      <c r="I34" s="43">
+        <f>IF($L34=0,"",INDEX(Flux!$K$2:$K$35,$L34))</f>
+        <v/>
+      </c>
+      <c r="J34" s="43">
+        <f>IF($L34=0,"",INDEX(Flux!$L$2:$L$35,$L34))</f>
+        <v/>
+      </c>
+      <c r="L34" s="39">
+        <f>IFERROR(MATCH(19,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M34" s="39">
+        <f>IF(L34=0,"",INDEX(Flux!$C$2:$C$35,L34))</f>
+        <v/>
+      </c>
+      <c r="N34" s="39">
+        <f>IF(L34&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" hidden="1" ht="22" customHeight="1">
+      <c r="B35" s="40">
+        <f>IF($L35=0,"",INDEX(Flux!$D$2:$D$35,$L35))</f>
+        <v/>
+      </c>
+      <c r="C35" s="41">
+        <f>IF($L35=0,"",INDEX(Flux!$E$2:$E$35,$L35))</f>
+        <v/>
+      </c>
+      <c r="D35" s="42">
+        <f>IF($L35=0,"",INDEX(Flux!$F$2:$F$35,$L35))</f>
+        <v/>
+      </c>
+      <c r="E35" s="43">
+        <f>IF($L35=0,"",INDEX(Flux!$G$2:$G$35,$L35))</f>
+        <v/>
+      </c>
+      <c r="F35" s="43">
+        <f>IF($L35=0,"",INDEX(Flux!$H$2:$H$35,$L35))</f>
+        <v/>
+      </c>
+      <c r="G35" s="43">
+        <f>IF($L35=0,"",INDEX(Flux!$I$2:$I$35,$L35))</f>
+        <v/>
+      </c>
+      <c r="H35" s="43">
+        <f>IF($L35=0,"",INDEX(Flux!$J$2:$J$35,$L35))</f>
+        <v/>
+      </c>
+      <c r="I35" s="43">
+        <f>IF($L35=0,"",INDEX(Flux!$K$2:$K$35,$L35))</f>
+        <v/>
+      </c>
+      <c r="J35" s="43">
+        <f>IF($L35=0,"",INDEX(Flux!$L$2:$L$35,$L35))</f>
+        <v/>
+      </c>
+      <c r="L35" s="39">
+        <f>IFERROR(MATCH(20,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M35" s="39">
+        <f>IF(L35=0,"",INDEX(Flux!$C$2:$C$35,L35))</f>
+        <v/>
+      </c>
+      <c r="N35" s="39">
+        <f>IF(L35&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" hidden="1" ht="22" customHeight="1">
+      <c r="B36" s="40">
+        <f>IF($L36=0,"",INDEX(Flux!$D$2:$D$35,$L36))</f>
+        <v/>
+      </c>
+      <c r="C36" s="41">
+        <f>IF($L36=0,"",INDEX(Flux!$E$2:$E$35,$L36))</f>
+        <v/>
+      </c>
+      <c r="D36" s="42">
+        <f>IF($L36=0,"",INDEX(Flux!$F$2:$F$35,$L36))</f>
+        <v/>
+      </c>
+      <c r="E36" s="43">
+        <f>IF($L36=0,"",INDEX(Flux!$G$2:$G$35,$L36))</f>
+        <v/>
+      </c>
+      <c r="F36" s="43">
+        <f>IF($L36=0,"",INDEX(Flux!$H$2:$H$35,$L36))</f>
+        <v/>
+      </c>
+      <c r="G36" s="43">
+        <f>IF($L36=0,"",INDEX(Flux!$I$2:$I$35,$L36))</f>
+        <v/>
+      </c>
+      <c r="H36" s="43">
+        <f>IF($L36=0,"",INDEX(Flux!$J$2:$J$35,$L36))</f>
+        <v/>
+      </c>
+      <c r="I36" s="43">
+        <f>IF($L36=0,"",INDEX(Flux!$K$2:$K$35,$L36))</f>
+        <v/>
+      </c>
+      <c r="J36" s="43">
+        <f>IF($L36=0,"",INDEX(Flux!$L$2:$L$35,$L36))</f>
+        <v/>
+      </c>
+      <c r="L36" s="39">
+        <f>IFERROR(MATCH(21,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M36" s="39">
+        <f>IF(L36=0,"",INDEX(Flux!$C$2:$C$35,L36))</f>
+        <v/>
+      </c>
+      <c r="N36" s="39">
+        <f>IF(L36&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" hidden="1" ht="22" customHeight="1">
+      <c r="B37" s="40">
+        <f>IF($L37=0,"",INDEX(Flux!$D$2:$D$35,$L37))</f>
+        <v/>
+      </c>
+      <c r="C37" s="41">
+        <f>IF($L37=0,"",INDEX(Flux!$E$2:$E$35,$L37))</f>
+        <v/>
+      </c>
+      <c r="D37" s="42">
+        <f>IF($L37=0,"",INDEX(Flux!$F$2:$F$35,$L37))</f>
+        <v/>
+      </c>
+      <c r="E37" s="43">
+        <f>IF($L37=0,"",INDEX(Flux!$G$2:$G$35,$L37))</f>
+        <v/>
+      </c>
+      <c r="F37" s="43">
+        <f>IF($L37=0,"",INDEX(Flux!$H$2:$H$35,$L37))</f>
+        <v/>
+      </c>
+      <c r="G37" s="43">
+        <f>IF($L37=0,"",INDEX(Flux!$I$2:$I$35,$L37))</f>
+        <v/>
+      </c>
+      <c r="H37" s="43">
+        <f>IF($L37=0,"",INDEX(Flux!$J$2:$J$35,$L37))</f>
+        <v/>
+      </c>
+      <c r="I37" s="43">
+        <f>IF($L37=0,"",INDEX(Flux!$K$2:$K$35,$L37))</f>
+        <v/>
+      </c>
+      <c r="J37" s="43">
+        <f>IF($L37=0,"",INDEX(Flux!$L$2:$L$35,$L37))</f>
+        <v/>
+      </c>
+      <c r="L37" s="39">
+        <f>IFERROR(MATCH(22,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M37" s="39">
+        <f>IF(L37=0,"",INDEX(Flux!$C$2:$C$35,L37))</f>
+        <v/>
+      </c>
+      <c r="N37" s="39">
+        <f>IF(L37&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" hidden="1" ht="22" customHeight="1">
+      <c r="B38" s="40">
+        <f>IF($L38=0,"",INDEX(Flux!$D$2:$D$35,$L38))</f>
+        <v/>
+      </c>
+      <c r="C38" s="41">
+        <f>IF($L38=0,"",INDEX(Flux!$E$2:$E$35,$L38))</f>
+        <v/>
+      </c>
+      <c r="D38" s="42">
+        <f>IF($L38=0,"",INDEX(Flux!$F$2:$F$35,$L38))</f>
+        <v/>
+      </c>
+      <c r="E38" s="43">
+        <f>IF($L38=0,"",INDEX(Flux!$G$2:$G$35,$L38))</f>
+        <v/>
+      </c>
+      <c r="F38" s="43">
+        <f>IF($L38=0,"",INDEX(Flux!$H$2:$H$35,$L38))</f>
+        <v/>
+      </c>
+      <c r="G38" s="43">
+        <f>IF($L38=0,"",INDEX(Flux!$I$2:$I$35,$L38))</f>
+        <v/>
+      </c>
+      <c r="H38" s="43">
+        <f>IF($L38=0,"",INDEX(Flux!$J$2:$J$35,$L38))</f>
+        <v/>
+      </c>
+      <c r="I38" s="43">
+        <f>IF($L38=0,"",INDEX(Flux!$K$2:$K$35,$L38))</f>
+        <v/>
+      </c>
+      <c r="J38" s="43">
+        <f>IF($L38=0,"",INDEX(Flux!$L$2:$L$35,$L38))</f>
+        <v/>
+      </c>
+      <c r="L38" s="39">
+        <f>IFERROR(MATCH(23,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M38" s="39">
+        <f>IF(L38=0,"",INDEX(Flux!$C$2:$C$35,L38))</f>
+        <v/>
+      </c>
+      <c r="N38" s="39">
+        <f>IF(L38&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" hidden="1" ht="22" customHeight="1">
+      <c r="B39" s="40">
+        <f>IF($L39=0,"",INDEX(Flux!$D$2:$D$35,$L39))</f>
+        <v/>
+      </c>
+      <c r="C39" s="41">
+        <f>IF($L39=0,"",INDEX(Flux!$E$2:$E$35,$L39))</f>
+        <v/>
+      </c>
+      <c r="D39" s="42">
+        <f>IF($L39=0,"",INDEX(Flux!$F$2:$F$35,$L39))</f>
+        <v/>
+      </c>
+      <c r="E39" s="43">
+        <f>IF($L39=0,"",INDEX(Flux!$G$2:$G$35,$L39))</f>
+        <v/>
+      </c>
+      <c r="F39" s="43">
+        <f>IF($L39=0,"",INDEX(Flux!$H$2:$H$35,$L39))</f>
+        <v/>
+      </c>
+      <c r="G39" s="43">
+        <f>IF($L39=0,"",INDEX(Flux!$I$2:$I$35,$L39))</f>
+        <v/>
+      </c>
+      <c r="H39" s="43">
+        <f>IF($L39=0,"",INDEX(Flux!$J$2:$J$35,$L39))</f>
+        <v/>
+      </c>
+      <c r="I39" s="43">
+        <f>IF($L39=0,"",INDEX(Flux!$K$2:$K$35,$L39))</f>
+        <v/>
+      </c>
+      <c r="J39" s="43">
+        <f>IF($L39=0,"",INDEX(Flux!$L$2:$L$35,$L39))</f>
+        <v/>
+      </c>
+      <c r="L39" s="39">
+        <f>IFERROR(MATCH(24,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M39" s="39">
+        <f>IF(L39=0,"",INDEX(Flux!$C$2:$C$35,L39))</f>
+        <v/>
+      </c>
+      <c r="N39" s="39">
+        <f>IF(L39&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" hidden="1" ht="22" customHeight="1">
+      <c r="B40" s="40">
+        <f>IF($L40=0,"",INDEX(Flux!$D$2:$D$35,$L40))</f>
+        <v/>
+      </c>
+      <c r="C40" s="41">
+        <f>IF($L40=0,"",INDEX(Flux!$E$2:$E$35,$L40))</f>
+        <v/>
+      </c>
+      <c r="D40" s="42">
+        <f>IF($L40=0,"",INDEX(Flux!$F$2:$F$35,$L40))</f>
+        <v/>
+      </c>
+      <c r="E40" s="43">
+        <f>IF($L40=0,"",INDEX(Flux!$G$2:$G$35,$L40))</f>
+        <v/>
+      </c>
+      <c r="F40" s="43">
+        <f>IF($L40=0,"",INDEX(Flux!$H$2:$H$35,$L40))</f>
+        <v/>
+      </c>
+      <c r="G40" s="43">
+        <f>IF($L40=0,"",INDEX(Flux!$I$2:$I$35,$L40))</f>
+        <v/>
+      </c>
+      <c r="H40" s="43">
+        <f>IF($L40=0,"",INDEX(Flux!$J$2:$J$35,$L40))</f>
+        <v/>
+      </c>
+      <c r="I40" s="43">
+        <f>IF($L40=0,"",INDEX(Flux!$K$2:$K$35,$L40))</f>
+        <v/>
+      </c>
+      <c r="J40" s="43">
+        <f>IF($L40=0,"",INDEX(Flux!$L$2:$L$35,$L40))</f>
+        <v/>
+      </c>
+      <c r="L40" s="39">
+        <f>IFERROR(MATCH(25,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M40" s="39">
+        <f>IF(L40=0,"",INDEX(Flux!$C$2:$C$35,L40))</f>
+        <v/>
+      </c>
+      <c r="N40" s="39">
+        <f>IF(L40&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" hidden="1" ht="22" customHeight="1">
+      <c r="B41" s="40">
+        <f>IF($L41=0,"",INDEX(Flux!$D$2:$D$35,$L41))</f>
+        <v/>
+      </c>
+      <c r="C41" s="41">
+        <f>IF($L41=0,"",INDEX(Flux!$E$2:$E$35,$L41))</f>
+        <v/>
+      </c>
+      <c r="D41" s="42">
+        <f>IF($L41=0,"",INDEX(Flux!$F$2:$F$35,$L41))</f>
+        <v/>
+      </c>
+      <c r="E41" s="43">
+        <f>IF($L41=0,"",INDEX(Flux!$G$2:$G$35,$L41))</f>
+        <v/>
+      </c>
+      <c r="F41" s="43">
+        <f>IF($L41=0,"",INDEX(Flux!$H$2:$H$35,$L41))</f>
+        <v/>
+      </c>
+      <c r="G41" s="43">
+        <f>IF($L41=0,"",INDEX(Flux!$I$2:$I$35,$L41))</f>
+        <v/>
+      </c>
+      <c r="H41" s="43">
+        <f>IF($L41=0,"",INDEX(Flux!$J$2:$J$35,$L41))</f>
+        <v/>
+      </c>
+      <c r="I41" s="43">
+        <f>IF($L41=0,"",INDEX(Flux!$K$2:$K$35,$L41))</f>
+        <v/>
+      </c>
+      <c r="J41" s="43">
+        <f>IF($L41=0,"",INDEX(Flux!$L$2:$L$35,$L41))</f>
+        <v/>
+      </c>
+      <c r="L41" s="39">
+        <f>IFERROR(MATCH(26,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M41" s="39">
+        <f>IF(L41=0,"",INDEX(Flux!$C$2:$C$35,L41))</f>
+        <v/>
+      </c>
+      <c r="N41" s="39">
+        <f>IF(L41&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" hidden="1" ht="22" customHeight="1">
+      <c r="B42" s="40">
+        <f>IF($L42=0,"",INDEX(Flux!$D$2:$D$35,$L42))</f>
+        <v/>
+      </c>
+      <c r="C42" s="41">
+        <f>IF($L42=0,"",INDEX(Flux!$E$2:$E$35,$L42))</f>
+        <v/>
+      </c>
+      <c r="D42" s="42">
+        <f>IF($L42=0,"",INDEX(Flux!$F$2:$F$35,$L42))</f>
+        <v/>
+      </c>
+      <c r="E42" s="43">
+        <f>IF($L42=0,"",INDEX(Flux!$G$2:$G$35,$L42))</f>
+        <v/>
+      </c>
+      <c r="F42" s="43">
+        <f>IF($L42=0,"",INDEX(Flux!$H$2:$H$35,$L42))</f>
+        <v/>
+      </c>
+      <c r="G42" s="43">
+        <f>IF($L42=0,"",INDEX(Flux!$I$2:$I$35,$L42))</f>
+        <v/>
+      </c>
+      <c r="H42" s="43">
+        <f>IF($L42=0,"",INDEX(Flux!$J$2:$J$35,$L42))</f>
+        <v/>
+      </c>
+      <c r="I42" s="43">
+        <f>IF($L42=0,"",INDEX(Flux!$K$2:$K$35,$L42))</f>
+        <v/>
+      </c>
+      <c r="J42" s="43">
+        <f>IF($L42=0,"",INDEX(Flux!$L$2:$L$35,$L42))</f>
+        <v/>
+      </c>
+      <c r="L42" s="39">
+        <f>IFERROR(MATCH(27,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M42" s="39">
+        <f>IF(L42=0,"",INDEX(Flux!$C$2:$C$35,L42))</f>
+        <v/>
+      </c>
+      <c r="N42" s="39">
+        <f>IF(L42&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" hidden="1" ht="22" customHeight="1">
+      <c r="B43" s="40">
+        <f>IF($L43=0,"",INDEX(Flux!$D$2:$D$35,$L43))</f>
+        <v/>
+      </c>
+      <c r="C43" s="41">
+        <f>IF($L43=0,"",INDEX(Flux!$E$2:$E$35,$L43))</f>
+        <v/>
+      </c>
+      <c r="D43" s="42">
+        <f>IF($L43=0,"",INDEX(Flux!$F$2:$F$35,$L43))</f>
+        <v/>
+      </c>
+      <c r="E43" s="43">
+        <f>IF($L43=0,"",INDEX(Flux!$G$2:$G$35,$L43))</f>
+        <v/>
+      </c>
+      <c r="F43" s="43">
+        <f>IF($L43=0,"",INDEX(Flux!$H$2:$H$35,$L43))</f>
+        <v/>
+      </c>
+      <c r="G43" s="43">
+        <f>IF($L43=0,"",INDEX(Flux!$I$2:$I$35,$L43))</f>
+        <v/>
+      </c>
+      <c r="H43" s="43">
+        <f>IF($L43=0,"",INDEX(Flux!$J$2:$J$35,$L43))</f>
+        <v/>
+      </c>
+      <c r="I43" s="43">
+        <f>IF($L43=0,"",INDEX(Flux!$K$2:$K$35,$L43))</f>
+        <v/>
+      </c>
+      <c r="J43" s="43">
+        <f>IF($L43=0,"",INDEX(Flux!$L$2:$L$35,$L43))</f>
+        <v/>
+      </c>
+      <c r="L43" s="39">
+        <f>IFERROR(MATCH(28,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M43" s="39">
+        <f>IF(L43=0,"",INDEX(Flux!$C$2:$C$35,L43))</f>
+        <v/>
+      </c>
+      <c r="N43" s="39">
+        <f>IF(L43&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" hidden="1" ht="22" customHeight="1">
+      <c r="B44" s="40">
+        <f>IF($L44=0,"",INDEX(Flux!$D$2:$D$35,$L44))</f>
+        <v/>
+      </c>
+      <c r="C44" s="41">
+        <f>IF($L44=0,"",INDEX(Flux!$E$2:$E$35,$L44))</f>
+        <v/>
+      </c>
+      <c r="D44" s="42">
+        <f>IF($L44=0,"",INDEX(Flux!$F$2:$F$35,$L44))</f>
+        <v/>
+      </c>
+      <c r="E44" s="43">
+        <f>IF($L44=0,"",INDEX(Flux!$G$2:$G$35,$L44))</f>
+        <v/>
+      </c>
+      <c r="F44" s="43">
+        <f>IF($L44=0,"",INDEX(Flux!$H$2:$H$35,$L44))</f>
+        <v/>
+      </c>
+      <c r="G44" s="43">
+        <f>IF($L44=0,"",INDEX(Flux!$I$2:$I$35,$L44))</f>
+        <v/>
+      </c>
+      <c r="H44" s="43">
+        <f>IF($L44=0,"",INDEX(Flux!$J$2:$J$35,$L44))</f>
+        <v/>
+      </c>
+      <c r="I44" s="43">
+        <f>IF($L44=0,"",INDEX(Flux!$K$2:$K$35,$L44))</f>
+        <v/>
+      </c>
+      <c r="J44" s="43">
+        <f>IF($L44=0,"",INDEX(Flux!$L$2:$L$35,$L44))</f>
+        <v/>
+      </c>
+      <c r="L44" s="39">
+        <f>IFERROR(MATCH(29,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M44" s="39">
+        <f>IF(L44=0,"",INDEX(Flux!$C$2:$C$35,L44))</f>
+        <v/>
+      </c>
+      <c r="N44" s="39">
+        <f>IF(L44&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" hidden="1" ht="22" customHeight="1">
+      <c r="B45" s="40">
+        <f>IF($L45=0,"",INDEX(Flux!$D$2:$D$35,$L45))</f>
+        <v/>
+      </c>
+      <c r="C45" s="41">
+        <f>IF($L45=0,"",INDEX(Flux!$E$2:$E$35,$L45))</f>
+        <v/>
+      </c>
+      <c r="D45" s="42">
+        <f>IF($L45=0,"",INDEX(Flux!$F$2:$F$35,$L45))</f>
+        <v/>
+      </c>
+      <c r="E45" s="43">
+        <f>IF($L45=0,"",INDEX(Flux!$G$2:$G$35,$L45))</f>
+        <v/>
+      </c>
+      <c r="F45" s="43">
+        <f>IF($L45=0,"",INDEX(Flux!$H$2:$H$35,$L45))</f>
+        <v/>
+      </c>
+      <c r="G45" s="43">
+        <f>IF($L45=0,"",INDEX(Flux!$I$2:$I$35,$L45))</f>
+        <v/>
+      </c>
+      <c r="H45" s="43">
+        <f>IF($L45=0,"",INDEX(Flux!$J$2:$J$35,$L45))</f>
+        <v/>
+      </c>
+      <c r="I45" s="43">
+        <f>IF($L45=0,"",INDEX(Flux!$K$2:$K$35,$L45))</f>
+        <v/>
+      </c>
+      <c r="J45" s="43">
+        <f>IF($L45=0,"",INDEX(Flux!$L$2:$L$35,$L45))</f>
+        <v/>
+      </c>
+      <c r="L45" s="39">
+        <f>IFERROR(MATCH(30,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M45" s="39">
+        <f>IF(L45=0,"",INDEX(Flux!$C$2:$C$35,L45))</f>
+        <v/>
+      </c>
+      <c r="N45" s="39">
+        <f>IF(L45&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" hidden="1" ht="22" customHeight="1">
+      <c r="B46" s="40">
+        <f>IF($L46=0,"",INDEX(Flux!$D$2:$D$35,$L46))</f>
+        <v/>
+      </c>
+      <c r="C46" s="41">
+        <f>IF($L46=0,"",INDEX(Flux!$E$2:$E$35,$L46))</f>
+        <v/>
+      </c>
+      <c r="D46" s="42">
+        <f>IF($L46=0,"",INDEX(Flux!$F$2:$F$35,$L46))</f>
+        <v/>
+      </c>
+      <c r="E46" s="43">
+        <f>IF($L46=0,"",INDEX(Flux!$G$2:$G$35,$L46))</f>
+        <v/>
+      </c>
+      <c r="F46" s="43">
+        <f>IF($L46=0,"",INDEX(Flux!$H$2:$H$35,$L46))</f>
+        <v/>
+      </c>
+      <c r="G46" s="43">
+        <f>IF($L46=0,"",INDEX(Flux!$I$2:$I$35,$L46))</f>
+        <v/>
+      </c>
+      <c r="H46" s="43">
+        <f>IF($L46=0,"",INDEX(Flux!$J$2:$J$35,$L46))</f>
+        <v/>
+      </c>
+      <c r="I46" s="43">
+        <f>IF($L46=0,"",INDEX(Flux!$K$2:$K$35,$L46))</f>
+        <v/>
+      </c>
+      <c r="J46" s="43">
+        <f>IF($L46=0,"",INDEX(Flux!$L$2:$L$35,$L46))</f>
+        <v/>
+      </c>
+      <c r="L46" s="39">
+        <f>IFERROR(MATCH(31,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M46" s="39">
+        <f>IF(L46=0,"",INDEX(Flux!$C$2:$C$35,L46))</f>
+        <v/>
+      </c>
+      <c r="N46" s="39">
+        <f>IF(L46&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" hidden="1" ht="22" customHeight="1">
+      <c r="B47" s="40">
+        <f>IF($L47=0,"",INDEX(Flux!$D$2:$D$35,$L47))</f>
+        <v/>
+      </c>
+      <c r="C47" s="41">
+        <f>IF($L47=0,"",INDEX(Flux!$E$2:$E$35,$L47))</f>
+        <v/>
+      </c>
+      <c r="D47" s="42">
+        <f>IF($L47=0,"",INDEX(Flux!$F$2:$F$35,$L47))</f>
+        <v/>
+      </c>
+      <c r="E47" s="43">
+        <f>IF($L47=0,"",INDEX(Flux!$G$2:$G$35,$L47))</f>
+        <v/>
+      </c>
+      <c r="F47" s="43">
+        <f>IF($L47=0,"",INDEX(Flux!$H$2:$H$35,$L47))</f>
+        <v/>
+      </c>
+      <c r="G47" s="43">
+        <f>IF($L47=0,"",INDEX(Flux!$I$2:$I$35,$L47))</f>
+        <v/>
+      </c>
+      <c r="H47" s="43">
+        <f>IF($L47=0,"",INDEX(Flux!$J$2:$J$35,$L47))</f>
+        <v/>
+      </c>
+      <c r="I47" s="43">
+        <f>IF($L47=0,"",INDEX(Flux!$K$2:$K$35,$L47))</f>
+        <v/>
+      </c>
+      <c r="J47" s="43">
+        <f>IF($L47=0,"",INDEX(Flux!$L$2:$L$35,$L47))</f>
+        <v/>
+      </c>
+      <c r="L47" s="39">
+        <f>IFERROR(MATCH(32,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M47" s="39">
+        <f>IF(L47=0,"",INDEX(Flux!$C$2:$C$35,L47))</f>
+        <v/>
+      </c>
+      <c r="N47" s="39">
+        <f>IF(L47&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" hidden="1" ht="22" customHeight="1">
+      <c r="B48" s="40">
+        <f>IF($L48=0,"",INDEX(Flux!$D$2:$D$35,$L48))</f>
+        <v/>
+      </c>
+      <c r="C48" s="41">
+        <f>IF($L48=0,"",INDEX(Flux!$E$2:$E$35,$L48))</f>
+        <v/>
+      </c>
+      <c r="D48" s="42">
+        <f>IF($L48=0,"",INDEX(Flux!$F$2:$F$35,$L48))</f>
+        <v/>
+      </c>
+      <c r="E48" s="43">
+        <f>IF($L48=0,"",INDEX(Flux!$G$2:$G$35,$L48))</f>
+        <v/>
+      </c>
+      <c r="F48" s="43">
+        <f>IF($L48=0,"",INDEX(Flux!$H$2:$H$35,$L48))</f>
+        <v/>
+      </c>
+      <c r="G48" s="43">
+        <f>IF($L48=0,"",INDEX(Flux!$I$2:$I$35,$L48))</f>
+        <v/>
+      </c>
+      <c r="H48" s="43">
+        <f>IF($L48=0,"",INDEX(Flux!$J$2:$J$35,$L48))</f>
+        <v/>
+      </c>
+      <c r="I48" s="43">
+        <f>IF($L48=0,"",INDEX(Flux!$K$2:$K$35,$L48))</f>
+        <v/>
+      </c>
+      <c r="J48" s="43">
+        <f>IF($L48=0,"",INDEX(Flux!$L$2:$L$35,$L48))</f>
+        <v/>
+      </c>
+      <c r="L48" s="39">
+        <f>IFERROR(MATCH(33,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M48" s="39">
+        <f>IF(L48=0,"",INDEX(Flux!$C$2:$C$35,L48))</f>
+        <v/>
+      </c>
+      <c r="N48" s="39">
+        <f>IF(L48&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" hidden="1" ht="22" customHeight="1">
+      <c r="B49" s="40">
+        <f>IF($L49=0,"",INDEX(Flux!$D$2:$D$35,$L49))</f>
+        <v/>
+      </c>
+      <c r="C49" s="41">
+        <f>IF($L49=0,"",INDEX(Flux!$E$2:$E$35,$L49))</f>
+        <v/>
+      </c>
+      <c r="D49" s="42">
+        <f>IF($L49=0,"",INDEX(Flux!$F$2:$F$35,$L49))</f>
+        <v/>
+      </c>
+      <c r="E49" s="43">
+        <f>IF($L49=0,"",INDEX(Flux!$G$2:$G$35,$L49))</f>
+        <v/>
+      </c>
+      <c r="F49" s="43">
+        <f>IF($L49=0,"",INDEX(Flux!$H$2:$H$35,$L49))</f>
+        <v/>
+      </c>
+      <c r="G49" s="43">
+        <f>IF($L49=0,"",INDEX(Flux!$I$2:$I$35,$L49))</f>
+        <v/>
+      </c>
+      <c r="H49" s="43">
+        <f>IF($L49=0,"",INDEX(Flux!$J$2:$J$35,$L49))</f>
+        <v/>
+      </c>
+      <c r="I49" s="43">
+        <f>IF($L49=0,"",INDEX(Flux!$K$2:$K$35,$L49))</f>
+        <v/>
+      </c>
+      <c r="J49" s="43">
+        <f>IF($L49=0,"",INDEX(Flux!$L$2:$L$35,$L49))</f>
+        <v/>
+      </c>
+      <c r="L49" s="39">
+        <f>IFERROR(MATCH(34,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M49" s="39">
+        <f>IF(L49=0,"",INDEX(Flux!$C$2:$C$35,L49))</f>
+        <v/>
+      </c>
+      <c r="N49" s="39">
+        <f>IF(L49&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" hidden="1" ht="22" customHeight="1">
+      <c r="B50" s="40">
+        <f>IF($L50=0,"",INDEX(Flux!$D$2:$D$35,$L50))</f>
+        <v/>
+      </c>
+      <c r="C50" s="41">
+        <f>IF($L50=0,"",INDEX(Flux!$E$2:$E$35,$L50))</f>
+        <v/>
+      </c>
+      <c r="D50" s="42">
+        <f>IF($L50=0,"",INDEX(Flux!$F$2:$F$35,$L50))</f>
+        <v/>
+      </c>
+      <c r="E50" s="43">
+        <f>IF($L50=0,"",INDEX(Flux!$G$2:$G$35,$L50))</f>
+        <v/>
+      </c>
+      <c r="F50" s="43">
+        <f>IF($L50=0,"",INDEX(Flux!$H$2:$H$35,$L50))</f>
+        <v/>
+      </c>
+      <c r="G50" s="43">
+        <f>IF($L50=0,"",INDEX(Flux!$I$2:$I$35,$L50))</f>
+        <v/>
+      </c>
+      <c r="H50" s="43">
+        <f>IF($L50=0,"",INDEX(Flux!$J$2:$J$35,$L50))</f>
+        <v/>
+      </c>
+      <c r="I50" s="43">
+        <f>IF($L50=0,"",INDEX(Flux!$K$2:$K$35,$L50))</f>
+        <v/>
+      </c>
+      <c r="J50" s="43">
+        <f>IF($L50=0,"",INDEX(Flux!$L$2:$L$35,$L50))</f>
+        <v/>
+      </c>
+      <c r="L50" s="39">
+        <f>IFERROR(MATCH(35,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M50" s="39">
+        <f>IF(L50=0,"",INDEX(Flux!$C$2:$C$35,L50))</f>
+        <v/>
+      </c>
+      <c r="N50" s="39">
+        <f>IF(L50&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" hidden="1" ht="22" customHeight="1">
+      <c r="B51" s="40">
+        <f>IF($L51=0,"",INDEX(Flux!$D$2:$D$35,$L51))</f>
+        <v/>
+      </c>
+      <c r="C51" s="41">
+        <f>IF($L51=0,"",INDEX(Flux!$E$2:$E$35,$L51))</f>
+        <v/>
+      </c>
+      <c r="D51" s="42">
+        <f>IF($L51=0,"",INDEX(Flux!$F$2:$F$35,$L51))</f>
+        <v/>
+      </c>
+      <c r="E51" s="43">
+        <f>IF($L51=0,"",INDEX(Flux!$G$2:$G$35,$L51))</f>
+        <v/>
+      </c>
+      <c r="F51" s="43">
+        <f>IF($L51=0,"",INDEX(Flux!$H$2:$H$35,$L51))</f>
+        <v/>
+      </c>
+      <c r="G51" s="43">
+        <f>IF($L51=0,"",INDEX(Flux!$I$2:$I$35,$L51))</f>
+        <v/>
+      </c>
+      <c r="H51" s="43">
+        <f>IF($L51=0,"",INDEX(Flux!$J$2:$J$35,$L51))</f>
+        <v/>
+      </c>
+      <c r="I51" s="43">
+        <f>IF($L51=0,"",INDEX(Flux!$K$2:$K$35,$L51))</f>
+        <v/>
+      </c>
+      <c r="J51" s="43">
+        <f>IF($L51=0,"",INDEX(Flux!$L$2:$L$35,$L51))</f>
+        <v/>
+      </c>
+      <c r="L51" s="39">
+        <f>IFERROR(MATCH(36,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M51" s="39">
+        <f>IF(L51=0,"",INDEX(Flux!$C$2:$C$35,L51))</f>
+        <v/>
+      </c>
+      <c r="N51" s="39">
+        <f>IF(L51&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" hidden="1" ht="22" customHeight="1">
+      <c r="B52" s="40">
+        <f>IF($L52=0,"",INDEX(Flux!$D$2:$D$35,$L52))</f>
+        <v/>
+      </c>
+      <c r="C52" s="41">
+        <f>IF($L52=0,"",INDEX(Flux!$E$2:$E$35,$L52))</f>
+        <v/>
+      </c>
+      <c r="D52" s="42">
+        <f>IF($L52=0,"",INDEX(Flux!$F$2:$F$35,$L52))</f>
+        <v/>
+      </c>
+      <c r="E52" s="43">
+        <f>IF($L52=0,"",INDEX(Flux!$G$2:$G$35,$L52))</f>
+        <v/>
+      </c>
+      <c r="F52" s="43">
+        <f>IF($L52=0,"",INDEX(Flux!$H$2:$H$35,$L52))</f>
+        <v/>
+      </c>
+      <c r="G52" s="43">
+        <f>IF($L52=0,"",INDEX(Flux!$I$2:$I$35,$L52))</f>
+        <v/>
+      </c>
+      <c r="H52" s="43">
+        <f>IF($L52=0,"",INDEX(Flux!$J$2:$J$35,$L52))</f>
+        <v/>
+      </c>
+      <c r="I52" s="43">
+        <f>IF($L52=0,"",INDEX(Flux!$K$2:$K$35,$L52))</f>
+        <v/>
+      </c>
+      <c r="J52" s="43">
+        <f>IF($L52=0,"",INDEX(Flux!$L$2:$L$35,$L52))</f>
+        <v/>
+      </c>
+      <c r="L52" s="39">
+        <f>IFERROR(MATCH(37,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M52" s="39">
+        <f>IF(L52=0,"",INDEX(Flux!$C$2:$C$35,L52))</f>
+        <v/>
+      </c>
+      <c r="N52" s="39">
+        <f>IF(L52&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" hidden="1" ht="22" customHeight="1">
+      <c r="B53" s="40">
+        <f>IF($L53=0,"",INDEX(Flux!$D$2:$D$35,$L53))</f>
+        <v/>
+      </c>
+      <c r="C53" s="41">
+        <f>IF($L53=0,"",INDEX(Flux!$E$2:$E$35,$L53))</f>
+        <v/>
+      </c>
+      <c r="D53" s="42">
+        <f>IF($L53=0,"",INDEX(Flux!$F$2:$F$35,$L53))</f>
+        <v/>
+      </c>
+      <c r="E53" s="43">
+        <f>IF($L53=0,"",INDEX(Flux!$G$2:$G$35,$L53))</f>
+        <v/>
+      </c>
+      <c r="F53" s="43">
+        <f>IF($L53=0,"",INDEX(Flux!$H$2:$H$35,$L53))</f>
+        <v/>
+      </c>
+      <c r="G53" s="43">
+        <f>IF($L53=0,"",INDEX(Flux!$I$2:$I$35,$L53))</f>
+        <v/>
+      </c>
+      <c r="H53" s="43">
+        <f>IF($L53=0,"",INDEX(Flux!$J$2:$J$35,$L53))</f>
+        <v/>
+      </c>
+      <c r="I53" s="43">
+        <f>IF($L53=0,"",INDEX(Flux!$K$2:$K$35,$L53))</f>
+        <v/>
+      </c>
+      <c r="J53" s="43">
+        <f>IF($L53=0,"",INDEX(Flux!$L$2:$L$35,$L53))</f>
+        <v/>
+      </c>
+      <c r="L53" s="39">
+        <f>IFERROR(MATCH(38,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M53" s="39">
+        <f>IF(L53=0,"",INDEX(Flux!$C$2:$C$35,L53))</f>
+        <v/>
+      </c>
+      <c r="N53" s="39">
+        <f>IF(L53&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" hidden="1" ht="22" customHeight="1">
+      <c r="B54" s="40">
+        <f>IF($L54=0,"",INDEX(Flux!$D$2:$D$35,$L54))</f>
+        <v/>
+      </c>
+      <c r="C54" s="41">
+        <f>IF($L54=0,"",INDEX(Flux!$E$2:$E$35,$L54))</f>
+        <v/>
+      </c>
+      <c r="D54" s="42">
+        <f>IF($L54=0,"",INDEX(Flux!$F$2:$F$35,$L54))</f>
+        <v/>
+      </c>
+      <c r="E54" s="43">
+        <f>IF($L54=0,"",INDEX(Flux!$G$2:$G$35,$L54))</f>
+        <v/>
+      </c>
+      <c r="F54" s="43">
+        <f>IF($L54=0,"",INDEX(Flux!$H$2:$H$35,$L54))</f>
+        <v/>
+      </c>
+      <c r="G54" s="43">
+        <f>IF($L54=0,"",INDEX(Flux!$I$2:$I$35,$L54))</f>
+        <v/>
+      </c>
+      <c r="H54" s="43">
+        <f>IF($L54=0,"",INDEX(Flux!$J$2:$J$35,$L54))</f>
+        <v/>
+      </c>
+      <c r="I54" s="43">
+        <f>IF($L54=0,"",INDEX(Flux!$K$2:$K$35,$L54))</f>
+        <v/>
+      </c>
+      <c r="J54" s="43">
+        <f>IF($L54=0,"",INDEX(Flux!$L$2:$L$35,$L54))</f>
+        <v/>
+      </c>
+      <c r="L54" s="39">
+        <f>IFERROR(MATCH(39,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M54" s="39">
+        <f>IF(L54=0,"",INDEX(Flux!$C$2:$C$35,L54))</f>
+        <v/>
+      </c>
+      <c r="N54" s="39">
+        <f>IF(L54&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" hidden="1" ht="22" customHeight="1">
+      <c r="B55" s="40">
+        <f>IF($L55=0,"",INDEX(Flux!$D$2:$D$35,$L55))</f>
+        <v/>
+      </c>
+      <c r="C55" s="41">
+        <f>IF($L55=0,"",INDEX(Flux!$E$2:$E$35,$L55))</f>
+        <v/>
+      </c>
+      <c r="D55" s="42">
+        <f>IF($L55=0,"",INDEX(Flux!$F$2:$F$35,$L55))</f>
+        <v/>
+      </c>
+      <c r="E55" s="43">
+        <f>IF($L55=0,"",INDEX(Flux!$G$2:$G$35,$L55))</f>
+        <v/>
+      </c>
+      <c r="F55" s="43">
+        <f>IF($L55=0,"",INDEX(Flux!$H$2:$H$35,$L55))</f>
+        <v/>
+      </c>
+      <c r="G55" s="43">
+        <f>IF($L55=0,"",INDEX(Flux!$I$2:$I$35,$L55))</f>
+        <v/>
+      </c>
+      <c r="H55" s="43">
+        <f>IF($L55=0,"",INDEX(Flux!$J$2:$J$35,$L55))</f>
+        <v/>
+      </c>
+      <c r="I55" s="43">
+        <f>IF($L55=0,"",INDEX(Flux!$K$2:$K$35,$L55))</f>
+        <v/>
+      </c>
+      <c r="J55" s="43">
+        <f>IF($L55=0,"",INDEX(Flux!$L$2:$L$35,$L55))</f>
+        <v/>
+      </c>
+      <c r="L55" s="39">
+        <f>IFERROR(MATCH(40,Flux!$B$2:$B$35,0),0)</f>
+        <v/>
+      </c>
+      <c r="M55" s="39">
+        <f>IF(L55=0,"",INDEX(Flux!$C$2:$C$35,L55))</f>
+        <v/>
+      </c>
+      <c r="N55" s="39">
+        <f>IF(L55&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1"/>
+    <row r="57" ht="22" customHeight="1"/>
     <row r="58" ht="20" customHeight="1">
-      <c r="B58" s="34">
+      <c r="B58" s="35">
         <f>INDEX(Textes!$B$2:$C$59,MATCH("sec_cond",Textes!$A$2:$A$59,0),Listes!$H$1)</f>
         <v/>
       </c>
-      <c r="C58" s="35" t="n"/>
-      <c r="D58" s="35" t="n"/>
-      <c r="E58" s="35" t="n"/>
-      <c r="F58" s="35" t="n"/>
-      <c r="G58" s="35" t="n"/>
-      <c r="H58" s="35" t="n"/>
-      <c r="I58" s="35" t="n"/>
-      <c r="J58" s="35" t="n"/>
-    </row>
-    <row r="59" ht="92" customHeight="1">
+      <c r="C58" s="36" t="n"/>
+      <c r="D58" s="36" t="n"/>
+      <c r="E58" s="36" t="n"/>
+      <c r="F58" s="36" t="n"/>
+      <c r="G58" s="36" t="n"/>
+      <c r="H58" s="36" t="n"/>
+      <c r="I58" s="36" t="n"/>
+      <c r="J58" s="36" t="n"/>
+    </row>
+    <row r="59" ht="80" customHeight="1">
       <c r="B59" s="44" t="inlineStr">
         <is>
           <t>La location s'entend depuis le jour de départ de la base d'origine jusqu'à son retour au même endroit.
@@ -4581,7 +4757,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="92" customHeight="1">
+    <row r="60" ht="80" customHeight="1">
       <c r="B60" s="44" t="inlineStr">
         <is>
           <t>The rental is from the day of departure from the base of origin until its return to the same place.
@@ -4660,6 +4836,25 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="B15:N55">
+    <filterColumn colId="0" hiddenButton="1" showButton="0"/>
+    <filterColumn colId="1" hiddenButton="1" showButton="0"/>
+    <filterColumn colId="2" hiddenButton="1" showButton="0"/>
+    <filterColumn colId="3" hiddenButton="1" showButton="0"/>
+    <filterColumn colId="4" hiddenButton="1" showButton="0"/>
+    <filterColumn colId="5" hiddenButton="1" showButton="0"/>
+    <filterColumn colId="6" hiddenButton="1" showButton="0"/>
+    <filterColumn colId="7" hiddenButton="1" showButton="0"/>
+    <filterColumn colId="8" hiddenButton="1" showButton="0"/>
+    <filterColumn colId="9" hiddenButton="1" showButton="0"/>
+    <filterColumn colId="10" hiddenButton="1" showButton="0">
+      <customFilters>
+        <customFilter val="0" operator="greaterThan"/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="11" hiddenButton="1" showButton="0"/>
+    <filterColumn colId="12" hiddenButton="1" showButton="0"/>
+  </autoFilter>
   <mergeCells count="36">
     <mergeCell ref="D9:G9"/>
     <mergeCell ref="B7:C7"/>
@@ -4668,6 +4863,7 @@
     <mergeCell ref="B14:J14"/>
     <mergeCell ref="B60:J60"/>
     <mergeCell ref="D5:G5"/>
+    <mergeCell ref="B13:J13"/>
     <mergeCell ref="H11:J11"/>
     <mergeCell ref="H7:J7"/>
     <mergeCell ref="B12:C12"/>
@@ -4692,7 +4888,6 @@
     <mergeCell ref="B59:J59"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="D7:G7"/>
-    <mergeCell ref="B56:J56"/>
     <mergeCell ref="H9:J9"/>
     <mergeCell ref="B58:J58"/>
     <mergeCell ref="D63:G66"/>
@@ -4731,9 +4926,6 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="56" min="0" max="16383" man="1"/>
-  </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -6098,7 +6290,7 @@
       </c>
       <c r="B54" s="59" t="inlineStr">
         <is>
-          <t>serrage inclus</t>
+          <t>serrage compris</t>
         </is>
       </c>
       <c r="C54" s="59" t="inlineStr">
@@ -6115,7 +6307,7 @@
       </c>
       <c r="B55" s="59" t="inlineStr">
         <is>
-          <t>transport inclus</t>
+          <t>transport compris</t>
         </is>
       </c>
       <c r="C55" s="59" t="inlineStr">
@@ -6132,7 +6324,7 @@
       </c>
       <c r="B56" s="59" t="inlineStr">
         <is>
-          <t>serrage et transport inclus</t>
+          <t>serrage et transport compris</t>
         </is>
       </c>
       <c r="C56" s="59" t="inlineStr">
@@ -7887,7 +8079,7 @@
         <v/>
       </c>
       <c r="E34">
-        <f>UPPER(INDEX(Textes!$B$2:$C$59,MATCH("forfait",Textes!$A$2:$A$59,0),Listes!$H$1))&amp;IF(IF('3 Options'!$G$13="Forfait calculé (S + O + UC)",'3 Options'!$C$15+'3 Options'!$C$16,IF('3 Options'!$G$13="Forfait par jour",'3 Options'!$E$13,""))&lt;&gt;"","  "&amp;IF('3 Options'!$G$13="Forfait calculé (S + O + UC)",'3 Options'!$C$15+'3 Options'!$C$16,IF('3 Options'!$G$13="Forfait par jour",'3 Options'!$E$13,""))&amp;" "&amp;INDEX(Textes!$B$2:$C$59,MATCH("days",Textes!$A$2:$A$59,0),Listes!$H$1),"")&amp;IF('3 Options'!$D$13&lt;&gt;"","   ·   "&amp;'3 Options'!$D$13,"")</f>
+        <f>UPPER(INDEX(Textes!$B$2:$C$59,MATCH("forfait",Textes!$A$2:$A$59,0),Listes!$H$1))&amp;IF(IF('3 Options'!$G$13="Forfait calculé (S + O + UC)",'3 Options'!$C$15+'3 Options'!$C$16,IF('3 Options'!$G$13="Forfait par jour",'3 Options'!$E$13,""))&lt;&gt;"","  "&amp;IF('3 Options'!$G$13="Forfait calculé (S + O + UC)",'3 Options'!$C$15+'3 Options'!$C$16,IF('3 Options'!$G$13="Forfait par jour",'3 Options'!$E$13,""))&amp;" "&amp;INDEX(Textes!$B$2:$C$59,MATCH("days",Textes!$A$2:$A$59,0),Listes!$H$1),"")&amp;IF(IF(AND(AND('3 Options'!$C$8="Oui",'3 Options'!$C$19="Oui"),AND(OR('3 Options'!$C$9="Oui",'3 Options'!$C$10="Oui"),'3 Options'!$C$20="Oui")),INDEX(Textes!$B$2:$C$59,MATCH("in_both",Textes!$A$2:$A$59,0),Listes!$H$1),IF(AND('3 Options'!$C$8="Oui",'3 Options'!$C$19="Oui"),INDEX(Textes!$B$2:$C$59,MATCH("in_tight",Textes!$A$2:$A$59,0),Listes!$H$1),IF(AND(OR('3 Options'!$C$9="Oui",'3 Options'!$C$10="Oui"),'3 Options'!$C$20="Oui"),INDEX(Textes!$B$2:$C$59,MATCH("in_tr",Textes!$A$2:$A$59,0),Listes!$H$1),"")))&lt;&gt;"","   ·   "&amp;IF(AND(AND('3 Options'!$C$8="Oui",'3 Options'!$C$19="Oui"),AND(OR('3 Options'!$C$9="Oui",'3 Options'!$C$10="Oui"),'3 Options'!$C$20="Oui")),INDEX(Textes!$B$2:$C$59,MATCH("in_both",Textes!$A$2:$A$59,0),Listes!$H$1),IF(AND('3 Options'!$C$8="Oui",'3 Options'!$C$19="Oui"),INDEX(Textes!$B$2:$C$59,MATCH("in_tight",Textes!$A$2:$A$59,0),Listes!$H$1),IF(AND(OR('3 Options'!$C$9="Oui",'3 Options'!$C$10="Oui"),'3 Options'!$C$20="Oui"),INDEX(Textes!$B$2:$C$59,MATCH("in_tr",Textes!$A$2:$A$59,0),Listes!$H$1),""))),"")&amp;IF('3 Options'!$D$13&lt;&gt;"","   ·   "&amp;'3 Options'!$D$13,"")</f>
         <v/>
       </c>
       <c r="F34">
@@ -7937,7 +8129,7 @@
         <v/>
       </c>
       <c r="E35">
-        <f>IF(AND(AND('3 Options'!$C$8="Oui",'3 Options'!$C$19="Oui"),AND(OR('3 Options'!$C$9="Oui",'3 Options'!$C$10="Oui"),'3 Options'!$C$20="Oui")),INDEX(Textes!$B$2:$C$59,MATCH("in_both",Textes!$A$2:$A$59,0),Listes!$H$1),IF(AND('3 Options'!$C$8="Oui",'3 Options'!$C$19="Oui"),INDEX(Textes!$B$2:$C$59,MATCH("in_tight",Textes!$A$2:$A$59,0),Listes!$H$1),IF(AND(OR('3 Options'!$C$9="Oui",'3 Options'!$C$10="Oui"),'3 Options'!$C$20="Oui"),INDEX(Textes!$B$2:$C$59,MATCH("in_tr",Textes!$A$2:$A$59,0),Listes!$H$1),"")))&amp;IF(AND(IF(AND(AND('3 Options'!$C$8="Oui",'3 Options'!$C$19="Oui"),AND(OR('3 Options'!$C$9="Oui",'3 Options'!$C$10="Oui"),'3 Options'!$C$20="Oui")),INDEX(Textes!$B$2:$C$59,MATCH("in_both",Textes!$A$2:$A$59,0),Listes!$H$1),IF(AND('3 Options'!$C$8="Oui",'3 Options'!$C$19="Oui"),INDEX(Textes!$B$2:$C$59,MATCH("in_tight",Textes!$A$2:$A$59,0),Listes!$H$1),IF(AND(OR('3 Options'!$C$9="Oui",'3 Options'!$C$10="Oui"),'3 Options'!$C$20="Oui"),INDEX(Textes!$B$2:$C$59,MATCH("in_tr",Textes!$A$2:$A$59,0),Listes!$H$1),"")))&lt;&gt;"",'3 Options'!$D$14&lt;&gt;""),"   ·   ","")&amp;'3 Options'!$D$14</f>
+        <f>'3 Options'!$D$14</f>
         <v/>
       </c>
       <c r="F35">
